--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C4C421-8D7C-46BA-A90C-E933B80A7019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BBFB59-D781-490E-A3DD-A1275B1C12BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="733" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="235">
   <si>
     <t>SUBSECRETARÍA DE EDUCACIÓN</t>
   </si>
@@ -862,6 +862,9 @@
     <t>CDC: Estudiantes OAP que postulan a 
 través del SAE</t>
   </si>
+  <si>
+    <t>OCTUBRE-2025</t>
+  </si>
 </sst>
 </file>
 
@@ -871,7 +874,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="91">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1517,8 +1520,16 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFF4EE00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1623,30 +1634,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF008080"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1661,6 +1648,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor theme="7"/>
       </patternFill>
     </fill>
   </fills>
@@ -4978,7 +4971,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="705">
+  <cellXfs count="706">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5524,9 +5517,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="186" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5542,9 +5532,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="157" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5557,10 +5544,10 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5664,16 +5651,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="209" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="80" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="212" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="213" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5700,7 +5678,7 @@
     <xf numFmtId="0" fontId="76" fillId="0" borderId="223" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="23" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="19" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0" applyBorder="1"/>
@@ -5887,22 +5865,22 @@
     <xf numFmtId="49" fontId="20" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="24" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5998,6 +5976,42 @@
     <xf numFmtId="0" fontId="88" fillId="0" borderId="231" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="259" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="258" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="89" fillId="0" borderId="261" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="89" fillId="0" borderId="261" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="157" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="80" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="186" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="212" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6580,31 +6594,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="90" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="90" fillId="4" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="198" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="198" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="192" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="192" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6622,7 +6639,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="137" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6634,19 +6651,19 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="185" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="200" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="164" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6720,27 +6737,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="259" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="258" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="89" fillId="0" borderId="261" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="89" fillId="0" borderId="261" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -6955,7 +6951,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF002060"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -6974,8 +6970,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF4EE00"/>
       <color rgb="FF008080"/>
-      <color rgb="FFF4EE00"/>
       <color rgb="FFCCFF66"/>
     </mruColors>
   </colors>
@@ -12775,7 +12771,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="es-CL"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="r"/>
@@ -21388,7 +21384,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286425"/>
+                  <a14:cameraTool cellRange="data_status_NC!C3:D5" spid="_x0000_s286449"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21444,7 +21440,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286426"/>
+                  <a14:cameraTool cellRange="data_status_NC!C20:D24" spid="_x0000_s286450"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21509,7 +21505,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286427"/>
+                  <a14:cameraTool cellRange="data_status_NC!C7:D13" spid="_x0000_s286451"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21574,7 +21570,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286428"/>
+                  <a14:cameraTool cellRange="data_status_NC!C15:D18" spid="_x0000_s286452"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21639,7 +21635,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286429"/>
+                  <a14:cameraTool cellRange="data_status_NC!C26:D33" spid="_x0000_s286453"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21704,7 +21700,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286430"/>
+                  <a14:cameraTool cellRange="data_status_NC!C35:D39" spid="_x0000_s286454"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21769,7 +21765,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286431"/>
+                  <a14:cameraTool cellRange="data_status_NC!C41:D46" spid="_x0000_s286455"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -21834,7 +21830,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286432"/>
+                  <a14:cameraTool cellRange="data_status_NC!C48:D54" spid="_x0000_s286456"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -24406,7 +24402,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>1147440</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>441107</xdr:rowOff>
+      <xdr:rowOff>441108</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -24467,7 +24463,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>672354</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>311726</xdr:rowOff>
+      <xdr:rowOff>311728</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -25212,16 +25208,16 @@
     <row r="11" spans="1:24" ht="39.75" customHeight="1">
       <c r="A11" s="98"/>
       <c r="B11" s="95"/>
-      <c r="C11" s="277"/>
-      <c r="D11" s="277"/>
-      <c r="E11" s="282"/>
-      <c r="F11" s="283" t="s">
+      <c r="C11" s="275"/>
+      <c r="D11" s="275"/>
+      <c r="E11" s="280"/>
+      <c r="F11" s="281" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="459">
+      <c r="G11" s="466">
         <v>2024</v>
       </c>
-      <c r="H11" s="459"/>
+      <c r="H11" s="466"/>
       <c r="I11" s="98"/>
       <c r="J11" s="98"/>
       <c r="K11" s="98"/>
@@ -25244,11 +25240,11 @@
       <c r="B12" s="95"/>
       <c r="C12" s="98"/>
       <c r="D12" s="98"/>
-      <c r="E12" s="284"/>
-      <c r="F12" s="460" t="s">
+      <c r="E12" s="282"/>
+      <c r="F12" s="467" t="s">
         <v>203</v>
       </c>
-      <c r="G12" s="461"/>
+      <c r="G12" s="468"/>
       <c r="H12" s="98"/>
       <c r="I12" s="98"/>
       <c r="J12" s="98"/>
@@ -25324,11 +25320,11 @@
       <c r="B15" s="95"/>
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
-      <c r="E15" s="281"/>
-      <c r="F15" s="457" t="s">
+      <c r="E15" s="279"/>
+      <c r="F15" s="464" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="457"/>
+      <c r="G15" s="464"/>
       <c r="H15" s="98"/>
       <c r="I15" s="98"/>
       <c r="J15" s="98"/>
@@ -25352,11 +25348,11 @@
       <c r="B16" s="95"/>
       <c r="C16" s="98"/>
       <c r="D16" s="98"/>
-      <c r="E16" s="281"/>
-      <c r="F16" s="457" t="s">
+      <c r="E16" s="279"/>
+      <c r="F16" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="G16" s="457"/>
+      <c r="G16" s="464"/>
       <c r="H16" s="98"/>
       <c r="I16" s="98"/>
       <c r="J16" s="98"/>
@@ -25380,9 +25376,9 @@
       <c r="B17" s="95"/>
       <c r="C17" s="98"/>
       <c r="D17" s="98"/>
-      <c r="E17" s="278"/>
-      <c r="F17" s="279"/>
-      <c r="G17" s="279"/>
+      <c r="E17" s="276"/>
+      <c r="F17" s="277"/>
+      <c r="G17" s="277"/>
       <c r="H17" s="98"/>
       <c r="I17" s="98"/>
       <c r="J17" s="98"/>
@@ -25406,11 +25402,11 @@
       <c r="B18" s="95"/>
       <c r="C18" s="98"/>
       <c r="D18" s="98"/>
-      <c r="E18" s="280"/>
-      <c r="F18" s="458" t="s">
+      <c r="E18" s="278"/>
+      <c r="F18" s="465" t="s">
         <v>206</v>
       </c>
-      <c r="G18" s="458"/>
+      <c r="G18" s="465"/>
       <c r="H18" s="98"/>
       <c r="I18" s="98"/>
       <c r="J18" s="98"/>
@@ -26053,32 +26049,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="206"/>
-      <c r="B1" s="542" t="s">
+      <c r="B1" s="549" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="543"/>
-      <c r="D1" s="543"/>
-      <c r="E1" s="543"/>
-      <c r="F1" s="543"/>
-      <c r="G1" s="543"/>
-      <c r="H1" s="543"/>
-      <c r="I1" s="543"/>
-      <c r="J1" s="543"/>
-      <c r="K1" s="543"/>
-      <c r="L1" s="543"/>
-      <c r="M1" s="543"/>
-      <c r="N1" s="543"/>
-      <c r="O1" s="543"/>
-      <c r="P1" s="543"/>
-      <c r="Q1" s="543"/>
-      <c r="R1" s="543"/>
-      <c r="S1" s="543"/>
-      <c r="T1" s="543"/>
-      <c r="U1" s="543"/>
-      <c r="V1" s="543"/>
-      <c r="W1" s="543"/>
-      <c r="X1" s="543"/>
-      <c r="Y1" s="544"/>
+      <c r="C1" s="550"/>
+      <c r="D1" s="550"/>
+      <c r="E1" s="550"/>
+      <c r="F1" s="550"/>
+      <c r="G1" s="550"/>
+      <c r="H1" s="550"/>
+      <c r="I1" s="550"/>
+      <c r="J1" s="550"/>
+      <c r="K1" s="550"/>
+      <c r="L1" s="550"/>
+      <c r="M1" s="550"/>
+      <c r="N1" s="550"/>
+      <c r="O1" s="550"/>
+      <c r="P1" s="550"/>
+      <c r="Q1" s="550"/>
+      <c r="R1" s="550"/>
+      <c r="S1" s="550"/>
+      <c r="T1" s="550"/>
+      <c r="U1" s="550"/>
+      <c r="V1" s="550"/>
+      <c r="W1" s="550"/>
+      <c r="X1" s="550"/>
+      <c r="Y1" s="551"/>
       <c r="Z1" s="201"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -26114,32 +26110,32 @@
       <c r="A3" s="207" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="545" t="s">
+      <c r="B3" s="552" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="546"/>
-      <c r="D3" s="546"/>
-      <c r="E3" s="546"/>
-      <c r="F3" s="546"/>
-      <c r="G3" s="546"/>
-      <c r="H3" s="546"/>
-      <c r="I3" s="546"/>
-      <c r="J3" s="546"/>
-      <c r="K3" s="546"/>
-      <c r="L3" s="546"/>
-      <c r="M3" s="546"/>
-      <c r="N3" s="546"/>
-      <c r="O3" s="546"/>
-      <c r="P3" s="546"/>
-      <c r="Q3" s="546"/>
-      <c r="R3" s="546"/>
-      <c r="S3" s="546"/>
-      <c r="T3" s="546"/>
-      <c r="U3" s="546"/>
-      <c r="V3" s="546"/>
-      <c r="W3" s="546"/>
-      <c r="X3" s="546"/>
-      <c r="Y3" s="547"/>
+      <c r="C3" s="553"/>
+      <c r="D3" s="553"/>
+      <c r="E3" s="553"/>
+      <c r="F3" s="553"/>
+      <c r="G3" s="553"/>
+      <c r="H3" s="553"/>
+      <c r="I3" s="553"/>
+      <c r="J3" s="553"/>
+      <c r="K3" s="553"/>
+      <c r="L3" s="553"/>
+      <c r="M3" s="553"/>
+      <c r="N3" s="553"/>
+      <c r="O3" s="553"/>
+      <c r="P3" s="553"/>
+      <c r="Q3" s="553"/>
+      <c r="R3" s="553"/>
+      <c r="S3" s="553"/>
+      <c r="T3" s="553"/>
+      <c r="U3" s="553"/>
+      <c r="V3" s="553"/>
+      <c r="W3" s="553"/>
+      <c r="X3" s="553"/>
+      <c r="Y3" s="554"/>
       <c r="Z3" s="202"/>
       <c r="AA3" s="119"/>
     </row>
@@ -26147,32 +26143,32 @@
       <c r="A4" s="208" t="s">
         <v>182</v>
       </c>
-      <c r="B4" s="548" t="s">
+      <c r="B4" s="555" t="s">
         <v>183</v>
       </c>
-      <c r="C4" s="549"/>
-      <c r="D4" s="549"/>
-      <c r="E4" s="549"/>
-      <c r="F4" s="549"/>
-      <c r="G4" s="549"/>
-      <c r="H4" s="549"/>
-      <c r="I4" s="549"/>
-      <c r="J4" s="549"/>
-      <c r="K4" s="549"/>
-      <c r="L4" s="549"/>
-      <c r="M4" s="549"/>
-      <c r="N4" s="549"/>
-      <c r="O4" s="549"/>
-      <c r="P4" s="549"/>
-      <c r="Q4" s="549"/>
-      <c r="R4" s="549"/>
-      <c r="S4" s="549"/>
-      <c r="T4" s="549"/>
-      <c r="U4" s="549"/>
-      <c r="V4" s="549"/>
-      <c r="W4" s="549"/>
-      <c r="X4" s="549"/>
-      <c r="Y4" s="550"/>
+      <c r="C4" s="556"/>
+      <c r="D4" s="556"/>
+      <c r="E4" s="556"/>
+      <c r="F4" s="556"/>
+      <c r="G4" s="556"/>
+      <c r="H4" s="556"/>
+      <c r="I4" s="556"/>
+      <c r="J4" s="556"/>
+      <c r="K4" s="556"/>
+      <c r="L4" s="556"/>
+      <c r="M4" s="556"/>
+      <c r="N4" s="556"/>
+      <c r="O4" s="556"/>
+      <c r="P4" s="556"/>
+      <c r="Q4" s="556"/>
+      <c r="R4" s="556"/>
+      <c r="S4" s="556"/>
+      <c r="T4" s="556"/>
+      <c r="U4" s="556"/>
+      <c r="V4" s="556"/>
+      <c r="W4" s="556"/>
+      <c r="X4" s="556"/>
+      <c r="Y4" s="557"/>
       <c r="Z4" s="203"/>
       <c r="AA4" s="119"/>
     </row>
@@ -26207,40 +26203,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="209"/>
-      <c r="B6" s="554" t="s">
+      <c r="B6" s="561" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="555"/>
-      <c r="D6" s="555"/>
-      <c r="E6" s="556"/>
+      <c r="C6" s="562"/>
+      <c r="D6" s="562"/>
+      <c r="E6" s="563"/>
       <c r="F6" s="105"/>
       <c r="G6" s="168"/>
-      <c r="H6" s="574" t="s">
+      <c r="H6" s="581" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="575"/>
-      <c r="J6" s="575"/>
-      <c r="K6" s="576"/>
+      <c r="I6" s="582"/>
+      <c r="J6" s="582"/>
+      <c r="K6" s="583"/>
       <c r="L6" s="105"/>
       <c r="M6" s="168"/>
-      <c r="N6" s="582" t="s">
+      <c r="N6" s="589" t="s">
         <v>162</v>
       </c>
-      <c r="O6" s="583"/>
-      <c r="P6" s="584"/>
+      <c r="O6" s="590"/>
+      <c r="P6" s="591"/>
       <c r="Q6" s="175"/>
       <c r="R6" s="177"/>
-      <c r="S6" s="534" t="s">
+      <c r="S6" s="541" t="s">
         <v>144</v>
       </c>
-      <c r="T6" s="535"/>
+      <c r="T6" s="542"/>
       <c r="U6" s="178"/>
       <c r="V6" s="182"/>
       <c r="W6" s="169"/>
-      <c r="X6" s="534" t="s">
+      <c r="X6" s="541" t="s">
         <v>145</v>
       </c>
-      <c r="Y6" s="535"/>
+      <c r="Y6" s="542"/>
       <c r="Z6" s="96"/>
       <c r="AA6" s="119"/>
     </row>
@@ -26260,36 +26256,36 @@
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="135"/>
-      <c r="H7" s="570">
+      <c r="H7" s="577">
         <f>I23</f>
         <v>0</v>
       </c>
-      <c r="I7" s="581"/>
-      <c r="J7" s="581"/>
-      <c r="K7" s="571"/>
+      <c r="I7" s="588"/>
+      <c r="J7" s="588"/>
+      <c r="K7" s="578"/>
       <c r="L7" s="105"/>
       <c r="M7" s="135"/>
-      <c r="N7" s="566">
+      <c r="N7" s="573">
         <f>L23</f>
         <v>0</v>
       </c>
-      <c r="O7" s="567"/>
-      <c r="P7" s="568"/>
+      <c r="O7" s="574"/>
+      <c r="P7" s="575"/>
       <c r="Q7" s="176"/>
       <c r="R7" s="178"/>
-      <c r="S7" s="570">
+      <c r="S7" s="577">
         <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T7" s="571"/>
+      <c r="T7" s="578"/>
       <c r="U7" s="105"/>
       <c r="V7" s="181"/>
       <c r="W7" s="98"/>
-      <c r="X7" s="570">
+      <c r="X7" s="577">
         <f>R23</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="571"/>
+      <c r="Y7" s="578"/>
       <c r="Z7" s="167"/>
       <c r="AA7" s="119"/>
     </row>
@@ -26358,27 +26354,27 @@
       <c r="D10" s="160"/>
       <c r="E10" s="231"/>
       <c r="F10" s="105"/>
-      <c r="G10" s="562" t="s">
+      <c r="G10" s="569" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="563"/>
-      <c r="I10" s="563"/>
-      <c r="J10" s="563"/>
-      <c r="K10" s="563"/>
-      <c r="L10" s="563"/>
-      <c r="M10" s="563"/>
-      <c r="N10" s="563"/>
-      <c r="O10" s="563"/>
-      <c r="P10" s="563"/>
-      <c r="Q10" s="563"/>
-      <c r="R10" s="563"/>
-      <c r="S10" s="563"/>
-      <c r="T10" s="563"/>
-      <c r="U10" s="563"/>
-      <c r="V10" s="563"/>
-      <c r="W10" s="563"/>
-      <c r="X10" s="563"/>
-      <c r="Y10" s="564"/>
+      <c r="H10" s="570"/>
+      <c r="I10" s="570"/>
+      <c r="J10" s="570"/>
+      <c r="K10" s="570"/>
+      <c r="L10" s="570"/>
+      <c r="M10" s="570"/>
+      <c r="N10" s="570"/>
+      <c r="O10" s="570"/>
+      <c r="P10" s="570"/>
+      <c r="Q10" s="570"/>
+      <c r="R10" s="570"/>
+      <c r="S10" s="570"/>
+      <c r="T10" s="570"/>
+      <c r="U10" s="570"/>
+      <c r="V10" s="570"/>
+      <c r="W10" s="570"/>
+      <c r="X10" s="570"/>
+      <c r="Y10" s="571"/>
       <c r="Z10" s="96"/>
       <c r="AA10" s="119"/>
     </row>
@@ -26389,35 +26385,35 @@
       <c r="D11" s="160"/>
       <c r="E11" s="231"/>
       <c r="F11" s="105"/>
-      <c r="G11" s="565" t="s">
+      <c r="G11" s="572" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="560"/>
-      <c r="I11" s="560" t="s">
+      <c r="H11" s="567"/>
+      <c r="I11" s="567" t="s">
         <v>148</v>
       </c>
-      <c r="J11" s="560"/>
-      <c r="K11" s="560"/>
-      <c r="L11" s="560" t="s">
+      <c r="J11" s="567"/>
+      <c r="K11" s="567"/>
+      <c r="L11" s="567" t="s">
         <v>149</v>
       </c>
-      <c r="M11" s="560"/>
-      <c r="N11" s="560"/>
-      <c r="O11" s="560" t="s">
+      <c r="M11" s="567"/>
+      <c r="N11" s="567"/>
+      <c r="O11" s="567" t="s">
         <v>150</v>
       </c>
-      <c r="P11" s="560"/>
-      <c r="Q11" s="560"/>
-      <c r="R11" s="560" t="s">
+      <c r="P11" s="567"/>
+      <c r="Q11" s="567"/>
+      <c r="R11" s="567" t="s">
         <v>145</v>
       </c>
-      <c r="S11" s="560"/>
-      <c r="T11" s="560"/>
-      <c r="U11" s="560"/>
-      <c r="V11" s="560"/>
-      <c r="W11" s="560"/>
-      <c r="X11" s="560"/>
-      <c r="Y11" s="561"/>
+      <c r="S11" s="567"/>
+      <c r="T11" s="567"/>
+      <c r="U11" s="567"/>
+      <c r="V11" s="567"/>
+      <c r="W11" s="567"/>
+      <c r="X11" s="567"/>
+      <c r="Y11" s="568"/>
       <c r="Z11" s="96"/>
       <c r="AA11" s="119"/>
     </row>
@@ -26428,33 +26424,33 @@
       <c r="D12" s="216"/>
       <c r="E12" s="231"/>
       <c r="F12" s="105"/>
-      <c r="G12" s="565"/>
-      <c r="H12" s="560"/>
-      <c r="I12" s="560"/>
-      <c r="J12" s="560"/>
-      <c r="K12" s="560"/>
-      <c r="L12" s="560"/>
-      <c r="M12" s="560"/>
-      <c r="N12" s="560"/>
-      <c r="O12" s="560"/>
-      <c r="P12" s="560"/>
-      <c r="Q12" s="560"/>
-      <c r="R12" s="536" t="s">
+      <c r="G12" s="572"/>
+      <c r="H12" s="567"/>
+      <c r="I12" s="567"/>
+      <c r="J12" s="567"/>
+      <c r="K12" s="567"/>
+      <c r="L12" s="567"/>
+      <c r="M12" s="567"/>
+      <c r="N12" s="567"/>
+      <c r="O12" s="567"/>
+      <c r="P12" s="567"/>
+      <c r="Q12" s="567"/>
+      <c r="R12" s="543" t="s">
         <v>151</v>
       </c>
-      <c r="S12" s="536"/>
-      <c r="T12" s="536" t="s">
+      <c r="S12" s="543"/>
+      <c r="T12" s="543" t="s">
         <v>152</v>
       </c>
-      <c r="U12" s="536"/>
-      <c r="V12" s="536" t="s">
+      <c r="U12" s="543"/>
+      <c r="V12" s="543" t="s">
         <v>153</v>
       </c>
-      <c r="W12" s="536"/>
-      <c r="X12" s="536" t="s">
+      <c r="W12" s="543"/>
+      <c r="X12" s="543" t="s">
         <v>154</v>
       </c>
-      <c r="Y12" s="557"/>
+      <c r="Y12" s="564"/>
       <c r="Z12" s="96"/>
       <c r="AA12" s="95"/>
     </row>
@@ -26465,25 +26461,25 @@
       <c r="D13" s="160"/>
       <c r="E13" s="231"/>
       <c r="F13" s="105"/>
-      <c r="G13" s="565"/>
-      <c r="H13" s="560"/>
-      <c r="I13" s="560"/>
-      <c r="J13" s="560"/>
-      <c r="K13" s="560"/>
-      <c r="L13" s="560"/>
-      <c r="M13" s="560"/>
-      <c r="N13" s="560"/>
-      <c r="O13" s="560"/>
-      <c r="P13" s="560"/>
-      <c r="Q13" s="560"/>
-      <c r="R13" s="536"/>
-      <c r="S13" s="536"/>
-      <c r="T13" s="536"/>
-      <c r="U13" s="536"/>
-      <c r="V13" s="536"/>
-      <c r="W13" s="536"/>
-      <c r="X13" s="558"/>
-      <c r="Y13" s="559"/>
+      <c r="G13" s="572"/>
+      <c r="H13" s="567"/>
+      <c r="I13" s="567"/>
+      <c r="J13" s="567"/>
+      <c r="K13" s="567"/>
+      <c r="L13" s="567"/>
+      <c r="M13" s="567"/>
+      <c r="N13" s="567"/>
+      <c r="O13" s="567"/>
+      <c r="P13" s="567"/>
+      <c r="Q13" s="567"/>
+      <c r="R13" s="543"/>
+      <c r="S13" s="543"/>
+      <c r="T13" s="543"/>
+      <c r="U13" s="543"/>
+      <c r="V13" s="543"/>
+      <c r="W13" s="543"/>
+      <c r="X13" s="565"/>
+      <c r="Y13" s="566"/>
       <c r="Z13" s="96"/>
       <c r="AA13" s="97"/>
     </row>
@@ -26494,25 +26490,25 @@
       <c r="D14" s="160"/>
       <c r="E14" s="231"/>
       <c r="F14" s="105"/>
-      <c r="G14" s="537"/>
-      <c r="H14" s="538"/>
-      <c r="I14" s="539"/>
-      <c r="J14" s="540"/>
-      <c r="K14" s="541"/>
-      <c r="L14" s="533"/>
-      <c r="M14" s="533"/>
-      <c r="N14" s="533"/>
-      <c r="O14" s="533"/>
-      <c r="P14" s="533"/>
-      <c r="Q14" s="533"/>
-      <c r="R14" s="533"/>
-      <c r="S14" s="533"/>
-      <c r="T14" s="533"/>
-      <c r="U14" s="533"/>
-      <c r="V14" s="533"/>
-      <c r="W14" s="539"/>
-      <c r="X14" s="533"/>
-      <c r="Y14" s="569"/>
+      <c r="G14" s="544"/>
+      <c r="H14" s="545"/>
+      <c r="I14" s="546"/>
+      <c r="J14" s="547"/>
+      <c r="K14" s="548"/>
+      <c r="L14" s="540"/>
+      <c r="M14" s="540"/>
+      <c r="N14" s="540"/>
+      <c r="O14" s="540"/>
+      <c r="P14" s="540"/>
+      <c r="Q14" s="540"/>
+      <c r="R14" s="540"/>
+      <c r="S14" s="540"/>
+      <c r="T14" s="540"/>
+      <c r="U14" s="540"/>
+      <c r="V14" s="540"/>
+      <c r="W14" s="546"/>
+      <c r="X14" s="540"/>
+      <c r="Y14" s="576"/>
       <c r="Z14" s="96"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -26522,25 +26518,25 @@
       <c r="D15" s="217"/>
       <c r="E15" s="232"/>
       <c r="F15" s="105"/>
-      <c r="G15" s="537"/>
-      <c r="H15" s="538"/>
-      <c r="I15" s="539"/>
-      <c r="J15" s="540"/>
-      <c r="K15" s="541"/>
-      <c r="L15" s="533"/>
-      <c r="M15" s="533"/>
-      <c r="N15" s="533"/>
-      <c r="O15" s="533"/>
-      <c r="P15" s="533"/>
-      <c r="Q15" s="533"/>
-      <c r="R15" s="533"/>
-      <c r="S15" s="533"/>
-      <c r="T15" s="533"/>
-      <c r="U15" s="533"/>
-      <c r="V15" s="533"/>
-      <c r="W15" s="539"/>
-      <c r="X15" s="533"/>
-      <c r="Y15" s="569"/>
+      <c r="G15" s="544"/>
+      <c r="H15" s="545"/>
+      <c r="I15" s="546"/>
+      <c r="J15" s="547"/>
+      <c r="K15" s="548"/>
+      <c r="L15" s="540"/>
+      <c r="M15" s="540"/>
+      <c r="N15" s="540"/>
+      <c r="O15" s="540"/>
+      <c r="P15" s="540"/>
+      <c r="Q15" s="540"/>
+      <c r="R15" s="540"/>
+      <c r="S15" s="540"/>
+      <c r="T15" s="540"/>
+      <c r="U15" s="540"/>
+      <c r="V15" s="540"/>
+      <c r="W15" s="546"/>
+      <c r="X15" s="540"/>
+      <c r="Y15" s="576"/>
       <c r="Z15" s="96"/>
       <c r="AA15" s="119"/>
     </row>
@@ -26551,57 +26547,57 @@
       <c r="D16" s="125"/>
       <c r="E16" s="125"/>
       <c r="F16" s="95"/>
-      <c r="G16" s="537"/>
-      <c r="H16" s="538"/>
-      <c r="I16" s="539"/>
-      <c r="J16" s="540"/>
-      <c r="K16" s="541"/>
-      <c r="L16" s="533"/>
-      <c r="M16" s="533"/>
-      <c r="N16" s="533"/>
-      <c r="O16" s="533"/>
-      <c r="P16" s="533"/>
-      <c r="Q16" s="533"/>
-      <c r="R16" s="533"/>
-      <c r="S16" s="533"/>
-      <c r="T16" s="533"/>
-      <c r="U16" s="533"/>
-      <c r="V16" s="533"/>
-      <c r="W16" s="539"/>
-      <c r="X16" s="533"/>
-      <c r="Y16" s="569"/>
+      <c r="G16" s="544"/>
+      <c r="H16" s="545"/>
+      <c r="I16" s="546"/>
+      <c r="J16" s="547"/>
+      <c r="K16" s="548"/>
+      <c r="L16" s="540"/>
+      <c r="M16" s="540"/>
+      <c r="N16" s="540"/>
+      <c r="O16" s="540"/>
+      <c r="P16" s="540"/>
+      <c r="Q16" s="540"/>
+      <c r="R16" s="540"/>
+      <c r="S16" s="540"/>
+      <c r="T16" s="540"/>
+      <c r="U16" s="540"/>
+      <c r="V16" s="540"/>
+      <c r="W16" s="546"/>
+      <c r="X16" s="540"/>
+      <c r="Y16" s="576"/>
       <c r="Z16" s="96"/>
       <c r="AA16" s="119"/>
       <c r="AB16" s="226"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="95"/>
-      <c r="B17" s="551" t="s">
+      <c r="B17" s="558" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="552"/>
-      <c r="D17" s="552"/>
-      <c r="E17" s="553"/>
+      <c r="C17" s="559"/>
+      <c r="D17" s="559"/>
+      <c r="E17" s="560"/>
       <c r="F17" s="105"/>
-      <c r="G17" s="537"/>
-      <c r="H17" s="538"/>
-      <c r="I17" s="539"/>
-      <c r="J17" s="540"/>
-      <c r="K17" s="541"/>
-      <c r="L17" s="533"/>
-      <c r="M17" s="533"/>
-      <c r="N17" s="533"/>
-      <c r="O17" s="533"/>
-      <c r="P17" s="533"/>
-      <c r="Q17" s="533"/>
-      <c r="R17" s="533"/>
-      <c r="S17" s="533"/>
-      <c r="T17" s="533"/>
-      <c r="U17" s="533"/>
-      <c r="V17" s="533"/>
-      <c r="W17" s="539"/>
-      <c r="X17" s="533"/>
-      <c r="Y17" s="569"/>
+      <c r="G17" s="544"/>
+      <c r="H17" s="545"/>
+      <c r="I17" s="546"/>
+      <c r="J17" s="547"/>
+      <c r="K17" s="548"/>
+      <c r="L17" s="540"/>
+      <c r="M17" s="540"/>
+      <c r="N17" s="540"/>
+      <c r="O17" s="540"/>
+      <c r="P17" s="540"/>
+      <c r="Q17" s="540"/>
+      <c r="R17" s="540"/>
+      <c r="S17" s="540"/>
+      <c r="T17" s="540"/>
+      <c r="U17" s="540"/>
+      <c r="V17" s="540"/>
+      <c r="W17" s="546"/>
+      <c r="X17" s="540"/>
+      <c r="Y17" s="576"/>
       <c r="Z17" s="96"/>
       <c r="AA17" s="119"/>
     </row>
@@ -26620,25 +26616,25 @@
         <v>158</v>
       </c>
       <c r="F18" s="105"/>
-      <c r="G18" s="537"/>
-      <c r="H18" s="538"/>
-      <c r="I18" s="539"/>
-      <c r="J18" s="540"/>
-      <c r="K18" s="541"/>
-      <c r="L18" s="533"/>
-      <c r="M18" s="533"/>
-      <c r="N18" s="533"/>
-      <c r="O18" s="533"/>
-      <c r="P18" s="533"/>
-      <c r="Q18" s="533"/>
-      <c r="R18" s="533"/>
-      <c r="S18" s="533"/>
-      <c r="T18" s="533"/>
-      <c r="U18" s="533"/>
-      <c r="V18" s="533"/>
-      <c r="W18" s="539"/>
-      <c r="X18" s="533"/>
-      <c r="Y18" s="569"/>
+      <c r="G18" s="544"/>
+      <c r="H18" s="545"/>
+      <c r="I18" s="546"/>
+      <c r="J18" s="547"/>
+      <c r="K18" s="548"/>
+      <c r="L18" s="540"/>
+      <c r="M18" s="540"/>
+      <c r="N18" s="540"/>
+      <c r="O18" s="540"/>
+      <c r="P18" s="540"/>
+      <c r="Q18" s="540"/>
+      <c r="R18" s="540"/>
+      <c r="S18" s="540"/>
+      <c r="T18" s="540"/>
+      <c r="U18" s="540"/>
+      <c r="V18" s="540"/>
+      <c r="W18" s="546"/>
+      <c r="X18" s="540"/>
+      <c r="Y18" s="576"/>
       <c r="Z18" s="96"/>
       <c r="AA18" s="119"/>
     </row>
@@ -26649,25 +26645,25 @@
       <c r="D19" s="165"/>
       <c r="E19" s="233"/>
       <c r="F19" s="105"/>
-      <c r="G19" s="537"/>
-      <c r="H19" s="538"/>
-      <c r="I19" s="539"/>
-      <c r="J19" s="540"/>
-      <c r="K19" s="541"/>
-      <c r="L19" s="533"/>
-      <c r="M19" s="533"/>
-      <c r="N19" s="533"/>
-      <c r="O19" s="533"/>
-      <c r="P19" s="533"/>
-      <c r="Q19" s="533"/>
-      <c r="R19" s="533"/>
-      <c r="S19" s="533"/>
-      <c r="T19" s="533"/>
-      <c r="U19" s="533"/>
-      <c r="V19" s="533"/>
-      <c r="W19" s="539"/>
-      <c r="X19" s="533"/>
-      <c r="Y19" s="569"/>
+      <c r="G19" s="544"/>
+      <c r="H19" s="545"/>
+      <c r="I19" s="546"/>
+      <c r="J19" s="547"/>
+      <c r="K19" s="548"/>
+      <c r="L19" s="540"/>
+      <c r="M19" s="540"/>
+      <c r="N19" s="540"/>
+      <c r="O19" s="540"/>
+      <c r="P19" s="540"/>
+      <c r="Q19" s="540"/>
+      <c r="R19" s="540"/>
+      <c r="S19" s="540"/>
+      <c r="T19" s="540"/>
+      <c r="U19" s="540"/>
+      <c r="V19" s="540"/>
+      <c r="W19" s="546"/>
+      <c r="X19" s="540"/>
+      <c r="Y19" s="576"/>
       <c r="Z19" s="96"/>
       <c r="AA19" s="119"/>
     </row>
@@ -26678,25 +26674,25 @@
       <c r="D20" s="165"/>
       <c r="E20" s="233"/>
       <c r="F20" s="105"/>
-      <c r="G20" s="537"/>
-      <c r="H20" s="538"/>
-      <c r="I20" s="539"/>
-      <c r="J20" s="540"/>
-      <c r="K20" s="541"/>
-      <c r="L20" s="533"/>
-      <c r="M20" s="533"/>
-      <c r="N20" s="533"/>
-      <c r="O20" s="533"/>
-      <c r="P20" s="533"/>
-      <c r="Q20" s="533"/>
-      <c r="R20" s="533"/>
-      <c r="S20" s="533"/>
-      <c r="T20" s="533"/>
-      <c r="U20" s="533"/>
-      <c r="V20" s="533"/>
-      <c r="W20" s="539"/>
-      <c r="X20" s="533"/>
-      <c r="Y20" s="569"/>
+      <c r="G20" s="544"/>
+      <c r="H20" s="545"/>
+      <c r="I20" s="546"/>
+      <c r="J20" s="547"/>
+      <c r="K20" s="548"/>
+      <c r="L20" s="540"/>
+      <c r="M20" s="540"/>
+      <c r="N20" s="540"/>
+      <c r="O20" s="540"/>
+      <c r="P20" s="540"/>
+      <c r="Q20" s="540"/>
+      <c r="R20" s="540"/>
+      <c r="S20" s="540"/>
+      <c r="T20" s="540"/>
+      <c r="U20" s="540"/>
+      <c r="V20" s="540"/>
+      <c r="W20" s="546"/>
+      <c r="X20" s="540"/>
+      <c r="Y20" s="576"/>
       <c r="Z20" s="96"/>
       <c r="AA20" s="119"/>
     </row>
@@ -26707,25 +26703,25 @@
       <c r="D21" s="165"/>
       <c r="E21" s="233"/>
       <c r="F21" s="105"/>
-      <c r="G21" s="537"/>
-      <c r="H21" s="538"/>
-      <c r="I21" s="539"/>
-      <c r="J21" s="540"/>
-      <c r="K21" s="541"/>
-      <c r="L21" s="533"/>
-      <c r="M21" s="533"/>
-      <c r="N21" s="533"/>
-      <c r="O21" s="533"/>
-      <c r="P21" s="533"/>
-      <c r="Q21" s="533"/>
-      <c r="R21" s="533"/>
-      <c r="S21" s="533"/>
-      <c r="T21" s="533"/>
-      <c r="U21" s="533"/>
-      <c r="V21" s="533"/>
-      <c r="W21" s="539"/>
-      <c r="X21" s="533"/>
-      <c r="Y21" s="569"/>
+      <c r="G21" s="544"/>
+      <c r="H21" s="545"/>
+      <c r="I21" s="546"/>
+      <c r="J21" s="547"/>
+      <c r="K21" s="548"/>
+      <c r="L21" s="540"/>
+      <c r="M21" s="540"/>
+      <c r="N21" s="540"/>
+      <c r="O21" s="540"/>
+      <c r="P21" s="540"/>
+      <c r="Q21" s="540"/>
+      <c r="R21" s="540"/>
+      <c r="S21" s="540"/>
+      <c r="T21" s="540"/>
+      <c r="U21" s="540"/>
+      <c r="V21" s="540"/>
+      <c r="W21" s="546"/>
+      <c r="X21" s="540"/>
+      <c r="Y21" s="576"/>
       <c r="Z21" s="96"/>
       <c r="AA21" s="119"/>
     </row>
@@ -26736,25 +26732,25 @@
       <c r="D22" s="165"/>
       <c r="E22" s="233"/>
       <c r="F22" s="105"/>
-      <c r="G22" s="537"/>
-      <c r="H22" s="538"/>
-      <c r="I22" s="539"/>
-      <c r="J22" s="540"/>
-      <c r="K22" s="541"/>
-      <c r="L22" s="533"/>
-      <c r="M22" s="533"/>
-      <c r="N22" s="533"/>
-      <c r="O22" s="533"/>
-      <c r="P22" s="533"/>
-      <c r="Q22" s="533"/>
-      <c r="R22" s="533"/>
-      <c r="S22" s="533"/>
-      <c r="T22" s="533"/>
-      <c r="U22" s="533"/>
-      <c r="V22" s="533"/>
-      <c r="W22" s="539"/>
-      <c r="X22" s="533"/>
-      <c r="Y22" s="569"/>
+      <c r="G22" s="544"/>
+      <c r="H22" s="545"/>
+      <c r="I22" s="546"/>
+      <c r="J22" s="547"/>
+      <c r="K22" s="548"/>
+      <c r="L22" s="540"/>
+      <c r="M22" s="540"/>
+      <c r="N22" s="540"/>
+      <c r="O22" s="540"/>
+      <c r="P22" s="540"/>
+      <c r="Q22" s="540"/>
+      <c r="R22" s="540"/>
+      <c r="S22" s="540"/>
+      <c r="T22" s="540"/>
+      <c r="U22" s="540"/>
+      <c r="V22" s="540"/>
+      <c r="W22" s="546"/>
+      <c r="X22" s="540"/>
+      <c r="Y22" s="576"/>
       <c r="Z22" s="96"/>
       <c r="AA22" s="119"/>
     </row>
@@ -26765,48 +26761,48 @@
       <c r="D23" s="187"/>
       <c r="E23" s="234"/>
       <c r="F23" s="105"/>
-      <c r="G23" s="580" t="s">
+      <c r="G23" s="587" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="572"/>
-      <c r="I23" s="572">
+      <c r="H23" s="579"/>
+      <c r="I23" s="579">
         <f>SUM(I14:K22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="572"/>
-      <c r="K23" s="572"/>
-      <c r="L23" s="572">
+      <c r="J23" s="579"/>
+      <c r="K23" s="579"/>
+      <c r="L23" s="579">
         <f>SUM(L14:N22)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="572"/>
-      <c r="N23" s="572"/>
-      <c r="O23" s="577">
+      <c r="M23" s="579"/>
+      <c r="N23" s="579"/>
+      <c r="O23" s="584">
         <f>SUM(O14:Q22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="578"/>
-      <c r="Q23" s="579"/>
-      <c r="R23" s="577">
+      <c r="P23" s="585"/>
+      <c r="Q23" s="586"/>
+      <c r="R23" s="584">
         <f>SUM(R14:S22)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="579"/>
-      <c r="T23" s="577">
+      <c r="S23" s="586"/>
+      <c r="T23" s="584">
         <f>SUM(T14:U22)</f>
         <v>0</v>
       </c>
-      <c r="U23" s="579"/>
-      <c r="V23" s="577">
+      <c r="U23" s="586"/>
+      <c r="V23" s="584">
         <f>SUM(V14:W22)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="578"/>
-      <c r="X23" s="572">
+      <c r="W23" s="585"/>
+      <c r="X23" s="579">
         <f>SUM(X14:Y22)</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="573"/>
+      <c r="Y23" s="580"/>
       <c r="Z23" s="96"/>
       <c r="AA23" s="119"/>
     </row>
@@ -26876,28 +26872,28 @@
       <c r="E26" s="98"/>
       <c r="F26" s="95"/>
       <c r="G26" s="161"/>
-      <c r="H26" s="617" t="s">
+      <c r="H26" s="624" t="s">
         <v>170</v>
       </c>
-      <c r="I26" s="618"/>
-      <c r="J26" s="619"/>
+      <c r="I26" s="625"/>
+      <c r="J26" s="626"/>
       <c r="K26" s="105"/>
-      <c r="L26" s="623" t="s">
+      <c r="L26" s="630" t="s">
         <v>163</v>
       </c>
-      <c r="M26" s="624"/>
-      <c r="N26" s="624"/>
-      <c r="O26" s="624"/>
-      <c r="P26" s="624"/>
-      <c r="Q26" s="624"/>
-      <c r="R26" s="624"/>
-      <c r="S26" s="624"/>
-      <c r="T26" s="624"/>
-      <c r="U26" s="624"/>
-      <c r="V26" s="624"/>
-      <c r="W26" s="624"/>
-      <c r="X26" s="624"/>
-      <c r="Y26" s="625"/>
+      <c r="M26" s="631"/>
+      <c r="N26" s="631"/>
+      <c r="O26" s="631"/>
+      <c r="P26" s="631"/>
+      <c r="Q26" s="631"/>
+      <c r="R26" s="631"/>
+      <c r="S26" s="631"/>
+      <c r="T26" s="631"/>
+      <c r="U26" s="631"/>
+      <c r="V26" s="631"/>
+      <c r="W26" s="631"/>
+      <c r="X26" s="631"/>
+      <c r="Y26" s="632"/>
       <c r="Z26" s="96"/>
       <c r="AA26" s="119"/>
     </row>
@@ -26909,41 +26905,41 @@
       <c r="E27" s="98"/>
       <c r="F27" s="95"/>
       <c r="G27" s="162"/>
-      <c r="H27" s="614">
+      <c r="H27" s="621">
         <f>Y38</f>
         <v>0</v>
       </c>
-      <c r="I27" s="615"/>
-      <c r="J27" s="616"/>
+      <c r="I27" s="622"/>
+      <c r="J27" s="623"/>
       <c r="K27" s="105"/>
-      <c r="L27" s="588" t="s">
+      <c r="L27" s="595" t="s">
         <v>147</v>
       </c>
-      <c r="M27" s="536"/>
-      <c r="N27" s="536"/>
-      <c r="O27" s="536" t="s">
+      <c r="M27" s="543"/>
+      <c r="N27" s="543"/>
+      <c r="O27" s="543" t="s">
         <v>164</v>
       </c>
-      <c r="P27" s="536"/>
-      <c r="Q27" s="536" t="s">
+      <c r="P27" s="543"/>
+      <c r="Q27" s="543" t="s">
         <v>165</v>
       </c>
-      <c r="R27" s="536"/>
-      <c r="S27" s="536" t="s">
+      <c r="R27" s="543"/>
+      <c r="S27" s="543" t="s">
         <v>166</v>
       </c>
-      <c r="T27" s="536" t="s">
+      <c r="T27" s="543" t="s">
         <v>167</v>
       </c>
-      <c r="U27" s="536"/>
-      <c r="V27" s="536" t="s">
+      <c r="U27" s="543"/>
+      <c r="V27" s="543" t="s">
         <v>168</v>
       </c>
-      <c r="W27" s="536" t="s">
+      <c r="W27" s="543" t="s">
         <v>169</v>
       </c>
-      <c r="X27" s="536"/>
-      <c r="Y27" s="557" t="s">
+      <c r="X27" s="543"/>
+      <c r="Y27" s="564" t="s">
         <v>155</v>
       </c>
       <c r="Z27" s="96"/>
@@ -26961,20 +26957,20 @@
       <c r="I28" s="98"/>
       <c r="J28" s="193"/>
       <c r="K28" s="105"/>
-      <c r="L28" s="588"/>
-      <c r="M28" s="536"/>
-      <c r="N28" s="536"/>
-      <c r="O28" s="536"/>
-      <c r="P28" s="536"/>
-      <c r="Q28" s="536"/>
-      <c r="R28" s="536"/>
-      <c r="S28" s="536"/>
-      <c r="T28" s="536"/>
-      <c r="U28" s="536"/>
-      <c r="V28" s="536"/>
-      <c r="W28" s="536"/>
-      <c r="X28" s="536"/>
-      <c r="Y28" s="557"/>
+      <c r="L28" s="595"/>
+      <c r="M28" s="543"/>
+      <c r="N28" s="543"/>
+      <c r="O28" s="543"/>
+      <c r="P28" s="543"/>
+      <c r="Q28" s="543"/>
+      <c r="R28" s="543"/>
+      <c r="S28" s="543"/>
+      <c r="T28" s="543"/>
+      <c r="U28" s="543"/>
+      <c r="V28" s="543"/>
+      <c r="W28" s="543"/>
+      <c r="X28" s="543"/>
+      <c r="Y28" s="564"/>
       <c r="Z28" s="96"/>
       <c r="AA28" s="119"/>
     </row>
@@ -26990,19 +26986,19 @@
       <c r="I29" s="194"/>
       <c r="J29" s="164"/>
       <c r="K29" s="105"/>
-      <c r="L29" s="585"/>
-      <c r="M29" s="586"/>
-      <c r="N29" s="586"/>
-      <c r="O29" s="586"/>
-      <c r="P29" s="586"/>
-      <c r="Q29" s="586"/>
-      <c r="R29" s="586"/>
+      <c r="L29" s="592"/>
+      <c r="M29" s="593"/>
+      <c r="N29" s="593"/>
+      <c r="O29" s="593"/>
+      <c r="P29" s="593"/>
+      <c r="Q29" s="593"/>
+      <c r="R29" s="593"/>
       <c r="S29" s="87"/>
-      <c r="T29" s="586"/>
-      <c r="U29" s="586"/>
+      <c r="T29" s="593"/>
+      <c r="U29" s="593"/>
       <c r="V29" s="87"/>
-      <c r="W29" s="586"/>
-      <c r="X29" s="587"/>
+      <c r="W29" s="593"/>
+      <c r="X29" s="594"/>
       <c r="Y29" s="227"/>
       <c r="Z29" s="96"/>
       <c r="AA29" s="119"/>
@@ -27019,19 +27015,19 @@
       <c r="I30" s="125"/>
       <c r="J30" s="125"/>
       <c r="K30" s="95"/>
-      <c r="L30" s="585"/>
-      <c r="M30" s="586"/>
-      <c r="N30" s="586"/>
-      <c r="O30" s="586"/>
-      <c r="P30" s="586"/>
-      <c r="Q30" s="586"/>
-      <c r="R30" s="586"/>
+      <c r="L30" s="592"/>
+      <c r="M30" s="593"/>
+      <c r="N30" s="593"/>
+      <c r="O30" s="593"/>
+      <c r="P30" s="593"/>
+      <c r="Q30" s="593"/>
+      <c r="R30" s="593"/>
       <c r="S30" s="87"/>
-      <c r="T30" s="586"/>
-      <c r="U30" s="586"/>
+      <c r="T30" s="593"/>
+      <c r="U30" s="593"/>
       <c r="V30" s="87"/>
-      <c r="W30" s="586"/>
-      <c r="X30" s="587"/>
+      <c r="W30" s="593"/>
+      <c r="X30" s="594"/>
       <c r="Y30" s="227"/>
       <c r="Z30" s="96"/>
       <c r="AA30" s="95"/>
@@ -27044,25 +27040,25 @@
       <c r="E31" s="98"/>
       <c r="F31" s="95"/>
       <c r="G31" s="161"/>
-      <c r="H31" s="620" t="s">
+      <c r="H31" s="627" t="s">
         <v>160</v>
       </c>
-      <c r="I31" s="621"/>
-      <c r="J31" s="622"/>
+      <c r="I31" s="628"/>
+      <c r="J31" s="629"/>
       <c r="K31" s="105"/>
-      <c r="L31" s="585"/>
-      <c r="M31" s="586"/>
-      <c r="N31" s="586"/>
-      <c r="O31" s="586"/>
-      <c r="P31" s="586"/>
-      <c r="Q31" s="586"/>
-      <c r="R31" s="586"/>
+      <c r="L31" s="592"/>
+      <c r="M31" s="593"/>
+      <c r="N31" s="593"/>
+      <c r="O31" s="593"/>
+      <c r="P31" s="593"/>
+      <c r="Q31" s="593"/>
+      <c r="R31" s="593"/>
       <c r="S31" s="87"/>
-      <c r="T31" s="586"/>
-      <c r="U31" s="586"/>
+      <c r="T31" s="593"/>
+      <c r="U31" s="593"/>
       <c r="V31" s="87"/>
-      <c r="W31" s="586"/>
-      <c r="X31" s="587"/>
+      <c r="W31" s="593"/>
+      <c r="X31" s="594"/>
       <c r="Y31" s="227"/>
       <c r="Z31" s="96"/>
       <c r="AA31" s="95"/>
@@ -27079,19 +27075,19 @@
       <c r="I32" s="98"/>
       <c r="J32" s="193"/>
       <c r="K32" s="105"/>
-      <c r="L32" s="585"/>
-      <c r="M32" s="586"/>
-      <c r="N32" s="586"/>
-      <c r="O32" s="586"/>
-      <c r="P32" s="586"/>
-      <c r="Q32" s="586"/>
-      <c r="R32" s="586"/>
+      <c r="L32" s="592"/>
+      <c r="M32" s="593"/>
+      <c r="N32" s="593"/>
+      <c r="O32" s="593"/>
+      <c r="P32" s="593"/>
+      <c r="Q32" s="593"/>
+      <c r="R32" s="593"/>
       <c r="S32" s="87"/>
-      <c r="T32" s="586"/>
-      <c r="U32" s="586"/>
+      <c r="T32" s="593"/>
+      <c r="U32" s="593"/>
       <c r="V32" s="87"/>
-      <c r="W32" s="586"/>
-      <c r="X32" s="587"/>
+      <c r="W32" s="593"/>
+      <c r="X32" s="594"/>
       <c r="Y32" s="227"/>
       <c r="Z32" s="96"/>
       <c r="AA32" s="95"/>
@@ -27104,26 +27100,26 @@
       <c r="E33" s="98"/>
       <c r="F33" s="95"/>
       <c r="G33" s="162"/>
-      <c r="H33" s="614">
+      <c r="H33" s="621">
         <f>O38</f>
         <v>0</v>
       </c>
-      <c r="I33" s="615"/>
-      <c r="J33" s="616"/>
+      <c r="I33" s="622"/>
+      <c r="J33" s="623"/>
       <c r="K33" s="105"/>
-      <c r="L33" s="585"/>
-      <c r="M33" s="586"/>
-      <c r="N33" s="586"/>
-      <c r="O33" s="586"/>
-      <c r="P33" s="586"/>
-      <c r="Q33" s="586"/>
-      <c r="R33" s="586"/>
+      <c r="L33" s="592"/>
+      <c r="M33" s="593"/>
+      <c r="N33" s="593"/>
+      <c r="O33" s="593"/>
+      <c r="P33" s="593"/>
+      <c r="Q33" s="593"/>
+      <c r="R33" s="593"/>
       <c r="S33" s="87"/>
-      <c r="T33" s="586"/>
-      <c r="U33" s="586"/>
+      <c r="T33" s="593"/>
+      <c r="U33" s="593"/>
       <c r="V33" s="87"/>
-      <c r="W33" s="586"/>
-      <c r="X33" s="587"/>
+      <c r="W33" s="593"/>
+      <c r="X33" s="594"/>
       <c r="Y33" s="227"/>
       <c r="Z33" s="96"/>
       <c r="AA33" s="225"/>
@@ -27140,19 +27136,19 @@
       <c r="I34" s="98"/>
       <c r="J34" s="193"/>
       <c r="K34" s="105"/>
-      <c r="L34" s="585"/>
-      <c r="M34" s="586"/>
-      <c r="N34" s="586"/>
-      <c r="O34" s="586"/>
-      <c r="P34" s="586"/>
-      <c r="Q34" s="586"/>
-      <c r="R34" s="586"/>
+      <c r="L34" s="592"/>
+      <c r="M34" s="593"/>
+      <c r="N34" s="593"/>
+      <c r="O34" s="593"/>
+      <c r="P34" s="593"/>
+      <c r="Q34" s="593"/>
+      <c r="R34" s="593"/>
       <c r="S34" s="87"/>
-      <c r="T34" s="586"/>
-      <c r="U34" s="586"/>
+      <c r="T34" s="593"/>
+      <c r="U34" s="593"/>
       <c r="V34" s="87"/>
-      <c r="W34" s="586"/>
-      <c r="X34" s="587"/>
+      <c r="W34" s="593"/>
+      <c r="X34" s="594"/>
       <c r="Y34" s="227"/>
       <c r="Z34" s="96"/>
       <c r="AA34" s="95"/>
@@ -27169,19 +27165,19 @@
       <c r="I35" s="194"/>
       <c r="J35" s="164"/>
       <c r="K35" s="105"/>
-      <c r="L35" s="585"/>
-      <c r="M35" s="586"/>
-      <c r="N35" s="586"/>
-      <c r="O35" s="589"/>
-      <c r="P35" s="589"/>
-      <c r="Q35" s="589"/>
-      <c r="R35" s="589"/>
+      <c r="L35" s="592"/>
+      <c r="M35" s="593"/>
+      <c r="N35" s="593"/>
+      <c r="O35" s="596"/>
+      <c r="P35" s="596"/>
+      <c r="Q35" s="596"/>
+      <c r="R35" s="596"/>
       <c r="S35" s="190"/>
-      <c r="T35" s="589"/>
-      <c r="U35" s="589"/>
+      <c r="T35" s="596"/>
+      <c r="U35" s="596"/>
       <c r="V35" s="190"/>
-      <c r="W35" s="589"/>
-      <c r="X35" s="590"/>
+      <c r="W35" s="596"/>
+      <c r="X35" s="597"/>
       <c r="Y35" s="227"/>
       <c r="Z35" s="96"/>
       <c r="AA35" s="119"/>
@@ -27198,19 +27194,19 @@
       <c r="I36" s="125"/>
       <c r="J36" s="125"/>
       <c r="K36" s="95"/>
-      <c r="L36" s="585"/>
-      <c r="M36" s="586"/>
-      <c r="N36" s="587"/>
-      <c r="O36" s="591"/>
-      <c r="P36" s="591"/>
-      <c r="Q36" s="591"/>
-      <c r="R36" s="591"/>
+      <c r="L36" s="592"/>
+      <c r="M36" s="593"/>
+      <c r="N36" s="594"/>
+      <c r="O36" s="598"/>
+      <c r="P36" s="598"/>
+      <c r="Q36" s="598"/>
+      <c r="R36" s="598"/>
       <c r="S36" s="191"/>
-      <c r="T36" s="591"/>
-      <c r="U36" s="591"/>
+      <c r="T36" s="598"/>
+      <c r="U36" s="598"/>
       <c r="V36" s="191"/>
-      <c r="W36" s="591"/>
-      <c r="X36" s="592"/>
+      <c r="W36" s="598"/>
+      <c r="X36" s="599"/>
       <c r="Y36" s="227"/>
       <c r="Z36" s="96"/>
       <c r="AA36" s="95"/>
@@ -27223,25 +27219,25 @@
       <c r="E37" s="98"/>
       <c r="F37" s="95"/>
       <c r="G37" s="161"/>
-      <c r="H37" s="620" t="s">
+      <c r="H37" s="627" t="s">
         <v>159</v>
       </c>
-      <c r="I37" s="621"/>
-      <c r="J37" s="622"/>
+      <c r="I37" s="628"/>
+      <c r="J37" s="629"/>
       <c r="K37" s="105"/>
-      <c r="L37" s="585"/>
-      <c r="M37" s="586"/>
-      <c r="N37" s="587"/>
-      <c r="O37" s="591"/>
-      <c r="P37" s="591"/>
-      <c r="Q37" s="591"/>
-      <c r="R37" s="591"/>
+      <c r="L37" s="592"/>
+      <c r="M37" s="593"/>
+      <c r="N37" s="594"/>
+      <c r="O37" s="598"/>
+      <c r="P37" s="598"/>
+      <c r="Q37" s="598"/>
+      <c r="R37" s="598"/>
       <c r="S37" s="191"/>
-      <c r="T37" s="591"/>
-      <c r="U37" s="591"/>
+      <c r="T37" s="598"/>
+      <c r="U37" s="598"/>
       <c r="V37" s="191"/>
-      <c r="W37" s="591"/>
-      <c r="X37" s="592"/>
+      <c r="W37" s="598"/>
+      <c r="X37" s="599"/>
       <c r="Y37" s="227"/>
       <c r="Z37" s="96"/>
     </row>
@@ -27257,39 +27253,39 @@
       <c r="I38" s="98"/>
       <c r="J38" s="193"/>
       <c r="K38" s="105"/>
-      <c r="L38" s="604" t="s">
+      <c r="L38" s="611" t="s">
         <v>155</v>
       </c>
-      <c r="M38" s="605"/>
-      <c r="N38" s="606"/>
-      <c r="O38" s="593">
+      <c r="M38" s="612"/>
+      <c r="N38" s="613"/>
+      <c r="O38" s="600">
         <f>SUM(O29:P37)</f>
         <v>0</v>
       </c>
-      <c r="P38" s="593"/>
-      <c r="Q38" s="593">
+      <c r="P38" s="600"/>
+      <c r="Q38" s="600">
         <f>SUM(Q29:R37)</f>
         <v>0</v>
       </c>
-      <c r="R38" s="593"/>
+      <c r="R38" s="600"/>
       <c r="S38" s="228">
         <f>SUM(S29:S37)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="593">
+      <c r="T38" s="600">
         <f>SUM(T29:U37)</f>
         <v>0</v>
       </c>
-      <c r="U38" s="593"/>
+      <c r="U38" s="600"/>
       <c r="V38" s="228">
         <f>SUM(V29:V37)</f>
         <v>0</v>
       </c>
-      <c r="W38" s="593">
+      <c r="W38" s="600">
         <f>SUM(W29:X37)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="593"/>
+      <c r="X38" s="600"/>
       <c r="Y38" s="229">
         <f>SUM(Y29:Y37)</f>
         <v>0</v>
@@ -27305,26 +27301,26 @@
       <c r="E39" s="98"/>
       <c r="F39" s="95"/>
       <c r="G39" s="162"/>
-      <c r="H39" s="614">
+      <c r="H39" s="621">
         <f>S38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="615"/>
-      <c r="J39" s="616"/>
+      <c r="I39" s="622"/>
+      <c r="J39" s="623"/>
       <c r="K39" s="105"/>
-      <c r="L39" s="599"/>
-      <c r="M39" s="607"/>
-      <c r="N39" s="608"/>
-      <c r="O39" s="599"/>
-      <c r="P39" s="600"/>
-      <c r="Q39" s="612"/>
-      <c r="R39" s="613"/>
+      <c r="L39" s="606"/>
+      <c r="M39" s="614"/>
+      <c r="N39" s="615"/>
+      <c r="O39" s="606"/>
+      <c r="P39" s="607"/>
+      <c r="Q39" s="619"/>
+      <c r="R39" s="620"/>
       <c r="S39" s="123"/>
-      <c r="T39" s="640"/>
-      <c r="U39" s="640"/>
+      <c r="T39" s="647"/>
+      <c r="U39" s="647"/>
       <c r="V39" s="123"/>
-      <c r="W39" s="640"/>
-      <c r="X39" s="640"/>
+      <c r="W39" s="647"/>
+      <c r="X39" s="647"/>
       <c r="Y39" s="154"/>
       <c r="Z39" s="98"/>
       <c r="AA39" s="95"/>
@@ -27341,19 +27337,19 @@
       <c r="I40" s="98"/>
       <c r="J40" s="193"/>
       <c r="K40" s="105"/>
-      <c r="L40" s="609"/>
-      <c r="M40" s="610"/>
-      <c r="N40" s="611"/>
-      <c r="O40" s="601"/>
-      <c r="P40" s="598"/>
-      <c r="Q40" s="597"/>
-      <c r="R40" s="598"/>
+      <c r="L40" s="616"/>
+      <c r="M40" s="617"/>
+      <c r="N40" s="618"/>
+      <c r="O40" s="608"/>
+      <c r="P40" s="605"/>
+      <c r="Q40" s="604"/>
+      <c r="R40" s="605"/>
       <c r="S40" s="98"/>
-      <c r="T40" s="641"/>
-      <c r="U40" s="641"/>
+      <c r="T40" s="648"/>
+      <c r="U40" s="648"/>
       <c r="V40" s="98"/>
-      <c r="W40" s="641"/>
-      <c r="X40" s="641"/>
+      <c r="W40" s="648"/>
+      <c r="X40" s="648"/>
       <c r="Y40" s="166"/>
       <c r="Z40" s="98"/>
     </row>
@@ -27369,19 +27365,19 @@
       <c r="I41" s="194"/>
       <c r="J41" s="164"/>
       <c r="K41" s="105"/>
-      <c r="L41" s="609"/>
-      <c r="M41" s="610"/>
-      <c r="N41" s="611"/>
-      <c r="O41" s="602"/>
-      <c r="P41" s="603"/>
-      <c r="Q41" s="609"/>
-      <c r="R41" s="611"/>
+      <c r="L41" s="616"/>
+      <c r="M41" s="617"/>
+      <c r="N41" s="618"/>
+      <c r="O41" s="609"/>
+      <c r="P41" s="610"/>
+      <c r="Q41" s="616"/>
+      <c r="R41" s="618"/>
       <c r="S41" s="98"/>
-      <c r="T41" s="609"/>
-      <c r="U41" s="611"/>
+      <c r="T41" s="616"/>
+      <c r="U41" s="618"/>
       <c r="V41" s="98"/>
-      <c r="W41" s="609"/>
-      <c r="X41" s="611"/>
+      <c r="W41" s="616"/>
+      <c r="X41" s="618"/>
       <c r="Y41" s="166"/>
       <c r="Z41" s="98"/>
       <c r="AA41" s="119"/>
@@ -27398,21 +27394,21 @@
       <c r="I42" s="125"/>
       <c r="J42" s="125"/>
       <c r="K42" s="95"/>
-      <c r="L42" s="594"/>
-      <c r="M42" s="595"/>
-      <c r="N42" s="596"/>
-      <c r="O42" s="612"/>
-      <c r="P42" s="613"/>
+      <c r="L42" s="601"/>
+      <c r="M42" s="602"/>
+      <c r="N42" s="603"/>
+      <c r="O42" s="619"/>
+      <c r="P42" s="620"/>
       <c r="Q42" s="98"/>
-      <c r="R42" s="638" t="s">
+      <c r="R42" s="645" t="s">
         <v>217</v>
       </c>
-      <c r="S42" s="639"/>
+      <c r="S42" s="646"/>
       <c r="T42" s="124"/>
-      <c r="U42" s="642"/>
-      <c r="V42" s="643"/>
-      <c r="W42" s="642"/>
-      <c r="X42" s="643"/>
+      <c r="U42" s="649"/>
+      <c r="V42" s="650"/>
+      <c r="W42" s="649"/>
+      <c r="X42" s="650"/>
       <c r="Y42" s="166"/>
       <c r="Z42" s="98"/>
       <c r="AA42" s="95"/>
@@ -27425,34 +27421,34 @@
       <c r="E43" s="98"/>
       <c r="F43" s="95"/>
       <c r="G43" s="161"/>
-      <c r="H43" s="645" t="s">
+      <c r="H43" s="652" t="s">
         <v>171</v>
       </c>
-      <c r="I43" s="645"/>
-      <c r="J43" s="646"/>
+      <c r="I43" s="652"/>
+      <c r="J43" s="653"/>
       <c r="K43" s="105"/>
       <c r="L43" s="161"/>
       <c r="M43" s="192"/>
-      <c r="N43" s="629" t="s">
+      <c r="N43" s="636" t="s">
         <v>161</v>
       </c>
-      <c r="O43" s="630"/>
-      <c r="P43" s="631"/>
+      <c r="O43" s="637"/>
+      <c r="P43" s="638"/>
       <c r="Q43" s="162"/>
-      <c r="R43" s="359" t="s">
+      <c r="R43" s="354" t="s">
         <v>218</v>
       </c>
-      <c r="S43" s="372"/>
-      <c r="T43" s="369" t="s">
+      <c r="S43" s="367"/>
+      <c r="T43" s="364" t="s">
         <v>221</v>
       </c>
-      <c r="U43" s="360"/>
-      <c r="V43" s="360"/>
-      <c r="W43" s="360"/>
-      <c r="X43" s="373"/>
-      <c r="Y43" s="366"/>
-      <c r="Z43" s="362"/>
-      <c r="AA43" s="367"/>
+      <c r="U43" s="355"/>
+      <c r="V43" s="355"/>
+      <c r="W43" s="355"/>
+      <c r="X43" s="368"/>
+      <c r="Y43" s="361"/>
+      <c r="Z43" s="357"/>
+      <c r="AA43" s="362"/>
     </row>
     <row r="44" spans="1:27" ht="12" customHeight="1">
       <c r="A44" s="98"/>
@@ -27471,17 +27467,17 @@
       <c r="N44" s="98"/>
       <c r="O44" s="98"/>
       <c r="P44" s="193"/>
-      <c r="Q44" s="379"/>
-      <c r="R44" s="361"/>
-      <c r="S44" s="376"/>
-      <c r="T44" s="377"/>
-      <c r="U44" s="374"/>
-      <c r="V44" s="375"/>
-      <c r="W44" s="375"/>
-      <c r="X44" s="375"/>
-      <c r="Y44" s="381"/>
-      <c r="Z44" s="375"/>
-      <c r="AA44" s="376"/>
+      <c r="Q44" s="374"/>
+      <c r="R44" s="356"/>
+      <c r="S44" s="371"/>
+      <c r="T44" s="372"/>
+      <c r="U44" s="369"/>
+      <c r="V44" s="370"/>
+      <c r="W44" s="370"/>
+      <c r="X44" s="370"/>
+      <c r="Y44" s="376"/>
+      <c r="Z44" s="370"/>
+      <c r="AA44" s="371"/>
     </row>
     <row r="45" spans="1:27" ht="27" customHeight="1">
       <c r="A45" s="98"/>
@@ -27491,36 +27487,36 @@
       <c r="E45" s="98"/>
       <c r="F45" s="95"/>
       <c r="G45" s="162"/>
-      <c r="H45" s="614">
+      <c r="H45" s="621">
         <f>SUM(V38)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="615"/>
-      <c r="J45" s="616"/>
+      <c r="I45" s="622"/>
+      <c r="J45" s="623"/>
       <c r="K45" s="105"/>
       <c r="L45" s="162"/>
       <c r="M45" s="98"/>
       <c r="N45" s="98"/>
-      <c r="O45" s="632">
+      <c r="O45" s="639">
         <f>SUM(Q38,T38,W38)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="633"/>
+      <c r="P45" s="640"/>
       <c r="Q45" s="162"/>
-      <c r="R45" s="360" t="s">
+      <c r="R45" s="355" t="s">
         <v>219</v>
       </c>
-      <c r="S45" s="370"/>
-      <c r="T45" s="368" t="s">
+      <c r="S45" s="365"/>
+      <c r="T45" s="363" t="s">
         <v>222</v>
       </c>
-      <c r="U45" s="369"/>
-      <c r="V45" s="362"/>
-      <c r="W45" s="362"/>
-      <c r="X45" s="367"/>
-      <c r="Y45" s="380"/>
-      <c r="Z45" s="362"/>
-      <c r="AA45" s="367"/>
+      <c r="U45" s="364"/>
+      <c r="V45" s="357"/>
+      <c r="W45" s="357"/>
+      <c r="X45" s="362"/>
+      <c r="Y45" s="375"/>
+      <c r="Z45" s="357"/>
+      <c r="AA45" s="362"/>
     </row>
     <row r="46" spans="1:27" ht="17.25" customHeight="1">
       <c r="A46" s="98"/>
@@ -27537,19 +27533,19 @@
       <c r="L46" s="162"/>
       <c r="M46" s="98"/>
       <c r="N46" s="98"/>
-      <c r="O46" s="634"/>
-      <c r="P46" s="635"/>
+      <c r="O46" s="641"/>
+      <c r="P46" s="642"/>
       <c r="Q46" s="162"/>
-      <c r="R46" s="361"/>
-      <c r="S46" s="376"/>
-      <c r="T46" s="377"/>
-      <c r="U46" s="374"/>
-      <c r="V46" s="375"/>
-      <c r="W46" s="375"/>
-      <c r="X46" s="375"/>
-      <c r="Y46" s="382"/>
-      <c r="Z46" s="375"/>
-      <c r="AA46" s="378"/>
+      <c r="R46" s="356"/>
+      <c r="S46" s="371"/>
+      <c r="T46" s="372"/>
+      <c r="U46" s="369"/>
+      <c r="V46" s="370"/>
+      <c r="W46" s="370"/>
+      <c r="X46" s="370"/>
+      <c r="Y46" s="377"/>
+      <c r="Z46" s="370"/>
+      <c r="AA46" s="373"/>
     </row>
     <row r="47" spans="1:27" ht="19.5" customHeight="1" thickBot="1">
       <c r="A47" s="98"/>
@@ -27568,20 +27564,20 @@
       <c r="N47" s="194"/>
       <c r="O47" s="194"/>
       <c r="P47" s="164"/>
-      <c r="R47" s="368" t="s">
+      <c r="R47" s="363" t="s">
         <v>220</v>
       </c>
-      <c r="S47" s="367"/>
-      <c r="T47" s="368" t="s">
+      <c r="S47" s="362"/>
+      <c r="T47" s="363" t="s">
         <v>223</v>
       </c>
-      <c r="U47" s="369"/>
-      <c r="V47" s="362"/>
-      <c r="W47" s="362"/>
-      <c r="X47" s="367"/>
-      <c r="Y47" s="383"/>
-      <c r="Z47" s="362"/>
-      <c r="AA47" s="371"/>
+      <c r="U47" s="364"/>
+      <c r="V47" s="357"/>
+      <c r="W47" s="357"/>
+      <c r="X47" s="362"/>
+      <c r="Y47" s="378"/>
+      <c r="Z47" s="357"/>
+      <c r="AA47" s="366"/>
     </row>
     <row r="48" spans="1:27" ht="18.75" customHeight="1">
       <c r="A48" s="98"/>
@@ -27649,9 +27645,9 @@
       <c r="E50" s="98"/>
       <c r="F50" s="95"/>
       <c r="G50" s="195"/>
-      <c r="H50" s="636"/>
-      <c r="I50" s="636"/>
-      <c r="J50" s="637"/>
+      <c r="H50" s="643"/>
+      <c r="I50" s="643"/>
+      <c r="J50" s="644"/>
       <c r="K50" s="96"/>
       <c r="L50" s="123"/>
       <c r="M50" s="123"/>
@@ -27706,9 +27702,9 @@
       <c r="E52" s="98"/>
       <c r="F52" s="98"/>
       <c r="G52" s="98"/>
-      <c r="H52" s="644"/>
-      <c r="I52" s="644"/>
-      <c r="J52" s="644"/>
+      <c r="H52" s="651"/>
+      <c r="I52" s="651"/>
+      <c r="J52" s="651"/>
       <c r="K52" s="98"/>
       <c r="L52" s="98"/>
       <c r="M52" s="98"/>
@@ -27809,11 +27805,11 @@
       <c r="U55" s="95"/>
       <c r="V55" s="98"/>
       <c r="W55" s="98"/>
-      <c r="X55" s="626"/>
-      <c r="Y55" s="627"/>
-      <c r="Z55" s="627"/>
-      <c r="AA55" s="627"/>
-      <c r="AB55" s="628"/>
+      <c r="X55" s="633"/>
+      <c r="Y55" s="634"/>
+      <c r="Z55" s="634"/>
+      <c r="AA55" s="634"/>
+      <c r="AB55" s="635"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="98"/>
@@ -27839,8 +27835,8 @@
       <c r="U56" s="95"/>
       <c r="V56" s="98"/>
       <c r="W56" s="98"/>
-      <c r="X56" s="363"/>
-      <c r="Y56" s="364"/>
+      <c r="X56" s="358"/>
+      <c r="Y56" s="359"/>
       <c r="Z56" s="98"/>
       <c r="AA56" s="98"/>
       <c r="AB56" s="95"/>
@@ -27869,8 +27865,8 @@
       <c r="U57" s="95"/>
       <c r="V57" s="98"/>
       <c r="W57" s="98"/>
-      <c r="X57" s="365"/>
-      <c r="Y57" s="364"/>
+      <c r="X57" s="360"/>
+      <c r="Y57" s="359"/>
       <c r="Z57" s="98"/>
       <c r="AA57" s="98"/>
       <c r="AB57" s="95"/>
@@ -27899,8 +27895,8 @@
       <c r="U58" s="95"/>
       <c r="V58" s="98"/>
       <c r="W58" s="98"/>
-      <c r="X58" s="363"/>
-      <c r="Y58" s="364"/>
+      <c r="X58" s="358"/>
+      <c r="Y58" s="359"/>
       <c r="Z58" s="98"/>
       <c r="AA58" s="98"/>
       <c r="AB58" s="95"/>
@@ -27929,8 +27925,8 @@
       <c r="U59" s="95"/>
       <c r="V59" s="98"/>
       <c r="W59" s="98"/>
-      <c r="X59" s="365"/>
-      <c r="Y59" s="364"/>
+      <c r="X59" s="360"/>
+      <c r="Y59" s="359"/>
       <c r="Z59" s="98"/>
       <c r="AA59" s="98"/>
       <c r="AB59" s="95"/>
@@ -28029,11 +28025,11 @@
       <c r="P63" s="98"/>
       <c r="Q63" s="95"/>
       <c r="R63" s="95"/>
-      <c r="U63" s="626"/>
-      <c r="V63" s="627"/>
-      <c r="W63" s="627"/>
-      <c r="X63" s="627"/>
-      <c r="Y63" s="628"/>
+      <c r="U63" s="633"/>
+      <c r="V63" s="634"/>
+      <c r="W63" s="634"/>
+      <c r="X63" s="634"/>
+      <c r="Y63" s="635"/>
       <c r="Z63" s="98"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -28055,8 +28051,8 @@
       <c r="P64" s="98"/>
       <c r="Q64" s="95"/>
       <c r="R64" s="95"/>
-      <c r="U64" s="363"/>
-      <c r="V64" s="364"/>
+      <c r="U64" s="358"/>
+      <c r="V64" s="359"/>
       <c r="W64" s="98"/>
       <c r="X64" s="98"/>
       <c r="Y64" s="95"/>
@@ -28081,8 +28077,8 @@
       <c r="P65" s="98"/>
       <c r="Q65" s="95"/>
       <c r="R65" s="95"/>
-      <c r="U65" s="365"/>
-      <c r="V65" s="364"/>
+      <c r="U65" s="360"/>
+      <c r="V65" s="359"/>
       <c r="W65" s="98"/>
       <c r="X65" s="98"/>
       <c r="Y65" s="95"/>
@@ -28107,8 +28103,8 @@
       <c r="P66" s="98"/>
       <c r="Q66" s="95"/>
       <c r="R66" s="95"/>
-      <c r="U66" s="363"/>
-      <c r="V66" s="364"/>
+      <c r="U66" s="358"/>
+      <c r="V66" s="359"/>
       <c r="W66" s="98"/>
       <c r="X66" s="98"/>
       <c r="Y66" s="95"/>
@@ -28135,8 +28131,8 @@
       <c r="R67" s="95"/>
       <c r="S67" s="98"/>
       <c r="T67" s="98"/>
-      <c r="U67" s="365"/>
-      <c r="V67" s="364"/>
+      <c r="U67" s="360"/>
+      <c r="V67" s="359"/>
       <c r="W67" s="98"/>
       <c r="X67" s="98"/>
       <c r="Y67" s="95"/>
@@ -28704,22 +28700,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="B2" s="649" t="s">
+      <c r="B2" s="656" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="649"/>
-      <c r="D2" s="649"/>
-      <c r="E2" s="649"/>
-      <c r="F2" s="649"/>
+      <c r="C2" s="656"/>
+      <c r="D2" s="656"/>
+      <c r="E2" s="656"/>
+      <c r="F2" s="656"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="B3" s="650" t="s">
+      <c r="B3" s="657" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="650"/>
-      <c r="D3" s="650"/>
-      <c r="E3" s="650"/>
-      <c r="F3" s="650"/>
+      <c r="C3" s="657"/>
+      <c r="D3" s="657"/>
+      <c r="E3" s="657"/>
+      <c r="F3" s="657"/>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="89" t="s">
@@ -28857,13 +28853,13 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75">
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="264" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="266" t="s">
+      <c r="D14" s="264" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="267" t="s">
+      <c r="E14" s="265" t="s">
         <v>155</v>
       </c>
     </row>
@@ -28926,10 +28922,10 @@
       <c r="C26" s="89"/>
       <c r="D26" s="89"/>
       <c r="E26" s="2"/>
-      <c r="G26" s="647" t="s">
+      <c r="G26" s="654" t="s">
         <v>179</v>
       </c>
-      <c r="H26" s="648">
+      <c r="H26" s="655">
         <v>5</v>
       </c>
     </row>
@@ -28937,36 +28933,36 @@
       <c r="C27" s="89"/>
       <c r="D27" s="89"/>
       <c r="E27" s="2"/>
-      <c r="G27" s="647"/>
-      <c r="H27" s="648"/>
+      <c r="G27" s="654"/>
+      <c r="H27" s="655"/>
     </row>
     <row r="28" spans="3:8">
       <c r="C28" s="89"/>
       <c r="D28" s="89"/>
       <c r="E28" s="2"/>
-      <c r="G28" s="647"/>
-      <c r="H28" s="648"/>
+      <c r="G28" s="654"/>
+      <c r="H28" s="655"/>
     </row>
     <row r="29" spans="3:8">
       <c r="C29" s="89"/>
       <c r="D29" s="89"/>
       <c r="E29" s="2"/>
-      <c r="G29" s="647"/>
-      <c r="H29" s="648"/>
+      <c r="G29" s="654"/>
+      <c r="H29" s="655"/>
     </row>
     <row r="30" spans="3:8">
       <c r="C30" s="89"/>
       <c r="D30" s="89"/>
       <c r="E30" s="2"/>
-      <c r="G30" s="647"/>
-      <c r="H30" s="648"/>
+      <c r="G30" s="654"/>
+      <c r="H30" s="655"/>
     </row>
     <row r="31" spans="3:8">
       <c r="C31" s="89"/>
       <c r="D31" s="89"/>
       <c r="E31" s="2"/>
-      <c r="G31" s="647"/>
-      <c r="H31" s="648">
+      <c r="G31" s="654"/>
+      <c r="H31" s="655">
         <v>4</v>
       </c>
     </row>
@@ -28974,36 +28970,36 @@
       <c r="C32" s="89"/>
       <c r="D32" s="89"/>
       <c r="E32" s="2"/>
-      <c r="G32" s="647"/>
-      <c r="H32" s="648"/>
+      <c r="G32" s="654"/>
+      <c r="H32" s="655"/>
     </row>
     <row r="33" spans="3:8">
       <c r="C33" s="89"/>
       <c r="D33" s="89"/>
       <c r="E33" s="2"/>
-      <c r="G33" s="647"/>
-      <c r="H33" s="648"/>
+      <c r="G33" s="654"/>
+      <c r="H33" s="655"/>
     </row>
     <row r="34" spans="3:8">
       <c r="C34" s="89"/>
       <c r="D34" s="89"/>
       <c r="E34" s="2"/>
-      <c r="G34" s="647"/>
-      <c r="H34" s="648"/>
+      <c r="G34" s="654"/>
+      <c r="H34" s="655"/>
     </row>
     <row r="35" spans="3:8">
       <c r="C35" s="89"/>
       <c r="D35" s="89"/>
       <c r="E35" s="2"/>
-      <c r="G35" s="647"/>
-      <c r="H35" s="648"/>
+      <c r="G35" s="654"/>
+      <c r="H35" s="655"/>
     </row>
     <row r="36" spans="3:8">
       <c r="C36" s="89"/>
       <c r="D36" s="89"/>
       <c r="E36" s="2"/>
-      <c r="G36" s="647"/>
-      <c r="H36" s="648">
+      <c r="G36" s="654"/>
+      <c r="H36" s="655">
         <v>3</v>
       </c>
     </row>
@@ -29011,252 +29007,252 @@
       <c r="C37" s="89"/>
       <c r="D37" s="89"/>
       <c r="E37" s="2"/>
-      <c r="G37" s="647"/>
-      <c r="H37" s="648"/>
+      <c r="G37" s="654"/>
+      <c r="H37" s="655"/>
     </row>
     <row r="38" spans="3:8">
       <c r="C38" s="89"/>
       <c r="D38" s="89"/>
       <c r="E38" s="2"/>
-      <c r="G38" s="647"/>
-      <c r="H38" s="648"/>
+      <c r="G38" s="654"/>
+      <c r="H38" s="655"/>
     </row>
     <row r="39" spans="3:8">
       <c r="C39" s="89"/>
       <c r="D39" s="89"/>
       <c r="E39" s="2"/>
-      <c r="G39" s="647"/>
-      <c r="H39" s="648"/>
+      <c r="G39" s="654"/>
+      <c r="H39" s="655"/>
     </row>
     <row r="40" spans="3:8">
-      <c r="G40" s="647"/>
-      <c r="H40" s="648"/>
+      <c r="G40" s="654"/>
+      <c r="H40" s="655"/>
     </row>
     <row r="41" spans="3:8">
-      <c r="G41" s="647"/>
-      <c r="H41" s="648">
+      <c r="G41" s="654"/>
+      <c r="H41" s="655">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="3:8">
-      <c r="G42" s="647"/>
-      <c r="H42" s="648"/>
+      <c r="G42" s="654"/>
+      <c r="H42" s="655"/>
     </row>
     <row r="43" spans="3:8">
-      <c r="G43" s="647"/>
-      <c r="H43" s="648"/>
+      <c r="G43" s="654"/>
+      <c r="H43" s="655"/>
     </row>
     <row r="44" spans="3:8">
-      <c r="G44" s="647"/>
-      <c r="H44" s="648"/>
+      <c r="G44" s="654"/>
+      <c r="H44" s="655"/>
     </row>
     <row r="45" spans="3:8">
-      <c r="G45" s="647"/>
-      <c r="H45" s="648"/>
+      <c r="G45" s="654"/>
+      <c r="H45" s="655"/>
     </row>
     <row r="46" spans="3:8">
-      <c r="G46" s="647"/>
-      <c r="H46" s="648">
+      <c r="G46" s="654"/>
+      <c r="H46" s="655">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="3:8">
-      <c r="G47" s="647"/>
-      <c r="H47" s="648"/>
+      <c r="G47" s="654"/>
+      <c r="H47" s="655"/>
     </row>
     <row r="48" spans="3:8">
-      <c r="G48" s="647"/>
-      <c r="H48" s="648"/>
+      <c r="G48" s="654"/>
+      <c r="H48" s="655"/>
     </row>
     <row r="49" spans="7:10">
-      <c r="G49" s="647"/>
-      <c r="H49" s="648"/>
+      <c r="G49" s="654"/>
+      <c r="H49" s="655"/>
     </row>
     <row r="50" spans="7:10">
-      <c r="G50" s="647"/>
-      <c r="H50" s="648"/>
+      <c r="G50" s="654"/>
+      <c r="H50" s="655"/>
     </row>
     <row r="55" spans="7:10">
       <c r="H55" s="200"/>
-      <c r="I55" s="648"/>
-      <c r="J55" s="647"/>
+      <c r="I55" s="655"/>
+      <c r="J55" s="654"/>
     </row>
     <row r="56" spans="7:10">
       <c r="H56" s="200"/>
-      <c r="I56" s="648"/>
-      <c r="J56" s="647"/>
+      <c r="I56" s="655"/>
+      <c r="J56" s="654"/>
     </row>
     <row r="57" spans="7:10">
       <c r="H57" s="200"/>
-      <c r="I57" s="648"/>
-      <c r="J57" s="647"/>
+      <c r="I57" s="655"/>
+      <c r="J57" s="654"/>
     </row>
     <row r="58" spans="7:10">
       <c r="H58" s="200"/>
-      <c r="I58" s="648"/>
-      <c r="J58" s="647"/>
+      <c r="I58" s="655"/>
+      <c r="J58" s="654"/>
     </row>
     <row r="59" spans="7:10">
       <c r="H59" s="200"/>
-      <c r="I59" s="648"/>
-      <c r="J59" s="647"/>
+      <c r="I59" s="655"/>
+      <c r="J59" s="654"/>
     </row>
     <row r="60" spans="7:10">
       <c r="H60" s="200"/>
-      <c r="I60" s="648"/>
-      <c r="J60" s="647"/>
+      <c r="I60" s="655"/>
+      <c r="J60" s="654"/>
     </row>
     <row r="61" spans="7:10">
       <c r="H61" s="200"/>
-      <c r="I61" s="648"/>
-      <c r="J61" s="647"/>
+      <c r="I61" s="655"/>
+      <c r="J61" s="654"/>
     </row>
     <row r="62" spans="7:10">
       <c r="H62" s="200"/>
-      <c r="I62" s="648"/>
-      <c r="J62" s="647"/>
+      <c r="I62" s="655"/>
+      <c r="J62" s="654"/>
     </row>
     <row r="63" spans="7:10">
       <c r="H63" s="200"/>
-      <c r="I63" s="648"/>
-      <c r="J63" s="647"/>
+      <c r="I63" s="655"/>
+      <c r="J63" s="654"/>
     </row>
     <row r="64" spans="7:10">
       <c r="H64" s="200"/>
-      <c r="I64" s="648"/>
-      <c r="J64" s="647"/>
+      <c r="I64" s="655"/>
+      <c r="J64" s="654"/>
     </row>
     <row r="65" spans="8:11">
       <c r="H65" s="200"/>
-      <c r="I65" s="648"/>
-      <c r="J65" s="647"/>
+      <c r="I65" s="655"/>
+      <c r="J65" s="654"/>
     </row>
     <row r="66" spans="8:11">
       <c r="H66" s="200"/>
-      <c r="I66" s="648"/>
-      <c r="J66" s="647"/>
+      <c r="I66" s="655"/>
+      <c r="J66" s="654"/>
     </row>
     <row r="67" spans="8:11">
       <c r="H67" s="200"/>
-      <c r="I67" s="648"/>
-      <c r="J67" s="647"/>
+      <c r="I67" s="655"/>
+      <c r="J67" s="654"/>
     </row>
     <row r="68" spans="8:11">
       <c r="H68" s="200"/>
-      <c r="I68" s="648"/>
-      <c r="J68" s="647"/>
+      <c r="I68" s="655"/>
+      <c r="J68" s="654"/>
     </row>
     <row r="69" spans="8:11">
       <c r="H69" s="200"/>
-      <c r="I69" s="648"/>
-      <c r="J69" s="647"/>
+      <c r="I69" s="655"/>
+      <c r="J69" s="654"/>
     </row>
     <row r="70" spans="8:11">
       <c r="H70" s="200"/>
-      <c r="I70" s="648"/>
-      <c r="J70" s="647"/>
-      <c r="K70" s="647" t="s">
+      <c r="I70" s="655"/>
+      <c r="J70" s="654"/>
+      <c r="K70" s="654" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="71" spans="8:11">
       <c r="H71" s="200"/>
-      <c r="I71" s="648"/>
-      <c r="J71" s="647"/>
-      <c r="K71" s="647"/>
+      <c r="I71" s="655"/>
+      <c r="J71" s="654"/>
+      <c r="K71" s="654"/>
     </row>
     <row r="72" spans="8:11">
       <c r="H72" s="200"/>
-      <c r="I72" s="648"/>
-      <c r="J72" s="647"/>
-      <c r="K72" s="647"/>
+      <c r="I72" s="655"/>
+      <c r="J72" s="654"/>
+      <c r="K72" s="654"/>
     </row>
     <row r="73" spans="8:11">
       <c r="H73" s="200"/>
-      <c r="I73" s="648"/>
-      <c r="J73" s="647"/>
-      <c r="K73" s="647"/>
+      <c r="I73" s="655"/>
+      <c r="J73" s="654"/>
+      <c r="K73" s="654"/>
     </row>
     <row r="74" spans="8:11">
       <c r="H74" s="200"/>
-      <c r="I74" s="648"/>
-      <c r="J74" s="647"/>
-      <c r="K74" s="647"/>
+      <c r="I74" s="655"/>
+      <c r="J74" s="654"/>
+      <c r="K74" s="654"/>
     </row>
     <row r="75" spans="8:11">
       <c r="H75" s="200"/>
-      <c r="I75" s="648"/>
-      <c r="J75" s="647"/>
-      <c r="K75" s="647"/>
+      <c r="I75" s="655"/>
+      <c r="J75" s="654"/>
+      <c r="K75" s="654"/>
     </row>
     <row r="76" spans="8:11">
       <c r="H76" s="200"/>
-      <c r="I76" s="648"/>
-      <c r="J76" s="647"/>
-      <c r="K76" s="647"/>
+      <c r="I76" s="655"/>
+      <c r="J76" s="654"/>
+      <c r="K76" s="654"/>
     </row>
     <row r="77" spans="8:11">
       <c r="H77" s="200"/>
-      <c r="I77" s="648"/>
-      <c r="J77" s="647"/>
-      <c r="K77" s="647"/>
+      <c r="I77" s="655"/>
+      <c r="J77" s="654"/>
+      <c r="K77" s="654"/>
     </row>
     <row r="78" spans="8:11">
       <c r="H78" s="200"/>
-      <c r="I78" s="648"/>
-      <c r="J78" s="647"/>
-      <c r="K78" s="647"/>
+      <c r="I78" s="655"/>
+      <c r="J78" s="654"/>
+      <c r="K78" s="654"/>
     </row>
     <row r="79" spans="8:11">
       <c r="H79" s="200"/>
-      <c r="I79" s="648"/>
-      <c r="J79" s="647"/>
-      <c r="K79" s="647"/>
+      <c r="I79" s="655"/>
+      <c r="J79" s="654"/>
+      <c r="K79" s="654"/>
     </row>
     <row r="80" spans="8:11">
-      <c r="K80" s="647"/>
+      <c r="K80" s="654"/>
     </row>
     <row r="81" spans="11:11">
-      <c r="K81" s="647"/>
+      <c r="K81" s="654"/>
     </row>
     <row r="82" spans="11:11">
-      <c r="K82" s="647"/>
+      <c r="K82" s="654"/>
     </row>
     <row r="83" spans="11:11">
-      <c r="K83" s="647"/>
+      <c r="K83" s="654"/>
     </row>
     <row r="84" spans="11:11">
-      <c r="K84" s="647"/>
+      <c r="K84" s="654"/>
     </row>
     <row r="85" spans="11:11">
-      <c r="K85" s="647"/>
+      <c r="K85" s="654"/>
     </row>
     <row r="86" spans="11:11">
-      <c r="K86" s="647"/>
+      <c r="K86" s="654"/>
     </row>
     <row r="87" spans="11:11">
-      <c r="K87" s="647"/>
+      <c r="K87" s="654"/>
     </row>
     <row r="88" spans="11:11">
-      <c r="K88" s="647"/>
+      <c r="K88" s="654"/>
     </row>
     <row r="89" spans="11:11">
-      <c r="K89" s="647"/>
+      <c r="K89" s="654"/>
     </row>
     <row r="90" spans="11:11">
-      <c r="K90" s="647"/>
+      <c r="K90" s="654"/>
     </row>
     <row r="91" spans="11:11">
-      <c r="K91" s="647"/>
+      <c r="K91" s="654"/>
     </row>
     <row r="92" spans="11:11">
-      <c r="K92" s="647"/>
+      <c r="K92" s="654"/>
     </row>
     <row r="93" spans="11:11">
-      <c r="K93" s="647"/>
+      <c r="K93" s="654"/>
     </row>
     <row r="94" spans="11:11">
-      <c r="K94" s="647"/>
+      <c r="K94" s="654"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -29309,55 +29305,57 @@
   <sheetData>
     <row r="1" spans="1:21" ht="21">
       <c r="A1" s="98"/>
-      <c r="B1" s="651" t="s">
+      <c r="B1" s="662" t="s">
         <v>188</v>
       </c>
-      <c r="C1" s="652"/>
-      <c r="D1" s="652"/>
-      <c r="E1" s="652"/>
-      <c r="F1" s="652"/>
-      <c r="G1" s="652"/>
-      <c r="H1" s="652"/>
-      <c r="I1" s="652"/>
-      <c r="J1" s="652"/>
-      <c r="K1" s="652"/>
-      <c r="L1" s="652"/>
-      <c r="M1" s="652"/>
-      <c r="N1" s="652"/>
-      <c r="O1" s="652"/>
-      <c r="P1" s="653"/>
+      <c r="C1" s="663"/>
+      <c r="D1" s="663"/>
+      <c r="E1" s="663"/>
+      <c r="F1" s="663"/>
+      <c r="G1" s="663"/>
+      <c r="H1" s="663"/>
+      <c r="I1" s="663"/>
+      <c r="J1" s="663"/>
+      <c r="K1" s="663"/>
+      <c r="L1" s="663"/>
+      <c r="M1" s="663"/>
+      <c r="N1" s="663"/>
+      <c r="O1" s="663"/>
+      <c r="P1" s="664"/>
       <c r="Q1" s="98"/>
       <c r="R1" s="98"/>
       <c r="S1" s="98"/>
       <c r="T1" s="98"/>
       <c r="U1" s="98"/>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1">
+    <row r="2" spans="1:21" ht="18.75" customHeight="1">
       <c r="A2" s="98"/>
-      <c r="B2" s="654" t="s">
+      <c r="B2" s="658" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="655"/>
-      <c r="D2" s="655"/>
-      <c r="E2" s="655"/>
-      <c r="F2" s="655"/>
-      <c r="G2" s="655"/>
-      <c r="H2" s="655"/>
-      <c r="I2" s="655"/>
-      <c r="J2" s="655"/>
-      <c r="K2" s="655"/>
-      <c r="L2" s="655"/>
-      <c r="M2" s="655"/>
-      <c r="N2" s="655"/>
-      <c r="O2" s="655"/>
-      <c r="P2" s="656"/>
+      <c r="C2" s="659"/>
+      <c r="D2" s="659"/>
+      <c r="E2" s="659"/>
+      <c r="F2" s="659"/>
+      <c r="G2" s="660" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="660"/>
+      <c r="I2" s="660"/>
+      <c r="J2" s="660"/>
+      <c r="K2" s="660"/>
+      <c r="L2" s="660"/>
+      <c r="M2" s="660"/>
+      <c r="N2" s="660"/>
+      <c r="O2" s="660"/>
+      <c r="P2" s="661"/>
       <c r="Q2" s="98"/>
       <c r="R2" s="98"/>
       <c r="S2" s="98"/>
       <c r="T2" s="98"/>
       <c r="U2" s="98"/>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1">
+    <row r="3" spans="1:21" ht="6" customHeight="1">
       <c r="A3" s="98"/>
       <c r="B3" s="245"/>
       <c r="C3" s="249"/>
@@ -29391,14 +29389,14 @@
       <c r="H4" s="96"/>
       <c r="I4" s="104"/>
       <c r="J4" s="251"/>
-      <c r="K4" s="669" t="s">
+      <c r="K4" s="677" t="s">
         <v>230</v>
       </c>
-      <c r="L4" s="669"/>
-      <c r="M4" s="669"/>
-      <c r="N4" s="669"/>
-      <c r="O4" s="669"/>
-      <c r="P4" s="669"/>
+      <c r="L4" s="677"/>
+      <c r="M4" s="677"/>
+      <c r="N4" s="677"/>
+      <c r="O4" s="677"/>
+      <c r="P4" s="677"/>
       <c r="Q4" s="98"/>
       <c r="R4" s="98"/>
       <c r="S4" s="98"/>
@@ -29411,18 +29409,18 @@
       <c r="H5" s="95"/>
       <c r="I5" s="98"/>
       <c r="J5" s="252"/>
-      <c r="K5" s="665" t="s">
+      <c r="K5" s="673" t="s">
         <v>191</v>
       </c>
-      <c r="L5" s="665"/>
-      <c r="M5" s="665" t="s">
+      <c r="L5" s="673"/>
+      <c r="M5" s="673" t="s">
         <v>194</v>
       </c>
-      <c r="N5" s="665"/>
-      <c r="O5" s="665" t="s">
+      <c r="N5" s="673"/>
+      <c r="O5" s="673" t="s">
         <v>195</v>
       </c>
-      <c r="P5" s="665"/>
+      <c r="P5" s="673"/>
       <c r="Q5" s="96"/>
       <c r="R5" s="98"/>
       <c r="S5" s="98"/>
@@ -29435,12 +29433,12 @@
       <c r="H6" s="95"/>
       <c r="I6" s="98"/>
       <c r="J6" s="95"/>
-      <c r="K6" s="680"/>
-      <c r="L6" s="661"/>
-      <c r="M6" s="660"/>
-      <c r="N6" s="661"/>
-      <c r="O6" s="660"/>
-      <c r="P6" s="666"/>
+      <c r="K6" s="688"/>
+      <c r="L6" s="669"/>
+      <c r="M6" s="668"/>
+      <c r="N6" s="669"/>
+      <c r="O6" s="668"/>
+      <c r="P6" s="674"/>
       <c r="Q6" s="96"/>
       <c r="R6" s="98"/>
       <c r="S6" s="98"/>
@@ -29451,18 +29449,18 @@
       <c r="A7" s="98"/>
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
-      <c r="E7" s="667"/>
-      <c r="F7" s="668"/>
-      <c r="G7" s="668"/>
-      <c r="H7" s="668"/>
+      <c r="E7" s="675"/>
+      <c r="F7" s="676"/>
+      <c r="G7" s="676"/>
+      <c r="H7" s="676"/>
       <c r="I7" s="98"/>
       <c r="J7" s="119"/>
-      <c r="K7" s="670"/>
-      <c r="L7" s="663"/>
-      <c r="M7" s="662"/>
-      <c r="N7" s="663"/>
-      <c r="O7" s="662"/>
-      <c r="P7" s="664"/>
+      <c r="K7" s="678"/>
+      <c r="L7" s="671"/>
+      <c r="M7" s="670"/>
+      <c r="N7" s="671"/>
+      <c r="O7" s="670"/>
+      <c r="P7" s="672"/>
       <c r="Q7" s="96"/>
       <c r="R7" s="98"/>
       <c r="S7" s="98"/>
@@ -29476,12 +29474,12 @@
       <c r="D8" s="98"/>
       <c r="I8" s="98"/>
       <c r="J8" s="95"/>
-      <c r="K8" s="670"/>
-      <c r="L8" s="663"/>
-      <c r="M8" s="662"/>
-      <c r="N8" s="663"/>
-      <c r="O8" s="662"/>
-      <c r="P8" s="664"/>
+      <c r="K8" s="678"/>
+      <c r="L8" s="671"/>
+      <c r="M8" s="670"/>
+      <c r="N8" s="671"/>
+      <c r="O8" s="670"/>
+      <c r="P8" s="672"/>
       <c r="Q8" s="96"/>
       <c r="R8" s="98"/>
       <c r="S8" s="98"/>
@@ -29495,12 +29493,12 @@
       <c r="D9" s="98"/>
       <c r="I9" s="98"/>
       <c r="J9" s="119"/>
-      <c r="K9" s="670"/>
-      <c r="L9" s="663"/>
-      <c r="M9" s="662"/>
-      <c r="N9" s="663"/>
-      <c r="O9" s="662"/>
-      <c r="P9" s="664"/>
+      <c r="K9" s="678"/>
+      <c r="L9" s="671"/>
+      <c r="M9" s="670"/>
+      <c r="N9" s="671"/>
+      <c r="O9" s="670"/>
+      <c r="P9" s="672"/>
       <c r="Q9" s="96"/>
       <c r="R9" s="98"/>
       <c r="S9" s="98"/>
@@ -29514,12 +29512,12 @@
       <c r="D10" s="98"/>
       <c r="I10" s="98"/>
       <c r="J10" s="95"/>
-      <c r="K10" s="670"/>
-      <c r="L10" s="663"/>
-      <c r="M10" s="662"/>
-      <c r="N10" s="663"/>
-      <c r="O10" s="662"/>
-      <c r="P10" s="664"/>
+      <c r="K10" s="678"/>
+      <c r="L10" s="671"/>
+      <c r="M10" s="670"/>
+      <c r="N10" s="671"/>
+      <c r="O10" s="670"/>
+      <c r="P10" s="672"/>
       <c r="Q10" s="96"/>
       <c r="R10" s="98"/>
       <c r="S10" s="98"/>
@@ -29531,20 +29529,20 @@
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
       <c r="D11" s="95"/>
-      <c r="E11" s="657" t="s">
+      <c r="E11" s="665" t="s">
         <v>193</v>
       </c>
-      <c r="F11" s="658"/>
-      <c r="G11" s="658"/>
-      <c r="H11" s="659"/>
+      <c r="F11" s="666"/>
+      <c r="G11" s="666"/>
+      <c r="H11" s="667"/>
       <c r="I11" s="96"/>
       <c r="J11" s="119"/>
-      <c r="K11" s="670"/>
-      <c r="L11" s="663"/>
-      <c r="M11" s="662"/>
-      <c r="N11" s="663"/>
-      <c r="O11" s="662"/>
-      <c r="P11" s="664"/>
+      <c r="K11" s="678"/>
+      <c r="L11" s="671"/>
+      <c r="M11" s="670"/>
+      <c r="N11" s="671"/>
+      <c r="O11" s="670"/>
+      <c r="P11" s="672"/>
       <c r="Q11" s="96"/>
       <c r="R11" s="98"/>
       <c r="S11" s="98"/>
@@ -29556,22 +29554,22 @@
       <c r="B12" s="98"/>
       <c r="C12" s="98"/>
       <c r="D12" s="95"/>
-      <c r="E12" s="671" t="s">
+      <c r="E12" s="679" t="s">
         <v>191</v>
       </c>
-      <c r="F12" s="672"/>
-      <c r="G12" s="673"/>
-      <c r="H12" s="261" t="s">
+      <c r="F12" s="680"/>
+      <c r="G12" s="681"/>
+      <c r="H12" s="459" t="s">
         <v>192</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="119"/>
-      <c r="K12" s="670"/>
-      <c r="L12" s="663"/>
-      <c r="M12" s="662"/>
-      <c r="N12" s="663"/>
-      <c r="O12" s="662"/>
-      <c r="P12" s="664"/>
+      <c r="K12" s="678"/>
+      <c r="L12" s="671"/>
+      <c r="M12" s="670"/>
+      <c r="N12" s="671"/>
+      <c r="O12" s="670"/>
+      <c r="P12" s="672"/>
       <c r="Q12" s="96"/>
       <c r="R12" s="98"/>
       <c r="S12" s="98"/>
@@ -29583,22 +29581,22 @@
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
       <c r="D13" s="95"/>
-      <c r="E13" s="674" t="s">
+      <c r="E13" s="682" t="s">
         <v>209</v>
       </c>
-      <c r="F13" s="675"/>
-      <c r="G13" s="676"/>
-      <c r="H13" s="322">
+      <c r="F13" s="683"/>
+      <c r="G13" s="684"/>
+      <c r="H13" s="317">
         <v>2</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="95"/>
-      <c r="K13" s="670"/>
-      <c r="L13" s="663"/>
-      <c r="M13" s="662"/>
-      <c r="N13" s="663"/>
-      <c r="O13" s="662"/>
-      <c r="P13" s="664"/>
+      <c r="K13" s="678"/>
+      <c r="L13" s="671"/>
+      <c r="M13" s="670"/>
+      <c r="N13" s="671"/>
+      <c r="O13" s="670"/>
+      <c r="P13" s="672"/>
       <c r="Q13" s="96"/>
       <c r="R13" s="98"/>
       <c r="S13" s="98"/>
@@ -29610,22 +29608,22 @@
       <c r="B14" s="98"/>
       <c r="C14" s="98"/>
       <c r="D14" s="95"/>
-      <c r="E14" s="677" t="s">
+      <c r="E14" s="685" t="s">
         <v>207</v>
       </c>
-      <c r="F14" s="678"/>
-      <c r="G14" s="679"/>
-      <c r="H14" s="323">
+      <c r="F14" s="686"/>
+      <c r="G14" s="687"/>
+      <c r="H14" s="318">
         <v>26</v>
       </c>
       <c r="I14" s="96"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="670"/>
-      <c r="L14" s="663"/>
-      <c r="M14" s="662"/>
-      <c r="N14" s="663"/>
-      <c r="O14" s="662"/>
-      <c r="P14" s="664"/>
+      <c r="K14" s="678"/>
+      <c r="L14" s="671"/>
+      <c r="M14" s="670"/>
+      <c r="N14" s="671"/>
+      <c r="O14" s="670"/>
+      <c r="P14" s="672"/>
       <c r="Q14" s="96"/>
       <c r="R14" s="98"/>
       <c r="S14" s="98"/>
@@ -29637,22 +29635,22 @@
       <c r="B15" s="98"/>
       <c r="C15" s="98"/>
       <c r="D15" s="95"/>
-      <c r="E15" s="677" t="s">
+      <c r="E15" s="685" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="678"/>
-      <c r="G15" s="679"/>
-      <c r="H15" s="323">
+      <c r="F15" s="686"/>
+      <c r="G15" s="687"/>
+      <c r="H15" s="318">
         <v>5</v>
       </c>
       <c r="I15" s="96"/>
       <c r="J15" s="95"/>
-      <c r="K15" s="670"/>
-      <c r="L15" s="663"/>
-      <c r="M15" s="662"/>
-      <c r="N15" s="663"/>
-      <c r="O15" s="662"/>
-      <c r="P15" s="664"/>
+      <c r="K15" s="678"/>
+      <c r="L15" s="671"/>
+      <c r="M15" s="670"/>
+      <c r="N15" s="671"/>
+      <c r="O15" s="670"/>
+      <c r="P15" s="672"/>
       <c r="Q15" s="96"/>
       <c r="R15" s="98"/>
       <c r="S15" s="98"/>
@@ -29664,22 +29662,22 @@
       <c r="B16" s="98"/>
       <c r="C16" s="98"/>
       <c r="D16" s="95"/>
-      <c r="E16" s="677" t="s">
+      <c r="E16" s="685" t="s">
         <v>210</v>
       </c>
-      <c r="F16" s="678"/>
-      <c r="G16" s="679"/>
-      <c r="H16" s="323">
+      <c r="F16" s="686"/>
+      <c r="G16" s="687"/>
+      <c r="H16" s="318">
         <v>29</v>
       </c>
       <c r="I16" s="96"/>
       <c r="J16" s="119"/>
-      <c r="K16" s="670"/>
-      <c r="L16" s="663"/>
-      <c r="M16" s="662"/>
-      <c r="N16" s="663"/>
-      <c r="O16" s="662"/>
-      <c r="P16" s="664"/>
+      <c r="K16" s="678"/>
+      <c r="L16" s="671"/>
+      <c r="M16" s="670"/>
+      <c r="N16" s="671"/>
+      <c r="O16" s="670"/>
+      <c r="P16" s="672"/>
       <c r="Q16" s="96"/>
       <c r="R16" s="98"/>
       <c r="S16" s="98"/>
@@ -29689,22 +29687,22 @@
     <row r="17" spans="1:21" ht="66" customHeight="1">
       <c r="A17" s="95"/>
       <c r="D17" s="114"/>
-      <c r="E17" s="677" t="s">
+      <c r="E17" s="685" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="678"/>
-      <c r="G17" s="679"/>
-      <c r="H17" s="323">
+      <c r="F17" s="686"/>
+      <c r="G17" s="687"/>
+      <c r="H17" s="318">
         <v>6</v>
       </c>
       <c r="I17" s="96"/>
       <c r="J17" s="119"/>
-      <c r="K17" s="670"/>
-      <c r="L17" s="663"/>
-      <c r="M17" s="662"/>
-      <c r="N17" s="663"/>
-      <c r="O17" s="662"/>
-      <c r="P17" s="664"/>
+      <c r="K17" s="678"/>
+      <c r="L17" s="671"/>
+      <c r="M17" s="670"/>
+      <c r="N17" s="671"/>
+      <c r="O17" s="670"/>
+      <c r="P17" s="672"/>
       <c r="Q17" s="96"/>
       <c r="R17" s="98"/>
       <c r="S17" s="98"/>
@@ -29715,22 +29713,22 @@
       <c r="A18" s="95"/>
       <c r="C18" s="123"/>
       <c r="D18" s="95"/>
-      <c r="E18" s="689" t="s">
+      <c r="E18" s="697" t="s">
         <v>212</v>
       </c>
-      <c r="F18" s="690"/>
-      <c r="G18" s="691"/>
-      <c r="H18" s="324">
+      <c r="F18" s="698"/>
+      <c r="G18" s="699"/>
+      <c r="H18" s="319">
         <v>25</v>
       </c>
       <c r="I18" s="96"/>
       <c r="J18" s="95"/>
-      <c r="K18" s="697"/>
-      <c r="L18" s="696"/>
-      <c r="M18" s="681"/>
-      <c r="N18" s="696"/>
-      <c r="O18" s="681"/>
-      <c r="P18" s="682"/>
+      <c r="K18" s="705"/>
+      <c r="L18" s="704"/>
+      <c r="M18" s="689"/>
+      <c r="N18" s="704"/>
+      <c r="O18" s="689"/>
+      <c r="P18" s="690"/>
       <c r="Q18" s="96"/>
       <c r="R18" s="98"/>
       <c r="S18" s="95"/>
@@ -29742,17 +29740,17 @@
       <c r="B19" s="99"/>
       <c r="C19" s="119"/>
       <c r="D19" s="106"/>
-      <c r="E19" s="262"/>
+      <c r="E19" s="260"/>
       <c r="F19" s="244"/>
       <c r="G19" s="244"/>
       <c r="H19" s="244"/>
       <c r="I19" s="106"/>
       <c r="J19" s="95"/>
-      <c r="K19" s="289"/>
+      <c r="K19" s="287"/>
       <c r="L19" s="103"/>
       <c r="M19" s="125"/>
       <c r="O19" s="123"/>
-      <c r="P19" s="314"/>
+      <c r="P19" s="309"/>
       <c r="Q19" s="96"/>
       <c r="R19" s="98"/>
       <c r="S19" s="95"/>
@@ -29761,10 +29759,10 @@
     </row>
     <row r="20" spans="1:21" ht="56.25" customHeight="1" thickBot="1">
       <c r="A20" s="95"/>
-      <c r="B20" s="311" t="s">
+      <c r="B20" s="460" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="255" t="s">
+      <c r="C20" s="461" t="s">
         <v>225</v>
       </c>
       <c r="D20" s="254"/>
@@ -29774,8 +29772,8 @@
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
       <c r="J20" s="103"/>
-      <c r="K20" s="315"/>
-      <c r="L20" s="308"/>
+      <c r="K20" s="310"/>
+      <c r="L20" s="306"/>
       <c r="M20" s="98"/>
       <c r="N20" s="98"/>
       <c r="O20" s="96"/>
@@ -29787,17 +29785,17 @@
     </row>
     <row r="21" spans="1:21" ht="3.75" customHeight="1" thickBot="1">
       <c r="A21" s="95"/>
-      <c r="B21" s="312"/>
-      <c r="C21" s="309"/>
-      <c r="D21" s="290"/>
-      <c r="E21" s="288"/>
-      <c r="F21" s="300"/>
-      <c r="G21" s="297"/>
-      <c r="H21" s="288"/>
-      <c r="I21" s="294"/>
-      <c r="J21" s="306"/>
-      <c r="K21" s="316"/>
-      <c r="L21" s="295"/>
+      <c r="B21" s="462"/>
+      <c r="C21" s="463"/>
+      <c r="D21" s="288"/>
+      <c r="E21" s="286"/>
+      <c r="F21" s="298"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="286"/>
+      <c r="I21" s="292"/>
+      <c r="J21" s="304"/>
+      <c r="K21" s="311"/>
+      <c r="L21" s="293"/>
       <c r="M21" s="95"/>
       <c r="N21" s="98"/>
       <c r="O21" s="96"/>
@@ -29809,21 +29807,21 @@
     </row>
     <row r="22" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A22" s="95"/>
-      <c r="B22" s="310"/>
-      <c r="C22" s="313"/>
-      <c r="D22" s="290"/>
-      <c r="E22" s="299"/>
-      <c r="F22" s="321" t="s">
+      <c r="B22" s="307"/>
+      <c r="C22" s="308"/>
+      <c r="D22" s="288"/>
+      <c r="E22" s="297"/>
+      <c r="F22" s="316" t="s">
         <v>193</v>
       </c>
-      <c r="G22" s="298"/>
-      <c r="H22" s="692" t="s">
+      <c r="G22" s="296"/>
+      <c r="H22" s="700" t="s">
         <v>196</v>
       </c>
-      <c r="I22" s="693"/>
-      <c r="J22" s="307"/>
-      <c r="K22" s="317"/>
-      <c r="L22" s="295"/>
+      <c r="I22" s="701"/>
+      <c r="J22" s="305"/>
+      <c r="K22" s="312"/>
+      <c r="L22" s="293"/>
       <c r="M22" s="123"/>
       <c r="N22" s="98"/>
       <c r="O22" s="96"/>
@@ -29835,25 +29833,25 @@
     </row>
     <row r="23" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A23" s="95"/>
-      <c r="B23" s="257"/>
-      <c r="C23" s="258"/>
-      <c r="D23" s="290"/>
-      <c r="E23" s="292"/>
-      <c r="F23" s="301">
+      <c r="B23" s="256"/>
+      <c r="C23" s="257"/>
+      <c r="D23" s="288"/>
+      <c r="E23" s="290"/>
+      <c r="F23" s="299">
         <f>SUM(H13:H18)</f>
         <v>93</v>
       </c>
-      <c r="G23" s="291"/>
-      <c r="H23" s="302">
+      <c r="G23" s="289"/>
+      <c r="H23" s="300">
         <f>SUM(C22:C27)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="293"/>
-      <c r="J23" s="307"/>
-      <c r="K23" s="318"/>
-      <c r="L23" s="296"/>
-      <c r="M23" s="319"/>
-      <c r="N23" s="319"/>
+      <c r="I23" s="291"/>
+      <c r="J23" s="305"/>
+      <c r="K23" s="313"/>
+      <c r="L23" s="294"/>
+      <c r="M23" s="314"/>
+      <c r="N23" s="314"/>
       <c r="O23" s="96"/>
       <c r="P23" s="193"/>
       <c r="Q23" s="96"/>
@@ -29863,8 +29861,8 @@
     </row>
     <row r="24" spans="1:21" ht="35.25" customHeight="1" thickBot="1">
       <c r="A24" s="95"/>
-      <c r="B24" s="259"/>
-      <c r="C24" s="260"/>
+      <c r="B24" s="258"/>
+      <c r="C24" s="259"/>
       <c r="D24" s="254"/>
       <c r="E24" s="125"/>
       <c r="F24" s="125"/>
@@ -29872,12 +29870,12 @@
       <c r="H24" s="123"/>
       <c r="I24" s="123"/>
       <c r="J24" s="97"/>
-      <c r="K24" s="289"/>
+      <c r="K24" s="287"/>
       <c r="L24" s="143"/>
       <c r="M24" s="144"/>
       <c r="N24" s="142"/>
       <c r="O24" s="99"/>
-      <c r="P24" s="398"/>
+      <c r="P24" s="393"/>
       <c r="Q24" s="96"/>
       <c r="R24" s="98"/>
       <c r="T24" s="98"/>
@@ -29885,22 +29883,22 @@
     </row>
     <row r="25" spans="1:21" ht="33" customHeight="1" thickBot="1">
       <c r="A25" s="95"/>
-      <c r="B25" s="259"/>
-      <c r="C25" s="260"/>
-      <c r="D25" s="290"/>
+      <c r="B25" s="258"/>
+      <c r="C25" s="259"/>
+      <c r="D25" s="288"/>
       <c r="E25" s="194"/>
       <c r="F25" s="194"/>
       <c r="G25" s="106"/>
       <c r="I25" s="174"/>
       <c r="J25" s="95"/>
-      <c r="K25" s="401" t="s">
+      <c r="K25" s="396" t="s">
         <v>227</v>
       </c>
       <c r="L25" s="192"/>
-      <c r="M25" s="400"/>
-      <c r="N25" s="403"/>
-      <c r="O25" s="402"/>
-      <c r="P25" s="294"/>
+      <c r="M25" s="395"/>
+      <c r="N25" s="398"/>
+      <c r="O25" s="397"/>
+      <c r="P25" s="292"/>
       <c r="Q25" s="96"/>
       <c r="R25" s="98"/>
       <c r="T25" s="98"/>
@@ -29908,24 +29906,24 @@
     </row>
     <row r="26" spans="1:21" ht="44.25" customHeight="1">
       <c r="A26" s="95"/>
-      <c r="B26" s="259"/>
-      <c r="C26" s="260"/>
-      <c r="D26" s="290"/>
-      <c r="E26" s="304"/>
-      <c r="F26" s="320" t="s">
+      <c r="B26" s="258"/>
+      <c r="C26" s="259"/>
+      <c r="D26" s="288"/>
+      <c r="E26" s="302"/>
+      <c r="F26" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="H26" s="694" t="s">
+      <c r="H26" s="702" t="s">
         <v>226</v>
       </c>
-      <c r="I26" s="695"/>
-      <c r="J26" s="399"/>
-      <c r="K26" s="683" t="s">
+      <c r="I26" s="703"/>
+      <c r="J26" s="394"/>
+      <c r="K26" s="691" t="s">
         <v>229</v>
       </c>
-      <c r="L26" s="684"/>
-      <c r="M26" s="684"/>
-      <c r="N26" s="685"/>
+      <c r="L26" s="692"/>
+      <c r="M26" s="692"/>
+      <c r="N26" s="693"/>
       <c r="O26" s="96"/>
       <c r="P26" s="193"/>
       <c r="Q26" s="96"/>
@@ -29935,26 +29933,26 @@
     </row>
     <row r="27" spans="1:21" ht="36.75" customHeight="1" thickBot="1">
       <c r="A27" s="95"/>
-      <c r="B27" s="263"/>
-      <c r="C27" s="264"/>
+      <c r="B27" s="261"/>
+      <c r="C27" s="262"/>
       <c r="D27" s="254"/>
-      <c r="E27" s="303"/>
-      <c r="F27" s="305">
+      <c r="E27" s="301"/>
+      <c r="F27" s="303">
         <v>45657</v>
       </c>
       <c r="G27" s="94"/>
-      <c r="H27" s="265">
+      <c r="H27" s="263">
         <f>COUNTA(O6:P27)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="256"/>
+      <c r="I27" s="255"/>
       <c r="J27" s="253"/>
-      <c r="K27" s="686" t="s">
+      <c r="K27" s="694" t="s">
         <v>228</v>
       </c>
-      <c r="L27" s="687"/>
-      <c r="M27" s="687"/>
-      <c r="N27" s="688"/>
+      <c r="L27" s="695"/>
+      <c r="M27" s="695"/>
+      <c r="N27" s="696"/>
       <c r="O27" s="194"/>
       <c r="P27" s="164"/>
       <c r="Q27" s="96"/>
@@ -29976,7 +29974,7 @@
       <c r="K28" s="143"/>
       <c r="L28" s="125"/>
       <c r="M28" s="125"/>
-      <c r="N28" s="326"/>
+      <c r="N28" s="321"/>
       <c r="O28" s="104"/>
       <c r="P28" s="123"/>
       <c r="Q28" s="98"/>
@@ -30400,7 +30398,7 @@
       <c r="U46" s="98"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="59">
     <mergeCell ref="K26:N26"/>
     <mergeCell ref="K27:N27"/>
     <mergeCell ref="E17:G17"/>
@@ -30422,11 +30420,13 @@
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="O13:P13"/>
     <mergeCell ref="O14:P14"/>
+    <mergeCell ref="K15:L15"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="K4:P4"/>
     <mergeCell ref="M15:N15"/>
@@ -30442,9 +30442,9 @@
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:P2"/>
     <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="M7:N7"/>
@@ -30458,7 +30458,6 @@
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="O9:P9"/>
     <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -30481,90 +30480,90 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="18.75">
-      <c r="A2" s="325" t="s">
+      <c r="A2" s="320" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="325" t="s">
+      <c r="B2" s="320" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="325" t="s">
+      <c r="C2" s="320" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="325" t="s">
+      <c r="D2" s="320" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="58.5" customHeight="1">
-      <c r="A3" s="702"/>
-      <c r="B3" s="698"/>
-      <c r="C3" s="704"/>
-      <c r="D3" s="704"/>
+      <c r="A3" s="456"/>
+      <c r="B3" s="452"/>
+      <c r="C3" s="458"/>
+      <c r="D3" s="458"/>
     </row>
     <row r="4" spans="1:4" ht="68.25" customHeight="1">
-      <c r="A4" s="703"/>
-      <c r="B4" s="699"/>
-      <c r="C4" s="704"/>
-      <c r="D4" s="704"/>
+      <c r="A4" s="457"/>
+      <c r="B4" s="453"/>
+      <c r="C4" s="458"/>
+      <c r="D4" s="458"/>
     </row>
     <row r="5" spans="1:4" ht="47.25" customHeight="1">
-      <c r="A5" s="703"/>
-      <c r="B5" s="698"/>
-      <c r="C5" s="704"/>
-      <c r="D5" s="704"/>
+      <c r="A5" s="457"/>
+      <c r="B5" s="452"/>
+      <c r="C5" s="458"/>
+      <c r="D5" s="458"/>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="703"/>
-      <c r="B6" s="699"/>
-      <c r="C6" s="704"/>
-      <c r="D6" s="704"/>
+      <c r="A6" s="457"/>
+      <c r="B6" s="453"/>
+      <c r="C6" s="458"/>
+      <c r="D6" s="458"/>
     </row>
     <row r="7" spans="1:4" ht="66" customHeight="1">
-      <c r="A7" s="703"/>
-      <c r="B7" s="698"/>
-      <c r="C7" s="704"/>
-      <c r="D7" s="704"/>
+      <c r="A7" s="457"/>
+      <c r="B7" s="452"/>
+      <c r="C7" s="458"/>
+      <c r="D7" s="458"/>
     </row>
     <row r="8" spans="1:4" ht="48.75" customHeight="1">
-      <c r="A8" s="703"/>
-      <c r="B8" s="699"/>
-      <c r="C8" s="704"/>
-      <c r="D8" s="704"/>
+      <c r="A8" s="457"/>
+      <c r="B8" s="453"/>
+      <c r="C8" s="458"/>
+      <c r="D8" s="458"/>
     </row>
     <row r="9" spans="1:4" ht="52.5" customHeight="1">
-      <c r="A9" s="703"/>
-      <c r="B9" s="698"/>
-      <c r="C9" s="704"/>
-      <c r="D9" s="704"/>
+      <c r="A9" s="457"/>
+      <c r="B9" s="452"/>
+      <c r="C9" s="458"/>
+      <c r="D9" s="458"/>
     </row>
     <row r="10" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A10" s="703"/>
-      <c r="B10" s="699"/>
-      <c r="C10" s="704"/>
-      <c r="D10" s="704"/>
+      <c r="A10" s="457"/>
+      <c r="B10" s="453"/>
+      <c r="C10" s="458"/>
+      <c r="D10" s="458"/>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A11" s="703"/>
-      <c r="B11" s="698"/>
-      <c r="C11" s="704"/>
-      <c r="D11" s="704"/>
+      <c r="A11" s="457"/>
+      <c r="B11" s="452"/>
+      <c r="C11" s="458"/>
+      <c r="D11" s="458"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="703"/>
-      <c r="B12" s="700"/>
-      <c r="C12" s="704"/>
-      <c r="D12" s="704"/>
+      <c r="A12" s="457"/>
+      <c r="B12" s="454"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="703"/>
-      <c r="B13" s="699"/>
-      <c r="C13" s="704"/>
-      <c r="D13" s="704"/>
+      <c r="A13" s="457"/>
+      <c r="B13" s="453"/>
+      <c r="C13" s="458"/>
+      <c r="D13" s="458"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="703"/>
-      <c r="B14" s="701"/>
-      <c r="C14" s="704"/>
-      <c r="D14" s="704"/>
+      <c r="A14" s="457"/>
+      <c r="B14" s="455"/>
+      <c r="C14" s="458"/>
+      <c r="D14" s="458"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30628,25 +30627,25 @@
     </row>
     <row r="2" spans="1:19" ht="37.35" customHeight="1">
       <c r="A2" s="29"/>
-      <c r="B2" s="327"/>
-      <c r="C2" s="327"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="327"/>
-      <c r="F2" s="327"/>
-      <c r="G2" s="327"/>
-      <c r="H2" s="327"/>
-      <c r="I2" s="327"/>
-      <c r="J2" s="463" t="s">
+      <c r="B2" s="322"/>
+      <c r="C2" s="322"/>
+      <c r="D2" s="322"/>
+      <c r="E2" s="322"/>
+      <c r="F2" s="322"/>
+      <c r="G2" s="322"/>
+      <c r="H2" s="322"/>
+      <c r="I2" s="322"/>
+      <c r="J2" s="470" t="s">
         <v>216</v>
       </c>
-      <c r="K2" s="463"/>
-      <c r="L2" s="463"/>
-      <c r="M2" s="463"/>
-      <c r="N2" s="463"/>
-      <c r="O2" s="463"/>
-      <c r="P2" s="327"/>
-      <c r="Q2" s="327"/>
-      <c r="R2" s="327"/>
+      <c r="K2" s="470"/>
+      <c r="L2" s="470"/>
+      <c r="M2" s="470"/>
+      <c r="N2" s="470"/>
+      <c r="O2" s="470"/>
+      <c r="P2" s="322"/>
+      <c r="Q2" s="322"/>
+      <c r="R2" s="322"/>
       <c r="S2" s="28"/>
     </row>
     <row r="3" spans="1:19" ht="7.35" customHeight="1">
@@ -30672,26 +30671,26 @@
     </row>
     <row r="4" spans="1:19" ht="33" customHeight="1">
       <c r="A4" s="29"/>
-      <c r="B4" s="328" t="s">
+      <c r="B4" s="323" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="328"/>
-      <c r="D4" s="328"/>
-      <c r="E4" s="328"/>
-      <c r="F4" s="328"/>
-      <c r="G4" s="328"/>
-      <c r="H4" s="328"/>
-      <c r="I4" s="328" t="s">
+      <c r="C4" s="323"/>
+      <c r="D4" s="323"/>
+      <c r="E4" s="323"/>
+      <c r="F4" s="323"/>
+      <c r="G4" s="323"/>
+      <c r="H4" s="323"/>
+      <c r="I4" s="323" t="s">
         <v>214</v>
       </c>
-      <c r="J4" s="462" t="s">
+      <c r="J4" s="469" t="s">
         <v>215</v>
       </c>
-      <c r="K4" s="462"/>
-      <c r="L4" s="462"/>
-      <c r="M4" s="462"/>
-      <c r="N4" s="462"/>
-      <c r="O4" s="462"/>
+      <c r="K4" s="469"/>
+      <c r="L4" s="469"/>
+      <c r="M4" s="469"/>
+      <c r="N4" s="469"/>
+      <c r="O4" s="469"/>
       <c r="P4" s="235"/>
       <c r="Q4" s="235"/>
       <c r="R4" s="236"/>
@@ -30699,27 +30698,27 @@
     </row>
     <row r="5" spans="1:19" ht="29.25" customHeight="1">
       <c r="A5" s="29"/>
-      <c r="B5" s="329"/>
-      <c r="C5" s="329"/>
-      <c r="D5" s="329"/>
-      <c r="E5" s="329"/>
-      <c r="F5" s="329"/>
-      <c r="G5" s="329"/>
-      <c r="H5" s="329"/>
-      <c r="I5" s="331"/>
-      <c r="J5" s="473" t="s">
+      <c r="B5" s="324"/>
+      <c r="C5" s="324"/>
+      <c r="D5" s="324"/>
+      <c r="E5" s="324"/>
+      <c r="F5" s="324"/>
+      <c r="G5" s="324"/>
+      <c r="H5" s="324"/>
+      <c r="I5" s="326"/>
+      <c r="J5" s="480" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="473"/>
-      <c r="L5" s="473"/>
-      <c r="M5" s="473"/>
-      <c r="N5" s="470" t="s">
+      <c r="K5" s="480"/>
+      <c r="L5" s="480"/>
+      <c r="M5" s="480"/>
+      <c r="N5" s="477" t="s">
         <v>186</v>
       </c>
-      <c r="O5" s="470"/>
-      <c r="P5" s="470"/>
-      <c r="Q5" s="330"/>
-      <c r="R5" s="330"/>
+      <c r="O5" s="477"/>
+      <c r="P5" s="477"/>
+      <c r="Q5" s="325"/>
+      <c r="R5" s="325"/>
       <c r="S5" s="28"/>
     </row>
     <row r="6" spans="1:19" ht="23.25" customHeight="1" thickBot="1">
@@ -30748,12 +30747,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="29"/>
-      <c r="C8" s="474" t="str">
+      <c r="C8" s="481" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO OCTUBRE - 2024</v>
       </c>
-      <c r="D8" s="475"/>
-      <c r="E8" s="476"/>
+      <c r="D8" s="482"/>
+      <c r="E8" s="483"/>
       <c r="G8" s="66" t="s">
         <v>1</v>
       </c>
@@ -30784,7 +30783,7 @@
       <c r="H9" s="53"/>
       <c r="I9" s="53"/>
       <c r="J9" s="53"/>
-      <c r="K9" s="358"/>
+      <c r="K9" s="353"/>
       <c r="L9" s="53"/>
       <c r="M9" s="53"/>
       <c r="N9" s="53"/>
@@ -30796,11 +30795,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="C10" s="477" t="s">
+      <c r="C10" s="484" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="477"/>
-      <c r="E10" s="477"/>
+      <c r="D10" s="484"/>
+      <c r="E10" s="484"/>
       <c r="G10" s="92" t="s">
         <v>8</v>
       </c>
@@ -30825,11 +30824,11 @@
       <c r="C11" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="464">
+      <c r="D11" s="471">
         <f>R13</f>
         <v>0</v>
       </c>
-      <c r="E11" s="464"/>
+      <c r="E11" s="471"/>
       <c r="G11" s="58" t="s">
         <v>9</v>
       </c>
@@ -30854,11 +30853,11 @@
       <c r="C12" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="464">
+      <c r="D12" s="471">
         <f>R12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="464"/>
+      <c r="E12" s="471"/>
       <c r="G12" s="58" t="s">
         <v>7</v>
       </c>
@@ -30883,11 +30882,11 @@
       <c r="C13" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="464">
+      <c r="D13" s="471">
         <f>R10</f>
         <v>0</v>
       </c>
-      <c r="E13" s="464"/>
+      <c r="E13" s="471"/>
       <c r="G13" s="93" t="s">
         <v>6</v>
       </c>
@@ -30912,11 +30911,11 @@
       <c r="C14" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="464">
+      <c r="D14" s="471">
         <f>R11</f>
         <v>0</v>
       </c>
-      <c r="E14" s="464"/>
+      <c r="E14" s="471"/>
       <c r="G14" s="64" t="s">
         <v>10</v>
       </c>
@@ -30950,11 +30949,11 @@
       <c r="C15" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="472">
+      <c r="D15" s="479">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="472"/>
+      <c r="E15" s="479"/>
       <c r="H15" s="45"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
@@ -30997,11 +30996,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="29"/>
-      <c r="C24" s="465" t="s">
+      <c r="C24" s="472" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="466"/>
-      <c r="E24" s="467"/>
+      <c r="D24" s="473"/>
+      <c r="E24" s="474"/>
       <c r="S24" s="28"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -31009,11 +31008,11 @@
       <c r="C25" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="468">
+      <c r="D25" s="475">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="469"/>
+      <c r="E25" s="476"/>
       <c r="S25" s="28"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -31021,11 +31020,11 @@
       <c r="C26" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="468">
+      <c r="D26" s="475">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="469"/>
+      <c r="E26" s="476"/>
       <c r="S26" s="28"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -31033,11 +31032,11 @@
       <c r="C27" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="464">
+      <c r="D27" s="471">
         <f>SUM(M10:O10)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="464"/>
+      <c r="E27" s="471"/>
       <c r="S27" s="28"/>
     </row>
     <row r="28" spans="1:19" ht="25.5" customHeight="1">
@@ -31045,11 +31044,11 @@
       <c r="C28" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="464">
+      <c r="D28" s="471">
         <f>SUM(M11:O11)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="464"/>
+      <c r="E28" s="471"/>
       <c r="S28" s="28"/>
     </row>
     <row r="29" spans="1:19" ht="33" customHeight="1">
@@ -31057,11 +31056,11 @@
       <c r="C29" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="471">
+      <c r="D29" s="478">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="471"/>
+      <c r="E29" s="478"/>
       <c r="S29" s="28"/>
     </row>
     <row r="30" spans="1:19">
@@ -31541,37 +31540,37 @@
       <c r="AA1" s="21"/>
     </row>
     <row r="2" spans="1:27" ht="37.15" customHeight="1">
-      <c r="A2" s="478" t="s">
+      <c r="A2" s="485" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="479"/>
-      <c r="C2" s="479"/>
-      <c r="D2" s="479"/>
-      <c r="E2" s="479"/>
-      <c r="F2" s="479"/>
-      <c r="G2" s="479"/>
-      <c r="H2" s="479"/>
-      <c r="I2" s="479"/>
-      <c r="J2" s="479"/>
-      <c r="K2" s="479"/>
-      <c r="L2" s="479"/>
-      <c r="M2" s="479"/>
-      <c r="N2" s="479"/>
-      <c r="O2" s="479"/>
-      <c r="P2" s="479"/>
-      <c r="Q2" s="479"/>
-      <c r="R2" s="479"/>
-      <c r="S2" s="479"/>
-      <c r="T2" s="480" t="s">
+      <c r="B2" s="486"/>
+      <c r="C2" s="486"/>
+      <c r="D2" s="486"/>
+      <c r="E2" s="486"/>
+      <c r="F2" s="486"/>
+      <c r="G2" s="486"/>
+      <c r="H2" s="486"/>
+      <c r="I2" s="486"/>
+      <c r="J2" s="486"/>
+      <c r="K2" s="486"/>
+      <c r="L2" s="486"/>
+      <c r="M2" s="486"/>
+      <c r="N2" s="486"/>
+      <c r="O2" s="486"/>
+      <c r="P2" s="486"/>
+      <c r="Q2" s="486"/>
+      <c r="R2" s="486"/>
+      <c r="S2" s="486"/>
+      <c r="T2" s="487" t="s">
         <v>89</v>
       </c>
-      <c r="U2" s="480"/>
-      <c r="V2" s="480"/>
-      <c r="W2" s="480"/>
-      <c r="X2" s="480"/>
-      <c r="Y2" s="480"/>
-      <c r="Z2" s="480"/>
-      <c r="AA2" s="481"/>
+      <c r="U2" s="487"/>
+      <c r="V2" s="487"/>
+      <c r="W2" s="487"/>
+      <c r="X2" s="487"/>
+      <c r="Y2" s="487"/>
+      <c r="Z2" s="487"/>
+      <c r="AA2" s="488"/>
     </row>
     <row r="3" spans="1:27" ht="2.4500000000000002" customHeight="1">
       <c r="A3" s="22"/>
@@ -33330,51 +33329,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75">
-      <c r="A1" s="482" t="s">
+      <c r="A1" s="489" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="483"/>
-      <c r="C1" s="483"/>
-      <c r="D1" s="483"/>
-      <c r="E1" s="483"/>
-      <c r="F1" s="483"/>
-      <c r="G1" s="483"/>
-      <c r="H1" s="483"/>
-      <c r="I1" s="483"/>
-      <c r="J1" s="483"/>
-      <c r="K1" s="483"/>
-      <c r="L1" s="483"/>
-      <c r="M1" s="483"/>
-      <c r="N1" s="483"/>
-      <c r="O1" s="483"/>
-      <c r="P1" s="483"/>
-      <c r="Q1" s="483"/>
-      <c r="R1" s="483"/>
+      <c r="B1" s="490"/>
+      <c r="C1" s="490"/>
+      <c r="D1" s="490"/>
+      <c r="E1" s="490"/>
+      <c r="F1" s="490"/>
+      <c r="G1" s="490"/>
+      <c r="H1" s="490"/>
+      <c r="I1" s="490"/>
+      <c r="J1" s="490"/>
+      <c r="K1" s="490"/>
+      <c r="L1" s="490"/>
+      <c r="M1" s="490"/>
+      <c r="N1" s="490"/>
+      <c r="O1" s="490"/>
+      <c r="P1" s="490"/>
+      <c r="Q1" s="490"/>
+      <c r="R1" s="490"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" thickBot="1">
-      <c r="A2" s="484" t="s">
+      <c r="A2" s="491" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="485"/>
-      <c r="C2" s="485"/>
-      <c r="D2" s="485"/>
-      <c r="E2" s="485"/>
-      <c r="F2" s="485"/>
-      <c r="G2" s="485"/>
-      <c r="H2" s="485"/>
-      <c r="I2" s="485"/>
-      <c r="J2" s="485"/>
-      <c r="K2" s="485"/>
-      <c r="L2" s="485"/>
-      <c r="M2" s="485"/>
-      <c r="N2" s="485"/>
-      <c r="O2" s="485"/>
-      <c r="P2" s="485"/>
-      <c r="Q2" s="485"/>
-      <c r="R2" s="485"/>
+      <c r="B2" s="492"/>
+      <c r="C2" s="492"/>
+      <c r="D2" s="492"/>
+      <c r="E2" s="492"/>
+      <c r="F2" s="492"/>
+      <c r="G2" s="492"/>
+      <c r="H2" s="492"/>
+      <c r="I2" s="492"/>
+      <c r="J2" s="492"/>
+      <c r="K2" s="492"/>
+      <c r="L2" s="492"/>
+      <c r="M2" s="492"/>
+      <c r="N2" s="492"/>
+      <c r="O2" s="492"/>
+      <c r="P2" s="492"/>
+      <c r="Q2" s="492"/>
+      <c r="R2" s="492"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="430"/>
+      <c r="A3" s="425"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -33394,9 +33393,9 @@
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A4" s="430"/>
-      <c r="B4" s="431"/>
-      <c r="C4" s="431"/>
+      <c r="A4" s="425"/>
+      <c r="B4" s="426"/>
+      <c r="C4" s="426"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -33414,632 +33413,632 @@
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:21" ht="88.5" customHeight="1" thickBot="1">
-      <c r="A5" s="430"/>
-      <c r="B5" s="448" t="s">
+      <c r="A5" s="425"/>
+      <c r="B5" s="443" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="486" t="s">
+      <c r="C5" s="493" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="486"/>
-      <c r="E5" s="486"/>
-      <c r="F5" s="486" t="s">
+      <c r="D5" s="493"/>
+      <c r="E5" s="493"/>
+      <c r="F5" s="493" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="486"/>
-      <c r="H5" s="486"/>
-      <c r="I5" s="486" t="s">
+      <c r="G5" s="493"/>
+      <c r="H5" s="493"/>
+      <c r="I5" s="493" t="s">
         <v>232</v>
       </c>
-      <c r="J5" s="486"/>
-      <c r="K5" s="486"/>
-      <c r="L5" s="486" t="s">
+      <c r="J5" s="493"/>
+      <c r="K5" s="493"/>
+      <c r="L5" s="493" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="486"/>
-      <c r="N5" s="486"/>
-      <c r="O5" s="486" t="s">
+      <c r="M5" s="493"/>
+      <c r="N5" s="493"/>
+      <c r="O5" s="493" t="s">
         <v>233</v>
       </c>
-      <c r="P5" s="486"/>
-      <c r="Q5" s="487"/>
-      <c r="R5" s="428"/>
-      <c r="S5" s="427"/>
+      <c r="P5" s="493"/>
+      <c r="Q5" s="494"/>
+      <c r="R5" s="423"/>
+      <c r="S5" s="422"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
     </row>
     <row r="6" spans="1:21" ht="21">
-      <c r="A6" s="430"/>
-      <c r="B6" s="449" t="s">
+      <c r="A6" s="425"/>
+      <c r="B6" s="444" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="434"/>
-      <c r="D6" s="435" t="str">
+      <c r="C6" s="429"/>
+      <c r="D6" s="430" t="str">
         <f>IF(data_status_reg!$E4="bajo",0,IF(data_status_reg!$E4="medio",0.5,IF(data_status_reg!$E4="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E6" s="436"/>
-      <c r="F6" s="436"/>
-      <c r="G6" s="435" t="str">
+      <c r="E6" s="431"/>
+      <c r="F6" s="431"/>
+      <c r="G6" s="430" t="str">
         <f>IF(data_status_reg!$E20="bajo",0,IF(data_status_reg!$E20="medio",0.5,IF(data_status_reg!$E20="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H6" s="436"/>
-      <c r="I6" s="436"/>
-      <c r="J6" s="435" t="str">
+      <c r="H6" s="431"/>
+      <c r="I6" s="431"/>
+      <c r="J6" s="430" t="str">
         <f>IF(data_status_reg!$E36="bajo",0,IF(data_status_reg!$E36="medio",0.5,IF(data_status_reg!$E36="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K6" s="436"/>
-      <c r="L6" s="436"/>
-      <c r="M6" s="435" t="str">
+      <c r="K6" s="431"/>
+      <c r="L6" s="431"/>
+      <c r="M6" s="430" t="str">
         <f>IF(data_status_reg!$E52="bajo",0,IF(data_status_reg!$E52="medio",0.5,IF(data_status_reg!$E52="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N6" s="437"/>
-      <c r="O6" s="451"/>
-      <c r="P6" s="435" t="str">
+      <c r="N6" s="432"/>
+      <c r="O6" s="446"/>
+      <c r="P6" s="430" t="str">
         <f>IF(data_status_reg!$E68="bajo",0,IF(data_status_reg!$E68="medio",0.5,IF(data_status_reg!$E68="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q6" s="438"/>
-      <c r="R6" s="429"/>
+      <c r="Q6" s="433"/>
+      <c r="R6" s="424"/>
     </row>
     <row r="7" spans="1:21" ht="21">
-      <c r="A7" s="430"/>
-      <c r="B7" s="449" t="s">
+      <c r="A7" s="425"/>
+      <c r="B7" s="444" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="439"/>
-      <c r="D7" s="424" t="str">
+      <c r="C7" s="434"/>
+      <c r="D7" s="419" t="str">
         <f>IF(data_status_reg!$E5="bajo",0,IF(data_status_reg!$E5="medio",0.5,IF(data_status_reg!$E5="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E7" s="425"/>
-      <c r="F7" s="425"/>
-      <c r="G7" s="424" t="str">
+      <c r="E7" s="420"/>
+      <c r="F7" s="420"/>
+      <c r="G7" s="419" t="str">
         <f>IF(data_status_reg!$E21="bajo",0,IF(data_status_reg!$E21="medio",0.5,IF(data_status_reg!$E21="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H7" s="425"/>
-      <c r="I7" s="425"/>
-      <c r="J7" s="424" t="str">
+      <c r="H7" s="420"/>
+      <c r="I7" s="420"/>
+      <c r="J7" s="419" t="str">
         <f>IF(data_status_reg!$E37="bajo",0,IF(data_status_reg!$E37="medio",0.5,IF(data_status_reg!$E37="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K7" s="425"/>
-      <c r="L7" s="425"/>
-      <c r="M7" s="424" t="str">
+      <c r="K7" s="420"/>
+      <c r="L7" s="420"/>
+      <c r="M7" s="419" t="str">
         <f>IF(data_status_reg!$E53="bajo",0,IF(data_status_reg!$E53="medio",0.5,IF(data_status_reg!$E53="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N7" s="422"/>
-      <c r="O7" s="452"/>
-      <c r="P7" s="424" t="str">
+      <c r="N7" s="417"/>
+      <c r="O7" s="447"/>
+      <c r="P7" s="419" t="str">
         <f>IF(data_status_reg!$E69="bajo",0,IF(data_status_reg!$E69="medio",0.5,IF(data_status_reg!$E69="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q7" s="440"/>
+      <c r="Q7" s="435"/>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:21" ht="21">
-      <c r="A8" s="430"/>
-      <c r="B8" s="449" t="s">
+      <c r="A8" s="425"/>
+      <c r="B8" s="444" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="439"/>
-      <c r="D8" s="424" t="str">
+      <c r="C8" s="434"/>
+      <c r="D8" s="419" t="str">
         <f>IF(data_status_reg!$E6="bajo",0,IF(data_status_reg!$E6="medio",0.5,IF(data_status_reg!$E6="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E8" s="425"/>
-      <c r="F8" s="425"/>
-      <c r="G8" s="424" t="str">
+      <c r="E8" s="420"/>
+      <c r="F8" s="420"/>
+      <c r="G8" s="419" t="str">
         <f>IF(data_status_reg!$E22="bajo",0,IF(data_status_reg!$E22="medio",0.5,IF(data_status_reg!$E22="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H8" s="425"/>
-      <c r="I8" s="425"/>
-      <c r="J8" s="424" t="str">
+      <c r="H8" s="420"/>
+      <c r="I8" s="420"/>
+      <c r="J8" s="419" t="str">
         <f>IF(data_status_reg!$E38="bajo",0,IF(data_status_reg!$E38="medio",0.5,IF(data_status_reg!$E38="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K8" s="425"/>
-      <c r="L8" s="425"/>
-      <c r="M8" s="424" t="str">
+      <c r="K8" s="420"/>
+      <c r="L8" s="420"/>
+      <c r="M8" s="419" t="str">
         <f>IF(data_status_reg!$E54="bajo",0,IF(data_status_reg!$E54="medio",0.5,IF(data_status_reg!$E54="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N8" s="422"/>
-      <c r="O8" s="452"/>
-      <c r="P8" s="424" t="str">
+      <c r="N8" s="417"/>
+      <c r="O8" s="447"/>
+      <c r="P8" s="419" t="str">
         <f>IF(data_status_reg!$E70="bajo",0,IF(data_status_reg!$E70="medio",0.5,IF(data_status_reg!$E70="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q8" s="440"/>
+      <c r="Q8" s="435"/>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:21" ht="21">
-      <c r="A9" s="430"/>
-      <c r="B9" s="449" t="s">
+      <c r="A9" s="425"/>
+      <c r="B9" s="444" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="439"/>
-      <c r="D9" s="424" t="str">
+      <c r="C9" s="434"/>
+      <c r="D9" s="419" t="str">
         <f>IF(data_status_reg!$E7="bajo",0,IF(data_status_reg!$E7="medio",0.5,IF(data_status_reg!$E7="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E9" s="425"/>
-      <c r="F9" s="425"/>
-      <c r="G9" s="424" t="str">
+      <c r="E9" s="420"/>
+      <c r="F9" s="420"/>
+      <c r="G9" s="419" t="str">
         <f>IF(data_status_reg!$E23="bajo",0,IF(data_status_reg!$E23="medio",0.5,IF(data_status_reg!$E23="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H9" s="425"/>
-      <c r="I9" s="425"/>
-      <c r="J9" s="424" t="str">
+      <c r="H9" s="420"/>
+      <c r="I9" s="420"/>
+      <c r="J9" s="419" t="str">
         <f>IF(data_status_reg!$E39="bajo",0,IF(data_status_reg!$E39="medio",0.5,IF(data_status_reg!$E39="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K9" s="425"/>
-      <c r="L9" s="425"/>
-      <c r="M9" s="424" t="str">
+      <c r="K9" s="420"/>
+      <c r="L9" s="420"/>
+      <c r="M9" s="419" t="str">
         <f>IF(data_status_reg!$E55="bajo",0,IF(data_status_reg!$E55="medio",0.5,IF(data_status_reg!$E55="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N9" s="422"/>
-      <c r="O9" s="452"/>
-      <c r="P9" s="424" t="str">
+      <c r="N9" s="417"/>
+      <c r="O9" s="447"/>
+      <c r="P9" s="419" t="str">
         <f>IF(data_status_reg!$E71="bajo",0,IF(data_status_reg!$E71="medio",0.5,IF(data_status_reg!$E71="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q9" s="440"/>
+      <c r="Q9" s="435"/>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:21" ht="21">
-      <c r="A10" s="430"/>
-      <c r="B10" s="449" t="s">
+      <c r="A10" s="425"/>
+      <c r="B10" s="444" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="439"/>
-      <c r="D10" s="424" t="str">
+      <c r="C10" s="434"/>
+      <c r="D10" s="419" t="str">
         <f>IF(data_status_reg!$E8="bajo",0,IF(data_status_reg!$E8="medio",0.5,IF(data_status_reg!$E8="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E10" s="425"/>
-      <c r="F10" s="425"/>
-      <c r="G10" s="424" t="str">
+      <c r="E10" s="420"/>
+      <c r="F10" s="420"/>
+      <c r="G10" s="419" t="str">
         <f>IF(data_status_reg!$E24="bajo",0,IF(data_status_reg!$E24="medio",0.5,IF(data_status_reg!$E24="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H10" s="425"/>
-      <c r="I10" s="425"/>
-      <c r="J10" s="424" t="str">
+      <c r="H10" s="420"/>
+      <c r="I10" s="420"/>
+      <c r="J10" s="419" t="str">
         <f>IF(data_status_reg!$E40="bajo",0,IF(data_status_reg!$E40="medio",0.5,IF(data_status_reg!$E40="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K10" s="425"/>
-      <c r="L10" s="425"/>
-      <c r="M10" s="424" t="str">
+      <c r="K10" s="420"/>
+      <c r="L10" s="420"/>
+      <c r="M10" s="419" t="str">
         <f>IF(data_status_reg!$E56="bajo",0,IF(data_status_reg!$E56="medio",0.5,IF(data_status_reg!$E56="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N10" s="422"/>
-      <c r="O10" s="452"/>
-      <c r="P10" s="424" t="str">
+      <c r="N10" s="417"/>
+      <c r="O10" s="447"/>
+      <c r="P10" s="419" t="str">
         <f>IF(data_status_reg!$E72="bajo",0,IF(data_status_reg!$E72="medio",0.5,IF(data_status_reg!$E72="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q10" s="440"/>
+      <c r="Q10" s="435"/>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:21" ht="21">
-      <c r="A11" s="430"/>
-      <c r="B11" s="449" t="s">
+      <c r="A11" s="425"/>
+      <c r="B11" s="444" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="439"/>
-      <c r="D11" s="424" t="str">
+      <c r="C11" s="434"/>
+      <c r="D11" s="419" t="str">
         <f>IF(data_status_reg!$E9="bajo",0,IF(data_status_reg!$E9="medio",0.5,IF(data_status_reg!$E9="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E11" s="425"/>
-      <c r="F11" s="425"/>
-      <c r="G11" s="424" t="str">
+      <c r="E11" s="420"/>
+      <c r="F11" s="420"/>
+      <c r="G11" s="419" t="str">
         <f>IF(data_status_reg!$E25="bajo",0,IF(data_status_reg!$E25="medio",0.5,IF(data_status_reg!$E25="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H11" s="425"/>
-      <c r="I11" s="425"/>
-      <c r="J11" s="424" t="str">
+      <c r="H11" s="420"/>
+      <c r="I11" s="420"/>
+      <c r="J11" s="419" t="str">
         <f>IF(data_status_reg!$E41="bajo",0,IF(data_status_reg!$E41="medio",0.5,IF(data_status_reg!$E41="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K11" s="425"/>
-      <c r="L11" s="425"/>
-      <c r="M11" s="424" t="str">
+      <c r="K11" s="420"/>
+      <c r="L11" s="420"/>
+      <c r="M11" s="419" t="str">
         <f>IF(data_status_reg!$E57="bajo",0,IF(data_status_reg!$E57="medio",0.5,IF(data_status_reg!$E57="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N11" s="422"/>
-      <c r="O11" s="452"/>
-      <c r="P11" s="424" t="str">
+      <c r="N11" s="417"/>
+      <c r="O11" s="447"/>
+      <c r="P11" s="419" t="str">
         <f>IF(data_status_reg!$E73="bajo",0,IF(data_status_reg!$E73="medio",0.5,IF(data_status_reg!$E73="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q11" s="440"/>
+      <c r="Q11" s="435"/>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="21">
-      <c r="A12" s="430"/>
-      <c r="B12" s="449" t="s">
+      <c r="A12" s="425"/>
+      <c r="B12" s="444" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="439"/>
-      <c r="D12" s="424" t="str">
+      <c r="C12" s="434"/>
+      <c r="D12" s="419" t="str">
         <f>IF(data_status_reg!$E10="bajo",0,IF(data_status_reg!$E10="medio",0.5,IF(data_status_reg!$E10="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E12" s="425"/>
-      <c r="F12" s="425"/>
-      <c r="G12" s="424" t="str">
+      <c r="E12" s="420"/>
+      <c r="F12" s="420"/>
+      <c r="G12" s="419" t="str">
         <f>IF(data_status_reg!$E26="bajo",0,IF(data_status_reg!$E26="medio",0.5,IF(data_status_reg!$E26="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H12" s="425"/>
-      <c r="I12" s="426"/>
-      <c r="J12" s="424" t="str">
+      <c r="H12" s="420"/>
+      <c r="I12" s="421"/>
+      <c r="J12" s="419" t="str">
         <f>IF(data_status_reg!$E42="bajo",0,IF(data_status_reg!$E42="medio",0.5,IF(data_status_reg!$E42="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K12" s="426"/>
-      <c r="L12" s="426"/>
-      <c r="M12" s="424" t="str">
+      <c r="K12" s="421"/>
+      <c r="L12" s="421"/>
+      <c r="M12" s="419" t="str">
         <f>IF(data_status_reg!$E58="bajo",0,IF(data_status_reg!$E58="medio",0.5,IF(data_status_reg!$E58="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N12" s="423"/>
-      <c r="O12" s="453"/>
-      <c r="P12" s="424" t="str">
+      <c r="N12" s="418"/>
+      <c r="O12" s="448"/>
+      <c r="P12" s="419" t="str">
         <f>IF(data_status_reg!$E74="bajo",0,IF(data_status_reg!$E74="medio",0.5,IF(data_status_reg!$E74="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q12" s="440"/>
+      <c r="Q12" s="435"/>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:21" ht="21">
-      <c r="A13" s="430"/>
-      <c r="B13" s="449" t="s">
+      <c r="A13" s="425"/>
+      <c r="B13" s="444" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="439"/>
-      <c r="D13" s="424" t="str">
+      <c r="C13" s="434"/>
+      <c r="D13" s="419" t="str">
         <f>IF(data_status_reg!$E11="bajo",0,IF(data_status_reg!$E11="medio",0.5,IF(data_status_reg!$E11="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E13" s="425"/>
-      <c r="F13" s="425"/>
-      <c r="G13" s="424" t="str">
+      <c r="E13" s="420"/>
+      <c r="F13" s="420"/>
+      <c r="G13" s="419" t="str">
         <f>IF(data_status_reg!$E27="bajo",0,IF(data_status_reg!$E27="medio",0.5,IF(data_status_reg!$E27="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H13" s="425"/>
-      <c r="I13" s="425"/>
-      <c r="J13" s="424" t="str">
+      <c r="H13" s="420"/>
+      <c r="I13" s="420"/>
+      <c r="J13" s="419" t="str">
         <f>IF(data_status_reg!$E43="bajo",0,IF(data_status_reg!$E43="medio",0.5,IF(data_status_reg!$E43="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K13" s="425"/>
-      <c r="L13" s="425"/>
-      <c r="M13" s="424" t="str">
+      <c r="K13" s="420"/>
+      <c r="L13" s="420"/>
+      <c r="M13" s="419" t="str">
         <f>IF(data_status_reg!$E59="bajo",0,IF(data_status_reg!$E59="medio",0.5,IF(data_status_reg!$E59="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N13" s="422"/>
-      <c r="O13" s="452"/>
-      <c r="P13" s="424" t="str">
+      <c r="N13" s="417"/>
+      <c r="O13" s="447"/>
+      <c r="P13" s="419" t="str">
         <f>IF(data_status_reg!$E75="bajo",0,IF(data_status_reg!$E75="medio",0.5,IF(data_status_reg!$E75="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q13" s="440"/>
+      <c r="Q13" s="435"/>
       <c r="R13" s="3"/>
       <c r="U13" s="16"/>
     </row>
     <row r="14" spans="1:21" ht="21">
-      <c r="A14" s="430"/>
-      <c r="B14" s="449" t="s">
+      <c r="A14" s="425"/>
+      <c r="B14" s="444" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="439"/>
-      <c r="D14" s="424" t="str">
+      <c r="C14" s="434"/>
+      <c r="D14" s="419" t="str">
         <f>IF(data_status_reg!$E12="bajo",0,IF(data_status_reg!$E12="medio",0.5,IF(data_status_reg!$E12="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E14" s="425"/>
-      <c r="F14" s="425"/>
-      <c r="G14" s="424" t="str">
+      <c r="E14" s="420"/>
+      <c r="F14" s="420"/>
+      <c r="G14" s="419" t="str">
         <f>IF(data_status_reg!$E28="bajo",0,IF(data_status_reg!$E28="medio",0.5,IF(data_status_reg!$E28="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H14" s="425"/>
-      <c r="I14" s="425"/>
-      <c r="J14" s="424" t="str">
+      <c r="H14" s="420"/>
+      <c r="I14" s="420"/>
+      <c r="J14" s="419" t="str">
         <f>IF(data_status_reg!$E44="bajo",0,IF(data_status_reg!$E44="medio",0.5,IF(data_status_reg!$E44="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K14" s="425"/>
-      <c r="L14" s="425"/>
-      <c r="M14" s="424" t="str">
+      <c r="K14" s="420"/>
+      <c r="L14" s="420"/>
+      <c r="M14" s="419" t="str">
         <f>IF(data_status_reg!$E60="bajo",0,IF(data_status_reg!$E60="medio",0.5,IF(data_status_reg!$E60="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N14" s="422"/>
-      <c r="O14" s="452"/>
-      <c r="P14" s="424" t="str">
+      <c r="N14" s="417"/>
+      <c r="O14" s="447"/>
+      <c r="P14" s="419" t="str">
         <f>IF(data_status_reg!$E76="bajo",0,IF(data_status_reg!$E76="medio",0.5,IF(data_status_reg!$E76="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q14" s="440"/>
+      <c r="Q14" s="435"/>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:21" ht="21">
-      <c r="A15" s="430"/>
-      <c r="B15" s="449" t="s">
+      <c r="A15" s="425"/>
+      <c r="B15" s="444" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="439"/>
-      <c r="D15" s="424" t="str">
+      <c r="C15" s="434"/>
+      <c r="D15" s="419" t="str">
         <f>IF(data_status_reg!$E13="bajo",0,IF(data_status_reg!$E13="medio",0.5,IF(data_status_reg!$E13="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E15" s="425"/>
-      <c r="F15" s="425"/>
-      <c r="G15" s="424" t="str">
+      <c r="E15" s="420"/>
+      <c r="F15" s="420"/>
+      <c r="G15" s="419" t="str">
         <f>IF(data_status_reg!$E29="bajo",0,IF(data_status_reg!$E29="medio",0.5,IF(data_status_reg!$E29="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H15" s="425"/>
-      <c r="I15" s="426"/>
-      <c r="J15" s="424" t="str">
+      <c r="H15" s="420"/>
+      <c r="I15" s="421"/>
+      <c r="J15" s="419" t="str">
         <f>IF(data_status_reg!$E45="bajo",0,IF(data_status_reg!$E45="medio",0.5,IF(data_status_reg!$E45="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K15" s="426"/>
-      <c r="L15" s="426"/>
-      <c r="M15" s="424" t="str">
+      <c r="K15" s="421"/>
+      <c r="L15" s="421"/>
+      <c r="M15" s="419" t="str">
         <f>IF(data_status_reg!$E61="bajo",0,IF(data_status_reg!$E61="medio",0.5,IF(data_status_reg!$E61="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N15" s="423"/>
-      <c r="O15" s="453"/>
-      <c r="P15" s="424" t="str">
+      <c r="N15" s="418"/>
+      <c r="O15" s="448"/>
+      <c r="P15" s="419" t="str">
         <f>IF(data_status_reg!$E77="bajo",0,IF(data_status_reg!$E77="medio",0.5,IF(data_status_reg!$E77="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q15" s="440"/>
+      <c r="Q15" s="435"/>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:21" ht="21">
-      <c r="A16" s="430"/>
-      <c r="B16" s="449" t="s">
+      <c r="A16" s="425"/>
+      <c r="B16" s="444" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="439"/>
-      <c r="D16" s="424" t="str">
+      <c r="C16" s="434"/>
+      <c r="D16" s="419" t="str">
         <f>IF(data_status_reg!$E14="bajo",0,IF(data_status_reg!$E14="medio",0.5,IF(data_status_reg!$E14="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E16" s="425"/>
-      <c r="F16" s="425"/>
-      <c r="G16" s="424" t="str">
+      <c r="E16" s="420"/>
+      <c r="F16" s="420"/>
+      <c r="G16" s="419" t="str">
         <f>IF(data_status_reg!$E30="bajo",0,IF(data_status_reg!$E30="medio",0.5,IF(data_status_reg!$E30="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H16" s="425"/>
-      <c r="I16" s="425"/>
-      <c r="J16" s="424" t="str">
+      <c r="H16" s="420"/>
+      <c r="I16" s="420"/>
+      <c r="J16" s="419" t="str">
         <f>IF(data_status_reg!$E46="bajo",0,IF(data_status_reg!$E46="medio",0.5,IF(data_status_reg!$E46="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K16" s="425"/>
-      <c r="L16" s="425"/>
-      <c r="M16" s="424" t="str">
+      <c r="K16" s="420"/>
+      <c r="L16" s="420"/>
+      <c r="M16" s="419" t="str">
         <f>IF(data_status_reg!$E62="bajo",0,IF(data_status_reg!$E62="medio",0.5,IF(data_status_reg!$E62="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N16" s="422"/>
-      <c r="O16" s="452"/>
-      <c r="P16" s="424" t="str">
+      <c r="N16" s="417"/>
+      <c r="O16" s="447"/>
+      <c r="P16" s="419" t="str">
         <f>IF(data_status_reg!$E78="bajo",0,IF(data_status_reg!$E78="medio",0.5,IF(data_status_reg!$E78="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q16" s="440"/>
+      <c r="Q16" s="435"/>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" ht="21">
-      <c r="A17" s="430"/>
-      <c r="B17" s="449" t="s">
+      <c r="A17" s="425"/>
+      <c r="B17" s="444" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="439"/>
-      <c r="D17" s="424" t="str">
+      <c r="C17" s="434"/>
+      <c r="D17" s="419" t="str">
         <f>IF(data_status_reg!$E15="bajo",0,IF(data_status_reg!$E15="medio",0.5,IF(data_status_reg!$E15="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E17" s="425"/>
-      <c r="F17" s="425"/>
-      <c r="G17" s="424" t="str">
+      <c r="E17" s="420"/>
+      <c r="F17" s="420"/>
+      <c r="G17" s="419" t="str">
         <f>IF(data_status_reg!$E31="bajo",0,IF(data_status_reg!$E31="medio",0.5,IF(data_status_reg!$E31="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H17" s="425"/>
-      <c r="I17" s="425"/>
-      <c r="J17" s="424" t="str">
+      <c r="H17" s="420"/>
+      <c r="I17" s="420"/>
+      <c r="J17" s="419" t="str">
         <f>IF(data_status_reg!$E47="bajo",0,IF(data_status_reg!$E47="medio",0.5,IF(data_status_reg!$E47="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K17" s="425"/>
-      <c r="L17" s="425"/>
-      <c r="M17" s="424" t="str">
+      <c r="K17" s="420"/>
+      <c r="L17" s="420"/>
+      <c r="M17" s="419" t="str">
         <f>IF(data_status_reg!$E63="bajo",0,IF(data_status_reg!$E63="medio",0.5,IF(data_status_reg!$E63="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N17" s="422"/>
-      <c r="O17" s="452"/>
-      <c r="P17" s="424" t="str">
+      <c r="N17" s="417"/>
+      <c r="O17" s="447"/>
+      <c r="P17" s="419" t="str">
         <f>IF(data_status_reg!$E79="bajo",0,IF(data_status_reg!$E79="medio",0.5,IF(data_status_reg!$E79="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q17" s="440"/>
+      <c r="Q17" s="435"/>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" ht="21">
-      <c r="A18" s="430"/>
-      <c r="B18" s="449" t="s">
+      <c r="A18" s="425"/>
+      <c r="B18" s="444" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="439"/>
-      <c r="D18" s="424" t="str">
+      <c r="C18" s="434"/>
+      <c r="D18" s="419" t="str">
         <f>IF(data_status_reg!$E16="bajo",0,IF(data_status_reg!$E16="medio",0.5,IF(data_status_reg!$E16="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E18" s="425"/>
-      <c r="F18" s="425"/>
-      <c r="G18" s="455" t="s">
+      <c r="E18" s="420"/>
+      <c r="F18" s="420"/>
+      <c r="G18" s="450" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="425"/>
-      <c r="I18" s="425"/>
-      <c r="J18" s="424" t="str">
+      <c r="H18" s="420"/>
+      <c r="I18" s="420"/>
+      <c r="J18" s="419" t="str">
         <f>IF(data_status_reg!$E48="bajo",0,IF(data_status_reg!$E48="medio",0.5,IF(data_status_reg!$E48="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K18" s="425"/>
-      <c r="M18" s="424" t="str">
+      <c r="K18" s="420"/>
+      <c r="M18" s="419" t="str">
         <f>IF(data_status_reg!$E64="bajo",0,IF(data_status_reg!$E64="medio",0.5,IF(data_status_reg!$E64="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N18" s="423"/>
-      <c r="O18" s="453"/>
-      <c r="P18" s="424" t="str">
+      <c r="N18" s="418"/>
+      <c r="O18" s="448"/>
+      <c r="P18" s="419" t="str">
         <f>IF(data_status_reg!$E80="bajo",0,IF(data_status_reg!$E80="medio",0.5,IF(data_status_reg!$E80="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q18" s="440"/>
+      <c r="Q18" s="435"/>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="21">
-      <c r="A19" s="430"/>
-      <c r="B19" s="449" t="s">
+      <c r="A19" s="425"/>
+      <c r="B19" s="444" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="439"/>
-      <c r="D19" s="424" t="str">
+      <c r="C19" s="434"/>
+      <c r="D19" s="419" t="str">
         <f>IF(data_status_reg!$E17="bajo",0,IF(data_status_reg!$E17="medio",0.5,IF(data_status_reg!$E17="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E19" s="425"/>
-      <c r="F19" s="425"/>
-      <c r="G19" s="424" t="str">
+      <c r="E19" s="420"/>
+      <c r="F19" s="420"/>
+      <c r="G19" s="419" t="str">
         <f>IF(data_status_reg!$E33="bajo",0,IF(data_status_reg!$E33="medio",0.5,IF(data_status_reg!$E33="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H19" s="425"/>
-      <c r="I19" s="425"/>
-      <c r="J19" s="424" t="str">
+      <c r="H19" s="420"/>
+      <c r="I19" s="420"/>
+      <c r="J19" s="419" t="str">
         <f>IF(data_status_reg!$E49="bajo",0,IF(data_status_reg!$E49="medio",0.5,IF(data_status_reg!$E49="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K19" s="425"/>
-      <c r="L19" s="425"/>
-      <c r="M19" s="424" t="str">
+      <c r="K19" s="420"/>
+      <c r="L19" s="420"/>
+      <c r="M19" s="419" t="str">
         <f>IF(data_status_reg!$E65="bajo",0,IF(data_status_reg!$E65="medio",0.5,IF(data_status_reg!$E65="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N19" s="422"/>
-      <c r="O19" s="452"/>
-      <c r="P19" s="424" t="str">
+      <c r="N19" s="417"/>
+      <c r="O19" s="447"/>
+      <c r="P19" s="419" t="str">
         <f>IF(data_status_reg!$E81="bajo",0,IF(data_status_reg!$E81="medio",0.5,IF(data_status_reg!$E81="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q19" s="440"/>
+      <c r="Q19" s="435"/>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" ht="21">
-      <c r="A20" s="430"/>
-      <c r="B20" s="449" t="s">
+      <c r="A20" s="425"/>
+      <c r="B20" s="444" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="439"/>
-      <c r="D20" s="424" t="str">
+      <c r="C20" s="434"/>
+      <c r="D20" s="419" t="str">
         <f>IF(data_status_reg!$E18="bajo",0,IF(data_status_reg!$E18="medio",0.5,IF(data_status_reg!$E18="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E20" s="425"/>
-      <c r="F20" s="425"/>
-      <c r="G20" s="424" t="str">
+      <c r="E20" s="420"/>
+      <c r="F20" s="420"/>
+      <c r="G20" s="419" t="str">
         <f>IF(data_status_reg!$E34="bajo",0,IF(data_status_reg!$E34="medio",0.5,IF(data_status_reg!$E34="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H20" s="425"/>
-      <c r="I20" s="425"/>
-      <c r="J20" s="424" t="str">
+      <c r="H20" s="420"/>
+      <c r="I20" s="420"/>
+      <c r="J20" s="419" t="str">
         <f>IF(data_status_reg!$E50="bajo",0,IF(data_status_reg!$E50="medio",0.5,IF(data_status_reg!$E50="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K20" s="425"/>
-      <c r="L20" s="425"/>
-      <c r="M20" s="424" t="str">
+      <c r="K20" s="420"/>
+      <c r="L20" s="420"/>
+      <c r="M20" s="419" t="str">
         <f>IF(data_status_reg!$E66="bajo",0,IF(data_status_reg!$E66="medio",0.5,IF(data_status_reg!$E66="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N20" s="422"/>
-      <c r="O20" s="452"/>
-      <c r="P20" s="424" t="str">
+      <c r="N20" s="417"/>
+      <c r="O20" s="447"/>
+      <c r="P20" s="419" t="str">
         <f>IF(data_status_reg!$E82="bajo",0,IF(data_status_reg!$E82="medio",0.5,IF(data_status_reg!$E82="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q20" s="440"/>
+      <c r="Q20" s="435"/>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="21.75" thickBot="1">
-      <c r="A21" s="430"/>
-      <c r="B21" s="450" t="s">
+      <c r="A21" s="425"/>
+      <c r="B21" s="445" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="441"/>
-      <c r="D21" s="442" t="str">
+      <c r="C21" s="436"/>
+      <c r="D21" s="437" t="str">
         <f>IF(data_status_reg!$E19="bajo",0,IF(data_status_reg!$E19="medio",0.5,IF(data_status_reg!$E19="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E21" s="443"/>
-      <c r="F21" s="443"/>
-      <c r="G21" s="456" t="s">
+      <c r="E21" s="438"/>
+      <c r="F21" s="438"/>
+      <c r="G21" s="451" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="443"/>
-      <c r="I21" s="443"/>
-      <c r="J21" s="442" t="str">
+      <c r="H21" s="438"/>
+      <c r="I21" s="438"/>
+      <c r="J21" s="437" t="str">
         <f>IF(data_status_reg!$E51="bajo",0,IF(data_status_reg!$E51="medio",0.5,IF(data_status_reg!$E51="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K21" s="443"/>
-      <c r="L21" s="444"/>
-      <c r="M21" s="445" t="str">
+      <c r="K21" s="438"/>
+      <c r="L21" s="439"/>
+      <c r="M21" s="440" t="str">
         <f>IF(data_status_reg!$E67="bajo",0,IF(data_status_reg!$E67="medio",0.5,IF(data_status_reg!$E67="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N21" s="446"/>
-      <c r="O21" s="454"/>
-      <c r="P21" s="442" t="str">
+      <c r="N21" s="441"/>
+      <c r="O21" s="449"/>
+      <c r="P21" s="437" t="str">
         <f>IF(data_status_reg!$E83="bajo",0,IF(data_status_reg!$E83="medio",0.5,IF(data_status_reg!$E83="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q21" s="447"/>
+      <c r="Q21" s="442"/>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="430"/>
+      <c r="A22" s="425"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -34059,24 +34058,24 @@
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A23" s="432"/>
-      <c r="B23" s="433"/>
-      <c r="C23" s="433"/>
-      <c r="D23" s="433"/>
-      <c r="E23" s="433"/>
-      <c r="F23" s="433"/>
-      <c r="G23" s="433"/>
-      <c r="H23" s="433"/>
-      <c r="I23" s="433"/>
-      <c r="J23" s="433"/>
-      <c r="K23" s="433"/>
-      <c r="L23" s="433"/>
-      <c r="M23" s="433"/>
-      <c r="N23" s="433"/>
-      <c r="O23" s="433"/>
-      <c r="P23" s="433"/>
-      <c r="Q23" s="433"/>
-      <c r="R23" s="433"/>
+      <c r="A23" s="427"/>
+      <c r="B23" s="428"/>
+      <c r="C23" s="428"/>
+      <c r="D23" s="428"/>
+      <c r="E23" s="428"/>
+      <c r="F23" s="428"/>
+      <c r="G23" s="428"/>
+      <c r="H23" s="428"/>
+      <c r="I23" s="428"/>
+      <c r="J23" s="428"/>
+      <c r="K23" s="428"/>
+      <c r="L23" s="428"/>
+      <c r="M23" s="428"/>
+      <c r="N23" s="428"/>
+      <c r="O23" s="428"/>
+      <c r="P23" s="428"/>
+      <c r="Q23" s="428"/>
+      <c r="R23" s="428"/>
     </row>
     <row r="26" spans="1:18" outlineLevel="1"/>
     <row r="27" spans="1:18" outlineLevel="1">
@@ -35547,150 +35546,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="336"/>
-      <c r="B1" s="356"/>
-      <c r="C1" s="350"/>
-      <c r="D1" s="350"/>
-      <c r="E1" s="350"/>
-      <c r="F1" s="350"/>
-      <c r="G1" s="350"/>
-      <c r="H1" s="350"/>
-      <c r="I1" s="350"/>
-      <c r="J1" s="350"/>
-      <c r="K1" s="350"/>
-      <c r="L1" s="350"/>
-      <c r="M1" s="350"/>
-      <c r="N1" s="350"/>
-      <c r="O1" s="350"/>
-      <c r="P1" s="350"/>
+      <c r="A1" s="331"/>
+      <c r="B1" s="351"/>
+      <c r="C1" s="345"/>
+      <c r="D1" s="345"/>
+      <c r="E1" s="345"/>
+      <c r="F1" s="345"/>
+      <c r="G1" s="345"/>
+      <c r="H1" s="345"/>
+      <c r="I1" s="345"/>
+      <c r="J1" s="345"/>
+      <c r="K1" s="345"/>
+      <c r="L1" s="345"/>
+      <c r="M1" s="345"/>
+      <c r="N1" s="345"/>
+      <c r="O1" s="345"/>
+      <c r="P1" s="345"/>
     </row>
     <row r="2" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A2" s="354"/>
-      <c r="B2" s="355"/>
-      <c r="N2" s="352"/>
-      <c r="O2" s="357"/>
-      <c r="P2" s="355"/>
+      <c r="A2" s="349"/>
+      <c r="B2" s="350"/>
+      <c r="N2" s="347"/>
+      <c r="O2" s="352"/>
+      <c r="P2" s="350"/>
     </row>
     <row r="3" spans="1:16" ht="37.35" customHeight="1">
       <c r="A3" s="37"/>
-      <c r="B3" s="488" t="s">
+      <c r="B3" s="495" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="489"/>
-      <c r="D3" s="489"/>
-      <c r="E3" s="489"/>
-      <c r="F3" s="489"/>
-      <c r="G3" s="489"/>
-      <c r="H3" s="489"/>
-      <c r="I3" s="489"/>
-      <c r="J3" s="489"/>
-      <c r="K3" s="489"/>
-      <c r="L3" s="489"/>
-      <c r="M3" s="489"/>
-      <c r="N3" s="489"/>
-      <c r="O3" s="490"/>
+      <c r="C3" s="496"/>
+      <c r="D3" s="496"/>
+      <c r="E3" s="496"/>
+      <c r="F3" s="496"/>
+      <c r="G3" s="496"/>
+      <c r="H3" s="496"/>
+      <c r="I3" s="496"/>
+      <c r="J3" s="496"/>
+      <c r="K3" s="496"/>
+      <c r="L3" s="496"/>
+      <c r="M3" s="496"/>
+      <c r="N3" s="496"/>
+      <c r="O3" s="497"/>
     </row>
     <row r="4" spans="1:16" ht="7.35" customHeight="1">
       <c r="A4" s="38"/>
-      <c r="B4" s="495" t="s">
+      <c r="B4" s="502" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="496"/>
-      <c r="D4" s="496"/>
-      <c r="E4" s="496"/>
-      <c r="F4" s="496"/>
-      <c r="G4" s="496"/>
-      <c r="H4" s="496"/>
-      <c r="I4" s="496"/>
-      <c r="J4" s="496"/>
-      <c r="K4" s="496"/>
-      <c r="L4" s="496"/>
-      <c r="M4" s="496"/>
-      <c r="N4" s="496"/>
-      <c r="O4" s="351"/>
+      <c r="C4" s="503"/>
+      <c r="D4" s="503"/>
+      <c r="E4" s="503"/>
+      <c r="F4" s="503"/>
+      <c r="G4" s="503"/>
+      <c r="H4" s="503"/>
+      <c r="I4" s="503"/>
+      <c r="J4" s="503"/>
+      <c r="K4" s="503"/>
+      <c r="L4" s="503"/>
+      <c r="M4" s="503"/>
+      <c r="N4" s="503"/>
+      <c r="O4" s="346"/>
     </row>
     <row r="5" spans="1:16" ht="43.5" customHeight="1">
       <c r="A5" s="38"/>
-      <c r="B5" s="495"/>
-      <c r="C5" s="496"/>
-      <c r="D5" s="496"/>
-      <c r="E5" s="496"/>
-      <c r="F5" s="496"/>
-      <c r="G5" s="496"/>
-      <c r="H5" s="496"/>
-      <c r="I5" s="496"/>
-      <c r="J5" s="496"/>
-      <c r="K5" s="496"/>
-      <c r="L5" s="496"/>
-      <c r="M5" s="496"/>
-      <c r="N5" s="496"/>
-      <c r="O5" s="351"/>
+      <c r="B5" s="502"/>
+      <c r="C5" s="503"/>
+      <c r="D5" s="503"/>
+      <c r="E5" s="503"/>
+      <c r="F5" s="503"/>
+      <c r="G5" s="503"/>
+      <c r="H5" s="503"/>
+      <c r="I5" s="503"/>
+      <c r="J5" s="503"/>
+      <c r="K5" s="503"/>
+      <c r="L5" s="503"/>
+      <c r="M5" s="503"/>
+      <c r="N5" s="503"/>
+      <c r="O5" s="346"/>
     </row>
     <row r="6" spans="1:16" ht="43.5" customHeight="1">
       <c r="A6" s="38"/>
-      <c r="B6" s="495"/>
-      <c r="C6" s="496"/>
-      <c r="D6" s="496"/>
-      <c r="E6" s="496"/>
-      <c r="F6" s="496"/>
-      <c r="G6" s="496"/>
-      <c r="H6" s="496"/>
-      <c r="I6" s="496"/>
-      <c r="J6" s="496"/>
-      <c r="K6" s="496"/>
-      <c r="L6" s="496"/>
-      <c r="M6" s="496"/>
-      <c r="N6" s="496"/>
-      <c r="O6" s="351"/>
+      <c r="B6" s="502"/>
+      <c r="C6" s="503"/>
+      <c r="D6" s="503"/>
+      <c r="E6" s="503"/>
+      <c r="F6" s="503"/>
+      <c r="G6" s="503"/>
+      <c r="H6" s="503"/>
+      <c r="I6" s="503"/>
+      <c r="J6" s="503"/>
+      <c r="K6" s="503"/>
+      <c r="L6" s="503"/>
+      <c r="M6" s="503"/>
+      <c r="N6" s="503"/>
+      <c r="O6" s="346"/>
     </row>
     <row r="7" spans="1:16" ht="8.1" customHeight="1">
       <c r="A7" s="38"/>
-      <c r="B7" s="341"/>
-      <c r="C7" s="332"/>
-      <c r="D7" s="332"/>
-      <c r="E7" s="332"/>
-      <c r="F7" s="332"/>
-      <c r="G7" s="332"/>
-      <c r="H7" s="332"/>
-      <c r="I7" s="332"/>
-      <c r="J7" s="332"/>
-      <c r="K7" s="332"/>
-      <c r="L7" s="332"/>
-      <c r="M7" s="332"/>
-      <c r="N7" s="332"/>
-      <c r="O7" s="351"/>
+      <c r="B7" s="336"/>
+      <c r="C7" s="327"/>
+      <c r="D7" s="327"/>
+      <c r="E7" s="327"/>
+      <c r="F7" s="327"/>
+      <c r="G7" s="327"/>
+      <c r="H7" s="327"/>
+      <c r="I7" s="327"/>
+      <c r="J7" s="327"/>
+      <c r="K7" s="327"/>
+      <c r="L7" s="327"/>
+      <c r="M7" s="327"/>
+      <c r="N7" s="327"/>
+      <c r="O7" s="346"/>
     </row>
     <row r="8" spans="1:16" ht="32.25" customHeight="1" thickBot="1">
-      <c r="A8" s="340"/>
-      <c r="B8" s="342"/>
-      <c r="O8" s="351"/>
+      <c r="A8" s="335"/>
+      <c r="B8" s="337"/>
+      <c r="O8" s="346"/>
     </row>
     <row r="9" spans="1:16" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="335"/>
-      <c r="B9" s="342"/>
-      <c r="C9" s="333"/>
-      <c r="D9" s="499" t="s">
+      <c r="A9" s="330"/>
+      <c r="B9" s="337"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="506" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="497"/>
-      <c r="F9" s="497"/>
-      <c r="G9" s="498"/>
-      <c r="I9" s="333"/>
-      <c r="J9" s="504" t="s">
+      <c r="E9" s="504"/>
+      <c r="F9" s="504"/>
+      <c r="G9" s="505"/>
+      <c r="I9" s="328"/>
+      <c r="J9" s="511" t="s">
         <v>98</v>
       </c>
-      <c r="K9" s="501"/>
-      <c r="L9" s="502"/>
-      <c r="M9" s="503"/>
-      <c r="O9" s="351"/>
+      <c r="K9" s="508"/>
+      <c r="L9" s="509"/>
+      <c r="M9" s="510"/>
+      <c r="O9" s="346"/>
     </row>
     <row r="10" spans="1:16" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A10" s="335"/>
-      <c r="B10" s="344"/>
+      <c r="A10" s="330"/>
+      <c r="B10" s="339"/>
       <c r="C10" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="500"/>
+      <c r="D10" s="507"/>
       <c r="E10" s="76" t="s">
         <v>100</v>
       </c>
@@ -35703,7 +35702,7 @@
       <c r="I10" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="505"/>
+      <c r="J10" s="512"/>
       <c r="K10" s="82" t="s">
         <v>100</v>
       </c>
@@ -35713,381 +35712,381 @@
       <c r="M10" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="O10" s="351"/>
+      <c r="O10" s="346"/>
     </row>
     <row r="11" spans="1:16" ht="18.75">
-      <c r="A11" s="337"/>
-      <c r="B11" s="342"/>
+      <c r="A11" s="332"/>
+      <c r="B11" s="337"/>
       <c r="C11" s="78"/>
       <c r="D11" s="79"/>
       <c r="E11" s="79"/>
       <c r="F11" s="79"/>
       <c r="G11" s="80"/>
       <c r="I11" s="84"/>
-      <c r="J11" s="416"/>
-      <c r="K11" s="416"/>
-      <c r="L11" s="416"/>
-      <c r="M11" s="418"/>
-      <c r="O11" s="351"/>
+      <c r="J11" s="411"/>
+      <c r="K11" s="411"/>
+      <c r="L11" s="411"/>
+      <c r="M11" s="413"/>
+      <c r="O11" s="346"/>
     </row>
     <row r="12" spans="1:16" ht="18.75">
       <c r="A12" s="38"/>
-      <c r="B12" s="342"/>
+      <c r="B12" s="337"/>
       <c r="C12" s="40"/>
       <c r="D12" s="71"/>
       <c r="E12" s="71"/>
       <c r="F12" s="71"/>
       <c r="G12" s="72"/>
       <c r="I12" s="41"/>
-      <c r="J12" s="417"/>
-      <c r="K12" s="417"/>
-      <c r="L12" s="417"/>
-      <c r="M12" s="419"/>
-      <c r="N12" s="352"/>
-      <c r="O12" s="343"/>
+      <c r="J12" s="412"/>
+      <c r="K12" s="412"/>
+      <c r="L12" s="412"/>
+      <c r="M12" s="414"/>
+      <c r="N12" s="347"/>
+      <c r="O12" s="338"/>
     </row>
     <row r="13" spans="1:16" ht="18.75">
       <c r="A13" s="38"/>
-      <c r="B13" s="342"/>
+      <c r="B13" s="337"/>
       <c r="C13" s="40"/>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
       <c r="G13" s="72"/>
       <c r="I13" s="41"/>
-      <c r="J13" s="417"/>
-      <c r="K13" s="417"/>
-      <c r="L13" s="417"/>
-      <c r="M13" s="419"/>
-      <c r="N13" s="352"/>
-      <c r="O13" s="343"/>
+      <c r="J13" s="412"/>
+      <c r="K13" s="412"/>
+      <c r="L13" s="412"/>
+      <c r="M13" s="414"/>
+      <c r="N13" s="347"/>
+      <c r="O13" s="338"/>
     </row>
     <row r="14" spans="1:16" ht="18.75">
-      <c r="A14" s="338"/>
-      <c r="B14" s="342"/>
+      <c r="A14" s="333"/>
+      <c r="B14" s="337"/>
       <c r="C14" s="40"/>
       <c r="D14" s="71"/>
       <c r="E14" s="71"/>
       <c r="F14" s="71"/>
       <c r="G14" s="72"/>
       <c r="I14" s="41"/>
-      <c r="J14" s="417"/>
-      <c r="K14" s="417"/>
-      <c r="L14" s="417"/>
-      <c r="M14" s="419"/>
-      <c r="N14" s="352"/>
-      <c r="O14" s="343"/>
+      <c r="J14" s="412"/>
+      <c r="K14" s="412"/>
+      <c r="L14" s="412"/>
+      <c r="M14" s="414"/>
+      <c r="N14" s="347"/>
+      <c r="O14" s="338"/>
     </row>
     <row r="15" spans="1:16" ht="18.75">
       <c r="A15" s="38"/>
-      <c r="B15" s="342"/>
+      <c r="B15" s="337"/>
       <c r="C15" s="67"/>
       <c r="D15" s="71"/>
       <c r="E15" s="71"/>
       <c r="F15" s="71"/>
       <c r="G15" s="72"/>
       <c r="I15" s="41"/>
-      <c r="J15" s="417"/>
-      <c r="K15" s="417"/>
-      <c r="L15" s="417"/>
-      <c r="M15" s="419"/>
-      <c r="N15" s="352"/>
-      <c r="O15" s="343"/>
+      <c r="J15" s="412"/>
+      <c r="K15" s="412"/>
+      <c r="L15" s="412"/>
+      <c r="M15" s="414"/>
+      <c r="N15" s="347"/>
+      <c r="O15" s="338"/>
     </row>
     <row r="16" spans="1:16" ht="18.75">
       <c r="A16" s="38"/>
-      <c r="B16" s="342"/>
+      <c r="B16" s="337"/>
       <c r="C16" s="67"/>
       <c r="D16" s="71"/>
       <c r="E16" s="71"/>
       <c r="F16" s="71"/>
       <c r="G16" s="72"/>
       <c r="I16" s="41"/>
-      <c r="J16" s="417"/>
-      <c r="K16" s="417"/>
-      <c r="L16" s="417"/>
-      <c r="M16" s="419"/>
-      <c r="N16" s="352"/>
-      <c r="O16" s="343"/>
+      <c r="J16" s="412"/>
+      <c r="K16" s="412"/>
+      <c r="L16" s="412"/>
+      <c r="M16" s="414"/>
+      <c r="N16" s="347"/>
+      <c r="O16" s="338"/>
     </row>
     <row r="17" spans="1:15" ht="18.75">
       <c r="A17" s="38"/>
-      <c r="B17" s="342"/>
+      <c r="B17" s="337"/>
       <c r="C17" s="67"/>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
       <c r="G17" s="72"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="417"/>
-      <c r="K17" s="417"/>
-      <c r="L17" s="417"/>
-      <c r="M17" s="419"/>
-      <c r="N17" s="352"/>
-      <c r="O17" s="343"/>
+      <c r="J17" s="412"/>
+      <c r="K17" s="412"/>
+      <c r="L17" s="412"/>
+      <c r="M17" s="414"/>
+      <c r="N17" s="347"/>
+      <c r="O17" s="338"/>
     </row>
     <row r="18" spans="1:15" ht="18.75">
       <c r="A18" s="38"/>
-      <c r="B18" s="342"/>
+      <c r="B18" s="337"/>
       <c r="C18" s="67"/>
       <c r="D18" s="71"/>
       <c r="E18" s="71"/>
       <c r="F18" s="71"/>
       <c r="G18" s="72"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="417"/>
-      <c r="K18" s="417"/>
-      <c r="L18" s="417"/>
-      <c r="M18" s="419"/>
-      <c r="N18" s="352"/>
-      <c r="O18" s="343"/>
+      <c r="J18" s="412"/>
+      <c r="K18" s="412"/>
+      <c r="L18" s="412"/>
+      <c r="M18" s="414"/>
+      <c r="N18" s="347"/>
+      <c r="O18" s="338"/>
     </row>
     <row r="19" spans="1:15" ht="18.75">
       <c r="A19" s="38"/>
-      <c r="B19" s="342"/>
+      <c r="B19" s="337"/>
       <c r="C19" s="40"/>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="72"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="417"/>
-      <c r="K19" s="417"/>
-      <c r="L19" s="417"/>
-      <c r="M19" s="419"/>
-      <c r="N19" s="352"/>
-      <c r="O19" s="343"/>
+      <c r="J19" s="412"/>
+      <c r="K19" s="412"/>
+      <c r="L19" s="412"/>
+      <c r="M19" s="414"/>
+      <c r="N19" s="347"/>
+      <c r="O19" s="338"/>
     </row>
     <row r="20" spans="1:15" ht="18.75">
       <c r="A20" s="38"/>
-      <c r="B20" s="342"/>
+      <c r="B20" s="337"/>
       <c r="C20" s="40"/>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
       <c r="G20" s="72"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="417"/>
-      <c r="K20" s="417"/>
-      <c r="L20" s="417"/>
-      <c r="M20" s="419"/>
-      <c r="N20" s="352"/>
-      <c r="O20" s="343"/>
+      <c r="J20" s="412"/>
+      <c r="K20" s="412"/>
+      <c r="L20" s="412"/>
+      <c r="M20" s="414"/>
+      <c r="N20" s="347"/>
+      <c r="O20" s="338"/>
     </row>
     <row r="21" spans="1:15" ht="18.75">
       <c r="A21" s="38"/>
-      <c r="B21" s="342"/>
+      <c r="B21" s="337"/>
       <c r="C21" s="39"/>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
       <c r="G21" s="72"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="417"/>
-      <c r="K21" s="417"/>
-      <c r="L21" s="417"/>
-      <c r="M21" s="419"/>
-      <c r="N21" s="352"/>
-      <c r="O21" s="343"/>
+      <c r="J21" s="412"/>
+      <c r="K21" s="412"/>
+      <c r="L21" s="412"/>
+      <c r="M21" s="414"/>
+      <c r="N21" s="347"/>
+      <c r="O21" s="338"/>
     </row>
     <row r="22" spans="1:15" ht="18.75">
       <c r="A22" s="38"/>
-      <c r="B22" s="342"/>
+      <c r="B22" s="337"/>
       <c r="C22" s="39"/>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
       <c r="G22" s="72"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="417"/>
-      <c r="K22" s="417"/>
-      <c r="L22" s="417"/>
-      <c r="M22" s="419"/>
-      <c r="N22" s="352"/>
-      <c r="O22" s="343"/>
+      <c r="J22" s="412"/>
+      <c r="K22" s="412"/>
+      <c r="L22" s="412"/>
+      <c r="M22" s="414"/>
+      <c r="N22" s="347"/>
+      <c r="O22" s="338"/>
     </row>
     <row r="23" spans="1:15" ht="18.75">
       <c r="A23" s="38"/>
-      <c r="B23" s="342"/>
+      <c r="B23" s="337"/>
       <c r="C23" s="40"/>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
       <c r="G23" s="72"/>
       <c r="I23" s="41"/>
-      <c r="J23" s="417"/>
-      <c r="K23" s="417"/>
-      <c r="L23" s="417"/>
-      <c r="M23" s="419"/>
-      <c r="N23" s="352"/>
-      <c r="O23" s="343"/>
+      <c r="J23" s="412"/>
+      <c r="K23" s="412"/>
+      <c r="L23" s="412"/>
+      <c r="M23" s="414"/>
+      <c r="N23" s="347"/>
+      <c r="O23" s="338"/>
     </row>
     <row r="24" spans="1:15" ht="18.75">
       <c r="A24" s="38"/>
-      <c r="B24" s="342"/>
+      <c r="B24" s="337"/>
       <c r="C24" s="39"/>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
       <c r="G24" s="72"/>
       <c r="I24" s="41"/>
-      <c r="J24" s="417"/>
-      <c r="K24" s="417"/>
-      <c r="L24" s="417"/>
-      <c r="M24" s="419"/>
-      <c r="N24" s="352"/>
-      <c r="O24" s="343"/>
+      <c r="J24" s="412"/>
+      <c r="K24" s="412"/>
+      <c r="L24" s="412"/>
+      <c r="M24" s="414"/>
+      <c r="N24" s="347"/>
+      <c r="O24" s="338"/>
     </row>
     <row r="25" spans="1:15" ht="18.75">
       <c r="A25" s="38"/>
-      <c r="B25" s="342"/>
+      <c r="B25" s="337"/>
       <c r="C25" s="39"/>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="72"/>
       <c r="I25" s="41"/>
-      <c r="J25" s="417"/>
-      <c r="K25" s="417"/>
-      <c r="L25" s="417"/>
-      <c r="M25" s="419"/>
-      <c r="N25" s="352"/>
-      <c r="O25" s="343"/>
+      <c r="J25" s="412"/>
+      <c r="K25" s="412"/>
+      <c r="L25" s="412"/>
+      <c r="M25" s="414"/>
+      <c r="N25" s="347"/>
+      <c r="O25" s="338"/>
     </row>
     <row r="26" spans="1:15" ht="19.5" thickBot="1">
       <c r="A26" s="38"/>
-      <c r="B26" s="342"/>
+      <c r="B26" s="337"/>
       <c r="C26" s="39"/>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
       <c r="G26" s="72"/>
       <c r="I26" s="42"/>
-      <c r="J26" s="420"/>
-      <c r="K26" s="420"/>
-      <c r="L26" s="420"/>
-      <c r="M26" s="421"/>
-      <c r="N26" s="352"/>
-      <c r="O26" s="343"/>
+      <c r="J26" s="415"/>
+      <c r="K26" s="415"/>
+      <c r="L26" s="415"/>
+      <c r="M26" s="416"/>
+      <c r="N26" s="347"/>
+      <c r="O26" s="338"/>
     </row>
     <row r="27" spans="1:15" ht="23.25" customHeight="1">
       <c r="A27" s="38"/>
-      <c r="B27" s="342"/>
+      <c r="B27" s="337"/>
       <c r="C27" s="39"/>
       <c r="D27" s="71"/>
       <c r="E27" s="71"/>
       <c r="F27" s="71"/>
       <c r="G27" s="72"/>
-      <c r="N27" s="352"/>
-      <c r="O27" s="343"/>
+      <c r="N27" s="347"/>
+      <c r="O27" s="338"/>
     </row>
     <row r="28" spans="1:15" ht="23.25" customHeight="1" thickBot="1">
       <c r="A28" s="38"/>
-      <c r="B28" s="342"/>
-      <c r="C28" s="414"/>
+      <c r="B28" s="337"/>
+      <c r="C28" s="409"/>
       <c r="D28" s="73"/>
       <c r="E28" s="73"/>
       <c r="F28" s="73"/>
-      <c r="G28" s="415"/>
-      <c r="N28" s="352"/>
-      <c r="O28" s="343"/>
+      <c r="G28" s="410"/>
+      <c r="N28" s="347"/>
+      <c r="O28" s="338"/>
     </row>
     <row r="29" spans="1:15" ht="28.5" customHeight="1" thickBot="1">
-      <c r="B29" s="342"/>
-      <c r="N29" s="352"/>
-      <c r="O29" s="343"/>
+      <c r="B29" s="337"/>
+      <c r="N29" s="347"/>
+      <c r="O29" s="338"/>
     </row>
     <row r="30" spans="1:15" ht="42" customHeight="1" thickBot="1">
       <c r="A30" s="38"/>
-      <c r="B30" s="344"/>
-      <c r="C30" s="514" t="s">
+      <c r="B30" s="339"/>
+      <c r="C30" s="521" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="515"/>
-      <c r="E30" s="515"/>
-      <c r="F30" s="515"/>
-      <c r="G30" s="516"/>
-      <c r="N30" s="352"/>
-      <c r="O30" s="343"/>
+      <c r="D30" s="522"/>
+      <c r="E30" s="522"/>
+      <c r="F30" s="522"/>
+      <c r="G30" s="523"/>
+      <c r="N30" s="347"/>
+      <c r="O30" s="338"/>
     </row>
     <row r="31" spans="1:15" ht="49.5" customHeight="1">
       <c r="A31" s="38"/>
-      <c r="B31" s="342"/>
-      <c r="C31" s="506" t="s">
+      <c r="B31" s="337"/>
+      <c r="C31" s="513" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="507"/>
-      <c r="E31" s="508" t="s">
+      <c r="D31" s="514"/>
+      <c r="E31" s="515" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="508"/>
-      <c r="G31" s="509"/>
-      <c r="N31" s="352"/>
-      <c r="O31" s="343"/>
+      <c r="F31" s="515"/>
+      <c r="G31" s="516"/>
+      <c r="N31" s="347"/>
+      <c r="O31" s="338"/>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="38"/>
-      <c r="B32" s="342"/>
-      <c r="C32" s="510" t="s">
+      <c r="B32" s="337"/>
+      <c r="C32" s="517" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="511"/>
-      <c r="E32" s="512" t="s">
+      <c r="D32" s="518"/>
+      <c r="E32" s="519" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="512"/>
-      <c r="G32" s="513"/>
-      <c r="N32" s="352"/>
-      <c r="O32" s="343"/>
+      <c r="F32" s="519"/>
+      <c r="G32" s="520"/>
+      <c r="N32" s="347"/>
+      <c r="O32" s="338"/>
     </row>
     <row r="33" spans="1:15" ht="66.75" customHeight="1" thickBot="1">
       <c r="A33" s="38"/>
-      <c r="B33" s="344"/>
-      <c r="C33" s="491" t="s">
+      <c r="B33" s="339"/>
+      <c r="C33" s="498" t="s">
         <v>102</v>
       </c>
-      <c r="D33" s="492"/>
-      <c r="E33" s="493" t="s">
+      <c r="D33" s="499"/>
+      <c r="E33" s="500" t="s">
         <v>106</v>
       </c>
-      <c r="F33" s="493"/>
-      <c r="G33" s="494"/>
-      <c r="H33" s="348"/>
-      <c r="J33" s="350"/>
-      <c r="K33" s="350"/>
-      <c r="L33" s="350"/>
-      <c r="M33" s="350"/>
-      <c r="N33" s="350"/>
-      <c r="O33" s="351"/>
+      <c r="F33" s="500"/>
+      <c r="G33" s="501"/>
+      <c r="H33" s="343"/>
+      <c r="J33" s="345"/>
+      <c r="K33" s="345"/>
+      <c r="L33" s="345"/>
+      <c r="M33" s="345"/>
+      <c r="N33" s="345"/>
+      <c r="O33" s="346"/>
     </row>
     <row r="34" spans="1:15" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A34" s="347"/>
-      <c r="B34" s="353"/>
-      <c r="C34" s="345"/>
-      <c r="D34" s="345"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
-      <c r="G34" s="345"/>
-      <c r="H34" s="345"/>
-      <c r="I34" s="349"/>
-      <c r="J34" s="345"/>
-      <c r="K34" s="345"/>
-      <c r="L34" s="345"/>
-      <c r="M34" s="345"/>
-      <c r="N34" s="345"/>
-      <c r="O34" s="346"/>
+      <c r="A34" s="342"/>
+      <c r="B34" s="348"/>
+      <c r="C34" s="340"/>
+      <c r="D34" s="340"/>
+      <c r="E34" s="340"/>
+      <c r="F34" s="340"/>
+      <c r="G34" s="340"/>
+      <c r="H34" s="340"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="340"/>
+      <c r="K34" s="340"/>
+      <c r="L34" s="340"/>
+      <c r="M34" s="340"/>
+      <c r="N34" s="340"/>
+      <c r="O34" s="341"/>
     </row>
     <row r="35" spans="1:15" ht="12" customHeight="1">
-      <c r="A35" s="334"/>
+      <c r="A35" s="329"/>
     </row>
     <row r="36" spans="1:15" ht="8.25" customHeight="1"/>
     <row r="38" spans="1:15" ht="3" customHeight="1">
-      <c r="C38" s="339"/>
-      <c r="D38" s="339"/>
-      <c r="E38" s="339"/>
-      <c r="F38" s="339"/>
-      <c r="G38" s="339"/>
-      <c r="H38" s="339"/>
+      <c r="C38" s="334"/>
+      <c r="D38" s="334"/>
+      <c r="E38" s="334"/>
+      <c r="F38" s="334"/>
+      <c r="G38" s="334"/>
+      <c r="H38" s="334"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -36149,9 +36148,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="114"/>
-      <c r="B1" s="522"/>
-      <c r="C1" s="523"/>
-      <c r="D1" s="524"/>
+      <c r="B1" s="529"/>
+      <c r="C1" s="530"/>
+      <c r="D1" s="531"/>
       <c r="E1" s="95"/>
       <c r="F1" s="98"/>
       <c r="G1" s="96"/>
@@ -36173,10 +36172,10 @@
       <c r="E2" s="104"/>
       <c r="G2" s="106"/>
       <c r="H2" s="98"/>
-      <c r="I2" s="531" t="s">
+      <c r="I2" s="538" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="532"/>
+      <c r="J2" s="539"/>
       <c r="K2" s="109"/>
       <c r="L2" s="98"/>
       <c r="M2" s="106"/>
@@ -36209,7 +36208,7 @@
       <c r="B4" s="156" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="404"/>
+      <c r="C4" s="399"/>
       <c r="D4" s="238"/>
       <c r="F4" s="237"/>
       <c r="G4" s="127"/>
@@ -36229,10 +36228,10 @@
       <c r="B5" s="157" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="525" t="s">
+      <c r="C5" s="532" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="526"/>
+      <c r="D5" s="533"/>
       <c r="E5" s="239" t="s">
         <v>110</v>
       </c>
@@ -36259,17 +36258,17 @@
       <c r="P5" s="123"/>
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
-      <c r="B6" s="268" t="s">
+      <c r="B6" s="266" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="527"/>
-      <c r="D6" s="528"/>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="271"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="272"/>
+      <c r="C6" s="534"/>
+      <c r="D6" s="535"/>
+      <c r="E6" s="269"/>
+      <c r="F6" s="269"/>
+      <c r="G6" s="269"/>
+      <c r="H6" s="269"/>
+      <c r="I6" s="269"/>
+      <c r="J6" s="270"/>
       <c r="K6" s="135"/>
       <c r="L6" s="98"/>
       <c r="M6" s="98"/>
@@ -36280,17 +36279,17 @@
     </row>
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="115"/>
-      <c r="B7" s="269" t="s">
+      <c r="B7" s="267" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="529"/>
-      <c r="D7" s="530"/>
-      <c r="E7" s="273"/>
-      <c r="F7" s="273"/>
-      <c r="G7" s="273"/>
-      <c r="H7" s="273"/>
-      <c r="I7" s="273"/>
-      <c r="J7" s="274"/>
+      <c r="C7" s="536"/>
+      <c r="D7" s="537"/>
+      <c r="E7" s="271"/>
+      <c r="F7" s="271"/>
+      <c r="G7" s="271"/>
+      <c r="H7" s="271"/>
+      <c r="I7" s="271"/>
+      <c r="J7" s="272"/>
       <c r="L7" s="98"/>
       <c r="M7" s="98"/>
       <c r="N7" s="98"/>
@@ -36299,17 +36298,17 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="116"/>
-      <c r="B8" s="269" t="s">
+      <c r="B8" s="267" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="529"/>
-      <c r="D8" s="530"/>
-      <c r="E8" s="273"/>
-      <c r="F8" s="273"/>
-      <c r="G8" s="273"/>
-      <c r="H8" s="273"/>
-      <c r="I8" s="273"/>
-      <c r="J8" s="274"/>
+      <c r="C8" s="536"/>
+      <c r="D8" s="537"/>
+      <c r="E8" s="271"/>
+      <c r="F8" s="271"/>
+      <c r="G8" s="271"/>
+      <c r="H8" s="271"/>
+      <c r="I8" s="271"/>
+      <c r="J8" s="272"/>
       <c r="K8" s="243"/>
       <c r="L8" s="98"/>
       <c r="M8" s="98"/>
@@ -36319,17 +36318,17 @@
     </row>
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="116"/>
-      <c r="B9" s="269" t="s">
+      <c r="B9" s="267" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="529"/>
-      <c r="D9" s="530"/>
-      <c r="E9" s="273"/>
-      <c r="F9" s="273"/>
-      <c r="G9" s="273"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="273"/>
-      <c r="J9" s="274"/>
+      <c r="C9" s="536"/>
+      <c r="D9" s="537"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="272"/>
       <c r="K9" s="178"/>
       <c r="L9" s="98"/>
       <c r="M9" s="98"/>
@@ -36340,17 +36339,17 @@
     </row>
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="118"/>
-      <c r="B10" s="269" t="s">
+      <c r="B10" s="267" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="529"/>
-      <c r="D10" s="530"/>
-      <c r="E10" s="273"/>
-      <c r="F10" s="273"/>
-      <c r="G10" s="273"/>
-      <c r="H10" s="273"/>
-      <c r="I10" s="273"/>
-      <c r="J10" s="274"/>
+      <c r="C10" s="536"/>
+      <c r="D10" s="537"/>
+      <c r="E10" s="271"/>
+      <c r="F10" s="271"/>
+      <c r="G10" s="271"/>
+      <c r="H10" s="271"/>
+      <c r="I10" s="271"/>
+      <c r="J10" s="272"/>
       <c r="K10" s="135"/>
       <c r="L10" s="98"/>
       <c r="M10" s="98"/>
@@ -36360,17 +36359,17 @@
     </row>
     <row r="11" spans="1:17" ht="44.25" customHeight="1">
       <c r="A11" s="117"/>
-      <c r="B11" s="269" t="s">
+      <c r="B11" s="267" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="529"/>
-      <c r="D11" s="530"/>
-      <c r="E11" s="273"/>
-      <c r="F11" s="273"/>
-      <c r="G11" s="273"/>
-      <c r="H11" s="273"/>
-      <c r="I11" s="273"/>
-      <c r="J11" s="274"/>
+      <c r="C11" s="536"/>
+      <c r="D11" s="537"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="271"/>
+      <c r="G11" s="271"/>
+      <c r="H11" s="271"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="272"/>
       <c r="L11" s="98"/>
       <c r="M11" s="106"/>
       <c r="N11" s="98"/>
@@ -36380,17 +36379,17 @@
     </row>
     <row r="12" spans="1:17" ht="66.75" customHeight="1" thickBot="1">
       <c r="A12" s="116"/>
-      <c r="B12" s="270" t="s">
+      <c r="B12" s="268" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="517"/>
-      <c r="D12" s="518"/>
-      <c r="E12" s="275"/>
-      <c r="F12" s="275"/>
-      <c r="G12" s="275"/>
-      <c r="H12" s="275"/>
-      <c r="I12" s="275"/>
-      <c r="J12" s="276"/>
+      <c r="C12" s="524"/>
+      <c r="D12" s="525"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="273"/>
+      <c r="G12" s="273"/>
+      <c r="H12" s="273"/>
+      <c r="I12" s="273"/>
+      <c r="J12" s="274"/>
       <c r="K12" s="243"/>
       <c r="L12" s="98"/>
       <c r="M12" s="98"/>
@@ -36417,11 +36416,11 @@
     </row>
     <row r="14" spans="1:17" ht="30.75" customHeight="1">
       <c r="A14" s="120"/>
-      <c r="B14" s="385" t="s">
+      <c r="B14" s="380" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="405"/>
-      <c r="D14" s="384" t="s">
+      <c r="C14" s="400"/>
+      <c r="D14" s="379" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="148"/>
@@ -36430,7 +36429,7 @@
       <c r="H14" s="151"/>
       <c r="I14" s="152"/>
       <c r="J14" s="153"/>
-      <c r="K14" s="409"/>
+      <c r="K14" s="404"/>
       <c r="L14" s="98"/>
       <c r="M14" s="98"/>
       <c r="N14" s="125"/>
@@ -36439,15 +36438,15 @@
     </row>
     <row r="15" spans="1:17" ht="8.25" customHeight="1" thickBot="1">
       <c r="A15" s="103"/>
-      <c r="B15" s="386"/>
-      <c r="C15" s="406"/>
-      <c r="D15" s="389"/>
-      <c r="E15" s="390"/>
-      <c r="F15" s="390"/>
-      <c r="G15" s="391"/>
-      <c r="H15" s="390"/>
-      <c r="I15" s="391"/>
-      <c r="J15" s="392"/>
+      <c r="B15" s="381"/>
+      <c r="C15" s="401"/>
+      <c r="D15" s="384"/>
+      <c r="E15" s="385"/>
+      <c r="F15" s="385"/>
+      <c r="G15" s="386"/>
+      <c r="H15" s="385"/>
+      <c r="I15" s="386"/>
+      <c r="J15" s="387"/>
       <c r="L15" s="98"/>
       <c r="M15" s="123"/>
       <c r="N15" s="98"/>
@@ -36456,20 +36455,20 @@
     </row>
     <row r="16" spans="1:17" ht="74.25" customHeight="1" thickBot="1">
       <c r="A16" s="120"/>
-      <c r="B16" s="387" t="s">
+      <c r="B16" s="382" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="407"/>
-      <c r="D16" s="393" t="s">
+      <c r="C16" s="402"/>
+      <c r="D16" s="388" t="s">
         <v>130</v>
       </c>
-      <c r="E16" s="519"/>
-      <c r="F16" s="520"/>
-      <c r="G16" s="520"/>
-      <c r="H16" s="520"/>
-      <c r="I16" s="520"/>
-      <c r="J16" s="521"/>
-      <c r="K16" s="410"/>
+      <c r="E16" s="526"/>
+      <c r="F16" s="527"/>
+      <c r="G16" s="527"/>
+      <c r="H16" s="527"/>
+      <c r="I16" s="527"/>
+      <c r="J16" s="528"/>
+      <c r="K16" s="405"/>
       <c r="L16" s="134"/>
       <c r="M16" s="132"/>
       <c r="N16" s="131"/>
@@ -36477,19 +36476,19 @@
     </row>
     <row r="17" spans="1:16" ht="108.75" customHeight="1" thickBot="1">
       <c r="A17" s="103"/>
-      <c r="B17" s="388" t="s">
+      <c r="B17" s="383" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="408"/>
-      <c r="D17" s="393" t="s">
+      <c r="C17" s="403"/>
+      <c r="D17" s="388" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="519"/>
-      <c r="F17" s="520"/>
-      <c r="G17" s="520"/>
-      <c r="H17" s="520"/>
-      <c r="I17" s="520"/>
-      <c r="J17" s="521"/>
+      <c r="E17" s="526"/>
+      <c r="F17" s="527"/>
+      <c r="G17" s="527"/>
+      <c r="H17" s="527"/>
+      <c r="I17" s="527"/>
+      <c r="J17" s="528"/>
       <c r="K17" s="162"/>
       <c r="L17" s="145"/>
       <c r="M17" s="134"/>
@@ -36499,19 +36498,19 @@
     </row>
     <row r="18" spans="1:16" ht="87" customHeight="1" thickBot="1">
       <c r="A18" s="121"/>
-      <c r="B18" s="388" t="s">
+      <c r="B18" s="383" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="408"/>
-      <c r="D18" s="394" t="s">
+      <c r="C18" s="403"/>
+      <c r="D18" s="389" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="519"/>
-      <c r="F18" s="520"/>
-      <c r="G18" s="520"/>
-      <c r="H18" s="520"/>
-      <c r="I18" s="520"/>
-      <c r="J18" s="521"/>
+      <c r="E18" s="526"/>
+      <c r="F18" s="527"/>
+      <c r="G18" s="527"/>
+      <c r="H18" s="527"/>
+      <c r="I18" s="527"/>
+      <c r="J18" s="528"/>
       <c r="L18" s="134"/>
       <c r="M18" s="130"/>
       <c r="N18" s="129"/>
@@ -36522,15 +36521,15 @@
       <c r="A19" s="98"/>
       <c r="B19" s="122"/>
       <c r="C19" s="103"/>
-      <c r="D19" s="395" t="s">
+      <c r="D19" s="390" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="519"/>
-      <c r="F19" s="520"/>
-      <c r="G19" s="520"/>
-      <c r="H19" s="520"/>
-      <c r="I19" s="520"/>
-      <c r="J19" s="521"/>
+      <c r="E19" s="526"/>
+      <c r="F19" s="527"/>
+      <c r="G19" s="527"/>
+      <c r="H19" s="527"/>
+      <c r="I19" s="527"/>
+      <c r="J19" s="528"/>
       <c r="K19" s="162"/>
       <c r="L19" s="145"/>
       <c r="M19" s="130"/>
@@ -36541,34 +36540,34 @@
     <row r="20" spans="1:16" ht="108" customHeight="1" thickBot="1">
       <c r="A20" s="95"/>
       <c r="B20" s="106"/>
-      <c r="D20" s="394" t="s">
+      <c r="D20" s="389" t="s">
         <v>133</v>
       </c>
-      <c r="E20" s="519"/>
-      <c r="F20" s="520"/>
-      <c r="G20" s="520"/>
-      <c r="H20" s="520"/>
-      <c r="I20" s="520"/>
-      <c r="J20" s="521"/>
-      <c r="K20" s="411"/>
-      <c r="L20" s="396"/>
+      <c r="E20" s="526"/>
+      <c r="F20" s="527"/>
+      <c r="G20" s="527"/>
+      <c r="H20" s="527"/>
+      <c r="I20" s="527"/>
+      <c r="J20" s="528"/>
+      <c r="K20" s="406"/>
+      <c r="L20" s="391"/>
       <c r="M20" s="133"/>
       <c r="N20" s="131"/>
       <c r="O20" s="129"/>
     </row>
-    <row r="21" spans="1:16" s="285" customFormat="1" ht="81.75" customHeight="1" thickBot="1">
-      <c r="B21" s="286"/>
-      <c r="C21" s="287"/>
-      <c r="D21" s="397" t="s">
+    <row r="21" spans="1:16" s="283" customFormat="1" ht="81.75" customHeight="1" thickBot="1">
+      <c r="B21" s="284"/>
+      <c r="C21" s="285"/>
+      <c r="D21" s="392" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="519"/>
-      <c r="F21" s="520"/>
-      <c r="G21" s="520"/>
-      <c r="H21" s="520"/>
-      <c r="I21" s="520"/>
-      <c r="J21" s="521"/>
-      <c r="K21" s="412"/>
+      <c r="E21" s="526"/>
+      <c r="F21" s="527"/>
+      <c r="G21" s="527"/>
+      <c r="H21" s="527"/>
+      <c r="I21" s="527"/>
+      <c r="J21" s="528"/>
+      <c r="K21" s="407"/>
       <c r="L21" s="68"/>
       <c r="M21" s="131"/>
       <c r="N21" s="131"/>
@@ -36578,15 +36577,15 @@
       <c r="A22" s="99"/>
       <c r="B22" s="125"/>
       <c r="C22" s="103"/>
-      <c r="D22" s="413" t="s">
+      <c r="D22" s="408" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="519"/>
-      <c r="F22" s="520"/>
-      <c r="G22" s="520"/>
-      <c r="H22" s="520"/>
-      <c r="I22" s="520"/>
-      <c r="J22" s="521"/>
+      <c r="E22" s="526"/>
+      <c r="F22" s="527"/>
+      <c r="G22" s="527"/>
+      <c r="H22" s="527"/>
+      <c r="I22" s="527"/>
+      <c r="J22" s="528"/>
       <c r="L22" s="131"/>
       <c r="M22" s="134"/>
       <c r="N22" s="134"/>

--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A50B53-3119-40C9-B07B-CD69BE58A8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E610CC-5F20-4BA9-B71C-9E29B723268C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11295" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6240" yWindow="855" windowWidth="20460" windowHeight="10770" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -9768,8 +9768,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="4.4308759803029896E-2"/>
-          <c:y val="4.2570660733148004E-2"/>
+          <c:x val="4.8405549178221811E-2"/>
+          <c:y val="0"/>
           <c:w val="0.92839209892452568"/>
           <c:h val="0.87797396482705137"/>
         </c:manualLayout>
@@ -10128,6 +10128,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10697682406354191"/>
+          <c:y val="4.1212112034207132E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10164,8 +10172,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="4.0125577630341101E-2"/>
-          <c:y val="0.22576923538662858"/>
+          <c:x val="5.4958833954806087E-2"/>
+          <c:y val="0.22576931318592031"/>
           <c:w val="0.91300096501850747"/>
           <c:h val="0.57180930885866232"/>
         </c:manualLayout>
@@ -14167,10 +14175,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="1.3060085544800641E-2"/>
-          <c:y val="2.9499386517305291E-2"/>
-          <c:w val="0.97318749094521595"/>
-          <c:h val="0.92741181102362202"/>
+          <c:x val="7.7842671480226888E-3"/>
+          <c:y val="9.2114234728880497E-3"/>
+          <c:w val="0.98905294856629578"/>
+          <c:h val="0.95418813441803541"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -14435,7 +14443,7 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -27581,13 +27589,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>440379</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>294657</xdr:rowOff>
+      <xdr:rowOff>225384</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>467591</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>246847</xdr:rowOff>
+      <xdr:rowOff>177574</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -27602,7 +27610,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6744197" y="5559384"/>
+          <a:off x="6744197" y="5490111"/>
           <a:ext cx="6261758" cy="437099"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -27660,13 +27668,13 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>622218</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>283971</xdr:rowOff>
+      <xdr:rowOff>232017</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>5645728</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>218949</xdr:rowOff>
+      <xdr:rowOff>166995</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -27681,7 +27689,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13160582" y="5548698"/>
+          <a:off x="13160582" y="5496744"/>
           <a:ext cx="9612828" cy="419887"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -27754,15 +27762,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>350076</xdr:colOff>
+      <xdr:colOff>277091</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>178131</xdr:rowOff>
+      <xdr:rowOff>34636</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>439140</xdr:colOff>
+      <xdr:colOff>421821</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>178130</xdr:rowOff>
+      <xdr:rowOff>22265</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -27777,8 +27785,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6653894" y="10620995"/>
-          <a:ext cx="6323610" cy="380999"/>
+          <a:off x="6580909" y="10477500"/>
+          <a:ext cx="6379276" cy="368629"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -27833,15 +27841,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>623454</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:colOff>640772</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>5559136</xdr:colOff>
+      <xdr:colOff>5645727</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>173182</xdr:rowOff>
+      <xdr:rowOff>17319</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -27856,8 +27864,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13161818" y="10633363"/>
-          <a:ext cx="9525000" cy="363683"/>
+          <a:off x="13179136" y="10477500"/>
+          <a:ext cx="9594273" cy="363683"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -27913,14 +27921,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>450273</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>51955</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>259774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>467591</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>467592</xdr:rowOff>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>69271</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27954,14 +27962,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>311727</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>69272</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>155864</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>415637</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>51953</xdr:rowOff>
+      <xdr:rowOff>51954</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -28265,9 +28273,9 @@
       <xdr:rowOff>329046</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>5628409</xdr:colOff>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>17318</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -28301,15 +28309,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>606136</xdr:colOff>
+      <xdr:colOff>640772</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:rowOff>17317</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>5583584</xdr:colOff>
+      <xdr:colOff>5645727</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:rowOff>86590</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -29711,7 +29719,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s313200"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327222"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29776,7 +29784,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s313201"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327223"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29893,7 +29901,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s313202"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s327224"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29958,7 +29966,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s313203"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s327225"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30023,7 +30031,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s313204"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s327226"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30088,7 +30096,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s313205"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s327227"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30153,7 +30161,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s313206"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s327228"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30218,7 +30226,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s313207"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s327229"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30283,7 +30291,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s313208"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s327230"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30348,7 +30356,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s313209"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s327231"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -33094,7 +33102,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="14" name="Gráfico 13">
+        <xdr:cNvPr id="14" name="signals_chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25950EC3-1590-32C4-829D-B644D554DDF0}"/>
@@ -33118,19 +33126,19 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>44822</xdr:colOff>
+      <xdr:colOff>717176</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>291354</xdr:rowOff>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>235323</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1008529</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="15" name="Gráfico 14">
+        <xdr:cNvPr id="15" name="ptr_chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44FBD140-EB46-B47C-FF82-ACD6C1641FD5}"/>

--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E610CC-5F20-4BA9-B71C-9E29B723268C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA894187-C151-425E-9DAA-B38745F4B323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="855" windowWidth="20460" windowHeight="10770" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -7569,24 +7569,42 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="72" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7599,24 +7617,6 @@
     <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="72" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -7734,6 +7734,12 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7743,45 +7749,39 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="13" borderId="205" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="13" borderId="205" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7797,6 +7797,285 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="13" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="13" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="13" borderId="162" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="144" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7833,45 +8112,18 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7887,258 +8139,6 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="162" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="144" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -8151,161 +8151,188 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="323" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="328" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="325" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="326" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="330" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="331" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="177" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="194" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="176" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="325" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="326" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8313,12 +8340,108 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="19" borderId="156" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="308" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="309" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="310" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="79" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="79" fillId="13" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="303" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8328,128 +8451,473 @@
     <xf numFmtId="0" fontId="100" fillId="0" borderId="304" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="268" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="269" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="270" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="266" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="249" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="250" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="234" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="235" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="284" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="215" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="259" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="234" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="235" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="271" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="270" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="272" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="189" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="250" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="256" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="257" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="264" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="231" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="233" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="258" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="257" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="273" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="274" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="275" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="285" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="238" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="238" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="265" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="267" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="214" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="239" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="239" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="276" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="261" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="277" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="262" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="79" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="79" fillId="13" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="177" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="194" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="176" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="19" borderId="156" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="308" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="309" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="310" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="298" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -8457,9 +8925,6 @@
     <xf numFmtId="0" fontId="93" fillId="0" borderId="295" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8484,15 +8949,6 @@
     <xf numFmtId="0" fontId="81" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="81" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8549,462 +9005,6 @@
     </xf>
     <xf numFmtId="0" fontId="92" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="238" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="265" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="264" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="231" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="233" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="234" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="235" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="234" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="235" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="276" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="261" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="238" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="239" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="277" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="262" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="239" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="273" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="274" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="275" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="284" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="285" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="215" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="267" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="214" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="259" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="271" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="270" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="272" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="189" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="250" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="256" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="257" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="258" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="257" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="268" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="269" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="270" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="266" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="249" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="250" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -29719,7 +29719,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327222"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327372"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29784,7 +29784,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327223"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327373"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29901,7 +29901,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s327224"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s327374"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29966,7 +29966,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s327225"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s327375"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30031,7 +30031,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s327226"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s327376"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30096,7 +30096,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s327227"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s327377"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30161,7 +30161,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s327228"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s327378"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30226,7 +30226,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s327229"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s327379"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30291,7 +30291,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s327230"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s327380"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30356,7 +30356,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s327231"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s327381"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -33059,14 +33059,14 @@
       <xdr:rowOff>3407</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>112059</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>1165412</xdr:rowOff>
+      <xdr:rowOff>100852</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="12" name="Gráfico 11">
+        <xdr:cNvPr id="12" name="ptr_chart_A">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07936B31-25FA-1FAE-3F05-45B9E8B1451B}"/>
@@ -34548,9 +34548,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="655"/>
-      <c r="C1" s="656"/>
-      <c r="D1" s="657"/>
+      <c r="B1" s="653"/>
+      <c r="C1" s="654"/>
+      <c r="D1" s="655"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -34572,10 +34572,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="651" t="s">
+      <c r="I2" s="662" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="652"/>
+      <c r="J2" s="663"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -34628,10 +34628,10 @@
       <c r="B5" s="578" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="658" t="s">
+      <c r="C5" s="656" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="659"/>
+      <c r="D5" s="657"/>
       <c r="E5" s="579" t="s">
         <v>60</v>
       </c>
@@ -34793,12 +34793,12 @@
       </c>
       <c r="C13" s="493"/>
       <c r="D13" s="294"/>
-      <c r="E13" s="648"/>
-      <c r="F13" s="649"/>
-      <c r="G13" s="649"/>
-      <c r="H13" s="649"/>
-      <c r="I13" s="649"/>
-      <c r="J13" s="650"/>
+      <c r="E13" s="650"/>
+      <c r="F13" s="651"/>
+      <c r="G13" s="651"/>
+      <c r="H13" s="651"/>
+      <c r="I13" s="651"/>
+      <c r="J13" s="652"/>
       <c r="K13" s="302"/>
       <c r="L13" s="115"/>
       <c r="M13" s="115"/>
@@ -34813,12 +34813,12 @@
       </c>
       <c r="C14" s="492"/>
       <c r="D14" s="294"/>
-      <c r="E14" s="648"/>
-      <c r="F14" s="649"/>
-      <c r="G14" s="649"/>
-      <c r="H14" s="649"/>
-      <c r="I14" s="649"/>
-      <c r="J14" s="650"/>
+      <c r="E14" s="650"/>
+      <c r="F14" s="651"/>
+      <c r="G14" s="651"/>
+      <c r="H14" s="651"/>
+      <c r="I14" s="651"/>
+      <c r="J14" s="652"/>
       <c r="K14" s="136"/>
       <c r="L14" s="115"/>
       <c r="M14" s="115"/>
@@ -35382,32 +35382,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="178"/>
-      <c r="B1" s="760" t="s">
+      <c r="B1" s="678" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="761"/>
-      <c r="D1" s="761"/>
-      <c r="E1" s="761"/>
-      <c r="F1" s="761"/>
-      <c r="G1" s="761"/>
-      <c r="H1" s="761"/>
-      <c r="I1" s="761"/>
-      <c r="J1" s="761"/>
-      <c r="K1" s="761"/>
-      <c r="L1" s="761"/>
-      <c r="M1" s="761"/>
-      <c r="N1" s="761"/>
-      <c r="O1" s="761"/>
-      <c r="P1" s="761"/>
-      <c r="Q1" s="761"/>
-      <c r="R1" s="761"/>
-      <c r="S1" s="761"/>
-      <c r="T1" s="761"/>
-      <c r="U1" s="761"/>
-      <c r="V1" s="761"/>
-      <c r="W1" s="761"/>
-      <c r="X1" s="761"/>
-      <c r="Y1" s="762"/>
+      <c r="C1" s="679"/>
+      <c r="D1" s="679"/>
+      <c r="E1" s="679"/>
+      <c r="F1" s="679"/>
+      <c r="G1" s="679"/>
+      <c r="H1" s="679"/>
+      <c r="I1" s="679"/>
+      <c r="J1" s="679"/>
+      <c r="K1" s="679"/>
+      <c r="L1" s="679"/>
+      <c r="M1" s="679"/>
+      <c r="N1" s="679"/>
+      <c r="O1" s="679"/>
+      <c r="P1" s="679"/>
+      <c r="Q1" s="679"/>
+      <c r="R1" s="679"/>
+      <c r="S1" s="679"/>
+      <c r="T1" s="679"/>
+      <c r="U1" s="679"/>
+      <c r="V1" s="679"/>
+      <c r="W1" s="679"/>
+      <c r="X1" s="679"/>
+      <c r="Y1" s="680"/>
       <c r="Z1" s="173"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -35443,32 +35443,32 @@
       <c r="A3" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="763" t="s">
+      <c r="B3" s="681" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="764"/>
-      <c r="D3" s="764"/>
-      <c r="E3" s="764"/>
-      <c r="F3" s="764"/>
-      <c r="G3" s="764"/>
-      <c r="H3" s="764"/>
-      <c r="I3" s="764"/>
-      <c r="J3" s="764"/>
-      <c r="K3" s="764"/>
-      <c r="L3" s="764"/>
-      <c r="M3" s="764"/>
-      <c r="N3" s="764"/>
-      <c r="O3" s="764"/>
-      <c r="P3" s="764"/>
-      <c r="Q3" s="764"/>
-      <c r="R3" s="764"/>
-      <c r="S3" s="764"/>
-      <c r="T3" s="764"/>
-      <c r="U3" s="764"/>
-      <c r="V3" s="764"/>
-      <c r="W3" s="764"/>
-      <c r="X3" s="764"/>
-      <c r="Y3" s="765"/>
+      <c r="C3" s="682"/>
+      <c r="D3" s="682"/>
+      <c r="E3" s="682"/>
+      <c r="F3" s="682"/>
+      <c r="G3" s="682"/>
+      <c r="H3" s="682"/>
+      <c r="I3" s="682"/>
+      <c r="J3" s="682"/>
+      <c r="K3" s="682"/>
+      <c r="L3" s="682"/>
+      <c r="M3" s="682"/>
+      <c r="N3" s="682"/>
+      <c r="O3" s="682"/>
+      <c r="P3" s="682"/>
+      <c r="Q3" s="682"/>
+      <c r="R3" s="682"/>
+      <c r="S3" s="682"/>
+      <c r="T3" s="682"/>
+      <c r="U3" s="682"/>
+      <c r="V3" s="682"/>
+      <c r="W3" s="682"/>
+      <c r="X3" s="682"/>
+      <c r="Y3" s="683"/>
       <c r="Z3" s="174"/>
       <c r="AA3" s="103"/>
     </row>
@@ -35476,32 +35476,32 @@
       <c r="A4" s="180" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="766" t="s">
+      <c r="B4" s="684" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="767"/>
-      <c r="D4" s="767"/>
-      <c r="E4" s="767"/>
-      <c r="F4" s="767"/>
-      <c r="G4" s="767"/>
-      <c r="H4" s="767"/>
-      <c r="I4" s="767"/>
-      <c r="J4" s="767"/>
-      <c r="K4" s="767"/>
-      <c r="L4" s="767"/>
-      <c r="M4" s="767"/>
-      <c r="N4" s="767"/>
-      <c r="O4" s="767"/>
-      <c r="P4" s="767"/>
-      <c r="Q4" s="767"/>
-      <c r="R4" s="767"/>
-      <c r="S4" s="767"/>
-      <c r="T4" s="767"/>
-      <c r="U4" s="767"/>
-      <c r="V4" s="767"/>
-      <c r="W4" s="767"/>
-      <c r="X4" s="767"/>
-      <c r="Y4" s="768"/>
+      <c r="C4" s="685"/>
+      <c r="D4" s="685"/>
+      <c r="E4" s="685"/>
+      <c r="F4" s="685"/>
+      <c r="G4" s="685"/>
+      <c r="H4" s="685"/>
+      <c r="I4" s="685"/>
+      <c r="J4" s="685"/>
+      <c r="K4" s="685"/>
+      <c r="L4" s="685"/>
+      <c r="M4" s="685"/>
+      <c r="N4" s="685"/>
+      <c r="O4" s="685"/>
+      <c r="P4" s="685"/>
+      <c r="Q4" s="685"/>
+      <c r="R4" s="685"/>
+      <c r="S4" s="685"/>
+      <c r="T4" s="685"/>
+      <c r="U4" s="685"/>
+      <c r="V4" s="685"/>
+      <c r="W4" s="685"/>
+      <c r="X4" s="685"/>
+      <c r="Y4" s="686"/>
       <c r="Z4" s="175"/>
       <c r="AA4" s="103"/>
     </row>
@@ -35536,40 +35536,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="181"/>
-      <c r="B6" s="772" t="s">
+      <c r="B6" s="690" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="773"/>
-      <c r="D6" s="773"/>
-      <c r="E6" s="774"/>
+      <c r="C6" s="691"/>
+      <c r="D6" s="691"/>
+      <c r="E6" s="692"/>
       <c r="F6" s="89"/>
       <c r="G6" s="142"/>
-      <c r="H6" s="738" t="s">
+      <c r="H6" s="710" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="739"/>
-      <c r="J6" s="739"/>
-      <c r="K6" s="740"/>
+      <c r="I6" s="711"/>
+      <c r="J6" s="711"/>
+      <c r="K6" s="712"/>
       <c r="L6" s="89"/>
       <c r="M6" s="142"/>
-      <c r="N6" s="750" t="s">
+      <c r="N6" s="718" t="s">
         <v>95</v>
       </c>
-      <c r="O6" s="751"/>
-      <c r="P6" s="752"/>
+      <c r="O6" s="719"/>
+      <c r="P6" s="720"/>
       <c r="Q6" s="149"/>
       <c r="R6" s="151"/>
-      <c r="S6" s="745" t="s">
+      <c r="S6" s="670" t="s">
         <v>77</v>
       </c>
-      <c r="T6" s="746"/>
+      <c r="T6" s="671"/>
       <c r="U6" s="152"/>
       <c r="V6" s="156"/>
       <c r="W6" s="143"/>
-      <c r="X6" s="745" t="s">
+      <c r="X6" s="670" t="s">
         <v>78</v>
       </c>
-      <c r="Y6" s="746"/>
+      <c r="Y6" s="671"/>
       <c r="Z6" s="80"/>
       <c r="AA6" s="103"/>
     </row>
@@ -35589,36 +35589,36 @@
       </c>
       <c r="F7" s="89"/>
       <c r="G7" s="116"/>
-      <c r="H7" s="747">
+      <c r="H7" s="706">
         <f>I23</f>
         <v>0</v>
       </c>
-      <c r="I7" s="749"/>
-      <c r="J7" s="749"/>
-      <c r="K7" s="748"/>
+      <c r="I7" s="717"/>
+      <c r="J7" s="717"/>
+      <c r="K7" s="707"/>
       <c r="L7" s="89"/>
       <c r="M7" s="116"/>
-      <c r="N7" s="753">
+      <c r="N7" s="702">
         <f>L23</f>
         <v>0</v>
       </c>
-      <c r="O7" s="754"/>
-      <c r="P7" s="755"/>
+      <c r="O7" s="703"/>
+      <c r="P7" s="704"/>
       <c r="Q7" s="150"/>
       <c r="R7" s="152"/>
-      <c r="S7" s="747">
+      <c r="S7" s="706">
         <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T7" s="748"/>
+      <c r="T7" s="707"/>
       <c r="U7" s="89"/>
       <c r="V7" s="155"/>
       <c r="W7" s="82"/>
-      <c r="X7" s="747">
+      <c r="X7" s="706">
         <f>R23</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="748"/>
+      <c r="Y7" s="707"/>
       <c r="Z7" s="141"/>
       <c r="AA7" s="103"/>
     </row>
@@ -35687,27 +35687,27 @@
       <c r="D10" s="134"/>
       <c r="E10" s="199"/>
       <c r="F10" s="89"/>
-      <c r="G10" s="779" t="s">
+      <c r="G10" s="698" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="780"/>
-      <c r="I10" s="780"/>
-      <c r="J10" s="780"/>
-      <c r="K10" s="780"/>
-      <c r="L10" s="780"/>
-      <c r="M10" s="780"/>
-      <c r="N10" s="780"/>
-      <c r="O10" s="780"/>
-      <c r="P10" s="780"/>
-      <c r="Q10" s="780"/>
-      <c r="R10" s="780"/>
-      <c r="S10" s="780"/>
-      <c r="T10" s="780"/>
-      <c r="U10" s="780"/>
-      <c r="V10" s="780"/>
-      <c r="W10" s="780"/>
-      <c r="X10" s="780"/>
-      <c r="Y10" s="781"/>
+      <c r="H10" s="699"/>
+      <c r="I10" s="699"/>
+      <c r="J10" s="699"/>
+      <c r="K10" s="699"/>
+      <c r="L10" s="699"/>
+      <c r="M10" s="699"/>
+      <c r="N10" s="699"/>
+      <c r="O10" s="699"/>
+      <c r="P10" s="699"/>
+      <c r="Q10" s="699"/>
+      <c r="R10" s="699"/>
+      <c r="S10" s="699"/>
+      <c r="T10" s="699"/>
+      <c r="U10" s="699"/>
+      <c r="V10" s="699"/>
+      <c r="W10" s="699"/>
+      <c r="X10" s="699"/>
+      <c r="Y10" s="700"/>
       <c r="Z10" s="80"/>
       <c r="AA10" s="103"/>
     </row>
@@ -35718,35 +35718,35 @@
       <c r="D11" s="134"/>
       <c r="E11" s="199"/>
       <c r="F11" s="89"/>
-      <c r="G11" s="782" t="s">
+      <c r="G11" s="701" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="777"/>
-      <c r="I11" s="777" t="s">
+      <c r="H11" s="696"/>
+      <c r="I11" s="696" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="777"/>
-      <c r="K11" s="777"/>
-      <c r="L11" s="777" t="s">
+      <c r="J11" s="696"/>
+      <c r="K11" s="696"/>
+      <c r="L11" s="696" t="s">
         <v>82</v>
       </c>
-      <c r="M11" s="777"/>
-      <c r="N11" s="777"/>
-      <c r="O11" s="777" t="s">
+      <c r="M11" s="696"/>
+      <c r="N11" s="696"/>
+      <c r="O11" s="696" t="s">
         <v>83</v>
       </c>
-      <c r="P11" s="777"/>
-      <c r="Q11" s="777"/>
-      <c r="R11" s="777" t="s">
+      <c r="P11" s="696"/>
+      <c r="Q11" s="696"/>
+      <c r="R11" s="696" t="s">
         <v>78</v>
       </c>
-      <c r="S11" s="777"/>
-      <c r="T11" s="777"/>
-      <c r="U11" s="777"/>
-      <c r="V11" s="777"/>
-      <c r="W11" s="777"/>
-      <c r="X11" s="777"/>
-      <c r="Y11" s="778"/>
+      <c r="S11" s="696"/>
+      <c r="T11" s="696"/>
+      <c r="U11" s="696"/>
+      <c r="V11" s="696"/>
+      <c r="W11" s="696"/>
+      <c r="X11" s="696"/>
+      <c r="Y11" s="697"/>
       <c r="Z11" s="80"/>
       <c r="AA11" s="103"/>
     </row>
@@ -35757,33 +35757,33 @@
       <c r="D12" s="185"/>
       <c r="E12" s="199"/>
       <c r="F12" s="89"/>
-      <c r="G12" s="782"/>
-      <c r="H12" s="777"/>
-      <c r="I12" s="777"/>
-      <c r="J12" s="777"/>
-      <c r="K12" s="777"/>
-      <c r="L12" s="777"/>
-      <c r="M12" s="777"/>
-      <c r="N12" s="777"/>
-      <c r="O12" s="777"/>
-      <c r="P12" s="777"/>
-      <c r="Q12" s="777"/>
-      <c r="R12" s="704" t="s">
+      <c r="G12" s="701"/>
+      <c r="H12" s="696"/>
+      <c r="I12" s="696"/>
+      <c r="J12" s="696"/>
+      <c r="K12" s="696"/>
+      <c r="L12" s="696"/>
+      <c r="M12" s="696"/>
+      <c r="N12" s="696"/>
+      <c r="O12" s="696"/>
+      <c r="P12" s="696"/>
+      <c r="Q12" s="696"/>
+      <c r="R12" s="672" t="s">
         <v>84</v>
       </c>
-      <c r="S12" s="704"/>
-      <c r="T12" s="704" t="s">
+      <c r="S12" s="672"/>
+      <c r="T12" s="672" t="s">
         <v>85</v>
       </c>
-      <c r="U12" s="704"/>
-      <c r="V12" s="704" t="s">
+      <c r="U12" s="672"/>
+      <c r="V12" s="672" t="s">
         <v>86</v>
       </c>
-      <c r="W12" s="704"/>
-      <c r="X12" s="704" t="s">
+      <c r="W12" s="672"/>
+      <c r="X12" s="672" t="s">
         <v>87</v>
       </c>
-      <c r="Y12" s="735"/>
+      <c r="Y12" s="693"/>
       <c r="Z12" s="80"/>
       <c r="AA12" s="79"/>
     </row>
@@ -35794,25 +35794,25 @@
       <c r="D13" s="134"/>
       <c r="E13" s="199"/>
       <c r="F13" s="89"/>
-      <c r="G13" s="782"/>
-      <c r="H13" s="777"/>
-      <c r="I13" s="777"/>
-      <c r="J13" s="777"/>
-      <c r="K13" s="777"/>
-      <c r="L13" s="777"/>
-      <c r="M13" s="777"/>
-      <c r="N13" s="777"/>
-      <c r="O13" s="777"/>
-      <c r="P13" s="777"/>
-      <c r="Q13" s="777"/>
-      <c r="R13" s="704"/>
-      <c r="S13" s="704"/>
-      <c r="T13" s="704"/>
-      <c r="U13" s="704"/>
-      <c r="V13" s="704"/>
-      <c r="W13" s="704"/>
-      <c r="X13" s="775"/>
-      <c r="Y13" s="776"/>
+      <c r="G13" s="701"/>
+      <c r="H13" s="696"/>
+      <c r="I13" s="696"/>
+      <c r="J13" s="696"/>
+      <c r="K13" s="696"/>
+      <c r="L13" s="696"/>
+      <c r="M13" s="696"/>
+      <c r="N13" s="696"/>
+      <c r="O13" s="696"/>
+      <c r="P13" s="696"/>
+      <c r="Q13" s="696"/>
+      <c r="R13" s="672"/>
+      <c r="S13" s="672"/>
+      <c r="T13" s="672"/>
+      <c r="U13" s="672"/>
+      <c r="V13" s="672"/>
+      <c r="W13" s="672"/>
+      <c r="X13" s="694"/>
+      <c r="Y13" s="695"/>
       <c r="Z13" s="80"/>
       <c r="AA13" s="81"/>
     </row>
@@ -35823,27 +35823,27 @@
       <c r="D14" s="134"/>
       <c r="E14" s="199"/>
       <c r="F14" s="89"/>
-      <c r="G14" s="756" t="s">
+      <c r="G14" s="673" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="757"/>
-      <c r="I14" s="734"/>
-      <c r="J14" s="758"/>
-      <c r="K14" s="759"/>
-      <c r="L14" s="732"/>
-      <c r="M14" s="732"/>
-      <c r="N14" s="732"/>
-      <c r="O14" s="732"/>
-      <c r="P14" s="732"/>
-      <c r="Q14" s="732"/>
-      <c r="R14" s="732"/>
-      <c r="S14" s="732"/>
-      <c r="T14" s="732"/>
-      <c r="U14" s="732"/>
-      <c r="V14" s="732"/>
-      <c r="W14" s="734"/>
-      <c r="X14" s="732"/>
-      <c r="Y14" s="733"/>
+      <c r="H14" s="674"/>
+      <c r="I14" s="675"/>
+      <c r="J14" s="676"/>
+      <c r="K14" s="677"/>
+      <c r="L14" s="669"/>
+      <c r="M14" s="669"/>
+      <c r="N14" s="669"/>
+      <c r="O14" s="669"/>
+      <c r="P14" s="669"/>
+      <c r="Q14" s="669"/>
+      <c r="R14" s="669"/>
+      <c r="S14" s="669"/>
+      <c r="T14" s="669"/>
+      <c r="U14" s="669"/>
+      <c r="V14" s="669"/>
+      <c r="W14" s="675"/>
+      <c r="X14" s="669"/>
+      <c r="Y14" s="705"/>
       <c r="Z14" s="80"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -35853,27 +35853,27 @@
       <c r="D15" s="186"/>
       <c r="E15" s="200"/>
       <c r="F15" s="89"/>
-      <c r="G15" s="756" t="s">
+      <c r="G15" s="673" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="757"/>
-      <c r="I15" s="734"/>
-      <c r="J15" s="758"/>
-      <c r="K15" s="759"/>
-      <c r="L15" s="732"/>
-      <c r="M15" s="732"/>
-      <c r="N15" s="732"/>
-      <c r="O15" s="732"/>
-      <c r="P15" s="732"/>
-      <c r="Q15" s="732"/>
-      <c r="R15" s="732"/>
-      <c r="S15" s="732"/>
-      <c r="T15" s="732"/>
-      <c r="U15" s="732"/>
-      <c r="V15" s="732"/>
-      <c r="W15" s="734"/>
-      <c r="X15" s="732"/>
-      <c r="Y15" s="733"/>
+      <c r="H15" s="674"/>
+      <c r="I15" s="675"/>
+      <c r="J15" s="676"/>
+      <c r="K15" s="677"/>
+      <c r="L15" s="669"/>
+      <c r="M15" s="669"/>
+      <c r="N15" s="669"/>
+      <c r="O15" s="669"/>
+      <c r="P15" s="669"/>
+      <c r="Q15" s="669"/>
+      <c r="R15" s="669"/>
+      <c r="S15" s="669"/>
+      <c r="T15" s="669"/>
+      <c r="U15" s="669"/>
+      <c r="V15" s="669"/>
+      <c r="W15" s="675"/>
+      <c r="X15" s="669"/>
+      <c r="Y15" s="705"/>
       <c r="Z15" s="80"/>
       <c r="AA15" s="103"/>
     </row>
@@ -35884,61 +35884,61 @@
       <c r="D16" s="106"/>
       <c r="E16" s="106"/>
       <c r="F16" s="79"/>
-      <c r="G16" s="756" t="s">
+      <c r="G16" s="673" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="757"/>
-      <c r="I16" s="734"/>
-      <c r="J16" s="758"/>
-      <c r="K16" s="759"/>
-      <c r="L16" s="732"/>
-      <c r="M16" s="732"/>
-      <c r="N16" s="732"/>
-      <c r="O16" s="732"/>
-      <c r="P16" s="732"/>
-      <c r="Q16" s="732"/>
-      <c r="R16" s="732"/>
-      <c r="S16" s="732"/>
-      <c r="T16" s="732"/>
-      <c r="U16" s="732"/>
-      <c r="V16" s="732"/>
-      <c r="W16" s="734"/>
-      <c r="X16" s="732"/>
-      <c r="Y16" s="733"/>
+      <c r="H16" s="674"/>
+      <c r="I16" s="675"/>
+      <c r="J16" s="676"/>
+      <c r="K16" s="677"/>
+      <c r="L16" s="669"/>
+      <c r="M16" s="669"/>
+      <c r="N16" s="669"/>
+      <c r="O16" s="669"/>
+      <c r="P16" s="669"/>
+      <c r="Q16" s="669"/>
+      <c r="R16" s="669"/>
+      <c r="S16" s="669"/>
+      <c r="T16" s="669"/>
+      <c r="U16" s="669"/>
+      <c r="V16" s="669"/>
+      <c r="W16" s="675"/>
+      <c r="X16" s="669"/>
+      <c r="Y16" s="705"/>
       <c r="Z16" s="80"/>
       <c r="AA16" s="103"/>
       <c r="AB16" s="194"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="79"/>
-      <c r="B17" s="769" t="s">
+      <c r="B17" s="687" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="770"/>
-      <c r="D17" s="770"/>
-      <c r="E17" s="771"/>
+      <c r="C17" s="688"/>
+      <c r="D17" s="688"/>
+      <c r="E17" s="689"/>
       <c r="F17" s="89"/>
-      <c r="G17" s="756" t="s">
+      <c r="G17" s="673" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="757"/>
-      <c r="I17" s="734"/>
-      <c r="J17" s="758"/>
-      <c r="K17" s="759"/>
-      <c r="L17" s="732"/>
-      <c r="M17" s="732"/>
-      <c r="N17" s="732"/>
-      <c r="O17" s="732"/>
-      <c r="P17" s="732"/>
-      <c r="Q17" s="732"/>
-      <c r="R17" s="732"/>
-      <c r="S17" s="732"/>
-      <c r="T17" s="732"/>
-      <c r="U17" s="732"/>
-      <c r="V17" s="732"/>
-      <c r="W17" s="734"/>
-      <c r="X17" s="732"/>
-      <c r="Y17" s="733"/>
+      <c r="H17" s="674"/>
+      <c r="I17" s="675"/>
+      <c r="J17" s="676"/>
+      <c r="K17" s="677"/>
+      <c r="L17" s="669"/>
+      <c r="M17" s="669"/>
+      <c r="N17" s="669"/>
+      <c r="O17" s="669"/>
+      <c r="P17" s="669"/>
+      <c r="Q17" s="669"/>
+      <c r="R17" s="669"/>
+      <c r="S17" s="669"/>
+      <c r="T17" s="669"/>
+      <c r="U17" s="669"/>
+      <c r="V17" s="669"/>
+      <c r="W17" s="675"/>
+      <c r="X17" s="669"/>
+      <c r="Y17" s="705"/>
       <c r="Z17" s="80"/>
       <c r="AA17" s="103"/>
     </row>
@@ -35957,27 +35957,27 @@
         <v>91</v>
       </c>
       <c r="F18" s="89"/>
-      <c r="G18" s="756" t="s">
+      <c r="G18" s="673" t="s">
         <v>167</v>
       </c>
-      <c r="H18" s="757"/>
-      <c r="I18" s="734"/>
-      <c r="J18" s="758"/>
-      <c r="K18" s="759"/>
-      <c r="L18" s="732"/>
-      <c r="M18" s="732"/>
-      <c r="N18" s="732"/>
-      <c r="O18" s="732"/>
-      <c r="P18" s="732"/>
-      <c r="Q18" s="732"/>
-      <c r="R18" s="732"/>
-      <c r="S18" s="732"/>
-      <c r="T18" s="732"/>
-      <c r="U18" s="732"/>
-      <c r="V18" s="732"/>
-      <c r="W18" s="734"/>
-      <c r="X18" s="732"/>
-      <c r="Y18" s="733"/>
+      <c r="H18" s="674"/>
+      <c r="I18" s="675"/>
+      <c r="J18" s="676"/>
+      <c r="K18" s="677"/>
+      <c r="L18" s="669"/>
+      <c r="M18" s="669"/>
+      <c r="N18" s="669"/>
+      <c r="O18" s="669"/>
+      <c r="P18" s="669"/>
+      <c r="Q18" s="669"/>
+      <c r="R18" s="669"/>
+      <c r="S18" s="669"/>
+      <c r="T18" s="669"/>
+      <c r="U18" s="669"/>
+      <c r="V18" s="669"/>
+      <c r="W18" s="675"/>
+      <c r="X18" s="669"/>
+      <c r="Y18" s="705"/>
       <c r="Z18" s="80"/>
       <c r="AA18" s="103"/>
     </row>
@@ -35988,27 +35988,27 @@
       <c r="D19" s="554"/>
       <c r="E19" s="201"/>
       <c r="F19" s="89"/>
-      <c r="G19" s="756" t="s">
+      <c r="G19" s="673" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="757"/>
-      <c r="I19" s="734"/>
-      <c r="J19" s="758"/>
-      <c r="K19" s="759"/>
-      <c r="L19" s="732"/>
-      <c r="M19" s="732"/>
-      <c r="N19" s="732"/>
-      <c r="O19" s="732"/>
-      <c r="P19" s="732"/>
-      <c r="Q19" s="732"/>
-      <c r="R19" s="732"/>
-      <c r="S19" s="732"/>
-      <c r="T19" s="732"/>
-      <c r="U19" s="732"/>
-      <c r="V19" s="732"/>
-      <c r="W19" s="734"/>
-      <c r="X19" s="732"/>
-      <c r="Y19" s="733"/>
+      <c r="H19" s="674"/>
+      <c r="I19" s="675"/>
+      <c r="J19" s="676"/>
+      <c r="K19" s="677"/>
+      <c r="L19" s="669"/>
+      <c r="M19" s="669"/>
+      <c r="N19" s="669"/>
+      <c r="O19" s="669"/>
+      <c r="P19" s="669"/>
+      <c r="Q19" s="669"/>
+      <c r="R19" s="669"/>
+      <c r="S19" s="669"/>
+      <c r="T19" s="669"/>
+      <c r="U19" s="669"/>
+      <c r="V19" s="669"/>
+      <c r="W19" s="675"/>
+      <c r="X19" s="669"/>
+      <c r="Y19" s="705"/>
       <c r="Z19" s="80"/>
       <c r="AA19" s="103"/>
     </row>
@@ -36019,27 +36019,27 @@
       <c r="D20" s="554"/>
       <c r="E20" s="201"/>
       <c r="F20" s="89"/>
-      <c r="G20" s="756" t="s">
+      <c r="G20" s="673" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="757"/>
-      <c r="I20" s="734"/>
-      <c r="J20" s="758"/>
-      <c r="K20" s="759"/>
-      <c r="L20" s="732"/>
-      <c r="M20" s="732"/>
-      <c r="N20" s="732"/>
-      <c r="O20" s="732"/>
-      <c r="P20" s="732"/>
-      <c r="Q20" s="732"/>
-      <c r="R20" s="732"/>
-      <c r="S20" s="732"/>
-      <c r="T20" s="732"/>
-      <c r="U20" s="732"/>
-      <c r="V20" s="732"/>
-      <c r="W20" s="734"/>
-      <c r="X20" s="732"/>
-      <c r="Y20" s="733"/>
+      <c r="H20" s="674"/>
+      <c r="I20" s="675"/>
+      <c r="J20" s="676"/>
+      <c r="K20" s="677"/>
+      <c r="L20" s="669"/>
+      <c r="M20" s="669"/>
+      <c r="N20" s="669"/>
+      <c r="O20" s="669"/>
+      <c r="P20" s="669"/>
+      <c r="Q20" s="669"/>
+      <c r="R20" s="669"/>
+      <c r="S20" s="669"/>
+      <c r="T20" s="669"/>
+      <c r="U20" s="669"/>
+      <c r="V20" s="669"/>
+      <c r="W20" s="675"/>
+      <c r="X20" s="669"/>
+      <c r="Y20" s="705"/>
       <c r="Z20" s="80"/>
       <c r="AA20" s="103"/>
     </row>
@@ -36050,27 +36050,27 @@
       <c r="D21" s="554"/>
       <c r="E21" s="201"/>
       <c r="F21" s="89"/>
-      <c r="G21" s="756" t="s">
+      <c r="G21" s="673" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="757"/>
-      <c r="I21" s="734"/>
-      <c r="J21" s="758"/>
-      <c r="K21" s="759"/>
-      <c r="L21" s="732"/>
-      <c r="M21" s="732"/>
-      <c r="N21" s="732"/>
-      <c r="O21" s="732"/>
-      <c r="P21" s="732"/>
-      <c r="Q21" s="732"/>
-      <c r="R21" s="732"/>
-      <c r="S21" s="732"/>
-      <c r="T21" s="732"/>
-      <c r="U21" s="732"/>
-      <c r="V21" s="732"/>
-      <c r="W21" s="734"/>
-      <c r="X21" s="732"/>
-      <c r="Y21" s="733"/>
+      <c r="H21" s="674"/>
+      <c r="I21" s="675"/>
+      <c r="J21" s="676"/>
+      <c r="K21" s="677"/>
+      <c r="L21" s="669"/>
+      <c r="M21" s="669"/>
+      <c r="N21" s="669"/>
+      <c r="O21" s="669"/>
+      <c r="P21" s="669"/>
+      <c r="Q21" s="669"/>
+      <c r="R21" s="669"/>
+      <c r="S21" s="669"/>
+      <c r="T21" s="669"/>
+      <c r="U21" s="669"/>
+      <c r="V21" s="669"/>
+      <c r="W21" s="675"/>
+      <c r="X21" s="669"/>
+      <c r="Y21" s="705"/>
       <c r="Z21" s="80"/>
       <c r="AA21" s="103"/>
     </row>
@@ -36081,27 +36081,27 @@
       <c r="D22" s="554"/>
       <c r="E22" s="201"/>
       <c r="F22" s="89"/>
-      <c r="G22" s="756" t="s">
+      <c r="G22" s="673" t="s">
         <v>169</v>
       </c>
-      <c r="H22" s="757"/>
-      <c r="I22" s="734"/>
-      <c r="J22" s="758"/>
-      <c r="K22" s="759"/>
-      <c r="L22" s="732"/>
-      <c r="M22" s="732"/>
-      <c r="N22" s="732"/>
-      <c r="O22" s="732"/>
-      <c r="P22" s="732"/>
-      <c r="Q22" s="732"/>
-      <c r="R22" s="732"/>
-      <c r="S22" s="732"/>
-      <c r="T22" s="732"/>
-      <c r="U22" s="732"/>
-      <c r="V22" s="732"/>
-      <c r="W22" s="734"/>
-      <c r="X22" s="732"/>
-      <c r="Y22" s="733"/>
+      <c r="H22" s="674"/>
+      <c r="I22" s="675"/>
+      <c r="J22" s="676"/>
+      <c r="K22" s="677"/>
+      <c r="L22" s="669"/>
+      <c r="M22" s="669"/>
+      <c r="N22" s="669"/>
+      <c r="O22" s="669"/>
+      <c r="P22" s="669"/>
+      <c r="Q22" s="669"/>
+      <c r="R22" s="669"/>
+      <c r="S22" s="669"/>
+      <c r="T22" s="669"/>
+      <c r="U22" s="669"/>
+      <c r="V22" s="669"/>
+      <c r="W22" s="675"/>
+      <c r="X22" s="669"/>
+      <c r="Y22" s="705"/>
       <c r="Z22" s="80"/>
       <c r="AA22" s="103"/>
     </row>
@@ -36112,48 +36112,48 @@
       <c r="D23" s="555"/>
       <c r="E23" s="202"/>
       <c r="F23" s="89"/>
-      <c r="G23" s="744" t="s">
+      <c r="G23" s="716" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="736"/>
-      <c r="I23" s="736">
+      <c r="H23" s="708"/>
+      <c r="I23" s="708">
         <f>SUM(I14:K22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="736"/>
-      <c r="K23" s="736"/>
-      <c r="L23" s="736">
+      <c r="J23" s="708"/>
+      <c r="K23" s="708"/>
+      <c r="L23" s="708">
         <f>SUM(L14:N22)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="736"/>
-      <c r="N23" s="736"/>
-      <c r="O23" s="741">
+      <c r="M23" s="708"/>
+      <c r="N23" s="708"/>
+      <c r="O23" s="713">
         <f>SUM(O14:Q22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="742"/>
-      <c r="Q23" s="743"/>
-      <c r="R23" s="741">
+      <c r="P23" s="714"/>
+      <c r="Q23" s="715"/>
+      <c r="R23" s="713">
         <f>SUM(R14:S22)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="743"/>
-      <c r="T23" s="741">
+      <c r="S23" s="715"/>
+      <c r="T23" s="713">
         <f>SUM(T14:U22)</f>
         <v>0</v>
       </c>
-      <c r="U23" s="743"/>
-      <c r="V23" s="741">
+      <c r="U23" s="715"/>
+      <c r="V23" s="713">
         <f>SUM(V14:W22)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="742"/>
-      <c r="X23" s="736">
+      <c r="W23" s="714"/>
+      <c r="X23" s="708">
         <f>SUM(X14:Y22)</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="737"/>
+      <c r="Y23" s="709"/>
       <c r="Z23" s="80"/>
       <c r="AA23" s="103"/>
     </row>
@@ -36223,28 +36223,28 @@
       <c r="E26" s="82"/>
       <c r="F26" s="79"/>
       <c r="G26" s="135"/>
-      <c r="H26" s="699" t="s">
+      <c r="H26" s="753" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="700"/>
-      <c r="J26" s="701"/>
+      <c r="I26" s="754"/>
+      <c r="J26" s="755"/>
       <c r="K26" s="89"/>
-      <c r="L26" s="708" t="s">
+      <c r="L26" s="759" t="s">
         <v>96</v>
       </c>
-      <c r="M26" s="709"/>
-      <c r="N26" s="709"/>
-      <c r="O26" s="709"/>
-      <c r="P26" s="709"/>
-      <c r="Q26" s="709"/>
-      <c r="R26" s="709"/>
-      <c r="S26" s="709"/>
-      <c r="T26" s="709"/>
-      <c r="U26" s="709"/>
-      <c r="V26" s="709"/>
-      <c r="W26" s="709"/>
-      <c r="X26" s="709"/>
-      <c r="Y26" s="710"/>
+      <c r="M26" s="760"/>
+      <c r="N26" s="760"/>
+      <c r="O26" s="760"/>
+      <c r="P26" s="760"/>
+      <c r="Q26" s="760"/>
+      <c r="R26" s="760"/>
+      <c r="S26" s="760"/>
+      <c r="T26" s="760"/>
+      <c r="U26" s="760"/>
+      <c r="V26" s="760"/>
+      <c r="W26" s="760"/>
+      <c r="X26" s="760"/>
+      <c r="Y26" s="761"/>
       <c r="Z26" s="80"/>
       <c r="AA26" s="103"/>
     </row>
@@ -36256,41 +36256,41 @@
       <c r="E27" s="82"/>
       <c r="F27" s="79"/>
       <c r="G27" s="136"/>
-      <c r="H27" s="681">
+      <c r="H27" s="750">
         <f>Y38</f>
         <v>0</v>
       </c>
-      <c r="I27" s="682"/>
-      <c r="J27" s="683"/>
+      <c r="I27" s="751"/>
+      <c r="J27" s="752"/>
       <c r="K27" s="89"/>
-      <c r="L27" s="730" t="s">
+      <c r="L27" s="724" t="s">
         <v>80</v>
       </c>
-      <c r="M27" s="704"/>
-      <c r="N27" s="704"/>
-      <c r="O27" s="704" t="s">
+      <c r="M27" s="672"/>
+      <c r="N27" s="672"/>
+      <c r="O27" s="672" t="s">
         <v>97</v>
       </c>
-      <c r="P27" s="704"/>
-      <c r="Q27" s="704" t="s">
+      <c r="P27" s="672"/>
+      <c r="Q27" s="672" t="s">
         <v>98</v>
       </c>
-      <c r="R27" s="704"/>
-      <c r="S27" s="704" t="s">
+      <c r="R27" s="672"/>
+      <c r="S27" s="672" t="s">
         <v>99</v>
       </c>
-      <c r="T27" s="704" t="s">
+      <c r="T27" s="672" t="s">
         <v>100</v>
       </c>
-      <c r="U27" s="704"/>
-      <c r="V27" s="704" t="s">
+      <c r="U27" s="672"/>
+      <c r="V27" s="672" t="s">
         <v>101</v>
       </c>
-      <c r="W27" s="704" t="s">
+      <c r="W27" s="672" t="s">
         <v>102</v>
       </c>
-      <c r="X27" s="704"/>
-      <c r="Y27" s="735" t="s">
+      <c r="X27" s="672"/>
+      <c r="Y27" s="693" t="s">
         <v>88</v>
       </c>
       <c r="Z27" s="80"/>
@@ -36308,20 +36308,20 @@
       <c r="I28" s="82"/>
       <c r="J28" s="165"/>
       <c r="K28" s="89"/>
-      <c r="L28" s="730"/>
-      <c r="M28" s="704"/>
-      <c r="N28" s="704"/>
-      <c r="O28" s="704"/>
-      <c r="P28" s="704"/>
-      <c r="Q28" s="704"/>
-      <c r="R28" s="704"/>
-      <c r="S28" s="704"/>
-      <c r="T28" s="704"/>
-      <c r="U28" s="704"/>
-      <c r="V28" s="704"/>
-      <c r="W28" s="704"/>
-      <c r="X28" s="704"/>
-      <c r="Y28" s="735"/>
+      <c r="L28" s="724"/>
+      <c r="M28" s="672"/>
+      <c r="N28" s="672"/>
+      <c r="O28" s="672"/>
+      <c r="P28" s="672"/>
+      <c r="Q28" s="672"/>
+      <c r="R28" s="672"/>
+      <c r="S28" s="672"/>
+      <c r="T28" s="672"/>
+      <c r="U28" s="672"/>
+      <c r="V28" s="672"/>
+      <c r="W28" s="672"/>
+      <c r="X28" s="672"/>
+      <c r="Y28" s="693"/>
       <c r="Z28" s="80"/>
       <c r="AA28" s="103"/>
     </row>
@@ -36337,21 +36337,21 @@
       <c r="I29" s="166"/>
       <c r="J29" s="138"/>
       <c r="K29" s="89"/>
-      <c r="L29" s="716" t="s">
+      <c r="L29" s="721" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="684"/>
-      <c r="N29" s="684"/>
-      <c r="O29" s="684"/>
-      <c r="P29" s="684"/>
-      <c r="Q29" s="684"/>
-      <c r="R29" s="684"/>
+      <c r="M29" s="722"/>
+      <c r="N29" s="722"/>
+      <c r="O29" s="722"/>
+      <c r="P29" s="722"/>
+      <c r="Q29" s="722"/>
+      <c r="R29" s="722"/>
       <c r="S29" s="71"/>
-      <c r="T29" s="684"/>
-      <c r="U29" s="684"/>
+      <c r="T29" s="722"/>
+      <c r="U29" s="722"/>
       <c r="V29" s="71"/>
-      <c r="W29" s="684"/>
-      <c r="X29" s="685"/>
+      <c r="W29" s="722"/>
+      <c r="X29" s="723"/>
       <c r="Y29" s="195"/>
       <c r="Z29" s="80"/>
       <c r="AA29" s="103"/>
@@ -36368,21 +36368,21 @@
       <c r="I30" s="106"/>
       <c r="J30" s="106"/>
       <c r="K30" s="79"/>
-      <c r="L30" s="716" t="s">
+      <c r="L30" s="721" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="684"/>
-      <c r="N30" s="684"/>
-      <c r="O30" s="684"/>
-      <c r="P30" s="684"/>
-      <c r="Q30" s="684"/>
-      <c r="R30" s="684"/>
+      <c r="M30" s="722"/>
+      <c r="N30" s="722"/>
+      <c r="O30" s="722"/>
+      <c r="P30" s="722"/>
+      <c r="Q30" s="722"/>
+      <c r="R30" s="722"/>
       <c r="S30" s="71"/>
-      <c r="T30" s="684"/>
-      <c r="U30" s="684"/>
+      <c r="T30" s="722"/>
+      <c r="U30" s="722"/>
       <c r="V30" s="71"/>
-      <c r="W30" s="684"/>
-      <c r="X30" s="685"/>
+      <c r="W30" s="722"/>
+      <c r="X30" s="723"/>
       <c r="Y30" s="195"/>
       <c r="Z30" s="80"/>
       <c r="AA30" s="79"/>
@@ -36395,27 +36395,27 @@
       <c r="E31" s="82"/>
       <c r="F31" s="79"/>
       <c r="G31" s="135"/>
-      <c r="H31" s="705" t="s">
+      <c r="H31" s="756" t="s">
         <v>93</v>
       </c>
-      <c r="I31" s="706"/>
-      <c r="J31" s="707"/>
+      <c r="I31" s="757"/>
+      <c r="J31" s="758"/>
       <c r="K31" s="89"/>
-      <c r="L31" s="716" t="s">
+      <c r="L31" s="721" t="s">
         <v>19</v>
       </c>
-      <c r="M31" s="684"/>
-      <c r="N31" s="684"/>
-      <c r="O31" s="684"/>
-      <c r="P31" s="684"/>
-      <c r="Q31" s="684"/>
-      <c r="R31" s="684"/>
+      <c r="M31" s="722"/>
+      <c r="N31" s="722"/>
+      <c r="O31" s="722"/>
+      <c r="P31" s="722"/>
+      <c r="Q31" s="722"/>
+      <c r="R31" s="722"/>
       <c r="S31" s="71"/>
-      <c r="T31" s="684"/>
-      <c r="U31" s="684"/>
+      <c r="T31" s="722"/>
+      <c r="U31" s="722"/>
       <c r="V31" s="71"/>
-      <c r="W31" s="684"/>
-      <c r="X31" s="685"/>
+      <c r="W31" s="722"/>
+      <c r="X31" s="723"/>
       <c r="Y31" s="195"/>
       <c r="Z31" s="80"/>
       <c r="AA31" s="79"/>
@@ -36432,21 +36432,21 @@
       <c r="I32" s="82"/>
       <c r="J32" s="165"/>
       <c r="K32" s="89"/>
-      <c r="L32" s="716" t="s">
+      <c r="L32" s="721" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="684"/>
-      <c r="N32" s="684"/>
-      <c r="O32" s="684"/>
-      <c r="P32" s="684"/>
-      <c r="Q32" s="684"/>
-      <c r="R32" s="684"/>
+      <c r="M32" s="722"/>
+      <c r="N32" s="722"/>
+      <c r="O32" s="722"/>
+      <c r="P32" s="722"/>
+      <c r="Q32" s="722"/>
+      <c r="R32" s="722"/>
       <c r="S32" s="71"/>
-      <c r="T32" s="684"/>
-      <c r="U32" s="684"/>
+      <c r="T32" s="722"/>
+      <c r="U32" s="722"/>
       <c r="V32" s="71"/>
-      <c r="W32" s="684"/>
-      <c r="X32" s="685"/>
+      <c r="W32" s="722"/>
+      <c r="X32" s="723"/>
       <c r="Y32" s="195"/>
       <c r="Z32" s="80"/>
       <c r="AA32" s="79"/>
@@ -36459,28 +36459,28 @@
       <c r="E33" s="82"/>
       <c r="F33" s="79"/>
       <c r="G33" s="136"/>
-      <c r="H33" s="681">
+      <c r="H33" s="750">
         <f>O38</f>
         <v>0</v>
       </c>
-      <c r="I33" s="682"/>
-      <c r="J33" s="683"/>
+      <c r="I33" s="751"/>
+      <c r="J33" s="752"/>
       <c r="K33" s="89"/>
-      <c r="L33" s="716" t="s">
+      <c r="L33" s="721" t="s">
         <v>167</v>
       </c>
-      <c r="M33" s="684"/>
-      <c r="N33" s="684"/>
-      <c r="O33" s="684"/>
-      <c r="P33" s="684"/>
-      <c r="Q33" s="684"/>
-      <c r="R33" s="684"/>
+      <c r="M33" s="722"/>
+      <c r="N33" s="722"/>
+      <c r="O33" s="722"/>
+      <c r="P33" s="722"/>
+      <c r="Q33" s="722"/>
+      <c r="R33" s="722"/>
       <c r="S33" s="71"/>
-      <c r="T33" s="684"/>
-      <c r="U33" s="684"/>
+      <c r="T33" s="722"/>
+      <c r="U33" s="722"/>
       <c r="V33" s="71"/>
-      <c r="W33" s="684"/>
-      <c r="X33" s="685"/>
+      <c r="W33" s="722"/>
+      <c r="X33" s="723"/>
       <c r="Y33" s="195"/>
       <c r="Z33" s="80"/>
       <c r="AA33" s="193"/>
@@ -36497,21 +36497,21 @@
       <c r="I34" s="82"/>
       <c r="J34" s="165"/>
       <c r="K34" s="89"/>
-      <c r="L34" s="716" t="s">
+      <c r="L34" s="721" t="s">
         <v>168</v>
       </c>
-      <c r="M34" s="684"/>
-      <c r="N34" s="684"/>
-      <c r="O34" s="684"/>
-      <c r="P34" s="684"/>
-      <c r="Q34" s="684"/>
-      <c r="R34" s="684"/>
+      <c r="M34" s="722"/>
+      <c r="N34" s="722"/>
+      <c r="O34" s="722"/>
+      <c r="P34" s="722"/>
+      <c r="Q34" s="722"/>
+      <c r="R34" s="722"/>
       <c r="S34" s="71"/>
-      <c r="T34" s="684"/>
-      <c r="U34" s="684"/>
+      <c r="T34" s="722"/>
+      <c r="U34" s="722"/>
       <c r="V34" s="71"/>
-      <c r="W34" s="684"/>
-      <c r="X34" s="685"/>
+      <c r="W34" s="722"/>
+      <c r="X34" s="723"/>
       <c r="Y34" s="195"/>
       <c r="Z34" s="80"/>
       <c r="AA34" s="79"/>
@@ -36528,21 +36528,21 @@
       <c r="I35" s="166"/>
       <c r="J35" s="138"/>
       <c r="K35" s="89"/>
-      <c r="L35" s="716" t="s">
+      <c r="L35" s="721" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="684"/>
-      <c r="N35" s="684"/>
-      <c r="O35" s="711"/>
-      <c r="P35" s="711"/>
-      <c r="Q35" s="711"/>
-      <c r="R35" s="711"/>
+      <c r="M35" s="722"/>
+      <c r="N35" s="722"/>
+      <c r="O35" s="725"/>
+      <c r="P35" s="725"/>
+      <c r="Q35" s="725"/>
+      <c r="R35" s="725"/>
       <c r="S35" s="162"/>
-      <c r="T35" s="711"/>
-      <c r="U35" s="711"/>
+      <c r="T35" s="725"/>
+      <c r="U35" s="725"/>
       <c r="V35" s="162"/>
-      <c r="W35" s="711"/>
-      <c r="X35" s="731"/>
+      <c r="W35" s="725"/>
+      <c r="X35" s="726"/>
       <c r="Y35" s="195"/>
       <c r="Z35" s="80"/>
       <c r="AA35" s="103"/>
@@ -36559,21 +36559,21 @@
       <c r="I36" s="106"/>
       <c r="J36" s="106"/>
       <c r="K36" s="79"/>
-      <c r="L36" s="716" t="s">
+      <c r="L36" s="721" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="684"/>
-      <c r="N36" s="685"/>
-      <c r="O36" s="688"/>
-      <c r="P36" s="688"/>
-      <c r="Q36" s="688"/>
-      <c r="R36" s="688"/>
+      <c r="M36" s="722"/>
+      <c r="N36" s="723"/>
+      <c r="O36" s="727"/>
+      <c r="P36" s="727"/>
+      <c r="Q36" s="727"/>
+      <c r="R36" s="727"/>
       <c r="S36" s="163"/>
-      <c r="T36" s="688"/>
-      <c r="U36" s="688"/>
+      <c r="T36" s="727"/>
+      <c r="U36" s="727"/>
       <c r="V36" s="163"/>
-      <c r="W36" s="688"/>
-      <c r="X36" s="712"/>
+      <c r="W36" s="727"/>
+      <c r="X36" s="728"/>
       <c r="Y36" s="195"/>
       <c r="Z36" s="80"/>
       <c r="AA36" s="79"/>
@@ -36586,27 +36586,27 @@
       <c r="E37" s="82"/>
       <c r="F37" s="79"/>
       <c r="G37" s="135"/>
-      <c r="H37" s="705" t="s">
+      <c r="H37" s="756" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="706"/>
-      <c r="J37" s="707"/>
+      <c r="I37" s="757"/>
+      <c r="J37" s="758"/>
       <c r="K37" s="89"/>
-      <c r="L37" s="716" t="s">
+      <c r="L37" s="721" t="s">
         <v>169</v>
       </c>
-      <c r="M37" s="684"/>
-      <c r="N37" s="685"/>
-      <c r="O37" s="688"/>
-      <c r="P37" s="688"/>
-      <c r="Q37" s="688"/>
-      <c r="R37" s="688"/>
+      <c r="M37" s="722"/>
+      <c r="N37" s="723"/>
+      <c r="O37" s="727"/>
+      <c r="P37" s="727"/>
+      <c r="Q37" s="727"/>
+      <c r="R37" s="727"/>
       <c r="S37" s="163"/>
-      <c r="T37" s="688"/>
-      <c r="U37" s="688"/>
+      <c r="T37" s="727"/>
+      <c r="U37" s="727"/>
       <c r="V37" s="163"/>
-      <c r="W37" s="688"/>
-      <c r="X37" s="712"/>
+      <c r="W37" s="727"/>
+      <c r="X37" s="728"/>
       <c r="Y37" s="195"/>
       <c r="Z37" s="80"/>
     </row>
@@ -36622,39 +36622,39 @@
       <c r="I38" s="82"/>
       <c r="J38" s="165"/>
       <c r="K38" s="89"/>
-      <c r="L38" s="724" t="s">
+      <c r="L38" s="740" t="s">
         <v>88</v>
       </c>
-      <c r="M38" s="725"/>
-      <c r="N38" s="726"/>
-      <c r="O38" s="689">
+      <c r="M38" s="741"/>
+      <c r="N38" s="742"/>
+      <c r="O38" s="729">
         <f>SUM(O29:P37)</f>
         <v>0</v>
       </c>
-      <c r="P38" s="689"/>
-      <c r="Q38" s="689">
+      <c r="P38" s="729"/>
+      <c r="Q38" s="729">
         <f>SUM(Q29:R37)</f>
         <v>0</v>
       </c>
-      <c r="R38" s="689"/>
+      <c r="R38" s="729"/>
       <c r="S38" s="196">
         <f>SUM(S29:S37)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="689">
+      <c r="T38" s="729">
         <f>SUM(T29:U37)</f>
         <v>0</v>
       </c>
-      <c r="U38" s="689"/>
+      <c r="U38" s="729"/>
       <c r="V38" s="196">
         <f>SUM(V29:V37)</f>
         <v>0</v>
       </c>
-      <c r="W38" s="689">
+      <c r="W38" s="729">
         <f>SUM(W29:X37)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="689"/>
+      <c r="X38" s="729"/>
       <c r="Y38" s="197">
         <f>SUM(Y29:Y37)</f>
         <v>0</v>
@@ -36670,26 +36670,26 @@
       <c r="E39" s="82"/>
       <c r="F39" s="79"/>
       <c r="G39" s="136"/>
-      <c r="H39" s="681">
+      <c r="H39" s="750">
         <f>S38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="682"/>
-      <c r="J39" s="683"/>
+      <c r="I39" s="751"/>
+      <c r="J39" s="752"/>
       <c r="K39" s="89"/>
-      <c r="L39" s="719"/>
-      <c r="M39" s="727"/>
-      <c r="N39" s="728"/>
-      <c r="O39" s="719"/>
-      <c r="P39" s="720"/>
-      <c r="Q39" s="702"/>
-      <c r="R39" s="703"/>
+      <c r="L39" s="735"/>
+      <c r="M39" s="743"/>
+      <c r="N39" s="744"/>
+      <c r="O39" s="735"/>
+      <c r="P39" s="736"/>
+      <c r="Q39" s="748"/>
+      <c r="R39" s="749"/>
       <c r="S39" s="104"/>
-      <c r="T39" s="690"/>
-      <c r="U39" s="690"/>
+      <c r="T39" s="776"/>
+      <c r="U39" s="776"/>
       <c r="V39" s="104"/>
-      <c r="W39" s="690"/>
-      <c r="X39" s="690"/>
+      <c r="W39" s="776"/>
+      <c r="X39" s="776"/>
       <c r="Y39" s="132"/>
       <c r="Z39" s="82"/>
       <c r="AA39" s="79"/>
@@ -36706,19 +36706,19 @@
       <c r="I40" s="82"/>
       <c r="J40" s="165"/>
       <c r="K40" s="89"/>
-      <c r="L40" s="692"/>
-      <c r="M40" s="729"/>
-      <c r="N40" s="693"/>
-      <c r="O40" s="721"/>
-      <c r="P40" s="718"/>
-      <c r="Q40" s="717"/>
-      <c r="R40" s="718"/>
+      <c r="L40" s="745"/>
+      <c r="M40" s="746"/>
+      <c r="N40" s="747"/>
+      <c r="O40" s="737"/>
+      <c r="P40" s="734"/>
+      <c r="Q40" s="733"/>
+      <c r="R40" s="734"/>
       <c r="S40" s="82"/>
-      <c r="T40" s="691"/>
-      <c r="U40" s="691"/>
+      <c r="T40" s="777"/>
+      <c r="U40" s="777"/>
       <c r="V40" s="82"/>
-      <c r="W40" s="691"/>
-      <c r="X40" s="691"/>
+      <c r="W40" s="777"/>
+      <c r="X40" s="777"/>
       <c r="Y40" s="140"/>
       <c r="Z40" s="82"/>
     </row>
@@ -36734,19 +36734,19 @@
       <c r="I41" s="166"/>
       <c r="J41" s="138"/>
       <c r="K41" s="89"/>
-      <c r="L41" s="692"/>
-      <c r="M41" s="729"/>
-      <c r="N41" s="693"/>
-      <c r="O41" s="722"/>
-      <c r="P41" s="723"/>
-      <c r="Q41" s="692"/>
-      <c r="R41" s="693"/>
+      <c r="L41" s="745"/>
+      <c r="M41" s="746"/>
+      <c r="N41" s="747"/>
+      <c r="O41" s="738"/>
+      <c r="P41" s="739"/>
+      <c r="Q41" s="745"/>
+      <c r="R41" s="747"/>
       <c r="S41" s="82"/>
-      <c r="T41" s="692"/>
-      <c r="U41" s="693"/>
+      <c r="T41" s="745"/>
+      <c r="U41" s="747"/>
       <c r="V41" s="82"/>
-      <c r="W41" s="692"/>
-      <c r="X41" s="693"/>
+      <c r="W41" s="745"/>
+      <c r="X41" s="747"/>
       <c r="Y41" s="140"/>
       <c r="Z41" s="82"/>
       <c r="AA41" s="103"/>
@@ -36763,21 +36763,21 @@
       <c r="I42" s="106"/>
       <c r="J42" s="106"/>
       <c r="K42" s="79"/>
-      <c r="L42" s="713"/>
-      <c r="M42" s="714"/>
-      <c r="N42" s="715"/>
-      <c r="O42" s="702"/>
-      <c r="P42" s="703"/>
+      <c r="L42" s="730"/>
+      <c r="M42" s="731"/>
+      <c r="N42" s="732"/>
+      <c r="O42" s="748"/>
+      <c r="P42" s="749"/>
       <c r="Q42" s="82"/>
-      <c r="R42" s="686" t="s">
+      <c r="R42" s="774" t="s">
         <v>136</v>
       </c>
-      <c r="S42" s="687"/>
+      <c r="S42" s="775"/>
       <c r="T42" s="105"/>
-      <c r="U42" s="694"/>
-      <c r="V42" s="695"/>
-      <c r="W42" s="694"/>
-      <c r="X42" s="695"/>
+      <c r="U42" s="778"/>
+      <c r="V42" s="779"/>
+      <c r="W42" s="778"/>
+      <c r="X42" s="779"/>
       <c r="Y42" s="140"/>
       <c r="Z42" s="82"/>
       <c r="AA42" s="79"/>
@@ -36790,19 +36790,19 @@
       <c r="E43" s="82"/>
       <c r="F43" s="79"/>
       <c r="G43" s="135"/>
-      <c r="H43" s="697" t="s">
+      <c r="H43" s="781" t="s">
         <v>104</v>
       </c>
-      <c r="I43" s="697"/>
-      <c r="J43" s="698"/>
+      <c r="I43" s="781"/>
+      <c r="J43" s="782"/>
       <c r="K43" s="89"/>
       <c r="L43" s="135"/>
       <c r="M43" s="164"/>
-      <c r="N43" s="672" t="s">
+      <c r="N43" s="765" t="s">
         <v>94</v>
       </c>
-      <c r="O43" s="673"/>
-      <c r="P43" s="674"/>
+      <c r="O43" s="766"/>
+      <c r="P43" s="767"/>
       <c r="Q43" s="136"/>
       <c r="R43" s="264" t="s">
         <v>137</v>
@@ -36856,21 +36856,21 @@
       <c r="E45" s="82"/>
       <c r="F45" s="79"/>
       <c r="G45" s="136"/>
-      <c r="H45" s="681">
+      <c r="H45" s="750">
         <f>SUM(V38)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="682"/>
-      <c r="J45" s="683"/>
+      <c r="I45" s="751"/>
+      <c r="J45" s="752"/>
       <c r="K45" s="89"/>
       <c r="L45" s="136"/>
       <c r="M45" s="82"/>
       <c r="N45" s="82"/>
-      <c r="O45" s="675">
+      <c r="O45" s="768">
         <f>SUM(Q38,T38,W38)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="676"/>
+      <c r="P45" s="769"/>
       <c r="Q45" s="136"/>
       <c r="R45" s="265" t="s">
         <v>138</v>
@@ -36902,8 +36902,8 @@
       <c r="L46" s="136"/>
       <c r="M46" s="82"/>
       <c r="N46" s="82"/>
-      <c r="O46" s="677"/>
-      <c r="P46" s="678"/>
+      <c r="O46" s="770"/>
+      <c r="P46" s="771"/>
       <c r="Q46" s="136"/>
       <c r="R46" s="266"/>
       <c r="S46" s="281"/>
@@ -37014,9 +37014,9 @@
       <c r="E50" s="82"/>
       <c r="F50" s="79"/>
       <c r="G50" s="167"/>
-      <c r="H50" s="679"/>
-      <c r="I50" s="679"/>
-      <c r="J50" s="680"/>
+      <c r="H50" s="772"/>
+      <c r="I50" s="772"/>
+      <c r="J50" s="773"/>
       <c r="K50" s="80"/>
       <c r="L50" s="104"/>
       <c r="M50" s="104"/>
@@ -37071,9 +37071,9 @@
       <c r="E52" s="82"/>
       <c r="F52" s="82"/>
       <c r="G52" s="82"/>
-      <c r="H52" s="696"/>
-      <c r="I52" s="696"/>
-      <c r="J52" s="696"/>
+      <c r="H52" s="780"/>
+      <c r="I52" s="780"/>
+      <c r="J52" s="780"/>
       <c r="K52" s="82"/>
       <c r="L52" s="82"/>
       <c r="M52" s="82"/>
@@ -37174,11 +37174,11 @@
       <c r="U55" s="79"/>
       <c r="V55" s="82"/>
       <c r="W55" s="82"/>
-      <c r="X55" s="669"/>
-      <c r="Y55" s="670"/>
-      <c r="Z55" s="670"/>
-      <c r="AA55" s="670"/>
-      <c r="AB55" s="671"/>
+      <c r="X55" s="762"/>
+      <c r="Y55" s="763"/>
+      <c r="Z55" s="763"/>
+      <c r="AA55" s="763"/>
+      <c r="AB55" s="764"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="82"/>
@@ -37394,11 +37394,11 @@
       <c r="P63" s="82"/>
       <c r="Q63" s="79"/>
       <c r="R63" s="79"/>
-      <c r="U63" s="669"/>
-      <c r="V63" s="670"/>
-      <c r="W63" s="670"/>
-      <c r="X63" s="670"/>
-      <c r="Y63" s="671"/>
+      <c r="U63" s="762"/>
+      <c r="V63" s="763"/>
+      <c r="W63" s="763"/>
+      <c r="X63" s="763"/>
+      <c r="Y63" s="764"/>
       <c r="Z63" s="82"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -37834,6 +37834,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="U63:Y63"/>
+    <mergeCell ref="X55:AB55"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="O45:P46"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="T40:U40"/>
+    <mergeCell ref="T41:U41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="W40:X40"/>
+    <mergeCell ref="W41:X41"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
     <mergeCell ref="O19:Q19"/>
     <mergeCell ref="X6:Y6"/>
     <mergeCell ref="V12:W13"/>
@@ -37858,178 +38030,6 @@
     <mergeCell ref="T12:U13"/>
     <mergeCell ref="T15:U15"/>
     <mergeCell ref="T16:U16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="U63:Y63"/>
-    <mergeCell ref="X55:AB55"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="O45:P46"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="T40:U40"/>
-    <mergeCell ref="T41:U41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="H43:J43"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="33" priority="10">
@@ -38819,78 +38819,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="793" t="s">
+      <c r="A1" s="828" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="793"/>
-      <c r="C1" s="793"/>
-      <c r="D1" s="793"/>
-      <c r="E1" s="793"/>
-      <c r="F1" s="793"/>
-      <c r="G1" s="793"/>
-      <c r="H1" s="793"/>
-      <c r="I1" s="793"/>
-      <c r="J1" s="793"/>
-      <c r="K1" s="793"/>
-      <c r="L1" s="793"/>
-      <c r="M1" s="793"/>
-      <c r="N1" s="793"/>
-      <c r="O1" s="794"/>
+      <c r="B1" s="828"/>
+      <c r="C1" s="828"/>
+      <c r="D1" s="828"/>
+      <c r="E1" s="828"/>
+      <c r="F1" s="828"/>
+      <c r="G1" s="828"/>
+      <c r="H1" s="828"/>
+      <c r="I1" s="828"/>
+      <c r="J1" s="828"/>
+      <c r="K1" s="828"/>
+      <c r="L1" s="828"/>
+      <c r="M1" s="828"/>
+      <c r="N1" s="828"/>
+      <c r="O1" s="829"/>
     </row>
     <row r="2" spans="1:15" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A2" s="795"/>
-      <c r="B2" s="795"/>
-      <c r="C2" s="795"/>
-      <c r="D2" s="795"/>
-      <c r="E2" s="795"/>
-      <c r="F2" s="795"/>
-      <c r="G2" s="795"/>
-      <c r="H2" s="795"/>
-      <c r="I2" s="795"/>
-      <c r="J2" s="795"/>
-      <c r="K2" s="795"/>
-      <c r="L2" s="795"/>
-      <c r="M2" s="795"/>
-      <c r="N2" s="795"/>
-      <c r="O2" s="796"/>
+      <c r="A2" s="830"/>
+      <c r="B2" s="830"/>
+      <c r="C2" s="830"/>
+      <c r="D2" s="830"/>
+      <c r="E2" s="830"/>
+      <c r="F2" s="830"/>
+      <c r="G2" s="830"/>
+      <c r="H2" s="830"/>
+      <c r="I2" s="830"/>
+      <c r="J2" s="830"/>
+      <c r="K2" s="830"/>
+      <c r="L2" s="830"/>
+      <c r="M2" s="830"/>
+      <c r="N2" s="830"/>
+      <c r="O2" s="831"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="797" t="s">
+      <c r="A3" s="832" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="797"/>
-      <c r="C3" s="797"/>
-      <c r="D3" s="797"/>
-      <c r="E3" s="797"/>
-      <c r="F3" s="797"/>
-      <c r="G3" s="797"/>
-      <c r="H3" s="797"/>
-      <c r="I3" s="797"/>
-      <c r="J3" s="797"/>
-      <c r="K3" s="797"/>
-      <c r="L3" s="797"/>
-      <c r="M3" s="797"/>
-      <c r="N3" s="797"/>
-      <c r="O3" s="798"/>
+      <c r="B3" s="832"/>
+      <c r="C3" s="832"/>
+      <c r="D3" s="832"/>
+      <c r="E3" s="832"/>
+      <c r="F3" s="832"/>
+      <c r="G3" s="832"/>
+      <c r="H3" s="832"/>
+      <c r="I3" s="832"/>
+      <c r="J3" s="832"/>
+      <c r="K3" s="832"/>
+      <c r="L3" s="832"/>
+      <c r="M3" s="832"/>
+      <c r="N3" s="832"/>
+      <c r="O3" s="833"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" thickBot="1">
-      <c r="A4" s="799" t="s">
+      <c r="A4" s="834" t="s">
         <v>182</v>
       </c>
-      <c r="B4" s="799"/>
-      <c r="C4" s="799"/>
-      <c r="D4" s="799"/>
-      <c r="E4" s="799"/>
-      <c r="F4" s="799"/>
-      <c r="G4" s="799"/>
-      <c r="H4" s="799"/>
-      <c r="I4" s="799"/>
-      <c r="J4" s="799"/>
-      <c r="K4" s="799"/>
-      <c r="L4" s="799"/>
-      <c r="M4" s="799"/>
-      <c r="N4" s="799"/>
-      <c r="O4" s="800"/>
+      <c r="B4" s="834"/>
+      <c r="C4" s="834"/>
+      <c r="D4" s="834"/>
+      <c r="E4" s="834"/>
+      <c r="F4" s="834"/>
+      <c r="G4" s="834"/>
+      <c r="H4" s="834"/>
+      <c r="I4" s="834"/>
+      <c r="J4" s="834"/>
+      <c r="K4" s="834"/>
+      <c r="L4" s="834"/>
+      <c r="M4" s="834"/>
+      <c r="N4" s="834"/>
+      <c r="O4" s="835"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" thickBot="1">
       <c r="A5" s="90"/>
@@ -38902,8 +38902,8 @@
       <c r="G5" s="516"/>
       <c r="H5" s="514"/>
       <c r="I5" s="82"/>
-      <c r="J5" s="801"/>
-      <c r="K5" s="801"/>
+      <c r="J5" s="836"/>
+      <c r="K5" s="836"/>
       <c r="L5" s="519"/>
       <c r="M5" s="516"/>
       <c r="N5" s="520"/>
@@ -38975,24 +38975,24 @@
       <c r="E8" s="106"/>
       <c r="F8" s="90"/>
       <c r="G8" s="104"/>
-      <c r="H8" s="791"/>
-      <c r="I8" s="792"/>
-      <c r="J8" s="791"/>
-      <c r="K8" s="791"/>
-      <c r="L8" s="791"/>
-      <c r="M8" s="791"/>
+      <c r="H8" s="826"/>
+      <c r="I8" s="827"/>
+      <c r="J8" s="826"/>
+      <c r="K8" s="826"/>
+      <c r="L8" s="826"/>
+      <c r="M8" s="826"/>
       <c r="N8" s="521"/>
       <c r="O8" s="406"/>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1">
-      <c r="A9" s="819" t="s">
+      <c r="A9" s="791" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="820"/>
-      <c r="C9" s="820"/>
-      <c r="D9" s="820"/>
-      <c r="E9" s="820"/>
-      <c r="F9" s="821"/>
+      <c r="B9" s="792"/>
+      <c r="C9" s="792"/>
+      <c r="D9" s="792"/>
+      <c r="E9" s="792"/>
+      <c r="F9" s="793"/>
       <c r="G9" s="83"/>
       <c r="H9" s="498"/>
       <c r="I9" s="503"/>
@@ -39004,12 +39004,12 @@
       <c r="O9" s="232"/>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A10" s="822"/>
-      <c r="B10" s="823"/>
-      <c r="C10" s="823"/>
-      <c r="D10" s="823"/>
-      <c r="E10" s="823"/>
-      <c r="F10" s="824"/>
+      <c r="A10" s="794"/>
+      <c r="B10" s="795"/>
+      <c r="C10" s="795"/>
+      <c r="D10" s="795"/>
+      <c r="E10" s="795"/>
+      <c r="F10" s="796"/>
       <c r="G10" s="80"/>
       <c r="H10" s="82"/>
       <c r="I10" s="501"/>
@@ -39021,22 +39021,22 @@
       <c r="O10" s="406"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="835" t="s">
+      <c r="A11" s="807" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="830" t="s">
+      <c r="B11" s="802" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="832" t="s">
+      <c r="C11" s="804" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="834" t="s">
+      <c r="D11" s="806" t="s">
         <v>154</v>
       </c>
-      <c r="E11" s="815" t="s">
+      <c r="E11" s="787" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="816"/>
+      <c r="F11" s="788"/>
       <c r="G11" s="80"/>
       <c r="H11" s="82"/>
       <c r="I11" s="501"/>
@@ -39048,12 +39048,12 @@
       <c r="O11" s="406"/>
     </row>
     <row r="12" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A12" s="836"/>
-      <c r="B12" s="831"/>
-      <c r="C12" s="833"/>
-      <c r="D12" s="822"/>
-      <c r="E12" s="817"/>
-      <c r="F12" s="818"/>
+      <c r="A12" s="808"/>
+      <c r="B12" s="803"/>
+      <c r="C12" s="805"/>
+      <c r="D12" s="794"/>
+      <c r="E12" s="789"/>
+      <c r="F12" s="790"/>
       <c r="G12" s="80"/>
       <c r="H12" s="82"/>
       <c r="I12" s="501"/>
@@ -39071,11 +39071,11 @@
       <c r="B13" s="564"/>
       <c r="C13" s="564"/>
       <c r="D13" s="565"/>
-      <c r="E13" s="825">
+      <c r="E13" s="797">
         <f>SUM(B13:D13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="826"/>
+      <c r="F13" s="798"/>
       <c r="G13" s="80"/>
       <c r="H13" s="82"/>
       <c r="I13" s="82"/>
@@ -39093,11 +39093,11 @@
       <c r="B14" s="506"/>
       <c r="C14" s="506"/>
       <c r="D14" s="566"/>
-      <c r="E14" s="827">
+      <c r="E14" s="799">
         <f>SUM(B14:D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="828"/>
+      <c r="F14" s="800"/>
       <c r="G14" s="80"/>
       <c r="H14" s="82"/>
       <c r="I14" s="501"/>
@@ -39115,11 +39115,11 @@
       <c r="B15" s="509"/>
       <c r="C15" s="509"/>
       <c r="D15" s="510"/>
-      <c r="E15" s="837">
+      <c r="E15" s="809">
         <f>SUM(B15:D15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="838"/>
+      <c r="F15" s="810"/>
       <c r="G15" s="80"/>
       <c r="H15" s="82"/>
       <c r="I15" s="501"/>
@@ -39154,11 +39154,11 @@
       <c r="D17" s="82"/>
       <c r="E17" s="89"/>
       <c r="F17" s="82"/>
-      <c r="H17" s="803" t="s">
+      <c r="H17" s="812" t="s">
         <v>157</v>
       </c>
-      <c r="I17" s="804"/>
-      <c r="J17" s="805"/>
+      <c r="I17" s="813"/>
+      <c r="J17" s="814"/>
       <c r="K17" s="227"/>
       <c r="L17" s="227"/>
       <c r="M17" s="227"/>
@@ -39225,10 +39225,10 @@
       <c r="K20" s="544" t="s">
         <v>52</v>
       </c>
-      <c r="L20" s="811" t="s">
+      <c r="L20" s="822" t="s">
         <v>53</v>
       </c>
-      <c r="M20" s="812"/>
+      <c r="M20" s="823"/>
       <c r="N20" s="402"/>
       <c r="O20" s="165"/>
     </row>
@@ -39253,8 +39253,8 @@
       <c r="I21" s="547"/>
       <c r="J21" s="547"/>
       <c r="K21" s="547"/>
-      <c r="L21" s="813"/>
-      <c r="M21" s="814"/>
+      <c r="L21" s="824"/>
+      <c r="M21" s="825"/>
       <c r="N21" s="80"/>
       <c r="O21" s="165"/>
     </row>
@@ -39270,27 +39270,27 @@
       <c r="I22" s="546"/>
       <c r="J22" s="546"/>
       <c r="K22" s="546"/>
-      <c r="L22" s="787"/>
-      <c r="M22" s="788"/>
+      <c r="L22" s="820"/>
+      <c r="M22" s="821"/>
       <c r="N22" s="80"/>
       <c r="O22" s="165"/>
     </row>
     <row r="23" spans="1:15" ht="27.75" customHeight="1" thickBot="1">
-      <c r="A23" s="808" t="s">
+      <c r="A23" s="817" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="809"/>
-      <c r="C23" s="809"/>
-      <c r="D23" s="809"/>
-      <c r="E23" s="809"/>
-      <c r="F23" s="810"/>
+      <c r="B23" s="818"/>
+      <c r="C23" s="818"/>
+      <c r="D23" s="818"/>
+      <c r="E23" s="818"/>
+      <c r="F23" s="819"/>
       <c r="G23" s="78"/>
       <c r="H23" s="550"/>
       <c r="I23" s="546"/>
       <c r="J23" s="546"/>
       <c r="K23" s="546"/>
-      <c r="L23" s="787"/>
-      <c r="M23" s="788"/>
+      <c r="L23" s="820"/>
+      <c r="M23" s="821"/>
       <c r="N23" s="80"/>
       <c r="O23" s="165"/>
     </row>
@@ -39298,10 +39298,10 @@
       <c r="A24" s="559" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="806" t="s">
+      <c r="B24" s="815" t="s">
         <v>184</v>
       </c>
-      <c r="C24" s="807"/>
+      <c r="C24" s="816"/>
       <c r="D24" s="560" t="s">
         <v>161</v>
       </c>
@@ -39316,8 +39316,8 @@
       <c r="I24" s="546"/>
       <c r="J24" s="546"/>
       <c r="K24" s="546"/>
-      <c r="L24" s="787"/>
-      <c r="M24" s="788"/>
+      <c r="L24" s="820"/>
+      <c r="M24" s="821"/>
       <c r="N24" s="80"/>
       <c r="O24" s="165"/>
     </row>
@@ -39325,8 +39325,8 @@
       <c r="A25" s="505" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="829"/>
-      <c r="C25" s="829"/>
+      <c r="B25" s="801"/>
+      <c r="C25" s="801"/>
       <c r="D25" s="512"/>
       <c r="E25" s="512"/>
       <c r="F25" s="511">
@@ -39338,8 +39338,8 @@
       <c r="I25" s="546"/>
       <c r="J25" s="546"/>
       <c r="K25" s="546"/>
-      <c r="L25" s="787"/>
-      <c r="M25" s="788"/>
+      <c r="L25" s="820"/>
+      <c r="M25" s="821"/>
       <c r="N25" s="80"/>
       <c r="O25" s="165"/>
     </row>
@@ -39352,16 +39352,16 @@
       <c r="I26" s="546"/>
       <c r="J26" s="546"/>
       <c r="K26" s="546"/>
-      <c r="L26" s="787"/>
-      <c r="M26" s="788"/>
+      <c r="L26" s="820"/>
+      <c r="M26" s="821"/>
       <c r="N26" s="80"/>
       <c r="O26" s="165"/>
     </row>
     <row r="27" spans="1:15" ht="27" customHeight="1">
-      <c r="A27" s="802"/>
-      <c r="B27" s="802"/>
-      <c r="C27" s="802"/>
-      <c r="D27" s="802"/>
+      <c r="A27" s="811"/>
+      <c r="B27" s="811"/>
+      <c r="C27" s="811"/>
+      <c r="D27" s="811"/>
       <c r="E27" s="499"/>
       <c r="F27" s="502"/>
       <c r="G27" s="89"/>
@@ -39369,8 +39369,8 @@
       <c r="I27" s="546"/>
       <c r="J27" s="546"/>
       <c r="K27" s="546"/>
-      <c r="L27" s="787"/>
-      <c r="M27" s="788"/>
+      <c r="L27" s="820"/>
+      <c r="M27" s="821"/>
       <c r="N27" s="80"/>
       <c r="O27" s="165"/>
     </row>
@@ -39386,8 +39386,8 @@
       <c r="I28" s="546"/>
       <c r="J28" s="546"/>
       <c r="K28" s="546"/>
-      <c r="L28" s="787"/>
-      <c r="M28" s="788"/>
+      <c r="L28" s="820"/>
+      <c r="M28" s="821"/>
       <c r="N28" s="105"/>
       <c r="O28" s="165"/>
     </row>
@@ -39402,8 +39402,8 @@
       <c r="I29" s="546"/>
       <c r="J29" s="546"/>
       <c r="K29" s="546"/>
-      <c r="L29" s="787"/>
-      <c r="M29" s="788"/>
+      <c r="L29" s="820"/>
+      <c r="M29" s="821"/>
       <c r="N29" s="80"/>
       <c r="O29" s="165"/>
     </row>
@@ -39419,8 +39419,8 @@
       <c r="I30" s="546"/>
       <c r="J30" s="546"/>
       <c r="K30" s="546"/>
-      <c r="L30" s="787"/>
-      <c r="M30" s="788"/>
+      <c r="L30" s="820"/>
+      <c r="M30" s="821"/>
       <c r="N30" s="80"/>
       <c r="O30" s="165"/>
     </row>
@@ -39436,8 +39436,8 @@
       <c r="I31" s="546"/>
       <c r="J31" s="546"/>
       <c r="K31" s="546"/>
-      <c r="L31" s="787"/>
-      <c r="M31" s="788"/>
+      <c r="L31" s="820"/>
+      <c r="M31" s="821"/>
       <c r="N31" s="80"/>
       <c r="O31" s="165"/>
     </row>
@@ -39453,8 +39453,8 @@
       <c r="I32" s="546"/>
       <c r="J32" s="546"/>
       <c r="K32" s="546"/>
-      <c r="L32" s="787"/>
-      <c r="M32" s="788"/>
+      <c r="L32" s="820"/>
+      <c r="M32" s="821"/>
       <c r="N32" s="80"/>
       <c r="O32" s="165"/>
     </row>
@@ -39470,8 +39470,8 @@
       <c r="I33" s="546"/>
       <c r="J33" s="546"/>
       <c r="K33" s="546"/>
-      <c r="L33" s="787"/>
-      <c r="M33" s="788"/>
+      <c r="L33" s="820"/>
+      <c r="M33" s="821"/>
       <c r="N33" s="80"/>
       <c r="O33" s="165"/>
     </row>
@@ -39487,8 +39487,8 @@
       <c r="I34" s="546"/>
       <c r="J34" s="546"/>
       <c r="K34" s="546"/>
-      <c r="L34" s="787"/>
-      <c r="M34" s="788"/>
+      <c r="L34" s="820"/>
+      <c r="M34" s="821"/>
       <c r="N34" s="80"/>
       <c r="O34" s="165"/>
     </row>
@@ -39504,8 +39504,8 @@
       <c r="I35" s="546"/>
       <c r="J35" s="546"/>
       <c r="K35" s="546"/>
-      <c r="L35" s="787"/>
-      <c r="M35" s="788"/>
+      <c r="L35" s="820"/>
+      <c r="M35" s="821"/>
       <c r="N35" s="80"/>
       <c r="O35" s="165"/>
     </row>
@@ -39520,8 +39520,8 @@
       <c r="I36" s="546"/>
       <c r="J36" s="546"/>
       <c r="K36" s="546"/>
-      <c r="L36" s="787"/>
-      <c r="M36" s="788"/>
+      <c r="L36" s="820"/>
+      <c r="M36" s="821"/>
       <c r="N36" s="80"/>
       <c r="O36" s="165"/>
     </row>
@@ -39537,23 +39537,29 @@
       <c r="I37" s="548"/>
       <c r="J37" s="548"/>
       <c r="K37" s="548"/>
-      <c r="L37" s="789"/>
-      <c r="M37" s="790"/>
+      <c r="L37" s="837"/>
+      <c r="M37" s="838"/>
       <c r="N37" s="80"/>
       <c r="O37" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="B24:C24"/>
@@ -39566,22 +39572,16 @@
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="L26:M26"/>
     <mergeCell ref="L27:M27"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E15:F15"/>
   </mergeCells>
   <conditionalFormatting sqref="I21:L37">
     <cfRule type="expression" dxfId="27" priority="1">
@@ -39622,22 +39622,22 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21">
       <c r="A1" s="82"/>
-      <c r="B1" s="872" t="s">
+      <c r="B1" s="842" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="873"/>
-      <c r="D1" s="873"/>
-      <c r="E1" s="873"/>
-      <c r="F1" s="873"/>
-      <c r="G1" s="873"/>
-      <c r="H1" s="873"/>
-      <c r="I1" s="873"/>
-      <c r="J1" s="873"/>
-      <c r="K1" s="873"/>
-      <c r="L1" s="873"/>
-      <c r="M1" s="873"/>
-      <c r="N1" s="873"/>
-      <c r="O1" s="874"/>
+      <c r="C1" s="843"/>
+      <c r="D1" s="843"/>
+      <c r="E1" s="843"/>
+      <c r="F1" s="843"/>
+      <c r="G1" s="843"/>
+      <c r="H1" s="843"/>
+      <c r="I1" s="843"/>
+      <c r="J1" s="843"/>
+      <c r="K1" s="843"/>
+      <c r="L1" s="843"/>
+      <c r="M1" s="843"/>
+      <c r="N1" s="843"/>
+      <c r="O1" s="844"/>
       <c r="P1" s="82"/>
       <c r="Q1" s="82"/>
       <c r="R1" s="82"/>
@@ -39646,24 +39646,24 @@
     </row>
     <row r="2" spans="1:20" ht="18.75" customHeight="1">
       <c r="A2" s="82"/>
-      <c r="B2" s="860" t="s">
+      <c r="B2" s="861" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="861"/>
-      <c r="D2" s="861"/>
-      <c r="E2" s="861"/>
-      <c r="F2" s="861"/>
-      <c r="G2" s="862" t="s">
+      <c r="C2" s="862"/>
+      <c r="D2" s="862"/>
+      <c r="E2" s="862"/>
+      <c r="F2" s="862"/>
+      <c r="G2" s="863" t="s">
         <v>164</v>
       </c>
-      <c r="H2" s="862"/>
-      <c r="I2" s="862"/>
-      <c r="J2" s="862"/>
-      <c r="K2" s="862"/>
-      <c r="L2" s="862"/>
-      <c r="M2" s="862"/>
-      <c r="N2" s="862"/>
-      <c r="O2" s="863"/>
+      <c r="H2" s="863"/>
+      <c r="I2" s="863"/>
+      <c r="J2" s="863"/>
+      <c r="K2" s="863"/>
+      <c r="L2" s="863"/>
+      <c r="M2" s="863"/>
+      <c r="N2" s="863"/>
+      <c r="O2" s="864"/>
       <c r="P2" s="82"/>
       <c r="Q2" s="82"/>
       <c r="R2" s="82"/>
@@ -39672,15 +39672,15 @@
     </row>
     <row r="3" spans="1:20" ht="28.5" customHeight="1" thickBot="1">
       <c r="A3" s="82"/>
-      <c r="B3" s="864" t="s">
+      <c r="B3" s="865" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="865"/>
-      <c r="D3" s="865"/>
-      <c r="E3" s="865"/>
-      <c r="F3" s="865"/>
-      <c r="G3" s="865"/>
-      <c r="H3" s="866"/>
+      <c r="C3" s="866"/>
+      <c r="D3" s="866"/>
+      <c r="E3" s="866"/>
+      <c r="F3" s="866"/>
+      <c r="G3" s="866"/>
+      <c r="H3" s="867"/>
       <c r="I3" s="208"/>
       <c r="J3" s="209"/>
       <c r="K3" s="479"/>
@@ -39705,13 +39705,13 @@
       <c r="H4" s="80"/>
       <c r="I4" s="88"/>
       <c r="J4" s="103"/>
-      <c r="K4" s="882" t="s">
+      <c r="K4" s="854" t="s">
         <v>188</v>
       </c>
-      <c r="L4" s="883"/>
-      <c r="M4" s="883"/>
-      <c r="N4" s="883"/>
-      <c r="O4" s="884"/>
+      <c r="L4" s="855"/>
+      <c r="M4" s="855"/>
+      <c r="N4" s="855"/>
+      <c r="O4" s="856"/>
       <c r="P4" s="80"/>
       <c r="Q4" s="82"/>
       <c r="R4" s="82"/>
@@ -39724,14 +39724,14 @@
       <c r="H5" s="79"/>
       <c r="I5" s="82"/>
       <c r="J5" s="210"/>
-      <c r="K5" s="879" t="s">
+      <c r="K5" s="851" t="s">
         <v>122</v>
       </c>
-      <c r="L5" s="878"/>
-      <c r="M5" s="878" t="s">
+      <c r="L5" s="850"/>
+      <c r="M5" s="850" t="s">
         <v>191</v>
       </c>
-      <c r="N5" s="878"/>
+      <c r="N5" s="850"/>
       <c r="O5" s="534" t="s">
         <v>70</v>
       </c>
@@ -39747,10 +39747,10 @@
       <c r="H6" s="79"/>
       <c r="I6" s="82"/>
       <c r="J6" s="79"/>
-      <c r="K6" s="885"/>
-      <c r="L6" s="886"/>
-      <c r="M6" s="876"/>
-      <c r="N6" s="877"/>
+      <c r="K6" s="857"/>
+      <c r="L6" s="858"/>
+      <c r="M6" s="846"/>
+      <c r="N6" s="847"/>
       <c r="O6" s="572"/>
       <c r="P6" s="80"/>
       <c r="Q6" s="82"/>
@@ -39762,16 +39762,16 @@
       <c r="A7" s="82"/>
       <c r="C7" s="82"/>
       <c r="D7" s="82"/>
-      <c r="E7" s="880"/>
-      <c r="F7" s="881"/>
-      <c r="G7" s="881"/>
-      <c r="H7" s="881"/>
+      <c r="E7" s="852"/>
+      <c r="F7" s="853"/>
+      <c r="G7" s="853"/>
+      <c r="H7" s="853"/>
       <c r="I7" s="82"/>
       <c r="J7" s="103"/>
-      <c r="K7" s="841"/>
-      <c r="L7" s="842"/>
-      <c r="M7" s="839"/>
-      <c r="N7" s="840"/>
+      <c r="K7" s="859"/>
+      <c r="L7" s="860"/>
+      <c r="M7" s="848"/>
+      <c r="N7" s="849"/>
       <c r="O7" s="573"/>
       <c r="P7" s="80"/>
       <c r="Q7" s="82"/>
@@ -39786,10 +39786,10 @@
       <c r="D8" s="82"/>
       <c r="I8" s="82"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="841"/>
-      <c r="L8" s="842"/>
-      <c r="M8" s="839"/>
-      <c r="N8" s="840"/>
+      <c r="K8" s="859"/>
+      <c r="L8" s="860"/>
+      <c r="M8" s="848"/>
+      <c r="N8" s="849"/>
       <c r="O8" s="573"/>
       <c r="P8" s="80"/>
       <c r="Q8" s="82"/>
@@ -39804,10 +39804,10 @@
       <c r="D9" s="82"/>
       <c r="I9" s="82"/>
       <c r="J9" s="103"/>
-      <c r="K9" s="841"/>
-      <c r="L9" s="842"/>
-      <c r="M9" s="839"/>
-      <c r="N9" s="840"/>
+      <c r="K9" s="859"/>
+      <c r="L9" s="860"/>
+      <c r="M9" s="848"/>
+      <c r="N9" s="849"/>
       <c r="O9" s="573"/>
       <c r="P9" s="80"/>
       <c r="Q9" s="82"/>
@@ -39824,10 +39824,10 @@
       <c r="D10" s="80"/>
       <c r="I10" s="82"/>
       <c r="J10" s="79"/>
-      <c r="K10" s="841"/>
-      <c r="L10" s="842"/>
-      <c r="M10" s="839"/>
-      <c r="N10" s="840"/>
+      <c r="K10" s="859"/>
+      <c r="L10" s="860"/>
+      <c r="M10" s="848"/>
+      <c r="N10" s="849"/>
       <c r="O10" s="573"/>
       <c r="P10" s="80"/>
       <c r="Q10" s="82"/>
@@ -39846,10 +39846,10 @@
       <c r="H11" s="87"/>
       <c r="I11" s="80"/>
       <c r="J11" s="103"/>
-      <c r="K11" s="841"/>
-      <c r="L11" s="842"/>
-      <c r="M11" s="839"/>
-      <c r="N11" s="840"/>
+      <c r="K11" s="859"/>
+      <c r="L11" s="860"/>
+      <c r="M11" s="848"/>
+      <c r="N11" s="849"/>
       <c r="O11" s="573"/>
       <c r="P11" s="80"/>
       <c r="Q11" s="82"/>
@@ -39865,10 +39865,10 @@
       <c r="G12" s="89"/>
       <c r="I12" s="80"/>
       <c r="J12" s="103"/>
-      <c r="K12" s="841"/>
-      <c r="L12" s="842"/>
-      <c r="M12" s="839"/>
-      <c r="N12" s="840"/>
+      <c r="K12" s="859"/>
+      <c r="L12" s="860"/>
+      <c r="M12" s="848"/>
+      <c r="N12" s="849"/>
       <c r="O12" s="573"/>
       <c r="P12" s="80"/>
       <c r="Q12" s="82"/>
@@ -39879,18 +39879,18 @@
     <row r="13" spans="1:20" ht="55.5" customHeight="1">
       <c r="A13" s="79"/>
       <c r="D13" s="89"/>
-      <c r="E13" s="875" t="s">
+      <c r="E13" s="845" t="s">
         <v>174</v>
       </c>
-      <c r="F13" s="875"/>
-      <c r="G13" s="875"/>
-      <c r="H13" s="875"/>
+      <c r="F13" s="845"/>
+      <c r="G13" s="845"/>
+      <c r="H13" s="845"/>
       <c r="I13" s="80"/>
       <c r="J13" s="103"/>
-      <c r="K13" s="841"/>
-      <c r="L13" s="842"/>
-      <c r="M13" s="839"/>
-      <c r="N13" s="840"/>
+      <c r="K13" s="859"/>
+      <c r="L13" s="860"/>
+      <c r="M13" s="848"/>
+      <c r="N13" s="849"/>
       <c r="O13" s="573"/>
       <c r="P13" s="80"/>
       <c r="Q13" s="82"/>
@@ -39900,25 +39900,25 @@
     </row>
     <row r="14" spans="1:20" ht="47.25" customHeight="1">
       <c r="A14" s="79"/>
-      <c r="B14" s="851" t="s">
+      <c r="B14" s="874" t="s">
         <v>170</v>
       </c>
-      <c r="C14" s="851"/>
+      <c r="C14" s="874"/>
       <c r="D14" s="89"/>
-      <c r="E14" s="868" t="s">
+      <c r="E14" s="869" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="868"/>
-      <c r="G14" s="868"/>
+      <c r="F14" s="869"/>
+      <c r="G14" s="869"/>
       <c r="H14" s="467" t="s">
         <v>123</v>
       </c>
       <c r="I14" s="80"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="841"/>
-      <c r="L14" s="842"/>
-      <c r="M14" s="839"/>
-      <c r="N14" s="840"/>
+      <c r="K14" s="859"/>
+      <c r="L14" s="860"/>
+      <c r="M14" s="848"/>
+      <c r="N14" s="849"/>
       <c r="O14" s="573"/>
       <c r="P14" s="80"/>
       <c r="Q14" s="82"/>
@@ -39935,16 +39935,16 @@
         <v>172</v>
       </c>
       <c r="D15" s="89"/>
-      <c r="E15" s="855"/>
-      <c r="F15" s="855"/>
-      <c r="G15" s="855"/>
+      <c r="E15" s="870"/>
+      <c r="F15" s="870"/>
+      <c r="G15" s="870"/>
       <c r="H15" s="476"/>
       <c r="I15" s="80"/>
       <c r="J15" s="103"/>
-      <c r="K15" s="841"/>
-      <c r="L15" s="842"/>
-      <c r="M15" s="839"/>
-      <c r="N15" s="840"/>
+      <c r="K15" s="859"/>
+      <c r="L15" s="860"/>
+      <c r="M15" s="848"/>
+      <c r="N15" s="849"/>
       <c r="O15" s="573"/>
       <c r="P15" s="80"/>
       <c r="Q15" s="82"/>
@@ -39957,16 +39957,16 @@
       <c r="B16" s="475"/>
       <c r="C16" s="475"/>
       <c r="D16" s="89"/>
-      <c r="E16" s="855"/>
-      <c r="F16" s="855"/>
-      <c r="G16" s="855"/>
+      <c r="E16" s="870"/>
+      <c r="F16" s="870"/>
+      <c r="G16" s="870"/>
       <c r="H16" s="476"/>
       <c r="I16" s="80"/>
       <c r="J16" s="103"/>
-      <c r="K16" s="841"/>
-      <c r="L16" s="842"/>
-      <c r="M16" s="839"/>
-      <c r="N16" s="840"/>
+      <c r="K16" s="859"/>
+      <c r="L16" s="860"/>
+      <c r="M16" s="848"/>
+      <c r="N16" s="849"/>
       <c r="O16" s="573"/>
       <c r="P16" s="80"/>
       <c r="Q16" s="82"/>
@@ -39979,16 +39979,16 @@
       <c r="B17" s="475"/>
       <c r="C17" s="475"/>
       <c r="D17" s="89"/>
-      <c r="E17" s="855"/>
-      <c r="F17" s="855"/>
-      <c r="G17" s="855"/>
+      <c r="E17" s="870"/>
+      <c r="F17" s="870"/>
+      <c r="G17" s="870"/>
       <c r="H17" s="476"/>
       <c r="I17" s="80"/>
       <c r="J17" s="79"/>
-      <c r="K17" s="841"/>
-      <c r="L17" s="842"/>
-      <c r="M17" s="839"/>
-      <c r="N17" s="840"/>
+      <c r="K17" s="859"/>
+      <c r="L17" s="860"/>
+      <c r="M17" s="848"/>
+      <c r="N17" s="849"/>
       <c r="O17" s="573"/>
       <c r="P17" s="80"/>
       <c r="Q17" s="82"/>
@@ -40001,16 +40001,16 @@
       <c r="B18" s="475"/>
       <c r="C18" s="475"/>
       <c r="D18" s="89"/>
-      <c r="E18" s="855"/>
-      <c r="F18" s="855"/>
-      <c r="G18" s="855"/>
+      <c r="E18" s="870"/>
+      <c r="F18" s="870"/>
+      <c r="G18" s="870"/>
       <c r="H18" s="476"/>
       <c r="I18" s="80"/>
       <c r="J18" s="87"/>
-      <c r="K18" s="858"/>
-      <c r="L18" s="859"/>
-      <c r="M18" s="846"/>
-      <c r="N18" s="847"/>
+      <c r="K18" s="882"/>
+      <c r="L18" s="883"/>
+      <c r="M18" s="880"/>
+      <c r="N18" s="881"/>
       <c r="O18" s="573"/>
       <c r="P18" s="80"/>
       <c r="Q18" s="82"/>
@@ -40023,15 +40023,15 @@
       <c r="B19" s="475"/>
       <c r="C19" s="475"/>
       <c r="D19" s="89"/>
-      <c r="E19" s="855"/>
-      <c r="F19" s="855"/>
-      <c r="G19" s="855"/>
+      <c r="E19" s="870"/>
+      <c r="F19" s="870"/>
+      <c r="G19" s="870"/>
       <c r="H19" s="476"/>
       <c r="I19" s="80"/>
       <c r="J19" s="79"/>
       <c r="K19" s="230"/>
-      <c r="M19" s="846"/>
-      <c r="N19" s="847"/>
+      <c r="M19" s="880"/>
+      <c r="N19" s="881"/>
       <c r="O19" s="573"/>
       <c r="P19" s="80"/>
       <c r="Q19" s="82"/>
@@ -40044,15 +40044,15 @@
       <c r="B20" s="475"/>
       <c r="C20" s="475"/>
       <c r="D20" s="89"/>
-      <c r="E20" s="856"/>
-      <c r="F20" s="856"/>
-      <c r="G20" s="856"/>
+      <c r="E20" s="878"/>
+      <c r="F20" s="878"/>
+      <c r="G20" s="878"/>
       <c r="H20" s="477"/>
       <c r="I20" s="80"/>
       <c r="J20" s="103"/>
       <c r="K20" s="230"/>
-      <c r="M20" s="846"/>
-      <c r="N20" s="847"/>
+      <c r="M20" s="880"/>
+      <c r="N20" s="881"/>
       <c r="O20" s="573"/>
       <c r="P20" s="80"/>
       <c r="Q20" s="82"/>
@@ -40065,11 +40065,11 @@
       <c r="B21" s="475"/>
       <c r="C21" s="475"/>
       <c r="D21" s="98"/>
-      <c r="E21" s="867" t="s">
+      <c r="E21" s="868" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="867"/>
-      <c r="G21" s="867"/>
+      <c r="F21" s="868"/>
+      <c r="G21" s="868"/>
       <c r="H21" s="478">
         <f>SUM(H15:H20)</f>
         <v>0</v>
@@ -40077,8 +40077,8 @@
       <c r="I21" s="80"/>
       <c r="J21" s="103"/>
       <c r="K21" s="230"/>
-      <c r="M21" s="846"/>
-      <c r="N21" s="847"/>
+      <c r="M21" s="880"/>
+      <c r="N21" s="881"/>
       <c r="O21" s="573"/>
       <c r="P21" s="80"/>
       <c r="Q21" s="82"/>
@@ -40096,17 +40096,17 @@
         <v>0</v>
       </c>
       <c r="D22" s="89"/>
-      <c r="E22" s="843" t="s">
+      <c r="E22" s="884" t="s">
         <v>171</v>
       </c>
-      <c r="F22" s="844"/>
-      <c r="G22" s="844"/>
-      <c r="H22" s="845"/>
+      <c r="F22" s="885"/>
+      <c r="G22" s="885"/>
+      <c r="H22" s="886"/>
       <c r="I22" s="80"/>
       <c r="J22" s="79"/>
       <c r="K22" s="230"/>
-      <c r="M22" s="846"/>
-      <c r="N22" s="847"/>
+      <c r="M22" s="880"/>
+      <c r="N22" s="881"/>
       <c r="O22" s="573"/>
       <c r="P22" s="80"/>
       <c r="Q22" s="82"/>
@@ -40121,8 +40121,8 @@
       <c r="J23" s="79"/>
       <c r="K23" s="230"/>
       <c r="L23" s="87"/>
-      <c r="M23" s="846"/>
-      <c r="N23" s="847"/>
+      <c r="M23" s="880"/>
+      <c r="N23" s="881"/>
       <c r="O23" s="573"/>
       <c r="P23" s="80"/>
       <c r="Q23" s="82"/>
@@ -40139,8 +40139,8 @@
       <c r="J24" s="87"/>
       <c r="K24" s="235"/>
       <c r="L24" s="234"/>
-      <c r="M24" s="846"/>
-      <c r="N24" s="847"/>
+      <c r="M24" s="880"/>
+      <c r="N24" s="881"/>
       <c r="O24" s="573"/>
       <c r="P24" s="80"/>
       <c r="Q24" s="82"/>
@@ -40157,8 +40157,8 @@
         <v>144</v>
       </c>
       <c r="L25" s="537"/>
-      <c r="M25" s="846"/>
-      <c r="N25" s="847"/>
+      <c r="M25" s="880"/>
+      <c r="N25" s="881"/>
       <c r="O25" s="573"/>
       <c r="P25" s="80"/>
       <c r="Q25" s="82"/>
@@ -40172,15 +40172,15 @@
       <c r="D26" s="231"/>
       <c r="E26" s="469"/>
       <c r="F26" s="470"/>
-      <c r="H26" s="857"/>
-      <c r="I26" s="857"/>
+      <c r="H26" s="879"/>
+      <c r="I26" s="879"/>
       <c r="J26" s="468"/>
-      <c r="K26" s="852" t="s">
+      <c r="K26" s="875" t="s">
         <v>192</v>
       </c>
-      <c r="L26" s="853"/>
-      <c r="M26" s="853"/>
-      <c r="N26" s="854"/>
+      <c r="L26" s="876"/>
+      <c r="M26" s="876"/>
+      <c r="N26" s="877"/>
       <c r="O26" s="535"/>
       <c r="P26" s="80"/>
       <c r="Q26" s="82"/>
@@ -40197,13 +40197,13 @@
       <c r="H27" s="472"/>
       <c r="I27" s="473"/>
       <c r="J27" s="211"/>
-      <c r="K27" s="848" t="s">
+      <c r="K27" s="871" t="s">
         <v>190</v>
       </c>
-      <c r="L27" s="849"/>
-      <c r="M27" s="849"/>
-      <c r="N27" s="849"/>
-      <c r="O27" s="850"/>
+      <c r="L27" s="872"/>
+      <c r="M27" s="872"/>
+      <c r="N27" s="872"/>
+      <c r="O27" s="873"/>
       <c r="P27" s="80"/>
       <c r="Q27" s="82"/>
       <c r="S27" s="82"/>
@@ -40212,13 +40212,13 @@
     <row r="28" spans="1:20" ht="32.25" customHeight="1" thickBot="1">
       <c r="A28" s="79"/>
       <c r="J28" s="78"/>
-      <c r="K28" s="869" t="s">
+      <c r="K28" s="839" t="s">
         <v>189</v>
       </c>
-      <c r="L28" s="870"/>
-      <c r="M28" s="870"/>
-      <c r="N28" s="870"/>
-      <c r="O28" s="871"/>
+      <c r="L28" s="840"/>
+      <c r="M28" s="840"/>
+      <c r="N28" s="840"/>
+      <c r="O28" s="841"/>
       <c r="P28" s="82"/>
       <c r="Q28" s="82"/>
       <c r="R28" s="79"/>
@@ -40610,6 +40610,46 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="K27:O27"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:O2"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
     <mergeCell ref="K28:O28"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="E13:H13"/>
@@ -40626,46 +40666,6 @@
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:O2"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K27:O27"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -40715,159 +40715,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="21.75" thickBot="1">
-      <c r="A1" s="920" t="s">
+      <c r="A1" s="977" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="921"/>
-      <c r="C1" s="921"/>
-      <c r="D1" s="921"/>
-      <c r="E1" s="921"/>
-      <c r="F1" s="921"/>
-      <c r="G1" s="921"/>
-      <c r="H1" s="921"/>
-      <c r="I1" s="921"/>
-      <c r="J1" s="921"/>
-      <c r="K1" s="921"/>
-      <c r="L1" s="921"/>
-      <c r="M1" s="921"/>
-      <c r="N1" s="921"/>
-      <c r="O1" s="921"/>
-      <c r="P1" s="921"/>
-      <c r="Q1" s="921"/>
-      <c r="R1" s="921"/>
-      <c r="S1" s="921"/>
-      <c r="T1" s="921"/>
-      <c r="U1" s="921"/>
-      <c r="V1" s="921"/>
-      <c r="W1" s="921"/>
-      <c r="X1" s="921"/>
-      <c r="Y1" s="921"/>
-      <c r="Z1" s="921"/>
-      <c r="AA1" s="921"/>
-      <c r="AB1" s="921"/>
-      <c r="AC1" s="921"/>
-      <c r="AD1" s="921"/>
-      <c r="AE1" s="921"/>
-      <c r="AF1" s="921"/>
-      <c r="AG1" s="921"/>
-      <c r="AH1" s="921"/>
-      <c r="AI1" s="922"/>
+      <c r="B1" s="978"/>
+      <c r="C1" s="978"/>
+      <c r="D1" s="978"/>
+      <c r="E1" s="978"/>
+      <c r="F1" s="978"/>
+      <c r="G1" s="978"/>
+      <c r="H1" s="978"/>
+      <c r="I1" s="978"/>
+      <c r="J1" s="978"/>
+      <c r="K1" s="978"/>
+      <c r="L1" s="978"/>
+      <c r="M1" s="978"/>
+      <c r="N1" s="978"/>
+      <c r="O1" s="978"/>
+      <c r="P1" s="978"/>
+      <c r="Q1" s="978"/>
+      <c r="R1" s="978"/>
+      <c r="S1" s="978"/>
+      <c r="T1" s="978"/>
+      <c r="U1" s="978"/>
+      <c r="V1" s="978"/>
+      <c r="W1" s="978"/>
+      <c r="X1" s="978"/>
+      <c r="Y1" s="978"/>
+      <c r="Z1" s="978"/>
+      <c r="AA1" s="978"/>
+      <c r="AB1" s="978"/>
+      <c r="AC1" s="978"/>
+      <c r="AD1" s="978"/>
+      <c r="AE1" s="978"/>
+      <c r="AF1" s="978"/>
+      <c r="AG1" s="978"/>
+      <c r="AH1" s="978"/>
+      <c r="AI1" s="979"/>
     </row>
     <row r="2" spans="1:36" ht="4.5" customHeight="1" thickBot="1">
-      <c r="A2" s="940"/>
-      <c r="B2" s="795"/>
-      <c r="C2" s="795"/>
-      <c r="D2" s="795"/>
-      <c r="E2" s="795"/>
-      <c r="F2" s="795"/>
-      <c r="G2" s="795"/>
-      <c r="H2" s="795"/>
-      <c r="I2" s="795"/>
-      <c r="J2" s="795"/>
-      <c r="K2" s="795"/>
-      <c r="L2" s="795"/>
-      <c r="M2" s="795"/>
-      <c r="N2" s="795"/>
-      <c r="O2" s="795"/>
-      <c r="P2" s="795"/>
-      <c r="Q2" s="795"/>
-      <c r="R2" s="795"/>
-      <c r="S2" s="795"/>
-      <c r="T2" s="795"/>
-      <c r="U2" s="795"/>
-      <c r="V2" s="795"/>
-      <c r="W2" s="795"/>
-      <c r="X2" s="795"/>
-      <c r="Y2" s="795"/>
-      <c r="Z2" s="795"/>
-      <c r="AA2" s="795"/>
-      <c r="AB2" s="795"/>
-      <c r="AC2" s="795"/>
-      <c r="AD2" s="795"/>
-      <c r="AE2" s="795"/>
-      <c r="AF2" s="795"/>
-      <c r="AG2" s="795"/>
-      <c r="AH2" s="795"/>
-      <c r="AI2" s="796"/>
+      <c r="A2" s="995"/>
+      <c r="B2" s="830"/>
+      <c r="C2" s="830"/>
+      <c r="D2" s="830"/>
+      <c r="E2" s="830"/>
+      <c r="F2" s="830"/>
+      <c r="G2" s="830"/>
+      <c r="H2" s="830"/>
+      <c r="I2" s="830"/>
+      <c r="J2" s="830"/>
+      <c r="K2" s="830"/>
+      <c r="L2" s="830"/>
+      <c r="M2" s="830"/>
+      <c r="N2" s="830"/>
+      <c r="O2" s="830"/>
+      <c r="P2" s="830"/>
+      <c r="Q2" s="830"/>
+      <c r="R2" s="830"/>
+      <c r="S2" s="830"/>
+      <c r="T2" s="830"/>
+      <c r="U2" s="830"/>
+      <c r="V2" s="830"/>
+      <c r="W2" s="830"/>
+      <c r="X2" s="830"/>
+      <c r="Y2" s="830"/>
+      <c r="Z2" s="830"/>
+      <c r="AA2" s="830"/>
+      <c r="AB2" s="830"/>
+      <c r="AC2" s="830"/>
+      <c r="AD2" s="830"/>
+      <c r="AE2" s="830"/>
+      <c r="AF2" s="830"/>
+      <c r="AG2" s="830"/>
+      <c r="AH2" s="830"/>
+      <c r="AI2" s="831"/>
     </row>
     <row r="3" spans="1:36" ht="15.75">
-      <c r="A3" s="956" t="s">
+      <c r="A3" s="1011" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="957"/>
-      <c r="C3" s="957"/>
-      <c r="D3" s="957"/>
-      <c r="E3" s="957"/>
-      <c r="F3" s="957"/>
-      <c r="G3" s="957"/>
-      <c r="H3" s="957"/>
-      <c r="I3" s="957"/>
-      <c r="J3" s="957"/>
-      <c r="K3" s="957"/>
-      <c r="L3" s="957"/>
-      <c r="M3" s="957"/>
-      <c r="N3" s="957"/>
-      <c r="O3" s="957"/>
-      <c r="P3" s="957"/>
-      <c r="Q3" s="957"/>
-      <c r="R3" s="957"/>
-      <c r="S3" s="957"/>
-      <c r="T3" s="957"/>
-      <c r="U3" s="957"/>
-      <c r="V3" s="957"/>
-      <c r="W3" s="957"/>
-      <c r="X3" s="957"/>
-      <c r="Y3" s="957"/>
-      <c r="Z3" s="957"/>
-      <c r="AA3" s="957"/>
-      <c r="AB3" s="957"/>
-      <c r="AC3" s="957"/>
-      <c r="AD3" s="957"/>
-      <c r="AE3" s="957"/>
-      <c r="AF3" s="957"/>
-      <c r="AG3" s="957"/>
-      <c r="AH3" s="957"/>
-      <c r="AI3" s="958"/>
+      <c r="B3" s="1012"/>
+      <c r="C3" s="1012"/>
+      <c r="D3" s="1012"/>
+      <c r="E3" s="1012"/>
+      <c r="F3" s="1012"/>
+      <c r="G3" s="1012"/>
+      <c r="H3" s="1012"/>
+      <c r="I3" s="1012"/>
+      <c r="J3" s="1012"/>
+      <c r="K3" s="1012"/>
+      <c r="L3" s="1012"/>
+      <c r="M3" s="1012"/>
+      <c r="N3" s="1012"/>
+      <c r="O3" s="1012"/>
+      <c r="P3" s="1012"/>
+      <c r="Q3" s="1012"/>
+      <c r="R3" s="1012"/>
+      <c r="S3" s="1012"/>
+      <c r="T3" s="1012"/>
+      <c r="U3" s="1012"/>
+      <c r="V3" s="1012"/>
+      <c r="W3" s="1012"/>
+      <c r="X3" s="1012"/>
+      <c r="Y3" s="1012"/>
+      <c r="Z3" s="1012"/>
+      <c r="AA3" s="1012"/>
+      <c r="AB3" s="1012"/>
+      <c r="AC3" s="1012"/>
+      <c r="AD3" s="1012"/>
+      <c r="AE3" s="1012"/>
+      <c r="AF3" s="1012"/>
+      <c r="AG3" s="1012"/>
+      <c r="AH3" s="1012"/>
+      <c r="AI3" s="1013"/>
       <c r="AJ3" s="98"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A4" s="953" t="s">
+      <c r="A4" s="1008" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="954"/>
-      <c r="C4" s="954"/>
-      <c r="D4" s="954"/>
-      <c r="E4" s="954"/>
-      <c r="F4" s="954"/>
-      <c r="G4" s="954"/>
-      <c r="H4" s="954"/>
-      <c r="I4" s="954"/>
-      <c r="J4" s="954"/>
-      <c r="K4" s="954"/>
-      <c r="L4" s="954"/>
-      <c r="M4" s="954"/>
-      <c r="N4" s="954"/>
-      <c r="O4" s="954"/>
-      <c r="P4" s="954"/>
-      <c r="Q4" s="954"/>
-      <c r="R4" s="954"/>
-      <c r="S4" s="954"/>
-      <c r="T4" s="954"/>
-      <c r="U4" s="954"/>
-      <c r="V4" s="954"/>
-      <c r="W4" s="954"/>
-      <c r="X4" s="954"/>
-      <c r="Y4" s="954"/>
-      <c r="Z4" s="954"/>
-      <c r="AA4" s="954"/>
-      <c r="AB4" s="954"/>
-      <c r="AC4" s="954"/>
-      <c r="AD4" s="954"/>
-      <c r="AE4" s="954"/>
-      <c r="AF4" s="954"/>
-      <c r="AG4" s="954"/>
-      <c r="AH4" s="954"/>
-      <c r="AI4" s="955"/>
+      <c r="B4" s="1009"/>
+      <c r="C4" s="1009"/>
+      <c r="D4" s="1009"/>
+      <c r="E4" s="1009"/>
+      <c r="F4" s="1009"/>
+      <c r="G4" s="1009"/>
+      <c r="H4" s="1009"/>
+      <c r="I4" s="1009"/>
+      <c r="J4" s="1009"/>
+      <c r="K4" s="1009"/>
+      <c r="L4" s="1009"/>
+      <c r="M4" s="1009"/>
+      <c r="N4" s="1009"/>
+      <c r="O4" s="1009"/>
+      <c r="P4" s="1009"/>
+      <c r="Q4" s="1009"/>
+      <c r="R4" s="1009"/>
+      <c r="S4" s="1009"/>
+      <c r="T4" s="1009"/>
+      <c r="U4" s="1009"/>
+      <c r="V4" s="1009"/>
+      <c r="W4" s="1009"/>
+      <c r="X4" s="1009"/>
+      <c r="Y4" s="1009"/>
+      <c r="Z4" s="1009"/>
+      <c r="AA4" s="1009"/>
+      <c r="AB4" s="1009"/>
+      <c r="AC4" s="1009"/>
+      <c r="AD4" s="1009"/>
+      <c r="AE4" s="1009"/>
+      <c r="AF4" s="1009"/>
+      <c r="AG4" s="1009"/>
+      <c r="AH4" s="1009"/>
+      <c r="AI4" s="1010"/>
     </row>
     <row r="5" spans="1:36" ht="11.25" customHeight="1" thickBot="1">
       <c r="A5" s="230"/>
@@ -40905,44 +40905,44 @@
       <c r="A6" s="136"/>
       <c r="C6" s="151"/>
       <c r="D6" s="124"/>
-      <c r="E6" s="968" t="s">
+      <c r="E6" s="1023" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="969"/>
-      <c r="G6" s="970"/>
+      <c r="F6" s="1024"/>
+      <c r="G6" s="1025"/>
       <c r="H6" s="356"/>
       <c r="I6" s="229"/>
-      <c r="J6" s="941" t="s">
+      <c r="J6" s="996" t="s">
         <v>92</v>
       </c>
-      <c r="K6" s="942"/>
-      <c r="L6" s="943"/>
+      <c r="K6" s="997"/>
+      <c r="L6" s="998"/>
       <c r="M6" s="359"/>
       <c r="N6" s="229"/>
       <c r="O6" s="362"/>
       <c r="P6" s="362"/>
-      <c r="Q6" s="962" t="s">
+      <c r="Q6" s="1017" t="s">
         <v>93</v>
       </c>
-      <c r="R6" s="963"/>
+      <c r="R6" s="1018"/>
       <c r="S6" s="360"/>
       <c r="T6" s="229"/>
       <c r="U6" s="362"/>
       <c r="V6" s="362"/>
-      <c r="W6" s="941" t="s">
+      <c r="W6" s="996" t="s">
         <v>104</v>
       </c>
-      <c r="X6" s="942"/>
-      <c r="Y6" s="942"/>
-      <c r="Z6" s="943"/>
+      <c r="X6" s="997"/>
+      <c r="Y6" s="997"/>
+      <c r="Z6" s="998"/>
       <c r="AA6" s="398"/>
       <c r="AB6" s="229"/>
       <c r="AC6" s="362"/>
-      <c r="AD6" s="934" t="s">
+      <c r="AD6" s="989" t="s">
         <v>94</v>
       </c>
-      <c r="AE6" s="935"/>
-      <c r="AF6" s="936"/>
+      <c r="AE6" s="990"/>
+      <c r="AF6" s="991"/>
       <c r="AG6" s="136"/>
       <c r="AH6" s="386"/>
       <c r="AI6" s="406"/>
@@ -40951,34 +40951,34 @@
       <c r="A7" s="136"/>
       <c r="B7" s="100"/>
       <c r="C7" s="23"/>
-      <c r="E7" s="971"/>
-      <c r="F7" s="972"/>
-      <c r="G7" s="973"/>
+      <c r="E7" s="1026"/>
+      <c r="F7" s="1027"/>
+      <c r="G7" s="1028"/>
       <c r="H7" s="356"/>
       <c r="I7" s="233"/>
-      <c r="J7" s="959"/>
-      <c r="K7" s="960"/>
-      <c r="L7" s="961"/>
+      <c r="J7" s="1014"/>
+      <c r="K7" s="1015"/>
+      <c r="L7" s="1016"/>
       <c r="M7" s="359"/>
       <c r="N7" s="233"/>
       <c r="O7" s="354"/>
       <c r="P7" s="361"/>
-      <c r="Q7" s="864"/>
-      <c r="R7" s="964"/>
+      <c r="Q7" s="865"/>
+      <c r="R7" s="1019"/>
       <c r="S7" s="360"/>
       <c r="T7" s="233"/>
       <c r="U7" s="354"/>
       <c r="V7" s="361"/>
-      <c r="W7" s="944"/>
-      <c r="X7" s="945"/>
-      <c r="Y7" s="945"/>
-      <c r="Z7" s="946"/>
+      <c r="W7" s="999"/>
+      <c r="X7" s="1000"/>
+      <c r="Y7" s="1000"/>
+      <c r="Z7" s="1001"/>
       <c r="AA7" s="398"/>
       <c r="AB7" s="233"/>
       <c r="AC7" s="354"/>
-      <c r="AD7" s="937"/>
-      <c r="AE7" s="938"/>
-      <c r="AF7" s="939"/>
+      <c r="AD7" s="992"/>
+      <c r="AE7" s="993"/>
+      <c r="AF7" s="994"/>
       <c r="AG7" s="136"/>
       <c r="AH7" s="386"/>
       <c r="AI7" s="406"/>
@@ -40987,44 +40987,44 @@
       <c r="A8" s="136"/>
       <c r="B8" s="363"/>
       <c r="C8" s="206"/>
-      <c r="E8" s="947">
+      <c r="E8" s="1002">
         <v>64</v>
       </c>
-      <c r="F8" s="948"/>
-      <c r="G8" s="974"/>
+      <c r="F8" s="1003"/>
+      <c r="G8" s="1029"/>
       <c r="H8" s="152"/>
       <c r="I8" s="136"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="978">
+      <c r="K8" s="1033">
         <v>16</v>
       </c>
-      <c r="L8" s="979"/>
+      <c r="L8" s="1034"/>
       <c r="M8" s="359"/>
       <c r="N8" s="136"/>
       <c r="O8" s="79"/>
-      <c r="P8" s="947">
+      <c r="P8" s="1002">
         <v>10</v>
       </c>
-      <c r="Q8" s="948"/>
-      <c r="R8" s="949"/>
+      <c r="Q8" s="1003"/>
+      <c r="R8" s="1004"/>
       <c r="S8" s="360"/>
       <c r="T8" s="136"/>
       <c r="U8" s="79"/>
-      <c r="V8" s="947">
+      <c r="V8" s="1002">
         <v>38</v>
       </c>
-      <c r="W8" s="948"/>
-      <c r="X8" s="948"/>
-      <c r="Y8" s="948"/>
-      <c r="Z8" s="949"/>
+      <c r="W8" s="1003"/>
+      <c r="X8" s="1003"/>
+      <c r="Y8" s="1003"/>
+      <c r="Z8" s="1004"/>
       <c r="AA8" s="399"/>
       <c r="AB8" s="136"/>
       <c r="AC8" s="79"/>
-      <c r="AD8" s="947">
+      <c r="AD8" s="1002">
         <v>20</v>
       </c>
-      <c r="AE8" s="948"/>
-      <c r="AF8" s="949"/>
+      <c r="AE8" s="1003"/>
+      <c r="AF8" s="1004"/>
       <c r="AG8" s="136"/>
       <c r="AH8" s="387"/>
       <c r="AI8" s="232"/>
@@ -41034,33 +41034,33 @@
       <c r="B9" s="100"/>
       <c r="C9" s="144"/>
       <c r="D9" s="352"/>
-      <c r="E9" s="975"/>
-      <c r="F9" s="976"/>
-      <c r="G9" s="977"/>
+      <c r="E9" s="1030"/>
+      <c r="F9" s="1031"/>
+      <c r="G9" s="1032"/>
       <c r="I9" s="137"/>
       <c r="J9" s="353"/>
-      <c r="K9" s="980"/>
-      <c r="L9" s="981"/>
+      <c r="K9" s="1035"/>
+      <c r="L9" s="1036"/>
       <c r="M9" s="360"/>
       <c r="N9" s="137"/>
       <c r="O9" s="353"/>
-      <c r="P9" s="950"/>
-      <c r="Q9" s="951"/>
-      <c r="R9" s="952"/>
+      <c r="P9" s="1005"/>
+      <c r="Q9" s="1006"/>
+      <c r="R9" s="1007"/>
       <c r="S9" s="360"/>
       <c r="T9" s="137"/>
       <c r="U9" s="353"/>
-      <c r="V9" s="950"/>
-      <c r="W9" s="951"/>
-      <c r="X9" s="951"/>
-      <c r="Y9" s="951"/>
-      <c r="Z9" s="952"/>
+      <c r="V9" s="1005"/>
+      <c r="W9" s="1006"/>
+      <c r="X9" s="1006"/>
+      <c r="Y9" s="1006"/>
+      <c r="Z9" s="1007"/>
       <c r="AA9" s="399"/>
       <c r="AB9" s="137"/>
       <c r="AC9" s="353"/>
-      <c r="AD9" s="950"/>
-      <c r="AE9" s="951"/>
-      <c r="AF9" s="952"/>
+      <c r="AD9" s="1005"/>
+      <c r="AE9" s="1006"/>
+      <c r="AF9" s="1007"/>
       <c r="AG9" s="400"/>
       <c r="AH9" s="387"/>
       <c r="AI9" s="165"/>
@@ -41116,23 +41116,23 @@
       <c r="M11" s="148"/>
       <c r="N11" s="148"/>
       <c r="O11" s="82"/>
-      <c r="Q11" s="887" t="s">
+      <c r="Q11" s="1043" t="s">
         <v>163</v>
       </c>
-      <c r="R11" s="888"/>
-      <c r="S11" s="888"/>
-      <c r="T11" s="888"/>
-      <c r="U11" s="888"/>
-      <c r="V11" s="888"/>
-      <c r="W11" s="888"/>
-      <c r="X11" s="888"/>
-      <c r="Y11" s="888"/>
-      <c r="Z11" s="888"/>
-      <c r="AA11" s="888"/>
-      <c r="AB11" s="888"/>
-      <c r="AC11" s="888"/>
-      <c r="AD11" s="888"/>
-      <c r="AE11" s="888"/>
+      <c r="R11" s="1044"/>
+      <c r="S11" s="1044"/>
+      <c r="T11" s="1044"/>
+      <c r="U11" s="1044"/>
+      <c r="V11" s="1044"/>
+      <c r="W11" s="1044"/>
+      <c r="X11" s="1044"/>
+      <c r="Y11" s="1044"/>
+      <c r="Z11" s="1044"/>
+      <c r="AA11" s="1044"/>
+      <c r="AB11" s="1044"/>
+      <c r="AC11" s="1044"/>
+      <c r="AD11" s="1044"/>
+      <c r="AE11" s="1044"/>
       <c r="AF11" s="438">
         <v>2025</v>
       </c>
@@ -41142,25 +41142,25 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1">
       <c r="A12" s="407"/>
-      <c r="B12" s="901" t="s">
+      <c r="B12" s="1053" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="902"/>
-      <c r="D12" s="902"/>
-      <c r="E12" s="903"/>
-      <c r="F12" s="891" t="s">
+      <c r="C12" s="1054"/>
+      <c r="D12" s="1054"/>
+      <c r="E12" s="1055"/>
+      <c r="F12" s="1046" t="s">
         <v>151</v>
       </c>
-      <c r="G12" s="892"/>
-      <c r="H12" s="892"/>
-      <c r="I12" s="892"/>
-      <c r="J12" s="892"/>
-      <c r="K12" s="892"/>
-      <c r="L12" s="892"/>
-      <c r="M12" s="891" t="s">
+      <c r="G12" s="1047"/>
+      <c r="H12" s="1047"/>
+      <c r="I12" s="1047"/>
+      <c r="J12" s="1047"/>
+      <c r="K12" s="1047"/>
+      <c r="L12" s="1047"/>
+      <c r="M12" s="1046" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="895"/>
+      <c r="N12" s="1050"/>
       <c r="O12" s="366"/>
       <c r="P12" s="79"/>
       <c r="Q12" s="436"/>
@@ -41213,19 +41213,19 @@
     </row>
     <row r="13" spans="1:36" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="230"/>
-      <c r="B13" s="904"/>
-      <c r="C13" s="905"/>
-      <c r="D13" s="905"/>
-      <c r="E13" s="906"/>
-      <c r="F13" s="893"/>
-      <c r="G13" s="894"/>
-      <c r="H13" s="894"/>
-      <c r="I13" s="894"/>
-      <c r="J13" s="894"/>
-      <c r="K13" s="894"/>
-      <c r="L13" s="894"/>
-      <c r="M13" s="896"/>
-      <c r="N13" s="897"/>
+      <c r="B13" s="1056"/>
+      <c r="C13" s="1057"/>
+      <c r="D13" s="1057"/>
+      <c r="E13" s="1058"/>
+      <c r="F13" s="1048"/>
+      <c r="G13" s="1049"/>
+      <c r="H13" s="1049"/>
+      <c r="I13" s="1049"/>
+      <c r="J13" s="1049"/>
+      <c r="K13" s="1049"/>
+      <c r="L13" s="1049"/>
+      <c r="M13" s="1051"/>
+      <c r="N13" s="1052"/>
       <c r="O13" s="366"/>
       <c r="P13" s="79"/>
       <c r="Q13" s="421"/>
@@ -41292,25 +41292,25 @@
     </row>
     <row r="14" spans="1:36" ht="13.5" customHeight="1">
       <c r="A14" s="407"/>
-      <c r="B14" s="904"/>
-      <c r="C14" s="905"/>
-      <c r="D14" s="905"/>
-      <c r="E14" s="906"/>
-      <c r="F14" s="910" t="s">
+      <c r="B14" s="1056"/>
+      <c r="C14" s="1057"/>
+      <c r="D14" s="1057"/>
+      <c r="E14" s="1058"/>
+      <c r="F14" s="1062" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="911"/>
-      <c r="H14" s="914" t="s">
+      <c r="G14" s="1063"/>
+      <c r="H14" s="1066" t="s">
         <v>153</v>
       </c>
-      <c r="I14" s="915"/>
-      <c r="J14" s="918" t="s">
+      <c r="I14" s="1067"/>
+      <c r="J14" s="1070" t="s">
         <v>154</v>
       </c>
-      <c r="K14" s="919"/>
-      <c r="L14" s="919"/>
-      <c r="M14" s="896"/>
-      <c r="N14" s="897"/>
+      <c r="K14" s="1071"/>
+      <c r="L14" s="1071"/>
+      <c r="M14" s="1051"/>
+      <c r="N14" s="1052"/>
       <c r="O14" s="366"/>
       <c r="P14" s="79"/>
       <c r="Q14" s="421"/>
@@ -41379,19 +41379,19 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1">
       <c r="A15" s="407"/>
-      <c r="B15" s="907"/>
-      <c r="C15" s="908"/>
-      <c r="D15" s="908"/>
-      <c r="E15" s="909"/>
-      <c r="F15" s="912"/>
-      <c r="G15" s="913"/>
-      <c r="H15" s="916"/>
-      <c r="I15" s="917"/>
-      <c r="J15" s="918"/>
-      <c r="K15" s="919"/>
-      <c r="L15" s="919"/>
-      <c r="M15" s="896"/>
-      <c r="N15" s="897"/>
+      <c r="B15" s="1059"/>
+      <c r="C15" s="1060"/>
+      <c r="D15" s="1060"/>
+      <c r="E15" s="1061"/>
+      <c r="F15" s="1064"/>
+      <c r="G15" s="1065"/>
+      <c r="H15" s="1068"/>
+      <c r="I15" s="1069"/>
+      <c r="J15" s="1070"/>
+      <c r="K15" s="1071"/>
+      <c r="L15" s="1071"/>
+      <c r="M15" s="1051"/>
+      <c r="N15" s="1052"/>
       <c r="P15" s="79"/>
       <c r="Q15" s="421"/>
       <c r="R15" s="411"/>
@@ -41457,12 +41457,12 @@
     </row>
     <row r="16" spans="1:36" ht="15.75">
       <c r="A16" s="230"/>
-      <c r="B16" s="898" t="s">
+      <c r="B16" s="1037" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="899"/>
-      <c r="D16" s="899"/>
-      <c r="E16" s="899"/>
+      <c r="C16" s="1038"/>
+      <c r="D16" s="1038"/>
+      <c r="E16" s="1038"/>
       <c r="F16" s="786">
         <v>2</v>
       </c>
@@ -41479,7 +41479,7 @@
       <c r="M16" s="786">
         <v>16</v>
       </c>
-      <c r="N16" s="900"/>
+      <c r="N16" s="1042"/>
       <c r="O16" s="366"/>
       <c r="P16" s="79"/>
       <c r="Q16" s="421"/>
@@ -41504,12 +41504,12 @@
     </row>
     <row r="17" spans="1:36" ht="15.75">
       <c r="A17" s="407"/>
-      <c r="B17" s="898" t="s">
+      <c r="B17" s="1037" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="899"/>
-      <c r="D17" s="899"/>
-      <c r="E17" s="899"/>
+      <c r="C17" s="1038"/>
+      <c r="D17" s="1038"/>
+      <c r="E17" s="1038"/>
       <c r="F17" s="786">
         <v>0</v>
       </c>
@@ -41526,7 +41526,7 @@
       <c r="M17" s="786">
         <v>10</v>
       </c>
-      <c r="N17" s="900"/>
+      <c r="N17" s="1042"/>
       <c r="O17" s="116"/>
       <c r="P17" s="79"/>
       <c r="Q17" s="418"/>
@@ -41593,29 +41593,29 @@
     </row>
     <row r="18" spans="1:36" ht="16.5" thickBot="1">
       <c r="A18" s="230"/>
-      <c r="B18" s="982" t="s">
+      <c r="B18" s="1039" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="983"/>
-      <c r="D18" s="983"/>
-      <c r="E18" s="983"/>
-      <c r="F18" s="889">
+      <c r="C18" s="1040"/>
+      <c r="D18" s="1040"/>
+      <c r="E18" s="1040"/>
+      <c r="F18" s="1041">
         <v>10</v>
       </c>
-      <c r="G18" s="889"/>
-      <c r="H18" s="889">
+      <c r="G18" s="1041"/>
+      <c r="H18" s="1041">
         <v>38</v>
       </c>
-      <c r="I18" s="889"/>
-      <c r="J18" s="965">
+      <c r="I18" s="1041"/>
+      <c r="J18" s="1020">
         <v>25</v>
       </c>
-      <c r="K18" s="966"/>
-      <c r="L18" s="967"/>
-      <c r="M18" s="889">
+      <c r="K18" s="1021"/>
+      <c r="L18" s="1022"/>
+      <c r="M18" s="1041">
         <v>38</v>
       </c>
-      <c r="N18" s="890"/>
+      <c r="N18" s="1045"/>
       <c r="O18" s="155"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="421"/>
@@ -42161,15 +42161,15 @@
       <c r="M27" s="82"/>
       <c r="N27" s="82"/>
       <c r="P27" s="392"/>
-      <c r="Q27" s="923" t="s">
+      <c r="Q27" s="980" t="s">
         <v>157</v>
       </c>
-      <c r="R27" s="924"/>
-      <c r="S27" s="924"/>
-      <c r="T27" s="924"/>
-      <c r="U27" s="924"/>
-      <c r="V27" s="924"/>
-      <c r="W27" s="925"/>
+      <c r="R27" s="981"/>
+      <c r="S27" s="981"/>
+      <c r="T27" s="981"/>
+      <c r="U27" s="981"/>
+      <c r="V27" s="981"/>
+      <c r="W27" s="982"/>
       <c r="X27" s="396"/>
       <c r="Y27" s="388"/>
       <c r="Z27" s="227"/>
@@ -42241,11 +42241,11 @@
       <c r="Q29" s="389"/>
       <c r="R29" s="193"/>
       <c r="S29" s="193"/>
-      <c r="T29" s="928" t="s">
+      <c r="T29" s="983" t="s">
         <v>156</v>
       </c>
-      <c r="U29" s="929"/>
-      <c r="V29" s="930"/>
+      <c r="U29" s="984"/>
+      <c r="V29" s="985"/>
       <c r="W29" s="402"/>
       <c r="X29" s="389"/>
       <c r="Y29" s="193"/>
@@ -42276,29 +42276,29 @@
       <c r="M30" s="82"/>
       <c r="N30" s="82"/>
       <c r="O30" s="88"/>
-      <c r="Q30" s="926" t="s">
+      <c r="Q30" s="911" t="s">
         <v>50</v>
       </c>
-      <c r="R30" s="927"/>
-      <c r="S30" s="927"/>
-      <c r="T30" s="931"/>
-      <c r="U30" s="932"/>
-      <c r="V30" s="933"/>
-      <c r="W30" s="926" t="s">
+      <c r="R30" s="912"/>
+      <c r="S30" s="912"/>
+      <c r="T30" s="986"/>
+      <c r="U30" s="987"/>
+      <c r="V30" s="988"/>
+      <c r="W30" s="911" t="s">
         <v>51</v>
       </c>
-      <c r="X30" s="927"/>
-      <c r="Y30" s="927"/>
-      <c r="Z30" s="1006" t="s">
+      <c r="X30" s="912"/>
+      <c r="Y30" s="912"/>
+      <c r="Z30" s="967" t="s">
         <v>52</v>
       </c>
-      <c r="AA30" s="927"/>
-      <c r="AB30" s="1015"/>
-      <c r="AC30" s="1006" t="s">
+      <c r="AA30" s="912"/>
+      <c r="AB30" s="972"/>
+      <c r="AC30" s="967" t="s">
         <v>53</v>
       </c>
-      <c r="AD30" s="927"/>
-      <c r="AE30" s="1007"/>
+      <c r="AD30" s="912"/>
+      <c r="AE30" s="968"/>
       <c r="AF30" s="390"/>
       <c r="AG30" s="227"/>
       <c r="AH30" s="82"/>
@@ -42321,21 +42321,21 @@
       <c r="N31" s="82"/>
       <c r="O31" s="83"/>
       <c r="P31" s="103"/>
-      <c r="Q31" s="1053"/>
-      <c r="R31" s="1054"/>
-      <c r="S31" s="1055"/>
-      <c r="T31" s="1056"/>
-      <c r="U31" s="1057"/>
-      <c r="V31" s="1058"/>
-      <c r="W31" s="1042"/>
-      <c r="X31" s="1043"/>
-      <c r="Y31" s="1043"/>
-      <c r="Z31" s="1008"/>
-      <c r="AA31" s="1009"/>
-      <c r="AB31" s="1016"/>
-      <c r="AC31" s="1008"/>
-      <c r="AD31" s="1009"/>
-      <c r="AE31" s="1010"/>
+      <c r="Q31" s="929"/>
+      <c r="R31" s="930"/>
+      <c r="S31" s="931"/>
+      <c r="T31" s="938"/>
+      <c r="U31" s="939"/>
+      <c r="V31" s="940"/>
+      <c r="W31" s="913"/>
+      <c r="X31" s="914"/>
+      <c r="Y31" s="914"/>
+      <c r="Z31" s="969"/>
+      <c r="AA31" s="970"/>
+      <c r="AB31" s="973"/>
+      <c r="AC31" s="969"/>
+      <c r="AD31" s="970"/>
+      <c r="AE31" s="971"/>
       <c r="AF31" s="391"/>
       <c r="AG31" s="82"/>
       <c r="AH31" s="82"/>
@@ -42358,21 +42358,21 @@
       <c r="N32" s="90"/>
       <c r="O32" s="83"/>
       <c r="P32" s="79"/>
-      <c r="Q32" s="993"/>
-      <c r="R32" s="994"/>
-      <c r="S32" s="995"/>
-      <c r="T32" s="1003"/>
-      <c r="U32" s="1004"/>
-      <c r="V32" s="1005"/>
-      <c r="W32" s="1001"/>
-      <c r="X32" s="1002"/>
-      <c r="Y32" s="1002"/>
-      <c r="Z32" s="1011"/>
-      <c r="AA32" s="1012"/>
-      <c r="AB32" s="1017"/>
-      <c r="AC32" s="1011"/>
-      <c r="AD32" s="1012"/>
-      <c r="AE32" s="1013"/>
+      <c r="Q32" s="932"/>
+      <c r="R32" s="933"/>
+      <c r="S32" s="934"/>
+      <c r="T32" s="922"/>
+      <c r="U32" s="923"/>
+      <c r="V32" s="924"/>
+      <c r="W32" s="915"/>
+      <c r="X32" s="916"/>
+      <c r="Y32" s="916"/>
+      <c r="Z32" s="952"/>
+      <c r="AA32" s="953"/>
+      <c r="AB32" s="964"/>
+      <c r="AC32" s="952"/>
+      <c r="AD32" s="953"/>
+      <c r="AE32" s="954"/>
       <c r="AF32" s="80"/>
       <c r="AG32" s="82"/>
       <c r="AH32" s="82"/>
@@ -42380,42 +42380,42 @@
     </row>
     <row r="33" spans="1:35" ht="19.5" thickBot="1">
       <c r="A33" s="230"/>
-      <c r="B33" s="1022" t="s">
+      <c r="B33" s="903" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="1023"/>
-      <c r="D33" s="1023"/>
-      <c r="E33" s="1024"/>
-      <c r="F33" s="1069" t="s">
+      <c r="C33" s="945"/>
+      <c r="D33" s="945"/>
+      <c r="E33" s="904"/>
+      <c r="F33" s="900" t="s">
         <v>159</v>
       </c>
-      <c r="G33" s="1070"/>
-      <c r="H33" s="1070"/>
-      <c r="I33" s="1070"/>
-      <c r="J33" s="1070"/>
-      <c r="K33" s="1070"/>
-      <c r="L33" s="1071"/>
-      <c r="M33" s="1022" t="s">
+      <c r="G33" s="901"/>
+      <c r="H33" s="901"/>
+      <c r="I33" s="901"/>
+      <c r="J33" s="901"/>
+      <c r="K33" s="901"/>
+      <c r="L33" s="902"/>
+      <c r="M33" s="903" t="s">
         <v>88</v>
       </c>
-      <c r="N33" s="1024"/>
+      <c r="N33" s="904"/>
       <c r="O33" s="78"/>
       <c r="P33" s="103"/>
-      <c r="Q33" s="993"/>
-      <c r="R33" s="994"/>
-      <c r="S33" s="995"/>
-      <c r="T33" s="1003"/>
-      <c r="U33" s="1004"/>
-      <c r="V33" s="1005"/>
-      <c r="W33" s="1001"/>
-      <c r="X33" s="1002"/>
-      <c r="Y33" s="1002"/>
-      <c r="Z33" s="1011"/>
-      <c r="AA33" s="1012"/>
-      <c r="AB33" s="1017"/>
-      <c r="AC33" s="1011"/>
-      <c r="AD33" s="1012"/>
-      <c r="AE33" s="1013"/>
+      <c r="Q33" s="932"/>
+      <c r="R33" s="933"/>
+      <c r="S33" s="934"/>
+      <c r="T33" s="922"/>
+      <c r="U33" s="923"/>
+      <c r="V33" s="924"/>
+      <c r="W33" s="915"/>
+      <c r="X33" s="916"/>
+      <c r="Y33" s="916"/>
+      <c r="Z33" s="952"/>
+      <c r="AA33" s="953"/>
+      <c r="AB33" s="964"/>
+      <c r="AC33" s="952"/>
+      <c r="AD33" s="953"/>
+      <c r="AE33" s="954"/>
       <c r="AF33" s="80"/>
       <c r="AG33" s="82"/>
       <c r="AH33" s="82"/>
@@ -42423,42 +42423,42 @@
     </row>
     <row r="34" spans="1:35" ht="30.75" customHeight="1" thickBot="1">
       <c r="A34" s="233"/>
-      <c r="B34" s="1025"/>
-      <c r="C34" s="1026"/>
-      <c r="D34" s="1026"/>
-      <c r="E34" s="1027"/>
-      <c r="F34" s="1028" t="s">
+      <c r="B34" s="905"/>
+      <c r="C34" s="946"/>
+      <c r="D34" s="946"/>
+      <c r="E34" s="906"/>
+      <c r="F34" s="947" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="1029"/>
-      <c r="H34" s="1030"/>
-      <c r="I34" s="1031" t="s">
+      <c r="G34" s="948"/>
+      <c r="H34" s="949"/>
+      <c r="I34" s="950" t="s">
         <v>161</v>
       </c>
-      <c r="J34" s="1032"/>
-      <c r="K34" s="1067" t="s">
+      <c r="J34" s="951"/>
+      <c r="K34" s="898" t="s">
         <v>162</v>
       </c>
-      <c r="L34" s="1068"/>
-      <c r="M34" s="1025"/>
-      <c r="N34" s="1027"/>
+      <c r="L34" s="899"/>
+      <c r="M34" s="905"/>
+      <c r="N34" s="906"/>
       <c r="O34" s="78"/>
       <c r="P34" s="103"/>
-      <c r="Q34" s="993"/>
-      <c r="R34" s="994"/>
-      <c r="S34" s="995"/>
-      <c r="T34" s="1003"/>
-      <c r="U34" s="1004"/>
-      <c r="V34" s="1005"/>
-      <c r="W34" s="1001"/>
-      <c r="X34" s="1002"/>
-      <c r="Y34" s="1002"/>
-      <c r="Z34" s="1011"/>
-      <c r="AA34" s="1012"/>
-      <c r="AB34" s="1017"/>
-      <c r="AC34" s="1011"/>
-      <c r="AD34" s="1012"/>
-      <c r="AE34" s="1013"/>
+      <c r="Q34" s="932"/>
+      <c r="R34" s="933"/>
+      <c r="S34" s="934"/>
+      <c r="T34" s="922"/>
+      <c r="U34" s="923"/>
+      <c r="V34" s="924"/>
+      <c r="W34" s="915"/>
+      <c r="X34" s="916"/>
+      <c r="Y34" s="916"/>
+      <c r="Z34" s="952"/>
+      <c r="AA34" s="953"/>
+      <c r="AB34" s="964"/>
+      <c r="AC34" s="952"/>
+      <c r="AD34" s="953"/>
+      <c r="AE34" s="954"/>
       <c r="AF34" s="80"/>
       <c r="AG34" s="82"/>
       <c r="AH34" s="82"/>
@@ -42466,46 +42466,46 @@
     </row>
     <row r="35" spans="1:35" ht="22.5" customHeight="1">
       <c r="A35" s="409"/>
-      <c r="B35" s="1041" t="s">
+      <c r="B35" s="910" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="1041"/>
-      <c r="D35" s="1041"/>
-      <c r="E35" s="1041"/>
-      <c r="F35" s="1041">
+      <c r="C35" s="910"/>
+      <c r="D35" s="910"/>
+      <c r="E35" s="910"/>
+      <c r="F35" s="910">
         <v>4</v>
       </c>
-      <c r="G35" s="1041"/>
-      <c r="H35" s="1041"/>
-      <c r="I35" s="1041">
+      <c r="G35" s="910"/>
+      <c r="H35" s="910"/>
+      <c r="I35" s="910">
         <v>10</v>
       </c>
-      <c r="J35" s="1041"/>
-      <c r="K35" s="1041">
+      <c r="J35" s="910"/>
+      <c r="K35" s="910">
         <v>0</v>
       </c>
-      <c r="L35" s="1041"/>
-      <c r="M35" s="1041">
+      <c r="L35" s="910"/>
+      <c r="M35" s="910">
         <v>20</v>
       </c>
-      <c r="N35" s="1041"/>
+      <c r="N35" s="910"/>
       <c r="O35" s="83"/>
       <c r="P35" s="79"/>
-      <c r="Q35" s="990"/>
-      <c r="R35" s="991"/>
-      <c r="S35" s="992"/>
-      <c r="T35" s="996"/>
-      <c r="U35" s="997"/>
-      <c r="V35" s="998"/>
-      <c r="W35" s="999"/>
-      <c r="X35" s="1000"/>
-      <c r="Y35" s="1000"/>
-      <c r="Z35" s="984"/>
-      <c r="AA35" s="985"/>
-      <c r="AB35" s="1014"/>
-      <c r="AC35" s="984"/>
-      <c r="AD35" s="985"/>
-      <c r="AE35" s="986"/>
+      <c r="Q35" s="935"/>
+      <c r="R35" s="936"/>
+      <c r="S35" s="937"/>
+      <c r="T35" s="907"/>
+      <c r="U35" s="908"/>
+      <c r="V35" s="909"/>
+      <c r="W35" s="896"/>
+      <c r="X35" s="897"/>
+      <c r="Y35" s="897"/>
+      <c r="Z35" s="955"/>
+      <c r="AA35" s="956"/>
+      <c r="AB35" s="962"/>
+      <c r="AC35" s="955"/>
+      <c r="AD35" s="956"/>
+      <c r="AE35" s="957"/>
       <c r="AF35" s="80"/>
       <c r="AG35" s="82"/>
       <c r="AH35" s="82"/>
@@ -42523,21 +42523,21 @@
       <c r="M36" s="404"/>
       <c r="N36" s="403"/>
       <c r="O36" s="90"/>
-      <c r="Q36" s="990"/>
-      <c r="R36" s="991"/>
-      <c r="S36" s="992"/>
-      <c r="T36" s="996"/>
-      <c r="U36" s="997"/>
-      <c r="V36" s="998"/>
-      <c r="W36" s="999"/>
-      <c r="X36" s="1000"/>
-      <c r="Y36" s="1000"/>
-      <c r="Z36" s="984"/>
-      <c r="AA36" s="985"/>
-      <c r="AB36" s="1014"/>
-      <c r="AC36" s="984"/>
-      <c r="AD36" s="985"/>
-      <c r="AE36" s="986"/>
+      <c r="Q36" s="935"/>
+      <c r="R36" s="936"/>
+      <c r="S36" s="937"/>
+      <c r="T36" s="907"/>
+      <c r="U36" s="908"/>
+      <c r="V36" s="909"/>
+      <c r="W36" s="896"/>
+      <c r="X36" s="897"/>
+      <c r="Y36" s="897"/>
+      <c r="Z36" s="955"/>
+      <c r="AA36" s="956"/>
+      <c r="AB36" s="962"/>
+      <c r="AC36" s="955"/>
+      <c r="AD36" s="956"/>
+      <c r="AE36" s="957"/>
       <c r="AF36" s="80"/>
       <c r="AG36" s="82"/>
       <c r="AH36" s="82"/>
@@ -42560,21 +42560,21 @@
       <c r="N37" s="82"/>
       <c r="O37" s="80"/>
       <c r="P37" s="79"/>
-      <c r="Q37" s="990"/>
-      <c r="R37" s="991"/>
-      <c r="S37" s="992"/>
-      <c r="T37" s="996"/>
-      <c r="U37" s="997"/>
-      <c r="V37" s="998"/>
-      <c r="W37" s="999"/>
-      <c r="X37" s="1000"/>
-      <c r="Y37" s="1000"/>
-      <c r="Z37" s="984"/>
-      <c r="AA37" s="985"/>
-      <c r="AB37" s="1014"/>
-      <c r="AC37" s="984"/>
-      <c r="AD37" s="985"/>
-      <c r="AE37" s="986"/>
+      <c r="Q37" s="935"/>
+      <c r="R37" s="936"/>
+      <c r="S37" s="937"/>
+      <c r="T37" s="907"/>
+      <c r="U37" s="908"/>
+      <c r="V37" s="909"/>
+      <c r="W37" s="896"/>
+      <c r="X37" s="897"/>
+      <c r="Y37" s="897"/>
+      <c r="Z37" s="955"/>
+      <c r="AA37" s="956"/>
+      <c r="AB37" s="962"/>
+      <c r="AC37" s="955"/>
+      <c r="AD37" s="956"/>
+      <c r="AE37" s="957"/>
       <c r="AF37" s="80"/>
       <c r="AG37" s="82"/>
       <c r="AH37" s="82"/>
@@ -42597,21 +42597,21 @@
       <c r="N38" s="82"/>
       <c r="O38" s="80"/>
       <c r="P38" s="79"/>
-      <c r="Q38" s="990"/>
-      <c r="R38" s="991"/>
-      <c r="S38" s="992"/>
-      <c r="T38" s="996"/>
-      <c r="U38" s="997"/>
-      <c r="V38" s="998"/>
-      <c r="W38" s="999"/>
-      <c r="X38" s="1000"/>
-      <c r="Y38" s="1000"/>
-      <c r="Z38" s="984"/>
-      <c r="AA38" s="985"/>
-      <c r="AB38" s="1014"/>
-      <c r="AC38" s="984"/>
-      <c r="AD38" s="985"/>
-      <c r="AE38" s="986"/>
+      <c r="Q38" s="935"/>
+      <c r="R38" s="936"/>
+      <c r="S38" s="937"/>
+      <c r="T38" s="907"/>
+      <c r="U38" s="908"/>
+      <c r="V38" s="909"/>
+      <c r="W38" s="896"/>
+      <c r="X38" s="897"/>
+      <c r="Y38" s="897"/>
+      <c r="Z38" s="955"/>
+      <c r="AA38" s="956"/>
+      <c r="AB38" s="962"/>
+      <c r="AC38" s="955"/>
+      <c r="AD38" s="956"/>
+      <c r="AE38" s="957"/>
       <c r="AF38" s="105"/>
       <c r="AG38" s="104"/>
       <c r="AH38" s="82"/>
@@ -42633,21 +42633,21 @@
       <c r="M39" s="82"/>
       <c r="N39" s="82"/>
       <c r="P39" s="79"/>
-      <c r="Q39" s="990"/>
-      <c r="R39" s="991"/>
-      <c r="S39" s="992"/>
-      <c r="T39" s="996"/>
-      <c r="U39" s="997"/>
-      <c r="V39" s="998"/>
-      <c r="W39" s="999"/>
-      <c r="X39" s="1000"/>
-      <c r="Y39" s="1000"/>
-      <c r="Z39" s="984"/>
-      <c r="AA39" s="985"/>
-      <c r="AB39" s="1014"/>
-      <c r="AC39" s="984"/>
-      <c r="AD39" s="985"/>
-      <c r="AE39" s="986"/>
+      <c r="Q39" s="935"/>
+      <c r="R39" s="936"/>
+      <c r="S39" s="937"/>
+      <c r="T39" s="907"/>
+      <c r="U39" s="908"/>
+      <c r="V39" s="909"/>
+      <c r="W39" s="896"/>
+      <c r="X39" s="897"/>
+      <c r="Y39" s="897"/>
+      <c r="Z39" s="955"/>
+      <c r="AA39" s="956"/>
+      <c r="AB39" s="962"/>
+      <c r="AC39" s="955"/>
+      <c r="AD39" s="956"/>
+      <c r="AE39" s="957"/>
       <c r="AF39" s="80"/>
       <c r="AG39" s="82"/>
       <c r="AH39" s="82"/>
@@ -42670,21 +42670,21 @@
       <c r="N40" s="82"/>
       <c r="O40" s="83"/>
       <c r="P40" s="87"/>
-      <c r="Q40" s="990"/>
-      <c r="R40" s="991"/>
-      <c r="S40" s="992"/>
-      <c r="T40" s="996"/>
-      <c r="U40" s="997"/>
-      <c r="V40" s="998"/>
-      <c r="W40" s="999"/>
-      <c r="X40" s="1000"/>
-      <c r="Y40" s="1000"/>
-      <c r="Z40" s="984"/>
-      <c r="AA40" s="985"/>
-      <c r="AB40" s="1014"/>
-      <c r="AC40" s="984"/>
-      <c r="AD40" s="985"/>
-      <c r="AE40" s="986"/>
+      <c r="Q40" s="935"/>
+      <c r="R40" s="936"/>
+      <c r="S40" s="937"/>
+      <c r="T40" s="907"/>
+      <c r="U40" s="908"/>
+      <c r="V40" s="909"/>
+      <c r="W40" s="896"/>
+      <c r="X40" s="897"/>
+      <c r="Y40" s="897"/>
+      <c r="Z40" s="955"/>
+      <c r="AA40" s="956"/>
+      <c r="AB40" s="962"/>
+      <c r="AC40" s="955"/>
+      <c r="AD40" s="956"/>
+      <c r="AE40" s="957"/>
       <c r="AF40" s="80"/>
       <c r="AG40" s="82"/>
       <c r="AH40" s="82"/>
@@ -42707,21 +42707,21 @@
       <c r="N41" s="82"/>
       <c r="O41" s="78"/>
       <c r="P41" s="79"/>
-      <c r="Q41" s="993"/>
-      <c r="R41" s="994"/>
-      <c r="S41" s="995"/>
-      <c r="T41" s="1003"/>
-      <c r="U41" s="1004"/>
-      <c r="V41" s="1005"/>
-      <c r="W41" s="1001"/>
-      <c r="X41" s="1002"/>
-      <c r="Y41" s="1002"/>
-      <c r="Z41" s="1011"/>
-      <c r="AA41" s="1012"/>
-      <c r="AB41" s="1017"/>
-      <c r="AC41" s="1011"/>
-      <c r="AD41" s="1012"/>
-      <c r="AE41" s="1013"/>
+      <c r="Q41" s="932"/>
+      <c r="R41" s="933"/>
+      <c r="S41" s="934"/>
+      <c r="T41" s="922"/>
+      <c r="U41" s="923"/>
+      <c r="V41" s="924"/>
+      <c r="W41" s="915"/>
+      <c r="X41" s="916"/>
+      <c r="Y41" s="916"/>
+      <c r="Z41" s="952"/>
+      <c r="AA41" s="953"/>
+      <c r="AB41" s="964"/>
+      <c r="AC41" s="952"/>
+      <c r="AD41" s="953"/>
+      <c r="AE41" s="954"/>
       <c r="AF41" s="80"/>
       <c r="AG41" s="82"/>
       <c r="AH41" s="82"/>
@@ -42744,21 +42744,21 @@
       <c r="N42" s="82"/>
       <c r="O42" s="80"/>
       <c r="P42" s="79"/>
-      <c r="Q42" s="993"/>
-      <c r="R42" s="994"/>
-      <c r="S42" s="995"/>
-      <c r="T42" s="1003"/>
-      <c r="U42" s="1004"/>
-      <c r="V42" s="1005"/>
-      <c r="W42" s="1001"/>
-      <c r="X42" s="1002"/>
-      <c r="Y42" s="1002"/>
-      <c r="Z42" s="1011"/>
-      <c r="AA42" s="1012"/>
-      <c r="AB42" s="1017"/>
-      <c r="AC42" s="1011"/>
-      <c r="AD42" s="1012"/>
-      <c r="AE42" s="1013"/>
+      <c r="Q42" s="932"/>
+      <c r="R42" s="933"/>
+      <c r="S42" s="934"/>
+      <c r="T42" s="922"/>
+      <c r="U42" s="923"/>
+      <c r="V42" s="924"/>
+      <c r="W42" s="915"/>
+      <c r="X42" s="916"/>
+      <c r="Y42" s="916"/>
+      <c r="Z42" s="952"/>
+      <c r="AA42" s="953"/>
+      <c r="AB42" s="964"/>
+      <c r="AC42" s="952"/>
+      <c r="AD42" s="953"/>
+      <c r="AE42" s="954"/>
       <c r="AF42" s="80"/>
       <c r="AG42" s="82"/>
       <c r="AH42" s="82"/>
@@ -42780,21 +42780,21 @@
       <c r="M43" s="82"/>
       <c r="N43" s="82"/>
       <c r="P43" s="79"/>
-      <c r="Q43" s="987"/>
-      <c r="R43" s="988"/>
-      <c r="S43" s="989"/>
-      <c r="T43" s="996"/>
-      <c r="U43" s="997"/>
-      <c r="V43" s="998"/>
-      <c r="W43" s="999"/>
-      <c r="X43" s="1000"/>
-      <c r="Y43" s="1000"/>
-      <c r="Z43" s="984"/>
-      <c r="AA43" s="985"/>
-      <c r="AB43" s="1014"/>
-      <c r="AC43" s="984"/>
-      <c r="AD43" s="985"/>
-      <c r="AE43" s="986"/>
+      <c r="Q43" s="974"/>
+      <c r="R43" s="975"/>
+      <c r="S43" s="976"/>
+      <c r="T43" s="907"/>
+      <c r="U43" s="908"/>
+      <c r="V43" s="909"/>
+      <c r="W43" s="896"/>
+      <c r="X43" s="897"/>
+      <c r="Y43" s="897"/>
+      <c r="Z43" s="955"/>
+      <c r="AA43" s="956"/>
+      <c r="AB43" s="962"/>
+      <c r="AC43" s="955"/>
+      <c r="AD43" s="956"/>
+      <c r="AE43" s="957"/>
       <c r="AF43" s="80"/>
       <c r="AG43" s="82"/>
       <c r="AH43" s="82"/>
@@ -42817,21 +42817,21 @@
       <c r="N44" s="82"/>
       <c r="O44" s="78"/>
       <c r="P44" s="103"/>
-      <c r="Q44" s="987"/>
-      <c r="R44" s="988"/>
-      <c r="S44" s="989"/>
-      <c r="T44" s="996"/>
-      <c r="U44" s="997"/>
-      <c r="V44" s="998"/>
-      <c r="W44" s="999"/>
-      <c r="X44" s="1000"/>
-      <c r="Y44" s="1000"/>
-      <c r="Z44" s="984"/>
-      <c r="AA44" s="985"/>
-      <c r="AB44" s="1014"/>
-      <c r="AC44" s="984"/>
-      <c r="AD44" s="985"/>
-      <c r="AE44" s="986"/>
+      <c r="Q44" s="974"/>
+      <c r="R44" s="975"/>
+      <c r="S44" s="976"/>
+      <c r="T44" s="907"/>
+      <c r="U44" s="908"/>
+      <c r="V44" s="909"/>
+      <c r="W44" s="896"/>
+      <c r="X44" s="897"/>
+      <c r="Y44" s="897"/>
+      <c r="Z44" s="955"/>
+      <c r="AA44" s="956"/>
+      <c r="AB44" s="962"/>
+      <c r="AC44" s="955"/>
+      <c r="AD44" s="956"/>
+      <c r="AE44" s="957"/>
       <c r="AF44" s="80"/>
       <c r="AG44" s="82"/>
       <c r="AH44" s="82"/>
@@ -42854,21 +42854,21 @@
       <c r="N45" s="82"/>
       <c r="O45" s="83"/>
       <c r="P45" s="103"/>
-      <c r="Q45" s="1062"/>
-      <c r="R45" s="1063"/>
-      <c r="S45" s="1064"/>
-      <c r="T45" s="1050"/>
-      <c r="U45" s="1051"/>
-      <c r="V45" s="1052"/>
-      <c r="W45" s="1039"/>
-      <c r="X45" s="1040"/>
-      <c r="Y45" s="1040"/>
-      <c r="Z45" s="1033"/>
-      <c r="AA45" s="1034"/>
-      <c r="AB45" s="1038"/>
-      <c r="AC45" s="1033"/>
-      <c r="AD45" s="1034"/>
-      <c r="AE45" s="1035"/>
+      <c r="Q45" s="890"/>
+      <c r="R45" s="891"/>
+      <c r="S45" s="892"/>
+      <c r="T45" s="926"/>
+      <c r="U45" s="927"/>
+      <c r="V45" s="928"/>
+      <c r="W45" s="965"/>
+      <c r="X45" s="966"/>
+      <c r="Y45" s="966"/>
+      <c r="Z45" s="958"/>
+      <c r="AA45" s="959"/>
+      <c r="AB45" s="963"/>
+      <c r="AC45" s="958"/>
+      <c r="AD45" s="959"/>
+      <c r="AE45" s="960"/>
       <c r="AF45" s="80"/>
       <c r="AG45" s="82"/>
       <c r="AH45" s="82"/>
@@ -42891,21 +42891,21 @@
       <c r="N46" s="82"/>
       <c r="O46" s="83"/>
       <c r="P46" s="103"/>
-      <c r="Q46" s="1065"/>
-      <c r="R46" s="1066"/>
-      <c r="S46" s="1066"/>
-      <c r="T46" s="1049"/>
-      <c r="U46" s="1049"/>
-      <c r="V46" s="1049"/>
-      <c r="W46" s="1036"/>
-      <c r="X46" s="1036"/>
-      <c r="Y46" s="1036"/>
-      <c r="Z46" s="1036"/>
-      <c r="AA46" s="1036"/>
-      <c r="AB46" s="1036"/>
-      <c r="AC46" s="1036"/>
-      <c r="AD46" s="1036"/>
-      <c r="AE46" s="1037"/>
+      <c r="Q46" s="893"/>
+      <c r="R46" s="894"/>
+      <c r="S46" s="894"/>
+      <c r="T46" s="925"/>
+      <c r="U46" s="925"/>
+      <c r="V46" s="925"/>
+      <c r="W46" s="895"/>
+      <c r="X46" s="895"/>
+      <c r="Y46" s="895"/>
+      <c r="Z46" s="895"/>
+      <c r="AA46" s="895"/>
+      <c r="AB46" s="895"/>
+      <c r="AC46" s="895"/>
+      <c r="AD46" s="895"/>
+      <c r="AE46" s="961"/>
       <c r="AF46" s="80"/>
       <c r="AG46" s="82"/>
       <c r="AH46" s="82"/>
@@ -42928,21 +42928,21 @@
       <c r="N47" s="82"/>
       <c r="O47" s="83"/>
       <c r="P47" s="103"/>
-      <c r="Q47" s="1059"/>
-      <c r="R47" s="1060"/>
-      <c r="S47" s="1061"/>
-      <c r="T47" s="1044"/>
-      <c r="U47" s="1045"/>
-      <c r="V47" s="1046"/>
-      <c r="W47" s="1047"/>
-      <c r="X47" s="1048"/>
-      <c r="Y47" s="1048"/>
-      <c r="Z47" s="1018"/>
-      <c r="AA47" s="1019"/>
-      <c r="AB47" s="1020"/>
-      <c r="AC47" s="1018"/>
-      <c r="AD47" s="1019"/>
-      <c r="AE47" s="1021"/>
+      <c r="Q47" s="887"/>
+      <c r="R47" s="888"/>
+      <c r="S47" s="889"/>
+      <c r="T47" s="917"/>
+      <c r="U47" s="918"/>
+      <c r="V47" s="919"/>
+      <c r="W47" s="920"/>
+      <c r="X47" s="921"/>
+      <c r="Y47" s="921"/>
+      <c r="Z47" s="941"/>
+      <c r="AA47" s="942"/>
+      <c r="AB47" s="943"/>
+      <c r="AC47" s="941"/>
+      <c r="AD47" s="942"/>
+      <c r="AE47" s="944"/>
       <c r="AF47" s="83"/>
       <c r="AG47" s="90"/>
       <c r="AH47" s="82"/>
@@ -43246,16 +43246,110 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="W46:Y46"/>
-    <mergeCell ref="W38:Y38"/>
-    <mergeCell ref="W39:Y39"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="F33:L33"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="T36:V36"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F12:L13"/>
+    <mergeCell ref="M12:N15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B12:E15"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="Q27:W27"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T29:V30"/>
+    <mergeCell ref="AD6:AF7"/>
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="W6:Z7"/>
+    <mergeCell ref="V8:Z9"/>
+    <mergeCell ref="AD8:AF9"/>
+    <mergeCell ref="A4:AI4"/>
+    <mergeCell ref="A3:AI3"/>
+    <mergeCell ref="J6:L7"/>
+    <mergeCell ref="P8:R9"/>
+    <mergeCell ref="Q6:R7"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="K8:L9"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="AC40:AE40"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="W40:Y40"/>
+    <mergeCell ref="W41:Y41"/>
+    <mergeCell ref="W42:Y42"/>
+    <mergeCell ref="W43:Y43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="T44:V44"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="AC33:AE33"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="Z31:AB31"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="AC38:AE38"/>
+    <mergeCell ref="AC39:AE39"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AC47:AE47"/>
+    <mergeCell ref="B33:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="AC41:AE41"/>
+    <mergeCell ref="AC42:AE42"/>
+    <mergeCell ref="AC43:AE43"/>
+    <mergeCell ref="AC44:AE44"/>
+    <mergeCell ref="AC45:AE45"/>
+    <mergeCell ref="AC46:AE46"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="W33:Y33"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="W35:Y35"/>
+    <mergeCell ref="W36:Y36"/>
+    <mergeCell ref="W37:Y37"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="I35:J35"/>
@@ -43280,110 +43374,16 @@
     <mergeCell ref="T33:V33"/>
     <mergeCell ref="T34:V34"/>
     <mergeCell ref="T35:V35"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AC47:AE47"/>
-    <mergeCell ref="B33:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="AC41:AE41"/>
-    <mergeCell ref="AC42:AE42"/>
-    <mergeCell ref="AC43:AE43"/>
-    <mergeCell ref="AC44:AE44"/>
-    <mergeCell ref="AC45:AE45"/>
-    <mergeCell ref="AC46:AE46"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="Z45:AB45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="W33:Y33"/>
-    <mergeCell ref="W34:Y34"/>
-    <mergeCell ref="W35:Y35"/>
-    <mergeCell ref="W36:Y36"/>
-    <mergeCell ref="W37:Y37"/>
-    <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="AC32:AE32"/>
-    <mergeCell ref="AC33:AE33"/>
-    <mergeCell ref="AC34:AE34"/>
-    <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="AC36:AE36"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="Z31:AB31"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="AC37:AE37"/>
-    <mergeCell ref="AC38:AE38"/>
-    <mergeCell ref="AC39:AE39"/>
-    <mergeCell ref="AC40:AE40"/>
-    <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="W40:Y40"/>
-    <mergeCell ref="W41:Y41"/>
-    <mergeCell ref="W42:Y42"/>
-    <mergeCell ref="W43:Y43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="T44:V44"/>
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="Q27:W27"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="T29:V30"/>
-    <mergeCell ref="AD6:AF7"/>
-    <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="W6:Z7"/>
-    <mergeCell ref="V8:Z9"/>
-    <mergeCell ref="AD8:AF9"/>
-    <mergeCell ref="A4:AI4"/>
-    <mergeCell ref="A3:AI3"/>
-    <mergeCell ref="J6:L7"/>
-    <mergeCell ref="P8:R9"/>
-    <mergeCell ref="Q6:R7"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="K8:L9"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F12:L13"/>
-    <mergeCell ref="M12:N15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B12:E15"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="W46:Y46"/>
+    <mergeCell ref="W38:Y38"/>
+    <mergeCell ref="W39:Y39"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="T36:V36"/>
   </mergeCells>
   <conditionalFormatting sqref="S13:AF13">
     <cfRule type="cellIs" dxfId="26" priority="29" operator="greaterThanOrEqual">
@@ -43661,14 +43661,14 @@
       <c r="G2" s="379"/>
       <c r="H2" s="379"/>
       <c r="I2" s="379"/>
-      <c r="J2" s="604" t="s">
+      <c r="J2" s="594" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="604"/>
-      <c r="L2" s="604"/>
-      <c r="M2" s="604"/>
-      <c r="N2" s="604"/>
-      <c r="O2" s="604"/>
+      <c r="K2" s="594"/>
+      <c r="L2" s="594"/>
+      <c r="M2" s="594"/>
+      <c r="N2" s="594"/>
+      <c r="O2" s="594"/>
       <c r="P2" s="379"/>
       <c r="Q2" s="379"/>
       <c r="R2" s="379"/>
@@ -43709,14 +43709,14 @@
       <c r="I4" s="380" t="s">
         <v>133</v>
       </c>
-      <c r="J4" s="603" t="s">
+      <c r="J4" s="593" t="s">
         <v>134</v>
       </c>
-      <c r="K4" s="603"/>
-      <c r="L4" s="603"/>
-      <c r="M4" s="603"/>
-      <c r="N4" s="603"/>
-      <c r="O4" s="603"/>
+      <c r="K4" s="593"/>
+      <c r="L4" s="593"/>
+      <c r="M4" s="593"/>
+      <c r="N4" s="593"/>
+      <c r="O4" s="593"/>
       <c r="P4" s="381"/>
       <c r="Q4" s="381"/>
       <c r="R4" s="382"/>
@@ -43732,17 +43732,17 @@
       <c r="G5" s="383"/>
       <c r="H5" s="383"/>
       <c r="I5" s="384"/>
-      <c r="J5" s="596" t="s">
+      <c r="J5" s="604" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="596"/>
-      <c r="L5" s="596"/>
-      <c r="M5" s="596"/>
-      <c r="N5" s="608" t="s">
+      <c r="K5" s="604"/>
+      <c r="L5" s="604"/>
+      <c r="M5" s="604"/>
+      <c r="N5" s="601" t="s">
         <v>164</v>
       </c>
-      <c r="O5" s="608"/>
-      <c r="P5" s="608"/>
+      <c r="O5" s="601"/>
+      <c r="P5" s="601"/>
       <c r="Q5" s="385"/>
       <c r="R5" s="385"/>
       <c r="S5" s="22"/>
@@ -43773,12 +43773,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="23"/>
-      <c r="C8" s="599" t="str">
+      <c r="C8" s="605" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO ABRIL - 2025</v>
       </c>
-      <c r="D8" s="600"/>
-      <c r="E8" s="601"/>
+      <c r="D8" s="606"/>
+      <c r="E8" s="607"/>
       <c r="G8" s="56" t="s">
         <v>1</v>
       </c>
@@ -43821,11 +43821,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="C10" s="602" t="s">
+      <c r="C10" s="608" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="602"/>
-      <c r="E10" s="602"/>
+      <c r="D10" s="608"/>
+      <c r="E10" s="608"/>
       <c r="G10" s="76" t="s">
         <v>8</v>
       </c>
@@ -43975,11 +43975,11 @@
       <c r="C15" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="594">
+      <c r="D15" s="603">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="594"/>
+      <c r="E15" s="603"/>
       <c r="H15" s="35"/>
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
@@ -44022,11 +44022,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="C24" s="605" t="s">
+      <c r="C24" s="596" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="606"/>
-      <c r="E24" s="607"/>
+      <c r="D24" s="597"/>
+      <c r="E24" s="598"/>
       <c r="S24" s="22"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -44034,11 +44034,11 @@
       <c r="C25" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="597">
+      <c r="D25" s="599">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="598"/>
+      <c r="E25" s="600"/>
       <c r="S25" s="22"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -44046,11 +44046,11 @@
       <c r="C26" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="597">
+      <c r="D26" s="599">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="598"/>
+      <c r="E26" s="600"/>
       <c r="S26" s="22"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -44082,11 +44082,11 @@
       <c r="C29" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="593">
+      <c r="D29" s="602">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="593"/>
+      <c r="E29" s="602"/>
       <c r="S29" s="22"/>
     </row>
     <row r="30" spans="1:19">
@@ -44200,12 +44200,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -44217,6 +44211,12 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -49004,9 +49004,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="655"/>
-      <c r="C1" s="656"/>
-      <c r="D1" s="657"/>
+      <c r="B1" s="653"/>
+      <c r="C1" s="654"/>
+      <c r="D1" s="655"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -49028,10 +49028,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="651" t="s">
+      <c r="I2" s="662" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="652"/>
+      <c r="J2" s="663"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -49084,10 +49084,10 @@
       <c r="B5" s="378" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="658" t="s">
+      <c r="C5" s="656" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="659"/>
+      <c r="D5" s="657"/>
       <c r="E5" s="375" t="s">
         <v>60</v>
       </c>
@@ -49115,8 +49115,8 @@
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
       <c r="B6" s="215"/>
-      <c r="C6" s="660"/>
-      <c r="D6" s="661"/>
+      <c r="C6" s="658"/>
+      <c r="D6" s="659"/>
       <c r="E6" s="459"/>
       <c r="F6" s="459"/>
       <c r="G6" s="459"/>
@@ -49134,8 +49134,8 @@
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="99"/>
       <c r="B7" s="216"/>
-      <c r="C7" s="662"/>
-      <c r="D7" s="663"/>
+      <c r="C7" s="660"/>
+      <c r="D7" s="661"/>
       <c r="E7" s="460"/>
       <c r="F7" s="460"/>
       <c r="G7" s="460"/>
@@ -49151,8 +49151,8 @@
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="100"/>
       <c r="B8" s="216"/>
-      <c r="C8" s="662"/>
-      <c r="D8" s="663"/>
+      <c r="C8" s="660"/>
+      <c r="D8" s="661"/>
       <c r="E8" s="460"/>
       <c r="F8" s="460"/>
       <c r="G8" s="460"/>
@@ -49169,8 +49169,8 @@
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="100"/>
       <c r="B9" s="216"/>
-      <c r="C9" s="662"/>
-      <c r="D9" s="663"/>
+      <c r="C9" s="660"/>
+      <c r="D9" s="661"/>
       <c r="E9" s="460"/>
       <c r="F9" s="460"/>
       <c r="G9" s="460"/>
@@ -49188,8 +49188,8 @@
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="102"/>
       <c r="B10" s="216"/>
-      <c r="C10" s="662"/>
-      <c r="D10" s="663"/>
+      <c r="C10" s="660"/>
+      <c r="D10" s="661"/>
       <c r="E10" s="460"/>
       <c r="F10" s="460"/>
       <c r="G10" s="460"/>
@@ -49206,8 +49206,8 @@
     <row r="11" spans="1:17" ht="44.25" customHeight="1">
       <c r="A11" s="101"/>
       <c r="B11" s="216"/>
-      <c r="C11" s="662"/>
-      <c r="D11" s="663"/>
+      <c r="C11" s="660"/>
+      <c r="D11" s="661"/>
       <c r="E11" s="460"/>
       <c r="F11" s="460"/>
       <c r="G11" s="460"/>
@@ -49224,8 +49224,8 @@
     <row r="12" spans="1:17" ht="66.75" customHeight="1" thickBot="1">
       <c r="A12" s="100"/>
       <c r="B12" s="217"/>
-      <c r="C12" s="653"/>
-      <c r="D12" s="654"/>
+      <c r="C12" s="648"/>
+      <c r="D12" s="649"/>
       <c r="E12" s="461"/>
       <c r="F12" s="461"/>
       <c r="G12" s="461"/>
@@ -49302,12 +49302,12 @@
       </c>
       <c r="C16" s="483"/>
       <c r="D16" s="294"/>
-      <c r="E16" s="648"/>
-      <c r="F16" s="649"/>
-      <c r="G16" s="649"/>
-      <c r="H16" s="649"/>
-      <c r="I16" s="649"/>
-      <c r="J16" s="650"/>
+      <c r="E16" s="650"/>
+      <c r="F16" s="651"/>
+      <c r="G16" s="651"/>
+      <c r="H16" s="651"/>
+      <c r="I16" s="651"/>
+      <c r="J16" s="652"/>
       <c r="K16" s="302"/>
       <c r="L16" s="115"/>
       <c r="M16" s="113"/>
@@ -49321,12 +49321,12 @@
       </c>
       <c r="C17" s="485"/>
       <c r="D17" s="294"/>
-      <c r="E17" s="648"/>
-      <c r="F17" s="649"/>
-      <c r="G17" s="649"/>
-      <c r="H17" s="649"/>
-      <c r="I17" s="649"/>
-      <c r="J17" s="650"/>
+      <c r="E17" s="650"/>
+      <c r="F17" s="651"/>
+      <c r="G17" s="651"/>
+      <c r="H17" s="651"/>
+      <c r="I17" s="651"/>
+      <c r="J17" s="652"/>
       <c r="K17" s="136"/>
       <c r="L17" s="123"/>
       <c r="M17" s="115"/>
@@ -49341,12 +49341,12 @@
       </c>
       <c r="C18" s="485"/>
       <c r="D18" s="295"/>
-      <c r="E18" s="648"/>
-      <c r="F18" s="649"/>
-      <c r="G18" s="649"/>
-      <c r="H18" s="649"/>
-      <c r="I18" s="649"/>
-      <c r="J18" s="650"/>
+      <c r="E18" s="650"/>
+      <c r="F18" s="651"/>
+      <c r="G18" s="651"/>
+      <c r="H18" s="651"/>
+      <c r="I18" s="651"/>
+      <c r="J18" s="652"/>
       <c r="L18" s="115"/>
       <c r="M18" s="111"/>
       <c r="N18" s="110"/>
@@ -49358,12 +49358,12 @@
       <c r="B19" s="87"/>
       <c r="C19" s="87"/>
       <c r="D19" s="296"/>
-      <c r="E19" s="648"/>
-      <c r="F19" s="649"/>
-      <c r="G19" s="649"/>
-      <c r="H19" s="649"/>
-      <c r="I19" s="649"/>
-      <c r="J19" s="650"/>
+      <c r="E19" s="650"/>
+      <c r="F19" s="651"/>
+      <c r="G19" s="651"/>
+      <c r="H19" s="651"/>
+      <c r="I19" s="651"/>
+      <c r="J19" s="652"/>
       <c r="K19" s="136"/>
       <c r="L19" s="123"/>
       <c r="M19" s="111"/>
@@ -49375,12 +49375,12 @@
       <c r="A20" s="79"/>
       <c r="B20" s="90"/>
       <c r="D20" s="295"/>
-      <c r="E20" s="648"/>
-      <c r="F20" s="649"/>
-      <c r="G20" s="649"/>
-      <c r="H20" s="649"/>
-      <c r="I20" s="649"/>
-      <c r="J20" s="650"/>
+      <c r="E20" s="650"/>
+      <c r="F20" s="651"/>
+      <c r="G20" s="651"/>
+      <c r="H20" s="651"/>
+      <c r="I20" s="651"/>
+      <c r="J20" s="652"/>
       <c r="K20" s="303"/>
       <c r="L20" s="297"/>
       <c r="M20" s="114"/>
@@ -49391,12 +49391,12 @@
       <c r="B21" s="227"/>
       <c r="C21" s="228"/>
       <c r="D21" s="298"/>
-      <c r="E21" s="648"/>
-      <c r="F21" s="649"/>
-      <c r="G21" s="649"/>
-      <c r="H21" s="649"/>
-      <c r="I21" s="649"/>
-      <c r="J21" s="650"/>
+      <c r="E21" s="650"/>
+      <c r="F21" s="651"/>
+      <c r="G21" s="651"/>
+      <c r="H21" s="651"/>
+      <c r="I21" s="651"/>
+      <c r="J21" s="652"/>
       <c r="K21" s="304"/>
       <c r="L21" s="58"/>
       <c r="M21" s="112"/>
@@ -49408,12 +49408,12 @@
       <c r="B22" s="106"/>
       <c r="C22" s="87"/>
       <c r="D22" s="305"/>
-      <c r="E22" s="648"/>
-      <c r="F22" s="649"/>
-      <c r="G22" s="649"/>
-      <c r="H22" s="649"/>
-      <c r="I22" s="649"/>
-      <c r="J22" s="650"/>
+      <c r="E22" s="650"/>
+      <c r="F22" s="651"/>
+      <c r="G22" s="651"/>
+      <c r="H22" s="651"/>
+      <c r="I22" s="651"/>
+      <c r="J22" s="652"/>
       <c r="L22" s="112"/>
       <c r="M22" s="115"/>
       <c r="N22" s="115"/>
@@ -49831,6 +49831,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E19:J19"/>
@@ -49843,11 +49848,6 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="47" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -49856,12 +49856,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50120,20 +50122,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -50158,18 +50167,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA894187-C151-425E-9DAA-B38745F4B323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70C8EBF-7C9D-4C4D-A5AA-7C99BE68D636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -6849,9 +6849,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -7734,53 +7731,56 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="13" borderId="205" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="63" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="13" borderId="205" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -29719,7 +29719,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327372"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327502"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29784,7 +29784,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327373"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s327503"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29901,7 +29901,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s327374"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s327504"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29966,7 +29966,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s327375"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s327505"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30031,7 +30031,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s327376"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s327506"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30096,7 +30096,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s327377"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s327507"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30161,7 +30161,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s327378"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s327508"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30226,7 +30226,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s327379"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s327509"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30291,7 +30291,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s327380"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s327510"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30356,7 +30356,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s327381"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s327511"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -33054,15 +33054,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>783956</xdr:colOff>
+      <xdr:colOff>783957</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>3407</xdr:rowOff>
+      <xdr:rowOff>3409</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>123264</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>100852</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>750795</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -33728,10 +33728,10 @@
       <c r="F11" s="224" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="590">
+      <c r="G11" s="589">
         <v>2025</v>
       </c>
-      <c r="H11" s="590"/>
+      <c r="H11" s="589"/>
       <c r="I11" s="82"/>
       <c r="J11" s="82"/>
       <c r="K11" s="82"/>
@@ -33755,10 +33755,10 @@
       <c r="C12" s="82"/>
       <c r="D12" s="82"/>
       <c r="E12" s="225"/>
-      <c r="F12" s="591" t="s">
+      <c r="F12" s="590" t="s">
         <v>164</v>
       </c>
-      <c r="G12" s="592"/>
+      <c r="G12" s="591"/>
       <c r="H12" s="82"/>
       <c r="I12" s="82"/>
       <c r="J12" s="82"/>
@@ -33835,10 +33835,10 @@
       <c r="C15" s="82"/>
       <c r="D15" s="82"/>
       <c r="E15" s="222"/>
-      <c r="F15" s="588" t="s">
+      <c r="F15" s="587" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="588"/>
+      <c r="G15" s="587"/>
       <c r="H15" s="82"/>
       <c r="I15" s="82"/>
       <c r="J15" s="82"/>
@@ -33863,10 +33863,10 @@
       <c r="C16" s="82"/>
       <c r="D16" s="82"/>
       <c r="E16" s="222"/>
-      <c r="F16" s="588" t="s">
+      <c r="F16" s="587" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="588"/>
+      <c r="G16" s="587"/>
       <c r="H16" s="82"/>
       <c r="I16" s="82"/>
       <c r="J16" s="82"/>
@@ -33917,10 +33917,10 @@
       <c r="C18" s="82"/>
       <c r="D18" s="82"/>
       <c r="E18" s="221"/>
-      <c r="F18" s="589" t="s">
+      <c r="F18" s="588" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="589"/>
+      <c r="G18" s="588"/>
       <c r="H18" s="82"/>
       <c r="I18" s="82"/>
       <c r="J18" s="82"/>
@@ -34548,9 +34548,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="653"/>
-      <c r="C1" s="654"/>
-      <c r="D1" s="655"/>
+      <c r="B1" s="647"/>
+      <c r="C1" s="648"/>
+      <c r="D1" s="649"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -34572,10 +34572,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="662" t="s">
+      <c r="I2" s="660" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="663"/>
+      <c r="J2" s="661"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -34625,29 +34625,29 @@
     </row>
     <row r="5" spans="1:17" ht="78" customHeight="1" thickBot="1">
       <c r="A5" s="89"/>
-      <c r="B5" s="578" t="s">
+      <c r="B5" s="577" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="656" t="s">
+      <c r="C5" s="653" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="657"/>
-      <c r="E5" s="579" t="s">
+      <c r="D5" s="654"/>
+      <c r="E5" s="578" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="579" t="s">
+      <c r="F5" s="578" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="579" t="s">
+      <c r="G5" s="578" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="580" t="s">
+      <c r="H5" s="579" t="s">
         <v>118</v>
       </c>
-      <c r="I5" s="580" t="s">
+      <c r="I5" s="579" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="581" t="s">
+      <c r="J5" s="580" t="s">
         <v>63</v>
       </c>
       <c r="K5" s="205"/>
@@ -34659,15 +34659,15 @@
     </row>
     <row r="6" spans="1:17" ht="29.25" thickBot="1">
       <c r="A6" s="79"/>
-      <c r="B6" s="582"/>
+      <c r="B6" s="581"/>
       <c r="C6" s="665"/>
       <c r="D6" s="666"/>
-      <c r="E6" s="583"/>
-      <c r="F6" s="583"/>
-      <c r="G6" s="583"/>
-      <c r="H6" s="583"/>
-      <c r="I6" s="583"/>
-      <c r="J6" s="584"/>
+      <c r="E6" s="582"/>
+      <c r="F6" s="582"/>
+      <c r="G6" s="582"/>
+      <c r="H6" s="582"/>
+      <c r="I6" s="582"/>
+      <c r="J6" s="583"/>
       <c r="K6" s="78"/>
       <c r="L6" s="82"/>
       <c r="M6" s="82"/>
@@ -34677,15 +34677,15 @@
     </row>
     <row r="7" spans="1:17" ht="28.5">
       <c r="A7" s="79"/>
-      <c r="B7" s="587"/>
+      <c r="B7" s="586"/>
       <c r="C7" s="667"/>
       <c r="D7" s="668"/>
-      <c r="E7" s="585"/>
-      <c r="F7" s="585"/>
-      <c r="G7" s="585"/>
-      <c r="H7" s="585"/>
-      <c r="I7" s="586"/>
-      <c r="J7" s="586"/>
+      <c r="E7" s="584"/>
+      <c r="F7" s="584"/>
+      <c r="G7" s="584"/>
+      <c r="H7" s="584"/>
+      <c r="I7" s="585"/>
+      <c r="J7" s="585"/>
       <c r="K7" s="82"/>
       <c r="L7" s="82"/>
       <c r="M7" s="82"/>
@@ -34733,12 +34733,12 @@
       <c r="A10" s="79"/>
       <c r="B10" s="166"/>
       <c r="C10" s="89"/>
-      <c r="D10" s="538"/>
-      <c r="E10" s="540"/>
-      <c r="F10" s="540"/>
-      <c r="G10" s="540"/>
-      <c r="H10" s="540"/>
-      <c r="I10" s="539"/>
+      <c r="D10" s="537"/>
+      <c r="E10" s="539"/>
+      <c r="F10" s="539"/>
+      <c r="G10" s="539"/>
+      <c r="H10" s="539"/>
+      <c r="I10" s="538"/>
       <c r="J10" s="87"/>
       <c r="K10" s="82"/>
       <c r="L10" s="82"/>
@@ -34749,10 +34749,10 @@
     </row>
     <row r="11" spans="1:17" ht="30.75" customHeight="1" thickBot="1">
       <c r="A11" s="79"/>
-      <c r="B11" s="482" t="s">
+      <c r="B11" s="481" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="494"/>
+      <c r="C11" s="493"/>
       <c r="D11" s="289" t="s">
         <v>68</v>
       </c>
@@ -34771,7 +34771,7 @@
     </row>
     <row r="12" spans="1:17" ht="8.25" customHeight="1" thickBot="1">
       <c r="A12" s="87"/>
-      <c r="B12" s="481"/>
+      <c r="B12" s="480"/>
       <c r="C12" s="300"/>
       <c r="D12" s="290"/>
       <c r="E12" s="291"/>
@@ -34788,10 +34788,10 @@
     </row>
     <row r="13" spans="1:17" ht="74.25" customHeight="1" thickBot="1">
       <c r="A13" s="79"/>
-      <c r="B13" s="484" t="s">
+      <c r="B13" s="483" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="493"/>
+      <c r="C13" s="492"/>
       <c r="D13" s="294"/>
       <c r="E13" s="650"/>
       <c r="F13" s="651"/>
@@ -34808,10 +34808,10 @@
     </row>
     <row r="14" spans="1:17" ht="108.75" customHeight="1" thickBot="1">
       <c r="A14" s="87"/>
-      <c r="B14" s="486" t="s">
+      <c r="B14" s="485" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="492"/>
+      <c r="C14" s="491"/>
       <c r="D14" s="294"/>
       <c r="E14" s="650"/>
       <c r="F14" s="651"/>
@@ -34828,11 +34828,11 @@
     </row>
     <row r="15" spans="1:17" ht="87" customHeight="1" thickBot="1">
       <c r="A15" s="78"/>
-      <c r="B15" s="486" t="s">
+      <c r="B15" s="485" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="485"/>
-      <c r="D15" s="491"/>
+      <c r="C15" s="484"/>
+      <c r="D15" s="490"/>
       <c r="E15" s="664"/>
       <c r="F15" s="664"/>
       <c r="G15" s="664"/>
@@ -34850,7 +34850,7 @@
       <c r="A16" s="82"/>
       <c r="B16" s="87"/>
       <c r="C16" s="82"/>
-      <c r="D16" s="488"/>
+      <c r="D16" s="487"/>
       <c r="E16" s="82"/>
       <c r="F16" s="82"/>
       <c r="G16" s="82"/>
@@ -34868,7 +34868,7 @@
       <c r="A17" s="79"/>
       <c r="B17" s="90"/>
       <c r="C17" s="104"/>
-      <c r="D17" s="495"/>
+      <c r="D17" s="494"/>
       <c r="E17" s="664"/>
       <c r="F17" s="664"/>
       <c r="G17" s="664"/>
@@ -34884,14 +34884,14 @@
     <row r="18" spans="1:16" s="226" customFormat="1" ht="81.75" customHeight="1">
       <c r="B18" s="227"/>
       <c r="C18" s="228"/>
-      <c r="D18" s="490"/>
+      <c r="D18" s="489"/>
       <c r="E18" s="664"/>
       <c r="F18" s="664"/>
       <c r="G18" s="664"/>
       <c r="H18" s="664"/>
       <c r="I18" s="664"/>
       <c r="J18" s="664"/>
-      <c r="K18" s="487"/>
+      <c r="K18" s="486"/>
       <c r="L18" s="58"/>
       <c r="M18" s="112"/>
       <c r="N18" s="112"/>
@@ -34901,7 +34901,7 @@
       <c r="A19" s="83"/>
       <c r="B19" s="106"/>
       <c r="C19" s="87"/>
-      <c r="D19" s="489"/>
+      <c r="D19" s="488"/>
       <c r="E19" s="664"/>
       <c r="F19" s="664"/>
       <c r="G19" s="664"/>
@@ -35575,16 +35575,16 @@
     </row>
     <row r="7" spans="1:28" ht="30.75" customHeight="1" thickBot="1">
       <c r="A7" s="181"/>
-      <c r="B7" s="367" t="s">
+      <c r="B7" s="366" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="368" t="s">
+      <c r="C7" s="367" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="369" t="s">
+      <c r="D7" s="368" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="370" t="s">
+      <c r="E7" s="369" t="s">
         <v>75</v>
       </c>
       <c r="F7" s="89"/>
@@ -35944,16 +35944,16 @@
     </row>
     <row r="18" spans="1:27" ht="34.5" customHeight="1">
       <c r="A18" s="79"/>
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="370" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="372" t="s">
+      <c r="C18" s="371" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="373" t="s">
+      <c r="D18" s="372" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="374" t="s">
+      <c r="E18" s="373" t="s">
         <v>91</v>
       </c>
       <c r="F18" s="89"/>
@@ -35985,7 +35985,7 @@
       <c r="A19" s="79"/>
       <c r="B19" s="157"/>
       <c r="C19" s="134"/>
-      <c r="D19" s="554"/>
+      <c r="D19" s="553"/>
       <c r="E19" s="201"/>
       <c r="F19" s="89"/>
       <c r="G19" s="673" t="s">
@@ -36016,7 +36016,7 @@
       <c r="A20" s="79"/>
       <c r="B20" s="157"/>
       <c r="C20" s="139"/>
-      <c r="D20" s="554"/>
+      <c r="D20" s="553"/>
       <c r="E20" s="201"/>
       <c r="F20" s="89"/>
       <c r="G20" s="673" t="s">
@@ -36047,7 +36047,7 @@
       <c r="A21" s="79"/>
       <c r="B21" s="157"/>
       <c r="C21" s="139"/>
-      <c r="D21" s="554"/>
+      <c r="D21" s="553"/>
       <c r="E21" s="201"/>
       <c r="F21" s="89"/>
       <c r="G21" s="673" t="s">
@@ -36078,7 +36078,7 @@
       <c r="A22" s="79"/>
       <c r="B22" s="157"/>
       <c r="C22" s="139"/>
-      <c r="D22" s="554"/>
+      <c r="D22" s="553"/>
       <c r="E22" s="201"/>
       <c r="F22" s="89"/>
       <c r="G22" s="673" t="s">
@@ -36109,7 +36109,7 @@
       <c r="A23" s="79"/>
       <c r="B23" s="158"/>
       <c r="C23" s="159"/>
-      <c r="D23" s="555"/>
+      <c r="D23" s="554"/>
       <c r="E23" s="202"/>
       <c r="F23" s="89"/>
       <c r="G23" s="716" t="s">
@@ -38894,78 +38894,78 @@
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" thickBot="1">
       <c r="A5" s="90"/>
-      <c r="B5" s="513"/>
+      <c r="B5" s="512"/>
       <c r="C5" s="82"/>
-      <c r="D5" s="514"/>
-      <c r="E5" s="515"/>
+      <c r="D5" s="513"/>
+      <c r="E5" s="514"/>
       <c r="F5" s="80"/>
-      <c r="G5" s="516"/>
-      <c r="H5" s="514"/>
+      <c r="G5" s="515"/>
+      <c r="H5" s="513"/>
       <c r="I5" s="82"/>
       <c r="J5" s="836"/>
       <c r="K5" s="836"/>
-      <c r="L5" s="519"/>
-      <c r="M5" s="516"/>
-      <c r="N5" s="520"/>
-      <c r="O5" s="406"/>
+      <c r="L5" s="518"/>
+      <c r="M5" s="515"/>
+      <c r="N5" s="519"/>
+      <c r="O5" s="405"/>
     </row>
     <row r="6" spans="1:15" ht="51.75" customHeight="1">
       <c r="A6" s="135"/>
-      <c r="B6" s="522" t="s">
+      <c r="B6" s="521" t="s">
         <v>155</v>
       </c>
       <c r="C6" s="89"/>
       <c r="D6" s="135"/>
-      <c r="E6" s="558" t="s">
+      <c r="E6" s="557" t="s">
         <v>92</v>
       </c>
       <c r="F6" s="89"/>
       <c r="G6" s="135"/>
-      <c r="H6" s="526" t="s">
+      <c r="H6" s="525" t="s">
         <v>93</v>
       </c>
       <c r="I6" s="89"/>
-      <c r="J6" s="524"/>
-      <c r="K6" s="558" t="s">
+      <c r="J6" s="523"/>
+      <c r="K6" s="557" t="s">
         <v>104</v>
       </c>
-      <c r="L6" s="517"/>
+      <c r="L6" s="516"/>
       <c r="M6" s="135"/>
-      <c r="N6" s="522" t="s">
+      <c r="N6" s="521" t="s">
         <v>181</v>
       </c>
       <c r="O6" s="232"/>
     </row>
     <row r="7" spans="1:15" ht="40.5" customHeight="1" thickBot="1">
       <c r="A7" s="137"/>
-      <c r="B7" s="523">
+      <c r="B7" s="522">
         <f>SUM(E13:E15)</f>
         <v>0</v>
       </c>
       <c r="C7" s="89"/>
       <c r="D7" s="137"/>
-      <c r="E7" s="523">
+      <c r="E7" s="522">
         <f>E13</f>
         <v>0</v>
       </c>
       <c r="F7" s="89"/>
       <c r="G7" s="137"/>
-      <c r="H7" s="523">
+      <c r="H7" s="522">
         <v>10</v>
       </c>
       <c r="I7" s="89"/>
-      <c r="J7" s="525"/>
-      <c r="K7" s="523">
+      <c r="J7" s="524"/>
+      <c r="K7" s="522">
         <f>E15</f>
         <v>0</v>
       </c>
-      <c r="L7" s="518"/>
+      <c r="L7" s="517"/>
       <c r="M7" s="137"/>
-      <c r="N7" s="523">
+      <c r="N7" s="522">
         <f>F25</f>
         <v>0</v>
       </c>
-      <c r="O7" s="406"/>
+      <c r="O7" s="405"/>
     </row>
     <row r="8" spans="1:15" ht="13.5" customHeight="1" thickBot="1">
       <c r="A8" s="106"/>
@@ -38981,8 +38981,8 @@
       <c r="K8" s="826"/>
       <c r="L8" s="826"/>
       <c r="M8" s="826"/>
-      <c r="N8" s="521"/>
-      <c r="O8" s="406"/>
+      <c r="N8" s="520"/>
+      <c r="O8" s="405"/>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1">
       <c r="A9" s="791" t="s">
@@ -38994,13 +38994,13 @@
       <c r="E9" s="792"/>
       <c r="F9" s="793"/>
       <c r="G9" s="83"/>
-      <c r="H9" s="498"/>
-      <c r="I9" s="503"/>
-      <c r="J9" s="503"/>
-      <c r="K9" s="503"/>
-      <c r="L9" s="503"/>
-      <c r="M9" s="503"/>
-      <c r="N9" s="503"/>
+      <c r="H9" s="497"/>
+      <c r="I9" s="502"/>
+      <c r="J9" s="502"/>
+      <c r="K9" s="502"/>
+      <c r="L9" s="502"/>
+      <c r="M9" s="502"/>
+      <c r="N9" s="502"/>
       <c r="O9" s="232"/>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1">
@@ -39012,13 +39012,13 @@
       <c r="F10" s="796"/>
       <c r="G10" s="80"/>
       <c r="H10" s="82"/>
-      <c r="I10" s="501"/>
-      <c r="J10" s="501"/>
-      <c r="K10" s="501"/>
-      <c r="L10" s="501"/>
-      <c r="M10" s="501"/>
-      <c r="N10" s="501"/>
-      <c r="O10" s="406"/>
+      <c r="I10" s="500"/>
+      <c r="J10" s="500"/>
+      <c r="K10" s="500"/>
+      <c r="L10" s="500"/>
+      <c r="M10" s="500"/>
+      <c r="N10" s="500"/>
+      <c r="O10" s="405"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="807" t="s">
@@ -39039,13 +39039,13 @@
       <c r="F11" s="788"/>
       <c r="G11" s="80"/>
       <c r="H11" s="82"/>
-      <c r="I11" s="501"/>
-      <c r="J11" s="501"/>
-      <c r="K11" s="501"/>
-      <c r="L11" s="501"/>
-      <c r="M11" s="501"/>
-      <c r="N11" s="501"/>
-      <c r="O11" s="406"/>
+      <c r="I11" s="500"/>
+      <c r="J11" s="500"/>
+      <c r="K11" s="500"/>
+      <c r="L11" s="500"/>
+      <c r="M11" s="500"/>
+      <c r="N11" s="500"/>
+      <c r="O11" s="405"/>
     </row>
     <row r="12" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
       <c r="A12" s="808"/>
@@ -39056,21 +39056,21 @@
       <c r="F12" s="790"/>
       <c r="G12" s="80"/>
       <c r="H12" s="82"/>
-      <c r="I12" s="501"/>
-      <c r="J12" s="501"/>
-      <c r="K12" s="501"/>
-      <c r="L12" s="501"/>
-      <c r="M12" s="501"/>
-      <c r="N12" s="501"/>
+      <c r="I12" s="500"/>
+      <c r="J12" s="500"/>
+      <c r="K12" s="500"/>
+      <c r="L12" s="500"/>
+      <c r="M12" s="500"/>
+      <c r="N12" s="500"/>
       <c r="O12" s="232"/>
     </row>
     <row r="13" spans="1:15" ht="21">
-      <c r="A13" s="563" t="s">
+      <c r="A13" s="562" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="564"/>
-      <c r="C13" s="564"/>
-      <c r="D13" s="565"/>
+      <c r="B13" s="563"/>
+      <c r="C13" s="563"/>
+      <c r="D13" s="564"/>
       <c r="E13" s="797">
         <f>SUM(B13:D13)</f>
         <v>0</v>
@@ -39079,20 +39079,20 @@
       <c r="G13" s="80"/>
       <c r="H13" s="82"/>
       <c r="I13" s="82"/>
-      <c r="J13" s="504"/>
+      <c r="J13" s="503"/>
       <c r="K13" s="82"/>
       <c r="L13" s="82"/>
       <c r="M13" s="82"/>
       <c r="N13" s="82"/>
-      <c r="O13" s="406"/>
+      <c r="O13" s="405"/>
     </row>
     <row r="14" spans="1:15" ht="21">
-      <c r="A14" s="507" t="s">
+      <c r="A14" s="506" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="506"/>
-      <c r="C14" s="506"/>
-      <c r="D14" s="566"/>
+      <c r="B14" s="505"/>
+      <c r="C14" s="505"/>
+      <c r="D14" s="565"/>
       <c r="E14" s="799">
         <f>SUM(B14:D14)</f>
         <v>0</v>
@@ -39100,21 +39100,21 @@
       <c r="F14" s="800"/>
       <c r="G14" s="80"/>
       <c r="H14" s="82"/>
-      <c r="I14" s="501"/>
-      <c r="J14" s="501"/>
-      <c r="K14" s="501"/>
-      <c r="L14" s="501"/>
-      <c r="M14" s="501"/>
-      <c r="N14" s="501"/>
+      <c r="I14" s="500"/>
+      <c r="J14" s="500"/>
+      <c r="K14" s="500"/>
+      <c r="L14" s="500"/>
+      <c r="M14" s="500"/>
+      <c r="N14" s="500"/>
       <c r="O14" s="232"/>
     </row>
     <row r="15" spans="1:15" ht="21.75" thickBot="1">
-      <c r="A15" s="508" t="s">
+      <c r="A15" s="507" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="509"/>
-      <c r="C15" s="509"/>
-      <c r="D15" s="510"/>
+      <c r="B15" s="508"/>
+      <c r="C15" s="508"/>
+      <c r="D15" s="509"/>
       <c r="E15" s="809">
         <f>SUM(B15:D15)</f>
         <v>0</v>
@@ -39122,25 +39122,25 @@
       <c r="F15" s="810"/>
       <c r="G15" s="80"/>
       <c r="H15" s="82"/>
-      <c r="I15" s="501"/>
-      <c r="J15" s="501"/>
-      <c r="K15" s="501"/>
-      <c r="L15" s="501"/>
-      <c r="M15" s="501"/>
-      <c r="N15" s="501"/>
+      <c r="I15" s="500"/>
+      <c r="J15" s="500"/>
+      <c r="K15" s="500"/>
+      <c r="L15" s="500"/>
+      <c r="M15" s="500"/>
+      <c r="N15" s="500"/>
       <c r="O15" s="232"/>
     </row>
     <row r="16" spans="1:15" ht="110.25" customHeight="1" thickBot="1">
-      <c r="A16" s="500"/>
-      <c r="B16" s="501"/>
+      <c r="A16" s="499"/>
+      <c r="B16" s="500"/>
       <c r="C16" s="82"/>
       <c r="D16" s="82"/>
       <c r="E16" s="98"/>
       <c r="F16" s="104"/>
       <c r="G16" s="105"/>
-      <c r="H16" s="397"/>
-      <c r="I16" s="397"/>
-      <c r="J16" s="413"/>
+      <c r="H16" s="396"/>
+      <c r="I16" s="396"/>
+      <c r="J16" s="412"/>
       <c r="K16" s="81"/>
       <c r="L16" s="81"/>
       <c r="M16" s="81"/>
@@ -39148,8 +39148,8 @@
       <c r="O16" s="165"/>
     </row>
     <row r="17" spans="1:15" ht="27.75" customHeight="1" thickBot="1">
-      <c r="A17" s="500"/>
-      <c r="B17" s="501"/>
+      <c r="A17" s="499"/>
+      <c r="B17" s="500"/>
       <c r="C17" s="82"/>
       <c r="D17" s="82"/>
       <c r="E17" s="89"/>
@@ -39166,16 +39166,16 @@
       <c r="O17" s="165"/>
     </row>
     <row r="18" spans="1:15" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A18" s="500"/>
-      <c r="B18" s="501"/>
+      <c r="A18" s="499"/>
+      <c r="B18" s="500"/>
       <c r="C18" s="82"/>
       <c r="D18" s="82"/>
       <c r="E18" s="89"/>
       <c r="F18" s="82"/>
       <c r="G18" s="80"/>
-      <c r="H18" s="394"/>
-      <c r="I18" s="394"/>
-      <c r="J18" s="394"/>
+      <c r="H18" s="393"/>
+      <c r="I18" s="393"/>
+      <c r="J18" s="393"/>
       <c r="K18" s="227"/>
       <c r="L18" s="227"/>
       <c r="M18" s="227"/>
@@ -39183,65 +39183,65 @@
       <c r="O18" s="165"/>
     </row>
     <row r="19" spans="1:15" ht="24" customHeight="1" thickBot="1">
-      <c r="A19" s="529"/>
-      <c r="B19" s="530"/>
-      <c r="C19" s="498"/>
+      <c r="A19" s="528"/>
+      <c r="B19" s="529"/>
+      <c r="C19" s="497"/>
       <c r="D19" s="82"/>
       <c r="E19" s="80"/>
       <c r="F19" s="105"/>
       <c r="H19" s="193"/>
-      <c r="I19" s="533" t="s">
+      <c r="I19" s="532" t="s">
         <v>177</v>
       </c>
-      <c r="J19" s="527"/>
-      <c r="K19" s="528"/>
-      <c r="L19" s="389"/>
-      <c r="M19" s="389"/>
+      <c r="J19" s="526"/>
+      <c r="K19" s="527"/>
+      <c r="L19" s="388"/>
+      <c r="M19" s="388"/>
       <c r="N19" s="104"/>
       <c r="O19" s="165"/>
     </row>
     <row r="20" spans="1:15" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A20" s="531" t="s">
+      <c r="A20" s="530" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="530" t="s">
+      <c r="B20" s="529" t="s">
         <v>179</v>
       </c>
-      <c r="C20" s="503" t="s">
+      <c r="C20" s="502" t="s">
         <v>180</v>
       </c>
       <c r="D20" s="82"/>
       <c r="E20" s="83"/>
       <c r="F20" s="83"/>
-      <c r="H20" s="545" t="s">
+      <c r="H20" s="544" t="s">
         <v>50</v>
       </c>
-      <c r="I20" s="542" t="s">
+      <c r="I20" s="541" t="s">
         <v>178</v>
       </c>
-      <c r="J20" s="543" t="s">
+      <c r="J20" s="542" t="s">
         <v>51</v>
       </c>
-      <c r="K20" s="544" t="s">
+      <c r="K20" s="543" t="s">
         <v>52</v>
       </c>
       <c r="L20" s="822" t="s">
         <v>53</v>
       </c>
       <c r="M20" s="823"/>
-      <c r="N20" s="402"/>
+      <c r="N20" s="401"/>
       <c r="O20" s="165"/>
     </row>
     <row r="21" spans="1:15" ht="22.5" customHeight="1">
-      <c r="A21" s="503">
+      <c r="A21" s="502">
         <f>SUM(B13:B15)</f>
         <v>0</v>
       </c>
-      <c r="B21" s="532">
+      <c r="B21" s="531">
         <f>SUM(C13:C15)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="503">
+      <c r="C21" s="502">
         <f>SUM(D13:D15)</f>
         <v>0</v>
       </c>
@@ -39249,10 +39249,10 @@
       <c r="E21" s="82"/>
       <c r="F21" s="82"/>
       <c r="G21" s="78"/>
-      <c r="H21" s="549"/>
-      <c r="I21" s="547"/>
-      <c r="J21" s="547"/>
-      <c r="K21" s="547"/>
+      <c r="H21" s="548"/>
+      <c r="I21" s="546"/>
+      <c r="J21" s="546"/>
+      <c r="K21" s="546"/>
       <c r="L21" s="824"/>
       <c r="M21" s="825"/>
       <c r="N21" s="80"/>
@@ -39266,10 +39266,10 @@
       <c r="E22" s="106"/>
       <c r="F22" s="106"/>
       <c r="G22" s="78"/>
-      <c r="H22" s="550"/>
-      <c r="I22" s="546"/>
-      <c r="J22" s="546"/>
-      <c r="K22" s="546"/>
+      <c r="H22" s="549"/>
+      <c r="I22" s="545"/>
+      <c r="J22" s="545"/>
+      <c r="K22" s="545"/>
       <c r="L22" s="820"/>
       <c r="M22" s="821"/>
       <c r="N22" s="80"/>
@@ -39285,73 +39285,73 @@
       <c r="E23" s="818"/>
       <c r="F23" s="819"/>
       <c r="G23" s="78"/>
-      <c r="H23" s="550"/>
-      <c r="I23" s="546"/>
-      <c r="J23" s="546"/>
-      <c r="K23" s="546"/>
+      <c r="H23" s="549"/>
+      <c r="I23" s="545"/>
+      <c r="J23" s="545"/>
+      <c r="K23" s="545"/>
       <c r="L23" s="820"/>
       <c r="M23" s="821"/>
       <c r="N23" s="80"/>
       <c r="O23" s="165"/>
     </row>
     <row r="24" spans="1:15" ht="36" customHeight="1" thickBot="1">
-      <c r="A24" s="559" t="s">
+      <c r="A24" s="558" t="s">
         <v>158</v>
       </c>
       <c r="B24" s="815" t="s">
         <v>184</v>
       </c>
       <c r="C24" s="816"/>
-      <c r="D24" s="560" t="s">
+      <c r="D24" s="559" t="s">
         <v>161</v>
       </c>
-      <c r="E24" s="561" t="s">
+      <c r="E24" s="560" t="s">
         <v>183</v>
       </c>
-      <c r="F24" s="562" t="s">
+      <c r="F24" s="561" t="s">
         <v>88</v>
       </c>
       <c r="G24" s="78"/>
-      <c r="H24" s="550"/>
-      <c r="I24" s="546"/>
-      <c r="J24" s="546"/>
-      <c r="K24" s="546"/>
+      <c r="H24" s="549"/>
+      <c r="I24" s="545"/>
+      <c r="J24" s="545"/>
+      <c r="K24" s="545"/>
       <c r="L24" s="820"/>
       <c r="M24" s="821"/>
       <c r="N24" s="80"/>
       <c r="O24" s="165"/>
     </row>
     <row r="25" spans="1:15" ht="24.75" customHeight="1">
-      <c r="A25" s="505" t="s">
+      <c r="A25" s="504" t="s">
         <v>94</v>
       </c>
       <c r="B25" s="801"/>
       <c r="C25" s="801"/>
-      <c r="D25" s="512"/>
-      <c r="E25" s="512"/>
-      <c r="F25" s="511">
+      <c r="D25" s="511"/>
+      <c r="E25" s="511"/>
+      <c r="F25" s="510">
         <f>SUM(B25:D25)</f>
         <v>0</v>
       </c>
       <c r="G25" s="78"/>
-      <c r="H25" s="551"/>
-      <c r="I25" s="546"/>
-      <c r="J25" s="546"/>
-      <c r="K25" s="546"/>
+      <c r="H25" s="550"/>
+      <c r="I25" s="545"/>
+      <c r="J25" s="545"/>
+      <c r="K25" s="545"/>
       <c r="L25" s="820"/>
       <c r="M25" s="821"/>
       <c r="N25" s="80"/>
       <c r="O25" s="165"/>
     </row>
     <row r="26" spans="1:15" ht="31.5" customHeight="1">
-      <c r="B26" s="496"/>
-      <c r="C26" s="496"/>
-      <c r="F26" s="497"/>
+      <c r="B26" s="495"/>
+      <c r="C26" s="495"/>
+      <c r="F26" s="496"/>
       <c r="G26" s="103"/>
-      <c r="H26" s="551"/>
-      <c r="I26" s="546"/>
-      <c r="J26" s="546"/>
-      <c r="K26" s="546"/>
+      <c r="H26" s="550"/>
+      <c r="I26" s="545"/>
+      <c r="J26" s="545"/>
+      <c r="K26" s="545"/>
       <c r="L26" s="820"/>
       <c r="M26" s="821"/>
       <c r="N26" s="80"/>
@@ -39362,13 +39362,13 @@
       <c r="B27" s="811"/>
       <c r="C27" s="811"/>
       <c r="D27" s="811"/>
-      <c r="E27" s="499"/>
-      <c r="F27" s="502"/>
+      <c r="E27" s="498"/>
+      <c r="F27" s="501"/>
       <c r="G27" s="89"/>
-      <c r="H27" s="551"/>
-      <c r="I27" s="546"/>
-      <c r="J27" s="546"/>
-      <c r="K27" s="546"/>
+      <c r="H27" s="550"/>
+      <c r="I27" s="545"/>
+      <c r="J27" s="545"/>
+      <c r="K27" s="545"/>
       <c r="L27" s="820"/>
       <c r="M27" s="821"/>
       <c r="N27" s="80"/>
@@ -39382,161 +39382,161 @@
       <c r="E28" s="82"/>
       <c r="F28" s="82"/>
       <c r="G28" s="89"/>
-      <c r="H28" s="551"/>
-      <c r="I28" s="546"/>
-      <c r="J28" s="546"/>
-      <c r="K28" s="546"/>
+      <c r="H28" s="550"/>
+      <c r="I28" s="545"/>
+      <c r="J28" s="545"/>
+      <c r="K28" s="545"/>
       <c r="L28" s="820"/>
       <c r="M28" s="821"/>
       <c r="N28" s="105"/>
       <c r="O28" s="165"/>
     </row>
     <row r="29" spans="1:15" ht="29.25" customHeight="1">
-      <c r="A29" s="500"/>
-      <c r="B29" s="501"/>
+      <c r="A29" s="499"/>
+      <c r="B29" s="500"/>
       <c r="C29" s="82"/>
       <c r="D29" s="82"/>
       <c r="E29" s="82"/>
       <c r="F29" s="82"/>
-      <c r="H29" s="551"/>
-      <c r="I29" s="546"/>
-      <c r="J29" s="546"/>
-      <c r="K29" s="546"/>
+      <c r="H29" s="550"/>
+      <c r="I29" s="545"/>
+      <c r="J29" s="545"/>
+      <c r="K29" s="545"/>
       <c r="L29" s="820"/>
       <c r="M29" s="821"/>
       <c r="N29" s="80"/>
       <c r="O29" s="165"/>
     </row>
     <row r="30" spans="1:15" ht="24.75" customHeight="1">
-      <c r="A30" s="500"/>
-      <c r="B30" s="501"/>
+      <c r="A30" s="499"/>
+      <c r="B30" s="500"/>
       <c r="C30" s="82"/>
       <c r="D30" s="82"/>
       <c r="E30" s="82"/>
       <c r="F30" s="82"/>
       <c r="G30" s="78"/>
-      <c r="H30" s="551"/>
-      <c r="I30" s="546"/>
-      <c r="J30" s="546"/>
-      <c r="K30" s="546"/>
+      <c r="H30" s="550"/>
+      <c r="I30" s="545"/>
+      <c r="J30" s="545"/>
+      <c r="K30" s="545"/>
       <c r="L30" s="820"/>
       <c r="M30" s="821"/>
       <c r="N30" s="80"/>
       <c r="O30" s="165"/>
     </row>
     <row r="31" spans="1:15" ht="24" customHeight="1">
-      <c r="A31" s="500"/>
-      <c r="B31" s="501"/>
+      <c r="A31" s="499"/>
+      <c r="B31" s="500"/>
       <c r="C31" s="82"/>
       <c r="D31" s="82"/>
       <c r="E31" s="82"/>
       <c r="F31" s="82"/>
       <c r="G31" s="78"/>
-      <c r="H31" s="550"/>
-      <c r="I31" s="546"/>
-      <c r="J31" s="546"/>
-      <c r="K31" s="546"/>
+      <c r="H31" s="549"/>
+      <c r="I31" s="545"/>
+      <c r="J31" s="545"/>
+      <c r="K31" s="545"/>
       <c r="L31" s="820"/>
       <c r="M31" s="821"/>
       <c r="N31" s="80"/>
       <c r="O31" s="165"/>
     </row>
     <row r="32" spans="1:15" ht="27.75" customHeight="1">
-      <c r="A32" s="500"/>
-      <c r="B32" s="501"/>
+      <c r="A32" s="499"/>
+      <c r="B32" s="500"/>
       <c r="C32" s="82"/>
       <c r="D32" s="82"/>
       <c r="E32" s="82"/>
       <c r="F32" s="82"/>
       <c r="G32" s="78"/>
-      <c r="H32" s="550"/>
-      <c r="I32" s="546"/>
-      <c r="J32" s="546"/>
-      <c r="K32" s="546"/>
+      <c r="H32" s="549"/>
+      <c r="I32" s="545"/>
+      <c r="J32" s="545"/>
+      <c r="K32" s="545"/>
       <c r="L32" s="820"/>
       <c r="M32" s="821"/>
       <c r="N32" s="80"/>
       <c r="O32" s="165"/>
     </row>
     <row r="33" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A33" s="500"/>
-      <c r="B33" s="501"/>
+      <c r="A33" s="499"/>
+      <c r="B33" s="500"/>
       <c r="C33" s="82"/>
       <c r="D33" s="82"/>
       <c r="E33" s="82"/>
       <c r="F33" s="82"/>
       <c r="G33" s="78"/>
-      <c r="H33" s="557"/>
-      <c r="I33" s="546"/>
-      <c r="J33" s="546"/>
-      <c r="K33" s="546"/>
+      <c r="H33" s="556"/>
+      <c r="I33" s="545"/>
+      <c r="J33" s="545"/>
+      <c r="K33" s="545"/>
       <c r="L33" s="820"/>
       <c r="M33" s="821"/>
       <c r="N33" s="80"/>
       <c r="O33" s="165"/>
     </row>
     <row r="34" spans="1:15" ht="27" customHeight="1">
-      <c r="A34" s="500"/>
-      <c r="B34" s="501"/>
+      <c r="A34" s="499"/>
+      <c r="B34" s="500"/>
       <c r="C34" s="82"/>
       <c r="D34" s="82"/>
       <c r="E34" s="82"/>
       <c r="F34" s="82"/>
       <c r="G34" s="78"/>
-      <c r="H34" s="557"/>
-      <c r="I34" s="546"/>
-      <c r="J34" s="546"/>
-      <c r="K34" s="546"/>
+      <c r="H34" s="556"/>
+      <c r="I34" s="545"/>
+      <c r="J34" s="545"/>
+      <c r="K34" s="545"/>
       <c r="L34" s="820"/>
       <c r="M34" s="821"/>
       <c r="N34" s="80"/>
       <c r="O34" s="165"/>
     </row>
     <row r="35" spans="1:15" ht="24" customHeight="1">
-      <c r="A35" s="500"/>
-      <c r="B35" s="501"/>
+      <c r="A35" s="499"/>
+      <c r="B35" s="500"/>
       <c r="C35" s="82"/>
       <c r="D35" s="82"/>
       <c r="E35" s="82"/>
       <c r="F35" s="82"/>
       <c r="G35" s="89"/>
-      <c r="H35" s="550"/>
-      <c r="I35" s="546"/>
-      <c r="J35" s="546"/>
-      <c r="K35" s="546"/>
+      <c r="H35" s="549"/>
+      <c r="I35" s="545"/>
+      <c r="J35" s="545"/>
+      <c r="K35" s="545"/>
       <c r="L35" s="820"/>
       <c r="M35" s="821"/>
       <c r="N35" s="80"/>
       <c r="O35" s="165"/>
     </row>
     <row r="36" spans="1:15" ht="24" customHeight="1">
-      <c r="A36" s="500"/>
-      <c r="B36" s="501"/>
+      <c r="A36" s="499"/>
+      <c r="B36" s="500"/>
       <c r="C36" s="82"/>
       <c r="D36" s="82"/>
       <c r="E36" s="82"/>
       <c r="F36" s="82"/>
-      <c r="H36" s="556"/>
-      <c r="I36" s="546"/>
-      <c r="J36" s="546"/>
-      <c r="K36" s="546"/>
+      <c r="H36" s="555"/>
+      <c r="I36" s="545"/>
+      <c r="J36" s="545"/>
+      <c r="K36" s="545"/>
       <c r="L36" s="820"/>
       <c r="M36" s="821"/>
       <c r="N36" s="80"/>
       <c r="O36" s="165"/>
     </row>
     <row r="37" spans="1:15" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A37" s="500"/>
-      <c r="B37" s="501"/>
+      <c r="A37" s="499"/>
+      <c r="B37" s="500"/>
       <c r="C37" s="82"/>
       <c r="D37" s="82"/>
       <c r="E37" s="82"/>
       <c r="F37" s="82"/>
       <c r="G37" s="78"/>
-      <c r="H37" s="552"/>
-      <c r="I37" s="548"/>
-      <c r="J37" s="548"/>
-      <c r="K37" s="548"/>
+      <c r="H37" s="551"/>
+      <c r="I37" s="547"/>
+      <c r="J37" s="547"/>
+      <c r="K37" s="547"/>
       <c r="L37" s="837"/>
       <c r="M37" s="838"/>
       <c r="N37" s="80"/>
@@ -39683,7 +39683,7 @@
       <c r="H3" s="867"/>
       <c r="I3" s="208"/>
       <c r="J3" s="209"/>
-      <c r="K3" s="479"/>
+      <c r="K3" s="478"/>
       <c r="L3" s="207"/>
       <c r="M3" s="207"/>
       <c r="N3" s="207"/>
@@ -39732,7 +39732,7 @@
         <v>191</v>
       </c>
       <c r="N5" s="850"/>
-      <c r="O5" s="534" t="s">
+      <c r="O5" s="533" t="s">
         <v>70</v>
       </c>
       <c r="P5" s="80"/>
@@ -39751,7 +39751,7 @@
       <c r="L6" s="858"/>
       <c r="M6" s="846"/>
       <c r="N6" s="847"/>
-      <c r="O6" s="572"/>
+      <c r="O6" s="571"/>
       <c r="P6" s="80"/>
       <c r="Q6" s="82"/>
       <c r="R6" s="82"/>
@@ -39772,7 +39772,7 @@
       <c r="L7" s="860"/>
       <c r="M7" s="848"/>
       <c r="N7" s="849"/>
-      <c r="O7" s="573"/>
+      <c r="O7" s="572"/>
       <c r="P7" s="80"/>
       <c r="Q7" s="82"/>
       <c r="R7" s="82"/>
@@ -39790,7 +39790,7 @@
       <c r="L8" s="860"/>
       <c r="M8" s="848"/>
       <c r="N8" s="849"/>
-      <c r="O8" s="573"/>
+      <c r="O8" s="572"/>
       <c r="P8" s="80"/>
       <c r="Q8" s="82"/>
       <c r="R8" s="82"/>
@@ -39808,7 +39808,7 @@
       <c r="L9" s="860"/>
       <c r="M9" s="848"/>
       <c r="N9" s="849"/>
-      <c r="O9" s="573"/>
+      <c r="O9" s="572"/>
       <c r="P9" s="80"/>
       <c r="Q9" s="82"/>
       <c r="R9" s="82"/>
@@ -39817,8 +39817,8 @@
     </row>
     <row r="10" spans="1:20" ht="51" customHeight="1" thickBot="1">
       <c r="A10" s="79"/>
-      <c r="B10" s="568"/>
-      <c r="C10" s="569" t="s">
+      <c r="B10" s="567"/>
+      <c r="C10" s="568" t="s">
         <v>185</v>
       </c>
       <c r="D10" s="80"/>
@@ -39828,7 +39828,7 @@
       <c r="L10" s="860"/>
       <c r="M10" s="848"/>
       <c r="N10" s="849"/>
-      <c r="O10" s="573"/>
+      <c r="O10" s="572"/>
       <c r="P10" s="80"/>
       <c r="Q10" s="82"/>
       <c r="R10" s="82"/>
@@ -39837,8 +39837,8 @@
     </row>
     <row r="11" spans="1:20" ht="57" customHeight="1" thickBot="1">
       <c r="A11" s="79"/>
-      <c r="B11" s="570"/>
-      <c r="C11" s="571" t="s">
+      <c r="B11" s="569"/>
+      <c r="C11" s="570" t="s">
         <v>186</v>
       </c>
       <c r="D11" s="89"/>
@@ -39850,7 +39850,7 @@
       <c r="L11" s="860"/>
       <c r="M11" s="848"/>
       <c r="N11" s="849"/>
-      <c r="O11" s="573"/>
+      <c r="O11" s="572"/>
       <c r="P11" s="80"/>
       <c r="Q11" s="82"/>
       <c r="R11" s="82"/>
@@ -39859,8 +39859,8 @@
     </row>
     <row r="12" spans="1:20" ht="49.5" customHeight="1">
       <c r="A12" s="79"/>
-      <c r="B12" s="567"/>
-      <c r="C12" s="567"/>
+      <c r="B12" s="566"/>
+      <c r="C12" s="566"/>
       <c r="D12" s="89"/>
       <c r="G12" s="89"/>
       <c r="I12" s="80"/>
@@ -39869,7 +39869,7 @@
       <c r="L12" s="860"/>
       <c r="M12" s="848"/>
       <c r="N12" s="849"/>
-      <c r="O12" s="573"/>
+      <c r="O12" s="572"/>
       <c r="P12" s="80"/>
       <c r="Q12" s="82"/>
       <c r="R12" s="82"/>
@@ -39891,7 +39891,7 @@
       <c r="L13" s="860"/>
       <c r="M13" s="848"/>
       <c r="N13" s="849"/>
-      <c r="O13" s="573"/>
+      <c r="O13" s="572"/>
       <c r="P13" s="80"/>
       <c r="Q13" s="82"/>
       <c r="R13" s="82"/>
@@ -39910,7 +39910,7 @@
       </c>
       <c r="F14" s="869"/>
       <c r="G14" s="869"/>
-      <c r="H14" s="467" t="s">
+      <c r="H14" s="466" t="s">
         <v>123</v>
       </c>
       <c r="I14" s="80"/>
@@ -39919,7 +39919,7 @@
       <c r="L14" s="860"/>
       <c r="M14" s="848"/>
       <c r="N14" s="849"/>
-      <c r="O14" s="573"/>
+      <c r="O14" s="572"/>
       <c r="P14" s="80"/>
       <c r="Q14" s="82"/>
       <c r="R14" s="82"/>
@@ -39928,24 +39928,24 @@
     </row>
     <row r="15" spans="1:20" ht="44.25" customHeight="1">
       <c r="A15" s="79"/>
-      <c r="B15" s="474" t="s">
+      <c r="B15" s="473" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="474" t="s">
+      <c r="C15" s="473" t="s">
         <v>172</v>
       </c>
       <c r="D15" s="89"/>
       <c r="E15" s="870"/>
       <c r="F15" s="870"/>
       <c r="G15" s="870"/>
-      <c r="H15" s="476"/>
+      <c r="H15" s="475"/>
       <c r="I15" s="80"/>
       <c r="J15" s="103"/>
       <c r="K15" s="859"/>
       <c r="L15" s="860"/>
       <c r="M15" s="848"/>
       <c r="N15" s="849"/>
-      <c r="O15" s="573"/>
+      <c r="O15" s="572"/>
       <c r="P15" s="80"/>
       <c r="Q15" s="82"/>
       <c r="R15" s="82"/>
@@ -39954,20 +39954,20 @@
     </row>
     <row r="16" spans="1:20" ht="47.25" customHeight="1">
       <c r="A16" s="79"/>
-      <c r="B16" s="475"/>
-      <c r="C16" s="475"/>
+      <c r="B16" s="474"/>
+      <c r="C16" s="474"/>
       <c r="D16" s="89"/>
       <c r="E16" s="870"/>
       <c r="F16" s="870"/>
       <c r="G16" s="870"/>
-      <c r="H16" s="476"/>
+      <c r="H16" s="475"/>
       <c r="I16" s="80"/>
       <c r="J16" s="103"/>
       <c r="K16" s="859"/>
       <c r="L16" s="860"/>
       <c r="M16" s="848"/>
       <c r="N16" s="849"/>
-      <c r="O16" s="573"/>
+      <c r="O16" s="572"/>
       <c r="P16" s="80"/>
       <c r="Q16" s="82"/>
       <c r="R16" s="82"/>
@@ -39976,20 +39976,20 @@
     </row>
     <row r="17" spans="1:20" ht="46.5" customHeight="1">
       <c r="A17" s="79"/>
-      <c r="B17" s="475"/>
-      <c r="C17" s="475"/>
+      <c r="B17" s="474"/>
+      <c r="C17" s="474"/>
       <c r="D17" s="89"/>
       <c r="E17" s="870"/>
       <c r="F17" s="870"/>
       <c r="G17" s="870"/>
-      <c r="H17" s="476"/>
+      <c r="H17" s="475"/>
       <c r="I17" s="80"/>
       <c r="J17" s="79"/>
       <c r="K17" s="859"/>
       <c r="L17" s="860"/>
       <c r="M17" s="848"/>
       <c r="N17" s="849"/>
-      <c r="O17" s="573"/>
+      <c r="O17" s="572"/>
       <c r="P17" s="80"/>
       <c r="Q17" s="82"/>
       <c r="R17" s="82"/>
@@ -39998,20 +39998,20 @@
     </row>
     <row r="18" spans="1:20" ht="54.75" customHeight="1" thickBot="1">
       <c r="A18" s="79"/>
-      <c r="B18" s="475"/>
-      <c r="C18" s="475"/>
+      <c r="B18" s="474"/>
+      <c r="C18" s="474"/>
       <c r="D18" s="89"/>
       <c r="E18" s="870"/>
       <c r="F18" s="870"/>
       <c r="G18" s="870"/>
-      <c r="H18" s="476"/>
+      <c r="H18" s="475"/>
       <c r="I18" s="80"/>
       <c r="J18" s="87"/>
       <c r="K18" s="882"/>
       <c r="L18" s="883"/>
       <c r="M18" s="880"/>
       <c r="N18" s="881"/>
-      <c r="O18" s="573"/>
+      <c r="O18" s="572"/>
       <c r="P18" s="80"/>
       <c r="Q18" s="82"/>
       <c r="R18" s="82"/>
@@ -40020,19 +40020,19 @@
     </row>
     <row r="19" spans="1:20" ht="42" customHeight="1" thickBot="1">
       <c r="A19" s="79"/>
-      <c r="B19" s="475"/>
-      <c r="C19" s="475"/>
+      <c r="B19" s="474"/>
+      <c r="C19" s="474"/>
       <c r="D19" s="89"/>
       <c r="E19" s="870"/>
       <c r="F19" s="870"/>
       <c r="G19" s="870"/>
-      <c r="H19" s="476"/>
+      <c r="H19" s="475"/>
       <c r="I19" s="80"/>
       <c r="J19" s="79"/>
       <c r="K19" s="230"/>
       <c r="M19" s="880"/>
       <c r="N19" s="881"/>
-      <c r="O19" s="573"/>
+      <c r="O19" s="572"/>
       <c r="P19" s="80"/>
       <c r="Q19" s="82"/>
       <c r="R19" s="82"/>
@@ -40041,19 +40041,19 @@
     </row>
     <row r="20" spans="1:20" ht="33.75" customHeight="1" thickBot="1">
       <c r="A20" s="79"/>
-      <c r="B20" s="475"/>
-      <c r="C20" s="475"/>
+      <c r="B20" s="474"/>
+      <c r="C20" s="474"/>
       <c r="D20" s="89"/>
       <c r="E20" s="878"/>
       <c r="F20" s="878"/>
       <c r="G20" s="878"/>
-      <c r="H20" s="477"/>
+      <c r="H20" s="476"/>
       <c r="I20" s="80"/>
       <c r="J20" s="103"/>
       <c r="K20" s="230"/>
       <c r="M20" s="880"/>
       <c r="N20" s="881"/>
-      <c r="O20" s="573"/>
+      <c r="O20" s="572"/>
       <c r="P20" s="80"/>
       <c r="Q20" s="82"/>
       <c r="R20" s="82"/>
@@ -40062,15 +40062,15 @@
     </row>
     <row r="21" spans="1:20" ht="46.5" customHeight="1" thickBot="1">
       <c r="A21" s="79"/>
-      <c r="B21" s="475"/>
-      <c r="C21" s="475"/>
+      <c r="B21" s="474"/>
+      <c r="C21" s="474"/>
       <c r="D21" s="98"/>
       <c r="E21" s="868" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="868"/>
       <c r="G21" s="868"/>
-      <c r="H21" s="478">
+      <c r="H21" s="477">
         <f>SUM(H15:H20)</f>
         <v>0</v>
       </c>
@@ -40079,7 +40079,7 @@
       <c r="K21" s="230"/>
       <c r="M21" s="880"/>
       <c r="N21" s="881"/>
-      <c r="O21" s="573"/>
+      <c r="O21" s="572"/>
       <c r="P21" s="80"/>
       <c r="Q21" s="82"/>
       <c r="R21" s="82"/>
@@ -40088,10 +40088,10 @@
     </row>
     <row r="22" spans="1:20" ht="37.5" customHeight="1" thickBot="1">
       <c r="A22" s="79"/>
-      <c r="B22" s="478" t="s">
+      <c r="B22" s="477" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="478">
+      <c r="C22" s="477">
         <f>SUM(C16:C21)</f>
         <v>0</v>
       </c>
@@ -40107,7 +40107,7 @@
       <c r="K22" s="230"/>
       <c r="M22" s="880"/>
       <c r="N22" s="881"/>
-      <c r="O22" s="573"/>
+      <c r="O22" s="572"/>
       <c r="P22" s="80"/>
       <c r="Q22" s="82"/>
       <c r="R22" s="79"/>
@@ -40123,7 +40123,7 @@
       <c r="L23" s="87"/>
       <c r="M23" s="880"/>
       <c r="N23" s="881"/>
-      <c r="O23" s="573"/>
+      <c r="O23" s="572"/>
       <c r="P23" s="80"/>
       <c r="Q23" s="82"/>
       <c r="R23" s="79"/>
@@ -40132,8 +40132,8 @@
     </row>
     <row r="24" spans="1:20" ht="25.5" customHeight="1" thickBot="1">
       <c r="A24" s="79"/>
-      <c r="B24" s="465"/>
-      <c r="C24" s="465"/>
+      <c r="B24" s="464"/>
+      <c r="C24" s="464"/>
       <c r="D24" s="212"/>
       <c r="I24" s="90"/>
       <c r="J24" s="87"/>
@@ -40141,7 +40141,7 @@
       <c r="L24" s="234"/>
       <c r="M24" s="880"/>
       <c r="N24" s="881"/>
-      <c r="O24" s="573"/>
+      <c r="O24" s="572"/>
       <c r="P24" s="80"/>
       <c r="Q24" s="82"/>
       <c r="S24" s="82"/>
@@ -40149,17 +40149,17 @@
     </row>
     <row r="25" spans="1:20" ht="25.5" customHeight="1" thickBot="1">
       <c r="A25" s="79"/>
-      <c r="B25" s="466"/>
-      <c r="C25" s="466"/>
+      <c r="B25" s="465"/>
+      <c r="C25" s="465"/>
       <c r="D25" s="231"/>
       <c r="J25" s="89"/>
-      <c r="K25" s="536" t="s">
+      <c r="K25" s="535" t="s">
         <v>144</v>
       </c>
-      <c r="L25" s="537"/>
+      <c r="L25" s="536"/>
       <c r="M25" s="880"/>
       <c r="N25" s="881"/>
-      <c r="O25" s="573"/>
+      <c r="O25" s="572"/>
       <c r="P25" s="80"/>
       <c r="Q25" s="82"/>
       <c r="S25" s="82"/>
@@ -40167,21 +40167,21 @@
     </row>
     <row r="26" spans="1:20" ht="21" customHeight="1">
       <c r="A26" s="79"/>
-      <c r="B26" s="466"/>
-      <c r="C26" s="466"/>
+      <c r="B26" s="465"/>
+      <c r="C26" s="465"/>
       <c r="D26" s="231"/>
-      <c r="E26" s="469"/>
-      <c r="F26" s="470"/>
+      <c r="E26" s="468"/>
+      <c r="F26" s="469"/>
       <c r="H26" s="879"/>
       <c r="I26" s="879"/>
-      <c r="J26" s="468"/>
+      <c r="J26" s="467"/>
       <c r="K26" s="875" t="s">
         <v>192</v>
       </c>
       <c r="L26" s="876"/>
       <c r="M26" s="876"/>
       <c r="N26" s="877"/>
-      <c r="O26" s="535"/>
+      <c r="O26" s="534"/>
       <c r="P26" s="80"/>
       <c r="Q26" s="82"/>
       <c r="S26" s="82"/>
@@ -40189,13 +40189,13 @@
     </row>
     <row r="27" spans="1:20" ht="26.25" customHeight="1">
       <c r="A27" s="79"/>
-      <c r="B27" s="466"/>
-      <c r="C27" s="466"/>
+      <c r="B27" s="465"/>
+      <c r="C27" s="465"/>
       <c r="D27" s="231"/>
-      <c r="E27" s="471"/>
-      <c r="F27" s="471"/>
-      <c r="H27" s="472"/>
-      <c r="I27" s="473"/>
+      <c r="E27" s="470"/>
+      <c r="F27" s="470"/>
+      <c r="H27" s="471"/>
+      <c r="I27" s="472"/>
       <c r="J27" s="211"/>
       <c r="K27" s="871" t="s">
         <v>190</v>
@@ -40872,34 +40872,34 @@
     <row r="5" spans="1:36" ht="11.25" customHeight="1" thickBot="1">
       <c r="A5" s="230"/>
       <c r="B5" s="104"/>
-      <c r="D5" s="355"/>
-      <c r="E5" s="355"/>
-      <c r="F5" s="355"/>
-      <c r="G5" s="355"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="354"/>
       <c r="H5" s="87"/>
-      <c r="I5" s="357"/>
-      <c r="J5" s="358"/>
-      <c r="L5" s="357"/>
+      <c r="I5" s="356"/>
+      <c r="J5" s="357"/>
+      <c r="L5" s="356"/>
       <c r="M5" s="104"/>
-      <c r="N5" s="358"/>
-      <c r="P5" s="357"/>
-      <c r="Q5" s="357"/>
-      <c r="R5" s="357"/>
+      <c r="N5" s="357"/>
+      <c r="P5" s="356"/>
+      <c r="Q5" s="356"/>
+      <c r="R5" s="356"/>
       <c r="S5" s="104"/>
-      <c r="U5" s="357"/>
-      <c r="V5" s="357"/>
-      <c r="W5" s="358"/>
-      <c r="X5" s="358"/>
-      <c r="Y5" s="358"/>
-      <c r="Z5" s="358"/>
+      <c r="U5" s="356"/>
+      <c r="V5" s="356"/>
+      <c r="W5" s="357"/>
+      <c r="X5" s="357"/>
+      <c r="Y5" s="357"/>
+      <c r="Z5" s="357"/>
       <c r="AA5" s="106"/>
       <c r="AB5" s="106"/>
       <c r="AC5" s="106"/>
       <c r="AD5" s="106"/>
       <c r="AE5" s="104"/>
-      <c r="AF5" s="358"/>
+      <c r="AF5" s="357"/>
       <c r="AH5" s="87"/>
-      <c r="AI5" s="405"/>
+      <c r="AI5" s="404"/>
     </row>
     <row r="6" spans="1:36" ht="9.75" customHeight="1">
       <c r="A6" s="136"/>
@@ -40910,42 +40910,42 @@
       </c>
       <c r="F6" s="1024"/>
       <c r="G6" s="1025"/>
-      <c r="H6" s="356"/>
+      <c r="H6" s="355"/>
       <c r="I6" s="229"/>
       <c r="J6" s="996" t="s">
         <v>92</v>
       </c>
       <c r="K6" s="997"/>
       <c r="L6" s="998"/>
-      <c r="M6" s="359"/>
+      <c r="M6" s="358"/>
       <c r="N6" s="229"/>
-      <c r="O6" s="362"/>
-      <c r="P6" s="362"/>
+      <c r="O6" s="361"/>
+      <c r="P6" s="361"/>
       <c r="Q6" s="1017" t="s">
         <v>93</v>
       </c>
       <c r="R6" s="1018"/>
-      <c r="S6" s="360"/>
+      <c r="S6" s="359"/>
       <c r="T6" s="229"/>
-      <c r="U6" s="362"/>
-      <c r="V6" s="362"/>
+      <c r="U6" s="361"/>
+      <c r="V6" s="361"/>
       <c r="W6" s="996" t="s">
         <v>104</v>
       </c>
       <c r="X6" s="997"/>
       <c r="Y6" s="997"/>
       <c r="Z6" s="998"/>
-      <c r="AA6" s="398"/>
+      <c r="AA6" s="397"/>
       <c r="AB6" s="229"/>
-      <c r="AC6" s="362"/>
+      <c r="AC6" s="361"/>
       <c r="AD6" s="989" t="s">
         <v>94</v>
       </c>
       <c r="AE6" s="990"/>
       <c r="AF6" s="991"/>
       <c r="AG6" s="136"/>
-      <c r="AH6" s="386"/>
-      <c r="AI6" s="406"/>
+      <c r="AH6" s="385"/>
+      <c r="AI6" s="405"/>
     </row>
     <row r="7" spans="1:36" ht="15.75" customHeight="1">
       <c r="A7" s="136"/>
@@ -40954,38 +40954,38 @@
       <c r="E7" s="1026"/>
       <c r="F7" s="1027"/>
       <c r="G7" s="1028"/>
-      <c r="H7" s="356"/>
+      <c r="H7" s="355"/>
       <c r="I7" s="233"/>
       <c r="J7" s="1014"/>
       <c r="K7" s="1015"/>
       <c r="L7" s="1016"/>
-      <c r="M7" s="359"/>
+      <c r="M7" s="358"/>
       <c r="N7" s="233"/>
-      <c r="O7" s="354"/>
-      <c r="P7" s="361"/>
+      <c r="O7" s="353"/>
+      <c r="P7" s="360"/>
       <c r="Q7" s="865"/>
       <c r="R7" s="1019"/>
-      <c r="S7" s="360"/>
+      <c r="S7" s="359"/>
       <c r="T7" s="233"/>
-      <c r="U7" s="354"/>
-      <c r="V7" s="361"/>
+      <c r="U7" s="353"/>
+      <c r="V7" s="360"/>
       <c r="W7" s="999"/>
       <c r="X7" s="1000"/>
       <c r="Y7" s="1000"/>
       <c r="Z7" s="1001"/>
-      <c r="AA7" s="398"/>
+      <c r="AA7" s="397"/>
       <c r="AB7" s="233"/>
-      <c r="AC7" s="354"/>
+      <c r="AC7" s="353"/>
       <c r="AD7" s="992"/>
       <c r="AE7" s="993"/>
       <c r="AF7" s="994"/>
       <c r="AG7" s="136"/>
-      <c r="AH7" s="386"/>
-      <c r="AI7" s="406"/>
+      <c r="AH7" s="385"/>
+      <c r="AI7" s="405"/>
     </row>
     <row r="8" spans="1:36" ht="12.75" customHeight="1">
       <c r="A8" s="136"/>
-      <c r="B8" s="363"/>
+      <c r="B8" s="362"/>
       <c r="C8" s="206"/>
       <c r="E8" s="1002">
         <v>64</v>
@@ -40999,7 +40999,7 @@
         <v>16</v>
       </c>
       <c r="L8" s="1034"/>
-      <c r="M8" s="359"/>
+      <c r="M8" s="358"/>
       <c r="N8" s="136"/>
       <c r="O8" s="79"/>
       <c r="P8" s="1002">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="Q8" s="1003"/>
       <c r="R8" s="1004"/>
-      <c r="S8" s="360"/>
+      <c r="S8" s="359"/>
       <c r="T8" s="136"/>
       <c r="U8" s="79"/>
       <c r="V8" s="1002">
@@ -41017,7 +41017,7 @@
       <c r="X8" s="1003"/>
       <c r="Y8" s="1003"/>
       <c r="Z8" s="1004"/>
-      <c r="AA8" s="399"/>
+      <c r="AA8" s="398"/>
       <c r="AB8" s="136"/>
       <c r="AC8" s="79"/>
       <c r="AD8" s="1002">
@@ -41026,43 +41026,43 @@
       <c r="AE8" s="1003"/>
       <c r="AF8" s="1004"/>
       <c r="AG8" s="136"/>
-      <c r="AH8" s="387"/>
+      <c r="AH8" s="386"/>
       <c r="AI8" s="232"/>
     </row>
     <row r="9" spans="1:36" ht="13.5" customHeight="1" thickBot="1">
       <c r="A9" s="230"/>
       <c r="B9" s="100"/>
       <c r="C9" s="144"/>
-      <c r="D9" s="352"/>
+      <c r="D9" s="351"/>
       <c r="E9" s="1030"/>
       <c r="F9" s="1031"/>
       <c r="G9" s="1032"/>
       <c r="I9" s="137"/>
-      <c r="J9" s="353"/>
+      <c r="J9" s="352"/>
       <c r="K9" s="1035"/>
       <c r="L9" s="1036"/>
-      <c r="M9" s="360"/>
+      <c r="M9" s="359"/>
       <c r="N9" s="137"/>
-      <c r="O9" s="353"/>
+      <c r="O9" s="352"/>
       <c r="P9" s="1005"/>
       <c r="Q9" s="1006"/>
       <c r="R9" s="1007"/>
-      <c r="S9" s="360"/>
+      <c r="S9" s="359"/>
       <c r="T9" s="137"/>
-      <c r="U9" s="353"/>
+      <c r="U9" s="352"/>
       <c r="V9" s="1005"/>
       <c r="W9" s="1006"/>
       <c r="X9" s="1006"/>
       <c r="Y9" s="1006"/>
       <c r="Z9" s="1007"/>
-      <c r="AA9" s="399"/>
+      <c r="AA9" s="398"/>
       <c r="AB9" s="137"/>
-      <c r="AC9" s="353"/>
+      <c r="AC9" s="352"/>
       <c r="AD9" s="1005"/>
       <c r="AE9" s="1006"/>
       <c r="AF9" s="1007"/>
-      <c r="AG9" s="400"/>
-      <c r="AH9" s="387"/>
+      <c r="AG9" s="399"/>
+      <c r="AH9" s="386"/>
       <c r="AI9" s="165"/>
     </row>
     <row r="10" spans="1:36" ht="13.5" customHeight="1" thickBot="1">
@@ -41070,34 +41070,34 @@
       <c r="B10" s="103"/>
       <c r="C10" s="107"/>
       <c r="D10" s="106"/>
-      <c r="E10" s="435"/>
-      <c r="F10" s="435"/>
-      <c r="G10" s="435"/>
+      <c r="E10" s="434"/>
+      <c r="F10" s="434"/>
+      <c r="G10" s="434"/>
       <c r="H10" s="82"/>
       <c r="I10" s="164"/>
-      <c r="K10" s="434"/>
-      <c r="L10" s="434"/>
+      <c r="K10" s="433"/>
+      <c r="L10" s="433"/>
       <c r="M10" s="80"/>
-      <c r="N10" s="433"/>
+      <c r="N10" s="432"/>
       <c r="O10" s="164"/>
-      <c r="P10" s="431"/>
-      <c r="Q10" s="429"/>
-      <c r="R10" s="439"/>
+      <c r="P10" s="430"/>
+      <c r="Q10" s="428"/>
+      <c r="R10" s="438"/>
       <c r="S10" s="103"/>
-      <c r="T10" s="412"/>
-      <c r="U10" s="365"/>
-      <c r="V10" s="440"/>
-      <c r="W10" s="429"/>
-      <c r="X10" s="439"/>
-      <c r="Y10" s="440"/>
-      <c r="Z10" s="440"/>
-      <c r="AA10" s="430"/>
-      <c r="AB10" s="365"/>
-      <c r="AD10" s="440"/>
-      <c r="AE10" s="440"/>
-      <c r="AF10" s="429"/>
+      <c r="T10" s="411"/>
+      <c r="U10" s="364"/>
+      <c r="V10" s="439"/>
+      <c r="W10" s="428"/>
+      <c r="X10" s="438"/>
+      <c r="Y10" s="439"/>
+      <c r="Z10" s="439"/>
+      <c r="AA10" s="429"/>
+      <c r="AB10" s="364"/>
+      <c r="AD10" s="439"/>
+      <c r="AE10" s="439"/>
+      <c r="AF10" s="428"/>
       <c r="AG10" s="90"/>
-      <c r="AH10" s="441"/>
+      <c r="AH10" s="440"/>
       <c r="AI10" s="165"/>
     </row>
     <row r="11" spans="1:36" ht="26.25" customHeight="1" thickBot="1">
@@ -41105,11 +41105,11 @@
       <c r="B11" s="148"/>
       <c r="C11" s="148"/>
       <c r="D11" s="148"/>
-      <c r="E11" s="352"/>
+      <c r="E11" s="351"/>
       <c r="F11" s="148"/>
-      <c r="G11" s="352"/>
+      <c r="G11" s="351"/>
       <c r="H11" s="148"/>
-      <c r="I11" s="352"/>
+      <c r="I11" s="351"/>
       <c r="J11" s="148"/>
       <c r="K11" s="148"/>
       <c r="L11" s="148"/>
@@ -41133,15 +41133,15 @@
       <c r="AC11" s="1044"/>
       <c r="AD11" s="1044"/>
       <c r="AE11" s="1044"/>
-      <c r="AF11" s="438">
+      <c r="AF11" s="437">
         <v>2025</v>
       </c>
-      <c r="AG11" s="449"/>
-      <c r="AH11" s="432"/>
-      <c r="AI11" s="406"/>
+      <c r="AG11" s="448"/>
+      <c r="AH11" s="431"/>
+      <c r="AI11" s="405"/>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1">
-      <c r="A12" s="407"/>
+      <c r="A12" s="406"/>
       <c r="B12" s="1053" t="s">
         <v>150</v>
       </c>
@@ -41161,54 +41161,54 @@
         <v>88</v>
       </c>
       <c r="N12" s="1050"/>
-      <c r="O12" s="366"/>
+      <c r="O12" s="365"/>
       <c r="P12" s="79"/>
-      <c r="Q12" s="436"/>
-      <c r="R12" s="437"/>
-      <c r="S12" s="427">
+      <c r="Q12" s="435"/>
+      <c r="R12" s="436"/>
+      <c r="S12" s="426">
         <v>0</v>
       </c>
-      <c r="T12" s="428">
+      <c r="T12" s="427">
         <v>1</v>
       </c>
-      <c r="U12" s="428">
+      <c r="U12" s="427">
         <v>2</v>
       </c>
-      <c r="V12" s="427">
+      <c r="V12" s="426">
         <v>3</v>
       </c>
-      <c r="W12" s="428">
+      <c r="W12" s="427">
         <v>4</v>
       </c>
-      <c r="X12" s="428">
+      <c r="X12" s="427">
         <v>5</v>
       </c>
-      <c r="Y12" s="427">
+      <c r="Y12" s="426">
         <v>6</v>
       </c>
-      <c r="Z12" s="428">
+      <c r="Z12" s="427">
         <v>7</v>
       </c>
-      <c r="AA12" s="428">
+      <c r="AA12" s="427">
         <v>8</v>
       </c>
-      <c r="AB12" s="427">
+      <c r="AB12" s="426">
         <v>9</v>
       </c>
-      <c r="AC12" s="428">
+      <c r="AC12" s="427">
         <v>10</v>
       </c>
-      <c r="AD12" s="428">
+      <c r="AD12" s="427">
         <v>11</v>
       </c>
-      <c r="AE12" s="427">
+      <c r="AE12" s="426">
         <v>12</v>
       </c>
-      <c r="AF12" s="445">
+      <c r="AF12" s="444">
         <v>13</v>
       </c>
-      <c r="AG12" s="414"/>
-      <c r="AH12" s="450"/>
+      <c r="AG12" s="413"/>
+      <c r="AH12" s="449"/>
       <c r="AI12" s="232"/>
     </row>
     <row r="13" spans="1:36" ht="15.75" customHeight="1" thickBot="1">
@@ -41226,72 +41226,72 @@
       <c r="L13" s="1049"/>
       <c r="M13" s="1051"/>
       <c r="N13" s="1052"/>
-      <c r="O13" s="366"/>
+      <c r="O13" s="365"/>
       <c r="P13" s="79"/>
-      <c r="Q13" s="421"/>
-      <c r="R13" s="411"/>
-      <c r="S13" s="426">
+      <c r="Q13" s="420"/>
+      <c r="R13" s="410"/>
+      <c r="S13" s="425">
         <f>IF(INT($J$18*14/64 - S$12) = 0,$J$18, INT($J$18*14/64 - S$12))</f>
         <v>5</v>
       </c>
-      <c r="T13" s="426">
+      <c r="T13" s="425">
         <f t="shared" ref="T13:AF13" si="0">IF(INT($J$18*14/64 - T$12) = 0,$J$18, INT($J$18*14/64 - T$12))</f>
         <v>4</v>
       </c>
-      <c r="U13" s="426">
+      <c r="U13" s="425">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="V13" s="426">
+      <c r="V13" s="425">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="W13" s="426">
+      <c r="W13" s="425">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="X13" s="426">
+      <c r="X13" s="425">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="Y13" s="426">
+      <c r="Y13" s="425">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="Z13" s="426">
+      <c r="Z13" s="425">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="AA13" s="426">
+      <c r="AA13" s="425">
         <f t="shared" si="0"/>
         <v>-3</v>
       </c>
-      <c r="AB13" s="426">
+      <c r="AB13" s="425">
         <f t="shared" si="0"/>
         <v>-4</v>
       </c>
-      <c r="AC13" s="426">
+      <c r="AC13" s="425">
         <f t="shared" si="0"/>
         <v>-5</v>
       </c>
-      <c r="AD13" s="426">
+      <c r="AD13" s="425">
         <f t="shared" si="0"/>
         <v>-6</v>
       </c>
-      <c r="AE13" s="426">
+      <c r="AE13" s="425">
         <f t="shared" si="0"/>
         <v>-7</v>
       </c>
-      <c r="AF13" s="444">
+      <c r="AF13" s="443">
         <f t="shared" si="0"/>
         <v>-8</v>
       </c>
-      <c r="AG13" s="411"/>
-      <c r="AH13" s="450"/>
-      <c r="AI13" s="406"/>
+      <c r="AG13" s="410"/>
+      <c r="AH13" s="449"/>
+      <c r="AI13" s="405"/>
     </row>
     <row r="14" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A14" s="407"/>
+      <c r="A14" s="406"/>
       <c r="B14" s="1056"/>
       <c r="C14" s="1057"/>
       <c r="D14" s="1057"/>
@@ -41311,74 +41311,74 @@
       <c r="L14" s="1071"/>
       <c r="M14" s="1051"/>
       <c r="N14" s="1052"/>
-      <c r="O14" s="366"/>
+      <c r="O14" s="365"/>
       <c r="P14" s="79"/>
-      <c r="Q14" s="421"/>
-      <c r="R14" s="415" t="s">
+      <c r="Q14" s="420"/>
+      <c r="R14" s="414" t="s">
         <v>104</v>
       </c>
-      <c r="S14" s="424">
+      <c r="S14" s="423">
         <f>IF(INT($H$18*14/64 - S$12) = 0,$H$18, INT($H$18*14/64 - S$12))</f>
         <v>8</v>
       </c>
-      <c r="T14" s="424">
+      <c r="T14" s="423">
         <f t="shared" ref="T14:AF14" si="1">IF(INT($H$18*14/64 - T$12) = 0,$H$18, INT($H$18*14/64 - T$12))</f>
         <v>7</v>
       </c>
-      <c r="U14" s="424">
+      <c r="U14" s="423">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="V14" s="424">
+      <c r="V14" s="423">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="W14" s="424">
+      <c r="W14" s="423">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="X14" s="424">
+      <c r="X14" s="423">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="Y14" s="424">
+      <c r="Y14" s="423">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="Z14" s="424">
+      <c r="Z14" s="423">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AA14" s="424">
+      <c r="AA14" s="423">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="AB14" s="424">
+      <c r="AB14" s="423">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="AC14" s="424">
+      <c r="AC14" s="423">
         <f t="shared" si="1"/>
         <v>-2</v>
       </c>
-      <c r="AD14" s="424">
+      <c r="AD14" s="423">
         <f t="shared" si="1"/>
         <v>-3</v>
       </c>
-      <c r="AE14" s="424">
+      <c r="AE14" s="423">
         <f t="shared" si="1"/>
         <v>-4</v>
       </c>
-      <c r="AF14" s="424">
+      <c r="AF14" s="423">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="AG14" s="411"/>
-      <c r="AH14" s="450"/>
-      <c r="AI14" s="406"/>
+      <c r="AG14" s="410"/>
+      <c r="AH14" s="449"/>
+      <c r="AI14" s="405"/>
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1">
-      <c r="A15" s="407"/>
+      <c r="A15" s="406"/>
       <c r="B15" s="1059"/>
       <c r="C15" s="1060"/>
       <c r="D15" s="1060"/>
@@ -41393,66 +41393,66 @@
       <c r="M15" s="1051"/>
       <c r="N15" s="1052"/>
       <c r="P15" s="79"/>
-      <c r="Q15" s="421"/>
-      <c r="R15" s="411"/>
-      <c r="S15" s="426">
+      <c r="Q15" s="420"/>
+      <c r="R15" s="410"/>
+      <c r="S15" s="425">
         <f>IF(INT($F$18*14/64 - S$12) = 0,$F$18, INT($F$18*14/64 - S$12))</f>
         <v>2</v>
       </c>
-      <c r="T15" s="426">
+      <c r="T15" s="425">
         <f t="shared" ref="T15:AF15" si="2">IF(INT($F$18*14/64 - T$12) = 0,$F$18, INT($F$18*14/64 - T$12))</f>
         <v>1</v>
       </c>
-      <c r="U15" s="426">
+      <c r="U15" s="425">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="V15" s="426">
+      <c r="V15" s="425">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="W15" s="426">
+      <c r="W15" s="425">
         <f t="shared" si="2"/>
         <v>-2</v>
       </c>
-      <c r="X15" s="426">
+      <c r="X15" s="425">
         <f t="shared" si="2"/>
         <v>-3</v>
       </c>
-      <c r="Y15" s="426">
+      <c r="Y15" s="425">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
-      <c r="Z15" s="426">
+      <c r="Z15" s="425">
         <f t="shared" si="2"/>
         <v>-5</v>
       </c>
-      <c r="AA15" s="426">
+      <c r="AA15" s="425">
         <f t="shared" si="2"/>
         <v>-6</v>
       </c>
-      <c r="AB15" s="426">
+      <c r="AB15" s="425">
         <f t="shared" si="2"/>
         <v>-7</v>
       </c>
-      <c r="AC15" s="426">
+      <c r="AC15" s="425">
         <f t="shared" si="2"/>
         <v>-8</v>
       </c>
-      <c r="AD15" s="426">
+      <c r="AD15" s="425">
         <f t="shared" si="2"/>
         <v>-9</v>
       </c>
-      <c r="AE15" s="426">
+      <c r="AE15" s="425">
         <f t="shared" si="2"/>
         <v>-10</v>
       </c>
-      <c r="AF15" s="444">
+      <c r="AF15" s="443">
         <f t="shared" si="2"/>
         <v>-11</v>
       </c>
-      <c r="AG15" s="411"/>
-      <c r="AH15" s="450"/>
+      <c r="AG15" s="410"/>
+      <c r="AH15" s="449"/>
       <c r="AI15" s="232"/>
     </row>
     <row r="16" spans="1:36" ht="15.75">
@@ -41480,30 +41480,30 @@
         <v>16</v>
       </c>
       <c r="N16" s="1042"/>
-      <c r="O16" s="366"/>
+      <c r="O16" s="365"/>
       <c r="P16" s="79"/>
-      <c r="Q16" s="421"/>
-      <c r="R16" s="411"/>
-      <c r="S16" s="416"/>
-      <c r="T16" s="411"/>
-      <c r="U16" s="411"/>
-      <c r="V16" s="411"/>
-      <c r="W16" s="417"/>
-      <c r="X16" s="411"/>
-      <c r="Y16" s="411"/>
-      <c r="Z16" s="411"/>
-      <c r="AA16" s="411"/>
-      <c r="AB16" s="411"/>
-      <c r="AC16" s="411"/>
-      <c r="AD16" s="411"/>
-      <c r="AE16" s="411"/>
-      <c r="AF16" s="443"/>
-      <c r="AG16" s="411"/>
-      <c r="AH16" s="450"/>
-      <c r="AI16" s="406"/>
+      <c r="Q16" s="420"/>
+      <c r="R16" s="410"/>
+      <c r="S16" s="415"/>
+      <c r="T16" s="410"/>
+      <c r="U16" s="410"/>
+      <c r="V16" s="410"/>
+      <c r="W16" s="416"/>
+      <c r="X16" s="410"/>
+      <c r="Y16" s="410"/>
+      <c r="Z16" s="410"/>
+      <c r="AA16" s="410"/>
+      <c r="AB16" s="410"/>
+      <c r="AC16" s="410"/>
+      <c r="AD16" s="410"/>
+      <c r="AE16" s="410"/>
+      <c r="AF16" s="442"/>
+      <c r="AG16" s="410"/>
+      <c r="AH16" s="449"/>
+      <c r="AI16" s="405"/>
     </row>
     <row r="17" spans="1:36" ht="15.75">
-      <c r="A17" s="407"/>
+      <c r="A17" s="406"/>
       <c r="B17" s="1037" t="s">
         <v>93</v>
       </c>
@@ -41529,66 +41529,66 @@
       <c r="N17" s="1042"/>
       <c r="O17" s="116"/>
       <c r="P17" s="79"/>
-      <c r="Q17" s="418"/>
-      <c r="R17" s="423"/>
-      <c r="S17" s="426">
+      <c r="Q17" s="417"/>
+      <c r="R17" s="422"/>
+      <c r="S17" s="425">
         <f>IF(INT($J$17*14/64 - S$12) = 0,$J$17, INT($J$17*14/64 - S$12))</f>
         <v>0</v>
       </c>
-      <c r="T17" s="426">
+      <c r="T17" s="425">
         <f t="shared" ref="T17:AF17" si="3">IF(INT($J$17*14/64 - T$12) = 0,$J$17, INT($J$17*14/64 - T$12))</f>
         <v>-1</v>
       </c>
-      <c r="U17" s="426">
+      <c r="U17" s="425">
         <f t="shared" si="3"/>
         <v>-2</v>
       </c>
-      <c r="V17" s="426">
+      <c r="V17" s="425">
         <f t="shared" si="3"/>
         <v>-3</v>
       </c>
-      <c r="W17" s="426">
+      <c r="W17" s="425">
         <f t="shared" si="3"/>
         <v>-4</v>
       </c>
-      <c r="X17" s="426">
+      <c r="X17" s="425">
         <f t="shared" si="3"/>
         <v>-5</v>
       </c>
-      <c r="Y17" s="426">
+      <c r="Y17" s="425">
         <f t="shared" si="3"/>
         <v>-6</v>
       </c>
-      <c r="Z17" s="426">
+      <c r="Z17" s="425">
         <f t="shared" si="3"/>
         <v>-7</v>
       </c>
-      <c r="AA17" s="426">
+      <c r="AA17" s="425">
         <f t="shared" si="3"/>
         <v>-8</v>
       </c>
-      <c r="AB17" s="426">
+      <c r="AB17" s="425">
         <f t="shared" si="3"/>
         <v>-9</v>
       </c>
-      <c r="AC17" s="426">
+      <c r="AC17" s="425">
         <f t="shared" si="3"/>
         <v>-10</v>
       </c>
-      <c r="AD17" s="426">
+      <c r="AD17" s="425">
         <f t="shared" si="3"/>
         <v>-11</v>
       </c>
-      <c r="AE17" s="426">
+      <c r="AE17" s="425">
         <f t="shared" si="3"/>
         <v>-12</v>
       </c>
-      <c r="AF17" s="444">
+      <c r="AF17" s="443">
         <f t="shared" si="3"/>
         <v>-13</v>
       </c>
-      <c r="AG17" s="411"/>
-      <c r="AH17" s="450"/>
+      <c r="AG17" s="410"/>
+      <c r="AH17" s="449"/>
       <c r="AI17" s="232"/>
     </row>
     <row r="18" spans="1:36" ht="16.5" thickBot="1">
@@ -41618,147 +41618,147 @@
       <c r="N18" s="1045"/>
       <c r="O18" s="155"/>
       <c r="P18" s="81"/>
-      <c r="Q18" s="421"/>
-      <c r="R18" s="422" t="s">
+      <c r="Q18" s="420"/>
+      <c r="R18" s="421" t="s">
         <v>93</v>
       </c>
-      <c r="S18" s="424">
+      <c r="S18" s="423">
         <f>IF(INT($H$17*14/64 - S$12) = 0,$H$17, INT($H$17*14/64 - S$12))</f>
         <v>2</v>
       </c>
-      <c r="T18" s="424">
+      <c r="T18" s="423">
         <f t="shared" ref="T18:AF18" si="4">IF(INT($H$17*14/64 - T$12) = 0,$H$17, INT($H$17*14/64 - T$12))</f>
         <v>1</v>
       </c>
-      <c r="U18" s="424">
+      <c r="U18" s="423">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="V18" s="424">
+      <c r="V18" s="423">
         <f t="shared" si="4"/>
         <v>-1</v>
       </c>
-      <c r="W18" s="424">
+      <c r="W18" s="423">
         <f t="shared" si="4"/>
         <v>-2</v>
       </c>
-      <c r="X18" s="424">
+      <c r="X18" s="423">
         <f t="shared" si="4"/>
         <v>-3</v>
       </c>
-      <c r="Y18" s="424">
+      <c r="Y18" s="423">
         <f t="shared" si="4"/>
         <v>-4</v>
       </c>
-      <c r="Z18" s="424">
+      <c r="Z18" s="423">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
-      <c r="AA18" s="424">
+      <c r="AA18" s="423">
         <f t="shared" si="4"/>
         <v>-6</v>
       </c>
-      <c r="AB18" s="424">
+      <c r="AB18" s="423">
         <f t="shared" si="4"/>
         <v>-7</v>
       </c>
-      <c r="AC18" s="424">
+      <c r="AC18" s="423">
         <f t="shared" si="4"/>
         <v>-8</v>
       </c>
-      <c r="AD18" s="424">
+      <c r="AD18" s="423">
         <f t="shared" si="4"/>
         <v>-9</v>
       </c>
-      <c r="AE18" s="424">
+      <c r="AE18" s="423">
         <f t="shared" si="4"/>
         <v>-10</v>
       </c>
-      <c r="AF18" s="424">
+      <c r="AF18" s="423">
         <f t="shared" si="4"/>
         <v>-11</v>
       </c>
-      <c r="AG18" s="411"/>
-      <c r="AH18" s="450"/>
+      <c r="AG18" s="410"/>
+      <c r="AH18" s="449"/>
       <c r="AI18" s="232"/>
     </row>
     <row r="19" spans="1:36" ht="14.25" customHeight="1">
       <c r="A19" s="233"/>
       <c r="B19" s="125"/>
-      <c r="C19" s="364"/>
-      <c r="D19" s="364"/>
-      <c r="E19" s="364"/>
+      <c r="C19" s="363"/>
+      <c r="D19" s="363"/>
+      <c r="E19" s="363"/>
       <c r="F19" s="107"/>
       <c r="G19" s="107"/>
-      <c r="I19" s="364"/>
+      <c r="I19" s="363"/>
       <c r="J19" s="107"/>
-      <c r="K19" s="364"/>
-      <c r="L19" s="364"/>
+      <c r="K19" s="363"/>
+      <c r="L19" s="363"/>
       <c r="M19" s="107"/>
       <c r="N19" s="124"/>
       <c r="O19" s="82"/>
       <c r="P19" s="79"/>
-      <c r="Q19" s="421"/>
+      <c r="Q19" s="420"/>
       <c r="R19" s="10"/>
-      <c r="S19" s="426">
+      <c r="S19" s="425">
         <f>IF(INT($F$17*14/64 - S$12) = 0,$F$17, INT($F$17*14/64 - S$12))</f>
         <v>0</v>
       </c>
-      <c r="T19" s="426">
+      <c r="T19" s="425">
         <f t="shared" ref="T19:AF19" si="5">IF(INT($F$17*14/64 - T$12) = 0,$F$17, INT($F$17*14/64 - T$12))</f>
         <v>-1</v>
       </c>
-      <c r="U19" s="426">
+      <c r="U19" s="425">
         <f t="shared" si="5"/>
         <v>-2</v>
       </c>
-      <c r="V19" s="426">
+      <c r="V19" s="425">
         <f t="shared" si="5"/>
         <v>-3</v>
       </c>
-      <c r="W19" s="426">
+      <c r="W19" s="425">
         <f t="shared" si="5"/>
         <v>-4</v>
       </c>
-      <c r="X19" s="426">
+      <c r="X19" s="425">
         <f t="shared" si="5"/>
         <v>-5</v>
       </c>
-      <c r="Y19" s="426">
+      <c r="Y19" s="425">
         <f t="shared" si="5"/>
         <v>-6</v>
       </c>
-      <c r="Z19" s="426">
+      <c r="Z19" s="425">
         <f t="shared" si="5"/>
         <v>-7</v>
       </c>
-      <c r="AA19" s="426">
+      <c r="AA19" s="425">
         <f t="shared" si="5"/>
         <v>-8</v>
       </c>
-      <c r="AB19" s="426">
+      <c r="AB19" s="425">
         <f t="shared" si="5"/>
         <v>-9</v>
       </c>
-      <c r="AC19" s="426">
+      <c r="AC19" s="425">
         <f t="shared" si="5"/>
         <v>-10</v>
       </c>
-      <c r="AD19" s="426">
+      <c r="AD19" s="425">
         <f t="shared" si="5"/>
         <v>-11</v>
       </c>
-      <c r="AE19" s="426">
+      <c r="AE19" s="425">
         <f t="shared" si="5"/>
         <v>-12</v>
       </c>
-      <c r="AF19" s="444">
+      <c r="AF19" s="443">
         <f t="shared" si="5"/>
         <v>-13</v>
       </c>
-      <c r="AG19" s="411"/>
-      <c r="AH19" s="450"/>
-      <c r="AI19" s="406"/>
+      <c r="AG19" s="410"/>
+      <c r="AH19" s="449"/>
+      <c r="AI19" s="405"/>
     </row>
     <row r="20" spans="1:36">
       <c r="A20" s="230"/>
@@ -41777,25 +41777,25 @@
       <c r="N20" s="82"/>
       <c r="O20" s="80"/>
       <c r="P20" s="79"/>
-      <c r="Q20" s="418"/>
+      <c r="Q20" s="417"/>
       <c r="R20" s="10"/>
-      <c r="S20" s="411"/>
-      <c r="T20" s="411"/>
-      <c r="U20" s="411"/>
-      <c r="V20" s="411"/>
-      <c r="W20" s="411"/>
-      <c r="X20" s="411"/>
-      <c r="Y20" s="411"/>
-      <c r="Z20" s="411"/>
-      <c r="AA20" s="411"/>
-      <c r="AB20" s="411"/>
-      <c r="AC20" s="411"/>
-      <c r="AD20" s="411"/>
-      <c r="AE20" s="411"/>
-      <c r="AF20" s="443"/>
-      <c r="AG20" s="411"/>
-      <c r="AH20" s="450"/>
-      <c r="AI20" s="408"/>
+      <c r="S20" s="410"/>
+      <c r="T20" s="410"/>
+      <c r="U20" s="410"/>
+      <c r="V20" s="410"/>
+      <c r="W20" s="410"/>
+      <c r="X20" s="410"/>
+      <c r="Y20" s="410"/>
+      <c r="Z20" s="410"/>
+      <c r="AA20" s="410"/>
+      <c r="AB20" s="410"/>
+      <c r="AC20" s="410"/>
+      <c r="AD20" s="410"/>
+      <c r="AE20" s="410"/>
+      <c r="AF20" s="442"/>
+      <c r="AG20" s="410"/>
+      <c r="AH20" s="449"/>
+      <c r="AI20" s="407"/>
     </row>
     <row r="21" spans="1:36">
       <c r="A21" s="136"/>
@@ -41814,67 +41814,67 @@
       <c r="N21" s="82"/>
       <c r="O21" s="83"/>
       <c r="P21" s="103"/>
-      <c r="Q21" s="420"/>
-      <c r="R21" s="410"/>
-      <c r="S21" s="425">
+      <c r="Q21" s="419"/>
+      <c r="R21" s="409"/>
+      <c r="S21" s="424">
         <f>IF(INT($J$16*14/64 - S$12) = 0,$J$16, INT($J$16*14/64 - S$12))</f>
         <v>0</v>
       </c>
-      <c r="T21" s="425">
+      <c r="T21" s="424">
         <f t="shared" ref="T21:AF21" si="6">IF(INT($J$16*14/64 - T$12) = 0,$J$16, INT($J$16*14/64 - T$12))</f>
         <v>-1</v>
       </c>
-      <c r="U21" s="425">
+      <c r="U21" s="424">
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="V21" s="425">
+      <c r="V21" s="424">
         <f t="shared" si="6"/>
         <v>-3</v>
       </c>
-      <c r="W21" s="425">
+      <c r="W21" s="424">
         <f t="shared" si="6"/>
         <v>-4</v>
       </c>
-      <c r="X21" s="425">
+      <c r="X21" s="424">
         <f t="shared" si="6"/>
         <v>-5</v>
       </c>
-      <c r="Y21" s="425">
+      <c r="Y21" s="424">
         <f t="shared" si="6"/>
         <v>-6</v>
       </c>
-      <c r="Z21" s="425">
+      <c r="Z21" s="424">
         <f t="shared" si="6"/>
         <v>-7</v>
       </c>
-      <c r="AA21" s="425">
+      <c r="AA21" s="424">
         <f t="shared" si="6"/>
         <v>-8</v>
       </c>
-      <c r="AB21" s="425">
+      <c r="AB21" s="424">
         <f t="shared" si="6"/>
         <v>-9</v>
       </c>
-      <c r="AC21" s="425">
+      <c r="AC21" s="424">
         <f t="shared" si="6"/>
         <v>-10</v>
       </c>
-      <c r="AD21" s="425">
+      <c r="AD21" s="424">
         <f t="shared" si="6"/>
         <v>-11</v>
       </c>
-      <c r="AE21" s="425">
+      <c r="AE21" s="424">
         <f t="shared" si="6"/>
         <v>-12</v>
       </c>
-      <c r="AF21" s="446">
+      <c r="AF21" s="445">
         <f t="shared" si="6"/>
         <v>-13</v>
       </c>
-      <c r="AG21" s="411"/>
-      <c r="AH21" s="450"/>
-      <c r="AI21" s="351"/>
+      <c r="AG21" s="410"/>
+      <c r="AH21" s="449"/>
+      <c r="AI21" s="350"/>
     </row>
     <row r="22" spans="1:36" ht="15.75">
       <c r="A22" s="303"/>
@@ -41893,68 +41893,68 @@
       <c r="N22" s="82"/>
       <c r="O22" s="80"/>
       <c r="P22" s="79"/>
-      <c r="Q22" s="421"/>
-      <c r="R22" s="422" t="s">
+      <c r="Q22" s="420"/>
+      <c r="R22" s="421" t="s">
         <v>92</v>
       </c>
-      <c r="S22" s="424">
+      <c r="S22" s="423">
         <f>IF(INT($H$16*14/64 - S$12) = 0,$H$16, INT($H$16*14/64 - S$12))</f>
         <v>3</v>
       </c>
-      <c r="T22" s="424">
+      <c r="T22" s="423">
         <f t="shared" ref="T22:AF22" si="7">IF(INT($H$16*14/64 - T$12) = 0,$H$16, INT($H$16*14/64 - T$12))</f>
         <v>2</v>
       </c>
-      <c r="U22" s="424">
+      <c r="U22" s="423">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="V22" s="424">
+      <c r="V22" s="423">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="W22" s="424">
+      <c r="W22" s="423">
         <f t="shared" si="7"/>
         <v>-1</v>
       </c>
-      <c r="X22" s="424">
+      <c r="X22" s="423">
         <f t="shared" si="7"/>
         <v>-2</v>
       </c>
-      <c r="Y22" s="424">
+      <c r="Y22" s="423">
         <f t="shared" si="7"/>
         <v>-3</v>
       </c>
-      <c r="Z22" s="424">
+      <c r="Z22" s="423">
         <f t="shared" si="7"/>
         <v>-4</v>
       </c>
-      <c r="AA22" s="424">
+      <c r="AA22" s="423">
         <f t="shared" si="7"/>
         <v>-5</v>
       </c>
-      <c r="AB22" s="424">
+      <c r="AB22" s="423">
         <f t="shared" si="7"/>
         <v>-6</v>
       </c>
-      <c r="AC22" s="424">
+      <c r="AC22" s="423">
         <f t="shared" si="7"/>
         <v>-7</v>
       </c>
-      <c r="AD22" s="424">
+      <c r="AD22" s="423">
         <f t="shared" si="7"/>
         <v>-8</v>
       </c>
-      <c r="AE22" s="424">
+      <c r="AE22" s="423">
         <f t="shared" si="7"/>
         <v>-9</v>
       </c>
-      <c r="AF22" s="424">
+      <c r="AF22" s="423">
         <f t="shared" si="7"/>
         <v>-10</v>
       </c>
-      <c r="AG22" s="411"/>
-      <c r="AH22" s="450"/>
+      <c r="AG22" s="410"/>
+      <c r="AH22" s="449"/>
       <c r="AI22" s="232"/>
     </row>
     <row r="23" spans="1:36" ht="15.75">
@@ -41974,66 +41974,66 @@
       <c r="N23" s="82"/>
       <c r="O23" s="80"/>
       <c r="P23" s="79"/>
-      <c r="Q23" s="421"/>
-      <c r="R23" s="411"/>
-      <c r="S23" s="426">
+      <c r="Q23" s="420"/>
+      <c r="R23" s="410"/>
+      <c r="S23" s="425">
         <f>IF(INT($F$16*14/64 - S$12) = 0,$F$16, INT($F$16*14/64 - S$12))</f>
         <v>2</v>
       </c>
-      <c r="T23" s="426">
+      <c r="T23" s="425">
         <f t="shared" ref="T23:AF23" si="8">IF(INT($F$16*14/64 - T$12) = 0,$F$16, INT($F$16*14/64 - T$12))</f>
         <v>-1</v>
       </c>
-      <c r="U23" s="426">
+      <c r="U23" s="425">
         <f t="shared" si="8"/>
         <v>-2</v>
       </c>
-      <c r="V23" s="426">
+      <c r="V23" s="425">
         <f t="shared" si="8"/>
         <v>-3</v>
       </c>
-      <c r="W23" s="426">
+      <c r="W23" s="425">
         <f t="shared" si="8"/>
         <v>-4</v>
       </c>
-      <c r="X23" s="426">
+      <c r="X23" s="425">
         <f t="shared" si="8"/>
         <v>-5</v>
       </c>
-      <c r="Y23" s="426">
+      <c r="Y23" s="425">
         <f t="shared" si="8"/>
         <v>-6</v>
       </c>
-      <c r="Z23" s="426">
+      <c r="Z23" s="425">
         <f t="shared" si="8"/>
         <v>-7</v>
       </c>
-      <c r="AA23" s="426">
+      <c r="AA23" s="425">
         <f t="shared" si="8"/>
         <v>-8</v>
       </c>
-      <c r="AB23" s="426">
+      <c r="AB23" s="425">
         <f t="shared" si="8"/>
         <v>-9</v>
       </c>
-      <c r="AC23" s="426">
+      <c r="AC23" s="425">
         <f t="shared" si="8"/>
         <v>-10</v>
       </c>
-      <c r="AD23" s="426">
+      <c r="AD23" s="425">
         <f t="shared" si="8"/>
         <v>-11</v>
       </c>
-      <c r="AE23" s="426">
+      <c r="AE23" s="425">
         <f t="shared" si="8"/>
         <v>-12</v>
       </c>
-      <c r="AF23" s="426">
+      <c r="AF23" s="425">
         <f t="shared" si="8"/>
         <v>-13</v>
       </c>
-      <c r="AG23" s="411"/>
-      <c r="AH23" s="450"/>
+      <c r="AG23" s="410"/>
+      <c r="AH23" s="449"/>
       <c r="AI23" s="232"/>
     </row>
     <row r="24" spans="1:36">
@@ -42053,25 +42053,25 @@
       <c r="N24" s="82"/>
       <c r="O24" s="80"/>
       <c r="P24" s="103"/>
-      <c r="Q24" s="421"/>
-      <c r="R24" s="411"/>
-      <c r="S24" s="448"/>
-      <c r="T24" s="448"/>
-      <c r="U24" s="448"/>
-      <c r="V24" s="448"/>
-      <c r="W24" s="448"/>
-      <c r="X24" s="448"/>
-      <c r="Y24" s="448"/>
-      <c r="Z24" s="448"/>
-      <c r="AA24" s="448"/>
-      <c r="AB24" s="448"/>
-      <c r="AC24" s="448"/>
-      <c r="AD24" s="448"/>
-      <c r="AE24" s="448"/>
-      <c r="AF24" s="416"/>
-      <c r="AG24" s="411"/>
-      <c r="AH24" s="450"/>
-      <c r="AI24" s="406"/>
+      <c r="Q24" s="420"/>
+      <c r="R24" s="410"/>
+      <c r="S24" s="447"/>
+      <c r="T24" s="447"/>
+      <c r="U24" s="447"/>
+      <c r="V24" s="447"/>
+      <c r="W24" s="447"/>
+      <c r="X24" s="447"/>
+      <c r="Y24" s="447"/>
+      <c r="Z24" s="447"/>
+      <c r="AA24" s="447"/>
+      <c r="AB24" s="447"/>
+      <c r="AC24" s="447"/>
+      <c r="AD24" s="447"/>
+      <c r="AE24" s="447"/>
+      <c r="AF24" s="415"/>
+      <c r="AG24" s="410"/>
+      <c r="AH24" s="449"/>
+      <c r="AI24" s="405"/>
     </row>
     <row r="25" spans="1:36" ht="15.75" thickBot="1">
       <c r="A25" s="136"/>
@@ -42090,25 +42090,25 @@
       <c r="N25" s="82"/>
       <c r="O25" s="105"/>
       <c r="P25" s="103"/>
-      <c r="Q25" s="442"/>
-      <c r="R25" s="419"/>
-      <c r="S25" s="419"/>
-      <c r="T25" s="419"/>
-      <c r="U25" s="419"/>
-      <c r="V25" s="419"/>
-      <c r="W25" s="419"/>
-      <c r="X25" s="419"/>
-      <c r="Y25" s="419"/>
-      <c r="Z25" s="419"/>
-      <c r="AA25" s="419"/>
-      <c r="AB25" s="419"/>
-      <c r="AC25" s="419"/>
-      <c r="AD25" s="419"/>
-      <c r="AE25" s="419"/>
-      <c r="AF25" s="447"/>
-      <c r="AG25" s="451"/>
-      <c r="AH25" s="452"/>
-      <c r="AI25" s="406"/>
+      <c r="Q25" s="441"/>
+      <c r="R25" s="418"/>
+      <c r="S25" s="418"/>
+      <c r="T25" s="418"/>
+      <c r="U25" s="418"/>
+      <c r="V25" s="418"/>
+      <c r="W25" s="418"/>
+      <c r="X25" s="418"/>
+      <c r="Y25" s="418"/>
+      <c r="Z25" s="418"/>
+      <c r="AA25" s="418"/>
+      <c r="AB25" s="418"/>
+      <c r="AC25" s="418"/>
+      <c r="AD25" s="418"/>
+      <c r="AE25" s="418"/>
+      <c r="AF25" s="446"/>
+      <c r="AG25" s="450"/>
+      <c r="AH25" s="451"/>
+      <c r="AI25" s="405"/>
     </row>
     <row r="26" spans="1:36" ht="11.25" customHeight="1" thickBot="1">
       <c r="A26" s="136"/>
@@ -42127,12 +42127,12 @@
       <c r="N26" s="82"/>
       <c r="O26" s="105"/>
       <c r="P26" s="82"/>
-      <c r="Q26" s="397"/>
-      <c r="S26" s="397"/>
-      <c r="T26" s="397"/>
-      <c r="U26" s="397"/>
-      <c r="V26" s="397"/>
-      <c r="W26" s="413"/>
+      <c r="Q26" s="396"/>
+      <c r="S26" s="396"/>
+      <c r="T26" s="396"/>
+      <c r="U26" s="396"/>
+      <c r="V26" s="396"/>
+      <c r="W26" s="412"/>
       <c r="X26" s="104"/>
       <c r="Z26" s="81"/>
       <c r="AA26" s="81"/>
@@ -42160,7 +42160,7 @@
       <c r="L27" s="82"/>
       <c r="M27" s="82"/>
       <c r="N27" s="82"/>
-      <c r="P27" s="392"/>
+      <c r="P27" s="391"/>
       <c r="Q27" s="980" t="s">
         <v>157</v>
       </c>
@@ -42170,8 +42170,8 @@
       <c r="U27" s="981"/>
       <c r="V27" s="981"/>
       <c r="W27" s="982"/>
-      <c r="X27" s="396"/>
-      <c r="Y27" s="388"/>
+      <c r="X27" s="395"/>
+      <c r="Y27" s="387"/>
       <c r="Z27" s="227"/>
       <c r="AA27" s="227"/>
       <c r="AB27" s="227"/>
@@ -42200,13 +42200,13 @@
       <c r="N28" s="82"/>
       <c r="O28" s="80"/>
       <c r="P28" s="103"/>
-      <c r="Q28" s="394"/>
-      <c r="R28" s="395"/>
-      <c r="S28" s="393"/>
-      <c r="T28" s="394"/>
+      <c r="Q28" s="393"/>
+      <c r="R28" s="394"/>
+      <c r="S28" s="392"/>
+      <c r="T28" s="393"/>
       <c r="U28" s="226"/>
-      <c r="V28" s="394"/>
-      <c r="W28" s="394"/>
+      <c r="V28" s="393"/>
+      <c r="W28" s="393"/>
       <c r="X28" s="227"/>
       <c r="Y28" s="227"/>
       <c r="Z28" s="227"/>
@@ -42219,7 +42219,7 @@
       <c r="AG28" s="82"/>
       <c r="AH28" s="82"/>
       <c r="AI28" s="165"/>
-      <c r="AJ28" s="401"/>
+      <c r="AJ28" s="400"/>
     </row>
     <row r="29" spans="1:36" ht="15.75" thickBot="1">
       <c r="A29" s="284"/>
@@ -42238,7 +42238,7 @@
       <c r="N29" s="82"/>
       <c r="O29" s="80"/>
       <c r="P29" s="82"/>
-      <c r="Q29" s="389"/>
+      <c r="Q29" s="388"/>
       <c r="R29" s="193"/>
       <c r="S29" s="193"/>
       <c r="T29" s="983" t="s">
@@ -42246,15 +42246,15 @@
       </c>
       <c r="U29" s="984"/>
       <c r="V29" s="985"/>
-      <c r="W29" s="402"/>
-      <c r="X29" s="389"/>
+      <c r="W29" s="401"/>
+      <c r="X29" s="388"/>
       <c r="Y29" s="193"/>
-      <c r="Z29" s="389"/>
+      <c r="Z29" s="388"/>
       <c r="AA29" s="226"/>
       <c r="AB29" s="193"/>
-      <c r="AC29" s="389"/>
+      <c r="AC29" s="388"/>
       <c r="AD29" s="226"/>
-      <c r="AE29" s="389"/>
+      <c r="AE29" s="388"/>
       <c r="AF29" s="104"/>
       <c r="AG29" s="104"/>
       <c r="AH29" s="82"/>
@@ -42299,7 +42299,7 @@
       </c>
       <c r="AD30" s="912"/>
       <c r="AE30" s="968"/>
-      <c r="AF30" s="390"/>
+      <c r="AF30" s="389"/>
       <c r="AG30" s="227"/>
       <c r="AH30" s="82"/>
       <c r="AI30" s="165"/>
@@ -42336,7 +42336,7 @@
       <c r="AC31" s="969"/>
       <c r="AD31" s="970"/>
       <c r="AE31" s="971"/>
-      <c r="AF31" s="391"/>
+      <c r="AF31" s="390"/>
       <c r="AG31" s="82"/>
       <c r="AH31" s="82"/>
       <c r="AI31" s="165"/>
@@ -42465,7 +42465,7 @@
       <c r="AI34" s="165"/>
     </row>
     <row r="35" spans="1:35" ht="22.5" customHeight="1">
-      <c r="A35" s="409"/>
+      <c r="A35" s="408"/>
       <c r="B35" s="910" t="s">
         <v>94</v>
       </c>
@@ -42512,16 +42512,16 @@
       <c r="AI35" s="165"/>
     </row>
     <row r="36" spans="1:35">
-      <c r="A36" s="400"/>
-      <c r="C36" s="403"/>
-      <c r="E36" s="403"/>
-      <c r="F36" s="403"/>
-      <c r="H36" s="403"/>
-      <c r="I36" s="403"/>
-      <c r="K36" s="403"/>
-      <c r="L36" s="404"/>
-      <c r="M36" s="404"/>
-      <c r="N36" s="403"/>
+      <c r="A36" s="399"/>
+      <c r="C36" s="402"/>
+      <c r="E36" s="402"/>
+      <c r="F36" s="402"/>
+      <c r="H36" s="402"/>
+      <c r="I36" s="402"/>
+      <c r="K36" s="402"/>
+      <c r="L36" s="403"/>
+      <c r="M36" s="403"/>
+      <c r="N36" s="402"/>
       <c r="O36" s="90"/>
       <c r="Q36" s="935"/>
       <c r="R36" s="936"/>
@@ -43514,80 +43514,80 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="343"/>
-      <c r="B3" s="455"/>
-      <c r="C3" s="344"/>
-      <c r="D3" s="344"/>
+      <c r="A3" s="342"/>
+      <c r="B3" s="454"/>
+      <c r="C3" s="343"/>
+      <c r="D3" s="343"/>
     </row>
     <row r="4" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A4" s="343"/>
-      <c r="B4" s="455"/>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
+      <c r="A4" s="342"/>
+      <c r="B4" s="454"/>
+      <c r="C4" s="343"/>
+      <c r="D4" s="343"/>
     </row>
     <row r="5" spans="1:4" ht="26.25" customHeight="1">
-      <c r="A5" s="343"/>
-      <c r="B5" s="455"/>
-      <c r="C5" s="344"/>
-      <c r="D5" s="344"/>
+      <c r="A5" s="342"/>
+      <c r="B5" s="454"/>
+      <c r="C5" s="343"/>
+      <c r="D5" s="343"/>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
-      <c r="A6" s="343"/>
-      <c r="B6" s="455"/>
-      <c r="C6" s="344"/>
-      <c r="D6" s="344"/>
+      <c r="A6" s="342"/>
+      <c r="B6" s="454"/>
+      <c r="C6" s="343"/>
+      <c r="D6" s="343"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A7" s="343"/>
-      <c r="B7" s="455"/>
-      <c r="C7" s="344"/>
-      <c r="D7" s="344"/>
+      <c r="A7" s="342"/>
+      <c r="B7" s="454"/>
+      <c r="C7" s="343"/>
+      <c r="D7" s="343"/>
     </row>
     <row r="8" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A8" s="343"/>
-      <c r="B8" s="455"/>
-      <c r="C8" s="344"/>
-      <c r="D8" s="344"/>
+      <c r="A8" s="342"/>
+      <c r="B8" s="454"/>
+      <c r="C8" s="343"/>
+      <c r="D8" s="343"/>
     </row>
     <row r="9" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A9" s="343"/>
-      <c r="B9" s="455"/>
-      <c r="C9" s="344"/>
-      <c r="D9" s="344"/>
+      <c r="A9" s="342"/>
+      <c r="B9" s="454"/>
+      <c r="C9" s="343"/>
+      <c r="D9" s="343"/>
     </row>
     <row r="10" spans="1:4" ht="33.75" customHeight="1">
-      <c r="A10" s="343"/>
-      <c r="B10" s="342"/>
-      <c r="C10" s="344"/>
-      <c r="D10" s="344"/>
+      <c r="A10" s="342"/>
+      <c r="B10" s="341"/>
+      <c r="C10" s="343"/>
+      <c r="D10" s="343"/>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A11" s="343"/>
-      <c r="B11" s="455"/>
-      <c r="C11" s="344"/>
-      <c r="D11" s="344"/>
+      <c r="A11" s="342"/>
+      <c r="B11" s="454"/>
+      <c r="C11" s="343"/>
+      <c r="D11" s="343"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="343"/>
-      <c r="B12" s="455"/>
-      <c r="C12" s="344"/>
-      <c r="D12" s="344"/>
+      <c r="A12" s="342"/>
+      <c r="B12" s="454"/>
+      <c r="C12" s="343"/>
+      <c r="D12" s="343"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="343"/>
-      <c r="B13" s="455"/>
-      <c r="C13" s="344"/>
-      <c r="D13" s="344"/>
+      <c r="A13" s="342"/>
+      <c r="B13" s="454"/>
+      <c r="C13" s="343"/>
+      <c r="D13" s="343"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="453"/>
-      <c r="B14" s="457"/>
-      <c r="C14" s="454"/>
-      <c r="D14" s="454"/>
+      <c r="A14" s="452"/>
+      <c r="B14" s="456"/>
+      <c r="C14" s="453"/>
+      <c r="D14" s="453"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="458"/>
-      <c r="B15" s="456"/>
+      <c r="A15" s="457"/>
+      <c r="B15" s="455"/>
       <c r="C15" s="71"/>
       <c r="D15" s="71"/>
     </row>
@@ -43653,25 +43653,25 @@
     </row>
     <row r="2" spans="1:19" ht="37.35" customHeight="1">
       <c r="A2" s="23"/>
-      <c r="B2" s="379"/>
-      <c r="C2" s="379"/>
-      <c r="D2" s="379"/>
-      <c r="E2" s="379"/>
-      <c r="F2" s="379"/>
-      <c r="G2" s="379"/>
-      <c r="H2" s="379"/>
-      <c r="I2" s="379"/>
-      <c r="J2" s="594" t="s">
+      <c r="B2" s="378"/>
+      <c r="C2" s="378"/>
+      <c r="D2" s="378"/>
+      <c r="E2" s="378"/>
+      <c r="F2" s="378"/>
+      <c r="G2" s="378"/>
+      <c r="H2" s="378"/>
+      <c r="I2" s="378"/>
+      <c r="J2" s="593" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="594"/>
-      <c r="L2" s="594"/>
-      <c r="M2" s="594"/>
-      <c r="N2" s="594"/>
-      <c r="O2" s="594"/>
-      <c r="P2" s="379"/>
-      <c r="Q2" s="379"/>
-      <c r="R2" s="379"/>
+      <c r="K2" s="593"/>
+      <c r="L2" s="593"/>
+      <c r="M2" s="593"/>
+      <c r="N2" s="593"/>
+      <c r="O2" s="593"/>
+      <c r="P2" s="378"/>
+      <c r="Q2" s="378"/>
+      <c r="R2" s="378"/>
       <c r="S2" s="22"/>
     </row>
     <row r="3" spans="1:19" ht="7.35" customHeight="1">
@@ -43697,54 +43697,54 @@
     </row>
     <row r="4" spans="1:19" ht="33" customHeight="1">
       <c r="A4" s="23"/>
-      <c r="B4" s="380" t="s">
+      <c r="B4" s="379" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="380"/>
-      <c r="D4" s="380"/>
-      <c r="E4" s="380"/>
-      <c r="F4" s="380"/>
-      <c r="G4" s="380"/>
-      <c r="H4" s="380"/>
-      <c r="I4" s="380" t="s">
+      <c r="C4" s="379"/>
+      <c r="D4" s="379"/>
+      <c r="E4" s="379"/>
+      <c r="F4" s="379"/>
+      <c r="G4" s="379"/>
+      <c r="H4" s="379"/>
+      <c r="I4" s="379" t="s">
         <v>133</v>
       </c>
-      <c r="J4" s="593" t="s">
+      <c r="J4" s="592" t="s">
         <v>134</v>
       </c>
-      <c r="K4" s="593"/>
-      <c r="L4" s="593"/>
-      <c r="M4" s="593"/>
-      <c r="N4" s="593"/>
-      <c r="O4" s="593"/>
-      <c r="P4" s="381"/>
-      <c r="Q4" s="381"/>
-      <c r="R4" s="382"/>
+      <c r="K4" s="592"/>
+      <c r="L4" s="592"/>
+      <c r="M4" s="592"/>
+      <c r="N4" s="592"/>
+      <c r="O4" s="592"/>
+      <c r="P4" s="380"/>
+      <c r="Q4" s="380"/>
+      <c r="R4" s="381"/>
       <c r="S4" s="22"/>
     </row>
     <row r="5" spans="1:19" ht="29.25" customHeight="1">
       <c r="A5" s="23"/>
-      <c r="B5" s="383"/>
-      <c r="C5" s="383"/>
-      <c r="D5" s="383"/>
-      <c r="E5" s="383"/>
-      <c r="F5" s="383"/>
-      <c r="G5" s="383"/>
-      <c r="H5" s="383"/>
-      <c r="I5" s="384"/>
-      <c r="J5" s="604" t="s">
+      <c r="B5" s="382"/>
+      <c r="C5" s="382"/>
+      <c r="D5" s="382"/>
+      <c r="E5" s="382"/>
+      <c r="F5" s="382"/>
+      <c r="G5" s="382"/>
+      <c r="H5" s="382"/>
+      <c r="I5" s="383"/>
+      <c r="J5" s="603" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="604"/>
-      <c r="L5" s="604"/>
-      <c r="M5" s="604"/>
-      <c r="N5" s="601" t="s">
+      <c r="K5" s="603"/>
+      <c r="L5" s="603"/>
+      <c r="M5" s="603"/>
+      <c r="N5" s="600" t="s">
         <v>164</v>
       </c>
-      <c r="O5" s="601"/>
-      <c r="P5" s="601"/>
-      <c r="Q5" s="385"/>
-      <c r="R5" s="385"/>
+      <c r="O5" s="600"/>
+      <c r="P5" s="600"/>
+      <c r="Q5" s="384"/>
+      <c r="R5" s="384"/>
       <c r="S5" s="22"/>
     </row>
     <row r="6" spans="1:19" ht="23.25" customHeight="1" thickBot="1">
@@ -43773,12 +43773,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="23"/>
-      <c r="C8" s="605" t="str">
+      <c r="C8" s="604" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO ABRIL - 2025</v>
       </c>
-      <c r="D8" s="606"/>
-      <c r="E8" s="607"/>
+      <c r="D8" s="605"/>
+      <c r="E8" s="606"/>
       <c r="G8" s="56" t="s">
         <v>1</v>
       </c>
@@ -43821,11 +43821,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="C10" s="608" t="s">
+      <c r="C10" s="607" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="608"/>
-      <c r="E10" s="608"/>
+      <c r="D10" s="607"/>
+      <c r="E10" s="607"/>
       <c r="G10" s="76" t="s">
         <v>8</v>
       </c>
@@ -43850,11 +43850,11 @@
       <c r="C11" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="595">
+      <c r="D11" s="594">
         <f>R13</f>
         <v>0</v>
       </c>
-      <c r="E11" s="595"/>
+      <c r="E11" s="594"/>
       <c r="G11" s="48" t="s">
         <v>9</v>
       </c>
@@ -43879,11 +43879,11 @@
       <c r="C12" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="595">
+      <c r="D12" s="594">
         <f>R12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="595"/>
+      <c r="E12" s="594"/>
       <c r="G12" s="48" t="s">
         <v>7</v>
       </c>
@@ -43908,11 +43908,11 @@
       <c r="C13" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="595">
+      <c r="D13" s="594">
         <f>R10</f>
         <v>0</v>
       </c>
-      <c r="E13" s="595"/>
+      <c r="E13" s="594"/>
       <c r="G13" s="77" t="s">
         <v>6</v>
       </c>
@@ -43937,11 +43937,11 @@
       <c r="C14" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="595">
+      <c r="D14" s="594">
         <f>R11</f>
         <v>0</v>
       </c>
-      <c r="E14" s="595"/>
+      <c r="E14" s="594"/>
       <c r="G14" s="54" t="s">
         <v>10</v>
       </c>
@@ -43975,11 +43975,11 @@
       <c r="C15" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="603">
+      <c r="D15" s="602">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="603"/>
+      <c r="E15" s="602"/>
       <c r="H15" s="35"/>
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
@@ -44022,11 +44022,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="C24" s="596" t="s">
+      <c r="C24" s="595" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="597"/>
-      <c r="E24" s="598"/>
+      <c r="D24" s="596"/>
+      <c r="E24" s="597"/>
       <c r="S24" s="22"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -44034,11 +44034,11 @@
       <c r="C25" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="599">
+      <c r="D25" s="598">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="600"/>
+      <c r="E25" s="599"/>
       <c r="S25" s="22"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -44046,11 +44046,11 @@
       <c r="C26" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="599">
+      <c r="D26" s="598">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="600"/>
+      <c r="E26" s="599"/>
       <c r="S26" s="22"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -44058,11 +44058,11 @@
       <c r="C27" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="595">
+      <c r="D27" s="594">
         <f>SUM(M10:O10)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="595"/>
+      <c r="E27" s="594"/>
       <c r="S27" s="22"/>
     </row>
     <row r="28" spans="1:19" ht="25.5" customHeight="1">
@@ -44070,11 +44070,11 @@
       <c r="C28" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="595">
+      <c r="D28" s="594">
         <f>SUM(M11:O11)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="595"/>
+      <c r="E28" s="594"/>
       <c r="S28" s="22"/>
     </row>
     <row r="29" spans="1:19" ht="33" customHeight="1">
@@ -44082,11 +44082,11 @@
       <c r="C29" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="602">
+      <c r="D29" s="601">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="602"/>
+      <c r="E29" s="601"/>
       <c r="S29" s="22"/>
     </row>
     <row r="30" spans="1:19">
@@ -44263,7 +44263,7 @@
     <row r="4" spans="2:5">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="553"/>
+      <c r="D4" s="552"/>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="2:5">
@@ -44576,37 +44576,37 @@
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="37.15" customHeight="1">
-      <c r="A2" s="609" t="s">
+      <c r="A2" s="608" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="610"/>
-      <c r="C2" s="610"/>
-      <c r="D2" s="610"/>
-      <c r="E2" s="610"/>
-      <c r="F2" s="610"/>
-      <c r="G2" s="610"/>
-      <c r="H2" s="610"/>
-      <c r="I2" s="610"/>
-      <c r="J2" s="610"/>
-      <c r="K2" s="610"/>
-      <c r="L2" s="610"/>
-      <c r="M2" s="610"/>
-      <c r="N2" s="610"/>
-      <c r="O2" s="610"/>
-      <c r="P2" s="610"/>
-      <c r="Q2" s="610"/>
-      <c r="R2" s="610"/>
-      <c r="S2" s="610"/>
-      <c r="T2" s="611" t="s">
+      <c r="B2" s="609"/>
+      <c r="C2" s="609"/>
+      <c r="D2" s="609"/>
+      <c r="E2" s="609"/>
+      <c r="F2" s="609"/>
+      <c r="G2" s="609"/>
+      <c r="H2" s="609"/>
+      <c r="I2" s="609"/>
+      <c r="J2" s="609"/>
+      <c r="K2" s="609"/>
+      <c r="L2" s="609"/>
+      <c r="M2" s="609"/>
+      <c r="N2" s="609"/>
+      <c r="O2" s="609"/>
+      <c r="P2" s="609"/>
+      <c r="Q2" s="609"/>
+      <c r="R2" s="609"/>
+      <c r="S2" s="609"/>
+      <c r="T2" s="610" t="s">
         <v>164</v>
       </c>
-      <c r="U2" s="611"/>
-      <c r="V2" s="611"/>
-      <c r="W2" s="611"/>
-      <c r="X2" s="611"/>
-      <c r="Y2" s="611"/>
-      <c r="Z2" s="611"/>
-      <c r="AA2" s="612"/>
+      <c r="U2" s="610"/>
+      <c r="V2" s="610"/>
+      <c r="W2" s="610"/>
+      <c r="X2" s="610"/>
+      <c r="Y2" s="610"/>
+      <c r="Z2" s="610"/>
+      <c r="AA2" s="611"/>
     </row>
     <row r="3" spans="1:27" ht="2.4500000000000002" customHeight="1">
       <c r="A3" s="16"/>
@@ -46365,51 +46365,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75">
-      <c r="A1" s="613" t="s">
+      <c r="A1" s="612" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="614"/>
-      <c r="C1" s="614"/>
-      <c r="D1" s="614"/>
-      <c r="E1" s="614"/>
-      <c r="F1" s="614"/>
-      <c r="G1" s="614"/>
-      <c r="H1" s="614"/>
-      <c r="I1" s="614"/>
-      <c r="J1" s="614"/>
-      <c r="K1" s="614"/>
-      <c r="L1" s="614"/>
-      <c r="M1" s="614"/>
-      <c r="N1" s="614"/>
-      <c r="O1" s="614"/>
-      <c r="P1" s="614"/>
-      <c r="Q1" s="614"/>
-      <c r="R1" s="614"/>
+      <c r="B1" s="613"/>
+      <c r="C1" s="613"/>
+      <c r="D1" s="613"/>
+      <c r="E1" s="613"/>
+      <c r="F1" s="613"/>
+      <c r="G1" s="613"/>
+      <c r="H1" s="613"/>
+      <c r="I1" s="613"/>
+      <c r="J1" s="613"/>
+      <c r="K1" s="613"/>
+      <c r="L1" s="613"/>
+      <c r="M1" s="613"/>
+      <c r="N1" s="613"/>
+      <c r="O1" s="613"/>
+      <c r="P1" s="613"/>
+      <c r="Q1" s="613"/>
+      <c r="R1" s="613"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" thickBot="1">
-      <c r="A2" s="615" t="s">
+      <c r="A2" s="614" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="616"/>
-      <c r="C2" s="616"/>
-      <c r="D2" s="616"/>
-      <c r="E2" s="616"/>
-      <c r="F2" s="616"/>
-      <c r="G2" s="616"/>
-      <c r="H2" s="616"/>
-      <c r="I2" s="616"/>
-      <c r="J2" s="616"/>
-      <c r="K2" s="616"/>
-      <c r="L2" s="616"/>
-      <c r="M2" s="616"/>
-      <c r="N2" s="616"/>
-      <c r="O2" s="616"/>
-      <c r="P2" s="616"/>
-      <c r="Q2" s="616"/>
-      <c r="R2" s="616"/>
+      <c r="B2" s="615"/>
+      <c r="C2" s="615"/>
+      <c r="D2" s="615"/>
+      <c r="E2" s="615"/>
+      <c r="F2" s="615"/>
+      <c r="G2" s="615"/>
+      <c r="H2" s="615"/>
+      <c r="I2" s="615"/>
+      <c r="J2" s="615"/>
+      <c r="K2" s="615"/>
+      <c r="L2" s="615"/>
+      <c r="M2" s="615"/>
+      <c r="N2" s="615"/>
+      <c r="O2" s="615"/>
+      <c r="P2" s="615"/>
+      <c r="Q2" s="615"/>
+      <c r="R2" s="615"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="315"/>
+      <c r="A3" s="314"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -46429,9 +46429,9 @@
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A4" s="315"/>
-      <c r="B4" s="316"/>
-      <c r="C4" s="316"/>
+      <c r="A4" s="314"/>
+      <c r="B4" s="315"/>
+      <c r="C4" s="315"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -46449,632 +46449,632 @@
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:21" ht="88.5" customHeight="1" thickBot="1">
-      <c r="A5" s="315"/>
-      <c r="B5" s="333" t="s">
+      <c r="A5" s="314"/>
+      <c r="B5" s="332" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="617" t="s">
+      <c r="C5" s="616" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="617"/>
-      <c r="E5" s="617"/>
-      <c r="F5" s="617" t="s">
+      <c r="D5" s="616"/>
+      <c r="E5" s="616"/>
+      <c r="F5" s="616" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="617"/>
-      <c r="H5" s="617"/>
-      <c r="I5" s="617" t="s">
+      <c r="G5" s="616"/>
+      <c r="H5" s="616"/>
+      <c r="I5" s="616" t="s">
         <v>146</v>
       </c>
-      <c r="J5" s="617"/>
-      <c r="K5" s="617"/>
-      <c r="L5" s="617" t="s">
+      <c r="J5" s="616"/>
+      <c r="K5" s="616"/>
+      <c r="L5" s="616" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="617"/>
-      <c r="N5" s="617"/>
-      <c r="O5" s="617" t="s">
+      <c r="M5" s="616"/>
+      <c r="N5" s="616"/>
+      <c r="O5" s="616" t="s">
         <v>147</v>
       </c>
-      <c r="P5" s="617"/>
-      <c r="Q5" s="618"/>
-      <c r="R5" s="313"/>
-      <c r="S5" s="312"/>
+      <c r="P5" s="616"/>
+      <c r="Q5" s="617"/>
+      <c r="R5" s="312"/>
+      <c r="S5" s="311"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
     </row>
     <row r="6" spans="1:21" ht="21">
-      <c r="A6" s="315"/>
-      <c r="B6" s="334" t="s">
+      <c r="A6" s="314"/>
+      <c r="B6" s="333" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="319"/>
-      <c r="D6" s="320" t="str">
+      <c r="C6" s="318"/>
+      <c r="D6" s="319" t="str">
         <f>IF(data_status_reg!$E4="bajo",0,IF(data_status_reg!$E4="medio",0.5,IF(data_status_reg!$E4="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E6" s="321"/>
-      <c r="F6" s="321"/>
-      <c r="G6" s="320" t="str">
+      <c r="E6" s="320"/>
+      <c r="F6" s="320"/>
+      <c r="G6" s="319" t="str">
         <f>IF(data_status_reg!$E20="bajo",0,IF(data_status_reg!$E20="medio",0.5,IF(data_status_reg!$E20="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H6" s="321"/>
-      <c r="I6" s="321"/>
-      <c r="J6" s="320" t="str">
+      <c r="H6" s="320"/>
+      <c r="I6" s="320"/>
+      <c r="J6" s="319" t="str">
         <f>IF(data_status_reg!$E36="bajo",0,IF(data_status_reg!$E36="medio",0.5,IF(data_status_reg!$E36="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K6" s="321"/>
-      <c r="L6" s="321"/>
-      <c r="M6" s="320" t="str">
+      <c r="K6" s="320"/>
+      <c r="L6" s="320"/>
+      <c r="M6" s="319" t="str">
         <f>IF(data_status_reg!$E52="bajo",0,IF(data_status_reg!$E52="medio",0.5,IF(data_status_reg!$E52="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N6" s="322"/>
-      <c r="O6" s="336"/>
-      <c r="P6" s="320" t="str">
+      <c r="N6" s="321"/>
+      <c r="O6" s="335"/>
+      <c r="P6" s="319" t="str">
         <f>IF(data_status_reg!$E68="bajo",0,IF(data_status_reg!$E68="medio",0.5,IF(data_status_reg!$E68="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q6" s="323"/>
-      <c r="R6" s="314"/>
+      <c r="Q6" s="322"/>
+      <c r="R6" s="313"/>
     </row>
     <row r="7" spans="1:21" ht="21">
-      <c r="A7" s="315"/>
-      <c r="B7" s="334" t="s">
+      <c r="A7" s="314"/>
+      <c r="B7" s="333" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="324"/>
-      <c r="D7" s="309" t="str">
+      <c r="C7" s="323"/>
+      <c r="D7" s="308" t="str">
         <f>IF(data_status_reg!$E5="bajo",0,IF(data_status_reg!$E5="medio",0.5,IF(data_status_reg!$E5="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E7" s="310"/>
-      <c r="F7" s="310"/>
-      <c r="G7" s="309" t="str">
+      <c r="E7" s="309"/>
+      <c r="F7" s="309"/>
+      <c r="G7" s="308" t="str">
         <f>IF(data_status_reg!$E21="bajo",0,IF(data_status_reg!$E21="medio",0.5,IF(data_status_reg!$E21="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H7" s="310"/>
-      <c r="I7" s="310"/>
-      <c r="J7" s="309" t="str">
+      <c r="H7" s="309"/>
+      <c r="I7" s="309"/>
+      <c r="J7" s="308" t="str">
         <f>IF(data_status_reg!$E37="bajo",0,IF(data_status_reg!$E37="medio",0.5,IF(data_status_reg!$E37="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K7" s="310"/>
-      <c r="L7" s="310"/>
-      <c r="M7" s="309" t="str">
+      <c r="K7" s="309"/>
+      <c r="L7" s="309"/>
+      <c r="M7" s="308" t="str">
         <f>IF(data_status_reg!$E53="bajo",0,IF(data_status_reg!$E53="medio",0.5,IF(data_status_reg!$E53="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N7" s="307"/>
-      <c r="O7" s="337"/>
-      <c r="P7" s="309" t="str">
+      <c r="N7" s="306"/>
+      <c r="O7" s="336"/>
+      <c r="P7" s="308" t="str">
         <f>IF(data_status_reg!$E69="bajo",0,IF(data_status_reg!$E69="medio",0.5,IF(data_status_reg!$E69="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q7" s="325"/>
+      <c r="Q7" s="324"/>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:21" ht="21">
-      <c r="A8" s="315"/>
-      <c r="B8" s="334" t="s">
+      <c r="A8" s="314"/>
+      <c r="B8" s="333" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="324"/>
-      <c r="D8" s="309" t="str">
+      <c r="C8" s="323"/>
+      <c r="D8" s="308" t="str">
         <f>IF(data_status_reg!$E6="bajo",0,IF(data_status_reg!$E6="medio",0.5,IF(data_status_reg!$E6="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E8" s="310"/>
-      <c r="F8" s="310"/>
-      <c r="G8" s="309" t="str">
+      <c r="E8" s="309"/>
+      <c r="F8" s="309"/>
+      <c r="G8" s="308" t="str">
         <f>IF(data_status_reg!$E22="bajo",0,IF(data_status_reg!$E22="medio",0.5,IF(data_status_reg!$E22="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H8" s="310"/>
-      <c r="I8" s="310"/>
-      <c r="J8" s="309" t="str">
+      <c r="H8" s="309"/>
+      <c r="I8" s="309"/>
+      <c r="J8" s="308" t="str">
         <f>IF(data_status_reg!$E38="bajo",0,IF(data_status_reg!$E38="medio",0.5,IF(data_status_reg!$E38="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K8" s="310"/>
-      <c r="L8" s="310"/>
-      <c r="M8" s="309" t="str">
+      <c r="K8" s="309"/>
+      <c r="L8" s="309"/>
+      <c r="M8" s="308" t="str">
         <f>IF(data_status_reg!$E54="bajo",0,IF(data_status_reg!$E54="medio",0.5,IF(data_status_reg!$E54="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N8" s="307"/>
-      <c r="O8" s="337"/>
-      <c r="P8" s="309" t="str">
+      <c r="N8" s="306"/>
+      <c r="O8" s="336"/>
+      <c r="P8" s="308" t="str">
         <f>IF(data_status_reg!$E70="bajo",0,IF(data_status_reg!$E70="medio",0.5,IF(data_status_reg!$E70="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q8" s="325"/>
+      <c r="Q8" s="324"/>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:21" ht="21">
-      <c r="A9" s="315"/>
-      <c r="B9" s="334" t="s">
+      <c r="A9" s="314"/>
+      <c r="B9" s="333" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="324"/>
-      <c r="D9" s="309" t="str">
+      <c r="C9" s="323"/>
+      <c r="D9" s="308" t="str">
         <f>IF(data_status_reg!$E7="bajo",0,IF(data_status_reg!$E7="medio",0.5,IF(data_status_reg!$E7="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E9" s="310"/>
-      <c r="F9" s="310"/>
-      <c r="G9" s="309" t="str">
+      <c r="E9" s="309"/>
+      <c r="F9" s="309"/>
+      <c r="G9" s="308" t="str">
         <f>IF(data_status_reg!$E23="bajo",0,IF(data_status_reg!$E23="medio",0.5,IF(data_status_reg!$E23="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H9" s="310"/>
-      <c r="I9" s="310"/>
-      <c r="J9" s="309" t="str">
+      <c r="H9" s="309"/>
+      <c r="I9" s="309"/>
+      <c r="J9" s="308" t="str">
         <f>IF(data_status_reg!$E39="bajo",0,IF(data_status_reg!$E39="medio",0.5,IF(data_status_reg!$E39="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K9" s="310"/>
-      <c r="L9" s="310"/>
-      <c r="M9" s="309" t="str">
+      <c r="K9" s="309"/>
+      <c r="L9" s="309"/>
+      <c r="M9" s="308" t="str">
         <f>IF(data_status_reg!$E55="bajo",0,IF(data_status_reg!$E55="medio",0.5,IF(data_status_reg!$E55="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N9" s="307"/>
-      <c r="O9" s="337"/>
-      <c r="P9" s="309" t="str">
+      <c r="N9" s="306"/>
+      <c r="O9" s="336"/>
+      <c r="P9" s="308" t="str">
         <f>IF(data_status_reg!$E71="bajo",0,IF(data_status_reg!$E71="medio",0.5,IF(data_status_reg!$E71="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q9" s="325"/>
+      <c r="Q9" s="324"/>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:21" ht="21">
-      <c r="A10" s="315"/>
-      <c r="B10" s="334" t="s">
+      <c r="A10" s="314"/>
+      <c r="B10" s="333" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="324"/>
-      <c r="D10" s="309" t="str">
+      <c r="C10" s="323"/>
+      <c r="D10" s="308" t="str">
         <f>IF(data_status_reg!$E8="bajo",0,IF(data_status_reg!$E8="medio",0.5,IF(data_status_reg!$E8="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E10" s="310"/>
-      <c r="F10" s="310"/>
-      <c r="G10" s="309" t="str">
+      <c r="E10" s="309"/>
+      <c r="F10" s="309"/>
+      <c r="G10" s="308" t="str">
         <f>IF(data_status_reg!$E24="bajo",0,IF(data_status_reg!$E24="medio",0.5,IF(data_status_reg!$E24="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H10" s="310"/>
-      <c r="I10" s="310"/>
-      <c r="J10" s="309" t="str">
+      <c r="H10" s="309"/>
+      <c r="I10" s="309"/>
+      <c r="J10" s="308" t="str">
         <f>IF(data_status_reg!$E40="bajo",0,IF(data_status_reg!$E40="medio",0.5,IF(data_status_reg!$E40="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K10" s="310"/>
-      <c r="L10" s="310"/>
-      <c r="M10" s="309" t="str">
+      <c r="K10" s="309"/>
+      <c r="L10" s="309"/>
+      <c r="M10" s="308" t="str">
         <f>IF(data_status_reg!$E56="bajo",0,IF(data_status_reg!$E56="medio",0.5,IF(data_status_reg!$E56="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N10" s="307"/>
-      <c r="O10" s="337"/>
-      <c r="P10" s="309" t="str">
+      <c r="N10" s="306"/>
+      <c r="O10" s="336"/>
+      <c r="P10" s="308" t="str">
         <f>IF(data_status_reg!$E72="bajo",0,IF(data_status_reg!$E72="medio",0.5,IF(data_status_reg!$E72="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q10" s="325"/>
+      <c r="Q10" s="324"/>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:21" ht="21">
-      <c r="A11" s="315"/>
-      <c r="B11" s="334" t="s">
+      <c r="A11" s="314"/>
+      <c r="B11" s="333" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="324"/>
-      <c r="D11" s="309" t="str">
+      <c r="C11" s="323"/>
+      <c r="D11" s="308" t="str">
         <f>IF(data_status_reg!$E9="bajo",0,IF(data_status_reg!$E9="medio",0.5,IF(data_status_reg!$E9="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E11" s="310"/>
-      <c r="F11" s="310"/>
-      <c r="G11" s="309" t="str">
+      <c r="E11" s="309"/>
+      <c r="F11" s="309"/>
+      <c r="G11" s="308" t="str">
         <f>IF(data_status_reg!$E25="bajo",0,IF(data_status_reg!$E25="medio",0.5,IF(data_status_reg!$E25="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H11" s="310"/>
-      <c r="I11" s="310"/>
-      <c r="J11" s="309" t="str">
+      <c r="H11" s="309"/>
+      <c r="I11" s="309"/>
+      <c r="J11" s="308" t="str">
         <f>IF(data_status_reg!$E41="bajo",0,IF(data_status_reg!$E41="medio",0.5,IF(data_status_reg!$E41="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K11" s="310"/>
-      <c r="L11" s="310"/>
-      <c r="M11" s="309" t="str">
+      <c r="K11" s="309"/>
+      <c r="L11" s="309"/>
+      <c r="M11" s="308" t="str">
         <f>IF(data_status_reg!$E57="bajo",0,IF(data_status_reg!$E57="medio",0.5,IF(data_status_reg!$E57="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N11" s="307"/>
-      <c r="O11" s="337"/>
-      <c r="P11" s="309" t="str">
+      <c r="N11" s="306"/>
+      <c r="O11" s="336"/>
+      <c r="P11" s="308" t="str">
         <f>IF(data_status_reg!$E73="bajo",0,IF(data_status_reg!$E73="medio",0.5,IF(data_status_reg!$E73="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q11" s="325"/>
+      <c r="Q11" s="324"/>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="21">
-      <c r="A12" s="315"/>
-      <c r="B12" s="334" t="s">
+      <c r="A12" s="314"/>
+      <c r="B12" s="333" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="324"/>
-      <c r="D12" s="309" t="str">
+      <c r="C12" s="323"/>
+      <c r="D12" s="308" t="str">
         <f>IF(data_status_reg!$E10="bajo",0,IF(data_status_reg!$E10="medio",0.5,IF(data_status_reg!$E10="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E12" s="310"/>
-      <c r="F12" s="310"/>
-      <c r="G12" s="309" t="str">
+      <c r="E12" s="309"/>
+      <c r="F12" s="309"/>
+      <c r="G12" s="308" t="str">
         <f>IF(data_status_reg!$E26="bajo",0,IF(data_status_reg!$E26="medio",0.5,IF(data_status_reg!$E26="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H12" s="310"/>
-      <c r="I12" s="311"/>
-      <c r="J12" s="309" t="str">
+      <c r="H12" s="309"/>
+      <c r="I12" s="310"/>
+      <c r="J12" s="308" t="str">
         <f>IF(data_status_reg!$E42="bajo",0,IF(data_status_reg!$E42="medio",0.5,IF(data_status_reg!$E42="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K12" s="311"/>
-      <c r="L12" s="311"/>
-      <c r="M12" s="309" t="str">
+      <c r="K12" s="310"/>
+      <c r="L12" s="310"/>
+      <c r="M12" s="308" t="str">
         <f>IF(data_status_reg!$E58="bajo",0,IF(data_status_reg!$E58="medio",0.5,IF(data_status_reg!$E58="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N12" s="308"/>
-      <c r="O12" s="338"/>
-      <c r="P12" s="309" t="str">
+      <c r="N12" s="307"/>
+      <c r="O12" s="337"/>
+      <c r="P12" s="308" t="str">
         <f>IF(data_status_reg!$E74="bajo",0,IF(data_status_reg!$E74="medio",0.5,IF(data_status_reg!$E74="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q12" s="325"/>
+      <c r="Q12" s="324"/>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:21" ht="21">
-      <c r="A13" s="315"/>
-      <c r="B13" s="334" t="s">
+      <c r="A13" s="314"/>
+      <c r="B13" s="333" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="324"/>
-      <c r="D13" s="309" t="str">
+      <c r="C13" s="323"/>
+      <c r="D13" s="308" t="str">
         <f>IF(data_status_reg!$E11="bajo",0,IF(data_status_reg!$E11="medio",0.5,IF(data_status_reg!$E11="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E13" s="310"/>
-      <c r="F13" s="310"/>
-      <c r="G13" s="309" t="str">
+      <c r="E13" s="309"/>
+      <c r="F13" s="309"/>
+      <c r="G13" s="308" t="str">
         <f>IF(data_status_reg!$E27="bajo",0,IF(data_status_reg!$E27="medio",0.5,IF(data_status_reg!$E27="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H13" s="310"/>
-      <c r="I13" s="310"/>
-      <c r="J13" s="309" t="str">
+      <c r="H13" s="309"/>
+      <c r="I13" s="309"/>
+      <c r="J13" s="308" t="str">
         <f>IF(data_status_reg!$E43="bajo",0,IF(data_status_reg!$E43="medio",0.5,IF(data_status_reg!$E43="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K13" s="310"/>
-      <c r="L13" s="310"/>
-      <c r="M13" s="309" t="str">
+      <c r="K13" s="309"/>
+      <c r="L13" s="309"/>
+      <c r="M13" s="308" t="str">
         <f>IF(data_status_reg!$E59="bajo",0,IF(data_status_reg!$E59="medio",0.5,IF(data_status_reg!$E59="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N13" s="307"/>
-      <c r="O13" s="337"/>
-      <c r="P13" s="309" t="str">
+      <c r="N13" s="306"/>
+      <c r="O13" s="336"/>
+      <c r="P13" s="308" t="str">
         <f>IF(data_status_reg!$E75="bajo",0,IF(data_status_reg!$E75="medio",0.5,IF(data_status_reg!$E75="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q13" s="325"/>
+      <c r="Q13" s="324"/>
       <c r="R13" s="3"/>
       <c r="U13" s="10"/>
     </row>
     <row r="14" spans="1:21" ht="21">
-      <c r="A14" s="315"/>
-      <c r="B14" s="334" t="s">
+      <c r="A14" s="314"/>
+      <c r="B14" s="333" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="324"/>
-      <c r="D14" s="309" t="str">
+      <c r="C14" s="323"/>
+      <c r="D14" s="308" t="str">
         <f>IF(data_status_reg!$E12="bajo",0,IF(data_status_reg!$E12="medio",0.5,IF(data_status_reg!$E12="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E14" s="310"/>
-      <c r="F14" s="310"/>
-      <c r="G14" s="309" t="str">
+      <c r="E14" s="309"/>
+      <c r="F14" s="309"/>
+      <c r="G14" s="308" t="str">
         <f>IF(data_status_reg!$E28="bajo",0,IF(data_status_reg!$E28="medio",0.5,IF(data_status_reg!$E28="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H14" s="310"/>
-      <c r="I14" s="310"/>
-      <c r="J14" s="309" t="str">
+      <c r="H14" s="309"/>
+      <c r="I14" s="309"/>
+      <c r="J14" s="308" t="str">
         <f>IF(data_status_reg!$E44="bajo",0,IF(data_status_reg!$E44="medio",0.5,IF(data_status_reg!$E44="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K14" s="310"/>
-      <c r="L14" s="310"/>
-      <c r="M14" s="309" t="str">
+      <c r="K14" s="309"/>
+      <c r="L14" s="309"/>
+      <c r="M14" s="308" t="str">
         <f>IF(data_status_reg!$E60="bajo",0,IF(data_status_reg!$E60="medio",0.5,IF(data_status_reg!$E60="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N14" s="307"/>
-      <c r="O14" s="337"/>
-      <c r="P14" s="309" t="str">
+      <c r="N14" s="306"/>
+      <c r="O14" s="336"/>
+      <c r="P14" s="308" t="str">
         <f>IF(data_status_reg!$E76="bajo",0,IF(data_status_reg!$E76="medio",0.5,IF(data_status_reg!$E76="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q14" s="325"/>
+      <c r="Q14" s="324"/>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:21" ht="21">
-      <c r="A15" s="315"/>
-      <c r="B15" s="334" t="s">
+      <c r="A15" s="314"/>
+      <c r="B15" s="333" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="324"/>
-      <c r="D15" s="309" t="str">
+      <c r="C15" s="323"/>
+      <c r="D15" s="308" t="str">
         <f>IF(data_status_reg!$E13="bajo",0,IF(data_status_reg!$E13="medio",0.5,IF(data_status_reg!$E13="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E15" s="310"/>
-      <c r="F15" s="310"/>
-      <c r="G15" s="309" t="str">
+      <c r="E15" s="309"/>
+      <c r="F15" s="309"/>
+      <c r="G15" s="308" t="str">
         <f>IF(data_status_reg!$E29="bajo",0,IF(data_status_reg!$E29="medio",0.5,IF(data_status_reg!$E29="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H15" s="310"/>
-      <c r="I15" s="311"/>
-      <c r="J15" s="309" t="str">
+      <c r="H15" s="309"/>
+      <c r="I15" s="310"/>
+      <c r="J15" s="308" t="str">
         <f>IF(data_status_reg!$E45="bajo",0,IF(data_status_reg!$E45="medio",0.5,IF(data_status_reg!$E45="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K15" s="311"/>
-      <c r="L15" s="311"/>
-      <c r="M15" s="309" t="str">
+      <c r="K15" s="310"/>
+      <c r="L15" s="310"/>
+      <c r="M15" s="308" t="str">
         <f>IF(data_status_reg!$E61="bajo",0,IF(data_status_reg!$E61="medio",0.5,IF(data_status_reg!$E61="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N15" s="308"/>
-      <c r="O15" s="338"/>
-      <c r="P15" s="309" t="str">
+      <c r="N15" s="307"/>
+      <c r="O15" s="337"/>
+      <c r="P15" s="308" t="str">
         <f>IF(data_status_reg!$E77="bajo",0,IF(data_status_reg!$E77="medio",0.5,IF(data_status_reg!$E77="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q15" s="325"/>
+      <c r="Q15" s="324"/>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:21" ht="21">
-      <c r="A16" s="315"/>
-      <c r="B16" s="334" t="s">
+      <c r="A16" s="314"/>
+      <c r="B16" s="333" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="324"/>
-      <c r="D16" s="309" t="str">
+      <c r="C16" s="323"/>
+      <c r="D16" s="308" t="str">
         <f>IF(data_status_reg!$E14="bajo",0,IF(data_status_reg!$E14="medio",0.5,IF(data_status_reg!$E14="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E16" s="310"/>
-      <c r="F16" s="310"/>
-      <c r="G16" s="309" t="str">
+      <c r="E16" s="309"/>
+      <c r="F16" s="309"/>
+      <c r="G16" s="308" t="str">
         <f>IF(data_status_reg!$E30="bajo",0,IF(data_status_reg!$E30="medio",0.5,IF(data_status_reg!$E30="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H16" s="310"/>
-      <c r="I16" s="310"/>
-      <c r="J16" s="309" t="str">
+      <c r="H16" s="309"/>
+      <c r="I16" s="309"/>
+      <c r="J16" s="308" t="str">
         <f>IF(data_status_reg!$E46="bajo",0,IF(data_status_reg!$E46="medio",0.5,IF(data_status_reg!$E46="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K16" s="310"/>
-      <c r="L16" s="310"/>
-      <c r="M16" s="309" t="str">
+      <c r="K16" s="309"/>
+      <c r="L16" s="309"/>
+      <c r="M16" s="308" t="str">
         <f>IF(data_status_reg!$E62="bajo",0,IF(data_status_reg!$E62="medio",0.5,IF(data_status_reg!$E62="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N16" s="307"/>
-      <c r="O16" s="337"/>
-      <c r="P16" s="309" t="str">
+      <c r="N16" s="306"/>
+      <c r="O16" s="336"/>
+      <c r="P16" s="308" t="str">
         <f>IF(data_status_reg!$E78="bajo",0,IF(data_status_reg!$E78="medio",0.5,IF(data_status_reg!$E78="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q16" s="325"/>
+      <c r="Q16" s="324"/>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" ht="21">
-      <c r="A17" s="315"/>
-      <c r="B17" s="334" t="s">
+      <c r="A17" s="314"/>
+      <c r="B17" s="333" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="324"/>
-      <c r="D17" s="309" t="str">
+      <c r="C17" s="323"/>
+      <c r="D17" s="308" t="str">
         <f>IF(data_status_reg!$E15="bajo",0,IF(data_status_reg!$E15="medio",0.5,IF(data_status_reg!$E15="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E17" s="310"/>
-      <c r="F17" s="310"/>
-      <c r="G17" s="309" t="str">
+      <c r="E17" s="309"/>
+      <c r="F17" s="309"/>
+      <c r="G17" s="308" t="str">
         <f>IF(data_status_reg!$E31="bajo",0,IF(data_status_reg!$E31="medio",0.5,IF(data_status_reg!$E31="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H17" s="310"/>
-      <c r="I17" s="310"/>
-      <c r="J17" s="309" t="str">
+      <c r="H17" s="309"/>
+      <c r="I17" s="309"/>
+      <c r="J17" s="308" t="str">
         <f>IF(data_status_reg!$E47="bajo",0,IF(data_status_reg!$E47="medio",0.5,IF(data_status_reg!$E47="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K17" s="310"/>
-      <c r="L17" s="310"/>
-      <c r="M17" s="309" t="str">
+      <c r="K17" s="309"/>
+      <c r="L17" s="309"/>
+      <c r="M17" s="308" t="str">
         <f>IF(data_status_reg!$E63="bajo",0,IF(data_status_reg!$E63="medio",0.5,IF(data_status_reg!$E63="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N17" s="307"/>
-      <c r="O17" s="337"/>
-      <c r="P17" s="309" t="str">
+      <c r="N17" s="306"/>
+      <c r="O17" s="336"/>
+      <c r="P17" s="308" t="str">
         <f>IF(data_status_reg!$E79="bajo",0,IF(data_status_reg!$E79="medio",0.5,IF(data_status_reg!$E79="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q17" s="325"/>
+      <c r="Q17" s="324"/>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" ht="21">
-      <c r="A18" s="315"/>
-      <c r="B18" s="334" t="s">
+      <c r="A18" s="314"/>
+      <c r="B18" s="333" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="324"/>
-      <c r="D18" s="309" t="str">
+      <c r="C18" s="323"/>
+      <c r="D18" s="308" t="str">
         <f>IF(data_status_reg!$E16="bajo",0,IF(data_status_reg!$E16="medio",0.5,IF(data_status_reg!$E16="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E18" s="310"/>
-      <c r="F18" s="310"/>
-      <c r="G18" s="340" t="s">
+      <c r="E18" s="309"/>
+      <c r="F18" s="309"/>
+      <c r="G18" s="339" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="310"/>
-      <c r="I18" s="310"/>
-      <c r="J18" s="309" t="str">
+      <c r="H18" s="309"/>
+      <c r="I18" s="309"/>
+      <c r="J18" s="308" t="str">
         <f>IF(data_status_reg!$E48="bajo",0,IF(data_status_reg!$E48="medio",0.5,IF(data_status_reg!$E48="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K18" s="310"/>
-      <c r="M18" s="309" t="str">
+      <c r="K18" s="309"/>
+      <c r="M18" s="308" t="str">
         <f>IF(data_status_reg!$E64="bajo",0,IF(data_status_reg!$E64="medio",0.5,IF(data_status_reg!$E64="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N18" s="308"/>
-      <c r="O18" s="338"/>
-      <c r="P18" s="309" t="str">
+      <c r="N18" s="307"/>
+      <c r="O18" s="337"/>
+      <c r="P18" s="308" t="str">
         <f>IF(data_status_reg!$E80="bajo",0,IF(data_status_reg!$E80="medio",0.5,IF(data_status_reg!$E80="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q18" s="325"/>
+      <c r="Q18" s="324"/>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" ht="21">
-      <c r="A19" s="315"/>
-      <c r="B19" s="334" t="s">
+      <c r="A19" s="314"/>
+      <c r="B19" s="333" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="324"/>
-      <c r="D19" s="309" t="str">
+      <c r="C19" s="323"/>
+      <c r="D19" s="308" t="str">
         <f>IF(data_status_reg!$E17="bajo",0,IF(data_status_reg!$E17="medio",0.5,IF(data_status_reg!$E17="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E19" s="310"/>
-      <c r="F19" s="310"/>
-      <c r="G19" s="309" t="str">
+      <c r="E19" s="309"/>
+      <c r="F19" s="309"/>
+      <c r="G19" s="308" t="str">
         <f>IF(data_status_reg!$E33="bajo",0,IF(data_status_reg!$E33="medio",0.5,IF(data_status_reg!$E33="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H19" s="310"/>
-      <c r="I19" s="310"/>
-      <c r="J19" s="309" t="str">
+      <c r="H19" s="309"/>
+      <c r="I19" s="309"/>
+      <c r="J19" s="308" t="str">
         <f>IF(data_status_reg!$E49="bajo",0,IF(data_status_reg!$E49="medio",0.5,IF(data_status_reg!$E49="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K19" s="310"/>
-      <c r="L19" s="310"/>
-      <c r="M19" s="309" t="str">
+      <c r="K19" s="309"/>
+      <c r="L19" s="309"/>
+      <c r="M19" s="308" t="str">
         <f>IF(data_status_reg!$E65="bajo",0,IF(data_status_reg!$E65="medio",0.5,IF(data_status_reg!$E65="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N19" s="307"/>
-      <c r="O19" s="337"/>
-      <c r="P19" s="309" t="str">
+      <c r="N19" s="306"/>
+      <c r="O19" s="336"/>
+      <c r="P19" s="308" t="str">
         <f>IF(data_status_reg!$E81="bajo",0,IF(data_status_reg!$E81="medio",0.5,IF(data_status_reg!$E81="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q19" s="325"/>
+      <c r="Q19" s="324"/>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" ht="21">
-      <c r="A20" s="315"/>
-      <c r="B20" s="334" t="s">
+      <c r="A20" s="314"/>
+      <c r="B20" s="333" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="324"/>
-      <c r="D20" s="309" t="str">
+      <c r="C20" s="323"/>
+      <c r="D20" s="308" t="str">
         <f>IF(data_status_reg!$E18="bajo",0,IF(data_status_reg!$E18="medio",0.5,IF(data_status_reg!$E18="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E20" s="310"/>
-      <c r="F20" s="310"/>
-      <c r="G20" s="309" t="str">
+      <c r="E20" s="309"/>
+      <c r="F20" s="309"/>
+      <c r="G20" s="308" t="str">
         <f>IF(data_status_reg!$E34="bajo",0,IF(data_status_reg!$E34="medio",0.5,IF(data_status_reg!$E34="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="H20" s="310"/>
-      <c r="I20" s="310"/>
-      <c r="J20" s="309" t="str">
+      <c r="H20" s="309"/>
+      <c r="I20" s="309"/>
+      <c r="J20" s="308" t="str">
         <f>IF(data_status_reg!$E50="bajo",0,IF(data_status_reg!$E50="medio",0.5,IF(data_status_reg!$E50="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K20" s="310"/>
-      <c r="L20" s="310"/>
-      <c r="M20" s="309" t="str">
+      <c r="K20" s="309"/>
+      <c r="L20" s="309"/>
+      <c r="M20" s="308" t="str">
         <f>IF(data_status_reg!$E66="bajo",0,IF(data_status_reg!$E66="medio",0.5,IF(data_status_reg!$E66="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N20" s="307"/>
-      <c r="O20" s="337"/>
-      <c r="P20" s="309" t="str">
+      <c r="N20" s="306"/>
+      <c r="O20" s="336"/>
+      <c r="P20" s="308" t="str">
         <f>IF(data_status_reg!$E82="bajo",0,IF(data_status_reg!$E82="medio",0.5,IF(data_status_reg!$E82="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q20" s="325"/>
+      <c r="Q20" s="324"/>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" ht="21.75" thickBot="1">
-      <c r="A21" s="315"/>
-      <c r="B21" s="335" t="s">
+      <c r="A21" s="314"/>
+      <c r="B21" s="334" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="326"/>
-      <c r="D21" s="327" t="str">
+      <c r="C21" s="325"/>
+      <c r="D21" s="326" t="str">
         <f>IF(data_status_reg!$E19="bajo",0,IF(data_status_reg!$E19="medio",0.5,IF(data_status_reg!$E19="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="E21" s="328"/>
-      <c r="F21" s="328"/>
-      <c r="G21" s="341" t="s">
+      <c r="E21" s="327"/>
+      <c r="F21" s="327"/>
+      <c r="G21" s="340" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="328"/>
-      <c r="I21" s="328"/>
-      <c r="J21" s="327" t="str">
+      <c r="H21" s="327"/>
+      <c r="I21" s="327"/>
+      <c r="J21" s="326" t="str">
         <f>IF(data_status_reg!$E51="bajo",0,IF(data_status_reg!$E51="medio",0.5,IF(data_status_reg!$E51="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="K21" s="328"/>
-      <c r="L21" s="329"/>
-      <c r="M21" s="330" t="str">
+      <c r="K21" s="327"/>
+      <c r="L21" s="328"/>
+      <c r="M21" s="329" t="str">
         <f>IF(data_status_reg!$E67="bajo",0,IF(data_status_reg!$E67="medio",0.5,IF(data_status_reg!$E67="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="N21" s="331"/>
-      <c r="O21" s="339"/>
-      <c r="P21" s="327" t="str">
+      <c r="N21" s="330"/>
+      <c r="O21" s="338"/>
+      <c r="P21" s="326" t="str">
         <f>IF(data_status_reg!$E83="bajo",0,IF(data_status_reg!$E83="medio",0.5,IF(data_status_reg!$E83="alto",1,"falta riesgo")))</f>
         <v>falta riesgo</v>
       </c>
-      <c r="Q21" s="332"/>
+      <c r="Q21" s="331"/>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="315"/>
+      <c r="A22" s="314"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -47094,24 +47094,24 @@
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1">
-      <c r="A23" s="317"/>
-      <c r="B23" s="318"/>
-      <c r="C23" s="318"/>
-      <c r="D23" s="318"/>
-      <c r="E23" s="318"/>
-      <c r="F23" s="318"/>
-      <c r="G23" s="318"/>
-      <c r="H23" s="318"/>
-      <c r="I23" s="318"/>
-      <c r="J23" s="318"/>
-      <c r="K23" s="318"/>
-      <c r="L23" s="318"/>
-      <c r="M23" s="318"/>
-      <c r="N23" s="318"/>
-      <c r="O23" s="318"/>
-      <c r="P23" s="318"/>
-      <c r="Q23" s="318"/>
-      <c r="R23" s="318"/>
+      <c r="A23" s="316"/>
+      <c r="B23" s="317"/>
+      <c r="C23" s="317"/>
+      <c r="D23" s="317"/>
+      <c r="E23" s="317"/>
+      <c r="F23" s="317"/>
+      <c r="G23" s="317"/>
+      <c r="H23" s="317"/>
+      <c r="I23" s="317"/>
+      <c r="J23" s="317"/>
+      <c r="K23" s="317"/>
+      <c r="L23" s="317"/>
+      <c r="M23" s="317"/>
+      <c r="N23" s="317"/>
+      <c r="O23" s="317"/>
+      <c r="P23" s="317"/>
+      <c r="Q23" s="317"/>
+      <c r="R23" s="317"/>
     </row>
     <row r="26" spans="1:18" outlineLevel="1"/>
     <row r="27" spans="1:18" outlineLevel="1">
@@ -47386,7 +47386,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="18" customHeight="1"/>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="541" t="str">
+      <c r="B3" s="540" t="str">
         <f>_xlfn.CONCAT($D3,":"," ","Auditorías del Plan Anual de Auditoría")</f>
         <v>: Auditorías del Plan Anual de Auditoría</v>
       </c>
@@ -47396,7 +47396,7 @@
       </c>
     </row>
     <row r="4" spans="2:3" ht="18" customHeight="1">
-      <c r="B4" s="541" t="str">
+      <c r="B4" s="540" t="str">
         <f>_xlfn.CONCAT($D4,":"," ","Documentos publicados en web Centro de Estudios")</f>
         <v>: Documentos publicados en web Centro de Estudios</v>
       </c>
@@ -47406,7 +47406,7 @@
       </c>
     </row>
     <row r="5" spans="2:3" ht="18" customHeight="1">
-      <c r="B5" s="541" t="str">
+      <c r="B5" s="540" t="str">
         <f>_xlfn.CONCAT($D5,":"," ","Solicitudes de información respondidas")</f>
         <v>: Solicitudes de información respondidas</v>
       </c>
@@ -47416,7 +47416,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" customHeight="1">
-      <c r="B6" s="541" t="str">
+      <c r="B6" s="540" t="str">
         <f>_xlfn.CONCAT($D6,":"," ","Solicitudes de certificados de estudio")</f>
         <v>: Solicitudes de certificados de estudio</v>
       </c>
@@ -47426,7 +47426,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" ht="18" customHeight="1">
-      <c r="B7" s="541" t="str">
+      <c r="B7" s="540" t="str">
         <f>_xlfn.CONCAT($D7,":"," ","Sistema Calidad de Servicio y Experiencia")</f>
         <v>: Sistema Calidad de Servicio y Experiencia</v>
       </c>
@@ -47436,7 +47436,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" ht="18" customHeight="1">
-      <c r="B8" s="541" t="str">
+      <c r="B8" s="540" t="str">
         <f>_xlfn.CONCAT($D8,":"," ","Medidas de Equidad y Género")</f>
         <v>: Medidas de Equidad y Género</v>
       </c>
@@ -47446,7 +47446,7 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" customHeight="1">
-      <c r="B9" s="541" t="str">
+      <c r="B9" s="540" t="str">
         <f>_xlfn.CONCAT($D9,":"," ","Acciones formativas del Centro de Innovación")</f>
         <v>: Acciones formativas del Centro de Innovación</v>
       </c>
@@ -47456,7 +47456,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" ht="18" customHeight="1">
-      <c r="B10" s="541" t="str">
+      <c r="B10" s="540" t="str">
         <f>_xlfn.CONCAT($D10,":"," ","Compra de equipamiento")</f>
         <v>: Compra de equipamiento</v>
       </c>
@@ -47466,7 +47466,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" ht="18" customHeight="1">
-      <c r="B11" s="541" t="str">
+      <c r="B11" s="540" t="str">
         <f>_xlfn.CONCAT($D11,":"," ","Elaboración de informe formación docente")</f>
         <v>: Elaboración de informe formación docente</v>
       </c>
@@ -47476,7 +47476,7 @@
       </c>
     </row>
     <row r="12" spans="2:3" ht="18" customHeight="1">
-      <c r="B12" s="541" t="str">
+      <c r="B12" s="540" t="str">
         <f>_xlfn.CONCAT($D12,":"," ","Provincias que participan de acciones de CPEIP")</f>
         <v>: Provincias que participan de acciones de CPEIP</v>
       </c>
@@ -47486,7 +47486,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" ht="18" customHeight="1">
-      <c r="B13" s="541" t="str">
+      <c r="B13" s="540" t="str">
         <f>_xlfn.CONCAT($D13,":"," ","Formación de bienestar docente")</f>
         <v>: Formación de bienestar docente</v>
       </c>
@@ -47496,7 +47496,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" ht="18" customHeight="1">
-      <c r="B14" s="541" t="str">
+      <c r="B14" s="540" t="str">
         <f>_xlfn.CONCAT($D14,":"," ","Informe proyecto de ley carrera directiva")</f>
         <v>: Informe proyecto de ley carrera directiva</v>
       </c>
@@ -47506,7 +47506,7 @@
       </c>
     </row>
     <row r="15" spans="2:3" ht="18" customHeight="1">
-      <c r="B15" s="541" t="str">
+      <c r="B15" s="540" t="str">
         <f>_xlfn.CONCAT($D15,":"," ","Implementación del Programa 'A convivir se Aprende'")</f>
         <v>: Implementación del Programa 'A convivir se Aprende'</v>
       </c>
@@ -47516,7 +47516,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B16" s="541" t="str">
+      <c r="B16" s="540" t="str">
         <f>_xlfn.CONCAT($D16,":"," ","Inscipción para completar los estudios")</f>
         <v>: Inscipción para completar los estudios</v>
       </c>
@@ -47526,7 +47526,7 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="18" customHeight="1">
-      <c r="B17" s="541" t="str">
+      <c r="B17" s="540" t="str">
         <f>_xlfn.CONCAT($D17,":"," ","Procesos de validación de estudios")</f>
         <v>: Procesos de validación de estudios</v>
       </c>
@@ -47536,7 +47536,7 @@
       </c>
     </row>
     <row r="18" spans="2:3" ht="18" customHeight="1">
-      <c r="B18" s="541" t="str">
+      <c r="B18" s="540" t="str">
         <f>_xlfn.CONCAT($D18,":"," ","Acciones plan de difusión")</f>
         <v>: Acciones plan de difusión</v>
       </c>
@@ -47546,7 +47546,7 @@
       </c>
     </row>
     <row r="19" spans="2:3" ht="18" customHeight="1">
-      <c r="B19" s="541" t="str">
+      <c r="B19" s="540" t="str">
         <f>_xlfn.CONCAT($D19,":"," ","Sistemas definidos como críticos")</f>
         <v>: Sistemas definidos como críticos</v>
       </c>
@@ -47556,7 +47556,7 @@
       </c>
     </row>
     <row r="20" spans="2:3" ht="18" customHeight="1">
-      <c r="B20" s="541" t="str">
+      <c r="B20" s="540" t="str">
         <f>_xlfn.CONCAT($D20,":"," ","Sitios web con certificados de sitio seguro")</f>
         <v>: Sitios web con certificados de sitio seguro</v>
       </c>
@@ -47566,7 +47566,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" ht="18" customHeight="1">
-      <c r="B21" s="541" t="str">
+      <c r="B21" s="540" t="str">
         <f>_xlfn.CONCAT($D21,":"," ","Tickets de atención resueltos")</f>
         <v>: Tickets de atención resueltos</v>
       </c>
@@ -47576,7 +47576,7 @@
       </c>
     </row>
     <row r="22" spans="2:3" ht="18" customHeight="1">
-      <c r="B22" s="541" t="str">
+      <c r="B22" s="540" t="str">
         <f>_xlfn.CONCAT($D22,":"," ","Transformación Digital")</f>
         <v>: Transformación Digital</v>
       </c>
@@ -47586,7 +47586,7 @@
       </c>
     </row>
     <row r="23" spans="2:3" ht="18" customHeight="1">
-      <c r="B23" s="541" t="str">
+      <c r="B23" s="540" t="str">
         <f>_xlfn.CONCAT($D23,":"," ","Concentración del Gasto")</f>
         <v>: Concentración del Gasto</v>
       </c>
@@ -47596,7 +47596,7 @@
       </c>
     </row>
     <row r="24" spans="2:3" ht="22.5" customHeight="1">
-      <c r="B24" s="541" t="str">
+      <c r="B24" s="540" t="str">
         <f>_xlfn.CONCAT($D24,":"," ","Asistencia vía SIGE")</f>
         <v>: Asistencia vía SIGE</v>
       </c>
@@ -47606,7 +47606,7 @@
       </c>
     </row>
     <row r="25" spans="2:3" ht="18" customHeight="1">
-      <c r="B25" s="541" t="str">
+      <c r="B25" s="540" t="str">
         <f>_xlfn.CONCAT($D25,":"," ","Transacciones a través del sistema SIGPA")</f>
         <v>: Transacciones a través del sistema SIGPA</v>
       </c>
@@ -47616,7 +47616,7 @@
       </c>
     </row>
     <row r="26" spans="2:3" ht="18" customHeight="1">
-      <c r="B26" s="541" t="str">
+      <c r="B26" s="540" t="str">
         <f>_xlfn.CONCAT($D26,":"," ","Procesos documentados URAE")</f>
         <v>: Procesos documentados URAE</v>
       </c>
@@ -47626,7 +47626,7 @@
       </c>
     </row>
     <row r="27" spans="2:3" ht="18" customHeight="1">
-      <c r="B27" s="541" t="str">
+      <c r="B27" s="540" t="str">
         <f>_xlfn.CONCAT($D27,":"," ","Solicitudes de beneficios y/o préstamos")</f>
         <v>: Solicitudes de beneficios y/o préstamos</v>
       </c>
@@ -47636,7 +47636,7 @@
       </c>
     </row>
     <row r="28" spans="2:3" ht="18" customHeight="1">
-      <c r="B28" s="541" t="str">
+      <c r="B28" s="540" t="str">
         <f>_xlfn.CONCAT($D28,":"," ","Expedientes de compras")</f>
         <v>: Expedientes de compras</v>
       </c>
@@ -47646,7 +47646,7 @@
       </c>
     </row>
     <row r="29" spans="2:3" ht="18" customHeight="1">
-      <c r="B29" s="541" t="str">
+      <c r="B29" s="540" t="str">
         <f>_xlfn.CONCAT($D29,":"," ","Sistema Estado Verde")</f>
         <v>: Sistema Estado Verde</v>
       </c>
@@ -47656,7 +47656,7 @@
       </c>
     </row>
     <row r="30" spans="2:3" ht="18" customHeight="1">
-      <c r="B30" s="541" t="str">
+      <c r="B30" s="540" t="str">
         <f>_xlfn.CONCAT($D30,":"," ","Sistema de Riesgos Psicosociales laborales")</f>
         <v>: Sistema de Riesgos Psicosociales laborales</v>
       </c>
@@ -47666,7 +47666,7 @@
       </c>
     </row>
     <row r="31" spans="2:3" ht="18" customHeight="1">
-      <c r="B31" s="541" t="str">
+      <c r="B31" s="540" t="str">
         <f>_xlfn.CONCAT($D31,":"," ","Cierres contables oportunos")</f>
         <v>: Cierres contables oportunos</v>
       </c>
@@ -47676,7 +47676,7 @@
       </c>
     </row>
     <row r="32" spans="2:3" ht="18" customHeight="1">
-      <c r="B32" s="541" t="str">
+      <c r="B32" s="540" t="str">
         <f>_xlfn.CONCAT($D32,":"," ","Contratos nuevos a honorarios NC")</f>
         <v>: Contratos nuevos a honorarios NC</v>
       </c>
@@ -47686,7 +47686,7 @@
       </c>
     </row>
     <row r="33" spans="2:3" ht="18" customHeight="1">
-      <c r="B33" s="541" t="str">
+      <c r="B33" s="540" t="str">
         <f>_xlfn.CONCAT($D33,":"," ","Recursos de Lectura, Aprendizaje y Bibliotecas")</f>
         <v>: Recursos de Lectura, Aprendizaje y Bibliotecas</v>
       </c>
@@ -47696,7 +47696,7 @@
       </c>
     </row>
     <row r="34" spans="2:3" ht="18" customHeight="1">
-      <c r="B34" s="541" t="str">
+      <c r="B34" s="540" t="str">
         <f>_xlfn.CONCAT($D34,":"," ","Ejecución del plan de Desarrollo Curricular")</f>
         <v>: Ejecución del plan de Desarrollo Curricular</v>
       </c>
@@ -47706,7 +47706,7 @@
       </c>
     </row>
     <row r="35" spans="2:3" ht="18" customHeight="1">
-      <c r="B35" s="541" t="str">
+      <c r="B35" s="540" t="str">
         <f>_xlfn.CONCAT($D35,":"," ","Difusión de instrumentos curriculares")</f>
         <v>: Difusión de instrumentos curriculares</v>
       </c>
@@ -47716,7 +47716,7 @@
       </c>
     </row>
     <row r="36" spans="2:3" ht="18" customHeight="1">
-      <c r="B36" s="541" t="str">
+      <c r="B36" s="540" t="str">
         <f>_xlfn.CONCAT($D36,":"," ","Ejecución del plan de Evaluación y Estándares")</f>
         <v>: Ejecución del plan de Evaluación y Estándares</v>
       </c>
@@ -47726,7 +47726,7 @@
       </c>
     </row>
     <row r="37" spans="2:3" ht="21" customHeight="1">
-      <c r="B37" s="541" t="str">
+      <c r="B37" s="540" t="str">
         <f>_xlfn.CONCAT($D37,":"," ","Modernización de textos escolares")</f>
         <v>: Modernización de textos escolares</v>
       </c>
@@ -47736,7 +47736,7 @@
       </c>
     </row>
     <row r="38" spans="2:3" ht="21" customHeight="1">
-      <c r="B38" s="541" t="str">
+      <c r="B38" s="540" t="str">
         <f>_xlfn.CONCAT($D38,":"," ","Textos Escolares entregados")</f>
         <v>: Textos Escolares entregados</v>
       </c>
@@ -47746,7 +47746,7 @@
       </c>
     </row>
     <row r="39" spans="2:3" ht="18" customHeight="1">
-      <c r="B39" s="541" t="str">
+      <c r="B39" s="540" t="str">
         <f>_xlfn.CONCAT($D39,":"," ","Entrega de Kit evaluativo de los EE subvencionados")</f>
         <v>: Entrega de Kit evaluativo de los EE subvencionados</v>
       </c>
@@ -47756,7 +47756,7 @@
       </c>
     </row>
     <row r="40" spans="2:3" ht="18" customHeight="1">
-      <c r="B40" s="541" t="str">
+      <c r="B40" s="540" t="str">
         <f>_xlfn.CONCAT($D40,":"," ","Actos administrativos con una Licitación Pública ")</f>
         <v xml:space="preserve">: Actos administrativos con una Licitación Pública </v>
       </c>
@@ -47766,7 +47766,7 @@
       </c>
     </row>
     <row r="41" spans="2:3" ht="18" customHeight="1">
-      <c r="B41" s="541" t="str">
+      <c r="B41" s="540" t="str">
         <f>_xlfn.CONCAT($D41,":"," ","Actos administrativos Bases Admin. y Técnicas")</f>
         <v>: Actos administrativos Bases Admin. y Técnicas</v>
       </c>
@@ -47776,7 +47776,7 @@
       </c>
     </row>
     <row r="42" spans="2:3" ht="18" customHeight="1">
-      <c r="B42" s="541" t="str">
+      <c r="B42" s="540" t="str">
         <f>_xlfn.CONCAT($D42,":"," ","Propuestas de convenios o reformulación")</f>
         <v>: Propuestas de convenios o reformulación</v>
       </c>
@@ -47786,7 +47786,7 @@
       </c>
     </row>
     <row r="43" spans="2:3" ht="18" customHeight="1">
-      <c r="B43" s="541" t="str">
+      <c r="B43" s="540" t="str">
         <f>_xlfn.CONCAT($D43,":"," ","Actos administrativos que transfieren recursos")</f>
         <v>: Actos administrativos que transfieren recursos</v>
       </c>
@@ -47796,7 +47796,7 @@
       </c>
     </row>
     <row r="44" spans="2:3" ht="18" customHeight="1">
-      <c r="B44" s="541" t="str">
+      <c r="B44" s="540" t="str">
         <f>_xlfn.CONCAT($D44,":"," ","Actos administrativos artículo 11 de la Ley N°20.159")</f>
         <v>: Actos administrativos artículo 11 de la Ley N°20.159</v>
       </c>
@@ -47806,7 +47806,7 @@
       </c>
     </row>
     <row r="45" spans="2:3" ht="20.25" customHeight="1">
-      <c r="B45" s="541" t="str">
+      <c r="B45" s="540" t="str">
         <f>_xlfn.CONCAT($D45,":"," ","Recursos de apelación, reclamación")</f>
         <v>: Recursos de apelación, reclamación</v>
       </c>
@@ -47816,7 +47816,7 @@
       </c>
     </row>
     <row r="46" spans="2:3" ht="18" customHeight="1">
-      <c r="B46" s="541" t="str">
+      <c r="B46" s="540" t="str">
         <f>_xlfn.CONCAT($D46,":"," ","Defensas a recursos de protección")</f>
         <v>: Defensas a recursos de protección</v>
       </c>
@@ -48426,74 +48426,74 @@
     </row>
     <row r="3" spans="1:16" ht="37.35" customHeight="1">
       <c r="A3" s="31"/>
-      <c r="B3" s="619" t="s">
+      <c r="B3" s="618" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="620"/>
-      <c r="D3" s="620"/>
-      <c r="E3" s="620"/>
-      <c r="F3" s="620"/>
-      <c r="G3" s="620"/>
-      <c r="H3" s="620"/>
-      <c r="I3" s="620"/>
-      <c r="J3" s="620"/>
-      <c r="K3" s="620"/>
-      <c r="L3" s="620"/>
-      <c r="M3" s="620"/>
-      <c r="N3" s="620"/>
-      <c r="O3" s="621"/>
+      <c r="C3" s="619"/>
+      <c r="D3" s="619"/>
+      <c r="E3" s="619"/>
+      <c r="F3" s="619"/>
+      <c r="G3" s="619"/>
+      <c r="H3" s="619"/>
+      <c r="I3" s="619"/>
+      <c r="J3" s="619"/>
+      <c r="K3" s="619"/>
+      <c r="L3" s="619"/>
+      <c r="M3" s="619"/>
+      <c r="N3" s="619"/>
+      <c r="O3" s="620"/>
     </row>
     <row r="4" spans="1:16" ht="7.35" customHeight="1">
       <c r="A4" s="32"/>
-      <c r="B4" s="626" t="s">
+      <c r="B4" s="625" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="627"/>
-      <c r="D4" s="627"/>
-      <c r="E4" s="627"/>
-      <c r="F4" s="627"/>
-      <c r="G4" s="627"/>
-      <c r="H4" s="627"/>
-      <c r="I4" s="627"/>
-      <c r="J4" s="627"/>
-      <c r="K4" s="627"/>
-      <c r="L4" s="627"/>
-      <c r="M4" s="627"/>
-      <c r="N4" s="627"/>
+      <c r="C4" s="626"/>
+      <c r="D4" s="626"/>
+      <c r="E4" s="626"/>
+      <c r="F4" s="626"/>
+      <c r="G4" s="626"/>
+      <c r="H4" s="626"/>
+      <c r="I4" s="626"/>
+      <c r="J4" s="626"/>
+      <c r="K4" s="626"/>
+      <c r="L4" s="626"/>
+      <c r="M4" s="626"/>
+      <c r="N4" s="626"/>
       <c r="O4" s="256"/>
     </row>
     <row r="5" spans="1:16" ht="43.5" customHeight="1">
       <c r="A5" s="32"/>
-      <c r="B5" s="626"/>
-      <c r="C5" s="627"/>
-      <c r="D5" s="627"/>
-      <c r="E5" s="627"/>
-      <c r="F5" s="627"/>
-      <c r="G5" s="627"/>
-      <c r="H5" s="627"/>
-      <c r="I5" s="627"/>
-      <c r="J5" s="627"/>
-      <c r="K5" s="627"/>
-      <c r="L5" s="627"/>
-      <c r="M5" s="627"/>
-      <c r="N5" s="627"/>
+      <c r="B5" s="625"/>
+      <c r="C5" s="626"/>
+      <c r="D5" s="626"/>
+      <c r="E5" s="626"/>
+      <c r="F5" s="626"/>
+      <c r="G5" s="626"/>
+      <c r="H5" s="626"/>
+      <c r="I5" s="626"/>
+      <c r="J5" s="626"/>
+      <c r="K5" s="626"/>
+      <c r="L5" s="626"/>
+      <c r="M5" s="626"/>
+      <c r="N5" s="626"/>
       <c r="O5" s="256"/>
     </row>
     <row r="6" spans="1:16" ht="43.5" customHeight="1">
       <c r="A6" s="32"/>
-      <c r="B6" s="626"/>
-      <c r="C6" s="627"/>
-      <c r="D6" s="627"/>
-      <c r="E6" s="627"/>
-      <c r="F6" s="627"/>
-      <c r="G6" s="627"/>
-      <c r="H6" s="627"/>
-      <c r="I6" s="627"/>
-      <c r="J6" s="627"/>
-      <c r="K6" s="627"/>
-      <c r="L6" s="627"/>
-      <c r="M6" s="627"/>
-      <c r="N6" s="627"/>
+      <c r="B6" s="625"/>
+      <c r="C6" s="626"/>
+      <c r="D6" s="626"/>
+      <c r="E6" s="626"/>
+      <c r="F6" s="626"/>
+      <c r="G6" s="626"/>
+      <c r="H6" s="626"/>
+      <c r="I6" s="626"/>
+      <c r="J6" s="626"/>
+      <c r="K6" s="626"/>
+      <c r="L6" s="626"/>
+      <c r="M6" s="626"/>
+      <c r="N6" s="626"/>
       <c r="O6" s="256"/>
     </row>
     <row r="7" spans="1:16" ht="8.1" customHeight="1">
@@ -48522,19 +48522,19 @@
       <c r="A9" s="240"/>
       <c r="B9" s="247"/>
       <c r="C9" s="238"/>
-      <c r="D9" s="630" t="s">
+      <c r="D9" s="629" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="628"/>
-      <c r="F9" s="628"/>
-      <c r="G9" s="629"/>
+      <c r="E9" s="627"/>
+      <c r="F9" s="627"/>
+      <c r="G9" s="628"/>
       <c r="I9" s="238"/>
-      <c r="J9" s="635" t="s">
+      <c r="J9" s="634" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="632"/>
-      <c r="L9" s="633"/>
-      <c r="M9" s="634"/>
+      <c r="K9" s="631"/>
+      <c r="L9" s="632"/>
+      <c r="M9" s="633"/>
       <c r="O9" s="256"/>
     </row>
     <row r="10" spans="1:16" ht="37.5" customHeight="1" thickBot="1">
@@ -48543,7 +48543,7 @@
       <c r="C10" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="631"/>
+      <c r="D10" s="630"/>
       <c r="E10" s="63" t="s">
         <v>51</v>
       </c>
@@ -48556,7 +48556,7 @@
       <c r="I10" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="636"/>
+      <c r="J10" s="635"/>
       <c r="K10" s="67" t="s">
         <v>51</v>
       </c>
@@ -48572,30 +48572,30 @@
       <c r="A11" s="242"/>
       <c r="B11" s="247"/>
       <c r="C11" s="65"/>
-      <c r="D11" s="345"/>
-      <c r="E11" s="345"/>
-      <c r="F11" s="345"/>
-      <c r="G11" s="346"/>
-      <c r="I11" s="575"/>
-      <c r="J11" s="345"/>
-      <c r="K11" s="345"/>
-      <c r="L11" s="345"/>
-      <c r="M11" s="346"/>
+      <c r="D11" s="344"/>
+      <c r="E11" s="344"/>
+      <c r="F11" s="344"/>
+      <c r="G11" s="345"/>
+      <c r="I11" s="574"/>
+      <c r="J11" s="344"/>
+      <c r="K11" s="344"/>
+      <c r="L11" s="344"/>
+      <c r="M11" s="345"/>
       <c r="O11" s="256"/>
     </row>
     <row r="12" spans="1:16" ht="18.75">
       <c r="A12" s="32"/>
       <c r="B12" s="247"/>
       <c r="C12" s="34"/>
-      <c r="D12" s="347"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
-      <c r="G12" s="348"/>
-      <c r="I12" s="576"/>
-      <c r="J12" s="347"/>
-      <c r="K12" s="347"/>
-      <c r="L12" s="347"/>
-      <c r="M12" s="348"/>
+      <c r="D12" s="346"/>
+      <c r="E12" s="346"/>
+      <c r="F12" s="346"/>
+      <c r="G12" s="347"/>
+      <c r="I12" s="575"/>
+      <c r="J12" s="346"/>
+      <c r="K12" s="346"/>
+      <c r="L12" s="346"/>
+      <c r="M12" s="347"/>
       <c r="N12" s="257"/>
       <c r="O12" s="248"/>
     </row>
@@ -48603,15 +48603,15 @@
       <c r="A13" s="32"/>
       <c r="B13" s="247"/>
       <c r="C13" s="34"/>
-      <c r="D13" s="347"/>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
-      <c r="G13" s="348"/>
-      <c r="I13" s="576"/>
-      <c r="J13" s="347"/>
-      <c r="K13" s="347"/>
-      <c r="L13" s="347"/>
-      <c r="M13" s="348"/>
+      <c r="D13" s="346"/>
+      <c r="E13" s="346"/>
+      <c r="F13" s="346"/>
+      <c r="G13" s="347"/>
+      <c r="I13" s="575"/>
+      <c r="J13" s="346"/>
+      <c r="K13" s="346"/>
+      <c r="L13" s="346"/>
+      <c r="M13" s="347"/>
       <c r="N13" s="257"/>
       <c r="O13" s="248"/>
     </row>
@@ -48619,15 +48619,15 @@
       <c r="A14" s="243"/>
       <c r="B14" s="247"/>
       <c r="C14" s="34"/>
-      <c r="D14" s="347"/>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
-      <c r="G14" s="348"/>
-      <c r="I14" s="576"/>
-      <c r="J14" s="347"/>
-      <c r="K14" s="347"/>
-      <c r="L14" s="347"/>
-      <c r="M14" s="348"/>
+      <c r="D14" s="346"/>
+      <c r="E14" s="346"/>
+      <c r="F14" s="346"/>
+      <c r="G14" s="347"/>
+      <c r="I14" s="575"/>
+      <c r="J14" s="346"/>
+      <c r="K14" s="346"/>
+      <c r="L14" s="346"/>
+      <c r="M14" s="347"/>
       <c r="N14" s="257"/>
       <c r="O14" s="248"/>
     </row>
@@ -48635,15 +48635,15 @@
       <c r="A15" s="32"/>
       <c r="B15" s="247"/>
       <c r="C15" s="57"/>
-      <c r="D15" s="347"/>
-      <c r="E15" s="347"/>
-      <c r="F15" s="347"/>
-      <c r="G15" s="348"/>
-      <c r="I15" s="576"/>
-      <c r="J15" s="347"/>
-      <c r="K15" s="347"/>
-      <c r="L15" s="347"/>
-      <c r="M15" s="348"/>
+      <c r="D15" s="346"/>
+      <c r="E15" s="346"/>
+      <c r="F15" s="346"/>
+      <c r="G15" s="347"/>
+      <c r="I15" s="575"/>
+      <c r="J15" s="346"/>
+      <c r="K15" s="346"/>
+      <c r="L15" s="346"/>
+      <c r="M15" s="347"/>
       <c r="N15" s="257"/>
       <c r="O15" s="248"/>
     </row>
@@ -48651,15 +48651,15 @@
       <c r="A16" s="32"/>
       <c r="B16" s="247"/>
       <c r="C16" s="57"/>
-      <c r="D16" s="347"/>
-      <c r="E16" s="347"/>
-      <c r="F16" s="347"/>
-      <c r="G16" s="348"/>
-      <c r="I16" s="576"/>
-      <c r="J16" s="347"/>
-      <c r="K16" s="347"/>
-      <c r="L16" s="347"/>
-      <c r="M16" s="348"/>
+      <c r="D16" s="346"/>
+      <c r="E16" s="346"/>
+      <c r="F16" s="346"/>
+      <c r="G16" s="347"/>
+      <c r="I16" s="575"/>
+      <c r="J16" s="346"/>
+      <c r="K16" s="346"/>
+      <c r="L16" s="346"/>
+      <c r="M16" s="347"/>
       <c r="N16" s="257"/>
       <c r="O16" s="248"/>
     </row>
@@ -48667,15 +48667,15 @@
       <c r="A17" s="32"/>
       <c r="B17" s="247"/>
       <c r="C17" s="57"/>
-      <c r="D17" s="347"/>
-      <c r="E17" s="347"/>
-      <c r="F17" s="347"/>
-      <c r="G17" s="348"/>
-      <c r="I17" s="576"/>
-      <c r="J17" s="347"/>
-      <c r="K17" s="347"/>
-      <c r="L17" s="347"/>
-      <c r="M17" s="348"/>
+      <c r="D17" s="346"/>
+      <c r="E17" s="346"/>
+      <c r="F17" s="346"/>
+      <c r="G17" s="347"/>
+      <c r="I17" s="575"/>
+      <c r="J17" s="346"/>
+      <c r="K17" s="346"/>
+      <c r="L17" s="346"/>
+      <c r="M17" s="347"/>
       <c r="N17" s="257"/>
       <c r="O17" s="248"/>
     </row>
@@ -48683,15 +48683,15 @@
       <c r="A18" s="32"/>
       <c r="B18" s="247"/>
       <c r="C18" s="57"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
-      <c r="G18" s="348"/>
-      <c r="I18" s="576"/>
-      <c r="J18" s="347"/>
-      <c r="K18" s="347"/>
-      <c r="L18" s="347"/>
-      <c r="M18" s="348"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+      <c r="G18" s="347"/>
+      <c r="I18" s="575"/>
+      <c r="J18" s="346"/>
+      <c r="K18" s="346"/>
+      <c r="L18" s="346"/>
+      <c r="M18" s="347"/>
       <c r="N18" s="257"/>
       <c r="O18" s="248"/>
     </row>
@@ -48699,15 +48699,15 @@
       <c r="A19" s="32"/>
       <c r="B19" s="247"/>
       <c r="C19" s="34"/>
-      <c r="D19" s="347"/>
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
-      <c r="G19" s="348"/>
-      <c r="I19" s="576"/>
-      <c r="J19" s="347"/>
-      <c r="K19" s="347"/>
-      <c r="L19" s="347"/>
-      <c r="M19" s="348"/>
+      <c r="D19" s="346"/>
+      <c r="E19" s="346"/>
+      <c r="F19" s="346"/>
+      <c r="G19" s="347"/>
+      <c r="I19" s="575"/>
+      <c r="J19" s="346"/>
+      <c r="K19" s="346"/>
+      <c r="L19" s="346"/>
+      <c r="M19" s="347"/>
       <c r="N19" s="257"/>
       <c r="O19" s="248"/>
     </row>
@@ -48715,15 +48715,15 @@
       <c r="A20" s="32"/>
       <c r="B20" s="247"/>
       <c r="C20" s="34"/>
-      <c r="D20" s="347"/>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
-      <c r="G20" s="348"/>
-      <c r="I20" s="576"/>
-      <c r="J20" s="347"/>
-      <c r="K20" s="347"/>
-      <c r="L20" s="347"/>
-      <c r="M20" s="348"/>
+      <c r="D20" s="346"/>
+      <c r="E20" s="346"/>
+      <c r="F20" s="346"/>
+      <c r="G20" s="347"/>
+      <c r="I20" s="575"/>
+      <c r="J20" s="346"/>
+      <c r="K20" s="346"/>
+      <c r="L20" s="346"/>
+      <c r="M20" s="347"/>
       <c r="N20" s="257"/>
       <c r="O20" s="248"/>
     </row>
@@ -48731,15 +48731,15 @@
       <c r="A21" s="32"/>
       <c r="B21" s="247"/>
       <c r="C21" s="33"/>
-      <c r="D21" s="347"/>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
-      <c r="G21" s="348"/>
-      <c r="I21" s="576"/>
-      <c r="J21" s="347"/>
-      <c r="K21" s="347"/>
-      <c r="L21" s="347"/>
-      <c r="M21" s="348"/>
+      <c r="D21" s="346"/>
+      <c r="E21" s="346"/>
+      <c r="F21" s="346"/>
+      <c r="G21" s="347"/>
+      <c r="I21" s="575"/>
+      <c r="J21" s="346"/>
+      <c r="K21" s="346"/>
+      <c r="L21" s="346"/>
+      <c r="M21" s="347"/>
       <c r="N21" s="257"/>
       <c r="O21" s="248"/>
     </row>
@@ -48747,15 +48747,15 @@
       <c r="A22" s="32"/>
       <c r="B22" s="247"/>
       <c r="C22" s="33"/>
-      <c r="D22" s="347"/>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
-      <c r="G22" s="348"/>
-      <c r="I22" s="576"/>
-      <c r="J22" s="347"/>
-      <c r="K22" s="347"/>
-      <c r="L22" s="347"/>
-      <c r="M22" s="348"/>
+      <c r="D22" s="346"/>
+      <c r="E22" s="346"/>
+      <c r="F22" s="346"/>
+      <c r="G22" s="347"/>
+      <c r="I22" s="575"/>
+      <c r="J22" s="346"/>
+      <c r="K22" s="346"/>
+      <c r="L22" s="346"/>
+      <c r="M22" s="347"/>
       <c r="N22" s="257"/>
       <c r="O22" s="248"/>
     </row>
@@ -48763,15 +48763,15 @@
       <c r="A23" s="32"/>
       <c r="B23" s="247"/>
       <c r="C23" s="34"/>
-      <c r="D23" s="347"/>
-      <c r="E23" s="347"/>
-      <c r="F23" s="347"/>
-      <c r="G23" s="348"/>
-      <c r="I23" s="576"/>
-      <c r="J23" s="347"/>
-      <c r="K23" s="347"/>
-      <c r="L23" s="347"/>
-      <c r="M23" s="348"/>
+      <c r="D23" s="346"/>
+      <c r="E23" s="346"/>
+      <c r="F23" s="346"/>
+      <c r="G23" s="347"/>
+      <c r="I23" s="575"/>
+      <c r="J23" s="346"/>
+      <c r="K23" s="346"/>
+      <c r="L23" s="346"/>
+      <c r="M23" s="347"/>
       <c r="N23" s="257"/>
       <c r="O23" s="248"/>
     </row>
@@ -48779,15 +48779,15 @@
       <c r="A24" s="32"/>
       <c r="B24" s="247"/>
       <c r="C24" s="33"/>
-      <c r="D24" s="347"/>
-      <c r="E24" s="347"/>
-      <c r="F24" s="347"/>
-      <c r="G24" s="348"/>
-      <c r="I24" s="576"/>
-      <c r="J24" s="347"/>
-      <c r="K24" s="347"/>
-      <c r="L24" s="347"/>
-      <c r="M24" s="348"/>
+      <c r="D24" s="346"/>
+      <c r="E24" s="346"/>
+      <c r="F24" s="346"/>
+      <c r="G24" s="347"/>
+      <c r="I24" s="575"/>
+      <c r="J24" s="346"/>
+      <c r="K24" s="346"/>
+      <c r="L24" s="346"/>
+      <c r="M24" s="347"/>
       <c r="N24" s="257"/>
       <c r="O24" s="248"/>
     </row>
@@ -48795,15 +48795,15 @@
       <c r="A25" s="32"/>
       <c r="B25" s="247"/>
       <c r="C25" s="33"/>
-      <c r="D25" s="347"/>
-      <c r="E25" s="347"/>
-      <c r="F25" s="347"/>
-      <c r="G25" s="348"/>
-      <c r="I25" s="576"/>
-      <c r="J25" s="347"/>
-      <c r="K25" s="347"/>
-      <c r="L25" s="347"/>
-      <c r="M25" s="348"/>
+      <c r="D25" s="346"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
+      <c r="G25" s="347"/>
+      <c r="I25" s="575"/>
+      <c r="J25" s="346"/>
+      <c r="K25" s="346"/>
+      <c r="L25" s="346"/>
+      <c r="M25" s="347"/>
       <c r="N25" s="257"/>
       <c r="O25" s="248"/>
     </row>
@@ -48811,15 +48811,15 @@
       <c r="A26" s="32"/>
       <c r="B26" s="247"/>
       <c r="C26" s="33"/>
-      <c r="D26" s="347"/>
-      <c r="E26" s="347"/>
-      <c r="F26" s="347"/>
-      <c r="G26" s="348"/>
-      <c r="I26" s="577"/>
-      <c r="J26" s="349"/>
-      <c r="K26" s="349"/>
-      <c r="L26" s="349"/>
-      <c r="M26" s="350"/>
+      <c r="D26" s="346"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
+      <c r="G26" s="347"/>
+      <c r="I26" s="576"/>
+      <c r="J26" s="348"/>
+      <c r="K26" s="348"/>
+      <c r="L26" s="348"/>
+      <c r="M26" s="349"/>
       <c r="N26" s="257"/>
       <c r="O26" s="248"/>
     </row>
@@ -48827,23 +48827,23 @@
       <c r="A27" s="32"/>
       <c r="B27" s="247"/>
       <c r="C27" s="33"/>
-      <c r="D27" s="347"/>
-      <c r="E27" s="347"/>
-      <c r="F27" s="347"/>
-      <c r="G27" s="348"/>
+      <c r="D27" s="346"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
+      <c r="G27" s="347"/>
       <c r="N27" s="257"/>
       <c r="O27" s="248"/>
     </row>
     <row r="28" spans="1:15" ht="23.25" customHeight="1" thickBot="1">
       <c r="A28" s="32"/>
       <c r="B28" s="247"/>
-      <c r="C28" s="306"/>
-      <c r="D28" s="349"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
-      <c r="G28" s="350"/>
-      <c r="I28" s="574"/>
-      <c r="J28" s="574"/>
+      <c r="C28" s="305"/>
+      <c r="D28" s="348"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="348"/>
+      <c r="G28" s="349"/>
+      <c r="I28" s="573"/>
+      <c r="J28" s="573"/>
       <c r="N28" s="257"/>
       <c r="O28" s="248"/>
     </row>
@@ -48855,58 +48855,58 @@
     <row r="30" spans="1:15" ht="42" customHeight="1" thickBot="1">
       <c r="A30" s="32"/>
       <c r="B30" s="249"/>
-      <c r="C30" s="645" t="s">
+      <c r="C30" s="644" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="646"/>
-      <c r="E30" s="646"/>
-      <c r="F30" s="646"/>
-      <c r="G30" s="647"/>
+      <c r="D30" s="645"/>
+      <c r="E30" s="645"/>
+      <c r="F30" s="645"/>
+      <c r="G30" s="646"/>
       <c r="N30" s="257"/>
       <c r="O30" s="248"/>
     </row>
     <row r="31" spans="1:15" ht="49.5" customHeight="1">
       <c r="A31" s="32"/>
       <c r="B31" s="247"/>
-      <c r="C31" s="637" t="s">
+      <c r="C31" s="636" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="638"/>
-      <c r="E31" s="639" t="s">
+      <c r="D31" s="637"/>
+      <c r="E31" s="638" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="639"/>
-      <c r="G31" s="640"/>
+      <c r="F31" s="638"/>
+      <c r="G31" s="639"/>
       <c r="N31" s="257"/>
       <c r="O31" s="248"/>
     </row>
     <row r="32" spans="1:15" ht="60" customHeight="1">
       <c r="A32" s="32"/>
       <c r="B32" s="247"/>
-      <c r="C32" s="641" t="s">
+      <c r="C32" s="640" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="642"/>
-      <c r="E32" s="643" t="s">
+      <c r="D32" s="641"/>
+      <c r="E32" s="642" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="643"/>
-      <c r="G32" s="644"/>
+      <c r="F32" s="642"/>
+      <c r="G32" s="643"/>
       <c r="N32" s="257"/>
       <c r="O32" s="248"/>
     </row>
     <row r="33" spans="1:15" ht="66.75" customHeight="1" thickBot="1">
       <c r="A33" s="32"/>
       <c r="B33" s="249"/>
-      <c r="C33" s="622" t="s">
+      <c r="C33" s="621" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="623"/>
-      <c r="E33" s="624" t="s">
+      <c r="D33" s="622"/>
+      <c r="E33" s="623" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="624"/>
-      <c r="G33" s="625"/>
+      <c r="F33" s="623"/>
+      <c r="G33" s="624"/>
       <c r="H33" s="253"/>
       <c r="J33" s="255"/>
       <c r="K33" s="255"/>
@@ -49004,9 +49004,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="653"/>
-      <c r="C1" s="654"/>
-      <c r="D1" s="655"/>
+      <c r="B1" s="647"/>
+      <c r="C1" s="648"/>
+      <c r="D1" s="649"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -49028,10 +49028,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="662" t="s">
+      <c r="I2" s="660" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="663"/>
+      <c r="J2" s="661"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -49081,29 +49081,29 @@
     </row>
     <row r="5" spans="1:17" ht="78" customHeight="1" thickBot="1">
       <c r="A5" s="89"/>
-      <c r="B5" s="378" t="s">
+      <c r="B5" s="377" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="656" t="s">
+      <c r="C5" s="653" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="657"/>
-      <c r="E5" s="375" t="s">
+      <c r="D5" s="654"/>
+      <c r="E5" s="374" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="375" t="s">
+      <c r="F5" s="374" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="375" t="s">
+      <c r="G5" s="374" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="376" t="s">
+      <c r="H5" s="375" t="s">
         <v>118</v>
       </c>
-      <c r="I5" s="376" t="s">
+      <c r="I5" s="375" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="377" t="s">
+      <c r="J5" s="376" t="s">
         <v>63</v>
       </c>
       <c r="K5" s="205"/>
@@ -49115,14 +49115,14 @@
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
       <c r="B6" s="215"/>
-      <c r="C6" s="658"/>
-      <c r="D6" s="659"/>
-      <c r="E6" s="459"/>
-      <c r="F6" s="459"/>
-      <c r="G6" s="459"/>
-      <c r="H6" s="459"/>
-      <c r="I6" s="459"/>
-      <c r="J6" s="462"/>
+      <c r="C6" s="655"/>
+      <c r="D6" s="656"/>
+      <c r="E6" s="458"/>
+      <c r="F6" s="458"/>
+      <c r="G6" s="458"/>
+      <c r="H6" s="458"/>
+      <c r="I6" s="458"/>
+      <c r="J6" s="461"/>
       <c r="K6" s="116"/>
       <c r="L6" s="82"/>
       <c r="M6" s="82"/>
@@ -49134,14 +49134,14 @@
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="99"/>
       <c r="B7" s="216"/>
-      <c r="C7" s="660"/>
-      <c r="D7" s="661"/>
-      <c r="E7" s="460"/>
-      <c r="F7" s="460"/>
-      <c r="G7" s="460"/>
-      <c r="H7" s="460"/>
-      <c r="I7" s="460"/>
-      <c r="J7" s="463"/>
+      <c r="C7" s="657"/>
+      <c r="D7" s="658"/>
+      <c r="E7" s="459"/>
+      <c r="F7" s="459"/>
+      <c r="G7" s="459"/>
+      <c r="H7" s="459"/>
+      <c r="I7" s="459"/>
+      <c r="J7" s="462"/>
       <c r="L7" s="82"/>
       <c r="M7" s="82"/>
       <c r="N7" s="82"/>
@@ -49151,14 +49151,14 @@
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="100"/>
       <c r="B8" s="216"/>
-      <c r="C8" s="660"/>
-      <c r="D8" s="661"/>
-      <c r="E8" s="460"/>
-      <c r="F8" s="460"/>
-      <c r="G8" s="460"/>
-      <c r="H8" s="460"/>
-      <c r="I8" s="460"/>
-      <c r="J8" s="463"/>
+      <c r="C8" s="657"/>
+      <c r="D8" s="658"/>
+      <c r="E8" s="459"/>
+      <c r="F8" s="459"/>
+      <c r="G8" s="459"/>
+      <c r="H8" s="459"/>
+      <c r="I8" s="459"/>
+      <c r="J8" s="462"/>
       <c r="K8" s="206"/>
       <c r="L8" s="82"/>
       <c r="M8" s="82"/>
@@ -49169,14 +49169,14 @@
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="100"/>
       <c r="B9" s="216"/>
-      <c r="C9" s="660"/>
-      <c r="D9" s="661"/>
-      <c r="E9" s="460"/>
-      <c r="F9" s="460"/>
-      <c r="G9" s="460"/>
-      <c r="H9" s="460"/>
-      <c r="I9" s="460"/>
-      <c r="J9" s="463"/>
+      <c r="C9" s="657"/>
+      <c r="D9" s="658"/>
+      <c r="E9" s="459"/>
+      <c r="F9" s="459"/>
+      <c r="G9" s="459"/>
+      <c r="H9" s="459"/>
+      <c r="I9" s="459"/>
+      <c r="J9" s="462"/>
       <c r="K9" s="152"/>
       <c r="L9" s="82"/>
       <c r="M9" s="82"/>
@@ -49188,14 +49188,14 @@
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="102"/>
       <c r="B10" s="216"/>
-      <c r="C10" s="660"/>
-      <c r="D10" s="661"/>
-      <c r="E10" s="460"/>
-      <c r="F10" s="460"/>
-      <c r="G10" s="460"/>
-      <c r="H10" s="460"/>
-      <c r="I10" s="460"/>
-      <c r="J10" s="463"/>
+      <c r="C10" s="657"/>
+      <c r="D10" s="658"/>
+      <c r="E10" s="459"/>
+      <c r="F10" s="459"/>
+      <c r="G10" s="459"/>
+      <c r="H10" s="459"/>
+      <c r="I10" s="459"/>
+      <c r="J10" s="462"/>
       <c r="K10" s="116"/>
       <c r="L10" s="82"/>
       <c r="M10" s="82"/>
@@ -49203,123 +49203,121 @@
       <c r="O10" s="81"/>
       <c r="P10" s="82"/>
     </row>
-    <row r="11" spans="1:17" ht="44.25" customHeight="1">
+    <row r="11" spans="1:17" ht="55.5" customHeight="1">
       <c r="A11" s="101"/>
       <c r="B11" s="216"/>
-      <c r="C11" s="660"/>
-      <c r="D11" s="661"/>
-      <c r="E11" s="460"/>
-      <c r="F11" s="460"/>
-      <c r="G11" s="460"/>
-      <c r="H11" s="460"/>
-      <c r="I11" s="460"/>
-      <c r="J11" s="463"/>
+      <c r="C11" s="657"/>
+      <c r="D11" s="659"/>
+      <c r="E11" s="459"/>
+      <c r="F11" s="459"/>
+      <c r="G11" s="459"/>
+      <c r="H11" s="459"/>
+      <c r="I11" s="459"/>
+      <c r="J11" s="462"/>
       <c r="L11" s="82"/>
       <c r="M11" s="90"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="89"/>
+      <c r="N11" s="90"/>
+      <c r="O11" s="98"/>
       <c r="P11" s="82"/>
-      <c r="Q11" s="103"/>
-    </row>
-    <row r="12" spans="1:17" ht="66.75" customHeight="1" thickBot="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="217"/>
-      <c r="C12" s="648"/>
-      <c r="D12" s="649"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
-      <c r="G12" s="461"/>
-      <c r="H12" s="461"/>
-      <c r="I12" s="461"/>
-      <c r="J12" s="464"/>
-      <c r="K12" s="206"/>
+    </row>
+    <row r="12" spans="1:17" ht="44.25" customHeight="1">
+      <c r="A12" s="101"/>
+      <c r="B12" s="216"/>
+      <c r="C12" s="657"/>
+      <c r="D12" s="658"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
+      <c r="G12" s="459"/>
+      <c r="H12" s="459"/>
+      <c r="I12" s="459"/>
+      <c r="J12" s="462"/>
       <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="82"/>
+      <c r="M12" s="90"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="89"/>
       <c r="P12" s="82"/>
       <c r="Q12" s="103"/>
     </row>
-    <row r="13" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A13" s="79"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="107"/>
-      <c r="F13" s="124"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="125"/>
-      <c r="K13" s="103"/>
+    <row r="13" spans="1:17" ht="66.75" customHeight="1" thickBot="1">
+      <c r="A13" s="100"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="662"/>
+      <c r="D13" s="663"/>
+      <c r="E13" s="460"/>
+      <c r="F13" s="460"/>
+      <c r="G13" s="460"/>
+      <c r="H13" s="460"/>
+      <c r="I13" s="460"/>
+      <c r="J13" s="463"/>
+      <c r="K13" s="206"/>
       <c r="L13" s="82"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="82"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="104"/>
       <c r="O13" s="82"/>
-      <c r="P13" s="79"/>
-    </row>
-    <row r="14" spans="1:17" ht="30.75" customHeight="1" thickBot="1">
+      <c r="P13" s="82"/>
+      <c r="Q13" s="103"/>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" thickBot="1">
       <c r="A14" s="79"/>
-      <c r="B14" s="482" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="480"/>
-      <c r="D14" s="289" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="126"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="301"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="107"/>
+      <c r="F14" s="124"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="103"/>
       <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="82"/>
       <c r="O14" s="82"/>
       <c r="P14" s="79"/>
     </row>
-    <row r="15" spans="1:17" ht="8.25" customHeight="1" thickBot="1">
-      <c r="A15" s="87"/>
-      <c r="B15" s="481"/>
-      <c r="C15" s="300"/>
-      <c r="D15" s="290"/>
-      <c r="E15" s="291"/>
-      <c r="F15" s="291"/>
-      <c r="G15" s="292"/>
-      <c r="H15" s="291"/>
-      <c r="I15" s="292"/>
-      <c r="J15" s="293"/>
+    <row r="15" spans="1:17" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A15" s="79"/>
+      <c r="B15" s="481" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="479"/>
+      <c r="D15" s="289" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="126"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="301"/>
       <c r="L15" s="82"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="79"/>
+      <c r="M15" s="82"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="82"/>
       <c r="P15" s="79"/>
     </row>
-    <row r="16" spans="1:17" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A16" s="79"/>
-      <c r="B16" s="484" t="s">
+    <row r="16" spans="1:17" ht="8.25" customHeight="1" thickBot="1">
+      <c r="A16" s="87"/>
+      <c r="B16" s="480"/>
+      <c r="C16" s="300"/>
+      <c r="D16" s="290"/>
+      <c r="E16" s="291"/>
+      <c r="F16" s="291"/>
+      <c r="G16" s="292"/>
+      <c r="H16" s="291"/>
+      <c r="I16" s="292"/>
+      <c r="J16" s="293"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="79"/>
+      <c r="P16" s="79"/>
+    </row>
+    <row r="17" spans="1:16" ht="74.25" customHeight="1" thickBot="1">
+      <c r="A17" s="79"/>
+      <c r="B17" s="483" t="s">
         <v>145</v>
       </c>
-      <c r="C16" s="483"/>
-      <c r="D16" s="294"/>
-      <c r="E16" s="650"/>
-      <c r="F16" s="651"/>
-      <c r="G16" s="651"/>
-      <c r="H16" s="651"/>
-      <c r="I16" s="651"/>
-      <c r="J16" s="652"/>
-      <c r="K16" s="302"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="112"/>
-      <c r="P16" s="79"/>
-    </row>
-    <row r="17" spans="1:16" ht="108.75" customHeight="1" thickBot="1">
-      <c r="A17" s="87"/>
-      <c r="B17" s="486" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="485"/>
+      <c r="C17" s="482"/>
       <c r="D17" s="294"/>
       <c r="E17" s="650"/>
       <c r="F17" s="651"/>
@@ -49327,98 +49325,100 @@
       <c r="H17" s="651"/>
       <c r="I17" s="651"/>
       <c r="J17" s="652"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="115"/>
-      <c r="O17" s="82"/>
+      <c r="K17" s="302"/>
+      <c r="L17" s="115"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="112"/>
       <c r="P17" s="79"/>
     </row>
-    <row r="18" spans="1:16" ht="87" customHeight="1" thickBot="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="486" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="485"/>
-      <c r="D18" s="295"/>
+    <row r="18" spans="1:16" ht="108.75" customHeight="1" thickBot="1">
+      <c r="A18" s="87"/>
+      <c r="B18" s="485" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="484"/>
+      <c r="D18" s="294"/>
       <c r="E18" s="650"/>
       <c r="F18" s="651"/>
       <c r="G18" s="651"/>
       <c r="H18" s="651"/>
       <c r="I18" s="651"/>
       <c r="J18" s="652"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="111"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="87"/>
-    </row>
-    <row r="19" spans="1:16" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A19" s="82"/>
-      <c r="B19" s="87"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="296"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="115"/>
+      <c r="O18" s="82"/>
+      <c r="P18" s="79"/>
+    </row>
+    <row r="19" spans="1:16" ht="87" customHeight="1" thickBot="1">
+      <c r="A19" s="78"/>
+      <c r="B19" s="485" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="484"/>
+      <c r="D19" s="295"/>
       <c r="E19" s="650"/>
       <c r="F19" s="651"/>
       <c r="G19" s="651"/>
       <c r="H19" s="651"/>
       <c r="I19" s="651"/>
       <c r="J19" s="652"/>
-      <c r="K19" s="136"/>
-      <c r="L19" s="123"/>
+      <c r="L19" s="115"/>
       <c r="M19" s="111"/>
       <c r="N19" s="110"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="78"/>
-    </row>
-    <row r="20" spans="1:16" ht="108" customHeight="1" thickBot="1">
-      <c r="A20" s="79"/>
-      <c r="B20" s="90"/>
-      <c r="D20" s="295"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="87"/>
+    </row>
+    <row r="20" spans="1:16" ht="74.25" customHeight="1" thickBot="1">
+      <c r="A20" s="82"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="296"/>
       <c r="E20" s="650"/>
       <c r="F20" s="651"/>
       <c r="G20" s="651"/>
       <c r="H20" s="651"/>
       <c r="I20" s="651"/>
       <c r="J20" s="652"/>
-      <c r="K20" s="303"/>
-      <c r="L20" s="297"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="112"/>
-      <c r="O20" s="110"/>
-    </row>
-    <row r="21" spans="1:16" s="226" customFormat="1" ht="81.75" customHeight="1" thickBot="1">
-      <c r="B21" s="227"/>
-      <c r="C21" s="228"/>
-      <c r="D21" s="298"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="78"/>
+    </row>
+    <row r="21" spans="1:16" ht="108" customHeight="1" thickBot="1">
+      <c r="A21" s="79"/>
+      <c r="B21" s="90"/>
+      <c r="D21" s="295"/>
       <c r="E21" s="650"/>
       <c r="F21" s="651"/>
       <c r="G21" s="651"/>
       <c r="H21" s="651"/>
       <c r="I21" s="651"/>
       <c r="J21" s="652"/>
-      <c r="K21" s="304"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="112"/>
+      <c r="K21" s="303"/>
+      <c r="L21" s="297"/>
+      <c r="M21" s="114"/>
       <c r="N21" s="112"/>
-      <c r="O21" s="117"/>
-    </row>
-    <row r="22" spans="1:16" ht="98.25" customHeight="1" thickBot="1">
-      <c r="A22" s="83"/>
-      <c r="B22" s="106"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="305"/>
+      <c r="O21" s="110"/>
+    </row>
+    <row r="22" spans="1:16" s="226" customFormat="1" ht="81.75" customHeight="1" thickBot="1">
+      <c r="B22" s="227"/>
+      <c r="C22" s="228"/>
+      <c r="D22" s="298"/>
       <c r="E22" s="650"/>
       <c r="F22" s="651"/>
       <c r="G22" s="651"/>
       <c r="H22" s="651"/>
       <c r="I22" s="651"/>
       <c r="J22" s="652"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="115"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="58"/>
+      <c r="K22" s="304"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="117"/>
     </row>
     <row r="23" spans="1:16" ht="23.25" customHeight="1">
       <c r="A23" s="83"/>
@@ -49832,21 +49832,21 @@
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="E18:J18"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="C12:D12"/>
     <mergeCell ref="E20:J20"/>
+    <mergeCell ref="B1:D1"/>
     <mergeCell ref="E19:J19"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E18:J18"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C11:D11"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -49856,17 +49856,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd0678842d65e4207392abd035356b9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d84746cc30da1fe182e7a313d44b54c" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -50121,7 +50110,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -50130,24 +50119,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE64779-B9F2-4AEC-A5E9-E8076DA89A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50166,10 +50149,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB47E070-1B7A-4E34-8FC7-E99E753E25DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77263F2E-038A-4143-B0B5-FFD96533B3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7965" yWindow="1395" windowWidth="15015" windowHeight="12210" tabRatio="719" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -29463,7 +29463,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341394"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341434"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29528,7 +29528,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341395"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341435"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29645,7 +29645,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341396"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341436"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29710,7 +29710,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341397"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341437"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29775,7 +29775,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341398"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341438"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29840,7 +29840,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341399"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341439"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29905,7 +29905,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341400"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341440"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29970,7 +29970,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341401"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341441"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30035,7 +30035,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341402"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341442"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30100,7 +30100,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341403"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341443"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>

--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77263F2E-038A-4143-B0B5-FFD96533B3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00297E93-2A58-4D44-BF89-21DE2E91BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7965" yWindow="1395" windowWidth="15015" windowHeight="12210" tabRatio="719" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7380" yWindow="0" windowWidth="21525" windowHeight="11295" tabRatio="719" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -29463,7 +29463,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341434"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341654"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29528,7 +29528,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341435"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341655"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29645,7 +29645,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341436"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341656"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29710,7 +29710,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341437"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341657"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29775,7 +29775,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341438"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341658"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29840,7 +29840,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341439"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341659"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29905,7 +29905,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341440"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341660"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29970,7 +29970,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341441"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341661"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30035,7 +30035,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341442"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341662"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30100,7 +30100,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341443"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341663"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -44009,7 +44009,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="5" scale="50" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="51" max="18" man="1"/>
   </rowBreaks>

--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00297E93-2A58-4D44-BF89-21DE2E91BD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED8162D-5640-4BD1-B5D7-F199452B0956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="0" windowWidth="21525" windowHeight="11295" tabRatio="719" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -7526,15 +7526,42 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="70" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7544,36 +7571,9 @@
     <xf numFmtId="0" fontId="32" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="72" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -7691,6 +7691,27 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7700,15 +7721,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="87" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7730,18 +7742,6 @@
     <xf numFmtId="14" fontId="63" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7784,17 +7784,266 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -7802,9 +8051,6 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7856,9 +8102,6 @@
     <xf numFmtId="0" fontId="40" fillId="13" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="47" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -7883,249 +8126,6 @@
     <xf numFmtId="0" fontId="50" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -8138,6 +8138,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="323" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="328" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="330" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="331" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="325" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="326" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8210,89 +8294,95 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="303" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="304" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="79" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="79" fillId="13" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="323" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="328" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="325" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="326" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="330" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="331" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="177" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8321,12 +8411,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="61" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8354,89 +8438,521 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="298" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="295" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="216" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="217" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="217" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="238" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="265" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="79" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="264" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="79" fillId="13" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="231" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="233" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="234" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="235" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="234" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="235" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="276" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="261" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="238" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="239" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="277" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="262" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="239" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="273" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="274" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="275" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="284" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="285" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="215" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="267" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="214" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="259" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="271" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="270" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="272" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="189" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="250" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="256" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="257" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="258" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="303" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="304" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="257" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="268" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8462,15 +8978,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="234" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="235" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -8485,513 +8992,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="284" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="215" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="259" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="234" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="235" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="271" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="270" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="272" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="189" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="250" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="256" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="257" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="264" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="231" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="233" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="258" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="257" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="273" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="274" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="275" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="285" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="238" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="238" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="265" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="267" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="214" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="239" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="239" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="276" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="261" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="277" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="262" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="298" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="295" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="216" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="217" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="217" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -29463,7 +29463,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341654"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341884"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29528,7 +29528,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341655"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341885"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29645,7 +29645,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341656"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341886"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29710,7 +29710,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341657"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341887"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29775,7 +29775,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341658"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341888"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29840,7 +29840,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341659"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341889"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29905,7 +29905,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341660"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341890"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29970,7 +29970,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341661"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341891"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30035,7 +30035,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341662"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341892"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30100,7 +30100,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341663"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341893"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -34292,9 +34292,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="647"/>
-      <c r="C1" s="648"/>
-      <c r="D1" s="649"/>
+      <c r="B1" s="654"/>
+      <c r="C1" s="655"/>
+      <c r="D1" s="656"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -34316,10 +34316,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="660" t="s">
+      <c r="I2" s="650" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="661"/>
+      <c r="J2" s="651"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -34372,10 +34372,10 @@
       <c r="B5" s="566" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="653" t="s">
+      <c r="C5" s="657" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="654"/>
+      <c r="D5" s="658"/>
       <c r="E5" s="567" t="s">
         <v>60</v>
       </c>
@@ -34422,8 +34422,8 @@
     <row r="7" spans="1:17" ht="28.5">
       <c r="A7" s="79"/>
       <c r="B7" s="216"/>
-      <c r="C7" s="657"/>
-      <c r="D7" s="659"/>
+      <c r="C7" s="661"/>
+      <c r="D7" s="663"/>
       <c r="E7" s="458"/>
       <c r="F7" s="458"/>
       <c r="G7" s="458"/>
@@ -34591,12 +34591,12 @@
       </c>
       <c r="C16" s="489"/>
       <c r="D16" s="294"/>
-      <c r="E16" s="650"/>
-      <c r="F16" s="651"/>
-      <c r="G16" s="651"/>
-      <c r="H16" s="651"/>
-      <c r="I16" s="651"/>
-      <c r="J16" s="652"/>
+      <c r="E16" s="647"/>
+      <c r="F16" s="648"/>
+      <c r="G16" s="648"/>
+      <c r="H16" s="648"/>
+      <c r="I16" s="648"/>
+      <c r="J16" s="649"/>
       <c r="K16" s="301"/>
       <c r="L16" s="115"/>
       <c r="M16" s="115"/>
@@ -34611,12 +34611,12 @@
       </c>
       <c r="C17" s="488"/>
       <c r="D17" s="294"/>
-      <c r="E17" s="650"/>
-      <c r="F17" s="651"/>
-      <c r="G17" s="651"/>
-      <c r="H17" s="651"/>
-      <c r="I17" s="651"/>
-      <c r="J17" s="652"/>
+      <c r="E17" s="647"/>
+      <c r="F17" s="648"/>
+      <c r="G17" s="648"/>
+      <c r="H17" s="648"/>
+      <c r="I17" s="648"/>
+      <c r="J17" s="649"/>
       <c r="K17" s="136"/>
       <c r="L17" s="115"/>
       <c r="M17" s="115"/>
@@ -35185,32 +35185,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="178"/>
-      <c r="B1" s="687" t="s">
+      <c r="B1" s="769" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="688"/>
-      <c r="D1" s="688"/>
-      <c r="E1" s="688"/>
-      <c r="F1" s="688"/>
-      <c r="G1" s="688"/>
-      <c r="H1" s="688"/>
-      <c r="I1" s="688"/>
-      <c r="J1" s="688"/>
-      <c r="K1" s="688"/>
-      <c r="L1" s="688"/>
-      <c r="M1" s="688"/>
-      <c r="N1" s="688"/>
-      <c r="O1" s="688"/>
-      <c r="P1" s="688"/>
-      <c r="Q1" s="688"/>
-      <c r="R1" s="688"/>
-      <c r="S1" s="688"/>
-      <c r="T1" s="688"/>
-      <c r="U1" s="688"/>
-      <c r="V1" s="688"/>
-      <c r="W1" s="688"/>
-      <c r="X1" s="688"/>
-      <c r="Y1" s="689"/>
+      <c r="C1" s="770"/>
+      <c r="D1" s="770"/>
+      <c r="E1" s="770"/>
+      <c r="F1" s="770"/>
+      <c r="G1" s="770"/>
+      <c r="H1" s="770"/>
+      <c r="I1" s="770"/>
+      <c r="J1" s="770"/>
+      <c r="K1" s="770"/>
+      <c r="L1" s="770"/>
+      <c r="M1" s="770"/>
+      <c r="N1" s="770"/>
+      <c r="O1" s="770"/>
+      <c r="P1" s="770"/>
+      <c r="Q1" s="770"/>
+      <c r="R1" s="770"/>
+      <c r="S1" s="770"/>
+      <c r="T1" s="770"/>
+      <c r="U1" s="770"/>
+      <c r="V1" s="770"/>
+      <c r="W1" s="770"/>
+      <c r="X1" s="770"/>
+      <c r="Y1" s="771"/>
       <c r="Z1" s="173"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -35246,32 +35246,32 @@
       <c r="A3" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="690" t="s">
+      <c r="B3" s="772" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="691"/>
-      <c r="D3" s="691"/>
-      <c r="E3" s="691"/>
-      <c r="F3" s="691"/>
-      <c r="G3" s="691"/>
-      <c r="H3" s="691"/>
-      <c r="I3" s="691"/>
-      <c r="J3" s="691"/>
-      <c r="K3" s="691"/>
-      <c r="L3" s="691"/>
-      <c r="M3" s="691"/>
-      <c r="N3" s="691"/>
-      <c r="O3" s="691"/>
-      <c r="P3" s="691"/>
-      <c r="Q3" s="691"/>
-      <c r="R3" s="691"/>
-      <c r="S3" s="691"/>
-      <c r="T3" s="691"/>
-      <c r="U3" s="691"/>
-      <c r="V3" s="691"/>
-      <c r="W3" s="691"/>
-      <c r="X3" s="691"/>
-      <c r="Y3" s="692"/>
+      <c r="C3" s="773"/>
+      <c r="D3" s="773"/>
+      <c r="E3" s="773"/>
+      <c r="F3" s="773"/>
+      <c r="G3" s="773"/>
+      <c r="H3" s="773"/>
+      <c r="I3" s="773"/>
+      <c r="J3" s="773"/>
+      <c r="K3" s="773"/>
+      <c r="L3" s="773"/>
+      <c r="M3" s="773"/>
+      <c r="N3" s="773"/>
+      <c r="O3" s="773"/>
+      <c r="P3" s="773"/>
+      <c r="Q3" s="773"/>
+      <c r="R3" s="773"/>
+      <c r="S3" s="773"/>
+      <c r="T3" s="773"/>
+      <c r="U3" s="773"/>
+      <c r="V3" s="773"/>
+      <c r="W3" s="773"/>
+      <c r="X3" s="773"/>
+      <c r="Y3" s="774"/>
       <c r="Z3" s="174"/>
       <c r="AA3" s="103"/>
     </row>
@@ -35279,32 +35279,32 @@
       <c r="A4" s="180" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="693" t="s">
+      <c r="B4" s="775" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="694"/>
-      <c r="D4" s="694"/>
-      <c r="E4" s="694"/>
-      <c r="F4" s="694"/>
-      <c r="G4" s="694"/>
-      <c r="H4" s="694"/>
-      <c r="I4" s="694"/>
-      <c r="J4" s="694"/>
-      <c r="K4" s="694"/>
-      <c r="L4" s="694"/>
-      <c r="M4" s="694"/>
-      <c r="N4" s="694"/>
-      <c r="O4" s="694"/>
-      <c r="P4" s="694"/>
-      <c r="Q4" s="694"/>
-      <c r="R4" s="694"/>
-      <c r="S4" s="694"/>
-      <c r="T4" s="694"/>
-      <c r="U4" s="694"/>
-      <c r="V4" s="694"/>
-      <c r="W4" s="694"/>
-      <c r="X4" s="694"/>
-      <c r="Y4" s="695"/>
+      <c r="C4" s="776"/>
+      <c r="D4" s="776"/>
+      <c r="E4" s="776"/>
+      <c r="F4" s="776"/>
+      <c r="G4" s="776"/>
+      <c r="H4" s="776"/>
+      <c r="I4" s="776"/>
+      <c r="J4" s="776"/>
+      <c r="K4" s="776"/>
+      <c r="L4" s="776"/>
+      <c r="M4" s="776"/>
+      <c r="N4" s="776"/>
+      <c r="O4" s="776"/>
+      <c r="P4" s="776"/>
+      <c r="Q4" s="776"/>
+      <c r="R4" s="776"/>
+      <c r="S4" s="776"/>
+      <c r="T4" s="776"/>
+      <c r="U4" s="776"/>
+      <c r="V4" s="776"/>
+      <c r="W4" s="776"/>
+      <c r="X4" s="776"/>
+      <c r="Y4" s="777"/>
       <c r="Z4" s="175"/>
       <c r="AA4" s="103"/>
     </row>
@@ -35339,40 +35339,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="181"/>
-      <c r="B6" s="699" t="s">
+      <c r="B6" s="781" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="700"/>
-      <c r="D6" s="700"/>
-      <c r="E6" s="701"/>
+      <c r="C6" s="782"/>
+      <c r="D6" s="782"/>
+      <c r="E6" s="783"/>
       <c r="F6" s="89"/>
       <c r="G6" s="142"/>
-      <c r="H6" s="719" t="s">
+      <c r="H6" s="747" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="720"/>
-      <c r="J6" s="720"/>
-      <c r="K6" s="721"/>
+      <c r="I6" s="748"/>
+      <c r="J6" s="748"/>
+      <c r="K6" s="749"/>
       <c r="L6" s="89"/>
       <c r="M6" s="142"/>
-      <c r="N6" s="727" t="s">
+      <c r="N6" s="759" t="s">
         <v>95</v>
       </c>
-      <c r="O6" s="728"/>
-      <c r="P6" s="729"/>
+      <c r="O6" s="760"/>
+      <c r="P6" s="761"/>
       <c r="Q6" s="149"/>
       <c r="R6" s="151"/>
-      <c r="S6" s="679" t="s">
+      <c r="S6" s="754" t="s">
         <v>77</v>
       </c>
-      <c r="T6" s="680"/>
+      <c r="T6" s="755"/>
       <c r="U6" s="152"/>
       <c r="V6" s="156"/>
       <c r="W6" s="143"/>
-      <c r="X6" s="679" t="s">
+      <c r="X6" s="754" t="s">
         <v>78</v>
       </c>
-      <c r="Y6" s="680"/>
+      <c r="Y6" s="755"/>
       <c r="Z6" s="80"/>
       <c r="AA6" s="103"/>
     </row>
@@ -35392,36 +35392,36 @@
       </c>
       <c r="F7" s="89"/>
       <c r="G7" s="116"/>
-      <c r="H7" s="715">
+      <c r="H7" s="756">
         <f>I23</f>
         <v>0</v>
       </c>
-      <c r="I7" s="726"/>
-      <c r="J7" s="726"/>
-      <c r="K7" s="716"/>
+      <c r="I7" s="758"/>
+      <c r="J7" s="758"/>
+      <c r="K7" s="757"/>
       <c r="L7" s="89"/>
       <c r="M7" s="116"/>
-      <c r="N7" s="711">
+      <c r="N7" s="762">
         <f>L23</f>
         <v>0</v>
       </c>
-      <c r="O7" s="712"/>
-      <c r="P7" s="713"/>
+      <c r="O7" s="763"/>
+      <c r="P7" s="764"/>
       <c r="Q7" s="150"/>
       <c r="R7" s="152"/>
-      <c r="S7" s="715">
+      <c r="S7" s="756">
         <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T7" s="716"/>
+      <c r="T7" s="757"/>
       <c r="U7" s="89"/>
       <c r="V7" s="155"/>
       <c r="W7" s="82"/>
-      <c r="X7" s="715">
+      <c r="X7" s="756">
         <f>R23</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="716"/>
+      <c r="Y7" s="757"/>
       <c r="Z7" s="141"/>
       <c r="AA7" s="103"/>
     </row>
@@ -35490,27 +35490,27 @@
       <c r="D10" s="134"/>
       <c r="E10" s="199"/>
       <c r="F10" s="89"/>
-      <c r="G10" s="707" t="s">
+      <c r="G10" s="788" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="708"/>
-      <c r="I10" s="708"/>
-      <c r="J10" s="708"/>
-      <c r="K10" s="708"/>
-      <c r="L10" s="708"/>
-      <c r="M10" s="708"/>
-      <c r="N10" s="708"/>
-      <c r="O10" s="708"/>
-      <c r="P10" s="708"/>
-      <c r="Q10" s="708"/>
-      <c r="R10" s="708"/>
-      <c r="S10" s="708"/>
-      <c r="T10" s="708"/>
-      <c r="U10" s="708"/>
-      <c r="V10" s="708"/>
-      <c r="W10" s="708"/>
-      <c r="X10" s="708"/>
-      <c r="Y10" s="709"/>
+      <c r="H10" s="789"/>
+      <c r="I10" s="789"/>
+      <c r="J10" s="789"/>
+      <c r="K10" s="789"/>
+      <c r="L10" s="789"/>
+      <c r="M10" s="789"/>
+      <c r="N10" s="789"/>
+      <c r="O10" s="789"/>
+      <c r="P10" s="789"/>
+      <c r="Q10" s="789"/>
+      <c r="R10" s="789"/>
+      <c r="S10" s="789"/>
+      <c r="T10" s="789"/>
+      <c r="U10" s="789"/>
+      <c r="V10" s="789"/>
+      <c r="W10" s="789"/>
+      <c r="X10" s="789"/>
+      <c r="Y10" s="790"/>
       <c r="Z10" s="80"/>
       <c r="AA10" s="103"/>
     </row>
@@ -35521,35 +35521,35 @@
       <c r="D11" s="134"/>
       <c r="E11" s="199"/>
       <c r="F11" s="89"/>
-      <c r="G11" s="710" t="s">
+      <c r="G11" s="791" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="705"/>
-      <c r="I11" s="705" t="s">
+      <c r="H11" s="786"/>
+      <c r="I11" s="786" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="705"/>
-      <c r="K11" s="705"/>
-      <c r="L11" s="705" t="s">
+      <c r="J11" s="786"/>
+      <c r="K11" s="786"/>
+      <c r="L11" s="786" t="s">
         <v>82</v>
       </c>
-      <c r="M11" s="705"/>
-      <c r="N11" s="705"/>
-      <c r="O11" s="705" t="s">
+      <c r="M11" s="786"/>
+      <c r="N11" s="786"/>
+      <c r="O11" s="786" t="s">
         <v>83</v>
       </c>
-      <c r="P11" s="705"/>
-      <c r="Q11" s="705"/>
-      <c r="R11" s="705" t="s">
+      <c r="P11" s="786"/>
+      <c r="Q11" s="786"/>
+      <c r="R11" s="786" t="s">
         <v>78</v>
       </c>
-      <c r="S11" s="705"/>
-      <c r="T11" s="705"/>
-      <c r="U11" s="705"/>
-      <c r="V11" s="705"/>
-      <c r="W11" s="705"/>
-      <c r="X11" s="705"/>
-      <c r="Y11" s="706"/>
+      <c r="S11" s="786"/>
+      <c r="T11" s="786"/>
+      <c r="U11" s="786"/>
+      <c r="V11" s="786"/>
+      <c r="W11" s="786"/>
+      <c r="X11" s="786"/>
+      <c r="Y11" s="787"/>
       <c r="Z11" s="80"/>
       <c r="AA11" s="103"/>
     </row>
@@ -35560,33 +35560,33 @@
       <c r="D12" s="185"/>
       <c r="E12" s="199"/>
       <c r="F12" s="89"/>
-      <c r="G12" s="710"/>
-      <c r="H12" s="705"/>
-      <c r="I12" s="705"/>
-      <c r="J12" s="705"/>
-      <c r="K12" s="705"/>
-      <c r="L12" s="705"/>
-      <c r="M12" s="705"/>
-      <c r="N12" s="705"/>
-      <c r="O12" s="705"/>
-      <c r="P12" s="705"/>
-      <c r="Q12" s="705"/>
-      <c r="R12" s="681" t="s">
+      <c r="G12" s="791"/>
+      <c r="H12" s="786"/>
+      <c r="I12" s="786"/>
+      <c r="J12" s="786"/>
+      <c r="K12" s="786"/>
+      <c r="L12" s="786"/>
+      <c r="M12" s="786"/>
+      <c r="N12" s="786"/>
+      <c r="O12" s="786"/>
+      <c r="P12" s="786"/>
+      <c r="Q12" s="786"/>
+      <c r="R12" s="713" t="s">
         <v>84</v>
       </c>
-      <c r="S12" s="681"/>
-      <c r="T12" s="681" t="s">
+      <c r="S12" s="713"/>
+      <c r="T12" s="713" t="s">
         <v>85</v>
       </c>
-      <c r="U12" s="681"/>
-      <c r="V12" s="681" t="s">
+      <c r="U12" s="713"/>
+      <c r="V12" s="713" t="s">
         <v>86</v>
       </c>
-      <c r="W12" s="681"/>
-      <c r="X12" s="681" t="s">
+      <c r="W12" s="713"/>
+      <c r="X12" s="713" t="s">
         <v>87</v>
       </c>
-      <c r="Y12" s="702"/>
+      <c r="Y12" s="744"/>
       <c r="Z12" s="80"/>
       <c r="AA12" s="79"/>
     </row>
@@ -35597,25 +35597,25 @@
       <c r="D13" s="134"/>
       <c r="E13" s="199"/>
       <c r="F13" s="89"/>
-      <c r="G13" s="710"/>
-      <c r="H13" s="705"/>
-      <c r="I13" s="705"/>
-      <c r="J13" s="705"/>
-      <c r="K13" s="705"/>
-      <c r="L13" s="705"/>
-      <c r="M13" s="705"/>
-      <c r="N13" s="705"/>
-      <c r="O13" s="705"/>
-      <c r="P13" s="705"/>
-      <c r="Q13" s="705"/>
-      <c r="R13" s="681"/>
-      <c r="S13" s="681"/>
-      <c r="T13" s="681"/>
-      <c r="U13" s="681"/>
-      <c r="V13" s="681"/>
-      <c r="W13" s="681"/>
-      <c r="X13" s="703"/>
-      <c r="Y13" s="704"/>
+      <c r="G13" s="791"/>
+      <c r="H13" s="786"/>
+      <c r="I13" s="786"/>
+      <c r="J13" s="786"/>
+      <c r="K13" s="786"/>
+      <c r="L13" s="786"/>
+      <c r="M13" s="786"/>
+      <c r="N13" s="786"/>
+      <c r="O13" s="786"/>
+      <c r="P13" s="786"/>
+      <c r="Q13" s="786"/>
+      <c r="R13" s="713"/>
+      <c r="S13" s="713"/>
+      <c r="T13" s="713"/>
+      <c r="U13" s="713"/>
+      <c r="V13" s="713"/>
+      <c r="W13" s="713"/>
+      <c r="X13" s="784"/>
+      <c r="Y13" s="785"/>
       <c r="Z13" s="80"/>
       <c r="AA13" s="81"/>
     </row>
@@ -35626,27 +35626,27 @@
       <c r="D14" s="134"/>
       <c r="E14" s="199"/>
       <c r="F14" s="89"/>
-      <c r="G14" s="682" t="s">
+      <c r="G14" s="765" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="683"/>
-      <c r="I14" s="684"/>
-      <c r="J14" s="685"/>
-      <c r="K14" s="686"/>
-      <c r="L14" s="678"/>
-      <c r="M14" s="678"/>
-      <c r="N14" s="678"/>
-      <c r="O14" s="678"/>
-      <c r="P14" s="678"/>
-      <c r="Q14" s="678"/>
-      <c r="R14" s="678"/>
-      <c r="S14" s="678"/>
-      <c r="T14" s="678"/>
-      <c r="U14" s="678"/>
-      <c r="V14" s="678"/>
-      <c r="W14" s="684"/>
-      <c r="X14" s="678"/>
-      <c r="Y14" s="714"/>
+      <c r="H14" s="766"/>
+      <c r="I14" s="743"/>
+      <c r="J14" s="767"/>
+      <c r="K14" s="768"/>
+      <c r="L14" s="741"/>
+      <c r="M14" s="741"/>
+      <c r="N14" s="741"/>
+      <c r="O14" s="741"/>
+      <c r="P14" s="741"/>
+      <c r="Q14" s="741"/>
+      <c r="R14" s="741"/>
+      <c r="S14" s="741"/>
+      <c r="T14" s="741"/>
+      <c r="U14" s="741"/>
+      <c r="V14" s="741"/>
+      <c r="W14" s="743"/>
+      <c r="X14" s="741"/>
+      <c r="Y14" s="742"/>
       <c r="Z14" s="80"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -35656,27 +35656,27 @@
       <c r="D15" s="186"/>
       <c r="E15" s="200"/>
       <c r="F15" s="89"/>
-      <c r="G15" s="682" t="s">
+      <c r="G15" s="765" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="683"/>
-      <c r="I15" s="684"/>
-      <c r="J15" s="685"/>
-      <c r="K15" s="686"/>
-      <c r="L15" s="678"/>
-      <c r="M15" s="678"/>
-      <c r="N15" s="678"/>
-      <c r="O15" s="678"/>
-      <c r="P15" s="678"/>
-      <c r="Q15" s="678"/>
-      <c r="R15" s="678"/>
-      <c r="S15" s="678"/>
-      <c r="T15" s="678"/>
-      <c r="U15" s="678"/>
-      <c r="V15" s="678"/>
-      <c r="W15" s="684"/>
-      <c r="X15" s="678"/>
-      <c r="Y15" s="714"/>
+      <c r="H15" s="766"/>
+      <c r="I15" s="743"/>
+      <c r="J15" s="767"/>
+      <c r="K15" s="768"/>
+      <c r="L15" s="741"/>
+      <c r="M15" s="741"/>
+      <c r="N15" s="741"/>
+      <c r="O15" s="741"/>
+      <c r="P15" s="741"/>
+      <c r="Q15" s="741"/>
+      <c r="R15" s="741"/>
+      <c r="S15" s="741"/>
+      <c r="T15" s="741"/>
+      <c r="U15" s="741"/>
+      <c r="V15" s="741"/>
+      <c r="W15" s="743"/>
+      <c r="X15" s="741"/>
+      <c r="Y15" s="742"/>
       <c r="Z15" s="80"/>
       <c r="AA15" s="103"/>
     </row>
@@ -35687,61 +35687,61 @@
       <c r="D16" s="106"/>
       <c r="E16" s="106"/>
       <c r="F16" s="79"/>
-      <c r="G16" s="682" t="s">
+      <c r="G16" s="765" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="683"/>
-      <c r="I16" s="684"/>
-      <c r="J16" s="685"/>
-      <c r="K16" s="686"/>
-      <c r="L16" s="678"/>
-      <c r="M16" s="678"/>
-      <c r="N16" s="678"/>
-      <c r="O16" s="678"/>
-      <c r="P16" s="678"/>
-      <c r="Q16" s="678"/>
-      <c r="R16" s="678"/>
-      <c r="S16" s="678"/>
-      <c r="T16" s="678"/>
-      <c r="U16" s="678"/>
-      <c r="V16" s="678"/>
-      <c r="W16" s="684"/>
-      <c r="X16" s="678"/>
-      <c r="Y16" s="714"/>
+      <c r="H16" s="766"/>
+      <c r="I16" s="743"/>
+      <c r="J16" s="767"/>
+      <c r="K16" s="768"/>
+      <c r="L16" s="741"/>
+      <c r="M16" s="741"/>
+      <c r="N16" s="741"/>
+      <c r="O16" s="741"/>
+      <c r="P16" s="741"/>
+      <c r="Q16" s="741"/>
+      <c r="R16" s="741"/>
+      <c r="S16" s="741"/>
+      <c r="T16" s="741"/>
+      <c r="U16" s="741"/>
+      <c r="V16" s="741"/>
+      <c r="W16" s="743"/>
+      <c r="X16" s="741"/>
+      <c r="Y16" s="742"/>
       <c r="Z16" s="80"/>
       <c r="AA16" s="103"/>
       <c r="AB16" s="194"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="79"/>
-      <c r="B17" s="696" t="s">
+      <c r="B17" s="778" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="697"/>
-      <c r="D17" s="697"/>
-      <c r="E17" s="698"/>
+      <c r="C17" s="779"/>
+      <c r="D17" s="779"/>
+      <c r="E17" s="780"/>
       <c r="F17" s="89"/>
-      <c r="G17" s="682" t="s">
+      <c r="G17" s="765" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="683"/>
-      <c r="I17" s="684"/>
-      <c r="J17" s="685"/>
-      <c r="K17" s="686"/>
-      <c r="L17" s="678"/>
-      <c r="M17" s="678"/>
-      <c r="N17" s="678"/>
-      <c r="O17" s="678"/>
-      <c r="P17" s="678"/>
-      <c r="Q17" s="678"/>
-      <c r="R17" s="678"/>
-      <c r="S17" s="678"/>
-      <c r="T17" s="678"/>
-      <c r="U17" s="678"/>
-      <c r="V17" s="678"/>
-      <c r="W17" s="684"/>
-      <c r="X17" s="678"/>
-      <c r="Y17" s="714"/>
+      <c r="H17" s="766"/>
+      <c r="I17" s="743"/>
+      <c r="J17" s="767"/>
+      <c r="K17" s="768"/>
+      <c r="L17" s="741"/>
+      <c r="M17" s="741"/>
+      <c r="N17" s="741"/>
+      <c r="O17" s="741"/>
+      <c r="P17" s="741"/>
+      <c r="Q17" s="741"/>
+      <c r="R17" s="741"/>
+      <c r="S17" s="741"/>
+      <c r="T17" s="741"/>
+      <c r="U17" s="741"/>
+      <c r="V17" s="741"/>
+      <c r="W17" s="743"/>
+      <c r="X17" s="741"/>
+      <c r="Y17" s="742"/>
       <c r="Z17" s="80"/>
       <c r="AA17" s="103"/>
     </row>
@@ -35760,27 +35760,27 @@
         <v>91</v>
       </c>
       <c r="F18" s="89"/>
-      <c r="G18" s="682" t="s">
+      <c r="G18" s="765" t="s">
         <v>167</v>
       </c>
-      <c r="H18" s="683"/>
-      <c r="I18" s="684"/>
-      <c r="J18" s="685"/>
-      <c r="K18" s="686"/>
-      <c r="L18" s="678"/>
-      <c r="M18" s="678"/>
-      <c r="N18" s="678"/>
-      <c r="O18" s="678"/>
-      <c r="P18" s="678"/>
-      <c r="Q18" s="678"/>
-      <c r="R18" s="678"/>
-      <c r="S18" s="678"/>
-      <c r="T18" s="678"/>
-      <c r="U18" s="678"/>
-      <c r="V18" s="678"/>
-      <c r="W18" s="684"/>
-      <c r="X18" s="678"/>
-      <c r="Y18" s="714"/>
+      <c r="H18" s="766"/>
+      <c r="I18" s="743"/>
+      <c r="J18" s="767"/>
+      <c r="K18" s="768"/>
+      <c r="L18" s="741"/>
+      <c r="M18" s="741"/>
+      <c r="N18" s="741"/>
+      <c r="O18" s="741"/>
+      <c r="P18" s="741"/>
+      <c r="Q18" s="741"/>
+      <c r="R18" s="741"/>
+      <c r="S18" s="741"/>
+      <c r="T18" s="741"/>
+      <c r="U18" s="741"/>
+      <c r="V18" s="741"/>
+      <c r="W18" s="743"/>
+      <c r="X18" s="741"/>
+      <c r="Y18" s="742"/>
       <c r="Z18" s="80"/>
       <c r="AA18" s="103"/>
     </row>
@@ -35791,27 +35791,27 @@
       <c r="D19" s="544"/>
       <c r="E19" s="201"/>
       <c r="F19" s="89"/>
-      <c r="G19" s="682" t="s">
+      <c r="G19" s="765" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="683"/>
-      <c r="I19" s="684"/>
-      <c r="J19" s="685"/>
-      <c r="K19" s="686"/>
-      <c r="L19" s="678"/>
-      <c r="M19" s="678"/>
-      <c r="N19" s="678"/>
-      <c r="O19" s="678"/>
-      <c r="P19" s="678"/>
-      <c r="Q19" s="678"/>
-      <c r="R19" s="678"/>
-      <c r="S19" s="678"/>
-      <c r="T19" s="678"/>
-      <c r="U19" s="678"/>
-      <c r="V19" s="678"/>
-      <c r="W19" s="684"/>
-      <c r="X19" s="678"/>
-      <c r="Y19" s="714"/>
+      <c r="H19" s="766"/>
+      <c r="I19" s="743"/>
+      <c r="J19" s="767"/>
+      <c r="K19" s="768"/>
+      <c r="L19" s="741"/>
+      <c r="M19" s="741"/>
+      <c r="N19" s="741"/>
+      <c r="O19" s="741"/>
+      <c r="P19" s="741"/>
+      <c r="Q19" s="741"/>
+      <c r="R19" s="741"/>
+      <c r="S19" s="741"/>
+      <c r="T19" s="741"/>
+      <c r="U19" s="741"/>
+      <c r="V19" s="741"/>
+      <c r="W19" s="743"/>
+      <c r="X19" s="741"/>
+      <c r="Y19" s="742"/>
       <c r="Z19" s="80"/>
       <c r="AA19" s="103"/>
     </row>
@@ -35822,27 +35822,27 @@
       <c r="D20" s="544"/>
       <c r="E20" s="201"/>
       <c r="F20" s="89"/>
-      <c r="G20" s="682" t="s">
+      <c r="G20" s="765" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="683"/>
-      <c r="I20" s="684"/>
-      <c r="J20" s="685"/>
-      <c r="K20" s="686"/>
-      <c r="L20" s="678"/>
-      <c r="M20" s="678"/>
-      <c r="N20" s="678"/>
-      <c r="O20" s="678"/>
-      <c r="P20" s="678"/>
-      <c r="Q20" s="678"/>
-      <c r="R20" s="678"/>
-      <c r="S20" s="678"/>
-      <c r="T20" s="678"/>
-      <c r="U20" s="678"/>
-      <c r="V20" s="678"/>
-      <c r="W20" s="684"/>
-      <c r="X20" s="678"/>
-      <c r="Y20" s="714"/>
+      <c r="H20" s="766"/>
+      <c r="I20" s="743"/>
+      <c r="J20" s="767"/>
+      <c r="K20" s="768"/>
+      <c r="L20" s="741"/>
+      <c r="M20" s="741"/>
+      <c r="N20" s="741"/>
+      <c r="O20" s="741"/>
+      <c r="P20" s="741"/>
+      <c r="Q20" s="741"/>
+      <c r="R20" s="741"/>
+      <c r="S20" s="741"/>
+      <c r="T20" s="741"/>
+      <c r="U20" s="741"/>
+      <c r="V20" s="741"/>
+      <c r="W20" s="743"/>
+      <c r="X20" s="741"/>
+      <c r="Y20" s="742"/>
       <c r="Z20" s="80"/>
       <c r="AA20" s="103"/>
     </row>
@@ -35853,27 +35853,27 @@
       <c r="D21" s="544"/>
       <c r="E21" s="201"/>
       <c r="F21" s="89"/>
-      <c r="G21" s="682" t="s">
+      <c r="G21" s="765" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="683"/>
-      <c r="I21" s="684"/>
-      <c r="J21" s="685"/>
-      <c r="K21" s="686"/>
-      <c r="L21" s="678"/>
-      <c r="M21" s="678"/>
-      <c r="N21" s="678"/>
-      <c r="O21" s="678"/>
-      <c r="P21" s="678"/>
-      <c r="Q21" s="678"/>
-      <c r="R21" s="678"/>
-      <c r="S21" s="678"/>
-      <c r="T21" s="678"/>
-      <c r="U21" s="678"/>
-      <c r="V21" s="678"/>
-      <c r="W21" s="684"/>
-      <c r="X21" s="678"/>
-      <c r="Y21" s="714"/>
+      <c r="H21" s="766"/>
+      <c r="I21" s="743"/>
+      <c r="J21" s="767"/>
+      <c r="K21" s="768"/>
+      <c r="L21" s="741"/>
+      <c r="M21" s="741"/>
+      <c r="N21" s="741"/>
+      <c r="O21" s="741"/>
+      <c r="P21" s="741"/>
+      <c r="Q21" s="741"/>
+      <c r="R21" s="741"/>
+      <c r="S21" s="741"/>
+      <c r="T21" s="741"/>
+      <c r="U21" s="741"/>
+      <c r="V21" s="741"/>
+      <c r="W21" s="743"/>
+      <c r="X21" s="741"/>
+      <c r="Y21" s="742"/>
       <c r="Z21" s="80"/>
       <c r="AA21" s="103"/>
     </row>
@@ -35884,27 +35884,27 @@
       <c r="D22" s="544"/>
       <c r="E22" s="201"/>
       <c r="F22" s="89"/>
-      <c r="G22" s="682" t="s">
+      <c r="G22" s="765" t="s">
         <v>169</v>
       </c>
-      <c r="H22" s="683"/>
-      <c r="I22" s="684"/>
-      <c r="J22" s="685"/>
-      <c r="K22" s="686"/>
-      <c r="L22" s="678"/>
-      <c r="M22" s="678"/>
-      <c r="N22" s="678"/>
-      <c r="O22" s="678"/>
-      <c r="P22" s="678"/>
-      <c r="Q22" s="678"/>
-      <c r="R22" s="678"/>
-      <c r="S22" s="678"/>
-      <c r="T22" s="678"/>
-      <c r="U22" s="678"/>
-      <c r="V22" s="678"/>
-      <c r="W22" s="684"/>
-      <c r="X22" s="678"/>
-      <c r="Y22" s="714"/>
+      <c r="H22" s="766"/>
+      <c r="I22" s="743"/>
+      <c r="J22" s="767"/>
+      <c r="K22" s="768"/>
+      <c r="L22" s="741"/>
+      <c r="M22" s="741"/>
+      <c r="N22" s="741"/>
+      <c r="O22" s="741"/>
+      <c r="P22" s="741"/>
+      <c r="Q22" s="741"/>
+      <c r="R22" s="741"/>
+      <c r="S22" s="741"/>
+      <c r="T22" s="741"/>
+      <c r="U22" s="741"/>
+      <c r="V22" s="741"/>
+      <c r="W22" s="743"/>
+      <c r="X22" s="741"/>
+      <c r="Y22" s="742"/>
       <c r="Z22" s="80"/>
       <c r="AA22" s="103"/>
     </row>
@@ -35915,48 +35915,48 @@
       <c r="D23" s="545"/>
       <c r="E23" s="202"/>
       <c r="F23" s="89"/>
-      <c r="G23" s="725" t="s">
+      <c r="G23" s="753" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="717"/>
-      <c r="I23" s="717">
+      <c r="H23" s="745"/>
+      <c r="I23" s="745">
         <f>SUM(I14:K22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="717"/>
-      <c r="K23" s="717"/>
-      <c r="L23" s="717">
+      <c r="J23" s="745"/>
+      <c r="K23" s="745"/>
+      <c r="L23" s="745">
         <f>SUM(L14:N22)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="717"/>
-      <c r="N23" s="717"/>
-      <c r="O23" s="722">
+      <c r="M23" s="745"/>
+      <c r="N23" s="745"/>
+      <c r="O23" s="750">
         <f>SUM(O14:Q22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="723"/>
-      <c r="Q23" s="724"/>
-      <c r="R23" s="722">
+      <c r="P23" s="751"/>
+      <c r="Q23" s="752"/>
+      <c r="R23" s="750">
         <f>SUM(R14:S22)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="724"/>
-      <c r="T23" s="722">
+      <c r="S23" s="752"/>
+      <c r="T23" s="750">
         <f>SUM(T14:U22)</f>
         <v>0</v>
       </c>
-      <c r="U23" s="724"/>
-      <c r="V23" s="722">
+      <c r="U23" s="752"/>
+      <c r="V23" s="750">
         <f>SUM(V14:W22)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="723"/>
-      <c r="X23" s="717">
+      <c r="W23" s="751"/>
+      <c r="X23" s="745">
         <f>SUM(X14:Y22)</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="718"/>
+      <c r="Y23" s="746"/>
       <c r="Z23" s="80"/>
       <c r="AA23" s="103"/>
     </row>
@@ -36026,28 +36026,28 @@
       <c r="E26" s="82"/>
       <c r="F26" s="79"/>
       <c r="G26" s="135"/>
-      <c r="H26" s="762" t="s">
+      <c r="H26" s="708" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="763"/>
-      <c r="J26" s="764"/>
+      <c r="I26" s="709"/>
+      <c r="J26" s="710"/>
       <c r="K26" s="89"/>
-      <c r="L26" s="768" t="s">
+      <c r="L26" s="717" t="s">
         <v>96</v>
       </c>
-      <c r="M26" s="769"/>
-      <c r="N26" s="769"/>
-      <c r="O26" s="769"/>
-      <c r="P26" s="769"/>
-      <c r="Q26" s="769"/>
-      <c r="R26" s="769"/>
-      <c r="S26" s="769"/>
-      <c r="T26" s="769"/>
-      <c r="U26" s="769"/>
-      <c r="V26" s="769"/>
-      <c r="W26" s="769"/>
-      <c r="X26" s="769"/>
-      <c r="Y26" s="770"/>
+      <c r="M26" s="718"/>
+      <c r="N26" s="718"/>
+      <c r="O26" s="718"/>
+      <c r="P26" s="718"/>
+      <c r="Q26" s="718"/>
+      <c r="R26" s="718"/>
+      <c r="S26" s="718"/>
+      <c r="T26" s="718"/>
+      <c r="U26" s="718"/>
+      <c r="V26" s="718"/>
+      <c r="W26" s="718"/>
+      <c r="X26" s="718"/>
+      <c r="Y26" s="719"/>
       <c r="Z26" s="80"/>
       <c r="AA26" s="103"/>
     </row>
@@ -36059,41 +36059,41 @@
       <c r="E27" s="82"/>
       <c r="F27" s="79"/>
       <c r="G27" s="136"/>
-      <c r="H27" s="759">
+      <c r="H27" s="690">
         <f>Y38</f>
         <v>0</v>
       </c>
-      <c r="I27" s="760"/>
-      <c r="J27" s="761"/>
+      <c r="I27" s="691"/>
+      <c r="J27" s="692"/>
       <c r="K27" s="89"/>
-      <c r="L27" s="733" t="s">
+      <c r="L27" s="739" t="s">
         <v>80</v>
       </c>
-      <c r="M27" s="681"/>
-      <c r="N27" s="681"/>
-      <c r="O27" s="681" t="s">
+      <c r="M27" s="713"/>
+      <c r="N27" s="713"/>
+      <c r="O27" s="713" t="s">
         <v>97</v>
       </c>
-      <c r="P27" s="681"/>
-      <c r="Q27" s="681" t="s">
+      <c r="P27" s="713"/>
+      <c r="Q27" s="713" t="s">
         <v>98</v>
       </c>
-      <c r="R27" s="681"/>
-      <c r="S27" s="681" t="s">
+      <c r="R27" s="713"/>
+      <c r="S27" s="713" t="s">
         <v>99</v>
       </c>
-      <c r="T27" s="681" t="s">
+      <c r="T27" s="713" t="s">
         <v>100</v>
       </c>
-      <c r="U27" s="681"/>
-      <c r="V27" s="681" t="s">
+      <c r="U27" s="713"/>
+      <c r="V27" s="713" t="s">
         <v>101</v>
       </c>
-      <c r="W27" s="681" t="s">
+      <c r="W27" s="713" t="s">
         <v>102</v>
       </c>
-      <c r="X27" s="681"/>
-      <c r="Y27" s="702" t="s">
+      <c r="X27" s="713"/>
+      <c r="Y27" s="744" t="s">
         <v>88</v>
       </c>
       <c r="Z27" s="80"/>
@@ -36111,20 +36111,20 @@
       <c r="I28" s="82"/>
       <c r="J28" s="165"/>
       <c r="K28" s="89"/>
-      <c r="L28" s="733"/>
-      <c r="M28" s="681"/>
-      <c r="N28" s="681"/>
-      <c r="O28" s="681"/>
-      <c r="P28" s="681"/>
-      <c r="Q28" s="681"/>
-      <c r="R28" s="681"/>
-      <c r="S28" s="681"/>
-      <c r="T28" s="681"/>
-      <c r="U28" s="681"/>
-      <c r="V28" s="681"/>
-      <c r="W28" s="681"/>
-      <c r="X28" s="681"/>
-      <c r="Y28" s="702"/>
+      <c r="L28" s="739"/>
+      <c r="M28" s="713"/>
+      <c r="N28" s="713"/>
+      <c r="O28" s="713"/>
+      <c r="P28" s="713"/>
+      <c r="Q28" s="713"/>
+      <c r="R28" s="713"/>
+      <c r="S28" s="713"/>
+      <c r="T28" s="713"/>
+      <c r="U28" s="713"/>
+      <c r="V28" s="713"/>
+      <c r="W28" s="713"/>
+      <c r="X28" s="713"/>
+      <c r="Y28" s="744"/>
       <c r="Z28" s="80"/>
       <c r="AA28" s="103"/>
     </row>
@@ -36140,21 +36140,21 @@
       <c r="I29" s="166"/>
       <c r="J29" s="138"/>
       <c r="K29" s="89"/>
-      <c r="L29" s="730" t="s">
+      <c r="L29" s="725" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="731"/>
-      <c r="N29" s="731"/>
-      <c r="O29" s="731"/>
-      <c r="P29" s="731"/>
-      <c r="Q29" s="731"/>
-      <c r="R29" s="731"/>
+      <c r="M29" s="693"/>
+      <c r="N29" s="693"/>
+      <c r="O29" s="693"/>
+      <c r="P29" s="693"/>
+      <c r="Q29" s="693"/>
+      <c r="R29" s="693"/>
       <c r="S29" s="71"/>
-      <c r="T29" s="731"/>
-      <c r="U29" s="731"/>
+      <c r="T29" s="693"/>
+      <c r="U29" s="693"/>
       <c r="V29" s="71"/>
-      <c r="W29" s="731"/>
-      <c r="X29" s="732"/>
+      <c r="W29" s="693"/>
+      <c r="X29" s="694"/>
       <c r="Y29" s="195"/>
       <c r="Z29" s="80"/>
       <c r="AA29" s="103"/>
@@ -36171,21 +36171,21 @@
       <c r="I30" s="106"/>
       <c r="J30" s="106"/>
       <c r="K30" s="79"/>
-      <c r="L30" s="730" t="s">
+      <c r="L30" s="725" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="731"/>
-      <c r="N30" s="731"/>
-      <c r="O30" s="731"/>
-      <c r="P30" s="731"/>
-      <c r="Q30" s="731"/>
-      <c r="R30" s="731"/>
+      <c r="M30" s="693"/>
+      <c r="N30" s="693"/>
+      <c r="O30" s="693"/>
+      <c r="P30" s="693"/>
+      <c r="Q30" s="693"/>
+      <c r="R30" s="693"/>
       <c r="S30" s="71"/>
-      <c r="T30" s="731"/>
-      <c r="U30" s="731"/>
+      <c r="T30" s="693"/>
+      <c r="U30" s="693"/>
       <c r="V30" s="71"/>
-      <c r="W30" s="731"/>
-      <c r="X30" s="732"/>
+      <c r="W30" s="693"/>
+      <c r="X30" s="694"/>
       <c r="Y30" s="195"/>
       <c r="Z30" s="80"/>
       <c r="AA30" s="79"/>
@@ -36198,27 +36198,27 @@
       <c r="E31" s="82"/>
       <c r="F31" s="79"/>
       <c r="G31" s="135"/>
-      <c r="H31" s="765" t="s">
+      <c r="H31" s="714" t="s">
         <v>93</v>
       </c>
-      <c r="I31" s="766"/>
-      <c r="J31" s="767"/>
+      <c r="I31" s="715"/>
+      <c r="J31" s="716"/>
       <c r="K31" s="89"/>
-      <c r="L31" s="730" t="s">
+      <c r="L31" s="725" t="s">
         <v>19</v>
       </c>
-      <c r="M31" s="731"/>
-      <c r="N31" s="731"/>
-      <c r="O31" s="731"/>
-      <c r="P31" s="731"/>
-      <c r="Q31" s="731"/>
-      <c r="R31" s="731"/>
+      <c r="M31" s="693"/>
+      <c r="N31" s="693"/>
+      <c r="O31" s="693"/>
+      <c r="P31" s="693"/>
+      <c r="Q31" s="693"/>
+      <c r="R31" s="693"/>
       <c r="S31" s="71"/>
-      <c r="T31" s="731"/>
-      <c r="U31" s="731"/>
+      <c r="T31" s="693"/>
+      <c r="U31" s="693"/>
       <c r="V31" s="71"/>
-      <c r="W31" s="731"/>
-      <c r="X31" s="732"/>
+      <c r="W31" s="693"/>
+      <c r="X31" s="694"/>
       <c r="Y31" s="195"/>
       <c r="Z31" s="80"/>
       <c r="AA31" s="79"/>
@@ -36235,21 +36235,21 @@
       <c r="I32" s="82"/>
       <c r="J32" s="165"/>
       <c r="K32" s="89"/>
-      <c r="L32" s="730" t="s">
+      <c r="L32" s="725" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="731"/>
-      <c r="N32" s="731"/>
-      <c r="O32" s="731"/>
-      <c r="P32" s="731"/>
-      <c r="Q32" s="731"/>
-      <c r="R32" s="731"/>
+      <c r="M32" s="693"/>
+      <c r="N32" s="693"/>
+      <c r="O32" s="693"/>
+      <c r="P32" s="693"/>
+      <c r="Q32" s="693"/>
+      <c r="R32" s="693"/>
       <c r="S32" s="71"/>
-      <c r="T32" s="731"/>
-      <c r="U32" s="731"/>
+      <c r="T32" s="693"/>
+      <c r="U32" s="693"/>
       <c r="V32" s="71"/>
-      <c r="W32" s="731"/>
-      <c r="X32" s="732"/>
+      <c r="W32" s="693"/>
+      <c r="X32" s="694"/>
       <c r="Y32" s="195"/>
       <c r="Z32" s="80"/>
       <c r="AA32" s="79"/>
@@ -36262,28 +36262,28 @@
       <c r="E33" s="82"/>
       <c r="F33" s="79"/>
       <c r="G33" s="136"/>
-      <c r="H33" s="759">
+      <c r="H33" s="690">
         <f>O38</f>
         <v>0</v>
       </c>
-      <c r="I33" s="760"/>
-      <c r="J33" s="761"/>
+      <c r="I33" s="691"/>
+      <c r="J33" s="692"/>
       <c r="K33" s="89"/>
-      <c r="L33" s="730" t="s">
+      <c r="L33" s="725" t="s">
         <v>167</v>
       </c>
-      <c r="M33" s="731"/>
-      <c r="N33" s="731"/>
-      <c r="O33" s="731"/>
-      <c r="P33" s="731"/>
-      <c r="Q33" s="731"/>
-      <c r="R33" s="731"/>
+      <c r="M33" s="693"/>
+      <c r="N33" s="693"/>
+      <c r="O33" s="693"/>
+      <c r="P33" s="693"/>
+      <c r="Q33" s="693"/>
+      <c r="R33" s="693"/>
       <c r="S33" s="71"/>
-      <c r="T33" s="731"/>
-      <c r="U33" s="731"/>
+      <c r="T33" s="693"/>
+      <c r="U33" s="693"/>
       <c r="V33" s="71"/>
-      <c r="W33" s="731"/>
-      <c r="X33" s="732"/>
+      <c r="W33" s="693"/>
+      <c r="X33" s="694"/>
       <c r="Y33" s="195"/>
       <c r="Z33" s="80"/>
       <c r="AA33" s="193"/>
@@ -36300,21 +36300,21 @@
       <c r="I34" s="82"/>
       <c r="J34" s="165"/>
       <c r="K34" s="89"/>
-      <c r="L34" s="730" t="s">
+      <c r="L34" s="725" t="s">
         <v>168</v>
       </c>
-      <c r="M34" s="731"/>
-      <c r="N34" s="731"/>
-      <c r="O34" s="731"/>
-      <c r="P34" s="731"/>
-      <c r="Q34" s="731"/>
-      <c r="R34" s="731"/>
+      <c r="M34" s="693"/>
+      <c r="N34" s="693"/>
+      <c r="O34" s="693"/>
+      <c r="P34" s="693"/>
+      <c r="Q34" s="693"/>
+      <c r="R34" s="693"/>
       <c r="S34" s="71"/>
-      <c r="T34" s="731"/>
-      <c r="U34" s="731"/>
+      <c r="T34" s="693"/>
+      <c r="U34" s="693"/>
       <c r="V34" s="71"/>
-      <c r="W34" s="731"/>
-      <c r="X34" s="732"/>
+      <c r="W34" s="693"/>
+      <c r="X34" s="694"/>
       <c r="Y34" s="195"/>
       <c r="Z34" s="80"/>
       <c r="AA34" s="79"/>
@@ -36331,21 +36331,21 @@
       <c r="I35" s="166"/>
       <c r="J35" s="138"/>
       <c r="K35" s="89"/>
-      <c r="L35" s="730" t="s">
+      <c r="L35" s="725" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="731"/>
-      <c r="N35" s="731"/>
-      <c r="O35" s="734"/>
-      <c r="P35" s="734"/>
-      <c r="Q35" s="734"/>
-      <c r="R35" s="734"/>
+      <c r="M35" s="693"/>
+      <c r="N35" s="693"/>
+      <c r="O35" s="720"/>
+      <c r="P35" s="720"/>
+      <c r="Q35" s="720"/>
+      <c r="R35" s="720"/>
       <c r="S35" s="162"/>
-      <c r="T35" s="734"/>
-      <c r="U35" s="734"/>
+      <c r="T35" s="720"/>
+      <c r="U35" s="720"/>
       <c r="V35" s="162"/>
-      <c r="W35" s="734"/>
-      <c r="X35" s="735"/>
+      <c r="W35" s="720"/>
+      <c r="X35" s="740"/>
       <c r="Y35" s="195"/>
       <c r="Z35" s="80"/>
       <c r="AA35" s="103"/>
@@ -36362,21 +36362,21 @@
       <c r="I36" s="106"/>
       <c r="J36" s="106"/>
       <c r="K36" s="79"/>
-      <c r="L36" s="730" t="s">
+      <c r="L36" s="725" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="731"/>
-      <c r="N36" s="732"/>
-      <c r="O36" s="736"/>
-      <c r="P36" s="736"/>
-      <c r="Q36" s="736"/>
-      <c r="R36" s="736"/>
+      <c r="M36" s="693"/>
+      <c r="N36" s="694"/>
+      <c r="O36" s="697"/>
+      <c r="P36" s="697"/>
+      <c r="Q36" s="697"/>
+      <c r="R36" s="697"/>
       <c r="S36" s="163"/>
-      <c r="T36" s="736"/>
-      <c r="U36" s="736"/>
+      <c r="T36" s="697"/>
+      <c r="U36" s="697"/>
       <c r="V36" s="163"/>
-      <c r="W36" s="736"/>
-      <c r="X36" s="737"/>
+      <c r="W36" s="697"/>
+      <c r="X36" s="721"/>
       <c r="Y36" s="195"/>
       <c r="Z36" s="80"/>
       <c r="AA36" s="79"/>
@@ -36389,27 +36389,27 @@
       <c r="E37" s="82"/>
       <c r="F37" s="79"/>
       <c r="G37" s="135"/>
-      <c r="H37" s="765" t="s">
+      <c r="H37" s="714" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="766"/>
-      <c r="J37" s="767"/>
+      <c r="I37" s="715"/>
+      <c r="J37" s="716"/>
       <c r="K37" s="89"/>
-      <c r="L37" s="730" t="s">
+      <c r="L37" s="725" t="s">
         <v>169</v>
       </c>
-      <c r="M37" s="731"/>
-      <c r="N37" s="732"/>
-      <c r="O37" s="736"/>
-      <c r="P37" s="736"/>
-      <c r="Q37" s="736"/>
-      <c r="R37" s="736"/>
+      <c r="M37" s="693"/>
+      <c r="N37" s="694"/>
+      <c r="O37" s="697"/>
+      <c r="P37" s="697"/>
+      <c r="Q37" s="697"/>
+      <c r="R37" s="697"/>
       <c r="S37" s="163"/>
-      <c r="T37" s="736"/>
-      <c r="U37" s="736"/>
+      <c r="T37" s="697"/>
+      <c r="U37" s="697"/>
       <c r="V37" s="163"/>
-      <c r="W37" s="736"/>
-      <c r="X37" s="737"/>
+      <c r="W37" s="697"/>
+      <c r="X37" s="721"/>
       <c r="Y37" s="195"/>
       <c r="Z37" s="80"/>
     </row>
@@ -36425,39 +36425,39 @@
       <c r="I38" s="82"/>
       <c r="J38" s="165"/>
       <c r="K38" s="89"/>
-      <c r="L38" s="749" t="s">
+      <c r="L38" s="733" t="s">
         <v>88</v>
       </c>
-      <c r="M38" s="750"/>
-      <c r="N38" s="751"/>
-      <c r="O38" s="738">
+      <c r="M38" s="734"/>
+      <c r="N38" s="735"/>
+      <c r="O38" s="698">
         <f>SUM(O29:P37)</f>
         <v>0</v>
       </c>
-      <c r="P38" s="738"/>
-      <c r="Q38" s="738">
+      <c r="P38" s="698"/>
+      <c r="Q38" s="698">
         <f>SUM(Q29:R37)</f>
         <v>0</v>
       </c>
-      <c r="R38" s="738"/>
+      <c r="R38" s="698"/>
       <c r="S38" s="196">
         <f>SUM(S29:S37)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="738">
+      <c r="T38" s="698">
         <f>SUM(T29:U37)</f>
         <v>0</v>
       </c>
-      <c r="U38" s="738"/>
+      <c r="U38" s="698"/>
       <c r="V38" s="196">
         <f>SUM(V29:V37)</f>
         <v>0</v>
       </c>
-      <c r="W38" s="738">
+      <c r="W38" s="698">
         <f>SUM(W29:X37)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="738"/>
+      <c r="X38" s="698"/>
       <c r="Y38" s="197">
         <f>SUM(Y29:Y37)</f>
         <v>0</v>
@@ -36473,26 +36473,26 @@
       <c r="E39" s="82"/>
       <c r="F39" s="79"/>
       <c r="G39" s="136"/>
-      <c r="H39" s="759">
+      <c r="H39" s="690">
         <f>S38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="760"/>
-      <c r="J39" s="761"/>
+      <c r="I39" s="691"/>
+      <c r="J39" s="692"/>
       <c r="K39" s="89"/>
-      <c r="L39" s="744"/>
-      <c r="M39" s="752"/>
-      <c r="N39" s="753"/>
-      <c r="O39" s="744"/>
-      <c r="P39" s="745"/>
-      <c r="Q39" s="757"/>
-      <c r="R39" s="758"/>
+      <c r="L39" s="728"/>
+      <c r="M39" s="736"/>
+      <c r="N39" s="737"/>
+      <c r="O39" s="728"/>
+      <c r="P39" s="729"/>
+      <c r="Q39" s="711"/>
+      <c r="R39" s="712"/>
       <c r="S39" s="104"/>
-      <c r="T39" s="785"/>
-      <c r="U39" s="785"/>
+      <c r="T39" s="699"/>
+      <c r="U39" s="699"/>
       <c r="V39" s="104"/>
-      <c r="W39" s="785"/>
-      <c r="X39" s="785"/>
+      <c r="W39" s="699"/>
+      <c r="X39" s="699"/>
       <c r="Y39" s="132"/>
       <c r="Z39" s="82"/>
       <c r="AA39" s="79"/>
@@ -36509,19 +36509,19 @@
       <c r="I40" s="82"/>
       <c r="J40" s="165"/>
       <c r="K40" s="89"/>
-      <c r="L40" s="754"/>
-      <c r="M40" s="755"/>
-      <c r="N40" s="756"/>
-      <c r="O40" s="746"/>
-      <c r="P40" s="743"/>
-      <c r="Q40" s="742"/>
-      <c r="R40" s="743"/>
+      <c r="L40" s="701"/>
+      <c r="M40" s="738"/>
+      <c r="N40" s="702"/>
+      <c r="O40" s="730"/>
+      <c r="P40" s="727"/>
+      <c r="Q40" s="726"/>
+      <c r="R40" s="727"/>
       <c r="S40" s="82"/>
-      <c r="T40" s="786"/>
-      <c r="U40" s="786"/>
+      <c r="T40" s="700"/>
+      <c r="U40" s="700"/>
       <c r="V40" s="82"/>
-      <c r="W40" s="786"/>
-      <c r="X40" s="786"/>
+      <c r="W40" s="700"/>
+      <c r="X40" s="700"/>
       <c r="Y40" s="140"/>
       <c r="Z40" s="82"/>
     </row>
@@ -36537,19 +36537,19 @@
       <c r="I41" s="166"/>
       <c r="J41" s="138"/>
       <c r="K41" s="89"/>
-      <c r="L41" s="754"/>
-      <c r="M41" s="755"/>
-      <c r="N41" s="756"/>
-      <c r="O41" s="747"/>
-      <c r="P41" s="748"/>
-      <c r="Q41" s="754"/>
-      <c r="R41" s="756"/>
+      <c r="L41" s="701"/>
+      <c r="M41" s="738"/>
+      <c r="N41" s="702"/>
+      <c r="O41" s="731"/>
+      <c r="P41" s="732"/>
+      <c r="Q41" s="701"/>
+      <c r="R41" s="702"/>
       <c r="S41" s="82"/>
-      <c r="T41" s="754"/>
-      <c r="U41" s="756"/>
+      <c r="T41" s="701"/>
+      <c r="U41" s="702"/>
       <c r="V41" s="82"/>
-      <c r="W41" s="754"/>
-      <c r="X41" s="756"/>
+      <c r="W41" s="701"/>
+      <c r="X41" s="702"/>
       <c r="Y41" s="140"/>
       <c r="Z41" s="82"/>
       <c r="AA41" s="103"/>
@@ -36566,21 +36566,21 @@
       <c r="I42" s="106"/>
       <c r="J42" s="106"/>
       <c r="K42" s="79"/>
-      <c r="L42" s="739"/>
-      <c r="M42" s="740"/>
-      <c r="N42" s="741"/>
-      <c r="O42" s="757"/>
-      <c r="P42" s="758"/>
+      <c r="L42" s="722"/>
+      <c r="M42" s="723"/>
+      <c r="N42" s="724"/>
+      <c r="O42" s="711"/>
+      <c r="P42" s="712"/>
       <c r="Q42" s="82"/>
-      <c r="R42" s="783" t="s">
+      <c r="R42" s="695" t="s">
         <v>136</v>
       </c>
-      <c r="S42" s="784"/>
+      <c r="S42" s="696"/>
       <c r="T42" s="105"/>
-      <c r="U42" s="787"/>
-      <c r="V42" s="788"/>
-      <c r="W42" s="787"/>
-      <c r="X42" s="788"/>
+      <c r="U42" s="703"/>
+      <c r="V42" s="704"/>
+      <c r="W42" s="703"/>
+      <c r="X42" s="704"/>
       <c r="Y42" s="140"/>
       <c r="Z42" s="82"/>
       <c r="AA42" s="79"/>
@@ -36593,19 +36593,19 @@
       <c r="E43" s="82"/>
       <c r="F43" s="79"/>
       <c r="G43" s="135"/>
-      <c r="H43" s="790" t="s">
+      <c r="H43" s="706" t="s">
         <v>104</v>
       </c>
-      <c r="I43" s="790"/>
-      <c r="J43" s="791"/>
+      <c r="I43" s="706"/>
+      <c r="J43" s="707"/>
       <c r="K43" s="89"/>
       <c r="L43" s="135"/>
       <c r="M43" s="164"/>
-      <c r="N43" s="774" t="s">
+      <c r="N43" s="681" t="s">
         <v>94</v>
       </c>
-      <c r="O43" s="775"/>
-      <c r="P43" s="776"/>
+      <c r="O43" s="682"/>
+      <c r="P43" s="683"/>
       <c r="Q43" s="136"/>
       <c r="R43" s="264" t="s">
         <v>137</v>
@@ -36659,21 +36659,21 @@
       <c r="E45" s="82"/>
       <c r="F45" s="79"/>
       <c r="G45" s="136"/>
-      <c r="H45" s="759">
+      <c r="H45" s="690">
         <f>SUM(V38)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="760"/>
-      <c r="J45" s="761"/>
+      <c r="I45" s="691"/>
+      <c r="J45" s="692"/>
       <c r="K45" s="89"/>
       <c r="L45" s="136"/>
       <c r="M45" s="82"/>
       <c r="N45" s="82"/>
-      <c r="O45" s="777">
+      <c r="O45" s="684">
         <f>SUM(Q38,T38,W38)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="778"/>
+      <c r="P45" s="685"/>
       <c r="Q45" s="136"/>
       <c r="R45" s="265" t="s">
         <v>138</v>
@@ -36705,8 +36705,8 @@
       <c r="L46" s="136"/>
       <c r="M46" s="82"/>
       <c r="N46" s="82"/>
-      <c r="O46" s="779"/>
-      <c r="P46" s="780"/>
+      <c r="O46" s="686"/>
+      <c r="P46" s="687"/>
       <c r="Q46" s="136"/>
       <c r="R46" s="266"/>
       <c r="S46" s="281"/>
@@ -36817,9 +36817,9 @@
       <c r="E50" s="82"/>
       <c r="F50" s="79"/>
       <c r="G50" s="167"/>
-      <c r="H50" s="781"/>
-      <c r="I50" s="781"/>
-      <c r="J50" s="782"/>
+      <c r="H50" s="688"/>
+      <c r="I50" s="688"/>
+      <c r="J50" s="689"/>
       <c r="K50" s="80"/>
       <c r="L50" s="104"/>
       <c r="M50" s="104"/>
@@ -36874,9 +36874,9 @@
       <c r="E52" s="82"/>
       <c r="F52" s="82"/>
       <c r="G52" s="82"/>
-      <c r="H52" s="789"/>
-      <c r="I52" s="789"/>
-      <c r="J52" s="789"/>
+      <c r="H52" s="705"/>
+      <c r="I52" s="705"/>
+      <c r="J52" s="705"/>
       <c r="K52" s="82"/>
       <c r="L52" s="82"/>
       <c r="M52" s="82"/>
@@ -36977,11 +36977,11 @@
       <c r="U55" s="79"/>
       <c r="V55" s="82"/>
       <c r="W55" s="82"/>
-      <c r="X55" s="771"/>
-      <c r="Y55" s="772"/>
-      <c r="Z55" s="772"/>
-      <c r="AA55" s="772"/>
-      <c r="AB55" s="773"/>
+      <c r="X55" s="678"/>
+      <c r="Y55" s="679"/>
+      <c r="Z55" s="679"/>
+      <c r="AA55" s="679"/>
+      <c r="AB55" s="680"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="82"/>
@@ -37197,11 +37197,11 @@
       <c r="P63" s="82"/>
       <c r="Q63" s="79"/>
       <c r="R63" s="79"/>
-      <c r="U63" s="771"/>
-      <c r="V63" s="772"/>
-      <c r="W63" s="772"/>
-      <c r="X63" s="772"/>
-      <c r="Y63" s="773"/>
+      <c r="U63" s="678"/>
+      <c r="V63" s="679"/>
+      <c r="W63" s="679"/>
+      <c r="X63" s="679"/>
+      <c r="Y63" s="680"/>
       <c r="Z63" s="82"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -37637,6 +37637,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="V12:W13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="X12:Y13"/>
+    <mergeCell ref="R11:Y11"/>
+    <mergeCell ref="G10:Y10"/>
+    <mergeCell ref="G11:H13"/>
+    <mergeCell ref="I11:K13"/>
+    <mergeCell ref="L11:N13"/>
+    <mergeCell ref="O11:Q13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
     <mergeCell ref="U63:Y63"/>
     <mergeCell ref="X55:AB55"/>
     <mergeCell ref="N43:P43"/>
@@ -37661,178 +37833,6 @@
     <mergeCell ref="W41:X41"/>
     <mergeCell ref="W42:X42"/>
     <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="V12:W13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="R11:Y11"/>
-    <mergeCell ref="G10:Y10"/>
-    <mergeCell ref="G11:H13"/>
-    <mergeCell ref="I11:K13"/>
-    <mergeCell ref="L11:N13"/>
-    <mergeCell ref="O11:Q13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="33" priority="10">
@@ -38622,78 +38622,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="837" t="s">
+      <c r="A1" s="802" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="837"/>
-      <c r="C1" s="837"/>
-      <c r="D1" s="837"/>
-      <c r="E1" s="837"/>
-      <c r="F1" s="837"/>
-      <c r="G1" s="837"/>
-      <c r="H1" s="837"/>
-      <c r="I1" s="837"/>
-      <c r="J1" s="837"/>
-      <c r="K1" s="837"/>
-      <c r="L1" s="837"/>
-      <c r="M1" s="837"/>
-      <c r="N1" s="837"/>
-      <c r="O1" s="838"/>
+      <c r="B1" s="802"/>
+      <c r="C1" s="802"/>
+      <c r="D1" s="802"/>
+      <c r="E1" s="802"/>
+      <c r="F1" s="802"/>
+      <c r="G1" s="802"/>
+      <c r="H1" s="802"/>
+      <c r="I1" s="802"/>
+      <c r="J1" s="802"/>
+      <c r="K1" s="802"/>
+      <c r="L1" s="802"/>
+      <c r="M1" s="802"/>
+      <c r="N1" s="802"/>
+      <c r="O1" s="803"/>
     </row>
     <row r="2" spans="1:15" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A2" s="839"/>
-      <c r="B2" s="839"/>
-      <c r="C2" s="839"/>
-      <c r="D2" s="839"/>
-      <c r="E2" s="839"/>
-      <c r="F2" s="839"/>
-      <c r="G2" s="839"/>
-      <c r="H2" s="839"/>
-      <c r="I2" s="839"/>
-      <c r="J2" s="839"/>
-      <c r="K2" s="839"/>
-      <c r="L2" s="839"/>
-      <c r="M2" s="839"/>
-      <c r="N2" s="839"/>
-      <c r="O2" s="840"/>
+      <c r="A2" s="804"/>
+      <c r="B2" s="804"/>
+      <c r="C2" s="804"/>
+      <c r="D2" s="804"/>
+      <c r="E2" s="804"/>
+      <c r="F2" s="804"/>
+      <c r="G2" s="804"/>
+      <c r="H2" s="804"/>
+      <c r="I2" s="804"/>
+      <c r="J2" s="804"/>
+      <c r="K2" s="804"/>
+      <c r="L2" s="804"/>
+      <c r="M2" s="804"/>
+      <c r="N2" s="804"/>
+      <c r="O2" s="805"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="841" t="s">
+      <c r="A3" s="806" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="841"/>
-      <c r="C3" s="841"/>
-      <c r="D3" s="841"/>
-      <c r="E3" s="841"/>
-      <c r="F3" s="841"/>
-      <c r="G3" s="841"/>
-      <c r="H3" s="841"/>
-      <c r="I3" s="841"/>
-      <c r="J3" s="841"/>
-      <c r="K3" s="841"/>
-      <c r="L3" s="841"/>
-      <c r="M3" s="841"/>
-      <c r="N3" s="841"/>
-      <c r="O3" s="842"/>
+      <c r="B3" s="806"/>
+      <c r="C3" s="806"/>
+      <c r="D3" s="806"/>
+      <c r="E3" s="806"/>
+      <c r="F3" s="806"/>
+      <c r="G3" s="806"/>
+      <c r="H3" s="806"/>
+      <c r="I3" s="806"/>
+      <c r="J3" s="806"/>
+      <c r="K3" s="806"/>
+      <c r="L3" s="806"/>
+      <c r="M3" s="806"/>
+      <c r="N3" s="806"/>
+      <c r="O3" s="807"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" thickBot="1">
-      <c r="A4" s="843" t="s">
+      <c r="A4" s="808" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="843"/>
-      <c r="C4" s="843"/>
-      <c r="D4" s="843"/>
-      <c r="E4" s="843"/>
-      <c r="F4" s="843"/>
-      <c r="G4" s="843"/>
-      <c r="H4" s="843"/>
-      <c r="I4" s="843"/>
-      <c r="J4" s="843"/>
-      <c r="K4" s="843"/>
-      <c r="L4" s="843"/>
-      <c r="M4" s="843"/>
-      <c r="N4" s="843"/>
-      <c r="O4" s="844"/>
+      <c r="B4" s="808"/>
+      <c r="C4" s="808"/>
+      <c r="D4" s="808"/>
+      <c r="E4" s="808"/>
+      <c r="F4" s="808"/>
+      <c r="G4" s="808"/>
+      <c r="H4" s="808"/>
+      <c r="I4" s="808"/>
+      <c r="J4" s="808"/>
+      <c r="K4" s="808"/>
+      <c r="L4" s="808"/>
+      <c r="M4" s="808"/>
+      <c r="N4" s="808"/>
+      <c r="O4" s="809"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" thickBot="1">
       <c r="A5" s="90"/>
@@ -38705,8 +38705,8 @@
       <c r="G5" s="512"/>
       <c r="H5" s="510"/>
       <c r="I5" s="82"/>
-      <c r="J5" s="845"/>
-      <c r="K5" s="845"/>
+      <c r="J5" s="810"/>
+      <c r="K5" s="810"/>
       <c r="L5" s="515"/>
       <c r="M5" s="512"/>
       <c r="N5" s="516"/>
@@ -38779,24 +38779,24 @@
       <c r="E8" s="106"/>
       <c r="F8" s="90"/>
       <c r="G8" s="104"/>
-      <c r="H8" s="835"/>
-      <c r="I8" s="836"/>
-      <c r="J8" s="835"/>
-      <c r="K8" s="835"/>
-      <c r="L8" s="835"/>
-      <c r="M8" s="835"/>
+      <c r="H8" s="800"/>
+      <c r="I8" s="801"/>
+      <c r="J8" s="800"/>
+      <c r="K8" s="800"/>
+      <c r="L8" s="800"/>
+      <c r="M8" s="800"/>
       <c r="N8" s="517"/>
       <c r="O8" s="404"/>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1">
-      <c r="A9" s="800" t="s">
+      <c r="A9" s="828" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="801"/>
-      <c r="C9" s="801"/>
-      <c r="D9" s="801"/>
-      <c r="E9" s="801"/>
-      <c r="F9" s="802"/>
+      <c r="B9" s="829"/>
+      <c r="C9" s="829"/>
+      <c r="D9" s="829"/>
+      <c r="E9" s="829"/>
+      <c r="F9" s="830"/>
       <c r="G9" s="83"/>
       <c r="H9" s="494"/>
       <c r="I9" s="499"/>
@@ -38808,12 +38808,12 @@
       <c r="O9" s="232"/>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A10" s="803"/>
-      <c r="B10" s="804"/>
-      <c r="C10" s="804"/>
-      <c r="D10" s="804"/>
-      <c r="E10" s="804"/>
-      <c r="F10" s="805"/>
+      <c r="A10" s="831"/>
+      <c r="B10" s="832"/>
+      <c r="C10" s="832"/>
+      <c r="D10" s="832"/>
+      <c r="E10" s="832"/>
+      <c r="F10" s="833"/>
       <c r="G10" s="80"/>
       <c r="H10" s="82"/>
       <c r="I10" s="497"/>
@@ -38825,22 +38825,22 @@
       <c r="O10" s="404"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="816" t="s">
+      <c r="A11" s="844" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="811" t="s">
+      <c r="B11" s="839" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="813" t="s">
+      <c r="C11" s="841" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="815" t="s">
+      <c r="D11" s="843" t="s">
         <v>154</v>
       </c>
-      <c r="E11" s="796" t="s">
+      <c r="E11" s="824" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="797"/>
+      <c r="F11" s="825"/>
       <c r="G11" s="80"/>
       <c r="H11" s="82"/>
       <c r="I11" s="497"/>
@@ -38852,12 +38852,12 @@
       <c r="O11" s="404"/>
     </row>
     <row r="12" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A12" s="817"/>
-      <c r="B12" s="812"/>
-      <c r="C12" s="814"/>
-      <c r="D12" s="803"/>
-      <c r="E12" s="798"/>
-      <c r="F12" s="799"/>
+      <c r="A12" s="845"/>
+      <c r="B12" s="840"/>
+      <c r="C12" s="842"/>
+      <c r="D12" s="831"/>
+      <c r="E12" s="826"/>
+      <c r="F12" s="827"/>
       <c r="G12" s="80"/>
       <c r="H12" s="82"/>
       <c r="I12" s="497"/>
@@ -38875,11 +38875,11 @@
       <c r="B13" s="552"/>
       <c r="C13" s="552"/>
       <c r="D13" s="553"/>
-      <c r="E13" s="806">
+      <c r="E13" s="834">
         <f>SUM(B13:D13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="807"/>
+      <c r="F13" s="835"/>
       <c r="G13" s="80"/>
       <c r="H13" s="82"/>
       <c r="I13" s="82"/>
@@ -38897,11 +38897,11 @@
       <c r="B14" s="502"/>
       <c r="C14" s="502"/>
       <c r="D14" s="554"/>
-      <c r="E14" s="808">
+      <c r="E14" s="836">
         <f>SUM(B14:D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="809"/>
+      <c r="F14" s="837"/>
       <c r="G14" s="80"/>
       <c r="H14" s="82"/>
       <c r="I14" s="497"/>
@@ -38919,11 +38919,11 @@
       <c r="B15" s="505"/>
       <c r="C15" s="505"/>
       <c r="D15" s="506"/>
-      <c r="E15" s="818">
+      <c r="E15" s="846">
         <f>SUM(B15:D15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="819"/>
+      <c r="F15" s="847"/>
       <c r="G15" s="80"/>
       <c r="H15" s="82"/>
       <c r="I15" s="497"/>
@@ -38958,11 +38958,11 @@
       <c r="D17" s="82"/>
       <c r="E17" s="89"/>
       <c r="F17" s="82"/>
-      <c r="H17" s="821" t="s">
+      <c r="H17" s="812" t="s">
         <v>157</v>
       </c>
-      <c r="I17" s="822"/>
-      <c r="J17" s="823"/>
+      <c r="I17" s="813"/>
+      <c r="J17" s="814"/>
       <c r="K17" s="227"/>
       <c r="L17" s="227"/>
       <c r="M17" s="227"/>
@@ -39023,10 +39023,10 @@
       <c r="K20" s="538" t="s">
         <v>52</v>
       </c>
-      <c r="L20" s="831" t="s">
+      <c r="L20" s="820" t="s">
         <v>53</v>
       </c>
-      <c r="M20" s="832"/>
+      <c r="M20" s="821"/>
       <c r="N20" s="400"/>
       <c r="O20" s="165"/>
     </row>
@@ -39042,8 +39042,8 @@
       <c r="I21" s="541"/>
       <c r="J21" s="541"/>
       <c r="K21" s="541"/>
-      <c r="L21" s="833"/>
-      <c r="M21" s="834"/>
+      <c r="L21" s="822"/>
+      <c r="M21" s="823"/>
       <c r="N21" s="80"/>
       <c r="O21" s="165"/>
     </row>
@@ -39059,27 +39059,27 @@
       <c r="I22" s="540"/>
       <c r="J22" s="540"/>
       <c r="K22" s="540"/>
-      <c r="L22" s="829"/>
-      <c r="M22" s="830"/>
+      <c r="L22" s="796"/>
+      <c r="M22" s="797"/>
       <c r="N22" s="80"/>
       <c r="O22" s="165"/>
     </row>
     <row r="23" spans="1:15" ht="27.75" customHeight="1" thickBot="1">
-      <c r="A23" s="826" t="s">
+      <c r="A23" s="817" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="827"/>
-      <c r="C23" s="827"/>
-      <c r="D23" s="827"/>
-      <c r="E23" s="827"/>
-      <c r="F23" s="828"/>
+      <c r="B23" s="818"/>
+      <c r="C23" s="818"/>
+      <c r="D23" s="818"/>
+      <c r="E23" s="818"/>
+      <c r="F23" s="819"/>
       <c r="G23" s="78"/>
       <c r="H23" s="580"/>
       <c r="I23" s="540"/>
       <c r="J23" s="540"/>
       <c r="K23" s="540"/>
-      <c r="L23" s="829"/>
-      <c r="M23" s="830"/>
+      <c r="L23" s="796"/>
+      <c r="M23" s="797"/>
       <c r="N23" s="80"/>
       <c r="O23" s="165"/>
     </row>
@@ -39087,10 +39087,10 @@
       <c r="A24" s="547" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="824" t="s">
+      <c r="B24" s="815" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="825"/>
+      <c r="C24" s="816"/>
       <c r="D24" s="548" t="s">
         <v>161</v>
       </c>
@@ -39105,8 +39105,8 @@
       <c r="I24" s="540"/>
       <c r="J24" s="540"/>
       <c r="K24" s="540"/>
-      <c r="L24" s="829"/>
-      <c r="M24" s="830"/>
+      <c r="L24" s="796"/>
+      <c r="M24" s="797"/>
       <c r="N24" s="80"/>
       <c r="O24" s="165"/>
     </row>
@@ -39114,8 +39114,8 @@
       <c r="A25" s="501" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="810"/>
-      <c r="C25" s="810"/>
+      <c r="B25" s="838"/>
+      <c r="C25" s="838"/>
       <c r="D25" s="508"/>
       <c r="E25" s="508"/>
       <c r="F25" s="507">
@@ -39127,8 +39127,8 @@
       <c r="I25" s="540"/>
       <c r="J25" s="540"/>
       <c r="K25" s="540"/>
-      <c r="L25" s="829"/>
-      <c r="M25" s="830"/>
+      <c r="L25" s="796"/>
+      <c r="M25" s="797"/>
       <c r="N25" s="80"/>
       <c r="O25" s="165"/>
     </row>
@@ -39141,16 +39141,16 @@
       <c r="I26" s="540"/>
       <c r="J26" s="540"/>
       <c r="K26" s="540"/>
-      <c r="L26" s="829"/>
-      <c r="M26" s="830"/>
+      <c r="L26" s="796"/>
+      <c r="M26" s="797"/>
       <c r="N26" s="80"/>
       <c r="O26" s="165"/>
     </row>
     <row r="27" spans="1:15" ht="27" customHeight="1">
-      <c r="A27" s="820"/>
-      <c r="B27" s="820"/>
-      <c r="C27" s="820"/>
-      <c r="D27" s="820"/>
+      <c r="A27" s="811"/>
+      <c r="B27" s="811"/>
+      <c r="C27" s="811"/>
+      <c r="D27" s="811"/>
       <c r="E27" s="495"/>
       <c r="F27" s="498"/>
       <c r="G27" s="89"/>
@@ -39158,8 +39158,8 @@
       <c r="I27" s="540"/>
       <c r="J27" s="540"/>
       <c r="K27" s="540"/>
-      <c r="L27" s="829"/>
-      <c r="M27" s="830"/>
+      <c r="L27" s="796"/>
+      <c r="M27" s="797"/>
       <c r="N27" s="80"/>
       <c r="O27" s="165"/>
     </row>
@@ -39175,8 +39175,8 @@
       <c r="I28" s="540"/>
       <c r="J28" s="540"/>
       <c r="K28" s="540"/>
-      <c r="L28" s="829"/>
-      <c r="M28" s="830"/>
+      <c r="L28" s="796"/>
+      <c r="M28" s="797"/>
       <c r="N28" s="105"/>
       <c r="O28" s="165"/>
     </row>
@@ -39191,8 +39191,8 @@
       <c r="I29" s="540"/>
       <c r="J29" s="540"/>
       <c r="K29" s="540"/>
-      <c r="L29" s="829"/>
-      <c r="M29" s="830"/>
+      <c r="L29" s="796"/>
+      <c r="M29" s="797"/>
       <c r="N29" s="80"/>
       <c r="O29" s="165"/>
     </row>
@@ -39208,8 +39208,8 @@
       <c r="I30" s="540"/>
       <c r="J30" s="540"/>
       <c r="K30" s="540"/>
-      <c r="L30" s="829"/>
-      <c r="M30" s="830"/>
+      <c r="L30" s="796"/>
+      <c r="M30" s="797"/>
       <c r="N30" s="80"/>
       <c r="O30" s="165"/>
     </row>
@@ -39225,8 +39225,8 @@
       <c r="I31" s="540"/>
       <c r="J31" s="540"/>
       <c r="K31" s="540"/>
-      <c r="L31" s="829"/>
-      <c r="M31" s="830"/>
+      <c r="L31" s="796"/>
+      <c r="M31" s="797"/>
       <c r="N31" s="80"/>
       <c r="O31" s="165"/>
     </row>
@@ -39242,8 +39242,8 @@
       <c r="I32" s="540"/>
       <c r="J32" s="540"/>
       <c r="K32" s="540"/>
-      <c r="L32" s="829"/>
-      <c r="M32" s="830"/>
+      <c r="L32" s="796"/>
+      <c r="M32" s="797"/>
       <c r="N32" s="80"/>
       <c r="O32" s="165"/>
     </row>
@@ -39259,8 +39259,8 @@
       <c r="I33" s="540"/>
       <c r="J33" s="540"/>
       <c r="K33" s="540"/>
-      <c r="L33" s="829"/>
-      <c r="M33" s="830"/>
+      <c r="L33" s="796"/>
+      <c r="M33" s="797"/>
       <c r="N33" s="80"/>
       <c r="O33" s="165"/>
     </row>
@@ -39276,8 +39276,8 @@
       <c r="I34" s="540"/>
       <c r="J34" s="540"/>
       <c r="K34" s="540"/>
-      <c r="L34" s="829"/>
-      <c r="M34" s="830"/>
+      <c r="L34" s="796"/>
+      <c r="M34" s="797"/>
       <c r="N34" s="80"/>
       <c r="O34" s="165"/>
     </row>
@@ -39293,8 +39293,8 @@
       <c r="I35" s="540"/>
       <c r="J35" s="540"/>
       <c r="K35" s="540"/>
-      <c r="L35" s="829"/>
-      <c r="M35" s="830"/>
+      <c r="L35" s="796"/>
+      <c r="M35" s="797"/>
       <c r="N35" s="80"/>
       <c r="O35" s="165"/>
     </row>
@@ -39309,8 +39309,8 @@
       <c r="I36" s="540"/>
       <c r="J36" s="540"/>
       <c r="K36" s="540"/>
-      <c r="L36" s="829"/>
-      <c r="M36" s="830"/>
+      <c r="L36" s="796"/>
+      <c r="M36" s="797"/>
       <c r="N36" s="80"/>
       <c r="O36" s="165"/>
     </row>
@@ -39326,29 +39326,23 @@
       <c r="I37" s="542"/>
       <c r="J37" s="542"/>
       <c r="K37" s="542"/>
-      <c r="L37" s="846"/>
-      <c r="M37" s="847"/>
+      <c r="L37" s="798"/>
+      <c r="M37" s="799"/>
       <c r="N37" s="80"/>
       <c r="O37" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="B24:C24"/>
@@ -39361,16 +39355,22 @@
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="L26:M26"/>
     <mergeCell ref="L27:M27"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
   </mergeCells>
   <conditionalFormatting sqref="I21:L37">
     <cfRule type="expression" dxfId="27" priority="1">
@@ -39411,22 +39411,22 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21">
       <c r="A1" s="82"/>
-      <c r="B1" s="851" t="s">
+      <c r="B1" s="881" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="852"/>
-      <c r="D1" s="852"/>
-      <c r="E1" s="852"/>
-      <c r="F1" s="852"/>
-      <c r="G1" s="852"/>
-      <c r="H1" s="852"/>
-      <c r="I1" s="852"/>
-      <c r="J1" s="852"/>
-      <c r="K1" s="852"/>
-      <c r="L1" s="852"/>
-      <c r="M1" s="852"/>
-      <c r="N1" s="852"/>
-      <c r="O1" s="853"/>
+      <c r="C1" s="882"/>
+      <c r="D1" s="882"/>
+      <c r="E1" s="882"/>
+      <c r="F1" s="882"/>
+      <c r="G1" s="882"/>
+      <c r="H1" s="882"/>
+      <c r="I1" s="882"/>
+      <c r="J1" s="882"/>
+      <c r="K1" s="882"/>
+      <c r="L1" s="882"/>
+      <c r="M1" s="882"/>
+      <c r="N1" s="882"/>
+      <c r="O1" s="883"/>
       <c r="P1" s="82"/>
       <c r="Q1" s="82"/>
       <c r="R1" s="82"/>
@@ -39435,24 +39435,24 @@
     </row>
     <row r="2" spans="1:20" ht="18.75" customHeight="1">
       <c r="A2" s="82"/>
-      <c r="B2" s="870" t="s">
+      <c r="B2" s="869" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="871"/>
-      <c r="D2" s="871"/>
-      <c r="E2" s="871"/>
-      <c r="F2" s="871"/>
-      <c r="G2" s="872" t="s">
+      <c r="C2" s="870"/>
+      <c r="D2" s="870"/>
+      <c r="E2" s="870"/>
+      <c r="F2" s="870"/>
+      <c r="G2" s="871" t="s">
         <v>164</v>
       </c>
-      <c r="H2" s="872"/>
-      <c r="I2" s="872"/>
-      <c r="J2" s="872"/>
-      <c r="K2" s="872"/>
-      <c r="L2" s="872"/>
-      <c r="M2" s="872"/>
-      <c r="N2" s="872"/>
-      <c r="O2" s="873"/>
+      <c r="H2" s="871"/>
+      <c r="I2" s="871"/>
+      <c r="J2" s="871"/>
+      <c r="K2" s="871"/>
+      <c r="L2" s="871"/>
+      <c r="M2" s="871"/>
+      <c r="N2" s="871"/>
+      <c r="O2" s="872"/>
       <c r="P2" s="82"/>
       <c r="Q2" s="82"/>
       <c r="R2" s="82"/>
@@ -39461,15 +39461,15 @@
     </row>
     <row r="3" spans="1:20" ht="28.5" customHeight="1" thickBot="1">
       <c r="A3" s="82"/>
-      <c r="B3" s="874" t="s">
+      <c r="B3" s="873" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="875"/>
-      <c r="D3" s="875"/>
-      <c r="E3" s="875"/>
-      <c r="F3" s="875"/>
-      <c r="G3" s="875"/>
-      <c r="H3" s="876"/>
+      <c r="C3" s="874"/>
+      <c r="D3" s="874"/>
+      <c r="E3" s="874"/>
+      <c r="F3" s="874"/>
+      <c r="G3" s="874"/>
+      <c r="H3" s="875"/>
       <c r="I3" s="208"/>
       <c r="J3" s="209"/>
       <c r="K3" s="477"/>
@@ -39494,13 +39494,13 @@
       <c r="H4" s="80"/>
       <c r="I4" s="88"/>
       <c r="J4" s="103"/>
-      <c r="K4" s="863" t="s">
+      <c r="K4" s="891" t="s">
         <v>187</v>
       </c>
-      <c r="L4" s="864"/>
-      <c r="M4" s="864"/>
-      <c r="N4" s="864"/>
-      <c r="O4" s="865"/>
+      <c r="L4" s="892"/>
+      <c r="M4" s="892"/>
+      <c r="N4" s="892"/>
+      <c r="O4" s="893"/>
       <c r="P4" s="80"/>
       <c r="Q4" s="82"/>
       <c r="R4" s="82"/>
@@ -39513,14 +39513,14 @@
       <c r="H5" s="79"/>
       <c r="I5" s="82"/>
       <c r="J5" s="210"/>
-      <c r="K5" s="860" t="s">
+      <c r="K5" s="888" t="s">
         <v>122</v>
       </c>
-      <c r="L5" s="859"/>
-      <c r="M5" s="859" t="s">
+      <c r="L5" s="887"/>
+      <c r="M5" s="887" t="s">
         <v>190</v>
       </c>
-      <c r="N5" s="859"/>
+      <c r="N5" s="887"/>
       <c r="O5" s="529" t="s">
         <v>70</v>
       </c>
@@ -39536,10 +39536,10 @@
       <c r="H6" s="79"/>
       <c r="I6" s="82"/>
       <c r="J6" s="79"/>
-      <c r="K6" s="866"/>
-      <c r="L6" s="867"/>
-      <c r="M6" s="855"/>
-      <c r="N6" s="856"/>
+      <c r="K6" s="894"/>
+      <c r="L6" s="895"/>
+      <c r="M6" s="885"/>
+      <c r="N6" s="886"/>
       <c r="O6" s="560"/>
       <c r="P6" s="80"/>
       <c r="Q6" s="82"/>
@@ -39551,16 +39551,16 @@
       <c r="A7" s="82"/>
       <c r="C7" s="82"/>
       <c r="D7" s="82"/>
-      <c r="E7" s="861"/>
-      <c r="F7" s="862"/>
-      <c r="G7" s="862"/>
-      <c r="H7" s="862"/>
+      <c r="E7" s="889"/>
+      <c r="F7" s="890"/>
+      <c r="G7" s="890"/>
+      <c r="H7" s="890"/>
       <c r="I7" s="82"/>
       <c r="J7" s="103"/>
-      <c r="K7" s="868"/>
-      <c r="L7" s="869"/>
-      <c r="M7" s="857"/>
-      <c r="N7" s="858"/>
+      <c r="K7" s="850"/>
+      <c r="L7" s="851"/>
+      <c r="M7" s="848"/>
+      <c r="N7" s="849"/>
       <c r="O7" s="561"/>
       <c r="P7" s="80"/>
       <c r="Q7" s="82"/>
@@ -39575,10 +39575,10 @@
       <c r="D8" s="82"/>
       <c r="I8" s="82"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="868"/>
-      <c r="L8" s="869"/>
-      <c r="M8" s="857"/>
-      <c r="N8" s="858"/>
+      <c r="K8" s="850"/>
+      <c r="L8" s="851"/>
+      <c r="M8" s="848"/>
+      <c r="N8" s="849"/>
       <c r="O8" s="561"/>
       <c r="P8" s="80"/>
       <c r="Q8" s="82"/>
@@ -39593,10 +39593,10 @@
       <c r="D9" s="82"/>
       <c r="I9" s="82"/>
       <c r="J9" s="103"/>
-      <c r="K9" s="868"/>
-      <c r="L9" s="869"/>
-      <c r="M9" s="857"/>
-      <c r="N9" s="858"/>
+      <c r="K9" s="850"/>
+      <c r="L9" s="851"/>
+      <c r="M9" s="848"/>
+      <c r="N9" s="849"/>
       <c r="O9" s="561"/>
       <c r="P9" s="80"/>
       <c r="Q9" s="82"/>
@@ -39613,10 +39613,10 @@
       <c r="D10" s="80"/>
       <c r="I10" s="82"/>
       <c r="J10" s="79"/>
-      <c r="K10" s="868"/>
-      <c r="L10" s="869"/>
-      <c r="M10" s="857"/>
-      <c r="N10" s="858"/>
+      <c r="K10" s="850"/>
+      <c r="L10" s="851"/>
+      <c r="M10" s="848"/>
+      <c r="N10" s="849"/>
       <c r="O10" s="561"/>
       <c r="P10" s="80"/>
       <c r="Q10" s="82"/>
@@ -39635,10 +39635,10 @@
       <c r="H11" s="87"/>
       <c r="I11" s="80"/>
       <c r="J11" s="103"/>
-      <c r="K11" s="868"/>
-      <c r="L11" s="869"/>
-      <c r="M11" s="857"/>
-      <c r="N11" s="858"/>
+      <c r="K11" s="850"/>
+      <c r="L11" s="851"/>
+      <c r="M11" s="848"/>
+      <c r="N11" s="849"/>
       <c r="O11" s="561"/>
       <c r="P11" s="80"/>
       <c r="Q11" s="82"/>
@@ -39654,10 +39654,10 @@
       <c r="G12" s="89"/>
       <c r="I12" s="80"/>
       <c r="J12" s="103"/>
-      <c r="K12" s="868"/>
-      <c r="L12" s="869"/>
-      <c r="M12" s="857"/>
-      <c r="N12" s="858"/>
+      <c r="K12" s="850"/>
+      <c r="L12" s="851"/>
+      <c r="M12" s="848"/>
+      <c r="N12" s="849"/>
       <c r="O12" s="561"/>
       <c r="P12" s="80"/>
       <c r="Q12" s="82"/>
@@ -39668,18 +39668,18 @@
     <row r="13" spans="1:20" ht="55.5" customHeight="1">
       <c r="A13" s="79"/>
       <c r="D13" s="89"/>
-      <c r="E13" s="854" t="s">
+      <c r="E13" s="884" t="s">
         <v>174</v>
       </c>
-      <c r="F13" s="854"/>
-      <c r="G13" s="854"/>
-      <c r="H13" s="854"/>
+      <c r="F13" s="884"/>
+      <c r="G13" s="884"/>
+      <c r="H13" s="884"/>
       <c r="I13" s="80"/>
       <c r="J13" s="103"/>
-      <c r="K13" s="868"/>
-      <c r="L13" s="869"/>
-      <c r="M13" s="857"/>
-      <c r="N13" s="858"/>
+      <c r="K13" s="850"/>
+      <c r="L13" s="851"/>
+      <c r="M13" s="848"/>
+      <c r="N13" s="849"/>
       <c r="O13" s="561"/>
       <c r="P13" s="80"/>
       <c r="Q13" s="82"/>
@@ -39689,25 +39689,25 @@
     </row>
     <row r="14" spans="1:20" ht="47.25" customHeight="1">
       <c r="A14" s="79"/>
-      <c r="B14" s="883" t="s">
+      <c r="B14" s="860" t="s">
         <v>170</v>
       </c>
-      <c r="C14" s="883"/>
+      <c r="C14" s="860"/>
       <c r="D14" s="89"/>
-      <c r="E14" s="878" t="s">
+      <c r="E14" s="877" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="878"/>
-      <c r="G14" s="878"/>
+      <c r="F14" s="877"/>
+      <c r="G14" s="877"/>
       <c r="H14" s="465" t="s">
         <v>123</v>
       </c>
       <c r="I14" s="80"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="868"/>
-      <c r="L14" s="869"/>
-      <c r="M14" s="857"/>
-      <c r="N14" s="858"/>
+      <c r="K14" s="850"/>
+      <c r="L14" s="851"/>
+      <c r="M14" s="848"/>
+      <c r="N14" s="849"/>
       <c r="O14" s="561"/>
       <c r="P14" s="80"/>
       <c r="Q14" s="82"/>
@@ -39724,16 +39724,16 @@
         <v>172</v>
       </c>
       <c r="D15" s="89"/>
-      <c r="E15" s="879"/>
-      <c r="F15" s="879"/>
-      <c r="G15" s="879"/>
+      <c r="E15" s="864"/>
+      <c r="F15" s="864"/>
+      <c r="G15" s="864"/>
       <c r="H15" s="474"/>
       <c r="I15" s="80"/>
       <c r="J15" s="103"/>
-      <c r="K15" s="868"/>
-      <c r="L15" s="869"/>
-      <c r="M15" s="857"/>
-      <c r="N15" s="858"/>
+      <c r="K15" s="850"/>
+      <c r="L15" s="851"/>
+      <c r="M15" s="848"/>
+      <c r="N15" s="849"/>
       <c r="O15" s="561"/>
       <c r="P15" s="80"/>
       <c r="Q15" s="82"/>
@@ -39746,16 +39746,16 @@
       <c r="B16" s="473"/>
       <c r="C16" s="473"/>
       <c r="D16" s="89"/>
-      <c r="E16" s="879"/>
-      <c r="F16" s="879"/>
-      <c r="G16" s="879"/>
+      <c r="E16" s="864"/>
+      <c r="F16" s="864"/>
+      <c r="G16" s="864"/>
       <c r="H16" s="474"/>
       <c r="I16" s="80"/>
       <c r="J16" s="103"/>
-      <c r="K16" s="868"/>
-      <c r="L16" s="869"/>
-      <c r="M16" s="857"/>
-      <c r="N16" s="858"/>
+      <c r="K16" s="850"/>
+      <c r="L16" s="851"/>
+      <c r="M16" s="848"/>
+      <c r="N16" s="849"/>
       <c r="O16" s="561"/>
       <c r="P16" s="80"/>
       <c r="Q16" s="82"/>
@@ -39768,16 +39768,16 @@
       <c r="B17" s="473"/>
       <c r="C17" s="473"/>
       <c r="D17" s="89"/>
-      <c r="E17" s="879"/>
-      <c r="F17" s="879"/>
-      <c r="G17" s="879"/>
+      <c r="E17" s="864"/>
+      <c r="F17" s="864"/>
+      <c r="G17" s="864"/>
       <c r="H17" s="474"/>
       <c r="I17" s="80"/>
       <c r="J17" s="79"/>
-      <c r="K17" s="868"/>
-      <c r="L17" s="869"/>
-      <c r="M17" s="857"/>
-      <c r="N17" s="858"/>
+      <c r="K17" s="850"/>
+      <c r="L17" s="851"/>
+      <c r="M17" s="848"/>
+      <c r="N17" s="849"/>
       <c r="O17" s="561"/>
       <c r="P17" s="80"/>
       <c r="Q17" s="82"/>
@@ -39790,16 +39790,16 @@
       <c r="B18" s="473"/>
       <c r="C18" s="473"/>
       <c r="D18" s="89"/>
-      <c r="E18" s="879"/>
-      <c r="F18" s="879"/>
-      <c r="G18" s="879"/>
+      <c r="E18" s="864"/>
+      <c r="F18" s="864"/>
+      <c r="G18" s="864"/>
       <c r="H18" s="474"/>
       <c r="I18" s="80"/>
       <c r="J18" s="87"/>
-      <c r="K18" s="891"/>
-      <c r="L18" s="892"/>
-      <c r="M18" s="889"/>
-      <c r="N18" s="890"/>
+      <c r="K18" s="867"/>
+      <c r="L18" s="868"/>
+      <c r="M18" s="855"/>
+      <c r="N18" s="856"/>
       <c r="O18" s="561"/>
       <c r="P18" s="80"/>
       <c r="Q18" s="82"/>
@@ -39812,15 +39812,15 @@
       <c r="B19" s="473"/>
       <c r="C19" s="473"/>
       <c r="D19" s="89"/>
-      <c r="E19" s="879"/>
-      <c r="F19" s="879"/>
-      <c r="G19" s="879"/>
+      <c r="E19" s="864"/>
+      <c r="F19" s="864"/>
+      <c r="G19" s="864"/>
       <c r="H19" s="474"/>
       <c r="I19" s="80"/>
       <c r="J19" s="79"/>
       <c r="K19" s="230"/>
-      <c r="M19" s="889"/>
-      <c r="N19" s="890"/>
+      <c r="M19" s="855"/>
+      <c r="N19" s="856"/>
       <c r="O19" s="561"/>
       <c r="P19" s="80"/>
       <c r="Q19" s="82"/>
@@ -39833,15 +39833,15 @@
       <c r="B20" s="473"/>
       <c r="C20" s="473"/>
       <c r="D20" s="89"/>
-      <c r="E20" s="887"/>
-      <c r="F20" s="887"/>
-      <c r="G20" s="887"/>
+      <c r="E20" s="865"/>
+      <c r="F20" s="865"/>
+      <c r="G20" s="865"/>
       <c r="H20" s="475"/>
       <c r="I20" s="80"/>
       <c r="J20" s="103"/>
       <c r="K20" s="230"/>
-      <c r="M20" s="889"/>
-      <c r="N20" s="890"/>
+      <c r="M20" s="855"/>
+      <c r="N20" s="856"/>
       <c r="O20" s="561"/>
       <c r="P20" s="80"/>
       <c r="Q20" s="82"/>
@@ -39854,11 +39854,11 @@
       <c r="B21" s="473"/>
       <c r="C21" s="473"/>
       <c r="D21" s="98"/>
-      <c r="E21" s="877" t="s">
+      <c r="E21" s="876" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="877"/>
-      <c r="G21" s="877"/>
+      <c r="F21" s="876"/>
+      <c r="G21" s="876"/>
       <c r="H21" s="476">
         <f>SUM(H15:H20)</f>
         <v>0</v>
@@ -39866,8 +39866,8 @@
       <c r="I21" s="80"/>
       <c r="J21" s="103"/>
       <c r="K21" s="230"/>
-      <c r="M21" s="889"/>
-      <c r="N21" s="890"/>
+      <c r="M21" s="855"/>
+      <c r="N21" s="856"/>
       <c r="O21" s="561"/>
       <c r="P21" s="80"/>
       <c r="Q21" s="82"/>
@@ -39885,17 +39885,17 @@
         <v>0</v>
       </c>
       <c r="D22" s="89"/>
-      <c r="E22" s="893" t="s">
+      <c r="E22" s="852" t="s">
         <v>171</v>
       </c>
-      <c r="F22" s="894"/>
-      <c r="G22" s="894"/>
-      <c r="H22" s="895"/>
+      <c r="F22" s="853"/>
+      <c r="G22" s="853"/>
+      <c r="H22" s="854"/>
       <c r="I22" s="80"/>
       <c r="J22" s="79"/>
       <c r="K22" s="230"/>
-      <c r="M22" s="889"/>
-      <c r="N22" s="890"/>
+      <c r="M22" s="855"/>
+      <c r="N22" s="856"/>
       <c r="O22" s="561"/>
       <c r="P22" s="80"/>
       <c r="Q22" s="82"/>
@@ -39910,8 +39910,8 @@
       <c r="J23" s="79"/>
       <c r="K23" s="230"/>
       <c r="L23" s="87"/>
-      <c r="M23" s="889"/>
-      <c r="N23" s="890"/>
+      <c r="M23" s="855"/>
+      <c r="N23" s="856"/>
       <c r="O23" s="561"/>
       <c r="P23" s="80"/>
       <c r="Q23" s="82"/>
@@ -39928,8 +39928,8 @@
       <c r="J24" s="87"/>
       <c r="K24" s="235"/>
       <c r="L24" s="234"/>
-      <c r="M24" s="889"/>
-      <c r="N24" s="890"/>
+      <c r="M24" s="855"/>
+      <c r="N24" s="856"/>
       <c r="O24" s="561"/>
       <c r="P24" s="80"/>
       <c r="Q24" s="82"/>
@@ -39946,8 +39946,8 @@
         <v>144</v>
       </c>
       <c r="L25" s="532"/>
-      <c r="M25" s="889"/>
-      <c r="N25" s="890"/>
+      <c r="M25" s="855"/>
+      <c r="N25" s="856"/>
       <c r="O25" s="561"/>
       <c r="P25" s="80"/>
       <c r="Q25" s="82"/>
@@ -39961,15 +39961,15 @@
       <c r="D26" s="231"/>
       <c r="E26" s="467"/>
       <c r="F26" s="468"/>
-      <c r="H26" s="888"/>
-      <c r="I26" s="888"/>
+      <c r="H26" s="866"/>
+      <c r="I26" s="866"/>
       <c r="J26" s="466"/>
-      <c r="K26" s="884" t="s">
+      <c r="K26" s="861" t="s">
         <v>191</v>
       </c>
-      <c r="L26" s="885"/>
-      <c r="M26" s="885"/>
-      <c r="N26" s="886"/>
+      <c r="L26" s="862"/>
+      <c r="M26" s="862"/>
+      <c r="N26" s="863"/>
       <c r="O26" s="530"/>
       <c r="P26" s="80"/>
       <c r="Q26" s="82"/>
@@ -39986,13 +39986,13 @@
       <c r="H27" s="470"/>
       <c r="I27" s="471"/>
       <c r="J27" s="211"/>
-      <c r="K27" s="880" t="s">
+      <c r="K27" s="857" t="s">
         <v>189</v>
       </c>
-      <c r="L27" s="881"/>
-      <c r="M27" s="881"/>
-      <c r="N27" s="881"/>
-      <c r="O27" s="882"/>
+      <c r="L27" s="858"/>
+      <c r="M27" s="858"/>
+      <c r="N27" s="858"/>
+      <c r="O27" s="859"/>
       <c r="P27" s="80"/>
       <c r="Q27" s="82"/>
       <c r="S27" s="82"/>
@@ -40001,13 +40001,13 @@
     <row r="28" spans="1:20" ht="32.25" customHeight="1" thickBot="1">
       <c r="A28" s="79"/>
       <c r="J28" s="78"/>
-      <c r="K28" s="848" t="s">
+      <c r="K28" s="878" t="s">
         <v>188</v>
       </c>
-      <c r="L28" s="849"/>
-      <c r="M28" s="849"/>
-      <c r="N28" s="849"/>
-      <c r="O28" s="850"/>
+      <c r="L28" s="879"/>
+      <c r="M28" s="879"/>
+      <c r="N28" s="879"/>
+      <c r="O28" s="880"/>
       <c r="P28" s="82"/>
       <c r="Q28" s="82"/>
       <c r="R28" s="79"/>
@@ -40399,30 +40399,22 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="K27:O27"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="K28:O28"/>
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:O2"/>
     <mergeCell ref="M14:N14"/>
@@ -40439,22 +40431,30 @@
     <mergeCell ref="M16:N16"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K28:O28"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="K4:O4"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K27:O27"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -40504,159 +40504,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="21.75" thickBot="1">
-      <c r="A1" s="986" t="s">
+      <c r="A1" s="929" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="987"/>
-      <c r="C1" s="987"/>
-      <c r="D1" s="987"/>
-      <c r="E1" s="987"/>
-      <c r="F1" s="987"/>
-      <c r="G1" s="987"/>
-      <c r="H1" s="987"/>
-      <c r="I1" s="987"/>
-      <c r="J1" s="987"/>
-      <c r="K1" s="987"/>
-      <c r="L1" s="987"/>
-      <c r="M1" s="987"/>
-      <c r="N1" s="987"/>
-      <c r="O1" s="987"/>
-      <c r="P1" s="987"/>
-      <c r="Q1" s="987"/>
-      <c r="R1" s="987"/>
-      <c r="S1" s="987"/>
-      <c r="T1" s="987"/>
-      <c r="U1" s="987"/>
-      <c r="V1" s="987"/>
-      <c r="W1" s="987"/>
-      <c r="X1" s="987"/>
-      <c r="Y1" s="987"/>
-      <c r="Z1" s="987"/>
-      <c r="AA1" s="987"/>
-      <c r="AB1" s="987"/>
-      <c r="AC1" s="987"/>
-      <c r="AD1" s="987"/>
-      <c r="AE1" s="987"/>
-      <c r="AF1" s="987"/>
-      <c r="AG1" s="987"/>
-      <c r="AH1" s="987"/>
-      <c r="AI1" s="988"/>
+      <c r="B1" s="930"/>
+      <c r="C1" s="930"/>
+      <c r="D1" s="930"/>
+      <c r="E1" s="930"/>
+      <c r="F1" s="930"/>
+      <c r="G1" s="930"/>
+      <c r="H1" s="930"/>
+      <c r="I1" s="930"/>
+      <c r="J1" s="930"/>
+      <c r="K1" s="930"/>
+      <c r="L1" s="930"/>
+      <c r="M1" s="930"/>
+      <c r="N1" s="930"/>
+      <c r="O1" s="930"/>
+      <c r="P1" s="930"/>
+      <c r="Q1" s="930"/>
+      <c r="R1" s="930"/>
+      <c r="S1" s="930"/>
+      <c r="T1" s="930"/>
+      <c r="U1" s="930"/>
+      <c r="V1" s="930"/>
+      <c r="W1" s="930"/>
+      <c r="X1" s="930"/>
+      <c r="Y1" s="930"/>
+      <c r="Z1" s="930"/>
+      <c r="AA1" s="930"/>
+      <c r="AB1" s="930"/>
+      <c r="AC1" s="930"/>
+      <c r="AD1" s="930"/>
+      <c r="AE1" s="930"/>
+      <c r="AF1" s="930"/>
+      <c r="AG1" s="930"/>
+      <c r="AH1" s="930"/>
+      <c r="AI1" s="931"/>
     </row>
     <row r="2" spans="1:36" ht="4.5" customHeight="1" thickBot="1">
-      <c r="A2" s="1004"/>
-      <c r="B2" s="839"/>
-      <c r="C2" s="839"/>
-      <c r="D2" s="839"/>
-      <c r="E2" s="839"/>
-      <c r="F2" s="839"/>
-      <c r="G2" s="839"/>
-      <c r="H2" s="839"/>
-      <c r="I2" s="839"/>
-      <c r="J2" s="839"/>
-      <c r="K2" s="839"/>
-      <c r="L2" s="839"/>
-      <c r="M2" s="839"/>
-      <c r="N2" s="839"/>
-      <c r="O2" s="839"/>
-      <c r="P2" s="839"/>
-      <c r="Q2" s="839"/>
-      <c r="R2" s="839"/>
-      <c r="S2" s="839"/>
-      <c r="T2" s="839"/>
-      <c r="U2" s="839"/>
-      <c r="V2" s="839"/>
-      <c r="W2" s="839"/>
-      <c r="X2" s="839"/>
-      <c r="Y2" s="839"/>
-      <c r="Z2" s="839"/>
-      <c r="AA2" s="839"/>
-      <c r="AB2" s="839"/>
-      <c r="AC2" s="839"/>
-      <c r="AD2" s="839"/>
-      <c r="AE2" s="839"/>
-      <c r="AF2" s="839"/>
-      <c r="AG2" s="839"/>
-      <c r="AH2" s="839"/>
-      <c r="AI2" s="840"/>
+      <c r="A2" s="949"/>
+      <c r="B2" s="804"/>
+      <c r="C2" s="804"/>
+      <c r="D2" s="804"/>
+      <c r="E2" s="804"/>
+      <c r="F2" s="804"/>
+      <c r="G2" s="804"/>
+      <c r="H2" s="804"/>
+      <c r="I2" s="804"/>
+      <c r="J2" s="804"/>
+      <c r="K2" s="804"/>
+      <c r="L2" s="804"/>
+      <c r="M2" s="804"/>
+      <c r="N2" s="804"/>
+      <c r="O2" s="804"/>
+      <c r="P2" s="804"/>
+      <c r="Q2" s="804"/>
+      <c r="R2" s="804"/>
+      <c r="S2" s="804"/>
+      <c r="T2" s="804"/>
+      <c r="U2" s="804"/>
+      <c r="V2" s="804"/>
+      <c r="W2" s="804"/>
+      <c r="X2" s="804"/>
+      <c r="Y2" s="804"/>
+      <c r="Z2" s="804"/>
+      <c r="AA2" s="804"/>
+      <c r="AB2" s="804"/>
+      <c r="AC2" s="804"/>
+      <c r="AD2" s="804"/>
+      <c r="AE2" s="804"/>
+      <c r="AF2" s="804"/>
+      <c r="AG2" s="804"/>
+      <c r="AH2" s="804"/>
+      <c r="AI2" s="805"/>
     </row>
     <row r="3" spans="1:36" ht="15.75">
-      <c r="A3" s="1020" t="s">
+      <c r="A3" s="965" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="1021"/>
-      <c r="C3" s="1021"/>
-      <c r="D3" s="1021"/>
-      <c r="E3" s="1021"/>
-      <c r="F3" s="1021"/>
-      <c r="G3" s="1021"/>
-      <c r="H3" s="1021"/>
-      <c r="I3" s="1021"/>
-      <c r="J3" s="1021"/>
-      <c r="K3" s="1021"/>
-      <c r="L3" s="1021"/>
-      <c r="M3" s="1021"/>
-      <c r="N3" s="1021"/>
-      <c r="O3" s="1021"/>
-      <c r="P3" s="1021"/>
-      <c r="Q3" s="1021"/>
-      <c r="R3" s="1021"/>
-      <c r="S3" s="1021"/>
-      <c r="T3" s="1021"/>
-      <c r="U3" s="1021"/>
-      <c r="V3" s="1021"/>
-      <c r="W3" s="1021"/>
-      <c r="X3" s="1021"/>
-      <c r="Y3" s="1021"/>
-      <c r="Z3" s="1021"/>
-      <c r="AA3" s="1021"/>
-      <c r="AB3" s="1021"/>
-      <c r="AC3" s="1021"/>
-      <c r="AD3" s="1021"/>
-      <c r="AE3" s="1021"/>
-      <c r="AF3" s="1021"/>
-      <c r="AG3" s="1021"/>
-      <c r="AH3" s="1021"/>
-      <c r="AI3" s="1022"/>
+      <c r="B3" s="966"/>
+      <c r="C3" s="966"/>
+      <c r="D3" s="966"/>
+      <c r="E3" s="966"/>
+      <c r="F3" s="966"/>
+      <c r="G3" s="966"/>
+      <c r="H3" s="966"/>
+      <c r="I3" s="966"/>
+      <c r="J3" s="966"/>
+      <c r="K3" s="966"/>
+      <c r="L3" s="966"/>
+      <c r="M3" s="966"/>
+      <c r="N3" s="966"/>
+      <c r="O3" s="966"/>
+      <c r="P3" s="966"/>
+      <c r="Q3" s="966"/>
+      <c r="R3" s="966"/>
+      <c r="S3" s="966"/>
+      <c r="T3" s="966"/>
+      <c r="U3" s="966"/>
+      <c r="V3" s="966"/>
+      <c r="W3" s="966"/>
+      <c r="X3" s="966"/>
+      <c r="Y3" s="966"/>
+      <c r="Z3" s="966"/>
+      <c r="AA3" s="966"/>
+      <c r="AB3" s="966"/>
+      <c r="AC3" s="966"/>
+      <c r="AD3" s="966"/>
+      <c r="AE3" s="966"/>
+      <c r="AF3" s="966"/>
+      <c r="AG3" s="966"/>
+      <c r="AH3" s="966"/>
+      <c r="AI3" s="967"/>
       <c r="AJ3" s="98"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A4" s="1017" t="s">
+      <c r="A4" s="962" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="1018"/>
-      <c r="C4" s="1018"/>
-      <c r="D4" s="1018"/>
-      <c r="E4" s="1018"/>
-      <c r="F4" s="1018"/>
-      <c r="G4" s="1018"/>
-      <c r="H4" s="1018"/>
-      <c r="I4" s="1018"/>
-      <c r="J4" s="1018"/>
-      <c r="K4" s="1018"/>
-      <c r="L4" s="1018"/>
-      <c r="M4" s="1018"/>
-      <c r="N4" s="1018"/>
-      <c r="O4" s="1018"/>
-      <c r="P4" s="1018"/>
-      <c r="Q4" s="1018"/>
-      <c r="R4" s="1018"/>
-      <c r="S4" s="1018"/>
-      <c r="T4" s="1018"/>
-      <c r="U4" s="1018"/>
-      <c r="V4" s="1018"/>
-      <c r="W4" s="1018"/>
-      <c r="X4" s="1018"/>
-      <c r="Y4" s="1018"/>
-      <c r="Z4" s="1018"/>
-      <c r="AA4" s="1018"/>
-      <c r="AB4" s="1018"/>
-      <c r="AC4" s="1018"/>
-      <c r="AD4" s="1018"/>
-      <c r="AE4" s="1018"/>
-      <c r="AF4" s="1018"/>
-      <c r="AG4" s="1018"/>
-      <c r="AH4" s="1018"/>
-      <c r="AI4" s="1019"/>
+      <c r="B4" s="963"/>
+      <c r="C4" s="963"/>
+      <c r="D4" s="963"/>
+      <c r="E4" s="963"/>
+      <c r="F4" s="963"/>
+      <c r="G4" s="963"/>
+      <c r="H4" s="963"/>
+      <c r="I4" s="963"/>
+      <c r="J4" s="963"/>
+      <c r="K4" s="963"/>
+      <c r="L4" s="963"/>
+      <c r="M4" s="963"/>
+      <c r="N4" s="963"/>
+      <c r="O4" s="963"/>
+      <c r="P4" s="963"/>
+      <c r="Q4" s="963"/>
+      <c r="R4" s="963"/>
+      <c r="S4" s="963"/>
+      <c r="T4" s="963"/>
+      <c r="U4" s="963"/>
+      <c r="V4" s="963"/>
+      <c r="W4" s="963"/>
+      <c r="X4" s="963"/>
+      <c r="Y4" s="963"/>
+      <c r="Z4" s="963"/>
+      <c r="AA4" s="963"/>
+      <c r="AB4" s="963"/>
+      <c r="AC4" s="963"/>
+      <c r="AD4" s="963"/>
+      <c r="AE4" s="963"/>
+      <c r="AF4" s="963"/>
+      <c r="AG4" s="963"/>
+      <c r="AH4" s="963"/>
+      <c r="AI4" s="964"/>
     </row>
     <row r="5" spans="1:36" ht="11.25" customHeight="1" thickBot="1">
       <c r="A5" s="230"/>
@@ -40694,44 +40694,44 @@
       <c r="A6" s="136"/>
       <c r="C6" s="151"/>
       <c r="D6" s="124"/>
-      <c r="E6" s="1032" t="s">
+      <c r="E6" s="977" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="1033"/>
-      <c r="G6" s="1034"/>
+      <c r="F6" s="978"/>
+      <c r="G6" s="979"/>
       <c r="H6" s="354"/>
       <c r="I6" s="229"/>
-      <c r="J6" s="1005" t="s">
+      <c r="J6" s="950" t="s">
         <v>92</v>
       </c>
-      <c r="K6" s="1006"/>
-      <c r="L6" s="1007"/>
+      <c r="K6" s="951"/>
+      <c r="L6" s="952"/>
       <c r="M6" s="357"/>
       <c r="N6" s="229"/>
       <c r="O6" s="360"/>
       <c r="P6" s="360"/>
-      <c r="Q6" s="1026" t="s">
+      <c r="Q6" s="971" t="s">
         <v>93</v>
       </c>
-      <c r="R6" s="1027"/>
+      <c r="R6" s="972"/>
       <c r="S6" s="358"/>
       <c r="T6" s="229"/>
       <c r="U6" s="360"/>
       <c r="V6" s="360"/>
-      <c r="W6" s="1005" t="s">
+      <c r="W6" s="950" t="s">
         <v>104</v>
       </c>
-      <c r="X6" s="1006"/>
-      <c r="Y6" s="1006"/>
-      <c r="Z6" s="1007"/>
+      <c r="X6" s="951"/>
+      <c r="Y6" s="951"/>
+      <c r="Z6" s="952"/>
       <c r="AA6" s="396"/>
       <c r="AB6" s="229"/>
       <c r="AC6" s="360"/>
-      <c r="AD6" s="998" t="s">
+      <c r="AD6" s="943" t="s">
         <v>94</v>
       </c>
-      <c r="AE6" s="999"/>
-      <c r="AF6" s="1000"/>
+      <c r="AE6" s="944"/>
+      <c r="AF6" s="945"/>
       <c r="AG6" s="136"/>
       <c r="AH6" s="384"/>
       <c r="AI6" s="404"/>
@@ -40740,34 +40740,34 @@
       <c r="A7" s="136"/>
       <c r="B7" s="100"/>
       <c r="C7" s="23"/>
-      <c r="E7" s="1035"/>
-      <c r="F7" s="1036"/>
-      <c r="G7" s="1037"/>
+      <c r="E7" s="980"/>
+      <c r="F7" s="981"/>
+      <c r="G7" s="982"/>
       <c r="H7" s="354"/>
       <c r="I7" s="233"/>
-      <c r="J7" s="1023"/>
-      <c r="K7" s="1024"/>
-      <c r="L7" s="1025"/>
+      <c r="J7" s="968"/>
+      <c r="K7" s="969"/>
+      <c r="L7" s="970"/>
       <c r="M7" s="357"/>
       <c r="N7" s="233"/>
       <c r="O7" s="352"/>
       <c r="P7" s="359"/>
-      <c r="Q7" s="874"/>
-      <c r="R7" s="1028"/>
+      <c r="Q7" s="873"/>
+      <c r="R7" s="973"/>
       <c r="S7" s="358"/>
       <c r="T7" s="233"/>
       <c r="U7" s="352"/>
       <c r="V7" s="359"/>
-      <c r="W7" s="1008"/>
-      <c r="X7" s="1009"/>
-      <c r="Y7" s="1009"/>
-      <c r="Z7" s="1010"/>
+      <c r="W7" s="953"/>
+      <c r="X7" s="954"/>
+      <c r="Y7" s="954"/>
+      <c r="Z7" s="955"/>
       <c r="AA7" s="396"/>
       <c r="AB7" s="233"/>
       <c r="AC7" s="352"/>
-      <c r="AD7" s="1001"/>
-      <c r="AE7" s="1002"/>
-      <c r="AF7" s="1003"/>
+      <c r="AD7" s="946"/>
+      <c r="AE7" s="947"/>
+      <c r="AF7" s="948"/>
       <c r="AG7" s="136"/>
       <c r="AH7" s="384"/>
       <c r="AI7" s="404"/>
@@ -40776,44 +40776,44 @@
       <c r="A8" s="136"/>
       <c r="B8" s="361"/>
       <c r="C8" s="206"/>
-      <c r="E8" s="1011">
+      <c r="E8" s="956">
         <v>64</v>
       </c>
-      <c r="F8" s="1012"/>
-      <c r="G8" s="1038"/>
+      <c r="F8" s="957"/>
+      <c r="G8" s="983"/>
       <c r="H8" s="152"/>
       <c r="I8" s="136"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="1042">
+      <c r="K8" s="987">
         <v>16</v>
       </c>
-      <c r="L8" s="1043"/>
+      <c r="L8" s="988"/>
       <c r="M8" s="357"/>
       <c r="N8" s="136"/>
       <c r="O8" s="79"/>
-      <c r="P8" s="1011">
+      <c r="P8" s="956">
         <v>10</v>
       </c>
-      <c r="Q8" s="1012"/>
-      <c r="R8" s="1013"/>
+      <c r="Q8" s="957"/>
+      <c r="R8" s="958"/>
       <c r="S8" s="358"/>
       <c r="T8" s="136"/>
       <c r="U8" s="79"/>
-      <c r="V8" s="1011">
+      <c r="V8" s="956">
         <v>38</v>
       </c>
-      <c r="W8" s="1012"/>
-      <c r="X8" s="1012"/>
-      <c r="Y8" s="1012"/>
-      <c r="Z8" s="1013"/>
+      <c r="W8" s="957"/>
+      <c r="X8" s="957"/>
+      <c r="Y8" s="957"/>
+      <c r="Z8" s="958"/>
       <c r="AA8" s="397"/>
       <c r="AB8" s="136"/>
       <c r="AC8" s="79"/>
-      <c r="AD8" s="1011">
+      <c r="AD8" s="956">
         <v>20</v>
       </c>
-      <c r="AE8" s="1012"/>
-      <c r="AF8" s="1013"/>
+      <c r="AE8" s="957"/>
+      <c r="AF8" s="958"/>
       <c r="AG8" s="136"/>
       <c r="AH8" s="385"/>
       <c r="AI8" s="232"/>
@@ -40823,33 +40823,33 @@
       <c r="B9" s="100"/>
       <c r="C9" s="144"/>
       <c r="D9" s="350"/>
-      <c r="E9" s="1039"/>
-      <c r="F9" s="1040"/>
-      <c r="G9" s="1041"/>
+      <c r="E9" s="984"/>
+      <c r="F9" s="985"/>
+      <c r="G9" s="986"/>
       <c r="I9" s="137"/>
       <c r="J9" s="351"/>
-      <c r="K9" s="1044"/>
-      <c r="L9" s="1045"/>
+      <c r="K9" s="989"/>
+      <c r="L9" s="990"/>
       <c r="M9" s="358"/>
       <c r="N9" s="137"/>
       <c r="O9" s="351"/>
-      <c r="P9" s="1014"/>
-      <c r="Q9" s="1015"/>
-      <c r="R9" s="1016"/>
+      <c r="P9" s="959"/>
+      <c r="Q9" s="960"/>
+      <c r="R9" s="961"/>
       <c r="S9" s="358"/>
       <c r="T9" s="137"/>
       <c r="U9" s="351"/>
-      <c r="V9" s="1014"/>
-      <c r="W9" s="1015"/>
-      <c r="X9" s="1015"/>
-      <c r="Y9" s="1015"/>
-      <c r="Z9" s="1016"/>
+      <c r="V9" s="959"/>
+      <c r="W9" s="960"/>
+      <c r="X9" s="960"/>
+      <c r="Y9" s="960"/>
+      <c r="Z9" s="961"/>
       <c r="AA9" s="397"/>
       <c r="AB9" s="137"/>
       <c r="AC9" s="351"/>
-      <c r="AD9" s="1014"/>
-      <c r="AE9" s="1015"/>
-      <c r="AF9" s="1016"/>
+      <c r="AD9" s="959"/>
+      <c r="AE9" s="960"/>
+      <c r="AF9" s="961"/>
       <c r="AG9" s="398"/>
       <c r="AH9" s="385"/>
       <c r="AI9" s="165"/>
@@ -40905,23 +40905,23 @@
       <c r="M11" s="148"/>
       <c r="N11" s="148"/>
       <c r="O11" s="82"/>
-      <c r="Q11" s="1052" t="s">
+      <c r="Q11" s="896" t="s">
         <v>163</v>
       </c>
-      <c r="R11" s="1053"/>
-      <c r="S11" s="1053"/>
-      <c r="T11" s="1053"/>
-      <c r="U11" s="1053"/>
-      <c r="V11" s="1053"/>
-      <c r="W11" s="1053"/>
-      <c r="X11" s="1053"/>
-      <c r="Y11" s="1053"/>
-      <c r="Z11" s="1053"/>
-      <c r="AA11" s="1053"/>
-      <c r="AB11" s="1053"/>
-      <c r="AC11" s="1053"/>
-      <c r="AD11" s="1053"/>
-      <c r="AE11" s="1053"/>
+      <c r="R11" s="897"/>
+      <c r="S11" s="897"/>
+      <c r="T11" s="897"/>
+      <c r="U11" s="897"/>
+      <c r="V11" s="897"/>
+      <c r="W11" s="897"/>
+      <c r="X11" s="897"/>
+      <c r="Y11" s="897"/>
+      <c r="Z11" s="897"/>
+      <c r="AA11" s="897"/>
+      <c r="AB11" s="897"/>
+      <c r="AC11" s="897"/>
+      <c r="AD11" s="897"/>
+      <c r="AE11" s="897"/>
       <c r="AF11" s="436">
         <v>2025</v>
       </c>
@@ -40931,25 +40931,25 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1">
       <c r="A12" s="405"/>
-      <c r="B12" s="1062" t="s">
+      <c r="B12" s="910" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="1063"/>
-      <c r="D12" s="1063"/>
-      <c r="E12" s="1064"/>
-      <c r="F12" s="1055" t="s">
+      <c r="C12" s="911"/>
+      <c r="D12" s="911"/>
+      <c r="E12" s="912"/>
+      <c r="F12" s="900" t="s">
         <v>151</v>
       </c>
-      <c r="G12" s="1056"/>
-      <c r="H12" s="1056"/>
-      <c r="I12" s="1056"/>
-      <c r="J12" s="1056"/>
-      <c r="K12" s="1056"/>
-      <c r="L12" s="1056"/>
-      <c r="M12" s="1055" t="s">
+      <c r="G12" s="901"/>
+      <c r="H12" s="901"/>
+      <c r="I12" s="901"/>
+      <c r="J12" s="901"/>
+      <c r="K12" s="901"/>
+      <c r="L12" s="901"/>
+      <c r="M12" s="900" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="1059"/>
+      <c r="N12" s="904"/>
       <c r="O12" s="364"/>
       <c r="P12" s="79"/>
       <c r="Q12" s="434"/>
@@ -41002,19 +41002,19 @@
     </row>
     <row r="13" spans="1:36" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="230"/>
-      <c r="B13" s="1065"/>
-      <c r="C13" s="1066"/>
-      <c r="D13" s="1066"/>
-      <c r="E13" s="1067"/>
-      <c r="F13" s="1057"/>
-      <c r="G13" s="1058"/>
-      <c r="H13" s="1058"/>
-      <c r="I13" s="1058"/>
-      <c r="J13" s="1058"/>
-      <c r="K13" s="1058"/>
-      <c r="L13" s="1058"/>
-      <c r="M13" s="1060"/>
-      <c r="N13" s="1061"/>
+      <c r="B13" s="913"/>
+      <c r="C13" s="914"/>
+      <c r="D13" s="914"/>
+      <c r="E13" s="915"/>
+      <c r="F13" s="902"/>
+      <c r="G13" s="903"/>
+      <c r="H13" s="903"/>
+      <c r="I13" s="903"/>
+      <c r="J13" s="903"/>
+      <c r="K13" s="903"/>
+      <c r="L13" s="903"/>
+      <c r="M13" s="905"/>
+      <c r="N13" s="906"/>
       <c r="O13" s="364"/>
       <c r="P13" s="79"/>
       <c r="Q13" s="419"/>
@@ -41081,25 +41081,25 @@
     </row>
     <row r="14" spans="1:36" ht="13.5" customHeight="1">
       <c r="A14" s="405"/>
-      <c r="B14" s="1065"/>
-      <c r="C14" s="1066"/>
-      <c r="D14" s="1066"/>
-      <c r="E14" s="1067"/>
-      <c r="F14" s="1071" t="s">
+      <c r="B14" s="913"/>
+      <c r="C14" s="914"/>
+      <c r="D14" s="914"/>
+      <c r="E14" s="915"/>
+      <c r="F14" s="919" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="1072"/>
-      <c r="H14" s="1075" t="s">
+      <c r="G14" s="920"/>
+      <c r="H14" s="923" t="s">
         <v>153</v>
       </c>
-      <c r="I14" s="1076"/>
-      <c r="J14" s="1079" t="s">
+      <c r="I14" s="924"/>
+      <c r="J14" s="927" t="s">
         <v>154</v>
       </c>
-      <c r="K14" s="1080"/>
-      <c r="L14" s="1080"/>
-      <c r="M14" s="1060"/>
-      <c r="N14" s="1061"/>
+      <c r="K14" s="928"/>
+      <c r="L14" s="928"/>
+      <c r="M14" s="905"/>
+      <c r="N14" s="906"/>
       <c r="O14" s="364"/>
       <c r="P14" s="79"/>
       <c r="Q14" s="419"/>
@@ -41168,19 +41168,19 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1">
       <c r="A15" s="405"/>
-      <c r="B15" s="1068"/>
-      <c r="C15" s="1069"/>
-      <c r="D15" s="1069"/>
-      <c r="E15" s="1070"/>
-      <c r="F15" s="1073"/>
-      <c r="G15" s="1074"/>
-      <c r="H15" s="1077"/>
-      <c r="I15" s="1078"/>
-      <c r="J15" s="1079"/>
-      <c r="K15" s="1080"/>
-      <c r="L15" s="1080"/>
-      <c r="M15" s="1060"/>
-      <c r="N15" s="1061"/>
+      <c r="B15" s="916"/>
+      <c r="C15" s="917"/>
+      <c r="D15" s="917"/>
+      <c r="E15" s="918"/>
+      <c r="F15" s="921"/>
+      <c r="G15" s="922"/>
+      <c r="H15" s="925"/>
+      <c r="I15" s="926"/>
+      <c r="J15" s="927"/>
+      <c r="K15" s="928"/>
+      <c r="L15" s="928"/>
+      <c r="M15" s="905"/>
+      <c r="N15" s="906"/>
       <c r="P15" s="79"/>
       <c r="Q15" s="419"/>
       <c r="R15" s="409"/>
@@ -41246,12 +41246,12 @@
     </row>
     <row r="16" spans="1:36" ht="15.75">
       <c r="A16" s="230"/>
-      <c r="B16" s="1046" t="s">
+      <c r="B16" s="907" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="1047"/>
-      <c r="D16" s="1047"/>
-      <c r="E16" s="1047"/>
+      <c r="C16" s="908"/>
+      <c r="D16" s="908"/>
+      <c r="E16" s="908"/>
       <c r="F16" s="795">
         <v>2</v>
       </c>
@@ -41268,7 +41268,7 @@
       <c r="M16" s="795">
         <v>16</v>
       </c>
-      <c r="N16" s="1051"/>
+      <c r="N16" s="909"/>
       <c r="O16" s="364"/>
       <c r="P16" s="79"/>
       <c r="Q16" s="419"/>
@@ -41293,12 +41293,12 @@
     </row>
     <row r="17" spans="1:36" ht="15.75">
       <c r="A17" s="405"/>
-      <c r="B17" s="1046" t="s">
+      <c r="B17" s="907" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="1047"/>
-      <c r="D17" s="1047"/>
-      <c r="E17" s="1047"/>
+      <c r="C17" s="908"/>
+      <c r="D17" s="908"/>
+      <c r="E17" s="908"/>
       <c r="F17" s="795">
         <v>0</v>
       </c>
@@ -41315,7 +41315,7 @@
       <c r="M17" s="795">
         <v>10</v>
       </c>
-      <c r="N17" s="1051"/>
+      <c r="N17" s="909"/>
       <c r="O17" s="116"/>
       <c r="P17" s="79"/>
       <c r="Q17" s="416"/>
@@ -41382,29 +41382,29 @@
     </row>
     <row r="18" spans="1:36" ht="16.5" thickBot="1">
       <c r="A18" s="230"/>
-      <c r="B18" s="1048" t="s">
+      <c r="B18" s="991" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="1049"/>
-      <c r="D18" s="1049"/>
-      <c r="E18" s="1049"/>
-      <c r="F18" s="1050">
+      <c r="C18" s="992"/>
+      <c r="D18" s="992"/>
+      <c r="E18" s="992"/>
+      <c r="F18" s="898">
         <v>10</v>
       </c>
-      <c r="G18" s="1050"/>
-      <c r="H18" s="1050">
+      <c r="G18" s="898"/>
+      <c r="H18" s="898">
         <v>38</v>
       </c>
-      <c r="I18" s="1050"/>
-      <c r="J18" s="1029">
+      <c r="I18" s="898"/>
+      <c r="J18" s="974">
         <v>25</v>
       </c>
-      <c r="K18" s="1030"/>
-      <c r="L18" s="1031"/>
-      <c r="M18" s="1050">
+      <c r="K18" s="975"/>
+      <c r="L18" s="976"/>
+      <c r="M18" s="898">
         <v>38</v>
       </c>
-      <c r="N18" s="1054"/>
+      <c r="N18" s="899"/>
       <c r="O18" s="155"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="419"/>
@@ -41950,15 +41950,15 @@
       <c r="M27" s="82"/>
       <c r="N27" s="82"/>
       <c r="P27" s="390"/>
-      <c r="Q27" s="989" t="s">
+      <c r="Q27" s="932" t="s">
         <v>157</v>
       </c>
-      <c r="R27" s="990"/>
-      <c r="S27" s="990"/>
-      <c r="T27" s="990"/>
-      <c r="U27" s="990"/>
-      <c r="V27" s="990"/>
-      <c r="W27" s="991"/>
+      <c r="R27" s="933"/>
+      <c r="S27" s="933"/>
+      <c r="T27" s="933"/>
+      <c r="U27" s="933"/>
+      <c r="V27" s="933"/>
+      <c r="W27" s="934"/>
       <c r="X27" s="394"/>
       <c r="Y27" s="386"/>
       <c r="Z27" s="227"/>
@@ -42030,11 +42030,11 @@
       <c r="Q29" s="387"/>
       <c r="R29" s="193"/>
       <c r="S29" s="193"/>
-      <c r="T29" s="992" t="s">
+      <c r="T29" s="937" t="s">
         <v>156</v>
       </c>
-      <c r="U29" s="993"/>
-      <c r="V29" s="994"/>
+      <c r="U29" s="938"/>
+      <c r="V29" s="939"/>
       <c r="W29" s="400"/>
       <c r="X29" s="387"/>
       <c r="Y29" s="193"/>
@@ -42065,29 +42065,29 @@
       <c r="M30" s="82"/>
       <c r="N30" s="82"/>
       <c r="O30" s="88"/>
-      <c r="Q30" s="920" t="s">
+      <c r="Q30" s="935" t="s">
         <v>50</v>
       </c>
-      <c r="R30" s="921"/>
-      <c r="S30" s="921"/>
-      <c r="T30" s="995"/>
-      <c r="U30" s="996"/>
-      <c r="V30" s="997"/>
-      <c r="W30" s="920" t="s">
+      <c r="R30" s="936"/>
+      <c r="S30" s="936"/>
+      <c r="T30" s="940"/>
+      <c r="U30" s="941"/>
+      <c r="V30" s="942"/>
+      <c r="W30" s="935" t="s">
         <v>51</v>
       </c>
-      <c r="X30" s="921"/>
-      <c r="Y30" s="921"/>
-      <c r="Z30" s="976" t="s">
+      <c r="X30" s="936"/>
+      <c r="Y30" s="936"/>
+      <c r="Z30" s="1015" t="s">
         <v>52</v>
       </c>
-      <c r="AA30" s="921"/>
-      <c r="AB30" s="981"/>
-      <c r="AC30" s="976" t="s">
+      <c r="AA30" s="936"/>
+      <c r="AB30" s="1024"/>
+      <c r="AC30" s="1015" t="s">
         <v>53</v>
       </c>
-      <c r="AD30" s="921"/>
-      <c r="AE30" s="977"/>
+      <c r="AD30" s="936"/>
+      <c r="AE30" s="1016"/>
       <c r="AF30" s="388"/>
       <c r="AG30" s="227"/>
       <c r="AH30" s="82"/>
@@ -42110,21 +42110,21 @@
       <c r="N31" s="82"/>
       <c r="O31" s="83"/>
       <c r="P31" s="103"/>
-      <c r="Q31" s="938"/>
-      <c r="R31" s="939"/>
-      <c r="S31" s="940"/>
-      <c r="T31" s="947"/>
-      <c r="U31" s="948"/>
-      <c r="V31" s="949"/>
-      <c r="W31" s="922"/>
-      <c r="X31" s="923"/>
-      <c r="Y31" s="923"/>
-      <c r="Z31" s="978"/>
-      <c r="AA31" s="979"/>
-      <c r="AB31" s="982"/>
-      <c r="AC31" s="978"/>
-      <c r="AD31" s="979"/>
-      <c r="AE31" s="980"/>
+      <c r="Q31" s="1062"/>
+      <c r="R31" s="1063"/>
+      <c r="S31" s="1064"/>
+      <c r="T31" s="1065"/>
+      <c r="U31" s="1066"/>
+      <c r="V31" s="1067"/>
+      <c r="W31" s="1051"/>
+      <c r="X31" s="1052"/>
+      <c r="Y31" s="1052"/>
+      <c r="Z31" s="1017"/>
+      <c r="AA31" s="1018"/>
+      <c r="AB31" s="1025"/>
+      <c r="AC31" s="1017"/>
+      <c r="AD31" s="1018"/>
+      <c r="AE31" s="1019"/>
       <c r="AF31" s="389"/>
       <c r="AG31" s="82"/>
       <c r="AH31" s="82"/>
@@ -42147,21 +42147,21 @@
       <c r="N32" s="90"/>
       <c r="O32" s="83"/>
       <c r="P32" s="79"/>
-      <c r="Q32" s="941"/>
-      <c r="R32" s="942"/>
-      <c r="S32" s="943"/>
-      <c r="T32" s="931"/>
-      <c r="U32" s="932"/>
-      <c r="V32" s="933"/>
-      <c r="W32" s="924"/>
-      <c r="X32" s="925"/>
-      <c r="Y32" s="925"/>
-      <c r="Z32" s="961"/>
-      <c r="AA32" s="962"/>
-      <c r="AB32" s="973"/>
-      <c r="AC32" s="961"/>
-      <c r="AD32" s="962"/>
-      <c r="AE32" s="963"/>
+      <c r="Q32" s="1002"/>
+      <c r="R32" s="1003"/>
+      <c r="S32" s="1004"/>
+      <c r="T32" s="1012"/>
+      <c r="U32" s="1013"/>
+      <c r="V32" s="1014"/>
+      <c r="W32" s="1010"/>
+      <c r="X32" s="1011"/>
+      <c r="Y32" s="1011"/>
+      <c r="Z32" s="1020"/>
+      <c r="AA32" s="1021"/>
+      <c r="AB32" s="1026"/>
+      <c r="AC32" s="1020"/>
+      <c r="AD32" s="1021"/>
+      <c r="AE32" s="1022"/>
       <c r="AF32" s="80"/>
       <c r="AG32" s="82"/>
       <c r="AH32" s="82"/>
@@ -42169,42 +42169,42 @@
     </row>
     <row r="33" spans="1:35" ht="19.5" thickBot="1">
       <c r="A33" s="230"/>
-      <c r="B33" s="912" t="s">
+      <c r="B33" s="1031" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="954"/>
-      <c r="D33" s="954"/>
-      <c r="E33" s="913"/>
-      <c r="F33" s="909" t="s">
+      <c r="C33" s="1032"/>
+      <c r="D33" s="1032"/>
+      <c r="E33" s="1033"/>
+      <c r="F33" s="1078" t="s">
         <v>159</v>
       </c>
-      <c r="G33" s="910"/>
-      <c r="H33" s="910"/>
-      <c r="I33" s="910"/>
-      <c r="J33" s="910"/>
-      <c r="K33" s="910"/>
-      <c r="L33" s="911"/>
-      <c r="M33" s="912" t="s">
+      <c r="G33" s="1079"/>
+      <c r="H33" s="1079"/>
+      <c r="I33" s="1079"/>
+      <c r="J33" s="1079"/>
+      <c r="K33" s="1079"/>
+      <c r="L33" s="1080"/>
+      <c r="M33" s="1031" t="s">
         <v>88</v>
       </c>
-      <c r="N33" s="913"/>
+      <c r="N33" s="1033"/>
       <c r="O33" s="78"/>
       <c r="P33" s="103"/>
-      <c r="Q33" s="941"/>
-      <c r="R33" s="942"/>
-      <c r="S33" s="943"/>
-      <c r="T33" s="931"/>
-      <c r="U33" s="932"/>
-      <c r="V33" s="933"/>
-      <c r="W33" s="924"/>
-      <c r="X33" s="925"/>
-      <c r="Y33" s="925"/>
-      <c r="Z33" s="961"/>
-      <c r="AA33" s="962"/>
-      <c r="AB33" s="973"/>
-      <c r="AC33" s="961"/>
-      <c r="AD33" s="962"/>
-      <c r="AE33" s="963"/>
+      <c r="Q33" s="1002"/>
+      <c r="R33" s="1003"/>
+      <c r="S33" s="1004"/>
+      <c r="T33" s="1012"/>
+      <c r="U33" s="1013"/>
+      <c r="V33" s="1014"/>
+      <c r="W33" s="1010"/>
+      <c r="X33" s="1011"/>
+      <c r="Y33" s="1011"/>
+      <c r="Z33" s="1020"/>
+      <c r="AA33" s="1021"/>
+      <c r="AB33" s="1026"/>
+      <c r="AC33" s="1020"/>
+      <c r="AD33" s="1021"/>
+      <c r="AE33" s="1022"/>
       <c r="AF33" s="80"/>
       <c r="AG33" s="82"/>
       <c r="AH33" s="82"/>
@@ -42212,42 +42212,42 @@
     </row>
     <row r="34" spans="1:35" ht="30.75" customHeight="1" thickBot="1">
       <c r="A34" s="233"/>
-      <c r="B34" s="914"/>
-      <c r="C34" s="955"/>
-      <c r="D34" s="955"/>
-      <c r="E34" s="915"/>
-      <c r="F34" s="956" t="s">
+      <c r="B34" s="1034"/>
+      <c r="C34" s="1035"/>
+      <c r="D34" s="1035"/>
+      <c r="E34" s="1036"/>
+      <c r="F34" s="1037" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="957"/>
-      <c r="H34" s="958"/>
-      <c r="I34" s="959" t="s">
+      <c r="G34" s="1038"/>
+      <c r="H34" s="1039"/>
+      <c r="I34" s="1040" t="s">
         <v>161</v>
       </c>
-      <c r="J34" s="960"/>
-      <c r="K34" s="907" t="s">
+      <c r="J34" s="1041"/>
+      <c r="K34" s="1076" t="s">
         <v>162</v>
       </c>
-      <c r="L34" s="908"/>
-      <c r="M34" s="914"/>
-      <c r="N34" s="915"/>
+      <c r="L34" s="1077"/>
+      <c r="M34" s="1034"/>
+      <c r="N34" s="1036"/>
       <c r="O34" s="78"/>
       <c r="P34" s="103"/>
-      <c r="Q34" s="941"/>
-      <c r="R34" s="942"/>
-      <c r="S34" s="943"/>
-      <c r="T34" s="931"/>
-      <c r="U34" s="932"/>
-      <c r="V34" s="933"/>
-      <c r="W34" s="924"/>
-      <c r="X34" s="925"/>
-      <c r="Y34" s="925"/>
-      <c r="Z34" s="961"/>
-      <c r="AA34" s="962"/>
-      <c r="AB34" s="973"/>
-      <c r="AC34" s="961"/>
-      <c r="AD34" s="962"/>
-      <c r="AE34" s="963"/>
+      <c r="Q34" s="1002"/>
+      <c r="R34" s="1003"/>
+      <c r="S34" s="1004"/>
+      <c r="T34" s="1012"/>
+      <c r="U34" s="1013"/>
+      <c r="V34" s="1014"/>
+      <c r="W34" s="1010"/>
+      <c r="X34" s="1011"/>
+      <c r="Y34" s="1011"/>
+      <c r="Z34" s="1020"/>
+      <c r="AA34" s="1021"/>
+      <c r="AB34" s="1026"/>
+      <c r="AC34" s="1020"/>
+      <c r="AD34" s="1021"/>
+      <c r="AE34" s="1022"/>
       <c r="AF34" s="80"/>
       <c r="AG34" s="82"/>
       <c r="AH34" s="82"/>
@@ -42255,46 +42255,46 @@
     </row>
     <row r="35" spans="1:35" ht="22.5" customHeight="1">
       <c r="A35" s="407"/>
-      <c r="B35" s="919" t="s">
+      <c r="B35" s="1050" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="919"/>
-      <c r="D35" s="919"/>
-      <c r="E35" s="919"/>
-      <c r="F35" s="919">
+      <c r="C35" s="1050"/>
+      <c r="D35" s="1050"/>
+      <c r="E35" s="1050"/>
+      <c r="F35" s="1050">
         <v>4</v>
       </c>
-      <c r="G35" s="919"/>
-      <c r="H35" s="919"/>
-      <c r="I35" s="919">
+      <c r="G35" s="1050"/>
+      <c r="H35" s="1050"/>
+      <c r="I35" s="1050">
         <v>10</v>
       </c>
-      <c r="J35" s="919"/>
-      <c r="K35" s="919">
+      <c r="J35" s="1050"/>
+      <c r="K35" s="1050">
         <v>0</v>
       </c>
-      <c r="L35" s="919"/>
-      <c r="M35" s="919">
+      <c r="L35" s="1050"/>
+      <c r="M35" s="1050">
         <v>20</v>
       </c>
-      <c r="N35" s="919"/>
+      <c r="N35" s="1050"/>
       <c r="O35" s="83"/>
       <c r="P35" s="79"/>
-      <c r="Q35" s="944"/>
-      <c r="R35" s="945"/>
-      <c r="S35" s="946"/>
-      <c r="T35" s="916"/>
-      <c r="U35" s="917"/>
-      <c r="V35" s="918"/>
-      <c r="W35" s="905"/>
-      <c r="X35" s="906"/>
-      <c r="Y35" s="906"/>
-      <c r="Z35" s="964"/>
-      <c r="AA35" s="965"/>
-      <c r="AB35" s="971"/>
-      <c r="AC35" s="964"/>
-      <c r="AD35" s="965"/>
-      <c r="AE35" s="966"/>
+      <c r="Q35" s="999"/>
+      <c r="R35" s="1000"/>
+      <c r="S35" s="1001"/>
+      <c r="T35" s="1005"/>
+      <c r="U35" s="1006"/>
+      <c r="V35" s="1007"/>
+      <c r="W35" s="1008"/>
+      <c r="X35" s="1009"/>
+      <c r="Y35" s="1009"/>
+      <c r="Z35" s="993"/>
+      <c r="AA35" s="994"/>
+      <c r="AB35" s="1023"/>
+      <c r="AC35" s="993"/>
+      <c r="AD35" s="994"/>
+      <c r="AE35" s="995"/>
       <c r="AF35" s="80"/>
       <c r="AG35" s="82"/>
       <c r="AH35" s="82"/>
@@ -42312,21 +42312,21 @@
       <c r="M36" s="402"/>
       <c r="N36" s="401"/>
       <c r="O36" s="90"/>
-      <c r="Q36" s="944"/>
-      <c r="R36" s="945"/>
-      <c r="S36" s="946"/>
-      <c r="T36" s="916"/>
-      <c r="U36" s="917"/>
-      <c r="V36" s="918"/>
-      <c r="W36" s="905"/>
-      <c r="X36" s="906"/>
-      <c r="Y36" s="906"/>
-      <c r="Z36" s="964"/>
-      <c r="AA36" s="965"/>
-      <c r="AB36" s="971"/>
-      <c r="AC36" s="964"/>
-      <c r="AD36" s="965"/>
-      <c r="AE36" s="966"/>
+      <c r="Q36" s="999"/>
+      <c r="R36" s="1000"/>
+      <c r="S36" s="1001"/>
+      <c r="T36" s="1005"/>
+      <c r="U36" s="1006"/>
+      <c r="V36" s="1007"/>
+      <c r="W36" s="1008"/>
+      <c r="X36" s="1009"/>
+      <c r="Y36" s="1009"/>
+      <c r="Z36" s="993"/>
+      <c r="AA36" s="994"/>
+      <c r="AB36" s="1023"/>
+      <c r="AC36" s="993"/>
+      <c r="AD36" s="994"/>
+      <c r="AE36" s="995"/>
       <c r="AF36" s="80"/>
       <c r="AG36" s="82"/>
       <c r="AH36" s="82"/>
@@ -42349,21 +42349,21 @@
       <c r="N37" s="82"/>
       <c r="O37" s="80"/>
       <c r="P37" s="79"/>
-      <c r="Q37" s="944"/>
-      <c r="R37" s="945"/>
-      <c r="S37" s="946"/>
-      <c r="T37" s="916"/>
-      <c r="U37" s="917"/>
-      <c r="V37" s="918"/>
-      <c r="W37" s="905"/>
-      <c r="X37" s="906"/>
-      <c r="Y37" s="906"/>
-      <c r="Z37" s="964"/>
-      <c r="AA37" s="965"/>
-      <c r="AB37" s="971"/>
-      <c r="AC37" s="964"/>
-      <c r="AD37" s="965"/>
-      <c r="AE37" s="966"/>
+      <c r="Q37" s="999"/>
+      <c r="R37" s="1000"/>
+      <c r="S37" s="1001"/>
+      <c r="T37" s="1005"/>
+      <c r="U37" s="1006"/>
+      <c r="V37" s="1007"/>
+      <c r="W37" s="1008"/>
+      <c r="X37" s="1009"/>
+      <c r="Y37" s="1009"/>
+      <c r="Z37" s="993"/>
+      <c r="AA37" s="994"/>
+      <c r="AB37" s="1023"/>
+      <c r="AC37" s="993"/>
+      <c r="AD37" s="994"/>
+      <c r="AE37" s="995"/>
       <c r="AF37" s="80"/>
       <c r="AG37" s="82"/>
       <c r="AH37" s="82"/>
@@ -42386,21 +42386,21 @@
       <c r="N38" s="82"/>
       <c r="O38" s="80"/>
       <c r="P38" s="79"/>
-      <c r="Q38" s="944"/>
-      <c r="R38" s="945"/>
-      <c r="S38" s="946"/>
-      <c r="T38" s="916"/>
-      <c r="U38" s="917"/>
-      <c r="V38" s="918"/>
-      <c r="W38" s="905"/>
-      <c r="X38" s="906"/>
-      <c r="Y38" s="906"/>
-      <c r="Z38" s="964"/>
-      <c r="AA38" s="965"/>
-      <c r="AB38" s="971"/>
-      <c r="AC38" s="964"/>
-      <c r="AD38" s="965"/>
-      <c r="AE38" s="966"/>
+      <c r="Q38" s="999"/>
+      <c r="R38" s="1000"/>
+      <c r="S38" s="1001"/>
+      <c r="T38" s="1005"/>
+      <c r="U38" s="1006"/>
+      <c r="V38" s="1007"/>
+      <c r="W38" s="1008"/>
+      <c r="X38" s="1009"/>
+      <c r="Y38" s="1009"/>
+      <c r="Z38" s="993"/>
+      <c r="AA38" s="994"/>
+      <c r="AB38" s="1023"/>
+      <c r="AC38" s="993"/>
+      <c r="AD38" s="994"/>
+      <c r="AE38" s="995"/>
       <c r="AF38" s="105"/>
       <c r="AG38" s="104"/>
       <c r="AH38" s="82"/>
@@ -42422,21 +42422,21 @@
       <c r="M39" s="82"/>
       <c r="N39" s="82"/>
       <c r="P39" s="79"/>
-      <c r="Q39" s="944"/>
-      <c r="R39" s="945"/>
-      <c r="S39" s="946"/>
-      <c r="T39" s="916"/>
-      <c r="U39" s="917"/>
-      <c r="V39" s="918"/>
-      <c r="W39" s="905"/>
-      <c r="X39" s="906"/>
-      <c r="Y39" s="906"/>
-      <c r="Z39" s="964"/>
-      <c r="AA39" s="965"/>
-      <c r="AB39" s="971"/>
-      <c r="AC39" s="964"/>
-      <c r="AD39" s="965"/>
-      <c r="AE39" s="966"/>
+      <c r="Q39" s="999"/>
+      <c r="R39" s="1000"/>
+      <c r="S39" s="1001"/>
+      <c r="T39" s="1005"/>
+      <c r="U39" s="1006"/>
+      <c r="V39" s="1007"/>
+      <c r="W39" s="1008"/>
+      <c r="X39" s="1009"/>
+      <c r="Y39" s="1009"/>
+      <c r="Z39" s="993"/>
+      <c r="AA39" s="994"/>
+      <c r="AB39" s="1023"/>
+      <c r="AC39" s="993"/>
+      <c r="AD39" s="994"/>
+      <c r="AE39" s="995"/>
       <c r="AF39" s="80"/>
       <c r="AG39" s="82"/>
       <c r="AH39" s="82"/>
@@ -42459,21 +42459,21 @@
       <c r="N40" s="82"/>
       <c r="O40" s="83"/>
       <c r="P40" s="87"/>
-      <c r="Q40" s="944"/>
-      <c r="R40" s="945"/>
-      <c r="S40" s="946"/>
-      <c r="T40" s="916"/>
-      <c r="U40" s="917"/>
-      <c r="V40" s="918"/>
-      <c r="W40" s="905"/>
-      <c r="X40" s="906"/>
-      <c r="Y40" s="906"/>
-      <c r="Z40" s="964"/>
-      <c r="AA40" s="965"/>
-      <c r="AB40" s="971"/>
-      <c r="AC40" s="964"/>
-      <c r="AD40" s="965"/>
-      <c r="AE40" s="966"/>
+      <c r="Q40" s="999"/>
+      <c r="R40" s="1000"/>
+      <c r="S40" s="1001"/>
+      <c r="T40" s="1005"/>
+      <c r="U40" s="1006"/>
+      <c r="V40" s="1007"/>
+      <c r="W40" s="1008"/>
+      <c r="X40" s="1009"/>
+      <c r="Y40" s="1009"/>
+      <c r="Z40" s="993"/>
+      <c r="AA40" s="994"/>
+      <c r="AB40" s="1023"/>
+      <c r="AC40" s="993"/>
+      <c r="AD40" s="994"/>
+      <c r="AE40" s="995"/>
       <c r="AF40" s="80"/>
       <c r="AG40" s="82"/>
       <c r="AH40" s="82"/>
@@ -42496,21 +42496,21 @@
       <c r="N41" s="82"/>
       <c r="O41" s="78"/>
       <c r="P41" s="79"/>
-      <c r="Q41" s="941"/>
-      <c r="R41" s="942"/>
-      <c r="S41" s="943"/>
-      <c r="T41" s="931"/>
-      <c r="U41" s="932"/>
-      <c r="V41" s="933"/>
-      <c r="W41" s="924"/>
-      <c r="X41" s="925"/>
-      <c r="Y41" s="925"/>
-      <c r="Z41" s="961"/>
-      <c r="AA41" s="962"/>
-      <c r="AB41" s="973"/>
-      <c r="AC41" s="961"/>
-      <c r="AD41" s="962"/>
-      <c r="AE41" s="963"/>
+      <c r="Q41" s="1002"/>
+      <c r="R41" s="1003"/>
+      <c r="S41" s="1004"/>
+      <c r="T41" s="1012"/>
+      <c r="U41" s="1013"/>
+      <c r="V41" s="1014"/>
+      <c r="W41" s="1010"/>
+      <c r="X41" s="1011"/>
+      <c r="Y41" s="1011"/>
+      <c r="Z41" s="1020"/>
+      <c r="AA41" s="1021"/>
+      <c r="AB41" s="1026"/>
+      <c r="AC41" s="1020"/>
+      <c r="AD41" s="1021"/>
+      <c r="AE41" s="1022"/>
       <c r="AF41" s="80"/>
       <c r="AG41" s="82"/>
       <c r="AH41" s="82"/>
@@ -42533,21 +42533,21 @@
       <c r="N42" s="82"/>
       <c r="O42" s="80"/>
       <c r="P42" s="79"/>
-      <c r="Q42" s="941"/>
-      <c r="R42" s="942"/>
-      <c r="S42" s="943"/>
-      <c r="T42" s="931"/>
-      <c r="U42" s="932"/>
-      <c r="V42" s="933"/>
-      <c r="W42" s="924"/>
-      <c r="X42" s="925"/>
-      <c r="Y42" s="925"/>
-      <c r="Z42" s="961"/>
-      <c r="AA42" s="962"/>
-      <c r="AB42" s="973"/>
-      <c r="AC42" s="961"/>
-      <c r="AD42" s="962"/>
-      <c r="AE42" s="963"/>
+      <c r="Q42" s="1002"/>
+      <c r="R42" s="1003"/>
+      <c r="S42" s="1004"/>
+      <c r="T42" s="1012"/>
+      <c r="U42" s="1013"/>
+      <c r="V42" s="1014"/>
+      <c r="W42" s="1010"/>
+      <c r="X42" s="1011"/>
+      <c r="Y42" s="1011"/>
+      <c r="Z42" s="1020"/>
+      <c r="AA42" s="1021"/>
+      <c r="AB42" s="1026"/>
+      <c r="AC42" s="1020"/>
+      <c r="AD42" s="1021"/>
+      <c r="AE42" s="1022"/>
       <c r="AF42" s="80"/>
       <c r="AG42" s="82"/>
       <c r="AH42" s="82"/>
@@ -42569,21 +42569,21 @@
       <c r="M43" s="82"/>
       <c r="N43" s="82"/>
       <c r="P43" s="79"/>
-      <c r="Q43" s="983"/>
-      <c r="R43" s="984"/>
-      <c r="S43" s="985"/>
-      <c r="T43" s="916"/>
-      <c r="U43" s="917"/>
-      <c r="V43" s="918"/>
-      <c r="W43" s="905"/>
-      <c r="X43" s="906"/>
-      <c r="Y43" s="906"/>
-      <c r="Z43" s="964"/>
-      <c r="AA43" s="965"/>
-      <c r="AB43" s="971"/>
-      <c r="AC43" s="964"/>
-      <c r="AD43" s="965"/>
-      <c r="AE43" s="966"/>
+      <c r="Q43" s="996"/>
+      <c r="R43" s="997"/>
+      <c r="S43" s="998"/>
+      <c r="T43" s="1005"/>
+      <c r="U43" s="1006"/>
+      <c r="V43" s="1007"/>
+      <c r="W43" s="1008"/>
+      <c r="X43" s="1009"/>
+      <c r="Y43" s="1009"/>
+      <c r="Z43" s="993"/>
+      <c r="AA43" s="994"/>
+      <c r="AB43" s="1023"/>
+      <c r="AC43" s="993"/>
+      <c r="AD43" s="994"/>
+      <c r="AE43" s="995"/>
       <c r="AF43" s="80"/>
       <c r="AG43" s="82"/>
       <c r="AH43" s="82"/>
@@ -42606,21 +42606,21 @@
       <c r="N44" s="82"/>
       <c r="O44" s="78"/>
       <c r="P44" s="103"/>
-      <c r="Q44" s="983"/>
-      <c r="R44" s="984"/>
-      <c r="S44" s="985"/>
-      <c r="T44" s="916"/>
-      <c r="U44" s="917"/>
-      <c r="V44" s="918"/>
-      <c r="W44" s="905"/>
-      <c r="X44" s="906"/>
-      <c r="Y44" s="906"/>
-      <c r="Z44" s="964"/>
-      <c r="AA44" s="965"/>
-      <c r="AB44" s="971"/>
-      <c r="AC44" s="964"/>
-      <c r="AD44" s="965"/>
-      <c r="AE44" s="966"/>
+      <c r="Q44" s="996"/>
+      <c r="R44" s="997"/>
+      <c r="S44" s="998"/>
+      <c r="T44" s="1005"/>
+      <c r="U44" s="1006"/>
+      <c r="V44" s="1007"/>
+      <c r="W44" s="1008"/>
+      <c r="X44" s="1009"/>
+      <c r="Y44" s="1009"/>
+      <c r="Z44" s="993"/>
+      <c r="AA44" s="994"/>
+      <c r="AB44" s="1023"/>
+      <c r="AC44" s="993"/>
+      <c r="AD44" s="994"/>
+      <c r="AE44" s="995"/>
       <c r="AF44" s="80"/>
       <c r="AG44" s="82"/>
       <c r="AH44" s="82"/>
@@ -42643,21 +42643,21 @@
       <c r="N45" s="82"/>
       <c r="O45" s="83"/>
       <c r="P45" s="103"/>
-      <c r="Q45" s="899"/>
-      <c r="R45" s="900"/>
-      <c r="S45" s="901"/>
-      <c r="T45" s="935"/>
-      <c r="U45" s="936"/>
-      <c r="V45" s="937"/>
-      <c r="W45" s="974"/>
-      <c r="X45" s="975"/>
-      <c r="Y45" s="975"/>
-      <c r="Z45" s="967"/>
-      <c r="AA45" s="968"/>
-      <c r="AB45" s="972"/>
-      <c r="AC45" s="967"/>
-      <c r="AD45" s="968"/>
-      <c r="AE45" s="969"/>
+      <c r="Q45" s="1071"/>
+      <c r="R45" s="1072"/>
+      <c r="S45" s="1073"/>
+      <c r="T45" s="1059"/>
+      <c r="U45" s="1060"/>
+      <c r="V45" s="1061"/>
+      <c r="W45" s="1048"/>
+      <c r="X45" s="1049"/>
+      <c r="Y45" s="1049"/>
+      <c r="Z45" s="1042"/>
+      <c r="AA45" s="1043"/>
+      <c r="AB45" s="1047"/>
+      <c r="AC45" s="1042"/>
+      <c r="AD45" s="1043"/>
+      <c r="AE45" s="1044"/>
       <c r="AF45" s="80"/>
       <c r="AG45" s="82"/>
       <c r="AH45" s="82"/>
@@ -42680,21 +42680,21 @@
       <c r="N46" s="82"/>
       <c r="O46" s="83"/>
       <c r="P46" s="103"/>
-      <c r="Q46" s="902"/>
-      <c r="R46" s="903"/>
-      <c r="S46" s="903"/>
-      <c r="T46" s="934"/>
-      <c r="U46" s="934"/>
-      <c r="V46" s="934"/>
-      <c r="W46" s="904"/>
-      <c r="X46" s="904"/>
-      <c r="Y46" s="904"/>
-      <c r="Z46" s="904"/>
-      <c r="AA46" s="904"/>
-      <c r="AB46" s="904"/>
-      <c r="AC46" s="904"/>
-      <c r="AD46" s="904"/>
-      <c r="AE46" s="970"/>
+      <c r="Q46" s="1074"/>
+      <c r="R46" s="1075"/>
+      <c r="S46" s="1075"/>
+      <c r="T46" s="1058"/>
+      <c r="U46" s="1058"/>
+      <c r="V46" s="1058"/>
+      <c r="W46" s="1045"/>
+      <c r="X46" s="1045"/>
+      <c r="Y46" s="1045"/>
+      <c r="Z46" s="1045"/>
+      <c r="AA46" s="1045"/>
+      <c r="AB46" s="1045"/>
+      <c r="AC46" s="1045"/>
+      <c r="AD46" s="1045"/>
+      <c r="AE46" s="1046"/>
       <c r="AF46" s="80"/>
       <c r="AG46" s="82"/>
       <c r="AH46" s="82"/>
@@ -42717,21 +42717,21 @@
       <c r="N47" s="82"/>
       <c r="O47" s="83"/>
       <c r="P47" s="103"/>
-      <c r="Q47" s="896"/>
-      <c r="R47" s="897"/>
-      <c r="S47" s="898"/>
-      <c r="T47" s="926"/>
-      <c r="U47" s="927"/>
-      <c r="V47" s="928"/>
-      <c r="W47" s="929"/>
-      <c r="X47" s="930"/>
-      <c r="Y47" s="930"/>
-      <c r="Z47" s="950"/>
-      <c r="AA47" s="951"/>
-      <c r="AB47" s="952"/>
-      <c r="AC47" s="950"/>
-      <c r="AD47" s="951"/>
-      <c r="AE47" s="953"/>
+      <c r="Q47" s="1068"/>
+      <c r="R47" s="1069"/>
+      <c r="S47" s="1070"/>
+      <c r="T47" s="1053"/>
+      <c r="U47" s="1054"/>
+      <c r="V47" s="1055"/>
+      <c r="W47" s="1056"/>
+      <c r="X47" s="1057"/>
+      <c r="Y47" s="1057"/>
+      <c r="Z47" s="1027"/>
+      <c r="AA47" s="1028"/>
+      <c r="AB47" s="1029"/>
+      <c r="AC47" s="1027"/>
+      <c r="AD47" s="1028"/>
+      <c r="AE47" s="1030"/>
       <c r="AF47" s="83"/>
       <c r="AG47" s="90"/>
       <c r="AH47" s="82"/>
@@ -43035,21 +43035,105 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F12:L13"/>
-    <mergeCell ref="M12:N15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B12:E15"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="W46:Y46"/>
+    <mergeCell ref="W38:Y38"/>
+    <mergeCell ref="W39:Y39"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="T36:V36"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="W30:Y30"/>
+    <mergeCell ref="W31:Y31"/>
+    <mergeCell ref="W32:Y32"/>
+    <mergeCell ref="T47:V47"/>
+    <mergeCell ref="W47:Y47"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="T46:V46"/>
+    <mergeCell ref="T45:V45"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="T31:V31"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="T35:V35"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AC47:AE47"/>
+    <mergeCell ref="B33:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="AC41:AE41"/>
+    <mergeCell ref="AC42:AE42"/>
+    <mergeCell ref="AC43:AE43"/>
+    <mergeCell ref="AC44:AE44"/>
+    <mergeCell ref="AC45:AE45"/>
+    <mergeCell ref="AC46:AE46"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="W33:Y33"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="W35:Y35"/>
+    <mergeCell ref="W36:Y36"/>
+    <mergeCell ref="W37:Y37"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="AC33:AE33"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="Z31:AB31"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="AC38:AE38"/>
+    <mergeCell ref="AC39:AE39"/>
+    <mergeCell ref="AC40:AE40"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="W40:Y40"/>
+    <mergeCell ref="W41:Y41"/>
+    <mergeCell ref="W42:Y42"/>
+    <mergeCell ref="W43:Y43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="T44:V44"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="Q30:S30"/>
@@ -43074,105 +43158,21 @@
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="J17:L17"/>
     <mergeCell ref="M17:N17"/>
-    <mergeCell ref="AC40:AE40"/>
-    <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="W40:Y40"/>
-    <mergeCell ref="W41:Y41"/>
-    <mergeCell ref="W42:Y42"/>
-    <mergeCell ref="W43:Y43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="T44:V44"/>
-    <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="AC32:AE32"/>
-    <mergeCell ref="AC33:AE33"/>
-    <mergeCell ref="AC34:AE34"/>
-    <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="AC36:AE36"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="Z31:AB31"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="AC37:AE37"/>
-    <mergeCell ref="AC38:AE38"/>
-    <mergeCell ref="AC39:AE39"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AC47:AE47"/>
-    <mergeCell ref="B33:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="AC41:AE41"/>
-    <mergeCell ref="AC42:AE42"/>
-    <mergeCell ref="AC43:AE43"/>
-    <mergeCell ref="AC44:AE44"/>
-    <mergeCell ref="AC45:AE45"/>
-    <mergeCell ref="AC46:AE46"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="Z45:AB45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="W33:Y33"/>
-    <mergeCell ref="W34:Y34"/>
-    <mergeCell ref="W35:Y35"/>
-    <mergeCell ref="W36:Y36"/>
-    <mergeCell ref="W37:Y37"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="W30:Y30"/>
-    <mergeCell ref="W31:Y31"/>
-    <mergeCell ref="W32:Y32"/>
-    <mergeCell ref="T47:V47"/>
-    <mergeCell ref="W47:Y47"/>
-    <mergeCell ref="T41:V41"/>
-    <mergeCell ref="T46:V46"/>
-    <mergeCell ref="T45:V45"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="T31:V31"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="T34:V34"/>
-    <mergeCell ref="T35:V35"/>
-    <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="W46:Y46"/>
-    <mergeCell ref="W38:Y38"/>
-    <mergeCell ref="W39:Y39"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="F33:L33"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="T36:V36"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F12:L13"/>
+    <mergeCell ref="M12:N15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B12:E15"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J14:L15"/>
   </mergeCells>
   <conditionalFormatting sqref="S13:AF13">
     <cfRule type="cellIs" dxfId="26" priority="29" operator="greaterThanOrEqual">
@@ -43450,14 +43450,14 @@
       <c r="G2" s="377"/>
       <c r="H2" s="377"/>
       <c r="I2" s="377"/>
-      <c r="J2" s="593" t="s">
+      <c r="J2" s="603" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="593"/>
-      <c r="L2" s="593"/>
-      <c r="M2" s="593"/>
-      <c r="N2" s="593"/>
-      <c r="O2" s="593"/>
+      <c r="K2" s="603"/>
+      <c r="L2" s="603"/>
+      <c r="M2" s="603"/>
+      <c r="N2" s="603"/>
+      <c r="O2" s="603"/>
       <c r="P2" s="377"/>
       <c r="Q2" s="377"/>
       <c r="R2" s="377"/>
@@ -43498,14 +43498,14 @@
       <c r="I4" s="378" t="s">
         <v>133</v>
       </c>
-      <c r="J4" s="592" t="s">
+      <c r="J4" s="602" t="s">
         <v>134</v>
       </c>
-      <c r="K4" s="592"/>
-      <c r="L4" s="592"/>
-      <c r="M4" s="592"/>
-      <c r="N4" s="592"/>
-      <c r="O4" s="592"/>
+      <c r="K4" s="602"/>
+      <c r="L4" s="602"/>
+      <c r="M4" s="602"/>
+      <c r="N4" s="602"/>
+      <c r="O4" s="602"/>
       <c r="P4" s="379"/>
       <c r="Q4" s="379"/>
       <c r="R4" s="380"/>
@@ -43521,17 +43521,17 @@
       <c r="G5" s="381"/>
       <c r="H5" s="381"/>
       <c r="I5" s="382"/>
-      <c r="J5" s="603" t="s">
+      <c r="J5" s="595" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="603"/>
-      <c r="L5" s="603"/>
-      <c r="M5" s="603"/>
-      <c r="N5" s="600" t="s">
+      <c r="K5" s="595"/>
+      <c r="L5" s="595"/>
+      <c r="M5" s="595"/>
+      <c r="N5" s="607" t="s">
         <v>164</v>
       </c>
-      <c r="O5" s="600"/>
-      <c r="P5" s="600"/>
+      <c r="O5" s="607"/>
+      <c r="P5" s="607"/>
       <c r="Q5" s="383"/>
       <c r="R5" s="383"/>
       <c r="S5" s="22"/>
@@ -43562,12 +43562,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="23"/>
-      <c r="C8" s="604" t="str">
+      <c r="C8" s="598" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO ABRIL - 2025</v>
       </c>
-      <c r="D8" s="605"/>
-      <c r="E8" s="606"/>
+      <c r="D8" s="599"/>
+      <c r="E8" s="600"/>
       <c r="G8" s="56" t="s">
         <v>1</v>
       </c>
@@ -43610,11 +43610,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="C10" s="607" t="s">
+      <c r="C10" s="601" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="607"/>
-      <c r="E10" s="607"/>
+      <c r="D10" s="601"/>
+      <c r="E10" s="601"/>
       <c r="G10" s="76" t="s">
         <v>8</v>
       </c>
@@ -43764,11 +43764,11 @@
       <c r="C15" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="602">
+      <c r="D15" s="593">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="602"/>
+      <c r="E15" s="593"/>
       <c r="H15" s="35"/>
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
@@ -43811,11 +43811,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="C24" s="595" t="s">
+      <c r="C24" s="604" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="596"/>
-      <c r="E24" s="597"/>
+      <c r="D24" s="605"/>
+      <c r="E24" s="606"/>
       <c r="S24" s="22"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -43823,11 +43823,11 @@
       <c r="C25" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="598">
+      <c r="D25" s="596">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="599"/>
+      <c r="E25" s="597"/>
       <c r="S25" s="22"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -43835,11 +43835,11 @@
       <c r="C26" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="598">
+      <c r="D26" s="596">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="599"/>
+      <c r="E26" s="597"/>
       <c r="S26" s="22"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -43871,11 +43871,11 @@
       <c r="C29" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="601">
+      <c r="D29" s="592">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="601"/>
+      <c r="E29" s="592"/>
       <c r="S29" s="22"/>
     </row>
     <row r="30" spans="1:19">
@@ -43989,6 +43989,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -44000,12 +44006,6 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -48777,9 +48777,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="647"/>
-      <c r="C1" s="648"/>
-      <c r="D1" s="649"/>
+      <c r="B1" s="654"/>
+      <c r="C1" s="655"/>
+      <c r="D1" s="656"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -48801,10 +48801,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="660" t="s">
+      <c r="I2" s="650" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="661"/>
+      <c r="J2" s="651"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -48858,10 +48858,10 @@
       <c r="B5" s="376" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="653" t="s">
+      <c r="C5" s="657" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="654"/>
+      <c r="D5" s="658"/>
       <c r="E5" s="373" t="s">
         <v>60</v>
       </c>
@@ -48889,8 +48889,8 @@
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
       <c r="B6" s="215"/>
-      <c r="C6" s="655"/>
-      <c r="D6" s="656"/>
+      <c r="C6" s="659"/>
+      <c r="D6" s="660"/>
       <c r="E6" s="457"/>
       <c r="F6" s="457"/>
       <c r="G6" s="457"/>
@@ -48908,8 +48908,8 @@
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="99"/>
       <c r="B7" s="216"/>
-      <c r="C7" s="657"/>
-      <c r="D7" s="658"/>
+      <c r="C7" s="661"/>
+      <c r="D7" s="662"/>
       <c r="E7" s="458"/>
       <c r="F7" s="458"/>
       <c r="G7" s="458"/>
@@ -48925,8 +48925,8 @@
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="100"/>
       <c r="B8" s="216"/>
-      <c r="C8" s="657"/>
-      <c r="D8" s="658"/>
+      <c r="C8" s="661"/>
+      <c r="D8" s="662"/>
       <c r="E8" s="458"/>
       <c r="F8" s="458"/>
       <c r="G8" s="458"/>
@@ -48943,8 +48943,8 @@
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="100"/>
       <c r="B9" s="216"/>
-      <c r="C9" s="657"/>
-      <c r="D9" s="658"/>
+      <c r="C9" s="661"/>
+      <c r="D9" s="662"/>
       <c r="E9" s="458"/>
       <c r="F9" s="458"/>
       <c r="G9" s="458"/>
@@ -48962,8 +48962,8 @@
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="102"/>
       <c r="B10" s="216"/>
-      <c r="C10" s="657"/>
-      <c r="D10" s="658"/>
+      <c r="C10" s="661"/>
+      <c r="D10" s="662"/>
       <c r="E10" s="458"/>
       <c r="F10" s="458"/>
       <c r="G10" s="458"/>
@@ -48980,8 +48980,8 @@
     <row r="11" spans="1:17" ht="55.5" customHeight="1">
       <c r="A11" s="101"/>
       <c r="B11" s="216"/>
-      <c r="C11" s="657"/>
-      <c r="D11" s="659"/>
+      <c r="C11" s="661"/>
+      <c r="D11" s="663"/>
       <c r="E11" s="458"/>
       <c r="F11" s="458"/>
       <c r="G11" s="458"/>
@@ -48997,8 +48997,8 @@
     <row r="12" spans="1:17" ht="44.25" customHeight="1">
       <c r="A12" s="101"/>
       <c r="B12" s="216"/>
-      <c r="C12" s="657"/>
-      <c r="D12" s="658"/>
+      <c r="C12" s="661"/>
+      <c r="D12" s="662"/>
       <c r="E12" s="458"/>
       <c r="F12" s="458"/>
       <c r="G12" s="458"/>
@@ -49015,8 +49015,8 @@
     <row r="13" spans="1:17" ht="63" customHeight="1" thickBot="1">
       <c r="A13" s="100"/>
       <c r="B13" s="217"/>
-      <c r="C13" s="662"/>
-      <c r="D13" s="663"/>
+      <c r="C13" s="652"/>
+      <c r="D13" s="653"/>
       <c r="E13" s="459"/>
       <c r="F13" s="459"/>
       <c r="G13" s="459"/>
@@ -49076,12 +49076,12 @@
       </c>
       <c r="C16" s="481"/>
       <c r="D16" s="294"/>
-      <c r="E16" s="650"/>
-      <c r="F16" s="651"/>
-      <c r="G16" s="651"/>
-      <c r="H16" s="651"/>
-      <c r="I16" s="651"/>
-      <c r="J16" s="652"/>
+      <c r="E16" s="647"/>
+      <c r="F16" s="648"/>
+      <c r="G16" s="648"/>
+      <c r="H16" s="648"/>
+      <c r="I16" s="648"/>
+      <c r="J16" s="649"/>
       <c r="K16" s="301"/>
       <c r="L16" s="115"/>
       <c r="M16" s="113"/>
@@ -49095,12 +49095,12 @@
       </c>
       <c r="C17" s="483"/>
       <c r="D17" s="294"/>
-      <c r="E17" s="650"/>
-      <c r="F17" s="651"/>
-      <c r="G17" s="651"/>
-      <c r="H17" s="651"/>
-      <c r="I17" s="651"/>
-      <c r="J17" s="652"/>
+      <c r="E17" s="647"/>
+      <c r="F17" s="648"/>
+      <c r="G17" s="648"/>
+      <c r="H17" s="648"/>
+      <c r="I17" s="648"/>
+      <c r="J17" s="649"/>
       <c r="K17" s="136"/>
       <c r="L17" s="123"/>
       <c r="M17" s="115"/>
@@ -49115,12 +49115,12 @@
       </c>
       <c r="C18" s="483"/>
       <c r="D18" s="295"/>
-      <c r="E18" s="650"/>
-      <c r="F18" s="651"/>
-      <c r="G18" s="651"/>
-      <c r="H18" s="651"/>
-      <c r="I18" s="651"/>
-      <c r="J18" s="652"/>
+      <c r="E18" s="647"/>
+      <c r="F18" s="648"/>
+      <c r="G18" s="648"/>
+      <c r="H18" s="648"/>
+      <c r="I18" s="648"/>
+      <c r="J18" s="649"/>
       <c r="L18" s="115"/>
       <c r="M18" s="111"/>
       <c r="N18" s="110"/>
@@ -49132,12 +49132,12 @@
       <c r="B19" s="87"/>
       <c r="C19" s="87"/>
       <c r="D19" s="296"/>
-      <c r="E19" s="650"/>
-      <c r="F19" s="651"/>
-      <c r="G19" s="651"/>
-      <c r="H19" s="651"/>
-      <c r="I19" s="651"/>
-      <c r="J19" s="652"/>
+      <c r="E19" s="647"/>
+      <c r="F19" s="648"/>
+      <c r="G19" s="648"/>
+      <c r="H19" s="648"/>
+      <c r="I19" s="648"/>
+      <c r="J19" s="649"/>
       <c r="K19" s="136"/>
       <c r="L19" s="123"/>
       <c r="M19" s="111"/>
@@ -49149,12 +49149,12 @@
       <c r="A20" s="79"/>
       <c r="B20" s="90"/>
       <c r="D20" s="295"/>
-      <c r="E20" s="650"/>
-      <c r="F20" s="651"/>
-      <c r="G20" s="651"/>
-      <c r="H20" s="651"/>
-      <c r="I20" s="651"/>
-      <c r="J20" s="652"/>
+      <c r="E20" s="647"/>
+      <c r="F20" s="648"/>
+      <c r="G20" s="648"/>
+      <c r="H20" s="648"/>
+      <c r="I20" s="648"/>
+      <c r="J20" s="649"/>
       <c r="K20" s="302"/>
       <c r="L20" s="297"/>
       <c r="M20" s="114"/>
@@ -49164,12 +49164,12 @@
     <row r="21" spans="1:16" ht="84.75" customHeight="1" thickBot="1">
       <c r="B21" s="90"/>
       <c r="D21" s="295"/>
-      <c r="E21" s="650"/>
-      <c r="F21" s="651"/>
-      <c r="G21" s="651"/>
-      <c r="H21" s="651"/>
-      <c r="I21" s="651"/>
-      <c r="J21" s="652"/>
+      <c r="E21" s="647"/>
+      <c r="F21" s="648"/>
+      <c r="G21" s="648"/>
+      <c r="H21" s="648"/>
+      <c r="I21" s="648"/>
+      <c r="J21" s="649"/>
       <c r="K21" s="302"/>
       <c r="L21" s="58"/>
       <c r="M21" s="114"/>
@@ -49180,12 +49180,12 @@
       <c r="B22" s="227"/>
       <c r="C22" s="228"/>
       <c r="D22" s="295"/>
-      <c r="E22" s="650"/>
-      <c r="F22" s="651"/>
-      <c r="G22" s="651"/>
-      <c r="H22" s="651"/>
-      <c r="I22" s="651"/>
-      <c r="J22" s="652"/>
+      <c r="E22" s="647"/>
+      <c r="F22" s="648"/>
+      <c r="G22" s="648"/>
+      <c r="H22" s="648"/>
+      <c r="I22" s="648"/>
+      <c r="J22" s="649"/>
       <c r="K22" s="303"/>
       <c r="L22" s="58"/>
       <c r="M22" s="112"/>
@@ -49603,14 +49603,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="E21:J21"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E18:J18"/>
     <mergeCell ref="C5:D5"/>
@@ -49621,6 +49613,14 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E20:J20"/>
+    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="E21:J21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -49630,14 +49630,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49896,27 +49894,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -49941,9 +49932,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED8162D-5640-4BD1-B5D7-F199452B0956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070F6000-654B-478A-926F-E3AB2F14DBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29463,7 +29463,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341884"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341924"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29528,7 +29528,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341885"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341925"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29645,7 +29645,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341886"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341926"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29710,7 +29710,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341887"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341927"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29775,7 +29775,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341888"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341928"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29840,7 +29840,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341889"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341929"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29905,7 +29905,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341890"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341930"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29970,7 +29970,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341891"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341931"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30035,7 +30035,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341892"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341932"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30100,7 +30100,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341893"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341933"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>

--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070F6000-654B-478A-926F-E3AB2F14DBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB1D1CB-DA50-4CD6-9234-6EC432B19F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -29463,7 +29463,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341924"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s355786"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29528,7 +29528,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s341925"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s355787"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29645,7 +29645,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s341926"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s355788"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29710,7 +29710,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s341927"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s355789"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29775,7 +29775,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s341928"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s355790"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29840,7 +29840,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s341929"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s355791"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29905,7 +29905,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s341930"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s355792"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29970,7 +29970,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s341931"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s355793"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30035,7 +30035,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s341932"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s355794"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30100,7 +30100,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s341933"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s355795"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -44009,7 +44009,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="5" scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="50" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="51" max="18" man="1"/>
   </rowBreaks>

--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB1D1CB-DA50-4CD6-9234-6EC432B19F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0A5189-EF72-4281-AC54-8646F233BB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Convenios ADP_II" sheetId="54" r:id="rId10"/>
     <sheet name="Gestión de riesgos" sheetId="48" r:id="rId11"/>
     <sheet name="data_riesgos" sheetId="49" state="hidden" r:id="rId12"/>
-    <sheet name="Planes de tratamientos" sheetId="55" r:id="rId13"/>
+    <sheet name="Planes de tratamientos" sheetId="55" state="hidden" r:id="rId13"/>
     <sheet name="programas sociales" sheetId="50" state="hidden" r:id="rId14"/>
     <sheet name="Planes tratamientos" sheetId="53" state="hidden" r:id="rId15"/>
     <sheet name="datos_graficos" sheetId="51" state="hidden" r:id="rId16"/>
@@ -7526,24 +7526,42 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="72" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7556,24 +7574,6 @@
     <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="72" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -7691,6 +7691,15 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="200" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7700,6 +7709,27 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="87" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="13" borderId="205" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7712,36 +7742,6 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="13" borderId="205" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="63" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7784,6 +7784,285 @@
     <xf numFmtId="0" fontId="64" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="13" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="13" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="13" borderId="162" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="144" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7820,45 +8099,18 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7874,258 +8126,6 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="13" borderId="162" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="144" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="13" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -8138,161 +8138,188 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="13" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="323" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="328" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="325" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="326" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="330" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="19" fillId="9" borderId="331" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="177" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="194" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="176" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="107" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="333" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="325" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="326" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="13" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8300,12 +8327,108 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="19" borderId="156" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="308" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="309" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="310" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="79" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="79" fillId="13" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="303" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8315,128 +8438,473 @@
     <xf numFmtId="0" fontId="100" fillId="0" borderId="304" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="268" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="269" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="270" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="266" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="249" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="250" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="234" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="235" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="284" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="215" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="259" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="234" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="235" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="271" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="270" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="272" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="189" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="250" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="256" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="257" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="264" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="231" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="233" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="258" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="18" borderId="257" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="273" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="274" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="275" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="285" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="238" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="238" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="265" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="267" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="214" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="239" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="239" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="276" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="261" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="277" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="262" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="173" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="79" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="79" fillId="13" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="177" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="194" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="176" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="19" borderId="156" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="308" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="309" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="310" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="318" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="319" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="298" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -8444,9 +8912,6 @@
     <xf numFmtId="0" fontId="93" fillId="0" borderId="295" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8471,15 +8936,6 @@
     <xf numFmtId="0" fontId="81" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="81" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8536,462 +8992,6 @@
     </xf>
     <xf numFmtId="0" fontId="92" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="13" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="228" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="229" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="189" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="189" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="13" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="13" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="136" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="218" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="238" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="265" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="264" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="231" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="233" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="234" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="235" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="234" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="235" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="232" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="233" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="276" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="261" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="238" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="231" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="239" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="277" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="262" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="239" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="273" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="274" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="275" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="284" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="285" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="215" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="267" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="214" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="259" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="271" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="269" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="270" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="272" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="189" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="250" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="256" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="257" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="258" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="256" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="84" fillId="18" borderId="257" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="268" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="269" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="270" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="266" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="249" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="250" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -29463,7 +29463,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s355786"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s356036"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29528,7 +29528,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s355787"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s356037"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29645,7 +29645,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s355788"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s356038"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29710,7 +29710,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s355789"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s356039"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29775,7 +29775,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s355790"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s356040"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29840,7 +29840,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s355791"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s356041"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29905,7 +29905,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s355792"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s356042"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29970,7 +29970,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s355793"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s356043"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30035,7 +30035,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s355794"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s356044"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30100,7 +30100,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s355795"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s356045"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -34292,9 +34292,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="654"/>
-      <c r="C1" s="655"/>
-      <c r="D1" s="656"/>
+      <c r="B1" s="647"/>
+      <c r="C1" s="648"/>
+      <c r="D1" s="649"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -34316,10 +34316,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="650" t="s">
+      <c r="I2" s="660" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="651"/>
+      <c r="J2" s="661"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -34372,10 +34372,10 @@
       <c r="B5" s="566" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="657" t="s">
+      <c r="C5" s="653" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="658"/>
+      <c r="D5" s="654"/>
       <c r="E5" s="567" t="s">
         <v>60</v>
       </c>
@@ -34422,8 +34422,8 @@
     <row r="7" spans="1:17" ht="28.5">
       <c r="A7" s="79"/>
       <c r="B7" s="216"/>
-      <c r="C7" s="661"/>
-      <c r="D7" s="663"/>
+      <c r="C7" s="657"/>
+      <c r="D7" s="659"/>
       <c r="E7" s="458"/>
       <c r="F7" s="458"/>
       <c r="G7" s="458"/>
@@ -34591,12 +34591,12 @@
       </c>
       <c r="C16" s="489"/>
       <c r="D16" s="294"/>
-      <c r="E16" s="647"/>
-      <c r="F16" s="648"/>
-      <c r="G16" s="648"/>
-      <c r="H16" s="648"/>
-      <c r="I16" s="648"/>
-      <c r="J16" s="649"/>
+      <c r="E16" s="650"/>
+      <c r="F16" s="651"/>
+      <c r="G16" s="651"/>
+      <c r="H16" s="651"/>
+      <c r="I16" s="651"/>
+      <c r="J16" s="652"/>
       <c r="K16" s="301"/>
       <c r="L16" s="115"/>
       <c r="M16" s="115"/>
@@ -34611,12 +34611,12 @@
       </c>
       <c r="C17" s="488"/>
       <c r="D17" s="294"/>
-      <c r="E17" s="647"/>
-      <c r="F17" s="648"/>
-      <c r="G17" s="648"/>
-      <c r="H17" s="648"/>
-      <c r="I17" s="648"/>
-      <c r="J17" s="649"/>
+      <c r="E17" s="650"/>
+      <c r="F17" s="651"/>
+      <c r="G17" s="651"/>
+      <c r="H17" s="651"/>
+      <c r="I17" s="651"/>
+      <c r="J17" s="652"/>
       <c r="K17" s="136"/>
       <c r="L17" s="115"/>
       <c r="M17" s="115"/>
@@ -35185,32 +35185,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="178"/>
-      <c r="B1" s="769" t="s">
+      <c r="B1" s="687" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="770"/>
-      <c r="D1" s="770"/>
-      <c r="E1" s="770"/>
-      <c r="F1" s="770"/>
-      <c r="G1" s="770"/>
-      <c r="H1" s="770"/>
-      <c r="I1" s="770"/>
-      <c r="J1" s="770"/>
-      <c r="K1" s="770"/>
-      <c r="L1" s="770"/>
-      <c r="M1" s="770"/>
-      <c r="N1" s="770"/>
-      <c r="O1" s="770"/>
-      <c r="P1" s="770"/>
-      <c r="Q1" s="770"/>
-      <c r="R1" s="770"/>
-      <c r="S1" s="770"/>
-      <c r="T1" s="770"/>
-      <c r="U1" s="770"/>
-      <c r="V1" s="770"/>
-      <c r="W1" s="770"/>
-      <c r="X1" s="770"/>
-      <c r="Y1" s="771"/>
+      <c r="C1" s="688"/>
+      <c r="D1" s="688"/>
+      <c r="E1" s="688"/>
+      <c r="F1" s="688"/>
+      <c r="G1" s="688"/>
+      <c r="H1" s="688"/>
+      <c r="I1" s="688"/>
+      <c r="J1" s="688"/>
+      <c r="K1" s="688"/>
+      <c r="L1" s="688"/>
+      <c r="M1" s="688"/>
+      <c r="N1" s="688"/>
+      <c r="O1" s="688"/>
+      <c r="P1" s="688"/>
+      <c r="Q1" s="688"/>
+      <c r="R1" s="688"/>
+      <c r="S1" s="688"/>
+      <c r="T1" s="688"/>
+      <c r="U1" s="688"/>
+      <c r="V1" s="688"/>
+      <c r="W1" s="688"/>
+      <c r="X1" s="688"/>
+      <c r="Y1" s="689"/>
       <c r="Z1" s="173"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -35246,32 +35246,32 @@
       <c r="A3" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="772" t="s">
+      <c r="B3" s="690" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="773"/>
-      <c r="D3" s="773"/>
-      <c r="E3" s="773"/>
-      <c r="F3" s="773"/>
-      <c r="G3" s="773"/>
-      <c r="H3" s="773"/>
-      <c r="I3" s="773"/>
-      <c r="J3" s="773"/>
-      <c r="K3" s="773"/>
-      <c r="L3" s="773"/>
-      <c r="M3" s="773"/>
-      <c r="N3" s="773"/>
-      <c r="O3" s="773"/>
-      <c r="P3" s="773"/>
-      <c r="Q3" s="773"/>
-      <c r="R3" s="773"/>
-      <c r="S3" s="773"/>
-      <c r="T3" s="773"/>
-      <c r="U3" s="773"/>
-      <c r="V3" s="773"/>
-      <c r="W3" s="773"/>
-      <c r="X3" s="773"/>
-      <c r="Y3" s="774"/>
+      <c r="C3" s="691"/>
+      <c r="D3" s="691"/>
+      <c r="E3" s="691"/>
+      <c r="F3" s="691"/>
+      <c r="G3" s="691"/>
+      <c r="H3" s="691"/>
+      <c r="I3" s="691"/>
+      <c r="J3" s="691"/>
+      <c r="K3" s="691"/>
+      <c r="L3" s="691"/>
+      <c r="M3" s="691"/>
+      <c r="N3" s="691"/>
+      <c r="O3" s="691"/>
+      <c r="P3" s="691"/>
+      <c r="Q3" s="691"/>
+      <c r="R3" s="691"/>
+      <c r="S3" s="691"/>
+      <c r="T3" s="691"/>
+      <c r="U3" s="691"/>
+      <c r="V3" s="691"/>
+      <c r="W3" s="691"/>
+      <c r="X3" s="691"/>
+      <c r="Y3" s="692"/>
       <c r="Z3" s="174"/>
       <c r="AA3" s="103"/>
     </row>
@@ -35279,32 +35279,32 @@
       <c r="A4" s="180" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="775" t="s">
+      <c r="B4" s="693" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="776"/>
-      <c r="D4" s="776"/>
-      <c r="E4" s="776"/>
-      <c r="F4" s="776"/>
-      <c r="G4" s="776"/>
-      <c r="H4" s="776"/>
-      <c r="I4" s="776"/>
-      <c r="J4" s="776"/>
-      <c r="K4" s="776"/>
-      <c r="L4" s="776"/>
-      <c r="M4" s="776"/>
-      <c r="N4" s="776"/>
-      <c r="O4" s="776"/>
-      <c r="P4" s="776"/>
-      <c r="Q4" s="776"/>
-      <c r="R4" s="776"/>
-      <c r="S4" s="776"/>
-      <c r="T4" s="776"/>
-      <c r="U4" s="776"/>
-      <c r="V4" s="776"/>
-      <c r="W4" s="776"/>
-      <c r="X4" s="776"/>
-      <c r="Y4" s="777"/>
+      <c r="C4" s="694"/>
+      <c r="D4" s="694"/>
+      <c r="E4" s="694"/>
+      <c r="F4" s="694"/>
+      <c r="G4" s="694"/>
+      <c r="H4" s="694"/>
+      <c r="I4" s="694"/>
+      <c r="J4" s="694"/>
+      <c r="K4" s="694"/>
+      <c r="L4" s="694"/>
+      <c r="M4" s="694"/>
+      <c r="N4" s="694"/>
+      <c r="O4" s="694"/>
+      <c r="P4" s="694"/>
+      <c r="Q4" s="694"/>
+      <c r="R4" s="694"/>
+      <c r="S4" s="694"/>
+      <c r="T4" s="694"/>
+      <c r="U4" s="694"/>
+      <c r="V4" s="694"/>
+      <c r="W4" s="694"/>
+      <c r="X4" s="694"/>
+      <c r="Y4" s="695"/>
       <c r="Z4" s="175"/>
       <c r="AA4" s="103"/>
     </row>
@@ -35339,40 +35339,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="181"/>
-      <c r="B6" s="781" t="s">
+      <c r="B6" s="699" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="782"/>
-      <c r="D6" s="782"/>
-      <c r="E6" s="783"/>
+      <c r="C6" s="700"/>
+      <c r="D6" s="700"/>
+      <c r="E6" s="701"/>
       <c r="F6" s="89"/>
       <c r="G6" s="142"/>
-      <c r="H6" s="747" t="s">
+      <c r="H6" s="719" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="748"/>
-      <c r="J6" s="748"/>
-      <c r="K6" s="749"/>
+      <c r="I6" s="720"/>
+      <c r="J6" s="720"/>
+      <c r="K6" s="721"/>
       <c r="L6" s="89"/>
       <c r="M6" s="142"/>
-      <c r="N6" s="759" t="s">
+      <c r="N6" s="727" t="s">
         <v>95</v>
       </c>
-      <c r="O6" s="760"/>
-      <c r="P6" s="761"/>
+      <c r="O6" s="728"/>
+      <c r="P6" s="729"/>
       <c r="Q6" s="149"/>
       <c r="R6" s="151"/>
-      <c r="S6" s="754" t="s">
+      <c r="S6" s="679" t="s">
         <v>77</v>
       </c>
-      <c r="T6" s="755"/>
+      <c r="T6" s="680"/>
       <c r="U6" s="152"/>
       <c r="V6" s="156"/>
       <c r="W6" s="143"/>
-      <c r="X6" s="754" t="s">
+      <c r="X6" s="679" t="s">
         <v>78</v>
       </c>
-      <c r="Y6" s="755"/>
+      <c r="Y6" s="680"/>
       <c r="Z6" s="80"/>
       <c r="AA6" s="103"/>
     </row>
@@ -35392,36 +35392,36 @@
       </c>
       <c r="F7" s="89"/>
       <c r="G7" s="116"/>
-      <c r="H7" s="756">
+      <c r="H7" s="715">
         <f>I23</f>
         <v>0</v>
       </c>
-      <c r="I7" s="758"/>
-      <c r="J7" s="758"/>
-      <c r="K7" s="757"/>
+      <c r="I7" s="726"/>
+      <c r="J7" s="726"/>
+      <c r="K7" s="716"/>
       <c r="L7" s="89"/>
       <c r="M7" s="116"/>
-      <c r="N7" s="762">
+      <c r="N7" s="711">
         <f>L23</f>
         <v>0</v>
       </c>
-      <c r="O7" s="763"/>
-      <c r="P7" s="764"/>
+      <c r="O7" s="712"/>
+      <c r="P7" s="713"/>
       <c r="Q7" s="150"/>
       <c r="R7" s="152"/>
-      <c r="S7" s="756">
+      <c r="S7" s="715">
         <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T7" s="757"/>
+      <c r="T7" s="716"/>
       <c r="U7" s="89"/>
       <c r="V7" s="155"/>
       <c r="W7" s="82"/>
-      <c r="X7" s="756">
+      <c r="X7" s="715">
         <f>R23</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="757"/>
+      <c r="Y7" s="716"/>
       <c r="Z7" s="141"/>
       <c r="AA7" s="103"/>
     </row>
@@ -35490,27 +35490,27 @@
       <c r="D10" s="134"/>
       <c r="E10" s="199"/>
       <c r="F10" s="89"/>
-      <c r="G10" s="788" t="s">
+      <c r="G10" s="707" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="789"/>
-      <c r="I10" s="789"/>
-      <c r="J10" s="789"/>
-      <c r="K10" s="789"/>
-      <c r="L10" s="789"/>
-      <c r="M10" s="789"/>
-      <c r="N10" s="789"/>
-      <c r="O10" s="789"/>
-      <c r="P10" s="789"/>
-      <c r="Q10" s="789"/>
-      <c r="R10" s="789"/>
-      <c r="S10" s="789"/>
-      <c r="T10" s="789"/>
-      <c r="U10" s="789"/>
-      <c r="V10" s="789"/>
-      <c r="W10" s="789"/>
-      <c r="X10" s="789"/>
-      <c r="Y10" s="790"/>
+      <c r="H10" s="708"/>
+      <c r="I10" s="708"/>
+      <c r="J10" s="708"/>
+      <c r="K10" s="708"/>
+      <c r="L10" s="708"/>
+      <c r="M10" s="708"/>
+      <c r="N10" s="708"/>
+      <c r="O10" s="708"/>
+      <c r="P10" s="708"/>
+      <c r="Q10" s="708"/>
+      <c r="R10" s="708"/>
+      <c r="S10" s="708"/>
+      <c r="T10" s="708"/>
+      <c r="U10" s="708"/>
+      <c r="V10" s="708"/>
+      <c r="W10" s="708"/>
+      <c r="X10" s="708"/>
+      <c r="Y10" s="709"/>
       <c r="Z10" s="80"/>
       <c r="AA10" s="103"/>
     </row>
@@ -35521,35 +35521,35 @@
       <c r="D11" s="134"/>
       <c r="E11" s="199"/>
       <c r="F11" s="89"/>
-      <c r="G11" s="791" t="s">
+      <c r="G11" s="710" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="786"/>
-      <c r="I11" s="786" t="s">
+      <c r="H11" s="705"/>
+      <c r="I11" s="705" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="786"/>
-      <c r="K11" s="786"/>
-      <c r="L11" s="786" t="s">
+      <c r="J11" s="705"/>
+      <c r="K11" s="705"/>
+      <c r="L11" s="705" t="s">
         <v>82</v>
       </c>
-      <c r="M11" s="786"/>
-      <c r="N11" s="786"/>
-      <c r="O11" s="786" t="s">
+      <c r="M11" s="705"/>
+      <c r="N11" s="705"/>
+      <c r="O11" s="705" t="s">
         <v>83</v>
       </c>
-      <c r="P11" s="786"/>
-      <c r="Q11" s="786"/>
-      <c r="R11" s="786" t="s">
+      <c r="P11" s="705"/>
+      <c r="Q11" s="705"/>
+      <c r="R11" s="705" t="s">
         <v>78</v>
       </c>
-      <c r="S11" s="786"/>
-      <c r="T11" s="786"/>
-      <c r="U11" s="786"/>
-      <c r="V11" s="786"/>
-      <c r="W11" s="786"/>
-      <c r="X11" s="786"/>
-      <c r="Y11" s="787"/>
+      <c r="S11" s="705"/>
+      <c r="T11" s="705"/>
+      <c r="U11" s="705"/>
+      <c r="V11" s="705"/>
+      <c r="W11" s="705"/>
+      <c r="X11" s="705"/>
+      <c r="Y11" s="706"/>
       <c r="Z11" s="80"/>
       <c r="AA11" s="103"/>
     </row>
@@ -35560,33 +35560,33 @@
       <c r="D12" s="185"/>
       <c r="E12" s="199"/>
       <c r="F12" s="89"/>
-      <c r="G12" s="791"/>
-      <c r="H12" s="786"/>
-      <c r="I12" s="786"/>
-      <c r="J12" s="786"/>
-      <c r="K12" s="786"/>
-      <c r="L12" s="786"/>
-      <c r="M12" s="786"/>
-      <c r="N12" s="786"/>
-      <c r="O12" s="786"/>
-      <c r="P12" s="786"/>
-      <c r="Q12" s="786"/>
-      <c r="R12" s="713" t="s">
+      <c r="G12" s="710"/>
+      <c r="H12" s="705"/>
+      <c r="I12" s="705"/>
+      <c r="J12" s="705"/>
+      <c r="K12" s="705"/>
+      <c r="L12" s="705"/>
+      <c r="M12" s="705"/>
+      <c r="N12" s="705"/>
+      <c r="O12" s="705"/>
+      <c r="P12" s="705"/>
+      <c r="Q12" s="705"/>
+      <c r="R12" s="681" t="s">
         <v>84</v>
       </c>
-      <c r="S12" s="713"/>
-      <c r="T12" s="713" t="s">
+      <c r="S12" s="681"/>
+      <c r="T12" s="681" t="s">
         <v>85</v>
       </c>
-      <c r="U12" s="713"/>
-      <c r="V12" s="713" t="s">
+      <c r="U12" s="681"/>
+      <c r="V12" s="681" t="s">
         <v>86</v>
       </c>
-      <c r="W12" s="713"/>
-      <c r="X12" s="713" t="s">
+      <c r="W12" s="681"/>
+      <c r="X12" s="681" t="s">
         <v>87</v>
       </c>
-      <c r="Y12" s="744"/>
+      <c r="Y12" s="702"/>
       <c r="Z12" s="80"/>
       <c r="AA12" s="79"/>
     </row>
@@ -35597,25 +35597,25 @@
       <c r="D13" s="134"/>
       <c r="E13" s="199"/>
       <c r="F13" s="89"/>
-      <c r="G13" s="791"/>
-      <c r="H13" s="786"/>
-      <c r="I13" s="786"/>
-      <c r="J13" s="786"/>
-      <c r="K13" s="786"/>
-      <c r="L13" s="786"/>
-      <c r="M13" s="786"/>
-      <c r="N13" s="786"/>
-      <c r="O13" s="786"/>
-      <c r="P13" s="786"/>
-      <c r="Q13" s="786"/>
-      <c r="R13" s="713"/>
-      <c r="S13" s="713"/>
-      <c r="T13" s="713"/>
-      <c r="U13" s="713"/>
-      <c r="V13" s="713"/>
-      <c r="W13" s="713"/>
-      <c r="X13" s="784"/>
-      <c r="Y13" s="785"/>
+      <c r="G13" s="710"/>
+      <c r="H13" s="705"/>
+      <c r="I13" s="705"/>
+      <c r="J13" s="705"/>
+      <c r="K13" s="705"/>
+      <c r="L13" s="705"/>
+      <c r="M13" s="705"/>
+      <c r="N13" s="705"/>
+      <c r="O13" s="705"/>
+      <c r="P13" s="705"/>
+      <c r="Q13" s="705"/>
+      <c r="R13" s="681"/>
+      <c r="S13" s="681"/>
+      <c r="T13" s="681"/>
+      <c r="U13" s="681"/>
+      <c r="V13" s="681"/>
+      <c r="W13" s="681"/>
+      <c r="X13" s="703"/>
+      <c r="Y13" s="704"/>
       <c r="Z13" s="80"/>
       <c r="AA13" s="81"/>
     </row>
@@ -35626,27 +35626,27 @@
       <c r="D14" s="134"/>
       <c r="E14" s="199"/>
       <c r="F14" s="89"/>
-      <c r="G14" s="765" t="s">
+      <c r="G14" s="682" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="766"/>
-      <c r="I14" s="743"/>
-      <c r="J14" s="767"/>
-      <c r="K14" s="768"/>
-      <c r="L14" s="741"/>
-      <c r="M14" s="741"/>
-      <c r="N14" s="741"/>
-      <c r="O14" s="741"/>
-      <c r="P14" s="741"/>
-      <c r="Q14" s="741"/>
-      <c r="R14" s="741"/>
-      <c r="S14" s="741"/>
-      <c r="T14" s="741"/>
-      <c r="U14" s="741"/>
-      <c r="V14" s="741"/>
-      <c r="W14" s="743"/>
-      <c r="X14" s="741"/>
-      <c r="Y14" s="742"/>
+      <c r="H14" s="683"/>
+      <c r="I14" s="684"/>
+      <c r="J14" s="685"/>
+      <c r="K14" s="686"/>
+      <c r="L14" s="678"/>
+      <c r="M14" s="678"/>
+      <c r="N14" s="678"/>
+      <c r="O14" s="678"/>
+      <c r="P14" s="678"/>
+      <c r="Q14" s="678"/>
+      <c r="R14" s="678"/>
+      <c r="S14" s="678"/>
+      <c r="T14" s="678"/>
+      <c r="U14" s="678"/>
+      <c r="V14" s="678"/>
+      <c r="W14" s="684"/>
+      <c r="X14" s="678"/>
+      <c r="Y14" s="714"/>
       <c r="Z14" s="80"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -35656,27 +35656,27 @@
       <c r="D15" s="186"/>
       <c r="E15" s="200"/>
       <c r="F15" s="89"/>
-      <c r="G15" s="765" t="s">
+      <c r="G15" s="682" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="766"/>
-      <c r="I15" s="743"/>
-      <c r="J15" s="767"/>
-      <c r="K15" s="768"/>
-      <c r="L15" s="741"/>
-      <c r="M15" s="741"/>
-      <c r="N15" s="741"/>
-      <c r="O15" s="741"/>
-      <c r="P15" s="741"/>
-      <c r="Q15" s="741"/>
-      <c r="R15" s="741"/>
-      <c r="S15" s="741"/>
-      <c r="T15" s="741"/>
-      <c r="U15" s="741"/>
-      <c r="V15" s="741"/>
-      <c r="W15" s="743"/>
-      <c r="X15" s="741"/>
-      <c r="Y15" s="742"/>
+      <c r="H15" s="683"/>
+      <c r="I15" s="684"/>
+      <c r="J15" s="685"/>
+      <c r="K15" s="686"/>
+      <c r="L15" s="678"/>
+      <c r="M15" s="678"/>
+      <c r="N15" s="678"/>
+      <c r="O15" s="678"/>
+      <c r="P15" s="678"/>
+      <c r="Q15" s="678"/>
+      <c r="R15" s="678"/>
+      <c r="S15" s="678"/>
+      <c r="T15" s="678"/>
+      <c r="U15" s="678"/>
+      <c r="V15" s="678"/>
+      <c r="W15" s="684"/>
+      <c r="X15" s="678"/>
+      <c r="Y15" s="714"/>
       <c r="Z15" s="80"/>
       <c r="AA15" s="103"/>
     </row>
@@ -35687,61 +35687,61 @@
       <c r="D16" s="106"/>
       <c r="E16" s="106"/>
       <c r="F16" s="79"/>
-      <c r="G16" s="765" t="s">
+      <c r="G16" s="682" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="766"/>
-      <c r="I16" s="743"/>
-      <c r="J16" s="767"/>
-      <c r="K16" s="768"/>
-      <c r="L16" s="741"/>
-      <c r="M16" s="741"/>
-      <c r="N16" s="741"/>
-      <c r="O16" s="741"/>
-      <c r="P16" s="741"/>
-      <c r="Q16" s="741"/>
-      <c r="R16" s="741"/>
-      <c r="S16" s="741"/>
-      <c r="T16" s="741"/>
-      <c r="U16" s="741"/>
-      <c r="V16" s="741"/>
-      <c r="W16" s="743"/>
-      <c r="X16" s="741"/>
-      <c r="Y16" s="742"/>
+      <c r="H16" s="683"/>
+      <c r="I16" s="684"/>
+      <c r="J16" s="685"/>
+      <c r="K16" s="686"/>
+      <c r="L16" s="678"/>
+      <c r="M16" s="678"/>
+      <c r="N16" s="678"/>
+      <c r="O16" s="678"/>
+      <c r="P16" s="678"/>
+      <c r="Q16" s="678"/>
+      <c r="R16" s="678"/>
+      <c r="S16" s="678"/>
+      <c r="T16" s="678"/>
+      <c r="U16" s="678"/>
+      <c r="V16" s="678"/>
+      <c r="W16" s="684"/>
+      <c r="X16" s="678"/>
+      <c r="Y16" s="714"/>
       <c r="Z16" s="80"/>
       <c r="AA16" s="103"/>
       <c r="AB16" s="194"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="79"/>
-      <c r="B17" s="778" t="s">
+      <c r="B17" s="696" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="779"/>
-      <c r="D17" s="779"/>
-      <c r="E17" s="780"/>
+      <c r="C17" s="697"/>
+      <c r="D17" s="697"/>
+      <c r="E17" s="698"/>
       <c r="F17" s="89"/>
-      <c r="G17" s="765" t="s">
+      <c r="G17" s="682" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="766"/>
-      <c r="I17" s="743"/>
-      <c r="J17" s="767"/>
-      <c r="K17" s="768"/>
-      <c r="L17" s="741"/>
-      <c r="M17" s="741"/>
-      <c r="N17" s="741"/>
-      <c r="O17" s="741"/>
-      <c r="P17" s="741"/>
-      <c r="Q17" s="741"/>
-      <c r="R17" s="741"/>
-      <c r="S17" s="741"/>
-      <c r="T17" s="741"/>
-      <c r="U17" s="741"/>
-      <c r="V17" s="741"/>
-      <c r="W17" s="743"/>
-      <c r="X17" s="741"/>
-      <c r="Y17" s="742"/>
+      <c r="H17" s="683"/>
+      <c r="I17" s="684"/>
+      <c r="J17" s="685"/>
+      <c r="K17" s="686"/>
+      <c r="L17" s="678"/>
+      <c r="M17" s="678"/>
+      <c r="N17" s="678"/>
+      <c r="O17" s="678"/>
+      <c r="P17" s="678"/>
+      <c r="Q17" s="678"/>
+      <c r="R17" s="678"/>
+      <c r="S17" s="678"/>
+      <c r="T17" s="678"/>
+      <c r="U17" s="678"/>
+      <c r="V17" s="678"/>
+      <c r="W17" s="684"/>
+      <c r="X17" s="678"/>
+      <c r="Y17" s="714"/>
       <c r="Z17" s="80"/>
       <c r="AA17" s="103"/>
     </row>
@@ -35760,27 +35760,27 @@
         <v>91</v>
       </c>
       <c r="F18" s="89"/>
-      <c r="G18" s="765" t="s">
+      <c r="G18" s="682" t="s">
         <v>167</v>
       </c>
-      <c r="H18" s="766"/>
-      <c r="I18" s="743"/>
-      <c r="J18" s="767"/>
-      <c r="K18" s="768"/>
-      <c r="L18" s="741"/>
-      <c r="M18" s="741"/>
-      <c r="N18" s="741"/>
-      <c r="O18" s="741"/>
-      <c r="P18" s="741"/>
-      <c r="Q18" s="741"/>
-      <c r="R18" s="741"/>
-      <c r="S18" s="741"/>
-      <c r="T18" s="741"/>
-      <c r="U18" s="741"/>
-      <c r="V18" s="741"/>
-      <c r="W18" s="743"/>
-      <c r="X18" s="741"/>
-      <c r="Y18" s="742"/>
+      <c r="H18" s="683"/>
+      <c r="I18" s="684"/>
+      <c r="J18" s="685"/>
+      <c r="K18" s="686"/>
+      <c r="L18" s="678"/>
+      <c r="M18" s="678"/>
+      <c r="N18" s="678"/>
+      <c r="O18" s="678"/>
+      <c r="P18" s="678"/>
+      <c r="Q18" s="678"/>
+      <c r="R18" s="678"/>
+      <c r="S18" s="678"/>
+      <c r="T18" s="678"/>
+      <c r="U18" s="678"/>
+      <c r="V18" s="678"/>
+      <c r="W18" s="684"/>
+      <c r="X18" s="678"/>
+      <c r="Y18" s="714"/>
       <c r="Z18" s="80"/>
       <c r="AA18" s="103"/>
     </row>
@@ -35791,27 +35791,27 @@
       <c r="D19" s="544"/>
       <c r="E19" s="201"/>
       <c r="F19" s="89"/>
-      <c r="G19" s="765" t="s">
+      <c r="G19" s="682" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="766"/>
-      <c r="I19" s="743"/>
-      <c r="J19" s="767"/>
-      <c r="K19" s="768"/>
-      <c r="L19" s="741"/>
-      <c r="M19" s="741"/>
-      <c r="N19" s="741"/>
-      <c r="O19" s="741"/>
-      <c r="P19" s="741"/>
-      <c r="Q19" s="741"/>
-      <c r="R19" s="741"/>
-      <c r="S19" s="741"/>
-      <c r="T19" s="741"/>
-      <c r="U19" s="741"/>
-      <c r="V19" s="741"/>
-      <c r="W19" s="743"/>
-      <c r="X19" s="741"/>
-      <c r="Y19" s="742"/>
+      <c r="H19" s="683"/>
+      <c r="I19" s="684"/>
+      <c r="J19" s="685"/>
+      <c r="K19" s="686"/>
+      <c r="L19" s="678"/>
+      <c r="M19" s="678"/>
+      <c r="N19" s="678"/>
+      <c r="O19" s="678"/>
+      <c r="P19" s="678"/>
+      <c r="Q19" s="678"/>
+      <c r="R19" s="678"/>
+      <c r="S19" s="678"/>
+      <c r="T19" s="678"/>
+      <c r="U19" s="678"/>
+      <c r="V19" s="678"/>
+      <c r="W19" s="684"/>
+      <c r="X19" s="678"/>
+      <c r="Y19" s="714"/>
       <c r="Z19" s="80"/>
       <c r="AA19" s="103"/>
     </row>
@@ -35822,27 +35822,27 @@
       <c r="D20" s="544"/>
       <c r="E20" s="201"/>
       <c r="F20" s="89"/>
-      <c r="G20" s="765" t="s">
+      <c r="G20" s="682" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="766"/>
-      <c r="I20" s="743"/>
-      <c r="J20" s="767"/>
-      <c r="K20" s="768"/>
-      <c r="L20" s="741"/>
-      <c r="M20" s="741"/>
-      <c r="N20" s="741"/>
-      <c r="O20" s="741"/>
-      <c r="P20" s="741"/>
-      <c r="Q20" s="741"/>
-      <c r="R20" s="741"/>
-      <c r="S20" s="741"/>
-      <c r="T20" s="741"/>
-      <c r="U20" s="741"/>
-      <c r="V20" s="741"/>
-      <c r="W20" s="743"/>
-      <c r="X20" s="741"/>
-      <c r="Y20" s="742"/>
+      <c r="H20" s="683"/>
+      <c r="I20" s="684"/>
+      <c r="J20" s="685"/>
+      <c r="K20" s="686"/>
+      <c r="L20" s="678"/>
+      <c r="M20" s="678"/>
+      <c r="N20" s="678"/>
+      <c r="O20" s="678"/>
+      <c r="P20" s="678"/>
+      <c r="Q20" s="678"/>
+      <c r="R20" s="678"/>
+      <c r="S20" s="678"/>
+      <c r="T20" s="678"/>
+      <c r="U20" s="678"/>
+      <c r="V20" s="678"/>
+      <c r="W20" s="684"/>
+      <c r="X20" s="678"/>
+      <c r="Y20" s="714"/>
       <c r="Z20" s="80"/>
       <c r="AA20" s="103"/>
     </row>
@@ -35853,27 +35853,27 @@
       <c r="D21" s="544"/>
       <c r="E21" s="201"/>
       <c r="F21" s="89"/>
-      <c r="G21" s="765" t="s">
+      <c r="G21" s="682" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="766"/>
-      <c r="I21" s="743"/>
-      <c r="J21" s="767"/>
-      <c r="K21" s="768"/>
-      <c r="L21" s="741"/>
-      <c r="M21" s="741"/>
-      <c r="N21" s="741"/>
-      <c r="O21" s="741"/>
-      <c r="P21" s="741"/>
-      <c r="Q21" s="741"/>
-      <c r="R21" s="741"/>
-      <c r="S21" s="741"/>
-      <c r="T21" s="741"/>
-      <c r="U21" s="741"/>
-      <c r="V21" s="741"/>
-      <c r="W21" s="743"/>
-      <c r="X21" s="741"/>
-      <c r="Y21" s="742"/>
+      <c r="H21" s="683"/>
+      <c r="I21" s="684"/>
+      <c r="J21" s="685"/>
+      <c r="K21" s="686"/>
+      <c r="L21" s="678"/>
+      <c r="M21" s="678"/>
+      <c r="N21" s="678"/>
+      <c r="O21" s="678"/>
+      <c r="P21" s="678"/>
+      <c r="Q21" s="678"/>
+      <c r="R21" s="678"/>
+      <c r="S21" s="678"/>
+      <c r="T21" s="678"/>
+      <c r="U21" s="678"/>
+      <c r="V21" s="678"/>
+      <c r="W21" s="684"/>
+      <c r="X21" s="678"/>
+      <c r="Y21" s="714"/>
       <c r="Z21" s="80"/>
       <c r="AA21" s="103"/>
     </row>
@@ -35884,27 +35884,27 @@
       <c r="D22" s="544"/>
       <c r="E22" s="201"/>
       <c r="F22" s="89"/>
-      <c r="G22" s="765" t="s">
+      <c r="G22" s="682" t="s">
         <v>169</v>
       </c>
-      <c r="H22" s="766"/>
-      <c r="I22" s="743"/>
-      <c r="J22" s="767"/>
-      <c r="K22" s="768"/>
-      <c r="L22" s="741"/>
-      <c r="M22" s="741"/>
-      <c r="N22" s="741"/>
-      <c r="O22" s="741"/>
-      <c r="P22" s="741"/>
-      <c r="Q22" s="741"/>
-      <c r="R22" s="741"/>
-      <c r="S22" s="741"/>
-      <c r="T22" s="741"/>
-      <c r="U22" s="741"/>
-      <c r="V22" s="741"/>
-      <c r="W22" s="743"/>
-      <c r="X22" s="741"/>
-      <c r="Y22" s="742"/>
+      <c r="H22" s="683"/>
+      <c r="I22" s="684"/>
+      <c r="J22" s="685"/>
+      <c r="K22" s="686"/>
+      <c r="L22" s="678"/>
+      <c r="M22" s="678"/>
+      <c r="N22" s="678"/>
+      <c r="O22" s="678"/>
+      <c r="P22" s="678"/>
+      <c r="Q22" s="678"/>
+      <c r="R22" s="678"/>
+      <c r="S22" s="678"/>
+      <c r="T22" s="678"/>
+      <c r="U22" s="678"/>
+      <c r="V22" s="678"/>
+      <c r="W22" s="684"/>
+      <c r="X22" s="678"/>
+      <c r="Y22" s="714"/>
       <c r="Z22" s="80"/>
       <c r="AA22" s="103"/>
     </row>
@@ -35915,48 +35915,48 @@
       <c r="D23" s="545"/>
       <c r="E23" s="202"/>
       <c r="F23" s="89"/>
-      <c r="G23" s="753" t="s">
+      <c r="G23" s="725" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="745"/>
-      <c r="I23" s="745">
+      <c r="H23" s="717"/>
+      <c r="I23" s="717">
         <f>SUM(I14:K22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="745"/>
-      <c r="K23" s="745"/>
-      <c r="L23" s="745">
+      <c r="J23" s="717"/>
+      <c r="K23" s="717"/>
+      <c r="L23" s="717">
         <f>SUM(L14:N22)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="745"/>
-      <c r="N23" s="745"/>
-      <c r="O23" s="750">
+      <c r="M23" s="717"/>
+      <c r="N23" s="717"/>
+      <c r="O23" s="722">
         <f>SUM(O14:Q22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="751"/>
-      <c r="Q23" s="752"/>
-      <c r="R23" s="750">
+      <c r="P23" s="723"/>
+      <c r="Q23" s="724"/>
+      <c r="R23" s="722">
         <f>SUM(R14:S22)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="752"/>
-      <c r="T23" s="750">
+      <c r="S23" s="724"/>
+      <c r="T23" s="722">
         <f>SUM(T14:U22)</f>
         <v>0</v>
       </c>
-      <c r="U23" s="752"/>
-      <c r="V23" s="750">
+      <c r="U23" s="724"/>
+      <c r="V23" s="722">
         <f>SUM(V14:W22)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="751"/>
-      <c r="X23" s="745">
+      <c r="W23" s="723"/>
+      <c r="X23" s="717">
         <f>SUM(X14:Y22)</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="746"/>
+      <c r="Y23" s="718"/>
       <c r="Z23" s="80"/>
       <c r="AA23" s="103"/>
     </row>
@@ -36026,28 +36026,28 @@
       <c r="E26" s="82"/>
       <c r="F26" s="79"/>
       <c r="G26" s="135"/>
-      <c r="H26" s="708" t="s">
+      <c r="H26" s="762" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="709"/>
-      <c r="J26" s="710"/>
+      <c r="I26" s="763"/>
+      <c r="J26" s="764"/>
       <c r="K26" s="89"/>
-      <c r="L26" s="717" t="s">
+      <c r="L26" s="768" t="s">
         <v>96</v>
       </c>
-      <c r="M26" s="718"/>
-      <c r="N26" s="718"/>
-      <c r="O26" s="718"/>
-      <c r="P26" s="718"/>
-      <c r="Q26" s="718"/>
-      <c r="R26" s="718"/>
-      <c r="S26" s="718"/>
-      <c r="T26" s="718"/>
-      <c r="U26" s="718"/>
-      <c r="V26" s="718"/>
-      <c r="W26" s="718"/>
-      <c r="X26" s="718"/>
-      <c r="Y26" s="719"/>
+      <c r="M26" s="769"/>
+      <c r="N26" s="769"/>
+      <c r="O26" s="769"/>
+      <c r="P26" s="769"/>
+      <c r="Q26" s="769"/>
+      <c r="R26" s="769"/>
+      <c r="S26" s="769"/>
+      <c r="T26" s="769"/>
+      <c r="U26" s="769"/>
+      <c r="V26" s="769"/>
+      <c r="W26" s="769"/>
+      <c r="X26" s="769"/>
+      <c r="Y26" s="770"/>
       <c r="Z26" s="80"/>
       <c r="AA26" s="103"/>
     </row>
@@ -36059,41 +36059,41 @@
       <c r="E27" s="82"/>
       <c r="F27" s="79"/>
       <c r="G27" s="136"/>
-      <c r="H27" s="690">
+      <c r="H27" s="759">
         <f>Y38</f>
         <v>0</v>
       </c>
-      <c r="I27" s="691"/>
-      <c r="J27" s="692"/>
+      <c r="I27" s="760"/>
+      <c r="J27" s="761"/>
       <c r="K27" s="89"/>
-      <c r="L27" s="739" t="s">
+      <c r="L27" s="733" t="s">
         <v>80</v>
       </c>
-      <c r="M27" s="713"/>
-      <c r="N27" s="713"/>
-      <c r="O27" s="713" t="s">
+      <c r="M27" s="681"/>
+      <c r="N27" s="681"/>
+      <c r="O27" s="681" t="s">
         <v>97</v>
       </c>
-      <c r="P27" s="713"/>
-      <c r="Q27" s="713" t="s">
+      <c r="P27" s="681"/>
+      <c r="Q27" s="681" t="s">
         <v>98</v>
       </c>
-      <c r="R27" s="713"/>
-      <c r="S27" s="713" t="s">
+      <c r="R27" s="681"/>
+      <c r="S27" s="681" t="s">
         <v>99</v>
       </c>
-      <c r="T27" s="713" t="s">
+      <c r="T27" s="681" t="s">
         <v>100</v>
       </c>
-      <c r="U27" s="713"/>
-      <c r="V27" s="713" t="s">
+      <c r="U27" s="681"/>
+      <c r="V27" s="681" t="s">
         <v>101</v>
       </c>
-      <c r="W27" s="713" t="s">
+      <c r="W27" s="681" t="s">
         <v>102</v>
       </c>
-      <c r="X27" s="713"/>
-      <c r="Y27" s="744" t="s">
+      <c r="X27" s="681"/>
+      <c r="Y27" s="702" t="s">
         <v>88</v>
       </c>
       <c r="Z27" s="80"/>
@@ -36111,20 +36111,20 @@
       <c r="I28" s="82"/>
       <c r="J28" s="165"/>
       <c r="K28" s="89"/>
-      <c r="L28" s="739"/>
-      <c r="M28" s="713"/>
-      <c r="N28" s="713"/>
-      <c r="O28" s="713"/>
-      <c r="P28" s="713"/>
-      <c r="Q28" s="713"/>
-      <c r="R28" s="713"/>
-      <c r="S28" s="713"/>
-      <c r="T28" s="713"/>
-      <c r="U28" s="713"/>
-      <c r="V28" s="713"/>
-      <c r="W28" s="713"/>
-      <c r="X28" s="713"/>
-      <c r="Y28" s="744"/>
+      <c r="L28" s="733"/>
+      <c r="M28" s="681"/>
+      <c r="N28" s="681"/>
+      <c r="O28" s="681"/>
+      <c r="P28" s="681"/>
+      <c r="Q28" s="681"/>
+      <c r="R28" s="681"/>
+      <c r="S28" s="681"/>
+      <c r="T28" s="681"/>
+      <c r="U28" s="681"/>
+      <c r="V28" s="681"/>
+      <c r="W28" s="681"/>
+      <c r="X28" s="681"/>
+      <c r="Y28" s="702"/>
       <c r="Z28" s="80"/>
       <c r="AA28" s="103"/>
     </row>
@@ -36140,21 +36140,21 @@
       <c r="I29" s="166"/>
       <c r="J29" s="138"/>
       <c r="K29" s="89"/>
-      <c r="L29" s="725" t="s">
+      <c r="L29" s="730" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="693"/>
-      <c r="N29" s="693"/>
-      <c r="O29" s="693"/>
-      <c r="P29" s="693"/>
-      <c r="Q29" s="693"/>
-      <c r="R29" s="693"/>
+      <c r="M29" s="731"/>
+      <c r="N29" s="731"/>
+      <c r="O29" s="731"/>
+      <c r="P29" s="731"/>
+      <c r="Q29" s="731"/>
+      <c r="R29" s="731"/>
       <c r="S29" s="71"/>
-      <c r="T29" s="693"/>
-      <c r="U29" s="693"/>
+      <c r="T29" s="731"/>
+      <c r="U29" s="731"/>
       <c r="V29" s="71"/>
-      <c r="W29" s="693"/>
-      <c r="X29" s="694"/>
+      <c r="W29" s="731"/>
+      <c r="X29" s="732"/>
       <c r="Y29" s="195"/>
       <c r="Z29" s="80"/>
       <c r="AA29" s="103"/>
@@ -36171,21 +36171,21 @@
       <c r="I30" s="106"/>
       <c r="J30" s="106"/>
       <c r="K30" s="79"/>
-      <c r="L30" s="725" t="s">
+      <c r="L30" s="730" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="693"/>
-      <c r="N30" s="693"/>
-      <c r="O30" s="693"/>
-      <c r="P30" s="693"/>
-      <c r="Q30" s="693"/>
-      <c r="R30" s="693"/>
+      <c r="M30" s="731"/>
+      <c r="N30" s="731"/>
+      <c r="O30" s="731"/>
+      <c r="P30" s="731"/>
+      <c r="Q30" s="731"/>
+      <c r="R30" s="731"/>
       <c r="S30" s="71"/>
-      <c r="T30" s="693"/>
-      <c r="U30" s="693"/>
+      <c r="T30" s="731"/>
+      <c r="U30" s="731"/>
       <c r="V30" s="71"/>
-      <c r="W30" s="693"/>
-      <c r="X30" s="694"/>
+      <c r="W30" s="731"/>
+      <c r="X30" s="732"/>
       <c r="Y30" s="195"/>
       <c r="Z30" s="80"/>
       <c r="AA30" s="79"/>
@@ -36198,27 +36198,27 @@
       <c r="E31" s="82"/>
       <c r="F31" s="79"/>
       <c r="G31" s="135"/>
-      <c r="H31" s="714" t="s">
+      <c r="H31" s="765" t="s">
         <v>93</v>
       </c>
-      <c r="I31" s="715"/>
-      <c r="J31" s="716"/>
+      <c r="I31" s="766"/>
+      <c r="J31" s="767"/>
       <c r="K31" s="89"/>
-      <c r="L31" s="725" t="s">
+      <c r="L31" s="730" t="s">
         <v>19</v>
       </c>
-      <c r="M31" s="693"/>
-      <c r="N31" s="693"/>
-      <c r="O31" s="693"/>
-      <c r="P31" s="693"/>
-      <c r="Q31" s="693"/>
-      <c r="R31" s="693"/>
+      <c r="M31" s="731"/>
+      <c r="N31" s="731"/>
+      <c r="O31" s="731"/>
+      <c r="P31" s="731"/>
+      <c r="Q31" s="731"/>
+      <c r="R31" s="731"/>
       <c r="S31" s="71"/>
-      <c r="T31" s="693"/>
-      <c r="U31" s="693"/>
+      <c r="T31" s="731"/>
+      <c r="U31" s="731"/>
       <c r="V31" s="71"/>
-      <c r="W31" s="693"/>
-      <c r="X31" s="694"/>
+      <c r="W31" s="731"/>
+      <c r="X31" s="732"/>
       <c r="Y31" s="195"/>
       <c r="Z31" s="80"/>
       <c r="AA31" s="79"/>
@@ -36235,21 +36235,21 @@
       <c r="I32" s="82"/>
       <c r="J32" s="165"/>
       <c r="K32" s="89"/>
-      <c r="L32" s="725" t="s">
+      <c r="L32" s="730" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="693"/>
-      <c r="N32" s="693"/>
-      <c r="O32" s="693"/>
-      <c r="P32" s="693"/>
-      <c r="Q32" s="693"/>
-      <c r="R32" s="693"/>
+      <c r="M32" s="731"/>
+      <c r="N32" s="731"/>
+      <c r="O32" s="731"/>
+      <c r="P32" s="731"/>
+      <c r="Q32" s="731"/>
+      <c r="R32" s="731"/>
       <c r="S32" s="71"/>
-      <c r="T32" s="693"/>
-      <c r="U32" s="693"/>
+      <c r="T32" s="731"/>
+      <c r="U32" s="731"/>
       <c r="V32" s="71"/>
-      <c r="W32" s="693"/>
-      <c r="X32" s="694"/>
+      <c r="W32" s="731"/>
+      <c r="X32" s="732"/>
       <c r="Y32" s="195"/>
       <c r="Z32" s="80"/>
       <c r="AA32" s="79"/>
@@ -36262,28 +36262,28 @@
       <c r="E33" s="82"/>
       <c r="F33" s="79"/>
       <c r="G33" s="136"/>
-      <c r="H33" s="690">
+      <c r="H33" s="759">
         <f>O38</f>
         <v>0</v>
       </c>
-      <c r="I33" s="691"/>
-      <c r="J33" s="692"/>
+      <c r="I33" s="760"/>
+      <c r="J33" s="761"/>
       <c r="K33" s="89"/>
-      <c r="L33" s="725" t="s">
+      <c r="L33" s="730" t="s">
         <v>167</v>
       </c>
-      <c r="M33" s="693"/>
-      <c r="N33" s="693"/>
-      <c r="O33" s="693"/>
-      <c r="P33" s="693"/>
-      <c r="Q33" s="693"/>
-      <c r="R33" s="693"/>
+      <c r="M33" s="731"/>
+      <c r="N33" s="731"/>
+      <c r="O33" s="731"/>
+      <c r="P33" s="731"/>
+      <c r="Q33" s="731"/>
+      <c r="R33" s="731"/>
       <c r="S33" s="71"/>
-      <c r="T33" s="693"/>
-      <c r="U33" s="693"/>
+      <c r="T33" s="731"/>
+      <c r="U33" s="731"/>
       <c r="V33" s="71"/>
-      <c r="W33" s="693"/>
-      <c r="X33" s="694"/>
+      <c r="W33" s="731"/>
+      <c r="X33" s="732"/>
       <c r="Y33" s="195"/>
       <c r="Z33" s="80"/>
       <c r="AA33" s="193"/>
@@ -36300,21 +36300,21 @@
       <c r="I34" s="82"/>
       <c r="J34" s="165"/>
       <c r="K34" s="89"/>
-      <c r="L34" s="725" t="s">
+      <c r="L34" s="730" t="s">
         <v>168</v>
       </c>
-      <c r="M34" s="693"/>
-      <c r="N34" s="693"/>
-      <c r="O34" s="693"/>
-      <c r="P34" s="693"/>
-      <c r="Q34" s="693"/>
-      <c r="R34" s="693"/>
+      <c r="M34" s="731"/>
+      <c r="N34" s="731"/>
+      <c r="O34" s="731"/>
+      <c r="P34" s="731"/>
+      <c r="Q34" s="731"/>
+      <c r="R34" s="731"/>
       <c r="S34" s="71"/>
-      <c r="T34" s="693"/>
-      <c r="U34" s="693"/>
+      <c r="T34" s="731"/>
+      <c r="U34" s="731"/>
       <c r="V34" s="71"/>
-      <c r="W34" s="693"/>
-      <c r="X34" s="694"/>
+      <c r="W34" s="731"/>
+      <c r="X34" s="732"/>
       <c r="Y34" s="195"/>
       <c r="Z34" s="80"/>
       <c r="AA34" s="79"/>
@@ -36331,21 +36331,21 @@
       <c r="I35" s="166"/>
       <c r="J35" s="138"/>
       <c r="K35" s="89"/>
-      <c r="L35" s="725" t="s">
+      <c r="L35" s="730" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="693"/>
-      <c r="N35" s="693"/>
-      <c r="O35" s="720"/>
-      <c r="P35" s="720"/>
-      <c r="Q35" s="720"/>
-      <c r="R35" s="720"/>
+      <c r="M35" s="731"/>
+      <c r="N35" s="731"/>
+      <c r="O35" s="734"/>
+      <c r="P35" s="734"/>
+      <c r="Q35" s="734"/>
+      <c r="R35" s="734"/>
       <c r="S35" s="162"/>
-      <c r="T35" s="720"/>
-      <c r="U35" s="720"/>
+      <c r="T35" s="734"/>
+      <c r="U35" s="734"/>
       <c r="V35" s="162"/>
-      <c r="W35" s="720"/>
-      <c r="X35" s="740"/>
+      <c r="W35" s="734"/>
+      <c r="X35" s="735"/>
       <c r="Y35" s="195"/>
       <c r="Z35" s="80"/>
       <c r="AA35" s="103"/>
@@ -36362,21 +36362,21 @@
       <c r="I36" s="106"/>
       <c r="J36" s="106"/>
       <c r="K36" s="79"/>
-      <c r="L36" s="725" t="s">
+      <c r="L36" s="730" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="693"/>
-      <c r="N36" s="694"/>
-      <c r="O36" s="697"/>
-      <c r="P36" s="697"/>
-      <c r="Q36" s="697"/>
-      <c r="R36" s="697"/>
+      <c r="M36" s="731"/>
+      <c r="N36" s="732"/>
+      <c r="O36" s="736"/>
+      <c r="P36" s="736"/>
+      <c r="Q36" s="736"/>
+      <c r="R36" s="736"/>
       <c r="S36" s="163"/>
-      <c r="T36" s="697"/>
-      <c r="U36" s="697"/>
+      <c r="T36" s="736"/>
+      <c r="U36" s="736"/>
       <c r="V36" s="163"/>
-      <c r="W36" s="697"/>
-      <c r="X36" s="721"/>
+      <c r="W36" s="736"/>
+      <c r="X36" s="737"/>
       <c r="Y36" s="195"/>
       <c r="Z36" s="80"/>
       <c r="AA36" s="79"/>
@@ -36389,27 +36389,27 @@
       <c r="E37" s="82"/>
       <c r="F37" s="79"/>
       <c r="G37" s="135"/>
-      <c r="H37" s="714" t="s">
+      <c r="H37" s="765" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="715"/>
-      <c r="J37" s="716"/>
+      <c r="I37" s="766"/>
+      <c r="J37" s="767"/>
       <c r="K37" s="89"/>
-      <c r="L37" s="725" t="s">
+      <c r="L37" s="730" t="s">
         <v>169</v>
       </c>
-      <c r="M37" s="693"/>
-      <c r="N37" s="694"/>
-      <c r="O37" s="697"/>
-      <c r="P37" s="697"/>
-      <c r="Q37" s="697"/>
-      <c r="R37" s="697"/>
+      <c r="M37" s="731"/>
+      <c r="N37" s="732"/>
+      <c r="O37" s="736"/>
+      <c r="P37" s="736"/>
+      <c r="Q37" s="736"/>
+      <c r="R37" s="736"/>
       <c r="S37" s="163"/>
-      <c r="T37" s="697"/>
-      <c r="U37" s="697"/>
+      <c r="T37" s="736"/>
+      <c r="U37" s="736"/>
       <c r="V37" s="163"/>
-      <c r="W37" s="697"/>
-      <c r="X37" s="721"/>
+      <c r="W37" s="736"/>
+      <c r="X37" s="737"/>
       <c r="Y37" s="195"/>
       <c r="Z37" s="80"/>
     </row>
@@ -36425,39 +36425,39 @@
       <c r="I38" s="82"/>
       <c r="J38" s="165"/>
       <c r="K38" s="89"/>
-      <c r="L38" s="733" t="s">
+      <c r="L38" s="749" t="s">
         <v>88</v>
       </c>
-      <c r="M38" s="734"/>
-      <c r="N38" s="735"/>
-      <c r="O38" s="698">
+      <c r="M38" s="750"/>
+      <c r="N38" s="751"/>
+      <c r="O38" s="738">
         <f>SUM(O29:P37)</f>
         <v>0</v>
       </c>
-      <c r="P38" s="698"/>
-      <c r="Q38" s="698">
+      <c r="P38" s="738"/>
+      <c r="Q38" s="738">
         <f>SUM(Q29:R37)</f>
         <v>0</v>
       </c>
-      <c r="R38" s="698"/>
+      <c r="R38" s="738"/>
       <c r="S38" s="196">
         <f>SUM(S29:S37)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="698">
+      <c r="T38" s="738">
         <f>SUM(T29:U37)</f>
         <v>0</v>
       </c>
-      <c r="U38" s="698"/>
+      <c r="U38" s="738"/>
       <c r="V38" s="196">
         <f>SUM(V29:V37)</f>
         <v>0</v>
       </c>
-      <c r="W38" s="698">
+      <c r="W38" s="738">
         <f>SUM(W29:X37)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="698"/>
+      <c r="X38" s="738"/>
       <c r="Y38" s="197">
         <f>SUM(Y29:Y37)</f>
         <v>0</v>
@@ -36473,26 +36473,26 @@
       <c r="E39" s="82"/>
       <c r="F39" s="79"/>
       <c r="G39" s="136"/>
-      <c r="H39" s="690">
+      <c r="H39" s="759">
         <f>S38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="691"/>
-      <c r="J39" s="692"/>
+      <c r="I39" s="760"/>
+      <c r="J39" s="761"/>
       <c r="K39" s="89"/>
-      <c r="L39" s="728"/>
-      <c r="M39" s="736"/>
-      <c r="N39" s="737"/>
-      <c r="O39" s="728"/>
-      <c r="P39" s="729"/>
-      <c r="Q39" s="711"/>
-      <c r="R39" s="712"/>
+      <c r="L39" s="744"/>
+      <c r="M39" s="752"/>
+      <c r="N39" s="753"/>
+      <c r="O39" s="744"/>
+      <c r="P39" s="745"/>
+      <c r="Q39" s="757"/>
+      <c r="R39" s="758"/>
       <c r="S39" s="104"/>
-      <c r="T39" s="699"/>
-      <c r="U39" s="699"/>
+      <c r="T39" s="785"/>
+      <c r="U39" s="785"/>
       <c r="V39" s="104"/>
-      <c r="W39" s="699"/>
-      <c r="X39" s="699"/>
+      <c r="W39" s="785"/>
+      <c r="X39" s="785"/>
       <c r="Y39" s="132"/>
       <c r="Z39" s="82"/>
       <c r="AA39" s="79"/>
@@ -36509,19 +36509,19 @@
       <c r="I40" s="82"/>
       <c r="J40" s="165"/>
       <c r="K40" s="89"/>
-      <c r="L40" s="701"/>
-      <c r="M40" s="738"/>
-      <c r="N40" s="702"/>
-      <c r="O40" s="730"/>
-      <c r="P40" s="727"/>
-      <c r="Q40" s="726"/>
-      <c r="R40" s="727"/>
+      <c r="L40" s="754"/>
+      <c r="M40" s="755"/>
+      <c r="N40" s="756"/>
+      <c r="O40" s="746"/>
+      <c r="P40" s="743"/>
+      <c r="Q40" s="742"/>
+      <c r="R40" s="743"/>
       <c r="S40" s="82"/>
-      <c r="T40" s="700"/>
-      <c r="U40" s="700"/>
+      <c r="T40" s="786"/>
+      <c r="U40" s="786"/>
       <c r="V40" s="82"/>
-      <c r="W40" s="700"/>
-      <c r="X40" s="700"/>
+      <c r="W40" s="786"/>
+      <c r="X40" s="786"/>
       <c r="Y40" s="140"/>
       <c r="Z40" s="82"/>
     </row>
@@ -36537,19 +36537,19 @@
       <c r="I41" s="166"/>
       <c r="J41" s="138"/>
       <c r="K41" s="89"/>
-      <c r="L41" s="701"/>
-      <c r="M41" s="738"/>
-      <c r="N41" s="702"/>
-      <c r="O41" s="731"/>
-      <c r="P41" s="732"/>
-      <c r="Q41" s="701"/>
-      <c r="R41" s="702"/>
+      <c r="L41" s="754"/>
+      <c r="M41" s="755"/>
+      <c r="N41" s="756"/>
+      <c r="O41" s="747"/>
+      <c r="P41" s="748"/>
+      <c r="Q41" s="754"/>
+      <c r="R41" s="756"/>
       <c r="S41" s="82"/>
-      <c r="T41" s="701"/>
-      <c r="U41" s="702"/>
+      <c r="T41" s="754"/>
+      <c r="U41" s="756"/>
       <c r="V41" s="82"/>
-      <c r="W41" s="701"/>
-      <c r="X41" s="702"/>
+      <c r="W41" s="754"/>
+      <c r="X41" s="756"/>
       <c r="Y41" s="140"/>
       <c r="Z41" s="82"/>
       <c r="AA41" s="103"/>
@@ -36566,21 +36566,21 @@
       <c r="I42" s="106"/>
       <c r="J42" s="106"/>
       <c r="K42" s="79"/>
-      <c r="L42" s="722"/>
-      <c r="M42" s="723"/>
-      <c r="N42" s="724"/>
-      <c r="O42" s="711"/>
-      <c r="P42" s="712"/>
+      <c r="L42" s="739"/>
+      <c r="M42" s="740"/>
+      <c r="N42" s="741"/>
+      <c r="O42" s="757"/>
+      <c r="P42" s="758"/>
       <c r="Q42" s="82"/>
-      <c r="R42" s="695" t="s">
+      <c r="R42" s="783" t="s">
         <v>136</v>
       </c>
-      <c r="S42" s="696"/>
+      <c r="S42" s="784"/>
       <c r="T42" s="105"/>
-      <c r="U42" s="703"/>
-      <c r="V42" s="704"/>
-      <c r="W42" s="703"/>
-      <c r="X42" s="704"/>
+      <c r="U42" s="787"/>
+      <c r="V42" s="788"/>
+      <c r="W42" s="787"/>
+      <c r="X42" s="788"/>
       <c r="Y42" s="140"/>
       <c r="Z42" s="82"/>
       <c r="AA42" s="79"/>
@@ -36593,19 +36593,19 @@
       <c r="E43" s="82"/>
       <c r="F43" s="79"/>
       <c r="G43" s="135"/>
-      <c r="H43" s="706" t="s">
+      <c r="H43" s="790" t="s">
         <v>104</v>
       </c>
-      <c r="I43" s="706"/>
-      <c r="J43" s="707"/>
+      <c r="I43" s="790"/>
+      <c r="J43" s="791"/>
       <c r="K43" s="89"/>
       <c r="L43" s="135"/>
       <c r="M43" s="164"/>
-      <c r="N43" s="681" t="s">
+      <c r="N43" s="774" t="s">
         <v>94</v>
       </c>
-      <c r="O43" s="682"/>
-      <c r="P43" s="683"/>
+      <c r="O43" s="775"/>
+      <c r="P43" s="776"/>
       <c r="Q43" s="136"/>
       <c r="R43" s="264" t="s">
         <v>137</v>
@@ -36659,21 +36659,21 @@
       <c r="E45" s="82"/>
       <c r="F45" s="79"/>
       <c r="G45" s="136"/>
-      <c r="H45" s="690">
+      <c r="H45" s="759">
         <f>SUM(V38)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="691"/>
-      <c r="J45" s="692"/>
+      <c r="I45" s="760"/>
+      <c r="J45" s="761"/>
       <c r="K45" s="89"/>
       <c r="L45" s="136"/>
       <c r="M45" s="82"/>
       <c r="N45" s="82"/>
-      <c r="O45" s="684">
+      <c r="O45" s="777">
         <f>SUM(Q38,T38,W38)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="685"/>
+      <c r="P45" s="778"/>
       <c r="Q45" s="136"/>
       <c r="R45" s="265" t="s">
         <v>138</v>
@@ -36705,8 +36705,8 @@
       <c r="L46" s="136"/>
       <c r="M46" s="82"/>
       <c r="N46" s="82"/>
-      <c r="O46" s="686"/>
-      <c r="P46" s="687"/>
+      <c r="O46" s="779"/>
+      <c r="P46" s="780"/>
       <c r="Q46" s="136"/>
       <c r="R46" s="266"/>
       <c r="S46" s="281"/>
@@ -36817,9 +36817,9 @@
       <c r="E50" s="82"/>
       <c r="F50" s="79"/>
       <c r="G50" s="167"/>
-      <c r="H50" s="688"/>
-      <c r="I50" s="688"/>
-      <c r="J50" s="689"/>
+      <c r="H50" s="781"/>
+      <c r="I50" s="781"/>
+      <c r="J50" s="782"/>
       <c r="K50" s="80"/>
       <c r="L50" s="104"/>
       <c r="M50" s="104"/>
@@ -36874,9 +36874,9 @@
       <c r="E52" s="82"/>
       <c r="F52" s="82"/>
       <c r="G52" s="82"/>
-      <c r="H52" s="705"/>
-      <c r="I52" s="705"/>
-      <c r="J52" s="705"/>
+      <c r="H52" s="789"/>
+      <c r="I52" s="789"/>
+      <c r="J52" s="789"/>
       <c r="K52" s="82"/>
       <c r="L52" s="82"/>
       <c r="M52" s="82"/>
@@ -36977,11 +36977,11 @@
       <c r="U55" s="79"/>
       <c r="V55" s="82"/>
       <c r="W55" s="82"/>
-      <c r="X55" s="678"/>
-      <c r="Y55" s="679"/>
-      <c r="Z55" s="679"/>
-      <c r="AA55" s="679"/>
-      <c r="AB55" s="680"/>
+      <c r="X55" s="771"/>
+      <c r="Y55" s="772"/>
+      <c r="Z55" s="772"/>
+      <c r="AA55" s="772"/>
+      <c r="AB55" s="773"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="82"/>
@@ -37197,11 +37197,11 @@
       <c r="P63" s="82"/>
       <c r="Q63" s="79"/>
       <c r="R63" s="79"/>
-      <c r="U63" s="678"/>
-      <c r="V63" s="679"/>
-      <c r="W63" s="679"/>
-      <c r="X63" s="679"/>
-      <c r="Y63" s="680"/>
+      <c r="U63" s="771"/>
+      <c r="V63" s="772"/>
+      <c r="W63" s="772"/>
+      <c r="X63" s="772"/>
+      <c r="Y63" s="773"/>
       <c r="Z63" s="82"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -37637,6 +37637,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="U63:Y63"/>
+    <mergeCell ref="X55:AB55"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="O45:P46"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="T40:U40"/>
+    <mergeCell ref="T41:U41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="W40:X40"/>
+    <mergeCell ref="W41:X41"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
     <mergeCell ref="O19:Q19"/>
     <mergeCell ref="X6:Y6"/>
     <mergeCell ref="V12:W13"/>
@@ -37661,178 +37833,6 @@
     <mergeCell ref="T12:U13"/>
     <mergeCell ref="T15:U15"/>
     <mergeCell ref="T16:U16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="U63:Y63"/>
-    <mergeCell ref="X55:AB55"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="O45:P46"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="T40:U40"/>
-    <mergeCell ref="T41:U41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="H43:J43"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="33" priority="10">
@@ -38622,78 +38622,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="802" t="s">
+      <c r="A1" s="837" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="802"/>
-      <c r="C1" s="802"/>
-      <c r="D1" s="802"/>
-      <c r="E1" s="802"/>
-      <c r="F1" s="802"/>
-      <c r="G1" s="802"/>
-      <c r="H1" s="802"/>
-      <c r="I1" s="802"/>
-      <c r="J1" s="802"/>
-      <c r="K1" s="802"/>
-      <c r="L1" s="802"/>
-      <c r="M1" s="802"/>
-      <c r="N1" s="802"/>
-      <c r="O1" s="803"/>
+      <c r="B1" s="837"/>
+      <c r="C1" s="837"/>
+      <c r="D1" s="837"/>
+      <c r="E1" s="837"/>
+      <c r="F1" s="837"/>
+      <c r="G1" s="837"/>
+      <c r="H1" s="837"/>
+      <c r="I1" s="837"/>
+      <c r="J1" s="837"/>
+      <c r="K1" s="837"/>
+      <c r="L1" s="837"/>
+      <c r="M1" s="837"/>
+      <c r="N1" s="837"/>
+      <c r="O1" s="838"/>
     </row>
     <row r="2" spans="1:15" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A2" s="804"/>
-      <c r="B2" s="804"/>
-      <c r="C2" s="804"/>
-      <c r="D2" s="804"/>
-      <c r="E2" s="804"/>
-      <c r="F2" s="804"/>
-      <c r="G2" s="804"/>
-      <c r="H2" s="804"/>
-      <c r="I2" s="804"/>
-      <c r="J2" s="804"/>
-      <c r="K2" s="804"/>
-      <c r="L2" s="804"/>
-      <c r="M2" s="804"/>
-      <c r="N2" s="804"/>
-      <c r="O2" s="805"/>
+      <c r="A2" s="839"/>
+      <c r="B2" s="839"/>
+      <c r="C2" s="839"/>
+      <c r="D2" s="839"/>
+      <c r="E2" s="839"/>
+      <c r="F2" s="839"/>
+      <c r="G2" s="839"/>
+      <c r="H2" s="839"/>
+      <c r="I2" s="839"/>
+      <c r="J2" s="839"/>
+      <c r="K2" s="839"/>
+      <c r="L2" s="839"/>
+      <c r="M2" s="839"/>
+      <c r="N2" s="839"/>
+      <c r="O2" s="840"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="806" t="s">
+      <c r="A3" s="841" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="806"/>
-      <c r="C3" s="806"/>
-      <c r="D3" s="806"/>
-      <c r="E3" s="806"/>
-      <c r="F3" s="806"/>
-      <c r="G3" s="806"/>
-      <c r="H3" s="806"/>
-      <c r="I3" s="806"/>
-      <c r="J3" s="806"/>
-      <c r="K3" s="806"/>
-      <c r="L3" s="806"/>
-      <c r="M3" s="806"/>
-      <c r="N3" s="806"/>
-      <c r="O3" s="807"/>
+      <c r="B3" s="841"/>
+      <c r="C3" s="841"/>
+      <c r="D3" s="841"/>
+      <c r="E3" s="841"/>
+      <c r="F3" s="841"/>
+      <c r="G3" s="841"/>
+      <c r="H3" s="841"/>
+      <c r="I3" s="841"/>
+      <c r="J3" s="841"/>
+      <c r="K3" s="841"/>
+      <c r="L3" s="841"/>
+      <c r="M3" s="841"/>
+      <c r="N3" s="841"/>
+      <c r="O3" s="842"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" thickBot="1">
-      <c r="A4" s="808" t="s">
+      <c r="A4" s="843" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="808"/>
-      <c r="C4" s="808"/>
-      <c r="D4" s="808"/>
-      <c r="E4" s="808"/>
-      <c r="F4" s="808"/>
-      <c r="G4" s="808"/>
-      <c r="H4" s="808"/>
-      <c r="I4" s="808"/>
-      <c r="J4" s="808"/>
-      <c r="K4" s="808"/>
-      <c r="L4" s="808"/>
-      <c r="M4" s="808"/>
-      <c r="N4" s="808"/>
-      <c r="O4" s="809"/>
+      <c r="B4" s="843"/>
+      <c r="C4" s="843"/>
+      <c r="D4" s="843"/>
+      <c r="E4" s="843"/>
+      <c r="F4" s="843"/>
+      <c r="G4" s="843"/>
+      <c r="H4" s="843"/>
+      <c r="I4" s="843"/>
+      <c r="J4" s="843"/>
+      <c r="K4" s="843"/>
+      <c r="L4" s="843"/>
+      <c r="M4" s="843"/>
+      <c r="N4" s="843"/>
+      <c r="O4" s="844"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" thickBot="1">
       <c r="A5" s="90"/>
@@ -38705,8 +38705,8 @@
       <c r="G5" s="512"/>
       <c r="H5" s="510"/>
       <c r="I5" s="82"/>
-      <c r="J5" s="810"/>
-      <c r="K5" s="810"/>
+      <c r="J5" s="845"/>
+      <c r="K5" s="845"/>
       <c r="L5" s="515"/>
       <c r="M5" s="512"/>
       <c r="N5" s="516"/>
@@ -38779,24 +38779,24 @@
       <c r="E8" s="106"/>
       <c r="F8" s="90"/>
       <c r="G8" s="104"/>
-      <c r="H8" s="800"/>
-      <c r="I8" s="801"/>
-      <c r="J8" s="800"/>
-      <c r="K8" s="800"/>
-      <c r="L8" s="800"/>
-      <c r="M8" s="800"/>
+      <c r="H8" s="835"/>
+      <c r="I8" s="836"/>
+      <c r="J8" s="835"/>
+      <c r="K8" s="835"/>
+      <c r="L8" s="835"/>
+      <c r="M8" s="835"/>
       <c r="N8" s="517"/>
       <c r="O8" s="404"/>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1">
-      <c r="A9" s="828" t="s">
+      <c r="A9" s="800" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="829"/>
-      <c r="C9" s="829"/>
-      <c r="D9" s="829"/>
-      <c r="E9" s="829"/>
-      <c r="F9" s="830"/>
+      <c r="B9" s="801"/>
+      <c r="C9" s="801"/>
+      <c r="D9" s="801"/>
+      <c r="E9" s="801"/>
+      <c r="F9" s="802"/>
       <c r="G9" s="83"/>
       <c r="H9" s="494"/>
       <c r="I9" s="499"/>
@@ -38808,12 +38808,12 @@
       <c r="O9" s="232"/>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A10" s="831"/>
-      <c r="B10" s="832"/>
-      <c r="C10" s="832"/>
-      <c r="D10" s="832"/>
-      <c r="E10" s="832"/>
-      <c r="F10" s="833"/>
+      <c r="A10" s="803"/>
+      <c r="B10" s="804"/>
+      <c r="C10" s="804"/>
+      <c r="D10" s="804"/>
+      <c r="E10" s="804"/>
+      <c r="F10" s="805"/>
       <c r="G10" s="80"/>
       <c r="H10" s="82"/>
       <c r="I10" s="497"/>
@@ -38825,22 +38825,22 @@
       <c r="O10" s="404"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="844" t="s">
+      <c r="A11" s="816" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="839" t="s">
+      <c r="B11" s="811" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="841" t="s">
+      <c r="C11" s="813" t="s">
         <v>179</v>
       </c>
-      <c r="D11" s="843" t="s">
+      <c r="D11" s="815" t="s">
         <v>154</v>
       </c>
-      <c r="E11" s="824" t="s">
+      <c r="E11" s="796" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="825"/>
+      <c r="F11" s="797"/>
       <c r="G11" s="80"/>
       <c r="H11" s="82"/>
       <c r="I11" s="497"/>
@@ -38852,12 +38852,12 @@
       <c r="O11" s="404"/>
     </row>
     <row r="12" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A12" s="845"/>
-      <c r="B12" s="840"/>
-      <c r="C12" s="842"/>
-      <c r="D12" s="831"/>
-      <c r="E12" s="826"/>
-      <c r="F12" s="827"/>
+      <c r="A12" s="817"/>
+      <c r="B12" s="812"/>
+      <c r="C12" s="814"/>
+      <c r="D12" s="803"/>
+      <c r="E12" s="798"/>
+      <c r="F12" s="799"/>
       <c r="G12" s="80"/>
       <c r="H12" s="82"/>
       <c r="I12" s="497"/>
@@ -38875,11 +38875,11 @@
       <c r="B13" s="552"/>
       <c r="C13" s="552"/>
       <c r="D13" s="553"/>
-      <c r="E13" s="834">
+      <c r="E13" s="806">
         <f>SUM(B13:D13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="835"/>
+      <c r="F13" s="807"/>
       <c r="G13" s="80"/>
       <c r="H13" s="82"/>
       <c r="I13" s="82"/>
@@ -38897,11 +38897,11 @@
       <c r="B14" s="502"/>
       <c r="C14" s="502"/>
       <c r="D14" s="554"/>
-      <c r="E14" s="836">
+      <c r="E14" s="808">
         <f>SUM(B14:D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="837"/>
+      <c r="F14" s="809"/>
       <c r="G14" s="80"/>
       <c r="H14" s="82"/>
       <c r="I14" s="497"/>
@@ -38919,11 +38919,11 @@
       <c r="B15" s="505"/>
       <c r="C15" s="505"/>
       <c r="D15" s="506"/>
-      <c r="E15" s="846">
+      <c r="E15" s="818">
         <f>SUM(B15:D15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="847"/>
+      <c r="F15" s="819"/>
       <c r="G15" s="80"/>
       <c r="H15" s="82"/>
       <c r="I15" s="497"/>
@@ -38958,11 +38958,11 @@
       <c r="D17" s="82"/>
       <c r="E17" s="89"/>
       <c r="F17" s="82"/>
-      <c r="H17" s="812" t="s">
+      <c r="H17" s="821" t="s">
         <v>157</v>
       </c>
-      <c r="I17" s="813"/>
-      <c r="J17" s="814"/>
+      <c r="I17" s="822"/>
+      <c r="J17" s="823"/>
       <c r="K17" s="227"/>
       <c r="L17" s="227"/>
       <c r="M17" s="227"/>
@@ -39023,10 +39023,10 @@
       <c r="K20" s="538" t="s">
         <v>52</v>
       </c>
-      <c r="L20" s="820" t="s">
+      <c r="L20" s="831" t="s">
         <v>53</v>
       </c>
-      <c r="M20" s="821"/>
+      <c r="M20" s="832"/>
       <c r="N20" s="400"/>
       <c r="O20" s="165"/>
     </row>
@@ -39042,8 +39042,8 @@
       <c r="I21" s="541"/>
       <c r="J21" s="541"/>
       <c r="K21" s="541"/>
-      <c r="L21" s="822"/>
-      <c r="M21" s="823"/>
+      <c r="L21" s="833"/>
+      <c r="M21" s="834"/>
       <c r="N21" s="80"/>
       <c r="O21" s="165"/>
     </row>
@@ -39059,27 +39059,27 @@
       <c r="I22" s="540"/>
       <c r="J22" s="540"/>
       <c r="K22" s="540"/>
-      <c r="L22" s="796"/>
-      <c r="M22" s="797"/>
+      <c r="L22" s="829"/>
+      <c r="M22" s="830"/>
       <c r="N22" s="80"/>
       <c r="O22" s="165"/>
     </row>
     <row r="23" spans="1:15" ht="27.75" customHeight="1" thickBot="1">
-      <c r="A23" s="817" t="s">
+      <c r="A23" s="826" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="818"/>
-      <c r="C23" s="818"/>
-      <c r="D23" s="818"/>
-      <c r="E23" s="818"/>
-      <c r="F23" s="819"/>
+      <c r="B23" s="827"/>
+      <c r="C23" s="827"/>
+      <c r="D23" s="827"/>
+      <c r="E23" s="827"/>
+      <c r="F23" s="828"/>
       <c r="G23" s="78"/>
       <c r="H23" s="580"/>
       <c r="I23" s="540"/>
       <c r="J23" s="540"/>
       <c r="K23" s="540"/>
-      <c r="L23" s="796"/>
-      <c r="M23" s="797"/>
+      <c r="L23" s="829"/>
+      <c r="M23" s="830"/>
       <c r="N23" s="80"/>
       <c r="O23" s="165"/>
     </row>
@@ -39087,10 +39087,10 @@
       <c r="A24" s="547" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="815" t="s">
+      <c r="B24" s="824" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="816"/>
+      <c r="C24" s="825"/>
       <c r="D24" s="548" t="s">
         <v>161</v>
       </c>
@@ -39105,8 +39105,8 @@
       <c r="I24" s="540"/>
       <c r="J24" s="540"/>
       <c r="K24" s="540"/>
-      <c r="L24" s="796"/>
-      <c r="M24" s="797"/>
+      <c r="L24" s="829"/>
+      <c r="M24" s="830"/>
       <c r="N24" s="80"/>
       <c r="O24" s="165"/>
     </row>
@@ -39114,8 +39114,8 @@
       <c r="A25" s="501" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="838"/>
-      <c r="C25" s="838"/>
+      <c r="B25" s="810"/>
+      <c r="C25" s="810"/>
       <c r="D25" s="508"/>
       <c r="E25" s="508"/>
       <c r="F25" s="507">
@@ -39127,8 +39127,8 @@
       <c r="I25" s="540"/>
       <c r="J25" s="540"/>
       <c r="K25" s="540"/>
-      <c r="L25" s="796"/>
-      <c r="M25" s="797"/>
+      <c r="L25" s="829"/>
+      <c r="M25" s="830"/>
       <c r="N25" s="80"/>
       <c r="O25" s="165"/>
     </row>
@@ -39141,16 +39141,16 @@
       <c r="I26" s="540"/>
       <c r="J26" s="540"/>
       <c r="K26" s="540"/>
-      <c r="L26" s="796"/>
-      <c r="M26" s="797"/>
+      <c r="L26" s="829"/>
+      <c r="M26" s="830"/>
       <c r="N26" s="80"/>
       <c r="O26" s="165"/>
     </row>
     <row r="27" spans="1:15" ht="27" customHeight="1">
-      <c r="A27" s="811"/>
-      <c r="B27" s="811"/>
-      <c r="C27" s="811"/>
-      <c r="D27" s="811"/>
+      <c r="A27" s="820"/>
+      <c r="B27" s="820"/>
+      <c r="C27" s="820"/>
+      <c r="D27" s="820"/>
       <c r="E27" s="495"/>
       <c r="F27" s="498"/>
       <c r="G27" s="89"/>
@@ -39158,8 +39158,8 @@
       <c r="I27" s="540"/>
       <c r="J27" s="540"/>
       <c r="K27" s="540"/>
-      <c r="L27" s="796"/>
-      <c r="M27" s="797"/>
+      <c r="L27" s="829"/>
+      <c r="M27" s="830"/>
       <c r="N27" s="80"/>
       <c r="O27" s="165"/>
     </row>
@@ -39175,8 +39175,8 @@
       <c r="I28" s="540"/>
       <c r="J28" s="540"/>
       <c r="K28" s="540"/>
-      <c r="L28" s="796"/>
-      <c r="M28" s="797"/>
+      <c r="L28" s="829"/>
+      <c r="M28" s="830"/>
       <c r="N28" s="105"/>
       <c r="O28" s="165"/>
     </row>
@@ -39191,8 +39191,8 @@
       <c r="I29" s="540"/>
       <c r="J29" s="540"/>
       <c r="K29" s="540"/>
-      <c r="L29" s="796"/>
-      <c r="M29" s="797"/>
+      <c r="L29" s="829"/>
+      <c r="M29" s="830"/>
       <c r="N29" s="80"/>
       <c r="O29" s="165"/>
     </row>
@@ -39208,8 +39208,8 @@
       <c r="I30" s="540"/>
       <c r="J30" s="540"/>
       <c r="K30" s="540"/>
-      <c r="L30" s="796"/>
-      <c r="M30" s="797"/>
+      <c r="L30" s="829"/>
+      <c r="M30" s="830"/>
       <c r="N30" s="80"/>
       <c r="O30" s="165"/>
     </row>
@@ -39225,8 +39225,8 @@
       <c r="I31" s="540"/>
       <c r="J31" s="540"/>
       <c r="K31" s="540"/>
-      <c r="L31" s="796"/>
-      <c r="M31" s="797"/>
+      <c r="L31" s="829"/>
+      <c r="M31" s="830"/>
       <c r="N31" s="80"/>
       <c r="O31" s="165"/>
     </row>
@@ -39242,8 +39242,8 @@
       <c r="I32" s="540"/>
       <c r="J32" s="540"/>
       <c r="K32" s="540"/>
-      <c r="L32" s="796"/>
-      <c r="M32" s="797"/>
+      <c r="L32" s="829"/>
+      <c r="M32" s="830"/>
       <c r="N32" s="80"/>
       <c r="O32" s="165"/>
     </row>
@@ -39259,8 +39259,8 @@
       <c r="I33" s="540"/>
       <c r="J33" s="540"/>
       <c r="K33" s="540"/>
-      <c r="L33" s="796"/>
-      <c r="M33" s="797"/>
+      <c r="L33" s="829"/>
+      <c r="M33" s="830"/>
       <c r="N33" s="80"/>
       <c r="O33" s="165"/>
     </row>
@@ -39276,8 +39276,8 @@
       <c r="I34" s="540"/>
       <c r="J34" s="540"/>
       <c r="K34" s="540"/>
-      <c r="L34" s="796"/>
-      <c r="M34" s="797"/>
+      <c r="L34" s="829"/>
+      <c r="M34" s="830"/>
       <c r="N34" s="80"/>
       <c r="O34" s="165"/>
     </row>
@@ -39293,8 +39293,8 @@
       <c r="I35" s="540"/>
       <c r="J35" s="540"/>
       <c r="K35" s="540"/>
-      <c r="L35" s="796"/>
-      <c r="M35" s="797"/>
+      <c r="L35" s="829"/>
+      <c r="M35" s="830"/>
       <c r="N35" s="80"/>
       <c r="O35" s="165"/>
     </row>
@@ -39309,8 +39309,8 @@
       <c r="I36" s="540"/>
       <c r="J36" s="540"/>
       <c r="K36" s="540"/>
-      <c r="L36" s="796"/>
-      <c r="M36" s="797"/>
+      <c r="L36" s="829"/>
+      <c r="M36" s="830"/>
       <c r="N36" s="80"/>
       <c r="O36" s="165"/>
     </row>
@@ -39326,23 +39326,29 @@
       <c r="I37" s="542"/>
       <c r="J37" s="542"/>
       <c r="K37" s="542"/>
-      <c r="L37" s="798"/>
-      <c r="M37" s="799"/>
+      <c r="L37" s="846"/>
+      <c r="M37" s="847"/>
       <c r="N37" s="80"/>
       <c r="O37" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="B24:C24"/>
@@ -39355,22 +39361,16 @@
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="L26:M26"/>
     <mergeCell ref="L27:M27"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E15:F15"/>
   </mergeCells>
   <conditionalFormatting sqref="I21:L37">
     <cfRule type="expression" dxfId="27" priority="1">
@@ -39411,22 +39411,22 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21">
       <c r="A1" s="82"/>
-      <c r="B1" s="881" t="s">
+      <c r="B1" s="851" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="882"/>
-      <c r="D1" s="882"/>
-      <c r="E1" s="882"/>
-      <c r="F1" s="882"/>
-      <c r="G1" s="882"/>
-      <c r="H1" s="882"/>
-      <c r="I1" s="882"/>
-      <c r="J1" s="882"/>
-      <c r="K1" s="882"/>
-      <c r="L1" s="882"/>
-      <c r="M1" s="882"/>
-      <c r="N1" s="882"/>
-      <c r="O1" s="883"/>
+      <c r="C1" s="852"/>
+      <c r="D1" s="852"/>
+      <c r="E1" s="852"/>
+      <c r="F1" s="852"/>
+      <c r="G1" s="852"/>
+      <c r="H1" s="852"/>
+      <c r="I1" s="852"/>
+      <c r="J1" s="852"/>
+      <c r="K1" s="852"/>
+      <c r="L1" s="852"/>
+      <c r="M1" s="852"/>
+      <c r="N1" s="852"/>
+      <c r="O1" s="853"/>
       <c r="P1" s="82"/>
       <c r="Q1" s="82"/>
       <c r="R1" s="82"/>
@@ -39435,24 +39435,24 @@
     </row>
     <row r="2" spans="1:20" ht="18.75" customHeight="1">
       <c r="A2" s="82"/>
-      <c r="B2" s="869" t="s">
+      <c r="B2" s="870" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="870"/>
-      <c r="D2" s="870"/>
-      <c r="E2" s="870"/>
-      <c r="F2" s="870"/>
-      <c r="G2" s="871" t="s">
+      <c r="C2" s="871"/>
+      <c r="D2" s="871"/>
+      <c r="E2" s="871"/>
+      <c r="F2" s="871"/>
+      <c r="G2" s="872" t="s">
         <v>164</v>
       </c>
-      <c r="H2" s="871"/>
-      <c r="I2" s="871"/>
-      <c r="J2" s="871"/>
-      <c r="K2" s="871"/>
-      <c r="L2" s="871"/>
-      <c r="M2" s="871"/>
-      <c r="N2" s="871"/>
-      <c r="O2" s="872"/>
+      <c r="H2" s="872"/>
+      <c r="I2" s="872"/>
+      <c r="J2" s="872"/>
+      <c r="K2" s="872"/>
+      <c r="L2" s="872"/>
+      <c r="M2" s="872"/>
+      <c r="N2" s="872"/>
+      <c r="O2" s="873"/>
       <c r="P2" s="82"/>
       <c r="Q2" s="82"/>
       <c r="R2" s="82"/>
@@ -39461,15 +39461,15 @@
     </row>
     <row r="3" spans="1:20" ht="28.5" customHeight="1" thickBot="1">
       <c r="A3" s="82"/>
-      <c r="B3" s="873" t="s">
+      <c r="B3" s="874" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="874"/>
-      <c r="D3" s="874"/>
-      <c r="E3" s="874"/>
-      <c r="F3" s="874"/>
-      <c r="G3" s="874"/>
-      <c r="H3" s="875"/>
+      <c r="C3" s="875"/>
+      <c r="D3" s="875"/>
+      <c r="E3" s="875"/>
+      <c r="F3" s="875"/>
+      <c r="G3" s="875"/>
+      <c r="H3" s="876"/>
       <c r="I3" s="208"/>
       <c r="J3" s="209"/>
       <c r="K3" s="477"/>
@@ -39494,13 +39494,13 @@
       <c r="H4" s="80"/>
       <c r="I4" s="88"/>
       <c r="J4" s="103"/>
-      <c r="K4" s="891" t="s">
+      <c r="K4" s="863" t="s">
         <v>187</v>
       </c>
-      <c r="L4" s="892"/>
-      <c r="M4" s="892"/>
-      <c r="N4" s="892"/>
-      <c r="O4" s="893"/>
+      <c r="L4" s="864"/>
+      <c r="M4" s="864"/>
+      <c r="N4" s="864"/>
+      <c r="O4" s="865"/>
       <c r="P4" s="80"/>
       <c r="Q4" s="82"/>
       <c r="R4" s="82"/>
@@ -39513,14 +39513,14 @@
       <c r="H5" s="79"/>
       <c r="I5" s="82"/>
       <c r="J5" s="210"/>
-      <c r="K5" s="888" t="s">
+      <c r="K5" s="860" t="s">
         <v>122</v>
       </c>
-      <c r="L5" s="887"/>
-      <c r="M5" s="887" t="s">
+      <c r="L5" s="859"/>
+      <c r="M5" s="859" t="s">
         <v>190</v>
       </c>
-      <c r="N5" s="887"/>
+      <c r="N5" s="859"/>
       <c r="O5" s="529" t="s">
         <v>70</v>
       </c>
@@ -39536,10 +39536,10 @@
       <c r="H6" s="79"/>
       <c r="I6" s="82"/>
       <c r="J6" s="79"/>
-      <c r="K6" s="894"/>
-      <c r="L6" s="895"/>
-      <c r="M6" s="885"/>
-      <c r="N6" s="886"/>
+      <c r="K6" s="866"/>
+      <c r="L6" s="867"/>
+      <c r="M6" s="855"/>
+      <c r="N6" s="856"/>
       <c r="O6" s="560"/>
       <c r="P6" s="80"/>
       <c r="Q6" s="82"/>
@@ -39551,16 +39551,16 @@
       <c r="A7" s="82"/>
       <c r="C7" s="82"/>
       <c r="D7" s="82"/>
-      <c r="E7" s="889"/>
-      <c r="F7" s="890"/>
-      <c r="G7" s="890"/>
-      <c r="H7" s="890"/>
+      <c r="E7" s="861"/>
+      <c r="F7" s="862"/>
+      <c r="G7" s="862"/>
+      <c r="H7" s="862"/>
       <c r="I7" s="82"/>
       <c r="J7" s="103"/>
-      <c r="K7" s="850"/>
-      <c r="L7" s="851"/>
-      <c r="M7" s="848"/>
-      <c r="N7" s="849"/>
+      <c r="K7" s="868"/>
+      <c r="L7" s="869"/>
+      <c r="M7" s="857"/>
+      <c r="N7" s="858"/>
       <c r="O7" s="561"/>
       <c r="P7" s="80"/>
       <c r="Q7" s="82"/>
@@ -39575,10 +39575,10 @@
       <c r="D8" s="82"/>
       <c r="I8" s="82"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="850"/>
-      <c r="L8" s="851"/>
-      <c r="M8" s="848"/>
-      <c r="N8" s="849"/>
+      <c r="K8" s="868"/>
+      <c r="L8" s="869"/>
+      <c r="M8" s="857"/>
+      <c r="N8" s="858"/>
       <c r="O8" s="561"/>
       <c r="P8" s="80"/>
       <c r="Q8" s="82"/>
@@ -39593,10 +39593,10 @@
       <c r="D9" s="82"/>
       <c r="I9" s="82"/>
       <c r="J9" s="103"/>
-      <c r="K9" s="850"/>
-      <c r="L9" s="851"/>
-      <c r="M9" s="848"/>
-      <c r="N9" s="849"/>
+      <c r="K9" s="868"/>
+      <c r="L9" s="869"/>
+      <c r="M9" s="857"/>
+      <c r="N9" s="858"/>
       <c r="O9" s="561"/>
       <c r="P9" s="80"/>
       <c r="Q9" s="82"/>
@@ -39613,10 +39613,10 @@
       <c r="D10" s="80"/>
       <c r="I10" s="82"/>
       <c r="J10" s="79"/>
-      <c r="K10" s="850"/>
-      <c r="L10" s="851"/>
-      <c r="M10" s="848"/>
-      <c r="N10" s="849"/>
+      <c r="K10" s="868"/>
+      <c r="L10" s="869"/>
+      <c r="M10" s="857"/>
+      <c r="N10" s="858"/>
       <c r="O10" s="561"/>
       <c r="P10" s="80"/>
       <c r="Q10" s="82"/>
@@ -39635,10 +39635,10 @@
       <c r="H11" s="87"/>
       <c r="I11" s="80"/>
       <c r="J11" s="103"/>
-      <c r="K11" s="850"/>
-      <c r="L11" s="851"/>
-      <c r="M11" s="848"/>
-      <c r="N11" s="849"/>
+      <c r="K11" s="868"/>
+      <c r="L11" s="869"/>
+      <c r="M11" s="857"/>
+      <c r="N11" s="858"/>
       <c r="O11" s="561"/>
       <c r="P11" s="80"/>
       <c r="Q11" s="82"/>
@@ -39654,10 +39654,10 @@
       <c r="G12" s="89"/>
       <c r="I12" s="80"/>
       <c r="J12" s="103"/>
-      <c r="K12" s="850"/>
-      <c r="L12" s="851"/>
-      <c r="M12" s="848"/>
-      <c r="N12" s="849"/>
+      <c r="K12" s="868"/>
+      <c r="L12" s="869"/>
+      <c r="M12" s="857"/>
+      <c r="N12" s="858"/>
       <c r="O12" s="561"/>
       <c r="P12" s="80"/>
       <c r="Q12" s="82"/>
@@ -39668,18 +39668,18 @@
     <row r="13" spans="1:20" ht="55.5" customHeight="1">
       <c r="A13" s="79"/>
       <c r="D13" s="89"/>
-      <c r="E13" s="884" t="s">
+      <c r="E13" s="854" t="s">
         <v>174</v>
       </c>
-      <c r="F13" s="884"/>
-      <c r="G13" s="884"/>
-      <c r="H13" s="884"/>
+      <c r="F13" s="854"/>
+      <c r="G13" s="854"/>
+      <c r="H13" s="854"/>
       <c r="I13" s="80"/>
       <c r="J13" s="103"/>
-      <c r="K13" s="850"/>
-      <c r="L13" s="851"/>
-      <c r="M13" s="848"/>
-      <c r="N13" s="849"/>
+      <c r="K13" s="868"/>
+      <c r="L13" s="869"/>
+      <c r="M13" s="857"/>
+      <c r="N13" s="858"/>
       <c r="O13" s="561"/>
       <c r="P13" s="80"/>
       <c r="Q13" s="82"/>
@@ -39689,25 +39689,25 @@
     </row>
     <row r="14" spans="1:20" ht="47.25" customHeight="1">
       <c r="A14" s="79"/>
-      <c r="B14" s="860" t="s">
+      <c r="B14" s="883" t="s">
         <v>170</v>
       </c>
-      <c r="C14" s="860"/>
+      <c r="C14" s="883"/>
       <c r="D14" s="89"/>
-      <c r="E14" s="877" t="s">
+      <c r="E14" s="878" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="877"/>
-      <c r="G14" s="877"/>
+      <c r="F14" s="878"/>
+      <c r="G14" s="878"/>
       <c r="H14" s="465" t="s">
         <v>123</v>
       </c>
       <c r="I14" s="80"/>
       <c r="J14" s="103"/>
-      <c r="K14" s="850"/>
-      <c r="L14" s="851"/>
-      <c r="M14" s="848"/>
-      <c r="N14" s="849"/>
+      <c r="K14" s="868"/>
+      <c r="L14" s="869"/>
+      <c r="M14" s="857"/>
+      <c r="N14" s="858"/>
       <c r="O14" s="561"/>
       <c r="P14" s="80"/>
       <c r="Q14" s="82"/>
@@ -39724,16 +39724,16 @@
         <v>172</v>
       </c>
       <c r="D15" s="89"/>
-      <c r="E15" s="864"/>
-      <c r="F15" s="864"/>
-      <c r="G15" s="864"/>
+      <c r="E15" s="879"/>
+      <c r="F15" s="879"/>
+      <c r="G15" s="879"/>
       <c r="H15" s="474"/>
       <c r="I15" s="80"/>
       <c r="J15" s="103"/>
-      <c r="K15" s="850"/>
-      <c r="L15" s="851"/>
-      <c r="M15" s="848"/>
-      <c r="N15" s="849"/>
+      <c r="K15" s="868"/>
+      <c r="L15" s="869"/>
+      <c r="M15" s="857"/>
+      <c r="N15" s="858"/>
       <c r="O15" s="561"/>
       <c r="P15" s="80"/>
       <c r="Q15" s="82"/>
@@ -39746,16 +39746,16 @@
       <c r="B16" s="473"/>
       <c r="C16" s="473"/>
       <c r="D16" s="89"/>
-      <c r="E16" s="864"/>
-      <c r="F16" s="864"/>
-      <c r="G16" s="864"/>
+      <c r="E16" s="879"/>
+      <c r="F16" s="879"/>
+      <c r="G16" s="879"/>
       <c r="H16" s="474"/>
       <c r="I16" s="80"/>
       <c r="J16" s="103"/>
-      <c r="K16" s="850"/>
-      <c r="L16" s="851"/>
-      <c r="M16" s="848"/>
-      <c r="N16" s="849"/>
+      <c r="K16" s="868"/>
+      <c r="L16" s="869"/>
+      <c r="M16" s="857"/>
+      <c r="N16" s="858"/>
       <c r="O16" s="561"/>
       <c r="P16" s="80"/>
       <c r="Q16" s="82"/>
@@ -39768,16 +39768,16 @@
       <c r="B17" s="473"/>
       <c r="C17" s="473"/>
       <c r="D17" s="89"/>
-      <c r="E17" s="864"/>
-      <c r="F17" s="864"/>
-      <c r="G17" s="864"/>
+      <c r="E17" s="879"/>
+      <c r="F17" s="879"/>
+      <c r="G17" s="879"/>
       <c r="H17" s="474"/>
       <c r="I17" s="80"/>
       <c r="J17" s="79"/>
-      <c r="K17" s="850"/>
-      <c r="L17" s="851"/>
-      <c r="M17" s="848"/>
-      <c r="N17" s="849"/>
+      <c r="K17" s="868"/>
+      <c r="L17" s="869"/>
+      <c r="M17" s="857"/>
+      <c r="N17" s="858"/>
       <c r="O17" s="561"/>
       <c r="P17" s="80"/>
       <c r="Q17" s="82"/>
@@ -39790,16 +39790,16 @@
       <c r="B18" s="473"/>
       <c r="C18" s="473"/>
       <c r="D18" s="89"/>
-      <c r="E18" s="864"/>
-      <c r="F18" s="864"/>
-      <c r="G18" s="864"/>
+      <c r="E18" s="879"/>
+      <c r="F18" s="879"/>
+      <c r="G18" s="879"/>
       <c r="H18" s="474"/>
       <c r="I18" s="80"/>
       <c r="J18" s="87"/>
-      <c r="K18" s="867"/>
-      <c r="L18" s="868"/>
-      <c r="M18" s="855"/>
-      <c r="N18" s="856"/>
+      <c r="K18" s="891"/>
+      <c r="L18" s="892"/>
+      <c r="M18" s="889"/>
+      <c r="N18" s="890"/>
       <c r="O18" s="561"/>
       <c r="P18" s="80"/>
       <c r="Q18" s="82"/>
@@ -39812,15 +39812,15 @@
       <c r="B19" s="473"/>
       <c r="C19" s="473"/>
       <c r="D19" s="89"/>
-      <c r="E19" s="864"/>
-      <c r="F19" s="864"/>
-      <c r="G19" s="864"/>
+      <c r="E19" s="879"/>
+      <c r="F19" s="879"/>
+      <c r="G19" s="879"/>
       <c r="H19" s="474"/>
       <c r="I19" s="80"/>
       <c r="J19" s="79"/>
       <c r="K19" s="230"/>
-      <c r="M19" s="855"/>
-      <c r="N19" s="856"/>
+      <c r="M19" s="889"/>
+      <c r="N19" s="890"/>
       <c r="O19" s="561"/>
       <c r="P19" s="80"/>
       <c r="Q19" s="82"/>
@@ -39833,15 +39833,15 @@
       <c r="B20" s="473"/>
       <c r="C20" s="473"/>
       <c r="D20" s="89"/>
-      <c r="E20" s="865"/>
-      <c r="F20" s="865"/>
-      <c r="G20" s="865"/>
+      <c r="E20" s="887"/>
+      <c r="F20" s="887"/>
+      <c r="G20" s="887"/>
       <c r="H20" s="475"/>
       <c r="I20" s="80"/>
       <c r="J20" s="103"/>
       <c r="K20" s="230"/>
-      <c r="M20" s="855"/>
-      <c r="N20" s="856"/>
+      <c r="M20" s="889"/>
+      <c r="N20" s="890"/>
       <c r="O20" s="561"/>
       <c r="P20" s="80"/>
       <c r="Q20" s="82"/>
@@ -39854,11 +39854,11 @@
       <c r="B21" s="473"/>
       <c r="C21" s="473"/>
       <c r="D21" s="98"/>
-      <c r="E21" s="876" t="s">
+      <c r="E21" s="877" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="876"/>
-      <c r="G21" s="876"/>
+      <c r="F21" s="877"/>
+      <c r="G21" s="877"/>
       <c r="H21" s="476">
         <f>SUM(H15:H20)</f>
         <v>0</v>
@@ -39866,8 +39866,8 @@
       <c r="I21" s="80"/>
       <c r="J21" s="103"/>
       <c r="K21" s="230"/>
-      <c r="M21" s="855"/>
-      <c r="N21" s="856"/>
+      <c r="M21" s="889"/>
+      <c r="N21" s="890"/>
       <c r="O21" s="561"/>
       <c r="P21" s="80"/>
       <c r="Q21" s="82"/>
@@ -39885,17 +39885,17 @@
         <v>0</v>
       </c>
       <c r="D22" s="89"/>
-      <c r="E22" s="852" t="s">
+      <c r="E22" s="893" t="s">
         <v>171</v>
       </c>
-      <c r="F22" s="853"/>
-      <c r="G22" s="853"/>
-      <c r="H22" s="854"/>
+      <c r="F22" s="894"/>
+      <c r="G22" s="894"/>
+      <c r="H22" s="895"/>
       <c r="I22" s="80"/>
       <c r="J22" s="79"/>
       <c r="K22" s="230"/>
-      <c r="M22" s="855"/>
-      <c r="N22" s="856"/>
+      <c r="M22" s="889"/>
+      <c r="N22" s="890"/>
       <c r="O22" s="561"/>
       <c r="P22" s="80"/>
       <c r="Q22" s="82"/>
@@ -39910,8 +39910,8 @@
       <c r="J23" s="79"/>
       <c r="K23" s="230"/>
       <c r="L23" s="87"/>
-      <c r="M23" s="855"/>
-      <c r="N23" s="856"/>
+      <c r="M23" s="889"/>
+      <c r="N23" s="890"/>
       <c r="O23" s="561"/>
       <c r="P23" s="80"/>
       <c r="Q23" s="82"/>
@@ -39928,8 +39928,8 @@
       <c r="J24" s="87"/>
       <c r="K24" s="235"/>
       <c r="L24" s="234"/>
-      <c r="M24" s="855"/>
-      <c r="N24" s="856"/>
+      <c r="M24" s="889"/>
+      <c r="N24" s="890"/>
       <c r="O24" s="561"/>
       <c r="P24" s="80"/>
       <c r="Q24" s="82"/>
@@ -39946,8 +39946,8 @@
         <v>144</v>
       </c>
       <c r="L25" s="532"/>
-      <c r="M25" s="855"/>
-      <c r="N25" s="856"/>
+      <c r="M25" s="889"/>
+      <c r="N25" s="890"/>
       <c r="O25" s="561"/>
       <c r="P25" s="80"/>
       <c r="Q25" s="82"/>
@@ -39961,15 +39961,15 @@
       <c r="D26" s="231"/>
       <c r="E26" s="467"/>
       <c r="F26" s="468"/>
-      <c r="H26" s="866"/>
-      <c r="I26" s="866"/>
+      <c r="H26" s="888"/>
+      <c r="I26" s="888"/>
       <c r="J26" s="466"/>
-      <c r="K26" s="861" t="s">
+      <c r="K26" s="884" t="s">
         <v>191</v>
       </c>
-      <c r="L26" s="862"/>
-      <c r="M26" s="862"/>
-      <c r="N26" s="863"/>
+      <c r="L26" s="885"/>
+      <c r="M26" s="885"/>
+      <c r="N26" s="886"/>
       <c r="O26" s="530"/>
       <c r="P26" s="80"/>
       <c r="Q26" s="82"/>
@@ -39986,13 +39986,13 @@
       <c r="H27" s="470"/>
       <c r="I27" s="471"/>
       <c r="J27" s="211"/>
-      <c r="K27" s="857" t="s">
+      <c r="K27" s="880" t="s">
         <v>189</v>
       </c>
-      <c r="L27" s="858"/>
-      <c r="M27" s="858"/>
-      <c r="N27" s="858"/>
-      <c r="O27" s="859"/>
+      <c r="L27" s="881"/>
+      <c r="M27" s="881"/>
+      <c r="N27" s="881"/>
+      <c r="O27" s="882"/>
       <c r="P27" s="80"/>
       <c r="Q27" s="82"/>
       <c r="S27" s="82"/>
@@ -40001,13 +40001,13 @@
     <row r="28" spans="1:20" ht="32.25" customHeight="1" thickBot="1">
       <c r="A28" s="79"/>
       <c r="J28" s="78"/>
-      <c r="K28" s="878" t="s">
+      <c r="K28" s="848" t="s">
         <v>188</v>
       </c>
-      <c r="L28" s="879"/>
-      <c r="M28" s="879"/>
-      <c r="N28" s="879"/>
-      <c r="O28" s="880"/>
+      <c r="L28" s="849"/>
+      <c r="M28" s="849"/>
+      <c r="N28" s="849"/>
+      <c r="O28" s="850"/>
       <c r="P28" s="82"/>
       <c r="Q28" s="82"/>
       <c r="R28" s="79"/>
@@ -40399,6 +40399,46 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="K27:O27"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:O2"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
     <mergeCell ref="K28:O28"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="E13:H13"/>
@@ -40415,46 +40455,6 @@
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:O2"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K27:O27"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -40504,159 +40504,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="21.75" thickBot="1">
-      <c r="A1" s="929" t="s">
+      <c r="A1" s="986" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="930"/>
-      <c r="C1" s="930"/>
-      <c r="D1" s="930"/>
-      <c r="E1" s="930"/>
-      <c r="F1" s="930"/>
-      <c r="G1" s="930"/>
-      <c r="H1" s="930"/>
-      <c r="I1" s="930"/>
-      <c r="J1" s="930"/>
-      <c r="K1" s="930"/>
-      <c r="L1" s="930"/>
-      <c r="M1" s="930"/>
-      <c r="N1" s="930"/>
-      <c r="O1" s="930"/>
-      <c r="P1" s="930"/>
-      <c r="Q1" s="930"/>
-      <c r="R1" s="930"/>
-      <c r="S1" s="930"/>
-      <c r="T1" s="930"/>
-      <c r="U1" s="930"/>
-      <c r="V1" s="930"/>
-      <c r="W1" s="930"/>
-      <c r="X1" s="930"/>
-      <c r="Y1" s="930"/>
-      <c r="Z1" s="930"/>
-      <c r="AA1" s="930"/>
-      <c r="AB1" s="930"/>
-      <c r="AC1" s="930"/>
-      <c r="AD1" s="930"/>
-      <c r="AE1" s="930"/>
-      <c r="AF1" s="930"/>
-      <c r="AG1" s="930"/>
-      <c r="AH1" s="930"/>
-      <c r="AI1" s="931"/>
+      <c r="B1" s="987"/>
+      <c r="C1" s="987"/>
+      <c r="D1" s="987"/>
+      <c r="E1" s="987"/>
+      <c r="F1" s="987"/>
+      <c r="G1" s="987"/>
+      <c r="H1" s="987"/>
+      <c r="I1" s="987"/>
+      <c r="J1" s="987"/>
+      <c r="K1" s="987"/>
+      <c r="L1" s="987"/>
+      <c r="M1" s="987"/>
+      <c r="N1" s="987"/>
+      <c r="O1" s="987"/>
+      <c r="P1" s="987"/>
+      <c r="Q1" s="987"/>
+      <c r="R1" s="987"/>
+      <c r="S1" s="987"/>
+      <c r="T1" s="987"/>
+      <c r="U1" s="987"/>
+      <c r="V1" s="987"/>
+      <c r="W1" s="987"/>
+      <c r="X1" s="987"/>
+      <c r="Y1" s="987"/>
+      <c r="Z1" s="987"/>
+      <c r="AA1" s="987"/>
+      <c r="AB1" s="987"/>
+      <c r="AC1" s="987"/>
+      <c r="AD1" s="987"/>
+      <c r="AE1" s="987"/>
+      <c r="AF1" s="987"/>
+      <c r="AG1" s="987"/>
+      <c r="AH1" s="987"/>
+      <c r="AI1" s="988"/>
     </row>
     <row r="2" spans="1:36" ht="4.5" customHeight="1" thickBot="1">
-      <c r="A2" s="949"/>
-      <c r="B2" s="804"/>
-      <c r="C2" s="804"/>
-      <c r="D2" s="804"/>
-      <c r="E2" s="804"/>
-      <c r="F2" s="804"/>
-      <c r="G2" s="804"/>
-      <c r="H2" s="804"/>
-      <c r="I2" s="804"/>
-      <c r="J2" s="804"/>
-      <c r="K2" s="804"/>
-      <c r="L2" s="804"/>
-      <c r="M2" s="804"/>
-      <c r="N2" s="804"/>
-      <c r="O2" s="804"/>
-      <c r="P2" s="804"/>
-      <c r="Q2" s="804"/>
-      <c r="R2" s="804"/>
-      <c r="S2" s="804"/>
-      <c r="T2" s="804"/>
-      <c r="U2" s="804"/>
-      <c r="V2" s="804"/>
-      <c r="W2" s="804"/>
-      <c r="X2" s="804"/>
-      <c r="Y2" s="804"/>
-      <c r="Z2" s="804"/>
-      <c r="AA2" s="804"/>
-      <c r="AB2" s="804"/>
-      <c r="AC2" s="804"/>
-      <c r="AD2" s="804"/>
-      <c r="AE2" s="804"/>
-      <c r="AF2" s="804"/>
-      <c r="AG2" s="804"/>
-      <c r="AH2" s="804"/>
-      <c r="AI2" s="805"/>
+      <c r="A2" s="1004"/>
+      <c r="B2" s="839"/>
+      <c r="C2" s="839"/>
+      <c r="D2" s="839"/>
+      <c r="E2" s="839"/>
+      <c r="F2" s="839"/>
+      <c r="G2" s="839"/>
+      <c r="H2" s="839"/>
+      <c r="I2" s="839"/>
+      <c r="J2" s="839"/>
+      <c r="K2" s="839"/>
+      <c r="L2" s="839"/>
+      <c r="M2" s="839"/>
+      <c r="N2" s="839"/>
+      <c r="O2" s="839"/>
+      <c r="P2" s="839"/>
+      <c r="Q2" s="839"/>
+      <c r="R2" s="839"/>
+      <c r="S2" s="839"/>
+      <c r="T2" s="839"/>
+      <c r="U2" s="839"/>
+      <c r="V2" s="839"/>
+      <c r="W2" s="839"/>
+      <c r="X2" s="839"/>
+      <c r="Y2" s="839"/>
+      <c r="Z2" s="839"/>
+      <c r="AA2" s="839"/>
+      <c r="AB2" s="839"/>
+      <c r="AC2" s="839"/>
+      <c r="AD2" s="839"/>
+      <c r="AE2" s="839"/>
+      <c r="AF2" s="839"/>
+      <c r="AG2" s="839"/>
+      <c r="AH2" s="839"/>
+      <c r="AI2" s="840"/>
     </row>
     <row r="3" spans="1:36" ht="15.75">
-      <c r="A3" s="965" t="s">
+      <c r="A3" s="1020" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="966"/>
-      <c r="C3" s="966"/>
-      <c r="D3" s="966"/>
-      <c r="E3" s="966"/>
-      <c r="F3" s="966"/>
-      <c r="G3" s="966"/>
-      <c r="H3" s="966"/>
-      <c r="I3" s="966"/>
-      <c r="J3" s="966"/>
-      <c r="K3" s="966"/>
-      <c r="L3" s="966"/>
-      <c r="M3" s="966"/>
-      <c r="N3" s="966"/>
-      <c r="O3" s="966"/>
-      <c r="P3" s="966"/>
-      <c r="Q3" s="966"/>
-      <c r="R3" s="966"/>
-      <c r="S3" s="966"/>
-      <c r="T3" s="966"/>
-      <c r="U3" s="966"/>
-      <c r="V3" s="966"/>
-      <c r="W3" s="966"/>
-      <c r="X3" s="966"/>
-      <c r="Y3" s="966"/>
-      <c r="Z3" s="966"/>
-      <c r="AA3" s="966"/>
-      <c r="AB3" s="966"/>
-      <c r="AC3" s="966"/>
-      <c r="AD3" s="966"/>
-      <c r="AE3" s="966"/>
-      <c r="AF3" s="966"/>
-      <c r="AG3" s="966"/>
-      <c r="AH3" s="966"/>
-      <c r="AI3" s="967"/>
+      <c r="B3" s="1021"/>
+      <c r="C3" s="1021"/>
+      <c r="D3" s="1021"/>
+      <c r="E3" s="1021"/>
+      <c r="F3" s="1021"/>
+      <c r="G3" s="1021"/>
+      <c r="H3" s="1021"/>
+      <c r="I3" s="1021"/>
+      <c r="J3" s="1021"/>
+      <c r="K3" s="1021"/>
+      <c r="L3" s="1021"/>
+      <c r="M3" s="1021"/>
+      <c r="N3" s="1021"/>
+      <c r="O3" s="1021"/>
+      <c r="P3" s="1021"/>
+      <c r="Q3" s="1021"/>
+      <c r="R3" s="1021"/>
+      <c r="S3" s="1021"/>
+      <c r="T3" s="1021"/>
+      <c r="U3" s="1021"/>
+      <c r="V3" s="1021"/>
+      <c r="W3" s="1021"/>
+      <c r="X3" s="1021"/>
+      <c r="Y3" s="1021"/>
+      <c r="Z3" s="1021"/>
+      <c r="AA3" s="1021"/>
+      <c r="AB3" s="1021"/>
+      <c r="AC3" s="1021"/>
+      <c r="AD3" s="1021"/>
+      <c r="AE3" s="1021"/>
+      <c r="AF3" s="1021"/>
+      <c r="AG3" s="1021"/>
+      <c r="AH3" s="1021"/>
+      <c r="AI3" s="1022"/>
       <c r="AJ3" s="98"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A4" s="962" t="s">
+      <c r="A4" s="1017" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="963"/>
-      <c r="C4" s="963"/>
-      <c r="D4" s="963"/>
-      <c r="E4" s="963"/>
-      <c r="F4" s="963"/>
-      <c r="G4" s="963"/>
-      <c r="H4" s="963"/>
-      <c r="I4" s="963"/>
-      <c r="J4" s="963"/>
-      <c r="K4" s="963"/>
-      <c r="L4" s="963"/>
-      <c r="M4" s="963"/>
-      <c r="N4" s="963"/>
-      <c r="O4" s="963"/>
-      <c r="P4" s="963"/>
-      <c r="Q4" s="963"/>
-      <c r="R4" s="963"/>
-      <c r="S4" s="963"/>
-      <c r="T4" s="963"/>
-      <c r="U4" s="963"/>
-      <c r="V4" s="963"/>
-      <c r="W4" s="963"/>
-      <c r="X4" s="963"/>
-      <c r="Y4" s="963"/>
-      <c r="Z4" s="963"/>
-      <c r="AA4" s="963"/>
-      <c r="AB4" s="963"/>
-      <c r="AC4" s="963"/>
-      <c r="AD4" s="963"/>
-      <c r="AE4" s="963"/>
-      <c r="AF4" s="963"/>
-      <c r="AG4" s="963"/>
-      <c r="AH4" s="963"/>
-      <c r="AI4" s="964"/>
+      <c r="B4" s="1018"/>
+      <c r="C4" s="1018"/>
+      <c r="D4" s="1018"/>
+      <c r="E4" s="1018"/>
+      <c r="F4" s="1018"/>
+      <c r="G4" s="1018"/>
+      <c r="H4" s="1018"/>
+      <c r="I4" s="1018"/>
+      <c r="J4" s="1018"/>
+      <c r="K4" s="1018"/>
+      <c r="L4" s="1018"/>
+      <c r="M4" s="1018"/>
+      <c r="N4" s="1018"/>
+      <c r="O4" s="1018"/>
+      <c r="P4" s="1018"/>
+      <c r="Q4" s="1018"/>
+      <c r="R4" s="1018"/>
+      <c r="S4" s="1018"/>
+      <c r="T4" s="1018"/>
+      <c r="U4" s="1018"/>
+      <c r="V4" s="1018"/>
+      <c r="W4" s="1018"/>
+      <c r="X4" s="1018"/>
+      <c r="Y4" s="1018"/>
+      <c r="Z4" s="1018"/>
+      <c r="AA4" s="1018"/>
+      <c r="AB4" s="1018"/>
+      <c r="AC4" s="1018"/>
+      <c r="AD4" s="1018"/>
+      <c r="AE4" s="1018"/>
+      <c r="AF4" s="1018"/>
+      <c r="AG4" s="1018"/>
+      <c r="AH4" s="1018"/>
+      <c r="AI4" s="1019"/>
     </row>
     <row r="5" spans="1:36" ht="11.25" customHeight="1" thickBot="1">
       <c r="A5" s="230"/>
@@ -40694,44 +40694,44 @@
       <c r="A6" s="136"/>
       <c r="C6" s="151"/>
       <c r="D6" s="124"/>
-      <c r="E6" s="977" t="s">
+      <c r="E6" s="1032" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="978"/>
-      <c r="G6" s="979"/>
+      <c r="F6" s="1033"/>
+      <c r="G6" s="1034"/>
       <c r="H6" s="354"/>
       <c r="I6" s="229"/>
-      <c r="J6" s="950" t="s">
+      <c r="J6" s="1005" t="s">
         <v>92</v>
       </c>
-      <c r="K6" s="951"/>
-      <c r="L6" s="952"/>
+      <c r="K6" s="1006"/>
+      <c r="L6" s="1007"/>
       <c r="M6" s="357"/>
       <c r="N6" s="229"/>
       <c r="O6" s="360"/>
       <c r="P6" s="360"/>
-      <c r="Q6" s="971" t="s">
+      <c r="Q6" s="1026" t="s">
         <v>93</v>
       </c>
-      <c r="R6" s="972"/>
+      <c r="R6" s="1027"/>
       <c r="S6" s="358"/>
       <c r="T6" s="229"/>
       <c r="U6" s="360"/>
       <c r="V6" s="360"/>
-      <c r="W6" s="950" t="s">
+      <c r="W6" s="1005" t="s">
         <v>104</v>
       </c>
-      <c r="X6" s="951"/>
-      <c r="Y6" s="951"/>
-      <c r="Z6" s="952"/>
+      <c r="X6" s="1006"/>
+      <c r="Y6" s="1006"/>
+      <c r="Z6" s="1007"/>
       <c r="AA6" s="396"/>
       <c r="AB6" s="229"/>
       <c r="AC6" s="360"/>
-      <c r="AD6" s="943" t="s">
+      <c r="AD6" s="998" t="s">
         <v>94</v>
       </c>
-      <c r="AE6" s="944"/>
-      <c r="AF6" s="945"/>
+      <c r="AE6" s="999"/>
+      <c r="AF6" s="1000"/>
       <c r="AG6" s="136"/>
       <c r="AH6" s="384"/>
       <c r="AI6" s="404"/>
@@ -40740,34 +40740,34 @@
       <c r="A7" s="136"/>
       <c r="B7" s="100"/>
       <c r="C7" s="23"/>
-      <c r="E7" s="980"/>
-      <c r="F7" s="981"/>
-      <c r="G7" s="982"/>
+      <c r="E7" s="1035"/>
+      <c r="F7" s="1036"/>
+      <c r="G7" s="1037"/>
       <c r="H7" s="354"/>
       <c r="I7" s="233"/>
-      <c r="J7" s="968"/>
-      <c r="K7" s="969"/>
-      <c r="L7" s="970"/>
+      <c r="J7" s="1023"/>
+      <c r="K7" s="1024"/>
+      <c r="L7" s="1025"/>
       <c r="M7" s="357"/>
       <c r="N7" s="233"/>
       <c r="O7" s="352"/>
       <c r="P7" s="359"/>
-      <c r="Q7" s="873"/>
-      <c r="R7" s="973"/>
+      <c r="Q7" s="874"/>
+      <c r="R7" s="1028"/>
       <c r="S7" s="358"/>
       <c r="T7" s="233"/>
       <c r="U7" s="352"/>
       <c r="V7" s="359"/>
-      <c r="W7" s="953"/>
-      <c r="X7" s="954"/>
-      <c r="Y7" s="954"/>
-      <c r="Z7" s="955"/>
+      <c r="W7" s="1008"/>
+      <c r="X7" s="1009"/>
+      <c r="Y7" s="1009"/>
+      <c r="Z7" s="1010"/>
       <c r="AA7" s="396"/>
       <c r="AB7" s="233"/>
       <c r="AC7" s="352"/>
-      <c r="AD7" s="946"/>
-      <c r="AE7" s="947"/>
-      <c r="AF7" s="948"/>
+      <c r="AD7" s="1001"/>
+      <c r="AE7" s="1002"/>
+      <c r="AF7" s="1003"/>
       <c r="AG7" s="136"/>
       <c r="AH7" s="384"/>
       <c r="AI7" s="404"/>
@@ -40776,44 +40776,44 @@
       <c r="A8" s="136"/>
       <c r="B8" s="361"/>
       <c r="C8" s="206"/>
-      <c r="E8" s="956">
+      <c r="E8" s="1011">
         <v>64</v>
       </c>
-      <c r="F8" s="957"/>
-      <c r="G8" s="983"/>
+      <c r="F8" s="1012"/>
+      <c r="G8" s="1038"/>
       <c r="H8" s="152"/>
       <c r="I8" s="136"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="987">
+      <c r="K8" s="1042">
         <v>16</v>
       </c>
-      <c r="L8" s="988"/>
+      <c r="L8" s="1043"/>
       <c r="M8" s="357"/>
       <c r="N8" s="136"/>
       <c r="O8" s="79"/>
-      <c r="P8" s="956">
+      <c r="P8" s="1011">
         <v>10</v>
       </c>
-      <c r="Q8" s="957"/>
-      <c r="R8" s="958"/>
+      <c r="Q8" s="1012"/>
+      <c r="R8" s="1013"/>
       <c r="S8" s="358"/>
       <c r="T8" s="136"/>
       <c r="U8" s="79"/>
-      <c r="V8" s="956">
+      <c r="V8" s="1011">
         <v>38</v>
       </c>
-      <c r="W8" s="957"/>
-      <c r="X8" s="957"/>
-      <c r="Y8" s="957"/>
-      <c r="Z8" s="958"/>
+      <c r="W8" s="1012"/>
+      <c r="X8" s="1012"/>
+      <c r="Y8" s="1012"/>
+      <c r="Z8" s="1013"/>
       <c r="AA8" s="397"/>
       <c r="AB8" s="136"/>
       <c r="AC8" s="79"/>
-      <c r="AD8" s="956">
+      <c r="AD8" s="1011">
         <v>20</v>
       </c>
-      <c r="AE8" s="957"/>
-      <c r="AF8" s="958"/>
+      <c r="AE8" s="1012"/>
+      <c r="AF8" s="1013"/>
       <c r="AG8" s="136"/>
       <c r="AH8" s="385"/>
       <c r="AI8" s="232"/>
@@ -40823,33 +40823,33 @@
       <c r="B9" s="100"/>
       <c r="C9" s="144"/>
       <c r="D9" s="350"/>
-      <c r="E9" s="984"/>
-      <c r="F9" s="985"/>
-      <c r="G9" s="986"/>
+      <c r="E9" s="1039"/>
+      <c r="F9" s="1040"/>
+      <c r="G9" s="1041"/>
       <c r="I9" s="137"/>
       <c r="J9" s="351"/>
-      <c r="K9" s="989"/>
-      <c r="L9" s="990"/>
+      <c r="K9" s="1044"/>
+      <c r="L9" s="1045"/>
       <c r="M9" s="358"/>
       <c r="N9" s="137"/>
       <c r="O9" s="351"/>
-      <c r="P9" s="959"/>
-      <c r="Q9" s="960"/>
-      <c r="R9" s="961"/>
+      <c r="P9" s="1014"/>
+      <c r="Q9" s="1015"/>
+      <c r="R9" s="1016"/>
       <c r="S9" s="358"/>
       <c r="T9" s="137"/>
       <c r="U9" s="351"/>
-      <c r="V9" s="959"/>
-      <c r="W9" s="960"/>
-      <c r="X9" s="960"/>
-      <c r="Y9" s="960"/>
-      <c r="Z9" s="961"/>
+      <c r="V9" s="1014"/>
+      <c r="W9" s="1015"/>
+      <c r="X9" s="1015"/>
+      <c r="Y9" s="1015"/>
+      <c r="Z9" s="1016"/>
       <c r="AA9" s="397"/>
       <c r="AB9" s="137"/>
       <c r="AC9" s="351"/>
-      <c r="AD9" s="959"/>
-      <c r="AE9" s="960"/>
-      <c r="AF9" s="961"/>
+      <c r="AD9" s="1014"/>
+      <c r="AE9" s="1015"/>
+      <c r="AF9" s="1016"/>
       <c r="AG9" s="398"/>
       <c r="AH9" s="385"/>
       <c r="AI9" s="165"/>
@@ -40905,23 +40905,23 @@
       <c r="M11" s="148"/>
       <c r="N11" s="148"/>
       <c r="O11" s="82"/>
-      <c r="Q11" s="896" t="s">
+      <c r="Q11" s="1052" t="s">
         <v>163</v>
       </c>
-      <c r="R11" s="897"/>
-      <c r="S11" s="897"/>
-      <c r="T11" s="897"/>
-      <c r="U11" s="897"/>
-      <c r="V11" s="897"/>
-      <c r="W11" s="897"/>
-      <c r="X11" s="897"/>
-      <c r="Y11" s="897"/>
-      <c r="Z11" s="897"/>
-      <c r="AA11" s="897"/>
-      <c r="AB11" s="897"/>
-      <c r="AC11" s="897"/>
-      <c r="AD11" s="897"/>
-      <c r="AE11" s="897"/>
+      <c r="R11" s="1053"/>
+      <c r="S11" s="1053"/>
+      <c r="T11" s="1053"/>
+      <c r="U11" s="1053"/>
+      <c r="V11" s="1053"/>
+      <c r="W11" s="1053"/>
+      <c r="X11" s="1053"/>
+      <c r="Y11" s="1053"/>
+      <c r="Z11" s="1053"/>
+      <c r="AA11" s="1053"/>
+      <c r="AB11" s="1053"/>
+      <c r="AC11" s="1053"/>
+      <c r="AD11" s="1053"/>
+      <c r="AE11" s="1053"/>
       <c r="AF11" s="436">
         <v>2025</v>
       </c>
@@ -40931,25 +40931,25 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1">
       <c r="A12" s="405"/>
-      <c r="B12" s="910" t="s">
+      <c r="B12" s="1062" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="911"/>
-      <c r="D12" s="911"/>
-      <c r="E12" s="912"/>
-      <c r="F12" s="900" t="s">
+      <c r="C12" s="1063"/>
+      <c r="D12" s="1063"/>
+      <c r="E12" s="1064"/>
+      <c r="F12" s="1055" t="s">
         <v>151</v>
       </c>
-      <c r="G12" s="901"/>
-      <c r="H12" s="901"/>
-      <c r="I12" s="901"/>
-      <c r="J12" s="901"/>
-      <c r="K12" s="901"/>
-      <c r="L12" s="901"/>
-      <c r="M12" s="900" t="s">
+      <c r="G12" s="1056"/>
+      <c r="H12" s="1056"/>
+      <c r="I12" s="1056"/>
+      <c r="J12" s="1056"/>
+      <c r="K12" s="1056"/>
+      <c r="L12" s="1056"/>
+      <c r="M12" s="1055" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="904"/>
+      <c r="N12" s="1059"/>
       <c r="O12" s="364"/>
       <c r="P12" s="79"/>
       <c r="Q12" s="434"/>
@@ -41002,19 +41002,19 @@
     </row>
     <row r="13" spans="1:36" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="230"/>
-      <c r="B13" s="913"/>
-      <c r="C13" s="914"/>
-      <c r="D13" s="914"/>
-      <c r="E13" s="915"/>
-      <c r="F13" s="902"/>
-      <c r="G13" s="903"/>
-      <c r="H13" s="903"/>
-      <c r="I13" s="903"/>
-      <c r="J13" s="903"/>
-      <c r="K13" s="903"/>
-      <c r="L13" s="903"/>
-      <c r="M13" s="905"/>
-      <c r="N13" s="906"/>
+      <c r="B13" s="1065"/>
+      <c r="C13" s="1066"/>
+      <c r="D13" s="1066"/>
+      <c r="E13" s="1067"/>
+      <c r="F13" s="1057"/>
+      <c r="G13" s="1058"/>
+      <c r="H13" s="1058"/>
+      <c r="I13" s="1058"/>
+      <c r="J13" s="1058"/>
+      <c r="K13" s="1058"/>
+      <c r="L13" s="1058"/>
+      <c r="M13" s="1060"/>
+      <c r="N13" s="1061"/>
       <c r="O13" s="364"/>
       <c r="P13" s="79"/>
       <c r="Q13" s="419"/>
@@ -41081,25 +41081,25 @@
     </row>
     <row r="14" spans="1:36" ht="13.5" customHeight="1">
       <c r="A14" s="405"/>
-      <c r="B14" s="913"/>
-      <c r="C14" s="914"/>
-      <c r="D14" s="914"/>
-      <c r="E14" s="915"/>
-      <c r="F14" s="919" t="s">
+      <c r="B14" s="1065"/>
+      <c r="C14" s="1066"/>
+      <c r="D14" s="1066"/>
+      <c r="E14" s="1067"/>
+      <c r="F14" s="1071" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="920"/>
-      <c r="H14" s="923" t="s">
+      <c r="G14" s="1072"/>
+      <c r="H14" s="1075" t="s">
         <v>153</v>
       </c>
-      <c r="I14" s="924"/>
-      <c r="J14" s="927" t="s">
+      <c r="I14" s="1076"/>
+      <c r="J14" s="1079" t="s">
         <v>154</v>
       </c>
-      <c r="K14" s="928"/>
-      <c r="L14" s="928"/>
-      <c r="M14" s="905"/>
-      <c r="N14" s="906"/>
+      <c r="K14" s="1080"/>
+      <c r="L14" s="1080"/>
+      <c r="M14" s="1060"/>
+      <c r="N14" s="1061"/>
       <c r="O14" s="364"/>
       <c r="P14" s="79"/>
       <c r="Q14" s="419"/>
@@ -41168,19 +41168,19 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1">
       <c r="A15" s="405"/>
-      <c r="B15" s="916"/>
-      <c r="C15" s="917"/>
-      <c r="D15" s="917"/>
-      <c r="E15" s="918"/>
-      <c r="F15" s="921"/>
-      <c r="G15" s="922"/>
-      <c r="H15" s="925"/>
-      <c r="I15" s="926"/>
-      <c r="J15" s="927"/>
-      <c r="K15" s="928"/>
-      <c r="L15" s="928"/>
-      <c r="M15" s="905"/>
-      <c r="N15" s="906"/>
+      <c r="B15" s="1068"/>
+      <c r="C15" s="1069"/>
+      <c r="D15" s="1069"/>
+      <c r="E15" s="1070"/>
+      <c r="F15" s="1073"/>
+      <c r="G15" s="1074"/>
+      <c r="H15" s="1077"/>
+      <c r="I15" s="1078"/>
+      <c r="J15" s="1079"/>
+      <c r="K15" s="1080"/>
+      <c r="L15" s="1080"/>
+      <c r="M15" s="1060"/>
+      <c r="N15" s="1061"/>
       <c r="P15" s="79"/>
       <c r="Q15" s="419"/>
       <c r="R15" s="409"/>
@@ -41246,12 +41246,12 @@
     </row>
     <row r="16" spans="1:36" ht="15.75">
       <c r="A16" s="230"/>
-      <c r="B16" s="907" t="s">
+      <c r="B16" s="1046" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="908"/>
-      <c r="D16" s="908"/>
-      <c r="E16" s="908"/>
+      <c r="C16" s="1047"/>
+      <c r="D16" s="1047"/>
+      <c r="E16" s="1047"/>
       <c r="F16" s="795">
         <v>2</v>
       </c>
@@ -41268,7 +41268,7 @@
       <c r="M16" s="795">
         <v>16</v>
       </c>
-      <c r="N16" s="909"/>
+      <c r="N16" s="1051"/>
       <c r="O16" s="364"/>
       <c r="P16" s="79"/>
       <c r="Q16" s="419"/>
@@ -41293,12 +41293,12 @@
     </row>
     <row r="17" spans="1:36" ht="15.75">
       <c r="A17" s="405"/>
-      <c r="B17" s="907" t="s">
+      <c r="B17" s="1046" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="908"/>
-      <c r="D17" s="908"/>
-      <c r="E17" s="908"/>
+      <c r="C17" s="1047"/>
+      <c r="D17" s="1047"/>
+      <c r="E17" s="1047"/>
       <c r="F17" s="795">
         <v>0</v>
       </c>
@@ -41315,7 +41315,7 @@
       <c r="M17" s="795">
         <v>10</v>
       </c>
-      <c r="N17" s="909"/>
+      <c r="N17" s="1051"/>
       <c r="O17" s="116"/>
       <c r="P17" s="79"/>
       <c r="Q17" s="416"/>
@@ -41382,29 +41382,29 @@
     </row>
     <row r="18" spans="1:36" ht="16.5" thickBot="1">
       <c r="A18" s="230"/>
-      <c r="B18" s="991" t="s">
+      <c r="B18" s="1048" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="992"/>
-      <c r="D18" s="992"/>
-      <c r="E18" s="992"/>
-      <c r="F18" s="898">
+      <c r="C18" s="1049"/>
+      <c r="D18" s="1049"/>
+      <c r="E18" s="1049"/>
+      <c r="F18" s="1050">
         <v>10</v>
       </c>
-      <c r="G18" s="898"/>
-      <c r="H18" s="898">
+      <c r="G18" s="1050"/>
+      <c r="H18" s="1050">
         <v>38</v>
       </c>
-      <c r="I18" s="898"/>
-      <c r="J18" s="974">
+      <c r="I18" s="1050"/>
+      <c r="J18" s="1029">
         <v>25</v>
       </c>
-      <c r="K18" s="975"/>
-      <c r="L18" s="976"/>
-      <c r="M18" s="898">
+      <c r="K18" s="1030"/>
+      <c r="L18" s="1031"/>
+      <c r="M18" s="1050">
         <v>38</v>
       </c>
-      <c r="N18" s="899"/>
+      <c r="N18" s="1054"/>
       <c r="O18" s="155"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="419"/>
@@ -41950,15 +41950,15 @@
       <c r="M27" s="82"/>
       <c r="N27" s="82"/>
       <c r="P27" s="390"/>
-      <c r="Q27" s="932" t="s">
+      <c r="Q27" s="989" t="s">
         <v>157</v>
       </c>
-      <c r="R27" s="933"/>
-      <c r="S27" s="933"/>
-      <c r="T27" s="933"/>
-      <c r="U27" s="933"/>
-      <c r="V27" s="933"/>
-      <c r="W27" s="934"/>
+      <c r="R27" s="990"/>
+      <c r="S27" s="990"/>
+      <c r="T27" s="990"/>
+      <c r="U27" s="990"/>
+      <c r="V27" s="990"/>
+      <c r="W27" s="991"/>
       <c r="X27" s="394"/>
       <c r="Y27" s="386"/>
       <c r="Z27" s="227"/>
@@ -42030,11 +42030,11 @@
       <c r="Q29" s="387"/>
       <c r="R29" s="193"/>
       <c r="S29" s="193"/>
-      <c r="T29" s="937" t="s">
+      <c r="T29" s="992" t="s">
         <v>156</v>
       </c>
-      <c r="U29" s="938"/>
-      <c r="V29" s="939"/>
+      <c r="U29" s="993"/>
+      <c r="V29" s="994"/>
       <c r="W29" s="400"/>
       <c r="X29" s="387"/>
       <c r="Y29" s="193"/>
@@ -42065,29 +42065,29 @@
       <c r="M30" s="82"/>
       <c r="N30" s="82"/>
       <c r="O30" s="88"/>
-      <c r="Q30" s="935" t="s">
+      <c r="Q30" s="920" t="s">
         <v>50</v>
       </c>
-      <c r="R30" s="936"/>
-      <c r="S30" s="936"/>
-      <c r="T30" s="940"/>
-      <c r="U30" s="941"/>
-      <c r="V30" s="942"/>
-      <c r="W30" s="935" t="s">
+      <c r="R30" s="921"/>
+      <c r="S30" s="921"/>
+      <c r="T30" s="995"/>
+      <c r="U30" s="996"/>
+      <c r="V30" s="997"/>
+      <c r="W30" s="920" t="s">
         <v>51</v>
       </c>
-      <c r="X30" s="936"/>
-      <c r="Y30" s="936"/>
-      <c r="Z30" s="1015" t="s">
+      <c r="X30" s="921"/>
+      <c r="Y30" s="921"/>
+      <c r="Z30" s="976" t="s">
         <v>52</v>
       </c>
-      <c r="AA30" s="936"/>
-      <c r="AB30" s="1024"/>
-      <c r="AC30" s="1015" t="s">
+      <c r="AA30" s="921"/>
+      <c r="AB30" s="981"/>
+      <c r="AC30" s="976" t="s">
         <v>53</v>
       </c>
-      <c r="AD30" s="936"/>
-      <c r="AE30" s="1016"/>
+      <c r="AD30" s="921"/>
+      <c r="AE30" s="977"/>
       <c r="AF30" s="388"/>
       <c r="AG30" s="227"/>
       <c r="AH30" s="82"/>
@@ -42110,21 +42110,21 @@
       <c r="N31" s="82"/>
       <c r="O31" s="83"/>
       <c r="P31" s="103"/>
-      <c r="Q31" s="1062"/>
-      <c r="R31" s="1063"/>
-      <c r="S31" s="1064"/>
-      <c r="T31" s="1065"/>
-      <c r="U31" s="1066"/>
-      <c r="V31" s="1067"/>
-      <c r="W31" s="1051"/>
-      <c r="X31" s="1052"/>
-      <c r="Y31" s="1052"/>
-      <c r="Z31" s="1017"/>
-      <c r="AA31" s="1018"/>
-      <c r="AB31" s="1025"/>
-      <c r="AC31" s="1017"/>
-      <c r="AD31" s="1018"/>
-      <c r="AE31" s="1019"/>
+      <c r="Q31" s="938"/>
+      <c r="R31" s="939"/>
+      <c r="S31" s="940"/>
+      <c r="T31" s="947"/>
+      <c r="U31" s="948"/>
+      <c r="V31" s="949"/>
+      <c r="W31" s="922"/>
+      <c r="X31" s="923"/>
+      <c r="Y31" s="923"/>
+      <c r="Z31" s="978"/>
+      <c r="AA31" s="979"/>
+      <c r="AB31" s="982"/>
+      <c r="AC31" s="978"/>
+      <c r="AD31" s="979"/>
+      <c r="AE31" s="980"/>
       <c r="AF31" s="389"/>
       <c r="AG31" s="82"/>
       <c r="AH31" s="82"/>
@@ -42147,21 +42147,21 @@
       <c r="N32" s="90"/>
       <c r="O32" s="83"/>
       <c r="P32" s="79"/>
-      <c r="Q32" s="1002"/>
-      <c r="R32" s="1003"/>
-      <c r="S32" s="1004"/>
-      <c r="T32" s="1012"/>
-      <c r="U32" s="1013"/>
-      <c r="V32" s="1014"/>
-      <c r="W32" s="1010"/>
-      <c r="X32" s="1011"/>
-      <c r="Y32" s="1011"/>
-      <c r="Z32" s="1020"/>
-      <c r="AA32" s="1021"/>
-      <c r="AB32" s="1026"/>
-      <c r="AC32" s="1020"/>
-      <c r="AD32" s="1021"/>
-      <c r="AE32" s="1022"/>
+      <c r="Q32" s="941"/>
+      <c r="R32" s="942"/>
+      <c r="S32" s="943"/>
+      <c r="T32" s="931"/>
+      <c r="U32" s="932"/>
+      <c r="V32" s="933"/>
+      <c r="W32" s="924"/>
+      <c r="X32" s="925"/>
+      <c r="Y32" s="925"/>
+      <c r="Z32" s="961"/>
+      <c r="AA32" s="962"/>
+      <c r="AB32" s="973"/>
+      <c r="AC32" s="961"/>
+      <c r="AD32" s="962"/>
+      <c r="AE32" s="963"/>
       <c r="AF32" s="80"/>
       <c r="AG32" s="82"/>
       <c r="AH32" s="82"/>
@@ -42169,42 +42169,42 @@
     </row>
     <row r="33" spans="1:35" ht="19.5" thickBot="1">
       <c r="A33" s="230"/>
-      <c r="B33" s="1031" t="s">
+      <c r="B33" s="912" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="1032"/>
-      <c r="D33" s="1032"/>
-      <c r="E33" s="1033"/>
-      <c r="F33" s="1078" t="s">
+      <c r="C33" s="954"/>
+      <c r="D33" s="954"/>
+      <c r="E33" s="913"/>
+      <c r="F33" s="909" t="s">
         <v>159</v>
       </c>
-      <c r="G33" s="1079"/>
-      <c r="H33" s="1079"/>
-      <c r="I33" s="1079"/>
-      <c r="J33" s="1079"/>
-      <c r="K33" s="1079"/>
-      <c r="L33" s="1080"/>
-      <c r="M33" s="1031" t="s">
+      <c r="G33" s="910"/>
+      <c r="H33" s="910"/>
+      <c r="I33" s="910"/>
+      <c r="J33" s="910"/>
+      <c r="K33" s="910"/>
+      <c r="L33" s="911"/>
+      <c r="M33" s="912" t="s">
         <v>88</v>
       </c>
-      <c r="N33" s="1033"/>
+      <c r="N33" s="913"/>
       <c r="O33" s="78"/>
       <c r="P33" s="103"/>
-      <c r="Q33" s="1002"/>
-      <c r="R33" s="1003"/>
-      <c r="S33" s="1004"/>
-      <c r="T33" s="1012"/>
-      <c r="U33" s="1013"/>
-      <c r="V33" s="1014"/>
-      <c r="W33" s="1010"/>
-      <c r="X33" s="1011"/>
-      <c r="Y33" s="1011"/>
-      <c r="Z33" s="1020"/>
-      <c r="AA33" s="1021"/>
-      <c r="AB33" s="1026"/>
-      <c r="AC33" s="1020"/>
-      <c r="AD33" s="1021"/>
-      <c r="AE33" s="1022"/>
+      <c r="Q33" s="941"/>
+      <c r="R33" s="942"/>
+      <c r="S33" s="943"/>
+      <c r="T33" s="931"/>
+      <c r="U33" s="932"/>
+      <c r="V33" s="933"/>
+      <c r="W33" s="924"/>
+      <c r="X33" s="925"/>
+      <c r="Y33" s="925"/>
+      <c r="Z33" s="961"/>
+      <c r="AA33" s="962"/>
+      <c r="AB33" s="973"/>
+      <c r="AC33" s="961"/>
+      <c r="AD33" s="962"/>
+      <c r="AE33" s="963"/>
       <c r="AF33" s="80"/>
       <c r="AG33" s="82"/>
       <c r="AH33" s="82"/>
@@ -42212,42 +42212,42 @@
     </row>
     <row r="34" spans="1:35" ht="30.75" customHeight="1" thickBot="1">
       <c r="A34" s="233"/>
-      <c r="B34" s="1034"/>
-      <c r="C34" s="1035"/>
-      <c r="D34" s="1035"/>
-      <c r="E34" s="1036"/>
-      <c r="F34" s="1037" t="s">
+      <c r="B34" s="914"/>
+      <c r="C34" s="955"/>
+      <c r="D34" s="955"/>
+      <c r="E34" s="915"/>
+      <c r="F34" s="956" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="1038"/>
-      <c r="H34" s="1039"/>
-      <c r="I34" s="1040" t="s">
+      <c r="G34" s="957"/>
+      <c r="H34" s="958"/>
+      <c r="I34" s="959" t="s">
         <v>161</v>
       </c>
-      <c r="J34" s="1041"/>
-      <c r="K34" s="1076" t="s">
+      <c r="J34" s="960"/>
+      <c r="K34" s="907" t="s">
         <v>162</v>
       </c>
-      <c r="L34" s="1077"/>
-      <c r="M34" s="1034"/>
-      <c r="N34" s="1036"/>
+      <c r="L34" s="908"/>
+      <c r="M34" s="914"/>
+      <c r="N34" s="915"/>
       <c r="O34" s="78"/>
       <c r="P34" s="103"/>
-      <c r="Q34" s="1002"/>
-      <c r="R34" s="1003"/>
-      <c r="S34" s="1004"/>
-      <c r="T34" s="1012"/>
-      <c r="U34" s="1013"/>
-      <c r="V34" s="1014"/>
-      <c r="W34" s="1010"/>
-      <c r="X34" s="1011"/>
-      <c r="Y34" s="1011"/>
-      <c r="Z34" s="1020"/>
-      <c r="AA34" s="1021"/>
-      <c r="AB34" s="1026"/>
-      <c r="AC34" s="1020"/>
-      <c r="AD34" s="1021"/>
-      <c r="AE34" s="1022"/>
+      <c r="Q34" s="941"/>
+      <c r="R34" s="942"/>
+      <c r="S34" s="943"/>
+      <c r="T34" s="931"/>
+      <c r="U34" s="932"/>
+      <c r="V34" s="933"/>
+      <c r="W34" s="924"/>
+      <c r="X34" s="925"/>
+      <c r="Y34" s="925"/>
+      <c r="Z34" s="961"/>
+      <c r="AA34" s="962"/>
+      <c r="AB34" s="973"/>
+      <c r="AC34" s="961"/>
+      <c r="AD34" s="962"/>
+      <c r="AE34" s="963"/>
       <c r="AF34" s="80"/>
       <c r="AG34" s="82"/>
       <c r="AH34" s="82"/>
@@ -42255,46 +42255,46 @@
     </row>
     <row r="35" spans="1:35" ht="22.5" customHeight="1">
       <c r="A35" s="407"/>
-      <c r="B35" s="1050" t="s">
+      <c r="B35" s="919" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="1050"/>
-      <c r="D35" s="1050"/>
-      <c r="E35" s="1050"/>
-      <c r="F35" s="1050">
+      <c r="C35" s="919"/>
+      <c r="D35" s="919"/>
+      <c r="E35" s="919"/>
+      <c r="F35" s="919">
         <v>4</v>
       </c>
-      <c r="G35" s="1050"/>
-      <c r="H35" s="1050"/>
-      <c r="I35" s="1050">
+      <c r="G35" s="919"/>
+      <c r="H35" s="919"/>
+      <c r="I35" s="919">
         <v>10</v>
       </c>
-      <c r="J35" s="1050"/>
-      <c r="K35" s="1050">
+      <c r="J35" s="919"/>
+      <c r="K35" s="919">
         <v>0</v>
       </c>
-      <c r="L35" s="1050"/>
-      <c r="M35" s="1050">
+      <c r="L35" s="919"/>
+      <c r="M35" s="919">
         <v>20</v>
       </c>
-      <c r="N35" s="1050"/>
+      <c r="N35" s="919"/>
       <c r="O35" s="83"/>
       <c r="P35" s="79"/>
-      <c r="Q35" s="999"/>
-      <c r="R35" s="1000"/>
-      <c r="S35" s="1001"/>
-      <c r="T35" s="1005"/>
-      <c r="U35" s="1006"/>
-      <c r="V35" s="1007"/>
-      <c r="W35" s="1008"/>
-      <c r="X35" s="1009"/>
-      <c r="Y35" s="1009"/>
-      <c r="Z35" s="993"/>
-      <c r="AA35" s="994"/>
-      <c r="AB35" s="1023"/>
-      <c r="AC35" s="993"/>
-      <c r="AD35" s="994"/>
-      <c r="AE35" s="995"/>
+      <c r="Q35" s="944"/>
+      <c r="R35" s="945"/>
+      <c r="S35" s="946"/>
+      <c r="T35" s="916"/>
+      <c r="U35" s="917"/>
+      <c r="V35" s="918"/>
+      <c r="W35" s="905"/>
+      <c r="X35" s="906"/>
+      <c r="Y35" s="906"/>
+      <c r="Z35" s="964"/>
+      <c r="AA35" s="965"/>
+      <c r="AB35" s="971"/>
+      <c r="AC35" s="964"/>
+      <c r="AD35" s="965"/>
+      <c r="AE35" s="966"/>
       <c r="AF35" s="80"/>
       <c r="AG35" s="82"/>
       <c r="AH35" s="82"/>
@@ -42312,21 +42312,21 @@
       <c r="M36" s="402"/>
       <c r="N36" s="401"/>
       <c r="O36" s="90"/>
-      <c r="Q36" s="999"/>
-      <c r="R36" s="1000"/>
-      <c r="S36" s="1001"/>
-      <c r="T36" s="1005"/>
-      <c r="U36" s="1006"/>
-      <c r="V36" s="1007"/>
-      <c r="W36" s="1008"/>
-      <c r="X36" s="1009"/>
-      <c r="Y36" s="1009"/>
-      <c r="Z36" s="993"/>
-      <c r="AA36" s="994"/>
-      <c r="AB36" s="1023"/>
-      <c r="AC36" s="993"/>
-      <c r="AD36" s="994"/>
-      <c r="AE36" s="995"/>
+      <c r="Q36" s="944"/>
+      <c r="R36" s="945"/>
+      <c r="S36" s="946"/>
+      <c r="T36" s="916"/>
+      <c r="U36" s="917"/>
+      <c r="V36" s="918"/>
+      <c r="W36" s="905"/>
+      <c r="X36" s="906"/>
+      <c r="Y36" s="906"/>
+      <c r="Z36" s="964"/>
+      <c r="AA36" s="965"/>
+      <c r="AB36" s="971"/>
+      <c r="AC36" s="964"/>
+      <c r="AD36" s="965"/>
+      <c r="AE36" s="966"/>
       <c r="AF36" s="80"/>
       <c r="AG36" s="82"/>
       <c r="AH36" s="82"/>
@@ -42349,21 +42349,21 @@
       <c r="N37" s="82"/>
       <c r="O37" s="80"/>
       <c r="P37" s="79"/>
-      <c r="Q37" s="999"/>
-      <c r="R37" s="1000"/>
-      <c r="S37" s="1001"/>
-      <c r="T37" s="1005"/>
-      <c r="U37" s="1006"/>
-      <c r="V37" s="1007"/>
-      <c r="W37" s="1008"/>
-      <c r="X37" s="1009"/>
-      <c r="Y37" s="1009"/>
-      <c r="Z37" s="993"/>
-      <c r="AA37" s="994"/>
-      <c r="AB37" s="1023"/>
-      <c r="AC37" s="993"/>
-      <c r="AD37" s="994"/>
-      <c r="AE37" s="995"/>
+      <c r="Q37" s="944"/>
+      <c r="R37" s="945"/>
+      <c r="S37" s="946"/>
+      <c r="T37" s="916"/>
+      <c r="U37" s="917"/>
+      <c r="V37" s="918"/>
+      <c r="W37" s="905"/>
+      <c r="X37" s="906"/>
+      <c r="Y37" s="906"/>
+      <c r="Z37" s="964"/>
+      <c r="AA37" s="965"/>
+      <c r="AB37" s="971"/>
+      <c r="AC37" s="964"/>
+      <c r="AD37" s="965"/>
+      <c r="AE37" s="966"/>
       <c r="AF37" s="80"/>
       <c r="AG37" s="82"/>
       <c r="AH37" s="82"/>
@@ -42386,21 +42386,21 @@
       <c r="N38" s="82"/>
       <c r="O38" s="80"/>
       <c r="P38" s="79"/>
-      <c r="Q38" s="999"/>
-      <c r="R38" s="1000"/>
-      <c r="S38" s="1001"/>
-      <c r="T38" s="1005"/>
-      <c r="U38" s="1006"/>
-      <c r="V38" s="1007"/>
-      <c r="W38" s="1008"/>
-      <c r="X38" s="1009"/>
-      <c r="Y38" s="1009"/>
-      <c r="Z38" s="993"/>
-      <c r="AA38" s="994"/>
-      <c r="AB38" s="1023"/>
-      <c r="AC38" s="993"/>
-      <c r="AD38" s="994"/>
-      <c r="AE38" s="995"/>
+      <c r="Q38" s="944"/>
+      <c r="R38" s="945"/>
+      <c r="S38" s="946"/>
+      <c r="T38" s="916"/>
+      <c r="U38" s="917"/>
+      <c r="V38" s="918"/>
+      <c r="W38" s="905"/>
+      <c r="X38" s="906"/>
+      <c r="Y38" s="906"/>
+      <c r="Z38" s="964"/>
+      <c r="AA38" s="965"/>
+      <c r="AB38" s="971"/>
+      <c r="AC38" s="964"/>
+      <c r="AD38" s="965"/>
+      <c r="AE38" s="966"/>
       <c r="AF38" s="105"/>
       <c r="AG38" s="104"/>
       <c r="AH38" s="82"/>
@@ -42422,21 +42422,21 @@
       <c r="M39" s="82"/>
       <c r="N39" s="82"/>
       <c r="P39" s="79"/>
-      <c r="Q39" s="999"/>
-      <c r="R39" s="1000"/>
-      <c r="S39" s="1001"/>
-      <c r="T39" s="1005"/>
-      <c r="U39" s="1006"/>
-      <c r="V39" s="1007"/>
-      <c r="W39" s="1008"/>
-      <c r="X39" s="1009"/>
-      <c r="Y39" s="1009"/>
-      <c r="Z39" s="993"/>
-      <c r="AA39" s="994"/>
-      <c r="AB39" s="1023"/>
-      <c r="AC39" s="993"/>
-      <c r="AD39" s="994"/>
-      <c r="AE39" s="995"/>
+      <c r="Q39" s="944"/>
+      <c r="R39" s="945"/>
+      <c r="S39" s="946"/>
+      <c r="T39" s="916"/>
+      <c r="U39" s="917"/>
+      <c r="V39" s="918"/>
+      <c r="W39" s="905"/>
+      <c r="X39" s="906"/>
+      <c r="Y39" s="906"/>
+      <c r="Z39" s="964"/>
+      <c r="AA39" s="965"/>
+      <c r="AB39" s="971"/>
+      <c r="AC39" s="964"/>
+      <c r="AD39" s="965"/>
+      <c r="AE39" s="966"/>
       <c r="AF39" s="80"/>
       <c r="AG39" s="82"/>
       <c r="AH39" s="82"/>
@@ -42459,21 +42459,21 @@
       <c r="N40" s="82"/>
       <c r="O40" s="83"/>
       <c r="P40" s="87"/>
-      <c r="Q40" s="999"/>
-      <c r="R40" s="1000"/>
-      <c r="S40" s="1001"/>
-      <c r="T40" s="1005"/>
-      <c r="U40" s="1006"/>
-      <c r="V40" s="1007"/>
-      <c r="W40" s="1008"/>
-      <c r="X40" s="1009"/>
-      <c r="Y40" s="1009"/>
-      <c r="Z40" s="993"/>
-      <c r="AA40" s="994"/>
-      <c r="AB40" s="1023"/>
-      <c r="AC40" s="993"/>
-      <c r="AD40" s="994"/>
-      <c r="AE40" s="995"/>
+      <c r="Q40" s="944"/>
+      <c r="R40" s="945"/>
+      <c r="S40" s="946"/>
+      <c r="T40" s="916"/>
+      <c r="U40" s="917"/>
+      <c r="V40" s="918"/>
+      <c r="W40" s="905"/>
+      <c r="X40" s="906"/>
+      <c r="Y40" s="906"/>
+      <c r="Z40" s="964"/>
+      <c r="AA40" s="965"/>
+      <c r="AB40" s="971"/>
+      <c r="AC40" s="964"/>
+      <c r="AD40" s="965"/>
+      <c r="AE40" s="966"/>
       <c r="AF40" s="80"/>
       <c r="AG40" s="82"/>
       <c r="AH40" s="82"/>
@@ -42496,21 +42496,21 @@
       <c r="N41" s="82"/>
       <c r="O41" s="78"/>
       <c r="P41" s="79"/>
-      <c r="Q41" s="1002"/>
-      <c r="R41" s="1003"/>
-      <c r="S41" s="1004"/>
-      <c r="T41" s="1012"/>
-      <c r="U41" s="1013"/>
-      <c r="V41" s="1014"/>
-      <c r="W41" s="1010"/>
-      <c r="X41" s="1011"/>
-      <c r="Y41" s="1011"/>
-      <c r="Z41" s="1020"/>
-      <c r="AA41" s="1021"/>
-      <c r="AB41" s="1026"/>
-      <c r="AC41" s="1020"/>
-      <c r="AD41" s="1021"/>
-      <c r="AE41" s="1022"/>
+      <c r="Q41" s="941"/>
+      <c r="R41" s="942"/>
+      <c r="S41" s="943"/>
+      <c r="T41" s="931"/>
+      <c r="U41" s="932"/>
+      <c r="V41" s="933"/>
+      <c r="W41" s="924"/>
+      <c r="X41" s="925"/>
+      <c r="Y41" s="925"/>
+      <c r="Z41" s="961"/>
+      <c r="AA41" s="962"/>
+      <c r="AB41" s="973"/>
+      <c r="AC41" s="961"/>
+      <c r="AD41" s="962"/>
+      <c r="AE41" s="963"/>
       <c r="AF41" s="80"/>
       <c r="AG41" s="82"/>
       <c r="AH41" s="82"/>
@@ -42533,21 +42533,21 @@
       <c r="N42" s="82"/>
       <c r="O42" s="80"/>
       <c r="P42" s="79"/>
-      <c r="Q42" s="1002"/>
-      <c r="R42" s="1003"/>
-      <c r="S42" s="1004"/>
-      <c r="T42" s="1012"/>
-      <c r="U42" s="1013"/>
-      <c r="V42" s="1014"/>
-      <c r="W42" s="1010"/>
-      <c r="X42" s="1011"/>
-      <c r="Y42" s="1011"/>
-      <c r="Z42" s="1020"/>
-      <c r="AA42" s="1021"/>
-      <c r="AB42" s="1026"/>
-      <c r="AC42" s="1020"/>
-      <c r="AD42" s="1021"/>
-      <c r="AE42" s="1022"/>
+      <c r="Q42" s="941"/>
+      <c r="R42" s="942"/>
+      <c r="S42" s="943"/>
+      <c r="T42" s="931"/>
+      <c r="U42" s="932"/>
+      <c r="V42" s="933"/>
+      <c r="W42" s="924"/>
+      <c r="X42" s="925"/>
+      <c r="Y42" s="925"/>
+      <c r="Z42" s="961"/>
+      <c r="AA42" s="962"/>
+      <c r="AB42" s="973"/>
+      <c r="AC42" s="961"/>
+      <c r="AD42" s="962"/>
+      <c r="AE42" s="963"/>
       <c r="AF42" s="80"/>
       <c r="AG42" s="82"/>
       <c r="AH42" s="82"/>
@@ -42569,21 +42569,21 @@
       <c r="M43" s="82"/>
       <c r="N43" s="82"/>
       <c r="P43" s="79"/>
-      <c r="Q43" s="996"/>
-      <c r="R43" s="997"/>
-      <c r="S43" s="998"/>
-      <c r="T43" s="1005"/>
-      <c r="U43" s="1006"/>
-      <c r="V43" s="1007"/>
-      <c r="W43" s="1008"/>
-      <c r="X43" s="1009"/>
-      <c r="Y43" s="1009"/>
-      <c r="Z43" s="993"/>
-      <c r="AA43" s="994"/>
-      <c r="AB43" s="1023"/>
-      <c r="AC43" s="993"/>
-      <c r="AD43" s="994"/>
-      <c r="AE43" s="995"/>
+      <c r="Q43" s="983"/>
+      <c r="R43" s="984"/>
+      <c r="S43" s="985"/>
+      <c r="T43" s="916"/>
+      <c r="U43" s="917"/>
+      <c r="V43" s="918"/>
+      <c r="W43" s="905"/>
+      <c r="X43" s="906"/>
+      <c r="Y43" s="906"/>
+      <c r="Z43" s="964"/>
+      <c r="AA43" s="965"/>
+      <c r="AB43" s="971"/>
+      <c r="AC43" s="964"/>
+      <c r="AD43" s="965"/>
+      <c r="AE43" s="966"/>
       <c r="AF43" s="80"/>
       <c r="AG43" s="82"/>
       <c r="AH43" s="82"/>
@@ -42606,21 +42606,21 @@
       <c r="N44" s="82"/>
       <c r="O44" s="78"/>
       <c r="P44" s="103"/>
-      <c r="Q44" s="996"/>
-      <c r="R44" s="997"/>
-      <c r="S44" s="998"/>
-      <c r="T44" s="1005"/>
-      <c r="U44" s="1006"/>
-      <c r="V44" s="1007"/>
-      <c r="W44" s="1008"/>
-      <c r="X44" s="1009"/>
-      <c r="Y44" s="1009"/>
-      <c r="Z44" s="993"/>
-      <c r="AA44" s="994"/>
-      <c r="AB44" s="1023"/>
-      <c r="AC44" s="993"/>
-      <c r="AD44" s="994"/>
-      <c r="AE44" s="995"/>
+      <c r="Q44" s="983"/>
+      <c r="R44" s="984"/>
+      <c r="S44" s="985"/>
+      <c r="T44" s="916"/>
+      <c r="U44" s="917"/>
+      <c r="V44" s="918"/>
+      <c r="W44" s="905"/>
+      <c r="X44" s="906"/>
+      <c r="Y44" s="906"/>
+      <c r="Z44" s="964"/>
+      <c r="AA44" s="965"/>
+      <c r="AB44" s="971"/>
+      <c r="AC44" s="964"/>
+      <c r="AD44" s="965"/>
+      <c r="AE44" s="966"/>
       <c r="AF44" s="80"/>
       <c r="AG44" s="82"/>
       <c r="AH44" s="82"/>
@@ -42643,21 +42643,21 @@
       <c r="N45" s="82"/>
       <c r="O45" s="83"/>
       <c r="P45" s="103"/>
-      <c r="Q45" s="1071"/>
-      <c r="R45" s="1072"/>
-      <c r="S45" s="1073"/>
-      <c r="T45" s="1059"/>
-      <c r="U45" s="1060"/>
-      <c r="V45" s="1061"/>
-      <c r="W45" s="1048"/>
-      <c r="X45" s="1049"/>
-      <c r="Y45" s="1049"/>
-      <c r="Z45" s="1042"/>
-      <c r="AA45" s="1043"/>
-      <c r="AB45" s="1047"/>
-      <c r="AC45" s="1042"/>
-      <c r="AD45" s="1043"/>
-      <c r="AE45" s="1044"/>
+      <c r="Q45" s="899"/>
+      <c r="R45" s="900"/>
+      <c r="S45" s="901"/>
+      <c r="T45" s="935"/>
+      <c r="U45" s="936"/>
+      <c r="V45" s="937"/>
+      <c r="W45" s="974"/>
+      <c r="X45" s="975"/>
+      <c r="Y45" s="975"/>
+      <c r="Z45" s="967"/>
+      <c r="AA45" s="968"/>
+      <c r="AB45" s="972"/>
+      <c r="AC45" s="967"/>
+      <c r="AD45" s="968"/>
+      <c r="AE45" s="969"/>
       <c r="AF45" s="80"/>
       <c r="AG45" s="82"/>
       <c r="AH45" s="82"/>
@@ -42680,21 +42680,21 @@
       <c r="N46" s="82"/>
       <c r="O46" s="83"/>
       <c r="P46" s="103"/>
-      <c r="Q46" s="1074"/>
-      <c r="R46" s="1075"/>
-      <c r="S46" s="1075"/>
-      <c r="T46" s="1058"/>
-      <c r="U46" s="1058"/>
-      <c r="V46" s="1058"/>
-      <c r="W46" s="1045"/>
-      <c r="X46" s="1045"/>
-      <c r="Y46" s="1045"/>
-      <c r="Z46" s="1045"/>
-      <c r="AA46" s="1045"/>
-      <c r="AB46" s="1045"/>
-      <c r="AC46" s="1045"/>
-      <c r="AD46" s="1045"/>
-      <c r="AE46" s="1046"/>
+      <c r="Q46" s="902"/>
+      <c r="R46" s="903"/>
+      <c r="S46" s="903"/>
+      <c r="T46" s="934"/>
+      <c r="U46" s="934"/>
+      <c r="V46" s="934"/>
+      <c r="W46" s="904"/>
+      <c r="X46" s="904"/>
+      <c r="Y46" s="904"/>
+      <c r="Z46" s="904"/>
+      <c r="AA46" s="904"/>
+      <c r="AB46" s="904"/>
+      <c r="AC46" s="904"/>
+      <c r="AD46" s="904"/>
+      <c r="AE46" s="970"/>
       <c r="AF46" s="80"/>
       <c r="AG46" s="82"/>
       <c r="AH46" s="82"/>
@@ -42717,21 +42717,21 @@
       <c r="N47" s="82"/>
       <c r="O47" s="83"/>
       <c r="P47" s="103"/>
-      <c r="Q47" s="1068"/>
-      <c r="R47" s="1069"/>
-      <c r="S47" s="1070"/>
-      <c r="T47" s="1053"/>
-      <c r="U47" s="1054"/>
-      <c r="V47" s="1055"/>
-      <c r="W47" s="1056"/>
-      <c r="X47" s="1057"/>
-      <c r="Y47" s="1057"/>
-      <c r="Z47" s="1027"/>
-      <c r="AA47" s="1028"/>
-      <c r="AB47" s="1029"/>
-      <c r="AC47" s="1027"/>
-      <c r="AD47" s="1028"/>
-      <c r="AE47" s="1030"/>
+      <c r="Q47" s="896"/>
+      <c r="R47" s="897"/>
+      <c r="S47" s="898"/>
+      <c r="T47" s="926"/>
+      <c r="U47" s="927"/>
+      <c r="V47" s="928"/>
+      <c r="W47" s="929"/>
+      <c r="X47" s="930"/>
+      <c r="Y47" s="930"/>
+      <c r="Z47" s="950"/>
+      <c r="AA47" s="951"/>
+      <c r="AB47" s="952"/>
+      <c r="AC47" s="950"/>
+      <c r="AD47" s="951"/>
+      <c r="AE47" s="953"/>
       <c r="AF47" s="83"/>
       <c r="AG47" s="90"/>
       <c r="AH47" s="82"/>
@@ -43035,16 +43035,110 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="W46:Y46"/>
-    <mergeCell ref="W38:Y38"/>
-    <mergeCell ref="W39:Y39"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="F33:L33"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="T36:V36"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F12:L13"/>
+    <mergeCell ref="M12:N15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B12:E15"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="Q27:W27"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T29:V30"/>
+    <mergeCell ref="AD6:AF7"/>
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="W6:Z7"/>
+    <mergeCell ref="V8:Z9"/>
+    <mergeCell ref="AD8:AF9"/>
+    <mergeCell ref="A4:AI4"/>
+    <mergeCell ref="A3:AI3"/>
+    <mergeCell ref="J6:L7"/>
+    <mergeCell ref="P8:R9"/>
+    <mergeCell ref="Q6:R7"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="E8:G9"/>
+    <mergeCell ref="K8:L9"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="AC40:AE40"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="W40:Y40"/>
+    <mergeCell ref="W41:Y41"/>
+    <mergeCell ref="W42:Y42"/>
+    <mergeCell ref="W43:Y43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="T44:V44"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="AC33:AE33"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="Z31:AB31"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="AC38:AE38"/>
+    <mergeCell ref="AC39:AE39"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AC47:AE47"/>
+    <mergeCell ref="B33:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="AC41:AE41"/>
+    <mergeCell ref="AC42:AE42"/>
+    <mergeCell ref="AC43:AE43"/>
+    <mergeCell ref="AC44:AE44"/>
+    <mergeCell ref="AC45:AE45"/>
+    <mergeCell ref="AC46:AE46"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="W33:Y33"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="W35:Y35"/>
+    <mergeCell ref="W36:Y36"/>
+    <mergeCell ref="W37:Y37"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="I35:J35"/>
@@ -43069,110 +43163,16 @@
     <mergeCell ref="T33:V33"/>
     <mergeCell ref="T34:V34"/>
     <mergeCell ref="T35:V35"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AC47:AE47"/>
-    <mergeCell ref="B33:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="AC41:AE41"/>
-    <mergeCell ref="AC42:AE42"/>
-    <mergeCell ref="AC43:AE43"/>
-    <mergeCell ref="AC44:AE44"/>
-    <mergeCell ref="AC45:AE45"/>
-    <mergeCell ref="AC46:AE46"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="Z45:AB45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="W33:Y33"/>
-    <mergeCell ref="W34:Y34"/>
-    <mergeCell ref="W35:Y35"/>
-    <mergeCell ref="W36:Y36"/>
-    <mergeCell ref="W37:Y37"/>
-    <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="AC32:AE32"/>
-    <mergeCell ref="AC33:AE33"/>
-    <mergeCell ref="AC34:AE34"/>
-    <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="AC36:AE36"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="Z31:AB31"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="AC37:AE37"/>
-    <mergeCell ref="AC38:AE38"/>
-    <mergeCell ref="AC39:AE39"/>
-    <mergeCell ref="AC40:AE40"/>
-    <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="W40:Y40"/>
-    <mergeCell ref="W41:Y41"/>
-    <mergeCell ref="W42:Y42"/>
-    <mergeCell ref="W43:Y43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="T44:V44"/>
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="Q27:W27"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="T29:V30"/>
-    <mergeCell ref="AD6:AF7"/>
-    <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="W6:Z7"/>
-    <mergeCell ref="V8:Z9"/>
-    <mergeCell ref="AD8:AF9"/>
-    <mergeCell ref="A4:AI4"/>
-    <mergeCell ref="A3:AI3"/>
-    <mergeCell ref="J6:L7"/>
-    <mergeCell ref="P8:R9"/>
-    <mergeCell ref="Q6:R7"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="E8:G9"/>
-    <mergeCell ref="K8:L9"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F12:L13"/>
-    <mergeCell ref="M12:N15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B12:E15"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="W46:Y46"/>
+    <mergeCell ref="W38:Y38"/>
+    <mergeCell ref="W39:Y39"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="T36:V36"/>
   </mergeCells>
   <conditionalFormatting sqref="S13:AF13">
     <cfRule type="cellIs" dxfId="26" priority="29" operator="greaterThanOrEqual">
@@ -43450,14 +43450,14 @@
       <c r="G2" s="377"/>
       <c r="H2" s="377"/>
       <c r="I2" s="377"/>
-      <c r="J2" s="603" t="s">
+      <c r="J2" s="593" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="603"/>
-      <c r="L2" s="603"/>
-      <c r="M2" s="603"/>
-      <c r="N2" s="603"/>
-      <c r="O2" s="603"/>
+      <c r="K2" s="593"/>
+      <c r="L2" s="593"/>
+      <c r="M2" s="593"/>
+      <c r="N2" s="593"/>
+      <c r="O2" s="593"/>
       <c r="P2" s="377"/>
       <c r="Q2" s="377"/>
       <c r="R2" s="377"/>
@@ -43498,14 +43498,14 @@
       <c r="I4" s="378" t="s">
         <v>133</v>
       </c>
-      <c r="J4" s="602" t="s">
+      <c r="J4" s="592" t="s">
         <v>134</v>
       </c>
-      <c r="K4" s="602"/>
-      <c r="L4" s="602"/>
-      <c r="M4" s="602"/>
-      <c r="N4" s="602"/>
-      <c r="O4" s="602"/>
+      <c r="K4" s="592"/>
+      <c r="L4" s="592"/>
+      <c r="M4" s="592"/>
+      <c r="N4" s="592"/>
+      <c r="O4" s="592"/>
       <c r="P4" s="379"/>
       <c r="Q4" s="379"/>
       <c r="R4" s="380"/>
@@ -43521,17 +43521,17 @@
       <c r="G5" s="381"/>
       <c r="H5" s="381"/>
       <c r="I5" s="382"/>
-      <c r="J5" s="595" t="s">
+      <c r="J5" s="603" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="595"/>
-      <c r="L5" s="595"/>
-      <c r="M5" s="595"/>
-      <c r="N5" s="607" t="s">
+      <c r="K5" s="603"/>
+      <c r="L5" s="603"/>
+      <c r="M5" s="603"/>
+      <c r="N5" s="600" t="s">
         <v>164</v>
       </c>
-      <c r="O5" s="607"/>
-      <c r="P5" s="607"/>
+      <c r="O5" s="600"/>
+      <c r="P5" s="600"/>
       <c r="Q5" s="383"/>
       <c r="R5" s="383"/>
       <c r="S5" s="22"/>
@@ -43562,12 +43562,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="23"/>
-      <c r="C8" s="598" t="str">
+      <c r="C8" s="604" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO ABRIL - 2025</v>
       </c>
-      <c r="D8" s="599"/>
-      <c r="E8" s="600"/>
+      <c r="D8" s="605"/>
+      <c r="E8" s="606"/>
       <c r="G8" s="56" t="s">
         <v>1</v>
       </c>
@@ -43610,11 +43610,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="C10" s="601" t="s">
+      <c r="C10" s="607" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="601"/>
-      <c r="E10" s="601"/>
+      <c r="D10" s="607"/>
+      <c r="E10" s="607"/>
       <c r="G10" s="76" t="s">
         <v>8</v>
       </c>
@@ -43764,11 +43764,11 @@
       <c r="C15" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="593">
+      <c r="D15" s="602">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="593"/>
+      <c r="E15" s="602"/>
       <c r="H15" s="35"/>
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
@@ -43811,11 +43811,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="C24" s="604" t="s">
+      <c r="C24" s="595" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="605"/>
-      <c r="E24" s="606"/>
+      <c r="D24" s="596"/>
+      <c r="E24" s="597"/>
       <c r="S24" s="22"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -43823,11 +43823,11 @@
       <c r="C25" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="596">
+      <c r="D25" s="598">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="597"/>
+      <c r="E25" s="599"/>
       <c r="S25" s="22"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -43835,11 +43835,11 @@
       <c r="C26" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="596">
+      <c r="D26" s="598">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="597"/>
+      <c r="E26" s="599"/>
       <c r="S26" s="22"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -43871,11 +43871,11 @@
       <c r="C29" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="592">
+      <c r="D29" s="601">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="592"/>
+      <c r="E29" s="601"/>
       <c r="S29" s="22"/>
     </row>
     <row r="30" spans="1:19">
@@ -43989,12 +43989,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -44006,10 +44000,16 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="5" scale="50" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="51" max="18" man="1"/>
   </rowBreaks>
@@ -48777,9 +48777,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="654"/>
-      <c r="C1" s="655"/>
-      <c r="D1" s="656"/>
+      <c r="B1" s="647"/>
+      <c r="C1" s="648"/>
+      <c r="D1" s="649"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -48801,10 +48801,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="650" t="s">
+      <c r="I2" s="660" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="651"/>
+      <c r="J2" s="661"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -48858,10 +48858,10 @@
       <c r="B5" s="376" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="657" t="s">
+      <c r="C5" s="653" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="658"/>
+      <c r="D5" s="654"/>
       <c r="E5" s="373" t="s">
         <v>60</v>
       </c>
@@ -48889,8 +48889,8 @@
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
       <c r="B6" s="215"/>
-      <c r="C6" s="659"/>
-      <c r="D6" s="660"/>
+      <c r="C6" s="655"/>
+      <c r="D6" s="656"/>
       <c r="E6" s="457"/>
       <c r="F6" s="457"/>
       <c r="G6" s="457"/>
@@ -48908,8 +48908,8 @@
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="99"/>
       <c r="B7" s="216"/>
-      <c r="C7" s="661"/>
-      <c r="D7" s="662"/>
+      <c r="C7" s="657"/>
+      <c r="D7" s="658"/>
       <c r="E7" s="458"/>
       <c r="F7" s="458"/>
       <c r="G7" s="458"/>
@@ -48925,8 +48925,8 @@
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="100"/>
       <c r="B8" s="216"/>
-      <c r="C8" s="661"/>
-      <c r="D8" s="662"/>
+      <c r="C8" s="657"/>
+      <c r="D8" s="658"/>
       <c r="E8" s="458"/>
       <c r="F8" s="458"/>
       <c r="G8" s="458"/>
@@ -48943,8 +48943,8 @@
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="100"/>
       <c r="B9" s="216"/>
-      <c r="C9" s="661"/>
-      <c r="D9" s="662"/>
+      <c r="C9" s="657"/>
+      <c r="D9" s="658"/>
       <c r="E9" s="458"/>
       <c r="F9" s="458"/>
       <c r="G9" s="458"/>
@@ -48962,8 +48962,8 @@
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="102"/>
       <c r="B10" s="216"/>
-      <c r="C10" s="661"/>
-      <c r="D10" s="662"/>
+      <c r="C10" s="657"/>
+      <c r="D10" s="658"/>
       <c r="E10" s="458"/>
       <c r="F10" s="458"/>
       <c r="G10" s="458"/>
@@ -48980,8 +48980,8 @@
     <row r="11" spans="1:17" ht="55.5" customHeight="1">
       <c r="A11" s="101"/>
       <c r="B11" s="216"/>
-      <c r="C11" s="661"/>
-      <c r="D11" s="663"/>
+      <c r="C11" s="657"/>
+      <c r="D11" s="659"/>
       <c r="E11" s="458"/>
       <c r="F11" s="458"/>
       <c r="G11" s="458"/>
@@ -48997,8 +48997,8 @@
     <row r="12" spans="1:17" ht="44.25" customHeight="1">
       <c r="A12" s="101"/>
       <c r="B12" s="216"/>
-      <c r="C12" s="661"/>
-      <c r="D12" s="662"/>
+      <c r="C12" s="657"/>
+      <c r="D12" s="658"/>
       <c r="E12" s="458"/>
       <c r="F12" s="458"/>
       <c r="G12" s="458"/>
@@ -49015,8 +49015,8 @@
     <row r="13" spans="1:17" ht="63" customHeight="1" thickBot="1">
       <c r="A13" s="100"/>
       <c r="B13" s="217"/>
-      <c r="C13" s="652"/>
-      <c r="D13" s="653"/>
+      <c r="C13" s="662"/>
+      <c r="D13" s="663"/>
       <c r="E13" s="459"/>
       <c r="F13" s="459"/>
       <c r="G13" s="459"/>
@@ -49076,12 +49076,12 @@
       </c>
       <c r="C16" s="481"/>
       <c r="D16" s="294"/>
-      <c r="E16" s="647"/>
-      <c r="F16" s="648"/>
-      <c r="G16" s="648"/>
-      <c r="H16" s="648"/>
-      <c r="I16" s="648"/>
-      <c r="J16" s="649"/>
+      <c r="E16" s="650"/>
+      <c r="F16" s="651"/>
+      <c r="G16" s="651"/>
+      <c r="H16" s="651"/>
+      <c r="I16" s="651"/>
+      <c r="J16" s="652"/>
       <c r="K16" s="301"/>
       <c r="L16" s="115"/>
       <c r="M16" s="113"/>
@@ -49095,12 +49095,12 @@
       </c>
       <c r="C17" s="483"/>
       <c r="D17" s="294"/>
-      <c r="E17" s="647"/>
-      <c r="F17" s="648"/>
-      <c r="G17" s="648"/>
-      <c r="H17" s="648"/>
-      <c r="I17" s="648"/>
-      <c r="J17" s="649"/>
+      <c r="E17" s="650"/>
+      <c r="F17" s="651"/>
+      <c r="G17" s="651"/>
+      <c r="H17" s="651"/>
+      <c r="I17" s="651"/>
+      <c r="J17" s="652"/>
       <c r="K17" s="136"/>
       <c r="L17" s="123"/>
       <c r="M17" s="115"/>
@@ -49115,12 +49115,12 @@
       </c>
       <c r="C18" s="483"/>
       <c r="D18" s="295"/>
-      <c r="E18" s="647"/>
-      <c r="F18" s="648"/>
-      <c r="G18" s="648"/>
-      <c r="H18" s="648"/>
-      <c r="I18" s="648"/>
-      <c r="J18" s="649"/>
+      <c r="E18" s="650"/>
+      <c r="F18" s="651"/>
+      <c r="G18" s="651"/>
+      <c r="H18" s="651"/>
+      <c r="I18" s="651"/>
+      <c r="J18" s="652"/>
       <c r="L18" s="115"/>
       <c r="M18" s="111"/>
       <c r="N18" s="110"/>
@@ -49132,12 +49132,12 @@
       <c r="B19" s="87"/>
       <c r="C19" s="87"/>
       <c r="D19" s="296"/>
-      <c r="E19" s="647"/>
-      <c r="F19" s="648"/>
-      <c r="G19" s="648"/>
-      <c r="H19" s="648"/>
-      <c r="I19" s="648"/>
-      <c r="J19" s="649"/>
+      <c r="E19" s="650"/>
+      <c r="F19" s="651"/>
+      <c r="G19" s="651"/>
+      <c r="H19" s="651"/>
+      <c r="I19" s="651"/>
+      <c r="J19" s="652"/>
       <c r="K19" s="136"/>
       <c r="L19" s="123"/>
       <c r="M19" s="111"/>
@@ -49149,12 +49149,12 @@
       <c r="A20" s="79"/>
       <c r="B20" s="90"/>
       <c r="D20" s="295"/>
-      <c r="E20" s="647"/>
-      <c r="F20" s="648"/>
-      <c r="G20" s="648"/>
-      <c r="H20" s="648"/>
-      <c r="I20" s="648"/>
-      <c r="J20" s="649"/>
+      <c r="E20" s="650"/>
+      <c r="F20" s="651"/>
+      <c r="G20" s="651"/>
+      <c r="H20" s="651"/>
+      <c r="I20" s="651"/>
+      <c r="J20" s="652"/>
       <c r="K20" s="302"/>
       <c r="L20" s="297"/>
       <c r="M20" s="114"/>
@@ -49164,12 +49164,12 @@
     <row r="21" spans="1:16" ht="84.75" customHeight="1" thickBot="1">
       <c r="B21" s="90"/>
       <c r="D21" s="295"/>
-      <c r="E21" s="647"/>
-      <c r="F21" s="648"/>
-      <c r="G21" s="648"/>
-      <c r="H21" s="648"/>
-      <c r="I21" s="648"/>
-      <c r="J21" s="649"/>
+      <c r="E21" s="650"/>
+      <c r="F21" s="651"/>
+      <c r="G21" s="651"/>
+      <c r="H21" s="651"/>
+      <c r="I21" s="651"/>
+      <c r="J21" s="652"/>
       <c r="K21" s="302"/>
       <c r="L21" s="58"/>
       <c r="M21" s="114"/>
@@ -49180,12 +49180,12 @@
       <c r="B22" s="227"/>
       <c r="C22" s="228"/>
       <c r="D22" s="295"/>
-      <c r="E22" s="647"/>
-      <c r="F22" s="648"/>
-      <c r="G22" s="648"/>
-      <c r="H22" s="648"/>
-      <c r="I22" s="648"/>
-      <c r="J22" s="649"/>
+      <c r="E22" s="650"/>
+      <c r="F22" s="651"/>
+      <c r="G22" s="651"/>
+      <c r="H22" s="651"/>
+      <c r="I22" s="651"/>
+      <c r="J22" s="652"/>
       <c r="K22" s="303"/>
       <c r="L22" s="58"/>
       <c r="M22" s="112"/>
@@ -49603,6 +49603,14 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E20:J20"/>
+    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="E21:J21"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E18:J18"/>
     <mergeCell ref="C5:D5"/>
@@ -49613,14 +49621,6 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="E21:J21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -49630,12 +49630,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49894,20 +49896,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -49932,18 +49941,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0A5189-EF72-4281-AC54-8646F233BB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DC4996-123C-4F7C-99A4-D3B332412DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" tabRatio="719" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Convenios ADP_II" sheetId="54" r:id="rId10"/>
     <sheet name="Gestión de riesgos" sheetId="48" r:id="rId11"/>
     <sheet name="data_riesgos" sheetId="49" state="hidden" r:id="rId12"/>
-    <sheet name="Planes de tratamientos" sheetId="55" state="hidden" r:id="rId13"/>
+    <sheet name="Planes de tratamientos" sheetId="55" r:id="rId13"/>
     <sheet name="programas sociales" sheetId="50" state="hidden" r:id="rId14"/>
     <sheet name="Planes tratamientos" sheetId="53" state="hidden" r:id="rId15"/>
     <sheet name="datos_graficos" sheetId="51" state="hidden" r:id="rId16"/>
@@ -29463,7 +29463,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s356036"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s370048"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29528,7 +29528,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s356037"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s370049"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29645,7 +29645,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s356038"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s370050"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29710,7 +29710,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s356039"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s370051"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29775,7 +29775,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s356040"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s370052"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29840,7 +29840,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s356041"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s370053"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29905,7 +29905,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s356042"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s370054"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -29970,7 +29970,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s356043"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s370055"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30035,7 +30035,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s356044"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s370056"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30100,7 +30100,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s356045"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s370057"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -44009,7 +44009,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="5" scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="50" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="51" max="18" man="1"/>
   </rowBreaks>
@@ -49630,6 +49630,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
@@ -49640,7 +49649,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd0678842d65e4207392abd035356b9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d84746cc30da1fe182e7a313d44b54c" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -49895,16 +49904,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -49921,7 +49929,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE64779-B9F2-4AEC-A5E9-E8076DA89A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49938,12 +49946,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80129A2D-69A8-4AF2-8089-5D069B1F5EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B6B6C8-9ED8-4B7A-8D02-CB699EC0B708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Convenios ADP_II" sheetId="54" state="hidden" r:id="rId10"/>
     <sheet name="Gestión de riesgos" sheetId="48" r:id="rId11"/>
     <sheet name="data_riesgos" sheetId="49" state="hidden" r:id="rId12"/>
-    <sheet name="Planes de tratamientos" sheetId="55" state="hidden" r:id="rId13"/>
+    <sheet name="Planes de tratamientos" sheetId="55" r:id="rId13"/>
     <sheet name="Planes tratamientos" sheetId="53" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames>
@@ -6913,15 +6913,42 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6931,36 +6958,9 @@
     <xf numFmtId="0" fontId="31" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="66" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -7078,6 +7078,27 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="193" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="60" fillId="0" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7087,15 +7108,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="193" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="79" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7117,18 +7129,6 @@
     <xf numFmtId="14" fontId="60" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="60" fillId="0" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7171,17 +7171,266 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -7189,9 +7438,6 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7243,9 +7489,6 @@
     <xf numFmtId="0" fontId="39" fillId="13" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -7270,249 +7513,6 @@
     <xf numFmtId="0" fontId="49" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="128" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="125" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="126" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="127" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="130" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -7525,6 +7525,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="305" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="310" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="312" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="13" borderId="182" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="13" borderId="184" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="221" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="316" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="151" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="307" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="9" borderId="308" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="88" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7597,88 +7681,523 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="289" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="286" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="207" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="208" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="208" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="13" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="221" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="221" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="316" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="151" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="305" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="310" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="151" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="307" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="308" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="182" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="184" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="179" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="209" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="229" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="222" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="256" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="222" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="224" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="0" borderId="223" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="76" fillId="0" borderId="222" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="76" fillId="0" borderId="224" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="225" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="13" borderId="182" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="226" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="13" borderId="184" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="225" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="226" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="223" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="222" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="224" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="267" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="247" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="229" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="222" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="230" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="268" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="230" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="264" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="266" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="273" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="275" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="158" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="276" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="244" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="240" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="258" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="205" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="245" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="242" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="243" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="171" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="250" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="262" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="260" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="261" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="17" borderId="182" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="239" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="240" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="241" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="246" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="312" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="247" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="248" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="247" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="76" fillId="17" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="259" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7705,15 +8224,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="225" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="226" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="58" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -7728,516 +8238,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="273" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="275" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="158" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="0" borderId="223" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="0" borderId="222" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="0" borderId="224" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="171" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="139" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="250" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="251" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="225" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="226" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="262" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="260" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="261" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="263" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="182" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="223" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="222" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="224" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="239" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="240" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="241" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="246" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="247" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="248" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="255" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="222" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="224" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="249" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="247" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="76" fillId="17" borderId="248" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="264" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="260" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="265" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="266" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="276" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="13" borderId="160" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="13" borderId="159" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="13" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="229" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="222" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="256" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="229" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="222" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="256" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="244" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="240" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="258" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="205" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="230" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="245" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="230" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="242" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="243" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="267" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="140" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="252" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="247" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="254" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="268" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="17" borderId="253" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="13" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="13" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="13" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="219" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="220" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="221" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="151" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="199" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="182" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="13" borderId="199" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="13" borderId="182" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="13" borderId="184" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="179" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="209" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="134" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="289" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="286" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="207" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="208" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="208" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -25550,7 +25550,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382352"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382782"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25615,7 +25615,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382353"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382783"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25732,7 +25732,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s382354"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s382784"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25797,7 +25797,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s382355"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s382785"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25862,7 +25862,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s382356"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s382786"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25927,7 +25927,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s382357"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s382787"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25992,7 +25992,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s382358"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s382788"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26057,7 +26057,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s382359"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s382789"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26122,7 +26122,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s382360"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s382790"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26187,7 +26187,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s382361"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s382791"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -30379,9 +30379,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="602"/>
-      <c r="C1" s="603"/>
-      <c r="D1" s="604"/>
+      <c r="B1" s="609"/>
+      <c r="C1" s="610"/>
+      <c r="D1" s="611"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -30403,10 +30403,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="615" t="s">
+      <c r="I2" s="605" t="s">
         <v>155</v>
       </c>
-      <c r="J2" s="616"/>
+      <c r="J2" s="606"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -30459,10 +30459,10 @@
       <c r="B5" s="521" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="608" t="s">
+      <c r="C5" s="612" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="609"/>
+      <c r="D5" s="613"/>
       <c r="E5" s="522" t="s">
         <v>60</v>
       </c>
@@ -30509,8 +30509,8 @@
     <row r="7" spans="1:17" ht="28.5">
       <c r="A7" s="79"/>
       <c r="B7" s="210"/>
-      <c r="C7" s="612"/>
-      <c r="D7" s="614"/>
+      <c r="C7" s="616"/>
+      <c r="D7" s="618"/>
       <c r="E7" s="439"/>
       <c r="F7" s="439"/>
       <c r="G7" s="439"/>
@@ -30678,12 +30678,12 @@
       </c>
       <c r="C16" s="455"/>
       <c r="D16" s="284"/>
-      <c r="E16" s="605"/>
-      <c r="F16" s="606"/>
-      <c r="G16" s="606"/>
-      <c r="H16" s="606"/>
-      <c r="I16" s="606"/>
-      <c r="J16" s="607"/>
+      <c r="E16" s="602"/>
+      <c r="F16" s="603"/>
+      <c r="G16" s="603"/>
+      <c r="H16" s="603"/>
+      <c r="I16" s="603"/>
+      <c r="J16" s="604"/>
       <c r="K16" s="291"/>
       <c r="L16" s="115"/>
       <c r="M16" s="115"/>
@@ -30698,12 +30698,12 @@
       </c>
       <c r="C17" s="454"/>
       <c r="D17" s="284"/>
-      <c r="E17" s="605"/>
-      <c r="F17" s="606"/>
-      <c r="G17" s="606"/>
-      <c r="H17" s="606"/>
-      <c r="I17" s="606"/>
-      <c r="J17" s="607"/>
+      <c r="E17" s="602"/>
+      <c r="F17" s="603"/>
+      <c r="G17" s="603"/>
+      <c r="H17" s="603"/>
+      <c r="I17" s="603"/>
+      <c r="J17" s="604"/>
       <c r="K17" s="136"/>
       <c r="L17" s="115"/>
       <c r="M17" s="115"/>
@@ -31272,32 +31272,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="29.25" customHeight="1" thickBot="1">
       <c r="A1" s="178"/>
-      <c r="B1" s="642" t="s">
+      <c r="B1" s="724" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="643"/>
-      <c r="D1" s="643"/>
-      <c r="E1" s="643"/>
-      <c r="F1" s="643"/>
-      <c r="G1" s="643"/>
-      <c r="H1" s="643"/>
-      <c r="I1" s="643"/>
-      <c r="J1" s="643"/>
-      <c r="K1" s="643"/>
-      <c r="L1" s="643"/>
-      <c r="M1" s="643"/>
-      <c r="N1" s="643"/>
-      <c r="O1" s="643"/>
-      <c r="P1" s="643"/>
-      <c r="Q1" s="643"/>
-      <c r="R1" s="643"/>
-      <c r="S1" s="643"/>
-      <c r="T1" s="643"/>
-      <c r="U1" s="643"/>
-      <c r="V1" s="643"/>
-      <c r="W1" s="643"/>
-      <c r="X1" s="643"/>
-      <c r="Y1" s="644"/>
+      <c r="C1" s="725"/>
+      <c r="D1" s="725"/>
+      <c r="E1" s="725"/>
+      <c r="F1" s="725"/>
+      <c r="G1" s="725"/>
+      <c r="H1" s="725"/>
+      <c r="I1" s="725"/>
+      <c r="J1" s="725"/>
+      <c r="K1" s="725"/>
+      <c r="L1" s="725"/>
+      <c r="M1" s="725"/>
+      <c r="N1" s="725"/>
+      <c r="O1" s="725"/>
+      <c r="P1" s="725"/>
+      <c r="Q1" s="725"/>
+      <c r="R1" s="725"/>
+      <c r="S1" s="725"/>
+      <c r="T1" s="725"/>
+      <c r="U1" s="725"/>
+      <c r="V1" s="725"/>
+      <c r="W1" s="725"/>
+      <c r="X1" s="725"/>
+      <c r="Y1" s="726"/>
       <c r="Z1" s="173"/>
     </row>
     <row r="2" spans="1:28" ht="9" customHeight="1" thickBot="1">
@@ -31333,32 +31333,32 @@
       <c r="A3" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="645" t="s">
+      <c r="B3" s="727" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="646"/>
-      <c r="D3" s="646"/>
-      <c r="E3" s="646"/>
-      <c r="F3" s="646"/>
-      <c r="G3" s="646"/>
-      <c r="H3" s="646"/>
-      <c r="I3" s="646"/>
-      <c r="J3" s="646"/>
-      <c r="K3" s="646"/>
-      <c r="L3" s="646"/>
-      <c r="M3" s="646"/>
-      <c r="N3" s="646"/>
-      <c r="O3" s="646"/>
-      <c r="P3" s="646"/>
-      <c r="Q3" s="646"/>
-      <c r="R3" s="646"/>
-      <c r="S3" s="646"/>
-      <c r="T3" s="646"/>
-      <c r="U3" s="646"/>
-      <c r="V3" s="646"/>
-      <c r="W3" s="646"/>
-      <c r="X3" s="646"/>
-      <c r="Y3" s="647"/>
+      <c r="C3" s="728"/>
+      <c r="D3" s="728"/>
+      <c r="E3" s="728"/>
+      <c r="F3" s="728"/>
+      <c r="G3" s="728"/>
+      <c r="H3" s="728"/>
+      <c r="I3" s="728"/>
+      <c r="J3" s="728"/>
+      <c r="K3" s="728"/>
+      <c r="L3" s="728"/>
+      <c r="M3" s="728"/>
+      <c r="N3" s="728"/>
+      <c r="O3" s="728"/>
+      <c r="P3" s="728"/>
+      <c r="Q3" s="728"/>
+      <c r="R3" s="728"/>
+      <c r="S3" s="728"/>
+      <c r="T3" s="728"/>
+      <c r="U3" s="728"/>
+      <c r="V3" s="728"/>
+      <c r="W3" s="728"/>
+      <c r="X3" s="728"/>
+      <c r="Y3" s="729"/>
       <c r="Z3" s="174"/>
       <c r="AA3" s="103"/>
     </row>
@@ -31366,32 +31366,32 @@
       <c r="A4" s="180" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="648" t="s">
+      <c r="B4" s="730" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="649"/>
-      <c r="D4" s="649"/>
-      <c r="E4" s="649"/>
-      <c r="F4" s="649"/>
-      <c r="G4" s="649"/>
-      <c r="H4" s="649"/>
-      <c r="I4" s="649"/>
-      <c r="J4" s="649"/>
-      <c r="K4" s="649"/>
-      <c r="L4" s="649"/>
-      <c r="M4" s="649"/>
-      <c r="N4" s="649"/>
-      <c r="O4" s="649"/>
-      <c r="P4" s="649"/>
-      <c r="Q4" s="649"/>
-      <c r="R4" s="649"/>
-      <c r="S4" s="649"/>
-      <c r="T4" s="649"/>
-      <c r="U4" s="649"/>
-      <c r="V4" s="649"/>
-      <c r="W4" s="649"/>
-      <c r="X4" s="649"/>
-      <c r="Y4" s="650"/>
+      <c r="C4" s="731"/>
+      <c r="D4" s="731"/>
+      <c r="E4" s="731"/>
+      <c r="F4" s="731"/>
+      <c r="G4" s="731"/>
+      <c r="H4" s="731"/>
+      <c r="I4" s="731"/>
+      <c r="J4" s="731"/>
+      <c r="K4" s="731"/>
+      <c r="L4" s="731"/>
+      <c r="M4" s="731"/>
+      <c r="N4" s="731"/>
+      <c r="O4" s="731"/>
+      <c r="P4" s="731"/>
+      <c r="Q4" s="731"/>
+      <c r="R4" s="731"/>
+      <c r="S4" s="731"/>
+      <c r="T4" s="731"/>
+      <c r="U4" s="731"/>
+      <c r="V4" s="731"/>
+      <c r="W4" s="731"/>
+      <c r="X4" s="731"/>
+      <c r="Y4" s="732"/>
       <c r="Z4" s="175"/>
       <c r="AA4" s="103"/>
     </row>
@@ -31426,40 +31426,40 @@
     </row>
     <row r="6" spans="1:28" ht="24.75" customHeight="1" thickBot="1">
       <c r="A6" s="181"/>
-      <c r="B6" s="654" t="s">
+      <c r="B6" s="736" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="655"/>
-      <c r="D6" s="655"/>
-      <c r="E6" s="656"/>
+      <c r="C6" s="737"/>
+      <c r="D6" s="737"/>
+      <c r="E6" s="738"/>
       <c r="F6" s="89"/>
       <c r="G6" s="142"/>
-      <c r="H6" s="674" t="s">
+      <c r="H6" s="702" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="675"/>
-      <c r="J6" s="675"/>
-      <c r="K6" s="676"/>
+      <c r="I6" s="703"/>
+      <c r="J6" s="703"/>
+      <c r="K6" s="704"/>
       <c r="L6" s="89"/>
       <c r="M6" s="142"/>
-      <c r="N6" s="682" t="s">
+      <c r="N6" s="714" t="s">
         <v>95</v>
       </c>
-      <c r="O6" s="683"/>
-      <c r="P6" s="684"/>
+      <c r="O6" s="715"/>
+      <c r="P6" s="716"/>
       <c r="Q6" s="149"/>
       <c r="R6" s="151"/>
-      <c r="S6" s="634" t="s">
+      <c r="S6" s="709" t="s">
         <v>77</v>
       </c>
-      <c r="T6" s="635"/>
+      <c r="T6" s="710"/>
       <c r="U6" s="152"/>
       <c r="V6" s="156"/>
       <c r="W6" s="143"/>
-      <c r="X6" s="634" t="s">
+      <c r="X6" s="709" t="s">
         <v>78</v>
       </c>
-      <c r="Y6" s="635"/>
+      <c r="Y6" s="710"/>
       <c r="Z6" s="80"/>
       <c r="AA6" s="103"/>
     </row>
@@ -31479,36 +31479,36 @@
       </c>
       <c r="F7" s="89"/>
       <c r="G7" s="116"/>
-      <c r="H7" s="670">
+      <c r="H7" s="711">
         <f>I23</f>
         <v>0</v>
       </c>
-      <c r="I7" s="681"/>
-      <c r="J7" s="681"/>
-      <c r="K7" s="671"/>
+      <c r="I7" s="713"/>
+      <c r="J7" s="713"/>
+      <c r="K7" s="712"/>
       <c r="L7" s="89"/>
       <c r="M7" s="116"/>
-      <c r="N7" s="666">
+      <c r="N7" s="717">
         <f>L23</f>
         <v>0</v>
       </c>
-      <c r="O7" s="667"/>
-      <c r="P7" s="668"/>
+      <c r="O7" s="718"/>
+      <c r="P7" s="719"/>
       <c r="Q7" s="150"/>
       <c r="R7" s="152"/>
-      <c r="S7" s="670">
+      <c r="S7" s="711">
         <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T7" s="671"/>
+      <c r="T7" s="712"/>
       <c r="U7" s="89"/>
       <c r="V7" s="155"/>
       <c r="W7" s="82"/>
-      <c r="X7" s="670">
+      <c r="X7" s="711">
         <f>R23</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="671"/>
+      <c r="Y7" s="712"/>
       <c r="Z7" s="141"/>
       <c r="AA7" s="103"/>
     </row>
@@ -31577,27 +31577,27 @@
       <c r="D10" s="134"/>
       <c r="E10" s="199"/>
       <c r="F10" s="89"/>
-      <c r="G10" s="662" t="s">
+      <c r="G10" s="743" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="663"/>
-      <c r="I10" s="663"/>
-      <c r="J10" s="663"/>
-      <c r="K10" s="663"/>
-      <c r="L10" s="663"/>
-      <c r="M10" s="663"/>
-      <c r="N10" s="663"/>
-      <c r="O10" s="663"/>
-      <c r="P10" s="663"/>
-      <c r="Q10" s="663"/>
-      <c r="R10" s="663"/>
-      <c r="S10" s="663"/>
-      <c r="T10" s="663"/>
-      <c r="U10" s="663"/>
-      <c r="V10" s="663"/>
-      <c r="W10" s="663"/>
-      <c r="X10" s="663"/>
-      <c r="Y10" s="664"/>
+      <c r="H10" s="744"/>
+      <c r="I10" s="744"/>
+      <c r="J10" s="744"/>
+      <c r="K10" s="744"/>
+      <c r="L10" s="744"/>
+      <c r="M10" s="744"/>
+      <c r="N10" s="744"/>
+      <c r="O10" s="744"/>
+      <c r="P10" s="744"/>
+      <c r="Q10" s="744"/>
+      <c r="R10" s="744"/>
+      <c r="S10" s="744"/>
+      <c r="T10" s="744"/>
+      <c r="U10" s="744"/>
+      <c r="V10" s="744"/>
+      <c r="W10" s="744"/>
+      <c r="X10" s="744"/>
+      <c r="Y10" s="745"/>
       <c r="Z10" s="80"/>
       <c r="AA10" s="103"/>
     </row>
@@ -31608,35 +31608,35 @@
       <c r="D11" s="134"/>
       <c r="E11" s="199"/>
       <c r="F11" s="89"/>
-      <c r="G11" s="665" t="s">
+      <c r="G11" s="746" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="660"/>
-      <c r="I11" s="660" t="s">
+      <c r="H11" s="741"/>
+      <c r="I11" s="741" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="660"/>
-      <c r="K11" s="660"/>
-      <c r="L11" s="660" t="s">
+      <c r="J11" s="741"/>
+      <c r="K11" s="741"/>
+      <c r="L11" s="741" t="s">
         <v>82</v>
       </c>
-      <c r="M11" s="660"/>
-      <c r="N11" s="660"/>
-      <c r="O11" s="660" t="s">
+      <c r="M11" s="741"/>
+      <c r="N11" s="741"/>
+      <c r="O11" s="741" t="s">
         <v>83</v>
       </c>
-      <c r="P11" s="660"/>
-      <c r="Q11" s="660"/>
-      <c r="R11" s="660" t="s">
+      <c r="P11" s="741"/>
+      <c r="Q11" s="741"/>
+      <c r="R11" s="741" t="s">
         <v>78</v>
       </c>
-      <c r="S11" s="660"/>
-      <c r="T11" s="660"/>
-      <c r="U11" s="660"/>
-      <c r="V11" s="660"/>
-      <c r="W11" s="660"/>
-      <c r="X11" s="660"/>
-      <c r="Y11" s="661"/>
+      <c r="S11" s="741"/>
+      <c r="T11" s="741"/>
+      <c r="U11" s="741"/>
+      <c r="V11" s="741"/>
+      <c r="W11" s="741"/>
+      <c r="X11" s="741"/>
+      <c r="Y11" s="742"/>
       <c r="Z11" s="80"/>
       <c r="AA11" s="103"/>
     </row>
@@ -31647,33 +31647,33 @@
       <c r="D12" s="185"/>
       <c r="E12" s="199"/>
       <c r="F12" s="89"/>
-      <c r="G12" s="665"/>
-      <c r="H12" s="660"/>
-      <c r="I12" s="660"/>
-      <c r="J12" s="660"/>
-      <c r="K12" s="660"/>
-      <c r="L12" s="660"/>
-      <c r="M12" s="660"/>
-      <c r="N12" s="660"/>
-      <c r="O12" s="660"/>
-      <c r="P12" s="660"/>
-      <c r="Q12" s="660"/>
-      <c r="R12" s="636" t="s">
+      <c r="G12" s="746"/>
+      <c r="H12" s="741"/>
+      <c r="I12" s="741"/>
+      <c r="J12" s="741"/>
+      <c r="K12" s="741"/>
+      <c r="L12" s="741"/>
+      <c r="M12" s="741"/>
+      <c r="N12" s="741"/>
+      <c r="O12" s="741"/>
+      <c r="P12" s="741"/>
+      <c r="Q12" s="741"/>
+      <c r="R12" s="668" t="s">
         <v>84</v>
       </c>
-      <c r="S12" s="636"/>
-      <c r="T12" s="636" t="s">
+      <c r="S12" s="668"/>
+      <c r="T12" s="668" t="s">
         <v>85</v>
       </c>
-      <c r="U12" s="636"/>
-      <c r="V12" s="636" t="s">
+      <c r="U12" s="668"/>
+      <c r="V12" s="668" t="s">
         <v>86</v>
       </c>
-      <c r="W12" s="636"/>
-      <c r="X12" s="636" t="s">
+      <c r="W12" s="668"/>
+      <c r="X12" s="668" t="s">
         <v>87</v>
       </c>
-      <c r="Y12" s="657"/>
+      <c r="Y12" s="699"/>
       <c r="Z12" s="80"/>
       <c r="AA12" s="79"/>
     </row>
@@ -31684,25 +31684,25 @@
       <c r="D13" s="134"/>
       <c r="E13" s="199"/>
       <c r="F13" s="89"/>
-      <c r="G13" s="665"/>
-      <c r="H13" s="660"/>
-      <c r="I13" s="660"/>
-      <c r="J13" s="660"/>
-      <c r="K13" s="660"/>
-      <c r="L13" s="660"/>
-      <c r="M13" s="660"/>
-      <c r="N13" s="660"/>
-      <c r="O13" s="660"/>
-      <c r="P13" s="660"/>
-      <c r="Q13" s="660"/>
-      <c r="R13" s="636"/>
-      <c r="S13" s="636"/>
-      <c r="T13" s="636"/>
-      <c r="U13" s="636"/>
-      <c r="V13" s="636"/>
-      <c r="W13" s="636"/>
-      <c r="X13" s="658"/>
-      <c r="Y13" s="659"/>
+      <c r="G13" s="746"/>
+      <c r="H13" s="741"/>
+      <c r="I13" s="741"/>
+      <c r="J13" s="741"/>
+      <c r="K13" s="741"/>
+      <c r="L13" s="741"/>
+      <c r="M13" s="741"/>
+      <c r="N13" s="741"/>
+      <c r="O13" s="741"/>
+      <c r="P13" s="741"/>
+      <c r="Q13" s="741"/>
+      <c r="R13" s="668"/>
+      <c r="S13" s="668"/>
+      <c r="T13" s="668"/>
+      <c r="U13" s="668"/>
+      <c r="V13" s="668"/>
+      <c r="W13" s="668"/>
+      <c r="X13" s="739"/>
+      <c r="Y13" s="740"/>
       <c r="Z13" s="80"/>
       <c r="AA13" s="81"/>
     </row>
@@ -31713,27 +31713,27 @@
       <c r="D14" s="134"/>
       <c r="E14" s="199"/>
       <c r="F14" s="89"/>
-      <c r="G14" s="637" t="s">
+      <c r="G14" s="720" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="638"/>
-      <c r="I14" s="639"/>
-      <c r="J14" s="640"/>
-      <c r="K14" s="641"/>
-      <c r="L14" s="633"/>
-      <c r="M14" s="633"/>
-      <c r="N14" s="633"/>
-      <c r="O14" s="633"/>
-      <c r="P14" s="633"/>
-      <c r="Q14" s="633"/>
-      <c r="R14" s="633"/>
-      <c r="S14" s="633"/>
-      <c r="T14" s="633"/>
-      <c r="U14" s="633"/>
-      <c r="V14" s="633"/>
-      <c r="W14" s="639"/>
-      <c r="X14" s="633"/>
-      <c r="Y14" s="669"/>
+      <c r="H14" s="721"/>
+      <c r="I14" s="698"/>
+      <c r="J14" s="722"/>
+      <c r="K14" s="723"/>
+      <c r="L14" s="696"/>
+      <c r="M14" s="696"/>
+      <c r="N14" s="696"/>
+      <c r="O14" s="696"/>
+      <c r="P14" s="696"/>
+      <c r="Q14" s="696"/>
+      <c r="R14" s="696"/>
+      <c r="S14" s="696"/>
+      <c r="T14" s="696"/>
+      <c r="U14" s="696"/>
+      <c r="V14" s="696"/>
+      <c r="W14" s="698"/>
+      <c r="X14" s="696"/>
+      <c r="Y14" s="697"/>
       <c r="Z14" s="80"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
@@ -31743,27 +31743,27 @@
       <c r="D15" s="186"/>
       <c r="E15" s="200"/>
       <c r="F15" s="89"/>
-      <c r="G15" s="637" t="s">
+      <c r="G15" s="720" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="638"/>
-      <c r="I15" s="639"/>
-      <c r="J15" s="640"/>
-      <c r="K15" s="641"/>
-      <c r="L15" s="633"/>
-      <c r="M15" s="633"/>
-      <c r="N15" s="633"/>
-      <c r="O15" s="633"/>
-      <c r="P15" s="633"/>
-      <c r="Q15" s="633"/>
-      <c r="R15" s="633"/>
-      <c r="S15" s="633"/>
-      <c r="T15" s="633"/>
-      <c r="U15" s="633"/>
-      <c r="V15" s="633"/>
-      <c r="W15" s="639"/>
-      <c r="X15" s="633"/>
-      <c r="Y15" s="669"/>
+      <c r="H15" s="721"/>
+      <c r="I15" s="698"/>
+      <c r="J15" s="722"/>
+      <c r="K15" s="723"/>
+      <c r="L15" s="696"/>
+      <c r="M15" s="696"/>
+      <c r="N15" s="696"/>
+      <c r="O15" s="696"/>
+      <c r="P15" s="696"/>
+      <c r="Q15" s="696"/>
+      <c r="R15" s="696"/>
+      <c r="S15" s="696"/>
+      <c r="T15" s="696"/>
+      <c r="U15" s="696"/>
+      <c r="V15" s="696"/>
+      <c r="W15" s="698"/>
+      <c r="X15" s="696"/>
+      <c r="Y15" s="697"/>
       <c r="Z15" s="80"/>
       <c r="AA15" s="103"/>
     </row>
@@ -31774,61 +31774,61 @@
       <c r="D16" s="106"/>
       <c r="E16" s="106"/>
       <c r="F16" s="79"/>
-      <c r="G16" s="637" t="s">
+      <c r="G16" s="720" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="638"/>
-      <c r="I16" s="639"/>
-      <c r="J16" s="640"/>
-      <c r="K16" s="641"/>
-      <c r="L16" s="633"/>
-      <c r="M16" s="633"/>
-      <c r="N16" s="633"/>
-      <c r="O16" s="633"/>
-      <c r="P16" s="633"/>
-      <c r="Q16" s="633"/>
-      <c r="R16" s="633"/>
-      <c r="S16" s="633"/>
-      <c r="T16" s="633"/>
-      <c r="U16" s="633"/>
-      <c r="V16" s="633"/>
-      <c r="W16" s="639"/>
-      <c r="X16" s="633"/>
-      <c r="Y16" s="669"/>
+      <c r="H16" s="721"/>
+      <c r="I16" s="698"/>
+      <c r="J16" s="722"/>
+      <c r="K16" s="723"/>
+      <c r="L16" s="696"/>
+      <c r="M16" s="696"/>
+      <c r="N16" s="696"/>
+      <c r="O16" s="696"/>
+      <c r="P16" s="696"/>
+      <c r="Q16" s="696"/>
+      <c r="R16" s="696"/>
+      <c r="S16" s="696"/>
+      <c r="T16" s="696"/>
+      <c r="U16" s="696"/>
+      <c r="V16" s="696"/>
+      <c r="W16" s="698"/>
+      <c r="X16" s="696"/>
+      <c r="Y16" s="697"/>
       <c r="Z16" s="80"/>
       <c r="AA16" s="103"/>
       <c r="AB16" s="194"/>
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="79"/>
-      <c r="B17" s="651" t="s">
+      <c r="B17" s="733" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="652"/>
-      <c r="D17" s="652"/>
-      <c r="E17" s="653"/>
+      <c r="C17" s="734"/>
+      <c r="D17" s="734"/>
+      <c r="E17" s="735"/>
       <c r="F17" s="89"/>
-      <c r="G17" s="637" t="s">
+      <c r="G17" s="720" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="638"/>
-      <c r="I17" s="639"/>
-      <c r="J17" s="640"/>
-      <c r="K17" s="641"/>
-      <c r="L17" s="633"/>
-      <c r="M17" s="633"/>
-      <c r="N17" s="633"/>
-      <c r="O17" s="633"/>
-      <c r="P17" s="633"/>
-      <c r="Q17" s="633"/>
-      <c r="R17" s="633"/>
-      <c r="S17" s="633"/>
-      <c r="T17" s="633"/>
-      <c r="U17" s="633"/>
-      <c r="V17" s="633"/>
-      <c r="W17" s="639"/>
-      <c r="X17" s="633"/>
-      <c r="Y17" s="669"/>
+      <c r="H17" s="721"/>
+      <c r="I17" s="698"/>
+      <c r="J17" s="722"/>
+      <c r="K17" s="723"/>
+      <c r="L17" s="696"/>
+      <c r="M17" s="696"/>
+      <c r="N17" s="696"/>
+      <c r="O17" s="696"/>
+      <c r="P17" s="696"/>
+      <c r="Q17" s="696"/>
+      <c r="R17" s="696"/>
+      <c r="S17" s="696"/>
+      <c r="T17" s="696"/>
+      <c r="U17" s="696"/>
+      <c r="V17" s="696"/>
+      <c r="W17" s="698"/>
+      <c r="X17" s="696"/>
+      <c r="Y17" s="697"/>
       <c r="Z17" s="80"/>
       <c r="AA17" s="103"/>
     </row>
@@ -31847,27 +31847,27 @@
         <v>91</v>
       </c>
       <c r="F18" s="89"/>
-      <c r="G18" s="637" t="s">
+      <c r="G18" s="720" t="s">
         <v>157</v>
       </c>
-      <c r="H18" s="638"/>
-      <c r="I18" s="639"/>
-      <c r="J18" s="640"/>
-      <c r="K18" s="641"/>
-      <c r="L18" s="633"/>
-      <c r="M18" s="633"/>
-      <c r="N18" s="633"/>
-      <c r="O18" s="633"/>
-      <c r="P18" s="633"/>
-      <c r="Q18" s="633"/>
-      <c r="R18" s="633"/>
-      <c r="S18" s="633"/>
-      <c r="T18" s="633"/>
-      <c r="U18" s="633"/>
-      <c r="V18" s="633"/>
-      <c r="W18" s="639"/>
-      <c r="X18" s="633"/>
-      <c r="Y18" s="669"/>
+      <c r="H18" s="721"/>
+      <c r="I18" s="698"/>
+      <c r="J18" s="722"/>
+      <c r="K18" s="723"/>
+      <c r="L18" s="696"/>
+      <c r="M18" s="696"/>
+      <c r="N18" s="696"/>
+      <c r="O18" s="696"/>
+      <c r="P18" s="696"/>
+      <c r="Q18" s="696"/>
+      <c r="R18" s="696"/>
+      <c r="S18" s="696"/>
+      <c r="T18" s="696"/>
+      <c r="U18" s="696"/>
+      <c r="V18" s="696"/>
+      <c r="W18" s="698"/>
+      <c r="X18" s="696"/>
+      <c r="Y18" s="697"/>
       <c r="Z18" s="80"/>
       <c r="AA18" s="103"/>
     </row>
@@ -31878,27 +31878,27 @@
       <c r="D19" s="506"/>
       <c r="E19" s="201"/>
       <c r="F19" s="89"/>
-      <c r="G19" s="637" t="s">
+      <c r="G19" s="720" t="s">
         <v>158</v>
       </c>
-      <c r="H19" s="638"/>
-      <c r="I19" s="639"/>
-      <c r="J19" s="640"/>
-      <c r="K19" s="641"/>
-      <c r="L19" s="633"/>
-      <c r="M19" s="633"/>
-      <c r="N19" s="633"/>
-      <c r="O19" s="633"/>
-      <c r="P19" s="633"/>
-      <c r="Q19" s="633"/>
-      <c r="R19" s="633"/>
-      <c r="S19" s="633"/>
-      <c r="T19" s="633"/>
-      <c r="U19" s="633"/>
-      <c r="V19" s="633"/>
-      <c r="W19" s="639"/>
-      <c r="X19" s="633"/>
-      <c r="Y19" s="669"/>
+      <c r="H19" s="721"/>
+      <c r="I19" s="698"/>
+      <c r="J19" s="722"/>
+      <c r="K19" s="723"/>
+      <c r="L19" s="696"/>
+      <c r="M19" s="696"/>
+      <c r="N19" s="696"/>
+      <c r="O19" s="696"/>
+      <c r="P19" s="696"/>
+      <c r="Q19" s="696"/>
+      <c r="R19" s="696"/>
+      <c r="S19" s="696"/>
+      <c r="T19" s="696"/>
+      <c r="U19" s="696"/>
+      <c r="V19" s="696"/>
+      <c r="W19" s="698"/>
+      <c r="X19" s="696"/>
+      <c r="Y19" s="697"/>
       <c r="Z19" s="80"/>
       <c r="AA19" s="103"/>
     </row>
@@ -31909,27 +31909,27 @@
       <c r="D20" s="506"/>
       <c r="E20" s="201"/>
       <c r="F20" s="89"/>
-      <c r="G20" s="637" t="s">
+      <c r="G20" s="720" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="638"/>
-      <c r="I20" s="639"/>
-      <c r="J20" s="640"/>
-      <c r="K20" s="641"/>
-      <c r="L20" s="633"/>
-      <c r="M20" s="633"/>
-      <c r="N20" s="633"/>
-      <c r="O20" s="633"/>
-      <c r="P20" s="633"/>
-      <c r="Q20" s="633"/>
-      <c r="R20" s="633"/>
-      <c r="S20" s="633"/>
-      <c r="T20" s="633"/>
-      <c r="U20" s="633"/>
-      <c r="V20" s="633"/>
-      <c r="W20" s="639"/>
-      <c r="X20" s="633"/>
-      <c r="Y20" s="669"/>
+      <c r="H20" s="721"/>
+      <c r="I20" s="698"/>
+      <c r="J20" s="722"/>
+      <c r="K20" s="723"/>
+      <c r="L20" s="696"/>
+      <c r="M20" s="696"/>
+      <c r="N20" s="696"/>
+      <c r="O20" s="696"/>
+      <c r="P20" s="696"/>
+      <c r="Q20" s="696"/>
+      <c r="R20" s="696"/>
+      <c r="S20" s="696"/>
+      <c r="T20" s="696"/>
+      <c r="U20" s="696"/>
+      <c r="V20" s="696"/>
+      <c r="W20" s="698"/>
+      <c r="X20" s="696"/>
+      <c r="Y20" s="697"/>
       <c r="Z20" s="80"/>
       <c r="AA20" s="103"/>
     </row>
@@ -31940,27 +31940,27 @@
       <c r="D21" s="506"/>
       <c r="E21" s="201"/>
       <c r="F21" s="89"/>
-      <c r="G21" s="637" t="s">
+      <c r="G21" s="720" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="638"/>
-      <c r="I21" s="639"/>
-      <c r="J21" s="640"/>
-      <c r="K21" s="641"/>
-      <c r="L21" s="633"/>
-      <c r="M21" s="633"/>
-      <c r="N21" s="633"/>
-      <c r="O21" s="633"/>
-      <c r="P21" s="633"/>
-      <c r="Q21" s="633"/>
-      <c r="R21" s="633"/>
-      <c r="S21" s="633"/>
-      <c r="T21" s="633"/>
-      <c r="U21" s="633"/>
-      <c r="V21" s="633"/>
-      <c r="W21" s="639"/>
-      <c r="X21" s="633"/>
-      <c r="Y21" s="669"/>
+      <c r="H21" s="721"/>
+      <c r="I21" s="698"/>
+      <c r="J21" s="722"/>
+      <c r="K21" s="723"/>
+      <c r="L21" s="696"/>
+      <c r="M21" s="696"/>
+      <c r="N21" s="696"/>
+      <c r="O21" s="696"/>
+      <c r="P21" s="696"/>
+      <c r="Q21" s="696"/>
+      <c r="R21" s="696"/>
+      <c r="S21" s="696"/>
+      <c r="T21" s="696"/>
+      <c r="U21" s="696"/>
+      <c r="V21" s="696"/>
+      <c r="W21" s="698"/>
+      <c r="X21" s="696"/>
+      <c r="Y21" s="697"/>
       <c r="Z21" s="80"/>
       <c r="AA21" s="103"/>
     </row>
@@ -31971,27 +31971,27 @@
       <c r="D22" s="506"/>
       <c r="E22" s="201"/>
       <c r="F22" s="89"/>
-      <c r="G22" s="637" t="s">
+      <c r="G22" s="720" t="s">
         <v>159</v>
       </c>
-      <c r="H22" s="638"/>
-      <c r="I22" s="639"/>
-      <c r="J22" s="640"/>
-      <c r="K22" s="641"/>
-      <c r="L22" s="633"/>
-      <c r="M22" s="633"/>
-      <c r="N22" s="633"/>
-      <c r="O22" s="633"/>
-      <c r="P22" s="633"/>
-      <c r="Q22" s="633"/>
-      <c r="R22" s="633"/>
-      <c r="S22" s="633"/>
-      <c r="T22" s="633"/>
-      <c r="U22" s="633"/>
-      <c r="V22" s="633"/>
-      <c r="W22" s="639"/>
-      <c r="X22" s="633"/>
-      <c r="Y22" s="669"/>
+      <c r="H22" s="721"/>
+      <c r="I22" s="698"/>
+      <c r="J22" s="722"/>
+      <c r="K22" s="723"/>
+      <c r="L22" s="696"/>
+      <c r="M22" s="696"/>
+      <c r="N22" s="696"/>
+      <c r="O22" s="696"/>
+      <c r="P22" s="696"/>
+      <c r="Q22" s="696"/>
+      <c r="R22" s="696"/>
+      <c r="S22" s="696"/>
+      <c r="T22" s="696"/>
+      <c r="U22" s="696"/>
+      <c r="V22" s="696"/>
+      <c r="W22" s="698"/>
+      <c r="X22" s="696"/>
+      <c r="Y22" s="697"/>
       <c r="Z22" s="80"/>
       <c r="AA22" s="103"/>
     </row>
@@ -32002,48 +32002,48 @@
       <c r="D23" s="507"/>
       <c r="E23" s="202"/>
       <c r="F23" s="89"/>
-      <c r="G23" s="680" t="s">
+      <c r="G23" s="708" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="672"/>
-      <c r="I23" s="672">
+      <c r="H23" s="700"/>
+      <c r="I23" s="700">
         <f>SUM(I14:K22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="672"/>
-      <c r="K23" s="672"/>
-      <c r="L23" s="672">
+      <c r="J23" s="700"/>
+      <c r="K23" s="700"/>
+      <c r="L23" s="700">
         <f>SUM(L14:N22)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="672"/>
-      <c r="N23" s="672"/>
-      <c r="O23" s="677">
+      <c r="M23" s="700"/>
+      <c r="N23" s="700"/>
+      <c r="O23" s="705">
         <f>SUM(O14:Q22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="678"/>
-      <c r="Q23" s="679"/>
-      <c r="R23" s="677">
+      <c r="P23" s="706"/>
+      <c r="Q23" s="707"/>
+      <c r="R23" s="705">
         <f>SUM(R14:S22)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="679"/>
-      <c r="T23" s="677">
+      <c r="S23" s="707"/>
+      <c r="T23" s="705">
         <f>SUM(T14:U22)</f>
         <v>0</v>
       </c>
-      <c r="U23" s="679"/>
-      <c r="V23" s="677">
+      <c r="U23" s="707"/>
+      <c r="V23" s="705">
         <f>SUM(V14:W22)</f>
         <v>0</v>
       </c>
-      <c r="W23" s="678"/>
-      <c r="X23" s="672">
+      <c r="W23" s="706"/>
+      <c r="X23" s="700">
         <f>SUM(X14:Y22)</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="673"/>
+      <c r="Y23" s="701"/>
       <c r="Z23" s="80"/>
       <c r="AA23" s="103"/>
     </row>
@@ -32113,28 +32113,28 @@
       <c r="E26" s="82"/>
       <c r="F26" s="79"/>
       <c r="G26" s="135"/>
-      <c r="H26" s="717" t="s">
+      <c r="H26" s="663" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="718"/>
-      <c r="J26" s="719"/>
+      <c r="I26" s="664"/>
+      <c r="J26" s="665"/>
       <c r="K26" s="89"/>
-      <c r="L26" s="723" t="s">
+      <c r="L26" s="672" t="s">
         <v>96</v>
       </c>
-      <c r="M26" s="724"/>
-      <c r="N26" s="724"/>
-      <c r="O26" s="724"/>
-      <c r="P26" s="724"/>
-      <c r="Q26" s="724"/>
-      <c r="R26" s="724"/>
-      <c r="S26" s="724"/>
-      <c r="T26" s="724"/>
-      <c r="U26" s="724"/>
-      <c r="V26" s="724"/>
-      <c r="W26" s="724"/>
-      <c r="X26" s="724"/>
-      <c r="Y26" s="725"/>
+      <c r="M26" s="673"/>
+      <c r="N26" s="673"/>
+      <c r="O26" s="673"/>
+      <c r="P26" s="673"/>
+      <c r="Q26" s="673"/>
+      <c r="R26" s="673"/>
+      <c r="S26" s="673"/>
+      <c r="T26" s="673"/>
+      <c r="U26" s="673"/>
+      <c r="V26" s="673"/>
+      <c r="W26" s="673"/>
+      <c r="X26" s="673"/>
+      <c r="Y26" s="674"/>
       <c r="Z26" s="80"/>
       <c r="AA26" s="103"/>
     </row>
@@ -32146,41 +32146,41 @@
       <c r="E27" s="82"/>
       <c r="F27" s="79"/>
       <c r="G27" s="136"/>
-      <c r="H27" s="714">
+      <c r="H27" s="645">
         <f>Y38</f>
         <v>0</v>
       </c>
-      <c r="I27" s="715"/>
-      <c r="J27" s="716"/>
+      <c r="I27" s="646"/>
+      <c r="J27" s="647"/>
       <c r="K27" s="89"/>
-      <c r="L27" s="688" t="s">
+      <c r="L27" s="694" t="s">
         <v>80</v>
       </c>
-      <c r="M27" s="636"/>
-      <c r="N27" s="636"/>
-      <c r="O27" s="636" t="s">
+      <c r="M27" s="668"/>
+      <c r="N27" s="668"/>
+      <c r="O27" s="668" t="s">
         <v>97</v>
       </c>
-      <c r="P27" s="636"/>
-      <c r="Q27" s="636" t="s">
+      <c r="P27" s="668"/>
+      <c r="Q27" s="668" t="s">
         <v>98</v>
       </c>
-      <c r="R27" s="636"/>
-      <c r="S27" s="636" t="s">
+      <c r="R27" s="668"/>
+      <c r="S27" s="668" t="s">
         <v>99</v>
       </c>
-      <c r="T27" s="636" t="s">
+      <c r="T27" s="668" t="s">
         <v>100</v>
       </c>
-      <c r="U27" s="636"/>
-      <c r="V27" s="636" t="s">
+      <c r="U27" s="668"/>
+      <c r="V27" s="668" t="s">
         <v>101</v>
       </c>
-      <c r="W27" s="636" t="s">
+      <c r="W27" s="668" t="s">
         <v>102</v>
       </c>
-      <c r="X27" s="636"/>
-      <c r="Y27" s="657" t="s">
+      <c r="X27" s="668"/>
+      <c r="Y27" s="699" t="s">
         <v>88</v>
       </c>
       <c r="Z27" s="80"/>
@@ -32198,20 +32198,20 @@
       <c r="I28" s="82"/>
       <c r="J28" s="165"/>
       <c r="K28" s="89"/>
-      <c r="L28" s="688"/>
-      <c r="M28" s="636"/>
-      <c r="N28" s="636"/>
-      <c r="O28" s="636"/>
-      <c r="P28" s="636"/>
-      <c r="Q28" s="636"/>
-      <c r="R28" s="636"/>
-      <c r="S28" s="636"/>
-      <c r="T28" s="636"/>
-      <c r="U28" s="636"/>
-      <c r="V28" s="636"/>
-      <c r="W28" s="636"/>
-      <c r="X28" s="636"/>
-      <c r="Y28" s="657"/>
+      <c r="L28" s="694"/>
+      <c r="M28" s="668"/>
+      <c r="N28" s="668"/>
+      <c r="O28" s="668"/>
+      <c r="P28" s="668"/>
+      <c r="Q28" s="668"/>
+      <c r="R28" s="668"/>
+      <c r="S28" s="668"/>
+      <c r="T28" s="668"/>
+      <c r="U28" s="668"/>
+      <c r="V28" s="668"/>
+      <c r="W28" s="668"/>
+      <c r="X28" s="668"/>
+      <c r="Y28" s="699"/>
       <c r="Z28" s="80"/>
       <c r="AA28" s="103"/>
     </row>
@@ -32227,21 +32227,21 @@
       <c r="I29" s="166"/>
       <c r="J29" s="138"/>
       <c r="K29" s="89"/>
-      <c r="L29" s="685" t="s">
+      <c r="L29" s="680" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="686"/>
-      <c r="N29" s="686"/>
-      <c r="O29" s="686"/>
-      <c r="P29" s="686"/>
-      <c r="Q29" s="686"/>
-      <c r="R29" s="686"/>
+      <c r="M29" s="648"/>
+      <c r="N29" s="648"/>
+      <c r="O29" s="648"/>
+      <c r="P29" s="648"/>
+      <c r="Q29" s="648"/>
+      <c r="R29" s="648"/>
       <c r="S29" s="71"/>
-      <c r="T29" s="686"/>
-      <c r="U29" s="686"/>
+      <c r="T29" s="648"/>
+      <c r="U29" s="648"/>
       <c r="V29" s="71"/>
-      <c r="W29" s="686"/>
-      <c r="X29" s="687"/>
+      <c r="W29" s="648"/>
+      <c r="X29" s="649"/>
       <c r="Y29" s="195"/>
       <c r="Z29" s="80"/>
       <c r="AA29" s="103"/>
@@ -32258,21 +32258,21 @@
       <c r="I30" s="106"/>
       <c r="J30" s="106"/>
       <c r="K30" s="79"/>
-      <c r="L30" s="685" t="s">
+      <c r="L30" s="680" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="686"/>
-      <c r="N30" s="686"/>
-      <c r="O30" s="686"/>
-      <c r="P30" s="686"/>
-      <c r="Q30" s="686"/>
-      <c r="R30" s="686"/>
+      <c r="M30" s="648"/>
+      <c r="N30" s="648"/>
+      <c r="O30" s="648"/>
+      <c r="P30" s="648"/>
+      <c r="Q30" s="648"/>
+      <c r="R30" s="648"/>
       <c r="S30" s="71"/>
-      <c r="T30" s="686"/>
-      <c r="U30" s="686"/>
+      <c r="T30" s="648"/>
+      <c r="U30" s="648"/>
       <c r="V30" s="71"/>
-      <c r="W30" s="686"/>
-      <c r="X30" s="687"/>
+      <c r="W30" s="648"/>
+      <c r="X30" s="649"/>
       <c r="Y30" s="195"/>
       <c r="Z30" s="80"/>
       <c r="AA30" s="79"/>
@@ -32285,27 +32285,27 @@
       <c r="E31" s="82"/>
       <c r="F31" s="79"/>
       <c r="G31" s="135"/>
-      <c r="H31" s="720" t="s">
+      <c r="H31" s="669" t="s">
         <v>93</v>
       </c>
-      <c r="I31" s="721"/>
-      <c r="J31" s="722"/>
+      <c r="I31" s="670"/>
+      <c r="J31" s="671"/>
       <c r="K31" s="89"/>
-      <c r="L31" s="685" t="s">
+      <c r="L31" s="680" t="s">
         <v>19</v>
       </c>
-      <c r="M31" s="686"/>
-      <c r="N31" s="686"/>
-      <c r="O31" s="686"/>
-      <c r="P31" s="686"/>
-      <c r="Q31" s="686"/>
-      <c r="R31" s="686"/>
+      <c r="M31" s="648"/>
+      <c r="N31" s="648"/>
+      <c r="O31" s="648"/>
+      <c r="P31" s="648"/>
+      <c r="Q31" s="648"/>
+      <c r="R31" s="648"/>
       <c r="S31" s="71"/>
-      <c r="T31" s="686"/>
-      <c r="U31" s="686"/>
+      <c r="T31" s="648"/>
+      <c r="U31" s="648"/>
       <c r="V31" s="71"/>
-      <c r="W31" s="686"/>
-      <c r="X31" s="687"/>
+      <c r="W31" s="648"/>
+      <c r="X31" s="649"/>
       <c r="Y31" s="195"/>
       <c r="Z31" s="80"/>
       <c r="AA31" s="79"/>
@@ -32322,21 +32322,21 @@
       <c r="I32" s="82"/>
       <c r="J32" s="165"/>
       <c r="K32" s="89"/>
-      <c r="L32" s="685" t="s">
+      <c r="L32" s="680" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="686"/>
-      <c r="N32" s="686"/>
-      <c r="O32" s="686"/>
-      <c r="P32" s="686"/>
-      <c r="Q32" s="686"/>
-      <c r="R32" s="686"/>
+      <c r="M32" s="648"/>
+      <c r="N32" s="648"/>
+      <c r="O32" s="648"/>
+      <c r="P32" s="648"/>
+      <c r="Q32" s="648"/>
+      <c r="R32" s="648"/>
       <c r="S32" s="71"/>
-      <c r="T32" s="686"/>
-      <c r="U32" s="686"/>
+      <c r="T32" s="648"/>
+      <c r="U32" s="648"/>
       <c r="V32" s="71"/>
-      <c r="W32" s="686"/>
-      <c r="X32" s="687"/>
+      <c r="W32" s="648"/>
+      <c r="X32" s="649"/>
       <c r="Y32" s="195"/>
       <c r="Z32" s="80"/>
       <c r="AA32" s="79"/>
@@ -32349,28 +32349,28 @@
       <c r="E33" s="82"/>
       <c r="F33" s="79"/>
       <c r="G33" s="136"/>
-      <c r="H33" s="714">
+      <c r="H33" s="645">
         <f>O38</f>
         <v>0</v>
       </c>
-      <c r="I33" s="715"/>
-      <c r="J33" s="716"/>
+      <c r="I33" s="646"/>
+      <c r="J33" s="647"/>
       <c r="K33" s="89"/>
-      <c r="L33" s="685" t="s">
+      <c r="L33" s="680" t="s">
         <v>157</v>
       </c>
-      <c r="M33" s="686"/>
-      <c r="N33" s="686"/>
-      <c r="O33" s="686"/>
-      <c r="P33" s="686"/>
-      <c r="Q33" s="686"/>
-      <c r="R33" s="686"/>
+      <c r="M33" s="648"/>
+      <c r="N33" s="648"/>
+      <c r="O33" s="648"/>
+      <c r="P33" s="648"/>
+      <c r="Q33" s="648"/>
+      <c r="R33" s="648"/>
       <c r="S33" s="71"/>
-      <c r="T33" s="686"/>
-      <c r="U33" s="686"/>
+      <c r="T33" s="648"/>
+      <c r="U33" s="648"/>
       <c r="V33" s="71"/>
-      <c r="W33" s="686"/>
-      <c r="X33" s="687"/>
+      <c r="W33" s="648"/>
+      <c r="X33" s="649"/>
       <c r="Y33" s="195"/>
       <c r="Z33" s="80"/>
       <c r="AA33" s="193"/>
@@ -32387,21 +32387,21 @@
       <c r="I34" s="82"/>
       <c r="J34" s="165"/>
       <c r="K34" s="89"/>
-      <c r="L34" s="685" t="s">
+      <c r="L34" s="680" t="s">
         <v>158</v>
       </c>
-      <c r="M34" s="686"/>
-      <c r="N34" s="686"/>
-      <c r="O34" s="686"/>
-      <c r="P34" s="686"/>
-      <c r="Q34" s="686"/>
-      <c r="R34" s="686"/>
+      <c r="M34" s="648"/>
+      <c r="N34" s="648"/>
+      <c r="O34" s="648"/>
+      <c r="P34" s="648"/>
+      <c r="Q34" s="648"/>
+      <c r="R34" s="648"/>
       <c r="S34" s="71"/>
-      <c r="T34" s="686"/>
-      <c r="U34" s="686"/>
+      <c r="T34" s="648"/>
+      <c r="U34" s="648"/>
       <c r="V34" s="71"/>
-      <c r="W34" s="686"/>
-      <c r="X34" s="687"/>
+      <c r="W34" s="648"/>
+      <c r="X34" s="649"/>
       <c r="Y34" s="195"/>
       <c r="Z34" s="80"/>
       <c r="AA34" s="79"/>
@@ -32418,21 +32418,21 @@
       <c r="I35" s="166"/>
       <c r="J35" s="138"/>
       <c r="K35" s="89"/>
-      <c r="L35" s="685" t="s">
+      <c r="L35" s="680" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="686"/>
-      <c r="N35" s="686"/>
-      <c r="O35" s="689"/>
-      <c r="P35" s="689"/>
-      <c r="Q35" s="689"/>
-      <c r="R35" s="689"/>
+      <c r="M35" s="648"/>
+      <c r="N35" s="648"/>
+      <c r="O35" s="675"/>
+      <c r="P35" s="675"/>
+      <c r="Q35" s="675"/>
+      <c r="R35" s="675"/>
       <c r="S35" s="162"/>
-      <c r="T35" s="689"/>
-      <c r="U35" s="689"/>
+      <c r="T35" s="675"/>
+      <c r="U35" s="675"/>
       <c r="V35" s="162"/>
-      <c r="W35" s="689"/>
-      <c r="X35" s="690"/>
+      <c r="W35" s="675"/>
+      <c r="X35" s="695"/>
       <c r="Y35" s="195"/>
       <c r="Z35" s="80"/>
       <c r="AA35" s="103"/>
@@ -32449,21 +32449,21 @@
       <c r="I36" s="106"/>
       <c r="J36" s="106"/>
       <c r="K36" s="79"/>
-      <c r="L36" s="685" t="s">
+      <c r="L36" s="680" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="686"/>
-      <c r="N36" s="687"/>
-      <c r="O36" s="691"/>
-      <c r="P36" s="691"/>
-      <c r="Q36" s="691"/>
-      <c r="R36" s="691"/>
+      <c r="M36" s="648"/>
+      <c r="N36" s="649"/>
+      <c r="O36" s="652"/>
+      <c r="P36" s="652"/>
+      <c r="Q36" s="652"/>
+      <c r="R36" s="652"/>
       <c r="S36" s="163"/>
-      <c r="T36" s="691"/>
-      <c r="U36" s="691"/>
+      <c r="T36" s="652"/>
+      <c r="U36" s="652"/>
       <c r="V36" s="163"/>
-      <c r="W36" s="691"/>
-      <c r="X36" s="692"/>
+      <c r="W36" s="652"/>
+      <c r="X36" s="676"/>
       <c r="Y36" s="195"/>
       <c r="Z36" s="80"/>
       <c r="AA36" s="79"/>
@@ -32476,27 +32476,27 @@
       <c r="E37" s="82"/>
       <c r="F37" s="79"/>
       <c r="G37" s="135"/>
-      <c r="H37" s="720" t="s">
+      <c r="H37" s="669" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="721"/>
-      <c r="J37" s="722"/>
+      <c r="I37" s="670"/>
+      <c r="J37" s="671"/>
       <c r="K37" s="89"/>
-      <c r="L37" s="685" t="s">
+      <c r="L37" s="680" t="s">
         <v>159</v>
       </c>
-      <c r="M37" s="686"/>
-      <c r="N37" s="687"/>
-      <c r="O37" s="691"/>
-      <c r="P37" s="691"/>
-      <c r="Q37" s="691"/>
-      <c r="R37" s="691"/>
+      <c r="M37" s="648"/>
+      <c r="N37" s="649"/>
+      <c r="O37" s="652"/>
+      <c r="P37" s="652"/>
+      <c r="Q37" s="652"/>
+      <c r="R37" s="652"/>
       <c r="S37" s="163"/>
-      <c r="T37" s="691"/>
-      <c r="U37" s="691"/>
+      <c r="T37" s="652"/>
+      <c r="U37" s="652"/>
       <c r="V37" s="163"/>
-      <c r="W37" s="691"/>
-      <c r="X37" s="692"/>
+      <c r="W37" s="652"/>
+      <c r="X37" s="676"/>
       <c r="Y37" s="195"/>
       <c r="Z37" s="80"/>
     </row>
@@ -32512,39 +32512,39 @@
       <c r="I38" s="82"/>
       <c r="J38" s="165"/>
       <c r="K38" s="89"/>
-      <c r="L38" s="704" t="s">
+      <c r="L38" s="688" t="s">
         <v>88</v>
       </c>
-      <c r="M38" s="705"/>
-      <c r="N38" s="706"/>
-      <c r="O38" s="693">
+      <c r="M38" s="689"/>
+      <c r="N38" s="690"/>
+      <c r="O38" s="653">
         <f>SUM(O29:P37)</f>
         <v>0</v>
       </c>
-      <c r="P38" s="693"/>
-      <c r="Q38" s="693">
+      <c r="P38" s="653"/>
+      <c r="Q38" s="653">
         <f>SUM(Q29:R37)</f>
         <v>0</v>
       </c>
-      <c r="R38" s="693"/>
+      <c r="R38" s="653"/>
       <c r="S38" s="196">
         <f>SUM(S29:S37)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="693">
+      <c r="T38" s="653">
         <f>SUM(T29:U37)</f>
         <v>0</v>
       </c>
-      <c r="U38" s="693"/>
+      <c r="U38" s="653"/>
       <c r="V38" s="196">
         <f>SUM(V29:V37)</f>
         <v>0</v>
       </c>
-      <c r="W38" s="693">
+      <c r="W38" s="653">
         <f>SUM(W29:X37)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="693"/>
+      <c r="X38" s="653"/>
       <c r="Y38" s="197">
         <f>SUM(Y29:Y37)</f>
         <v>0</v>
@@ -32560,26 +32560,26 @@
       <c r="E39" s="82"/>
       <c r="F39" s="79"/>
       <c r="G39" s="136"/>
-      <c r="H39" s="714">
+      <c r="H39" s="645">
         <f>S38</f>
         <v>0</v>
       </c>
-      <c r="I39" s="715"/>
-      <c r="J39" s="716"/>
+      <c r="I39" s="646"/>
+      <c r="J39" s="647"/>
       <c r="K39" s="89"/>
-      <c r="L39" s="699"/>
-      <c r="M39" s="707"/>
-      <c r="N39" s="708"/>
-      <c r="O39" s="699"/>
-      <c r="P39" s="700"/>
-      <c r="Q39" s="712"/>
-      <c r="R39" s="713"/>
+      <c r="L39" s="683"/>
+      <c r="M39" s="691"/>
+      <c r="N39" s="692"/>
+      <c r="O39" s="683"/>
+      <c r="P39" s="684"/>
+      <c r="Q39" s="666"/>
+      <c r="R39" s="667"/>
       <c r="S39" s="104"/>
-      <c r="T39" s="740"/>
-      <c r="U39" s="740"/>
+      <c r="T39" s="654"/>
+      <c r="U39" s="654"/>
       <c r="V39" s="104"/>
-      <c r="W39" s="740"/>
-      <c r="X39" s="740"/>
+      <c r="W39" s="654"/>
+      <c r="X39" s="654"/>
       <c r="Y39" s="132"/>
       <c r="Z39" s="82"/>
       <c r="AA39" s="79"/>
@@ -32596,19 +32596,19 @@
       <c r="I40" s="82"/>
       <c r="J40" s="165"/>
       <c r="K40" s="89"/>
-      <c r="L40" s="709"/>
-      <c r="M40" s="710"/>
-      <c r="N40" s="711"/>
-      <c r="O40" s="701"/>
-      <c r="P40" s="698"/>
-      <c r="Q40" s="697"/>
-      <c r="R40" s="698"/>
+      <c r="L40" s="656"/>
+      <c r="M40" s="693"/>
+      <c r="N40" s="657"/>
+      <c r="O40" s="685"/>
+      <c r="P40" s="682"/>
+      <c r="Q40" s="681"/>
+      <c r="R40" s="682"/>
       <c r="S40" s="82"/>
-      <c r="T40" s="741"/>
-      <c r="U40" s="741"/>
+      <c r="T40" s="655"/>
+      <c r="U40" s="655"/>
       <c r="V40" s="82"/>
-      <c r="W40" s="741"/>
-      <c r="X40" s="741"/>
+      <c r="W40" s="655"/>
+      <c r="X40" s="655"/>
       <c r="Y40" s="140"/>
       <c r="Z40" s="82"/>
     </row>
@@ -32624,19 +32624,19 @@
       <c r="I41" s="166"/>
       <c r="J41" s="138"/>
       <c r="K41" s="89"/>
-      <c r="L41" s="709"/>
-      <c r="M41" s="710"/>
-      <c r="N41" s="711"/>
-      <c r="O41" s="702"/>
-      <c r="P41" s="703"/>
-      <c r="Q41" s="709"/>
-      <c r="R41" s="711"/>
+      <c r="L41" s="656"/>
+      <c r="M41" s="693"/>
+      <c r="N41" s="657"/>
+      <c r="O41" s="686"/>
+      <c r="P41" s="687"/>
+      <c r="Q41" s="656"/>
+      <c r="R41" s="657"/>
       <c r="S41" s="82"/>
-      <c r="T41" s="709"/>
-      <c r="U41" s="711"/>
+      <c r="T41" s="656"/>
+      <c r="U41" s="657"/>
       <c r="V41" s="82"/>
-      <c r="W41" s="709"/>
-      <c r="X41" s="711"/>
+      <c r="W41" s="656"/>
+      <c r="X41" s="657"/>
       <c r="Y41" s="140"/>
       <c r="Z41" s="82"/>
       <c r="AA41" s="103"/>
@@ -32653,21 +32653,21 @@
       <c r="I42" s="106"/>
       <c r="J42" s="106"/>
       <c r="K42" s="79"/>
-      <c r="L42" s="694"/>
-      <c r="M42" s="695"/>
-      <c r="N42" s="696"/>
-      <c r="O42" s="712"/>
-      <c r="P42" s="713"/>
+      <c r="L42" s="677"/>
+      <c r="M42" s="678"/>
+      <c r="N42" s="679"/>
+      <c r="O42" s="666"/>
+      <c r="P42" s="667"/>
       <c r="Q42" s="82"/>
-      <c r="R42" s="738" t="s">
+      <c r="R42" s="650" t="s">
         <v>127</v>
       </c>
-      <c r="S42" s="739"/>
+      <c r="S42" s="651"/>
       <c r="T42" s="105"/>
-      <c r="U42" s="742"/>
-      <c r="V42" s="743"/>
-      <c r="W42" s="742"/>
-      <c r="X42" s="743"/>
+      <c r="U42" s="658"/>
+      <c r="V42" s="659"/>
+      <c r="W42" s="658"/>
+      <c r="X42" s="659"/>
       <c r="Y42" s="140"/>
       <c r="Z42" s="82"/>
       <c r="AA42" s="79"/>
@@ -32680,19 +32680,19 @@
       <c r="E43" s="82"/>
       <c r="F43" s="79"/>
       <c r="G43" s="135"/>
-      <c r="H43" s="745" t="s">
+      <c r="H43" s="661" t="s">
         <v>104</v>
       </c>
-      <c r="I43" s="745"/>
-      <c r="J43" s="746"/>
+      <c r="I43" s="661"/>
+      <c r="J43" s="662"/>
       <c r="K43" s="89"/>
       <c r="L43" s="135"/>
       <c r="M43" s="164"/>
-      <c r="N43" s="729" t="s">
+      <c r="N43" s="636" t="s">
         <v>94</v>
       </c>
-      <c r="O43" s="730"/>
-      <c r="P43" s="731"/>
+      <c r="O43" s="637"/>
+      <c r="P43" s="638"/>
       <c r="Q43" s="136"/>
       <c r="R43" s="254" t="s">
         <v>128</v>
@@ -32746,21 +32746,21 @@
       <c r="E45" s="82"/>
       <c r="F45" s="79"/>
       <c r="G45" s="136"/>
-      <c r="H45" s="714">
+      <c r="H45" s="645">
         <f>SUM(V38)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="715"/>
-      <c r="J45" s="716"/>
+      <c r="I45" s="646"/>
+      <c r="J45" s="647"/>
       <c r="K45" s="89"/>
       <c r="L45" s="136"/>
       <c r="M45" s="82"/>
       <c r="N45" s="82"/>
-      <c r="O45" s="732">
+      <c r="O45" s="639">
         <f>SUM(Q38,T38,W38)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="733"/>
+      <c r="P45" s="640"/>
       <c r="Q45" s="136"/>
       <c r="R45" s="255" t="s">
         <v>129</v>
@@ -32792,8 +32792,8 @@
       <c r="L46" s="136"/>
       <c r="M46" s="82"/>
       <c r="N46" s="82"/>
-      <c r="O46" s="734"/>
-      <c r="P46" s="735"/>
+      <c r="O46" s="641"/>
+      <c r="P46" s="642"/>
       <c r="Q46" s="136"/>
       <c r="R46" s="256"/>
       <c r="S46" s="271"/>
@@ -32904,9 +32904,9 @@
       <c r="E50" s="82"/>
       <c r="F50" s="79"/>
       <c r="G50" s="167"/>
-      <c r="H50" s="736"/>
-      <c r="I50" s="736"/>
-      <c r="J50" s="737"/>
+      <c r="H50" s="643"/>
+      <c r="I50" s="643"/>
+      <c r="J50" s="644"/>
       <c r="K50" s="80"/>
       <c r="L50" s="104"/>
       <c r="M50" s="104"/>
@@ -32961,9 +32961,9 @@
       <c r="E52" s="82"/>
       <c r="F52" s="82"/>
       <c r="G52" s="82"/>
-      <c r="H52" s="744"/>
-      <c r="I52" s="744"/>
-      <c r="J52" s="744"/>
+      <c r="H52" s="660"/>
+      <c r="I52" s="660"/>
+      <c r="J52" s="660"/>
       <c r="K52" s="82"/>
       <c r="L52" s="82"/>
       <c r="M52" s="82"/>
@@ -33064,11 +33064,11 @@
       <c r="U55" s="79"/>
       <c r="V55" s="82"/>
       <c r="W55" s="82"/>
-      <c r="X55" s="726"/>
-      <c r="Y55" s="727"/>
-      <c r="Z55" s="727"/>
-      <c r="AA55" s="727"/>
-      <c r="AB55" s="728"/>
+      <c r="X55" s="633"/>
+      <c r="Y55" s="634"/>
+      <c r="Z55" s="634"/>
+      <c r="AA55" s="634"/>
+      <c r="AB55" s="635"/>
     </row>
     <row r="56" spans="1:28" ht="23.25" hidden="1">
       <c r="A56" s="82"/>
@@ -33284,11 +33284,11 @@
       <c r="P63" s="82"/>
       <c r="Q63" s="79"/>
       <c r="R63" s="79"/>
-      <c r="U63" s="726"/>
-      <c r="V63" s="727"/>
-      <c r="W63" s="727"/>
-      <c r="X63" s="727"/>
-      <c r="Y63" s="728"/>
+      <c r="U63" s="633"/>
+      <c r="V63" s="634"/>
+      <c r="W63" s="634"/>
+      <c r="X63" s="634"/>
+      <c r="Y63" s="635"/>
       <c r="Z63" s="82"/>
     </row>
     <row r="64" spans="1:28" ht="23.25">
@@ -33724,6 +33724,178 @@
     </row>
   </sheetData>
   <mergeCells count="196">
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="V12:W13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B3:Y3"/>
+    <mergeCell ref="B4:Y4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="X12:Y13"/>
+    <mergeCell ref="R11:Y11"/>
+    <mergeCell ref="G10:Y10"/>
+    <mergeCell ref="G11:H13"/>
+    <mergeCell ref="I11:K13"/>
+    <mergeCell ref="L11:N13"/>
+    <mergeCell ref="O11:Q13"/>
+    <mergeCell ref="R12:S13"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="W27:X28"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L27:N28"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:R28"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="L26:Y26"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
     <mergeCell ref="U63:Y63"/>
     <mergeCell ref="X55:AB55"/>
     <mergeCell ref="N43:P43"/>
@@ -33748,178 +33920,6 @@
     <mergeCell ref="W41:X41"/>
     <mergeCell ref="W42:X42"/>
     <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="O27:P28"/>
-    <mergeCell ref="Q27:R28"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="L26:Y26"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="L27:N28"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="W27:X28"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="V12:W13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B3:Y3"/>
-    <mergeCell ref="B4:Y4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="X12:Y13"/>
-    <mergeCell ref="R11:Y11"/>
-    <mergeCell ref="G10:Y10"/>
-    <mergeCell ref="G11:H13"/>
-    <mergeCell ref="I11:K13"/>
-    <mergeCell ref="L11:N13"/>
-    <mergeCell ref="O11:Q13"/>
-    <mergeCell ref="R12:S13"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E15">
     <cfRule type="expression" dxfId="33" priority="10">
@@ -34709,78 +34709,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="792" t="s">
+      <c r="A1" s="757" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="792"/>
-      <c r="C1" s="792"/>
-      <c r="D1" s="792"/>
-      <c r="E1" s="792"/>
-      <c r="F1" s="792"/>
-      <c r="G1" s="792"/>
-      <c r="H1" s="792"/>
-      <c r="I1" s="792"/>
-      <c r="J1" s="792"/>
-      <c r="K1" s="792"/>
-      <c r="L1" s="792"/>
-      <c r="M1" s="792"/>
-      <c r="N1" s="792"/>
-      <c r="O1" s="793"/>
+      <c r="B1" s="757"/>
+      <c r="C1" s="757"/>
+      <c r="D1" s="757"/>
+      <c r="E1" s="757"/>
+      <c r="F1" s="757"/>
+      <c r="G1" s="757"/>
+      <c r="H1" s="757"/>
+      <c r="I1" s="757"/>
+      <c r="J1" s="757"/>
+      <c r="K1" s="757"/>
+      <c r="L1" s="757"/>
+      <c r="M1" s="757"/>
+      <c r="N1" s="757"/>
+      <c r="O1" s="758"/>
     </row>
     <row r="2" spans="1:15" ht="6.75" customHeight="1" thickBot="1">
-      <c r="A2" s="794"/>
-      <c r="B2" s="794"/>
-      <c r="C2" s="794"/>
-      <c r="D2" s="794"/>
-      <c r="E2" s="794"/>
-      <c r="F2" s="794"/>
-      <c r="G2" s="794"/>
-      <c r="H2" s="794"/>
-      <c r="I2" s="794"/>
-      <c r="J2" s="794"/>
-      <c r="K2" s="794"/>
-      <c r="L2" s="794"/>
-      <c r="M2" s="794"/>
-      <c r="N2" s="794"/>
-      <c r="O2" s="795"/>
+      <c r="A2" s="759"/>
+      <c r="B2" s="759"/>
+      <c r="C2" s="759"/>
+      <c r="D2" s="759"/>
+      <c r="E2" s="759"/>
+      <c r="F2" s="759"/>
+      <c r="G2" s="759"/>
+      <c r="H2" s="759"/>
+      <c r="I2" s="759"/>
+      <c r="J2" s="759"/>
+      <c r="K2" s="759"/>
+      <c r="L2" s="759"/>
+      <c r="M2" s="759"/>
+      <c r="N2" s="759"/>
+      <c r="O2" s="760"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="796" t="s">
+      <c r="A3" s="761" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="796"/>
-      <c r="C3" s="796"/>
-      <c r="D3" s="796"/>
-      <c r="E3" s="796"/>
-      <c r="F3" s="796"/>
-      <c r="G3" s="796"/>
-      <c r="H3" s="796"/>
-      <c r="I3" s="796"/>
-      <c r="J3" s="796"/>
-      <c r="K3" s="796"/>
-      <c r="L3" s="796"/>
-      <c r="M3" s="796"/>
-      <c r="N3" s="796"/>
-      <c r="O3" s="797"/>
+      <c r="B3" s="761"/>
+      <c r="C3" s="761"/>
+      <c r="D3" s="761"/>
+      <c r="E3" s="761"/>
+      <c r="F3" s="761"/>
+      <c r="G3" s="761"/>
+      <c r="H3" s="761"/>
+      <c r="I3" s="761"/>
+      <c r="J3" s="761"/>
+      <c r="K3" s="761"/>
+      <c r="L3" s="761"/>
+      <c r="M3" s="761"/>
+      <c r="N3" s="761"/>
+      <c r="O3" s="762"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" thickBot="1">
-      <c r="A4" s="798" t="s">
+      <c r="A4" s="763" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="798"/>
-      <c r="C4" s="798"/>
-      <c r="D4" s="798"/>
-      <c r="E4" s="798"/>
-      <c r="F4" s="798"/>
-      <c r="G4" s="798"/>
-      <c r="H4" s="798"/>
-      <c r="I4" s="798"/>
-      <c r="J4" s="798"/>
-      <c r="K4" s="798"/>
-      <c r="L4" s="798"/>
-      <c r="M4" s="798"/>
-      <c r="N4" s="798"/>
-      <c r="O4" s="799"/>
+      <c r="B4" s="763"/>
+      <c r="C4" s="763"/>
+      <c r="D4" s="763"/>
+      <c r="E4" s="763"/>
+      <c r="F4" s="763"/>
+      <c r="G4" s="763"/>
+      <c r="H4" s="763"/>
+      <c r="I4" s="763"/>
+      <c r="J4" s="763"/>
+      <c r="K4" s="763"/>
+      <c r="L4" s="763"/>
+      <c r="M4" s="763"/>
+      <c r="N4" s="763"/>
+      <c r="O4" s="764"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" thickBot="1">
       <c r="A5" s="90"/>
@@ -34792,8 +34792,8 @@
       <c r="G5" s="478"/>
       <c r="H5" s="476"/>
       <c r="I5" s="82"/>
-      <c r="J5" s="800"/>
-      <c r="K5" s="800"/>
+      <c r="J5" s="765"/>
+      <c r="K5" s="765"/>
       <c r="L5" s="481"/>
       <c r="M5" s="478"/>
       <c r="N5" s="482"/>
@@ -34866,24 +34866,24 @@
       <c r="E8" s="106"/>
       <c r="F8" s="90"/>
       <c r="G8" s="104"/>
-      <c r="H8" s="790"/>
-      <c r="I8" s="791"/>
-      <c r="J8" s="790"/>
-      <c r="K8" s="790"/>
-      <c r="L8" s="790"/>
-      <c r="M8" s="790"/>
+      <c r="H8" s="755"/>
+      <c r="I8" s="756"/>
+      <c r="J8" s="755"/>
+      <c r="K8" s="755"/>
+      <c r="L8" s="755"/>
+      <c r="M8" s="755"/>
       <c r="N8" s="483"/>
       <c r="O8" s="391"/>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1">
-      <c r="A9" s="755" t="s">
+      <c r="A9" s="783" t="s">
         <v>141</v>
       </c>
-      <c r="B9" s="756"/>
-      <c r="C9" s="756"/>
-      <c r="D9" s="756"/>
-      <c r="E9" s="756"/>
-      <c r="F9" s="757"/>
+      <c r="B9" s="784"/>
+      <c r="C9" s="784"/>
+      <c r="D9" s="784"/>
+      <c r="E9" s="784"/>
+      <c r="F9" s="785"/>
       <c r="G9" s="83"/>
       <c r="H9" s="460"/>
       <c r="I9" s="465"/>
@@ -34895,12 +34895,12 @@
       <c r="O9" s="225"/>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A10" s="758"/>
-      <c r="B10" s="759"/>
-      <c r="C10" s="759"/>
-      <c r="D10" s="759"/>
-      <c r="E10" s="759"/>
-      <c r="F10" s="760"/>
+      <c r="A10" s="786"/>
+      <c r="B10" s="787"/>
+      <c r="C10" s="787"/>
+      <c r="D10" s="787"/>
+      <c r="E10" s="787"/>
+      <c r="F10" s="788"/>
       <c r="G10" s="80"/>
       <c r="H10" s="82"/>
       <c r="I10" s="463"/>
@@ -34912,22 +34912,22 @@
       <c r="O10" s="391"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="771" t="s">
+      <c r="A11" s="799" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="766" t="s">
+      <c r="B11" s="794" t="s">
         <v>142</v>
       </c>
-      <c r="C11" s="768" t="s">
+      <c r="C11" s="796" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="770" t="s">
+      <c r="D11" s="798" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="751" t="s">
+      <c r="E11" s="779" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="752"/>
+      <c r="F11" s="780"/>
       <c r="G11" s="80"/>
       <c r="H11" s="82"/>
       <c r="I11" s="463"/>
@@ -34939,12 +34939,12 @@
       <c r="O11" s="391"/>
     </row>
     <row r="12" spans="1:15" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A12" s="772"/>
-      <c r="B12" s="767"/>
-      <c r="C12" s="769"/>
-      <c r="D12" s="758"/>
-      <c r="E12" s="753"/>
-      <c r="F12" s="754"/>
+      <c r="A12" s="800"/>
+      <c r="B12" s="795"/>
+      <c r="C12" s="797"/>
+      <c r="D12" s="786"/>
+      <c r="E12" s="781"/>
+      <c r="F12" s="782"/>
       <c r="G12" s="80"/>
       <c r="H12" s="82"/>
       <c r="I12" s="463"/>
@@ -34962,11 +34962,11 @@
       <c r="B13" s="514"/>
       <c r="C13" s="514"/>
       <c r="D13" s="515"/>
-      <c r="E13" s="761">
+      <c r="E13" s="789">
         <f>SUM(B13:D13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="762"/>
+      <c r="F13" s="790"/>
       <c r="G13" s="80"/>
       <c r="H13" s="82"/>
       <c r="I13" s="82"/>
@@ -34984,11 +34984,11 @@
       <c r="B14" s="468"/>
       <c r="C14" s="468"/>
       <c r="D14" s="516"/>
-      <c r="E14" s="763">
+      <c r="E14" s="791">
         <f>SUM(B14:D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="764"/>
+      <c r="F14" s="792"/>
       <c r="G14" s="80"/>
       <c r="H14" s="82"/>
       <c r="I14" s="463"/>
@@ -35006,11 +35006,11 @@
       <c r="B15" s="471"/>
       <c r="C15" s="471"/>
       <c r="D15" s="472"/>
-      <c r="E15" s="773">
+      <c r="E15" s="801">
         <f>SUM(B15:D15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="774"/>
+      <c r="F15" s="802"/>
       <c r="G15" s="80"/>
       <c r="H15" s="82"/>
       <c r="I15" s="463"/>
@@ -35045,11 +35045,11 @@
       <c r="D17" s="82"/>
       <c r="E17" s="89"/>
       <c r="F17" s="82"/>
-      <c r="H17" s="776" t="s">
+      <c r="H17" s="767" t="s">
         <v>147</v>
       </c>
-      <c r="I17" s="777"/>
-      <c r="J17" s="778"/>
+      <c r="I17" s="768"/>
+      <c r="J17" s="769"/>
       <c r="K17" s="221"/>
       <c r="L17" s="221"/>
       <c r="M17" s="221"/>
@@ -35110,10 +35110,10 @@
       <c r="K20" s="500" t="s">
         <v>52</v>
       </c>
-      <c r="L20" s="786" t="s">
+      <c r="L20" s="775" t="s">
         <v>53</v>
       </c>
-      <c r="M20" s="787"/>
+      <c r="M20" s="776"/>
       <c r="N20" s="387"/>
       <c r="O20" s="165"/>
     </row>
@@ -35129,8 +35129,8 @@
       <c r="I21" s="503"/>
       <c r="J21" s="503"/>
       <c r="K21" s="503"/>
-      <c r="L21" s="788"/>
-      <c r="M21" s="789"/>
+      <c r="L21" s="777"/>
+      <c r="M21" s="778"/>
       <c r="N21" s="80"/>
       <c r="O21" s="165"/>
     </row>
@@ -35146,27 +35146,27 @@
       <c r="I22" s="502"/>
       <c r="J22" s="502"/>
       <c r="K22" s="502"/>
-      <c r="L22" s="784"/>
-      <c r="M22" s="785"/>
+      <c r="L22" s="751"/>
+      <c r="M22" s="752"/>
       <c r="N22" s="80"/>
       <c r="O22" s="165"/>
     </row>
     <row r="23" spans="1:15" ht="27.75" customHeight="1" thickBot="1">
-      <c r="A23" s="781" t="s">
+      <c r="A23" s="772" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="782"/>
-      <c r="C23" s="782"/>
-      <c r="D23" s="782"/>
-      <c r="E23" s="782"/>
-      <c r="F23" s="783"/>
+      <c r="B23" s="773"/>
+      <c r="C23" s="773"/>
+      <c r="D23" s="773"/>
+      <c r="E23" s="773"/>
+      <c r="F23" s="774"/>
       <c r="G23" s="78"/>
       <c r="H23" s="535"/>
       <c r="I23" s="502"/>
       <c r="J23" s="502"/>
       <c r="K23" s="502"/>
-      <c r="L23" s="784"/>
-      <c r="M23" s="785"/>
+      <c r="L23" s="751"/>
+      <c r="M23" s="752"/>
       <c r="N23" s="80"/>
       <c r="O23" s="165"/>
     </row>
@@ -35174,10 +35174,10 @@
       <c r="A24" s="509" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="779" t="s">
+      <c r="B24" s="770" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="780"/>
+      <c r="C24" s="771"/>
       <c r="D24" s="510" t="s">
         <v>151</v>
       </c>
@@ -35192,8 +35192,8 @@
       <c r="I24" s="502"/>
       <c r="J24" s="502"/>
       <c r="K24" s="502"/>
-      <c r="L24" s="784"/>
-      <c r="M24" s="785"/>
+      <c r="L24" s="751"/>
+      <c r="M24" s="752"/>
       <c r="N24" s="80"/>
       <c r="O24" s="165"/>
     </row>
@@ -35201,8 +35201,8 @@
       <c r="A25" s="467" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="765"/>
-      <c r="C25" s="765"/>
+      <c r="B25" s="793"/>
+      <c r="C25" s="793"/>
       <c r="D25" s="474"/>
       <c r="E25" s="474"/>
       <c r="F25" s="473">
@@ -35214,8 +35214,8 @@
       <c r="I25" s="502"/>
       <c r="J25" s="502"/>
       <c r="K25" s="502"/>
-      <c r="L25" s="784"/>
-      <c r="M25" s="785"/>
+      <c r="L25" s="751"/>
+      <c r="M25" s="752"/>
       <c r="N25" s="80"/>
       <c r="O25" s="165"/>
     </row>
@@ -35228,16 +35228,16 @@
       <c r="I26" s="502"/>
       <c r="J26" s="502"/>
       <c r="K26" s="502"/>
-      <c r="L26" s="784"/>
-      <c r="M26" s="785"/>
+      <c r="L26" s="751"/>
+      <c r="M26" s="752"/>
       <c r="N26" s="80"/>
       <c r="O26" s="165"/>
     </row>
     <row r="27" spans="1:15" ht="27" customHeight="1">
-      <c r="A27" s="775"/>
-      <c r="B27" s="775"/>
-      <c r="C27" s="775"/>
-      <c r="D27" s="775"/>
+      <c r="A27" s="766"/>
+      <c r="B27" s="766"/>
+      <c r="C27" s="766"/>
+      <c r="D27" s="766"/>
       <c r="E27" s="461"/>
       <c r="F27" s="464"/>
       <c r="G27" s="89"/>
@@ -35245,8 +35245,8 @@
       <c r="I27" s="502"/>
       <c r="J27" s="502"/>
       <c r="K27" s="502"/>
-      <c r="L27" s="784"/>
-      <c r="M27" s="785"/>
+      <c r="L27" s="751"/>
+      <c r="M27" s="752"/>
       <c r="N27" s="80"/>
       <c r="O27" s="165"/>
     </row>
@@ -35262,8 +35262,8 @@
       <c r="I28" s="502"/>
       <c r="J28" s="502"/>
       <c r="K28" s="502"/>
-      <c r="L28" s="784"/>
-      <c r="M28" s="785"/>
+      <c r="L28" s="751"/>
+      <c r="M28" s="752"/>
       <c r="N28" s="105"/>
       <c r="O28" s="165"/>
     </row>
@@ -35278,8 +35278,8 @@
       <c r="I29" s="502"/>
       <c r="J29" s="502"/>
       <c r="K29" s="502"/>
-      <c r="L29" s="784"/>
-      <c r="M29" s="785"/>
+      <c r="L29" s="751"/>
+      <c r="M29" s="752"/>
       <c r="N29" s="80"/>
       <c r="O29" s="165"/>
     </row>
@@ -35295,8 +35295,8 @@
       <c r="I30" s="502"/>
       <c r="J30" s="502"/>
       <c r="K30" s="502"/>
-      <c r="L30" s="784"/>
-      <c r="M30" s="785"/>
+      <c r="L30" s="751"/>
+      <c r="M30" s="752"/>
       <c r="N30" s="80"/>
       <c r="O30" s="165"/>
     </row>
@@ -35312,8 +35312,8 @@
       <c r="I31" s="502"/>
       <c r="J31" s="502"/>
       <c r="K31" s="502"/>
-      <c r="L31" s="784"/>
-      <c r="M31" s="785"/>
+      <c r="L31" s="751"/>
+      <c r="M31" s="752"/>
       <c r="N31" s="80"/>
       <c r="O31" s="165"/>
     </row>
@@ -35329,8 +35329,8 @@
       <c r="I32" s="502"/>
       <c r="J32" s="502"/>
       <c r="K32" s="502"/>
-      <c r="L32" s="784"/>
-      <c r="M32" s="785"/>
+      <c r="L32" s="751"/>
+      <c r="M32" s="752"/>
       <c r="N32" s="80"/>
       <c r="O32" s="165"/>
     </row>
@@ -35346,8 +35346,8 @@
       <c r="I33" s="502"/>
       <c r="J33" s="502"/>
       <c r="K33" s="502"/>
-      <c r="L33" s="784"/>
-      <c r="M33" s="785"/>
+      <c r="L33" s="751"/>
+      <c r="M33" s="752"/>
       <c r="N33" s="80"/>
       <c r="O33" s="165"/>
     </row>
@@ -35363,8 +35363,8 @@
       <c r="I34" s="502"/>
       <c r="J34" s="502"/>
       <c r="K34" s="502"/>
-      <c r="L34" s="784"/>
-      <c r="M34" s="785"/>
+      <c r="L34" s="751"/>
+      <c r="M34" s="752"/>
       <c r="N34" s="80"/>
       <c r="O34" s="165"/>
     </row>
@@ -35380,8 +35380,8 @@
       <c r="I35" s="502"/>
       <c r="J35" s="502"/>
       <c r="K35" s="502"/>
-      <c r="L35" s="784"/>
-      <c r="M35" s="785"/>
+      <c r="L35" s="751"/>
+      <c r="M35" s="752"/>
       <c r="N35" s="80"/>
       <c r="O35" s="165"/>
     </row>
@@ -35396,8 +35396,8 @@
       <c r="I36" s="502"/>
       <c r="J36" s="502"/>
       <c r="K36" s="502"/>
-      <c r="L36" s="784"/>
-      <c r="M36" s="785"/>
+      <c r="L36" s="751"/>
+      <c r="M36" s="752"/>
       <c r="N36" s="80"/>
       <c r="O36" s="165"/>
     </row>
@@ -35413,29 +35413,23 @@
       <c r="I37" s="504"/>
       <c r="J37" s="504"/>
       <c r="K37" s="504"/>
-      <c r="L37" s="801"/>
-      <c r="M37" s="802"/>
+      <c r="L37" s="753"/>
+      <c r="M37" s="754"/>
       <c r="N37" s="80"/>
       <c r="O37" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="B24:C24"/>
@@ -35448,16 +35442,22 @@
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="L26:M26"/>
     <mergeCell ref="L27:M27"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
   </mergeCells>
   <conditionalFormatting sqref="I21:L37">
     <cfRule type="expression" dxfId="27" priority="1">
@@ -35511,159 +35511,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="21.75" thickBot="1">
-      <c r="A1" s="893" t="s">
+      <c r="A1" s="836" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="894"/>
-      <c r="C1" s="894"/>
-      <c r="D1" s="894"/>
-      <c r="E1" s="894"/>
-      <c r="F1" s="894"/>
-      <c r="G1" s="894"/>
-      <c r="H1" s="894"/>
-      <c r="I1" s="894"/>
-      <c r="J1" s="894"/>
-      <c r="K1" s="894"/>
-      <c r="L1" s="894"/>
-      <c r="M1" s="894"/>
-      <c r="N1" s="894"/>
-      <c r="O1" s="894"/>
-      <c r="P1" s="894"/>
-      <c r="Q1" s="894"/>
-      <c r="R1" s="894"/>
-      <c r="S1" s="894"/>
-      <c r="T1" s="894"/>
-      <c r="U1" s="894"/>
-      <c r="V1" s="894"/>
-      <c r="W1" s="894"/>
-      <c r="X1" s="894"/>
-      <c r="Y1" s="894"/>
-      <c r="Z1" s="894"/>
-      <c r="AA1" s="894"/>
-      <c r="AB1" s="894"/>
-      <c r="AC1" s="894"/>
-      <c r="AD1" s="894"/>
-      <c r="AE1" s="894"/>
-      <c r="AF1" s="894"/>
-      <c r="AG1" s="894"/>
-      <c r="AH1" s="894"/>
-      <c r="AI1" s="895"/>
+      <c r="B1" s="837"/>
+      <c r="C1" s="837"/>
+      <c r="D1" s="837"/>
+      <c r="E1" s="837"/>
+      <c r="F1" s="837"/>
+      <c r="G1" s="837"/>
+      <c r="H1" s="837"/>
+      <c r="I1" s="837"/>
+      <c r="J1" s="837"/>
+      <c r="K1" s="837"/>
+      <c r="L1" s="837"/>
+      <c r="M1" s="837"/>
+      <c r="N1" s="837"/>
+      <c r="O1" s="837"/>
+      <c r="P1" s="837"/>
+      <c r="Q1" s="837"/>
+      <c r="R1" s="837"/>
+      <c r="S1" s="837"/>
+      <c r="T1" s="837"/>
+      <c r="U1" s="837"/>
+      <c r="V1" s="837"/>
+      <c r="W1" s="837"/>
+      <c r="X1" s="837"/>
+      <c r="Y1" s="837"/>
+      <c r="Z1" s="837"/>
+      <c r="AA1" s="837"/>
+      <c r="AB1" s="837"/>
+      <c r="AC1" s="837"/>
+      <c r="AD1" s="837"/>
+      <c r="AE1" s="837"/>
+      <c r="AF1" s="837"/>
+      <c r="AG1" s="837"/>
+      <c r="AH1" s="837"/>
+      <c r="AI1" s="838"/>
     </row>
     <row r="2" spans="1:36" ht="4.5" customHeight="1" thickBot="1">
-      <c r="A2" s="911"/>
-      <c r="B2" s="794"/>
-      <c r="C2" s="794"/>
-      <c r="D2" s="794"/>
-      <c r="E2" s="794"/>
-      <c r="F2" s="794"/>
-      <c r="G2" s="794"/>
-      <c r="H2" s="794"/>
-      <c r="I2" s="794"/>
-      <c r="J2" s="794"/>
-      <c r="K2" s="794"/>
-      <c r="L2" s="794"/>
-      <c r="M2" s="794"/>
-      <c r="N2" s="794"/>
-      <c r="O2" s="794"/>
-      <c r="P2" s="794"/>
-      <c r="Q2" s="794"/>
-      <c r="R2" s="794"/>
-      <c r="S2" s="794"/>
-      <c r="T2" s="794"/>
-      <c r="U2" s="794"/>
-      <c r="V2" s="794"/>
-      <c r="W2" s="794"/>
-      <c r="X2" s="794"/>
-      <c r="Y2" s="794"/>
-      <c r="Z2" s="794"/>
-      <c r="AA2" s="794"/>
-      <c r="AB2" s="794"/>
-      <c r="AC2" s="794"/>
-      <c r="AD2" s="794"/>
-      <c r="AE2" s="794"/>
-      <c r="AF2" s="794"/>
-      <c r="AG2" s="794"/>
-      <c r="AH2" s="794"/>
-      <c r="AI2" s="795"/>
+      <c r="A2" s="856"/>
+      <c r="B2" s="759"/>
+      <c r="C2" s="759"/>
+      <c r="D2" s="759"/>
+      <c r="E2" s="759"/>
+      <c r="F2" s="759"/>
+      <c r="G2" s="759"/>
+      <c r="H2" s="759"/>
+      <c r="I2" s="759"/>
+      <c r="J2" s="759"/>
+      <c r="K2" s="759"/>
+      <c r="L2" s="759"/>
+      <c r="M2" s="759"/>
+      <c r="N2" s="759"/>
+      <c r="O2" s="759"/>
+      <c r="P2" s="759"/>
+      <c r="Q2" s="759"/>
+      <c r="R2" s="759"/>
+      <c r="S2" s="759"/>
+      <c r="T2" s="759"/>
+      <c r="U2" s="759"/>
+      <c r="V2" s="759"/>
+      <c r="W2" s="759"/>
+      <c r="X2" s="759"/>
+      <c r="Y2" s="759"/>
+      <c r="Z2" s="759"/>
+      <c r="AA2" s="759"/>
+      <c r="AB2" s="759"/>
+      <c r="AC2" s="759"/>
+      <c r="AD2" s="759"/>
+      <c r="AE2" s="759"/>
+      <c r="AF2" s="759"/>
+      <c r="AG2" s="759"/>
+      <c r="AH2" s="759"/>
+      <c r="AI2" s="760"/>
     </row>
     <row r="3" spans="1:36" ht="15.75">
-      <c r="A3" s="927" t="s">
+      <c r="A3" s="872" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="928"/>
-      <c r="C3" s="928"/>
-      <c r="D3" s="928"/>
-      <c r="E3" s="928"/>
-      <c r="F3" s="928"/>
-      <c r="G3" s="928"/>
-      <c r="H3" s="928"/>
-      <c r="I3" s="928"/>
-      <c r="J3" s="928"/>
-      <c r="K3" s="928"/>
-      <c r="L3" s="928"/>
-      <c r="M3" s="928"/>
-      <c r="N3" s="928"/>
-      <c r="O3" s="928"/>
-      <c r="P3" s="928"/>
-      <c r="Q3" s="928"/>
-      <c r="R3" s="928"/>
-      <c r="S3" s="928"/>
-      <c r="T3" s="928"/>
-      <c r="U3" s="928"/>
-      <c r="V3" s="928"/>
-      <c r="W3" s="928"/>
-      <c r="X3" s="928"/>
-      <c r="Y3" s="928"/>
-      <c r="Z3" s="928"/>
-      <c r="AA3" s="928"/>
-      <c r="AB3" s="928"/>
-      <c r="AC3" s="928"/>
-      <c r="AD3" s="928"/>
-      <c r="AE3" s="928"/>
-      <c r="AF3" s="928"/>
-      <c r="AG3" s="928"/>
-      <c r="AH3" s="928"/>
-      <c r="AI3" s="929"/>
+      <c r="B3" s="873"/>
+      <c r="C3" s="873"/>
+      <c r="D3" s="873"/>
+      <c r="E3" s="873"/>
+      <c r="F3" s="873"/>
+      <c r="G3" s="873"/>
+      <c r="H3" s="873"/>
+      <c r="I3" s="873"/>
+      <c r="J3" s="873"/>
+      <c r="K3" s="873"/>
+      <c r="L3" s="873"/>
+      <c r="M3" s="873"/>
+      <c r="N3" s="873"/>
+      <c r="O3" s="873"/>
+      <c r="P3" s="873"/>
+      <c r="Q3" s="873"/>
+      <c r="R3" s="873"/>
+      <c r="S3" s="873"/>
+      <c r="T3" s="873"/>
+      <c r="U3" s="873"/>
+      <c r="V3" s="873"/>
+      <c r="W3" s="873"/>
+      <c r="X3" s="873"/>
+      <c r="Y3" s="873"/>
+      <c r="Z3" s="873"/>
+      <c r="AA3" s="873"/>
+      <c r="AB3" s="873"/>
+      <c r="AC3" s="873"/>
+      <c r="AD3" s="873"/>
+      <c r="AE3" s="873"/>
+      <c r="AF3" s="873"/>
+      <c r="AG3" s="873"/>
+      <c r="AH3" s="873"/>
+      <c r="AI3" s="874"/>
       <c r="AJ3" s="98"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A4" s="924" t="s">
+      <c r="A4" s="869" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="925"/>
-      <c r="C4" s="925"/>
-      <c r="D4" s="925"/>
-      <c r="E4" s="925"/>
-      <c r="F4" s="925"/>
-      <c r="G4" s="925"/>
-      <c r="H4" s="925"/>
-      <c r="I4" s="925"/>
-      <c r="J4" s="925"/>
-      <c r="K4" s="925"/>
-      <c r="L4" s="925"/>
-      <c r="M4" s="925"/>
-      <c r="N4" s="925"/>
-      <c r="O4" s="925"/>
-      <c r="P4" s="925"/>
-      <c r="Q4" s="925"/>
-      <c r="R4" s="925"/>
-      <c r="S4" s="925"/>
-      <c r="T4" s="925"/>
-      <c r="U4" s="925"/>
-      <c r="V4" s="925"/>
-      <c r="W4" s="925"/>
-      <c r="X4" s="925"/>
-      <c r="Y4" s="925"/>
-      <c r="Z4" s="925"/>
-      <c r="AA4" s="925"/>
-      <c r="AB4" s="925"/>
-      <c r="AC4" s="925"/>
-      <c r="AD4" s="925"/>
-      <c r="AE4" s="925"/>
-      <c r="AF4" s="925"/>
-      <c r="AG4" s="925"/>
-      <c r="AH4" s="925"/>
-      <c r="AI4" s="926"/>
+      <c r="B4" s="870"/>
+      <c r="C4" s="870"/>
+      <c r="D4" s="870"/>
+      <c r="E4" s="870"/>
+      <c r="F4" s="870"/>
+      <c r="G4" s="870"/>
+      <c r="H4" s="870"/>
+      <c r="I4" s="870"/>
+      <c r="J4" s="870"/>
+      <c r="K4" s="870"/>
+      <c r="L4" s="870"/>
+      <c r="M4" s="870"/>
+      <c r="N4" s="870"/>
+      <c r="O4" s="870"/>
+      <c r="P4" s="870"/>
+      <c r="Q4" s="870"/>
+      <c r="R4" s="870"/>
+      <c r="S4" s="870"/>
+      <c r="T4" s="870"/>
+      <c r="U4" s="870"/>
+      <c r="V4" s="870"/>
+      <c r="W4" s="870"/>
+      <c r="X4" s="870"/>
+      <c r="Y4" s="870"/>
+      <c r="Z4" s="870"/>
+      <c r="AA4" s="870"/>
+      <c r="AB4" s="870"/>
+      <c r="AC4" s="870"/>
+      <c r="AD4" s="870"/>
+      <c r="AE4" s="870"/>
+      <c r="AF4" s="870"/>
+      <c r="AG4" s="870"/>
+      <c r="AH4" s="870"/>
+      <c r="AI4" s="871"/>
     </row>
     <row r="5" spans="1:36" ht="11.25" customHeight="1" thickBot="1">
       <c r="A5" s="224"/>
@@ -35701,44 +35701,44 @@
       <c r="A6" s="136"/>
       <c r="C6" s="151"/>
       <c r="D6" s="124"/>
-      <c r="E6" s="940" t="s">
+      <c r="E6" s="885" t="s">
         <v>145</v>
       </c>
-      <c r="F6" s="941"/>
-      <c r="G6" s="942"/>
+      <c r="F6" s="886"/>
+      <c r="G6" s="887"/>
       <c r="H6" s="341"/>
       <c r="I6" s="223"/>
-      <c r="J6" s="912" t="s">
+      <c r="J6" s="857" t="s">
         <v>92</v>
       </c>
-      <c r="K6" s="913"/>
-      <c r="L6" s="914"/>
+      <c r="K6" s="858"/>
+      <c r="L6" s="859"/>
       <c r="M6" s="344"/>
       <c r="N6" s="223"/>
       <c r="O6" s="347"/>
       <c r="P6" s="347"/>
-      <c r="Q6" s="933" t="s">
+      <c r="Q6" s="878" t="s">
         <v>93</v>
       </c>
-      <c r="R6" s="934"/>
+      <c r="R6" s="879"/>
       <c r="S6" s="345"/>
       <c r="T6" s="223"/>
       <c r="U6" s="347"/>
       <c r="V6" s="347"/>
-      <c r="W6" s="912" t="s">
+      <c r="W6" s="857" t="s">
         <v>104</v>
       </c>
-      <c r="X6" s="913"/>
-      <c r="Y6" s="913"/>
-      <c r="Z6" s="914"/>
+      <c r="X6" s="858"/>
+      <c r="Y6" s="858"/>
+      <c r="Z6" s="859"/>
       <c r="AA6" s="383"/>
       <c r="AB6" s="223"/>
       <c r="AC6" s="347"/>
-      <c r="AD6" s="905" t="s">
+      <c r="AD6" s="850" t="s">
         <v>94</v>
       </c>
-      <c r="AE6" s="906"/>
-      <c r="AF6" s="907"/>
+      <c r="AE6" s="851"/>
+      <c r="AF6" s="852"/>
       <c r="AG6" s="136"/>
       <c r="AH6" s="371"/>
       <c r="AI6" s="391"/>
@@ -35747,34 +35747,34 @@
       <c r="A7" s="136"/>
       <c r="B7" s="100"/>
       <c r="C7" s="23"/>
-      <c r="E7" s="943"/>
-      <c r="F7" s="944"/>
-      <c r="G7" s="945"/>
+      <c r="E7" s="888"/>
+      <c r="F7" s="889"/>
+      <c r="G7" s="890"/>
       <c r="H7" s="341"/>
       <c r="I7" s="226"/>
-      <c r="J7" s="930"/>
-      <c r="K7" s="931"/>
-      <c r="L7" s="932"/>
+      <c r="J7" s="875"/>
+      <c r="K7" s="876"/>
+      <c r="L7" s="877"/>
       <c r="M7" s="344"/>
       <c r="N7" s="226"/>
       <c r="O7" s="339"/>
       <c r="P7" s="346"/>
-      <c r="Q7" s="935"/>
-      <c r="R7" s="936"/>
+      <c r="Q7" s="880"/>
+      <c r="R7" s="881"/>
       <c r="S7" s="345"/>
       <c r="T7" s="226"/>
       <c r="U7" s="339"/>
       <c r="V7" s="346"/>
-      <c r="W7" s="915"/>
-      <c r="X7" s="916"/>
-      <c r="Y7" s="916"/>
-      <c r="Z7" s="917"/>
+      <c r="W7" s="860"/>
+      <c r="X7" s="861"/>
+      <c r="Y7" s="861"/>
+      <c r="Z7" s="862"/>
       <c r="AA7" s="383"/>
       <c r="AB7" s="226"/>
       <c r="AC7" s="339"/>
-      <c r="AD7" s="908"/>
-      <c r="AE7" s="909"/>
-      <c r="AF7" s="910"/>
+      <c r="AD7" s="853"/>
+      <c r="AE7" s="854"/>
+      <c r="AF7" s="855"/>
       <c r="AG7" s="136"/>
       <c r="AH7" s="371"/>
       <c r="AI7" s="391"/>
@@ -35783,44 +35783,44 @@
       <c r="A8" s="136"/>
       <c r="B8" s="348"/>
       <c r="C8" s="206"/>
-      <c r="E8" s="918">
+      <c r="E8" s="863">
         <v>64</v>
       </c>
-      <c r="F8" s="919"/>
-      <c r="G8" s="946"/>
+      <c r="F8" s="864"/>
+      <c r="G8" s="891"/>
       <c r="H8" s="152"/>
       <c r="I8" s="136"/>
       <c r="J8" s="79"/>
-      <c r="K8" s="950">
+      <c r="K8" s="895">
         <v>16</v>
       </c>
-      <c r="L8" s="951"/>
+      <c r="L8" s="896"/>
       <c r="M8" s="344"/>
       <c r="N8" s="136"/>
       <c r="O8" s="79"/>
-      <c r="P8" s="918">
+      <c r="P8" s="863">
         <v>10</v>
       </c>
-      <c r="Q8" s="919"/>
-      <c r="R8" s="920"/>
+      <c r="Q8" s="864"/>
+      <c r="R8" s="865"/>
       <c r="S8" s="345"/>
       <c r="T8" s="136"/>
       <c r="U8" s="79"/>
-      <c r="V8" s="918">
+      <c r="V8" s="863">
         <v>38</v>
       </c>
-      <c r="W8" s="919"/>
-      <c r="X8" s="919"/>
-      <c r="Y8" s="919"/>
-      <c r="Z8" s="920"/>
+      <c r="W8" s="864"/>
+      <c r="X8" s="864"/>
+      <c r="Y8" s="864"/>
+      <c r="Z8" s="865"/>
       <c r="AA8" s="384"/>
       <c r="AB8" s="136"/>
       <c r="AC8" s="79"/>
-      <c r="AD8" s="918">
+      <c r="AD8" s="863">
         <v>20</v>
       </c>
-      <c r="AE8" s="919"/>
-      <c r="AF8" s="920"/>
+      <c r="AE8" s="864"/>
+      <c r="AF8" s="865"/>
       <c r="AG8" s="136"/>
       <c r="AH8" s="372"/>
       <c r="AI8" s="225"/>
@@ -35830,33 +35830,33 @@
       <c r="B9" s="100"/>
       <c r="C9" s="144"/>
       <c r="D9" s="337"/>
-      <c r="E9" s="947"/>
-      <c r="F9" s="948"/>
-      <c r="G9" s="949"/>
+      <c r="E9" s="892"/>
+      <c r="F9" s="893"/>
+      <c r="G9" s="894"/>
       <c r="I9" s="137"/>
       <c r="J9" s="338"/>
-      <c r="K9" s="952"/>
-      <c r="L9" s="953"/>
+      <c r="K9" s="897"/>
+      <c r="L9" s="898"/>
       <c r="M9" s="345"/>
       <c r="N9" s="137"/>
       <c r="O9" s="338"/>
-      <c r="P9" s="921"/>
-      <c r="Q9" s="922"/>
-      <c r="R9" s="923"/>
+      <c r="P9" s="866"/>
+      <c r="Q9" s="867"/>
+      <c r="R9" s="868"/>
       <c r="S9" s="345"/>
       <c r="T9" s="137"/>
       <c r="U9" s="338"/>
-      <c r="V9" s="921"/>
-      <c r="W9" s="922"/>
-      <c r="X9" s="922"/>
-      <c r="Y9" s="922"/>
-      <c r="Z9" s="923"/>
+      <c r="V9" s="866"/>
+      <c r="W9" s="867"/>
+      <c r="X9" s="867"/>
+      <c r="Y9" s="867"/>
+      <c r="Z9" s="868"/>
       <c r="AA9" s="384"/>
       <c r="AB9" s="137"/>
       <c r="AC9" s="338"/>
-      <c r="AD9" s="921"/>
-      <c r="AE9" s="922"/>
-      <c r="AF9" s="923"/>
+      <c r="AD9" s="866"/>
+      <c r="AE9" s="867"/>
+      <c r="AF9" s="868"/>
       <c r="AG9" s="385"/>
       <c r="AH9" s="372"/>
       <c r="AI9" s="165"/>
@@ -35912,23 +35912,23 @@
       <c r="M11" s="148"/>
       <c r="N11" s="148"/>
       <c r="O11" s="82"/>
-      <c r="Q11" s="960" t="s">
+      <c r="Q11" s="803" t="s">
         <v>153</v>
       </c>
-      <c r="R11" s="961"/>
-      <c r="S11" s="961"/>
-      <c r="T11" s="961"/>
-      <c r="U11" s="961"/>
-      <c r="V11" s="961"/>
-      <c r="W11" s="961"/>
-      <c r="X11" s="961"/>
-      <c r="Y11" s="961"/>
-      <c r="Z11" s="961"/>
-      <c r="AA11" s="961"/>
-      <c r="AB11" s="961"/>
-      <c r="AC11" s="961"/>
-      <c r="AD11" s="961"/>
-      <c r="AE11" s="961"/>
+      <c r="R11" s="804"/>
+      <c r="S11" s="804"/>
+      <c r="T11" s="804"/>
+      <c r="U11" s="804"/>
+      <c r="V11" s="804"/>
+      <c r="W11" s="804"/>
+      <c r="X11" s="804"/>
+      <c r="Y11" s="804"/>
+      <c r="Z11" s="804"/>
+      <c r="AA11" s="804"/>
+      <c r="AB11" s="804"/>
+      <c r="AC11" s="804"/>
+      <c r="AD11" s="804"/>
+      <c r="AE11" s="804"/>
       <c r="AF11" s="423">
         <v>2025</v>
       </c>
@@ -35938,25 +35938,25 @@
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1">
       <c r="A12" s="392"/>
-      <c r="B12" s="970" t="s">
+      <c r="B12" s="817" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="971"/>
-      <c r="D12" s="971"/>
-      <c r="E12" s="972"/>
-      <c r="F12" s="963" t="s">
+      <c r="C12" s="818"/>
+      <c r="D12" s="818"/>
+      <c r="E12" s="819"/>
+      <c r="F12" s="807" t="s">
         <v>141</v>
       </c>
-      <c r="G12" s="964"/>
-      <c r="H12" s="964"/>
-      <c r="I12" s="964"/>
-      <c r="J12" s="964"/>
-      <c r="K12" s="964"/>
-      <c r="L12" s="964"/>
-      <c r="M12" s="963" t="s">
+      <c r="G12" s="808"/>
+      <c r="H12" s="808"/>
+      <c r="I12" s="808"/>
+      <c r="J12" s="808"/>
+      <c r="K12" s="808"/>
+      <c r="L12" s="808"/>
+      <c r="M12" s="807" t="s">
         <v>88</v>
       </c>
-      <c r="N12" s="967"/>
+      <c r="N12" s="811"/>
       <c r="O12" s="351"/>
       <c r="P12" s="79"/>
       <c r="Q12" s="421"/>
@@ -36009,19 +36009,19 @@
     </row>
     <row r="13" spans="1:36" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="224"/>
-      <c r="B13" s="973"/>
-      <c r="C13" s="974"/>
-      <c r="D13" s="974"/>
-      <c r="E13" s="975"/>
-      <c r="F13" s="965"/>
-      <c r="G13" s="966"/>
-      <c r="H13" s="966"/>
-      <c r="I13" s="966"/>
-      <c r="J13" s="966"/>
-      <c r="K13" s="966"/>
-      <c r="L13" s="966"/>
-      <c r="M13" s="968"/>
-      <c r="N13" s="969"/>
+      <c r="B13" s="820"/>
+      <c r="C13" s="821"/>
+      <c r="D13" s="821"/>
+      <c r="E13" s="822"/>
+      <c r="F13" s="809"/>
+      <c r="G13" s="810"/>
+      <c r="H13" s="810"/>
+      <c r="I13" s="810"/>
+      <c r="J13" s="810"/>
+      <c r="K13" s="810"/>
+      <c r="L13" s="810"/>
+      <c r="M13" s="812"/>
+      <c r="N13" s="813"/>
       <c r="O13" s="351"/>
       <c r="P13" s="79"/>
       <c r="Q13" s="406"/>
@@ -36088,25 +36088,25 @@
     </row>
     <row r="14" spans="1:36" ht="13.5" customHeight="1">
       <c r="A14" s="392"/>
-      <c r="B14" s="973"/>
-      <c r="C14" s="974"/>
-      <c r="D14" s="974"/>
-      <c r="E14" s="975"/>
-      <c r="F14" s="979" t="s">
+      <c r="B14" s="820"/>
+      <c r="C14" s="821"/>
+      <c r="D14" s="821"/>
+      <c r="E14" s="822"/>
+      <c r="F14" s="826" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="980"/>
-      <c r="H14" s="983" t="s">
+      <c r="G14" s="827"/>
+      <c r="H14" s="830" t="s">
         <v>143</v>
       </c>
-      <c r="I14" s="984"/>
-      <c r="J14" s="987" t="s">
+      <c r="I14" s="831"/>
+      <c r="J14" s="834" t="s">
         <v>144</v>
       </c>
-      <c r="K14" s="988"/>
-      <c r="L14" s="988"/>
-      <c r="M14" s="968"/>
-      <c r="N14" s="969"/>
+      <c r="K14" s="835"/>
+      <c r="L14" s="835"/>
+      <c r="M14" s="812"/>
+      <c r="N14" s="813"/>
       <c r="O14" s="351"/>
       <c r="P14" s="79"/>
       <c r="Q14" s="406"/>
@@ -36175,19 +36175,19 @@
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1">
       <c r="A15" s="392"/>
-      <c r="B15" s="976"/>
-      <c r="C15" s="977"/>
-      <c r="D15" s="977"/>
-      <c r="E15" s="978"/>
-      <c r="F15" s="981"/>
-      <c r="G15" s="982"/>
-      <c r="H15" s="985"/>
-      <c r="I15" s="986"/>
-      <c r="J15" s="987"/>
-      <c r="K15" s="988"/>
-      <c r="L15" s="988"/>
-      <c r="M15" s="968"/>
-      <c r="N15" s="969"/>
+      <c r="B15" s="823"/>
+      <c r="C15" s="824"/>
+      <c r="D15" s="824"/>
+      <c r="E15" s="825"/>
+      <c r="F15" s="828"/>
+      <c r="G15" s="829"/>
+      <c r="H15" s="832"/>
+      <c r="I15" s="833"/>
+      <c r="J15" s="834"/>
+      <c r="K15" s="835"/>
+      <c r="L15" s="835"/>
+      <c r="M15" s="812"/>
+      <c r="N15" s="813"/>
       <c r="P15" s="79"/>
       <c r="Q15" s="406"/>
       <c r="R15" s="396"/>
@@ -36253,12 +36253,12 @@
     </row>
     <row r="16" spans="1:36" ht="15.75">
       <c r="A16" s="224"/>
-      <c r="B16" s="954" t="s">
+      <c r="B16" s="814" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="955"/>
-      <c r="D16" s="955"/>
-      <c r="E16" s="955"/>
+      <c r="C16" s="815"/>
+      <c r="D16" s="815"/>
+      <c r="E16" s="815"/>
       <c r="F16" s="750">
         <v>2</v>
       </c>
@@ -36275,7 +36275,7 @@
       <c r="M16" s="750">
         <v>16</v>
       </c>
-      <c r="N16" s="959"/>
+      <c r="N16" s="816"/>
       <c r="O16" s="351"/>
       <c r="P16" s="79"/>
       <c r="Q16" s="406"/>
@@ -36300,12 +36300,12 @@
     </row>
     <row r="17" spans="1:36" ht="15.75">
       <c r="A17" s="392"/>
-      <c r="B17" s="954" t="s">
+      <c r="B17" s="814" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="955"/>
-      <c r="D17" s="955"/>
-      <c r="E17" s="955"/>
+      <c r="C17" s="815"/>
+      <c r="D17" s="815"/>
+      <c r="E17" s="815"/>
       <c r="F17" s="750">
         <v>0</v>
       </c>
@@ -36322,7 +36322,7 @@
       <c r="M17" s="750">
         <v>10</v>
       </c>
-      <c r="N17" s="959"/>
+      <c r="N17" s="816"/>
       <c r="O17" s="116"/>
       <c r="P17" s="79"/>
       <c r="Q17" s="403"/>
@@ -36389,29 +36389,29 @@
     </row>
     <row r="18" spans="1:36" ht="16.5" thickBot="1">
       <c r="A18" s="224"/>
-      <c r="B18" s="956" t="s">
+      <c r="B18" s="899" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="957"/>
-      <c r="D18" s="957"/>
-      <c r="E18" s="957"/>
-      <c r="F18" s="958">
+      <c r="C18" s="900"/>
+      <c r="D18" s="900"/>
+      <c r="E18" s="900"/>
+      <c r="F18" s="805">
         <v>10</v>
       </c>
-      <c r="G18" s="958"/>
-      <c r="H18" s="958">
+      <c r="G18" s="805"/>
+      <c r="H18" s="805">
         <v>38</v>
       </c>
-      <c r="I18" s="958"/>
-      <c r="J18" s="937">
+      <c r="I18" s="805"/>
+      <c r="J18" s="882">
         <v>25</v>
       </c>
-      <c r="K18" s="938"/>
-      <c r="L18" s="939"/>
-      <c r="M18" s="958">
+      <c r="K18" s="883"/>
+      <c r="L18" s="884"/>
+      <c r="M18" s="805">
         <v>38</v>
       </c>
-      <c r="N18" s="962"/>
+      <c r="N18" s="806"/>
       <c r="O18" s="155"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="406"/>
@@ -36957,15 +36957,15 @@
       <c r="M27" s="82"/>
       <c r="N27" s="82"/>
       <c r="P27" s="377"/>
-      <c r="Q27" s="896" t="s">
+      <c r="Q27" s="839" t="s">
         <v>147</v>
       </c>
-      <c r="R27" s="897"/>
-      <c r="S27" s="897"/>
-      <c r="T27" s="897"/>
-      <c r="U27" s="897"/>
-      <c r="V27" s="897"/>
-      <c r="W27" s="898"/>
+      <c r="R27" s="840"/>
+      <c r="S27" s="840"/>
+      <c r="T27" s="840"/>
+      <c r="U27" s="840"/>
+      <c r="V27" s="840"/>
+      <c r="W27" s="841"/>
       <c r="X27" s="381"/>
       <c r="Y27" s="373"/>
       <c r="Z27" s="221"/>
@@ -37037,11 +37037,11 @@
       <c r="Q29" s="374"/>
       <c r="R29" s="193"/>
       <c r="S29" s="193"/>
-      <c r="T29" s="899" t="s">
+      <c r="T29" s="844" t="s">
         <v>146</v>
       </c>
-      <c r="U29" s="900"/>
-      <c r="V29" s="901"/>
+      <c r="U29" s="845"/>
+      <c r="V29" s="846"/>
       <c r="W29" s="387"/>
       <c r="X29" s="374"/>
       <c r="Y29" s="193"/>
@@ -37072,29 +37072,29 @@
       <c r="M30" s="82"/>
       <c r="N30" s="82"/>
       <c r="O30" s="88"/>
-      <c r="Q30" s="827" t="s">
+      <c r="Q30" s="842" t="s">
         <v>50</v>
       </c>
-      <c r="R30" s="828"/>
-      <c r="S30" s="828"/>
-      <c r="T30" s="902"/>
-      <c r="U30" s="903"/>
-      <c r="V30" s="904"/>
-      <c r="W30" s="827" t="s">
+      <c r="R30" s="843"/>
+      <c r="S30" s="843"/>
+      <c r="T30" s="847"/>
+      <c r="U30" s="848"/>
+      <c r="V30" s="849"/>
+      <c r="W30" s="842" t="s">
         <v>51</v>
       </c>
-      <c r="X30" s="828"/>
-      <c r="Y30" s="828"/>
-      <c r="Z30" s="883" t="s">
+      <c r="X30" s="843"/>
+      <c r="Y30" s="843"/>
+      <c r="Z30" s="923" t="s">
         <v>52</v>
       </c>
-      <c r="AA30" s="828"/>
-      <c r="AB30" s="888"/>
-      <c r="AC30" s="883" t="s">
+      <c r="AA30" s="843"/>
+      <c r="AB30" s="932"/>
+      <c r="AC30" s="923" t="s">
         <v>53</v>
       </c>
-      <c r="AD30" s="828"/>
-      <c r="AE30" s="884"/>
+      <c r="AD30" s="843"/>
+      <c r="AE30" s="924"/>
       <c r="AF30" s="375"/>
       <c r="AG30" s="221"/>
       <c r="AH30" s="82"/>
@@ -37117,21 +37117,21 @@
       <c r="N31" s="82"/>
       <c r="O31" s="83"/>
       <c r="P31" s="103"/>
-      <c r="Q31" s="845"/>
-      <c r="R31" s="846"/>
-      <c r="S31" s="847"/>
-      <c r="T31" s="854"/>
-      <c r="U31" s="855"/>
-      <c r="V31" s="856"/>
-      <c r="W31" s="829"/>
-      <c r="X31" s="830"/>
-      <c r="Y31" s="830"/>
-      <c r="Z31" s="885"/>
-      <c r="AA31" s="886"/>
-      <c r="AB31" s="889"/>
-      <c r="AC31" s="885"/>
-      <c r="AD31" s="886"/>
-      <c r="AE31" s="887"/>
+      <c r="Q31" s="970"/>
+      <c r="R31" s="971"/>
+      <c r="S31" s="972"/>
+      <c r="T31" s="973"/>
+      <c r="U31" s="974"/>
+      <c r="V31" s="975"/>
+      <c r="W31" s="959"/>
+      <c r="X31" s="960"/>
+      <c r="Y31" s="960"/>
+      <c r="Z31" s="925"/>
+      <c r="AA31" s="926"/>
+      <c r="AB31" s="933"/>
+      <c r="AC31" s="925"/>
+      <c r="AD31" s="926"/>
+      <c r="AE31" s="927"/>
       <c r="AF31" s="376"/>
       <c r="AG31" s="82"/>
       <c r="AH31" s="82"/>
@@ -37154,21 +37154,21 @@
       <c r="N32" s="90"/>
       <c r="O32" s="83"/>
       <c r="P32" s="79"/>
-      <c r="Q32" s="848"/>
-      <c r="R32" s="849"/>
-      <c r="S32" s="850"/>
-      <c r="T32" s="838"/>
-      <c r="U32" s="839"/>
-      <c r="V32" s="840"/>
-      <c r="W32" s="831"/>
-      <c r="X32" s="832"/>
-      <c r="Y32" s="832"/>
-      <c r="Z32" s="868"/>
-      <c r="AA32" s="869"/>
-      <c r="AB32" s="880"/>
-      <c r="AC32" s="868"/>
-      <c r="AD32" s="869"/>
-      <c r="AE32" s="870"/>
+      <c r="Q32" s="910"/>
+      <c r="R32" s="911"/>
+      <c r="S32" s="912"/>
+      <c r="T32" s="920"/>
+      <c r="U32" s="921"/>
+      <c r="V32" s="922"/>
+      <c r="W32" s="918"/>
+      <c r="X32" s="919"/>
+      <c r="Y32" s="919"/>
+      <c r="Z32" s="928"/>
+      <c r="AA32" s="929"/>
+      <c r="AB32" s="934"/>
+      <c r="AC32" s="928"/>
+      <c r="AD32" s="929"/>
+      <c r="AE32" s="930"/>
       <c r="AF32" s="80"/>
       <c r="AG32" s="82"/>
       <c r="AH32" s="82"/>
@@ -37176,42 +37176,42 @@
     </row>
     <row r="33" spans="1:35" ht="19.5" thickBot="1">
       <c r="A33" s="224"/>
-      <c r="B33" s="819" t="s">
+      <c r="B33" s="939" t="s">
         <v>148</v>
       </c>
-      <c r="C33" s="861"/>
-      <c r="D33" s="861"/>
-      <c r="E33" s="820"/>
-      <c r="F33" s="816" t="s">
+      <c r="C33" s="940"/>
+      <c r="D33" s="940"/>
+      <c r="E33" s="941"/>
+      <c r="F33" s="986" t="s">
         <v>149</v>
       </c>
-      <c r="G33" s="817"/>
-      <c r="H33" s="817"/>
-      <c r="I33" s="817"/>
-      <c r="J33" s="817"/>
-      <c r="K33" s="817"/>
-      <c r="L33" s="818"/>
-      <c r="M33" s="819" t="s">
+      <c r="G33" s="987"/>
+      <c r="H33" s="987"/>
+      <c r="I33" s="987"/>
+      <c r="J33" s="987"/>
+      <c r="K33" s="987"/>
+      <c r="L33" s="988"/>
+      <c r="M33" s="939" t="s">
         <v>88</v>
       </c>
-      <c r="N33" s="820"/>
+      <c r="N33" s="941"/>
       <c r="O33" s="78"/>
       <c r="P33" s="103"/>
-      <c r="Q33" s="848"/>
-      <c r="R33" s="849"/>
-      <c r="S33" s="850"/>
-      <c r="T33" s="838"/>
-      <c r="U33" s="839"/>
-      <c r="V33" s="840"/>
-      <c r="W33" s="831"/>
-      <c r="X33" s="832"/>
-      <c r="Y33" s="832"/>
-      <c r="Z33" s="868"/>
-      <c r="AA33" s="869"/>
-      <c r="AB33" s="880"/>
-      <c r="AC33" s="868"/>
-      <c r="AD33" s="869"/>
-      <c r="AE33" s="870"/>
+      <c r="Q33" s="910"/>
+      <c r="R33" s="911"/>
+      <c r="S33" s="912"/>
+      <c r="T33" s="920"/>
+      <c r="U33" s="921"/>
+      <c r="V33" s="922"/>
+      <c r="W33" s="918"/>
+      <c r="X33" s="919"/>
+      <c r="Y33" s="919"/>
+      <c r="Z33" s="928"/>
+      <c r="AA33" s="929"/>
+      <c r="AB33" s="934"/>
+      <c r="AC33" s="928"/>
+      <c r="AD33" s="929"/>
+      <c r="AE33" s="930"/>
       <c r="AF33" s="80"/>
       <c r="AG33" s="82"/>
       <c r="AH33" s="82"/>
@@ -37219,42 +37219,42 @@
     </row>
     <row r="34" spans="1:35" ht="30.75" customHeight="1" thickBot="1">
       <c r="A34" s="226"/>
-      <c r="B34" s="821"/>
-      <c r="C34" s="862"/>
-      <c r="D34" s="862"/>
-      <c r="E34" s="822"/>
-      <c r="F34" s="863" t="s">
+      <c r="B34" s="942"/>
+      <c r="C34" s="943"/>
+      <c r="D34" s="943"/>
+      <c r="E34" s="944"/>
+      <c r="F34" s="945" t="s">
         <v>150</v>
       </c>
-      <c r="G34" s="864"/>
-      <c r="H34" s="865"/>
-      <c r="I34" s="866" t="s">
+      <c r="G34" s="946"/>
+      <c r="H34" s="947"/>
+      <c r="I34" s="948" t="s">
         <v>151</v>
       </c>
-      <c r="J34" s="867"/>
-      <c r="K34" s="814" t="s">
+      <c r="J34" s="949"/>
+      <c r="K34" s="984" t="s">
         <v>152</v>
       </c>
-      <c r="L34" s="815"/>
-      <c r="M34" s="821"/>
-      <c r="N34" s="822"/>
+      <c r="L34" s="985"/>
+      <c r="M34" s="942"/>
+      <c r="N34" s="944"/>
       <c r="O34" s="78"/>
       <c r="P34" s="103"/>
-      <c r="Q34" s="848"/>
-      <c r="R34" s="849"/>
-      <c r="S34" s="850"/>
-      <c r="T34" s="838"/>
-      <c r="U34" s="839"/>
-      <c r="V34" s="840"/>
-      <c r="W34" s="831"/>
-      <c r="X34" s="832"/>
-      <c r="Y34" s="832"/>
-      <c r="Z34" s="868"/>
-      <c r="AA34" s="869"/>
-      <c r="AB34" s="880"/>
-      <c r="AC34" s="868"/>
-      <c r="AD34" s="869"/>
-      <c r="AE34" s="870"/>
+      <c r="Q34" s="910"/>
+      <c r="R34" s="911"/>
+      <c r="S34" s="912"/>
+      <c r="T34" s="920"/>
+      <c r="U34" s="921"/>
+      <c r="V34" s="922"/>
+      <c r="W34" s="918"/>
+      <c r="X34" s="919"/>
+      <c r="Y34" s="919"/>
+      <c r="Z34" s="928"/>
+      <c r="AA34" s="929"/>
+      <c r="AB34" s="934"/>
+      <c r="AC34" s="928"/>
+      <c r="AD34" s="929"/>
+      <c r="AE34" s="930"/>
       <c r="AF34" s="80"/>
       <c r="AG34" s="82"/>
       <c r="AH34" s="82"/>
@@ -37262,46 +37262,46 @@
     </row>
     <row r="35" spans="1:35" ht="22.5" customHeight="1">
       <c r="A35" s="394"/>
-      <c r="B35" s="826" t="s">
+      <c r="B35" s="958" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="826"/>
-      <c r="D35" s="826"/>
-      <c r="E35" s="826"/>
-      <c r="F35" s="826">
+      <c r="C35" s="958"/>
+      <c r="D35" s="958"/>
+      <c r="E35" s="958"/>
+      <c r="F35" s="958">
         <v>4</v>
       </c>
-      <c r="G35" s="826"/>
-      <c r="H35" s="826"/>
-      <c r="I35" s="826">
+      <c r="G35" s="958"/>
+      <c r="H35" s="958"/>
+      <c r="I35" s="958">
         <v>10</v>
       </c>
-      <c r="J35" s="826"/>
-      <c r="K35" s="826">
+      <c r="J35" s="958"/>
+      <c r="K35" s="958">
         <v>0</v>
       </c>
-      <c r="L35" s="826"/>
-      <c r="M35" s="826">
+      <c r="L35" s="958"/>
+      <c r="M35" s="958">
         <v>20</v>
       </c>
-      <c r="N35" s="826"/>
+      <c r="N35" s="958"/>
       <c r="O35" s="83"/>
       <c r="P35" s="79"/>
-      <c r="Q35" s="851"/>
-      <c r="R35" s="852"/>
-      <c r="S35" s="853"/>
-      <c r="T35" s="823"/>
-      <c r="U35" s="824"/>
-      <c r="V35" s="825"/>
-      <c r="W35" s="812"/>
-      <c r="X35" s="813"/>
-      <c r="Y35" s="813"/>
-      <c r="Z35" s="871"/>
-      <c r="AA35" s="872"/>
-      <c r="AB35" s="878"/>
-      <c r="AC35" s="871"/>
-      <c r="AD35" s="872"/>
-      <c r="AE35" s="873"/>
+      <c r="Q35" s="907"/>
+      <c r="R35" s="908"/>
+      <c r="S35" s="909"/>
+      <c r="T35" s="913"/>
+      <c r="U35" s="914"/>
+      <c r="V35" s="915"/>
+      <c r="W35" s="916"/>
+      <c r="X35" s="917"/>
+      <c r="Y35" s="917"/>
+      <c r="Z35" s="901"/>
+      <c r="AA35" s="902"/>
+      <c r="AB35" s="931"/>
+      <c r="AC35" s="901"/>
+      <c r="AD35" s="902"/>
+      <c r="AE35" s="903"/>
       <c r="AF35" s="80"/>
       <c r="AG35" s="82"/>
       <c r="AH35" s="82"/>
@@ -37319,21 +37319,21 @@
       <c r="M36" s="389"/>
       <c r="N36" s="388"/>
       <c r="O36" s="90"/>
-      <c r="Q36" s="851"/>
-      <c r="R36" s="852"/>
-      <c r="S36" s="853"/>
-      <c r="T36" s="823"/>
-      <c r="U36" s="824"/>
-      <c r="V36" s="825"/>
-      <c r="W36" s="812"/>
-      <c r="X36" s="813"/>
-      <c r="Y36" s="813"/>
-      <c r="Z36" s="871"/>
-      <c r="AA36" s="872"/>
-      <c r="AB36" s="878"/>
-      <c r="AC36" s="871"/>
-      <c r="AD36" s="872"/>
-      <c r="AE36" s="873"/>
+      <c r="Q36" s="907"/>
+      <c r="R36" s="908"/>
+      <c r="S36" s="909"/>
+      <c r="T36" s="913"/>
+      <c r="U36" s="914"/>
+      <c r="V36" s="915"/>
+      <c r="W36" s="916"/>
+      <c r="X36" s="917"/>
+      <c r="Y36" s="917"/>
+      <c r="Z36" s="901"/>
+      <c r="AA36" s="902"/>
+      <c r="AB36" s="931"/>
+      <c r="AC36" s="901"/>
+      <c r="AD36" s="902"/>
+      <c r="AE36" s="903"/>
       <c r="AF36" s="80"/>
       <c r="AG36" s="82"/>
       <c r="AH36" s="82"/>
@@ -37356,21 +37356,21 @@
       <c r="N37" s="82"/>
       <c r="O37" s="80"/>
       <c r="P37" s="79"/>
-      <c r="Q37" s="851"/>
-      <c r="R37" s="852"/>
-      <c r="S37" s="853"/>
-      <c r="T37" s="823"/>
-      <c r="U37" s="824"/>
-      <c r="V37" s="825"/>
-      <c r="W37" s="812"/>
-      <c r="X37" s="813"/>
-      <c r="Y37" s="813"/>
-      <c r="Z37" s="871"/>
-      <c r="AA37" s="872"/>
-      <c r="AB37" s="878"/>
-      <c r="AC37" s="871"/>
-      <c r="AD37" s="872"/>
-      <c r="AE37" s="873"/>
+      <c r="Q37" s="907"/>
+      <c r="R37" s="908"/>
+      <c r="S37" s="909"/>
+      <c r="T37" s="913"/>
+      <c r="U37" s="914"/>
+      <c r="V37" s="915"/>
+      <c r="W37" s="916"/>
+      <c r="X37" s="917"/>
+      <c r="Y37" s="917"/>
+      <c r="Z37" s="901"/>
+      <c r="AA37" s="902"/>
+      <c r="AB37" s="931"/>
+      <c r="AC37" s="901"/>
+      <c r="AD37" s="902"/>
+      <c r="AE37" s="903"/>
       <c r="AF37" s="80"/>
       <c r="AG37" s="82"/>
       <c r="AH37" s="82"/>
@@ -37393,21 +37393,21 @@
       <c r="N38" s="82"/>
       <c r="O38" s="80"/>
       <c r="P38" s="79"/>
-      <c r="Q38" s="851"/>
-      <c r="R38" s="852"/>
-      <c r="S38" s="853"/>
-      <c r="T38" s="823"/>
-      <c r="U38" s="824"/>
-      <c r="V38" s="825"/>
-      <c r="W38" s="812"/>
-      <c r="X38" s="813"/>
-      <c r="Y38" s="813"/>
-      <c r="Z38" s="871"/>
-      <c r="AA38" s="872"/>
-      <c r="AB38" s="878"/>
-      <c r="AC38" s="871"/>
-      <c r="AD38" s="872"/>
-      <c r="AE38" s="873"/>
+      <c r="Q38" s="907"/>
+      <c r="R38" s="908"/>
+      <c r="S38" s="909"/>
+      <c r="T38" s="913"/>
+      <c r="U38" s="914"/>
+      <c r="V38" s="915"/>
+      <c r="W38" s="916"/>
+      <c r="X38" s="917"/>
+      <c r="Y38" s="917"/>
+      <c r="Z38" s="901"/>
+      <c r="AA38" s="902"/>
+      <c r="AB38" s="931"/>
+      <c r="AC38" s="901"/>
+      <c r="AD38" s="902"/>
+      <c r="AE38" s="903"/>
       <c r="AF38" s="105"/>
       <c r="AG38" s="104"/>
       <c r="AH38" s="82"/>
@@ -37429,21 +37429,21 @@
       <c r="M39" s="82"/>
       <c r="N39" s="82"/>
       <c r="P39" s="79"/>
-      <c r="Q39" s="851"/>
-      <c r="R39" s="852"/>
-      <c r="S39" s="853"/>
-      <c r="T39" s="823"/>
-      <c r="U39" s="824"/>
-      <c r="V39" s="825"/>
-      <c r="W39" s="812"/>
-      <c r="X39" s="813"/>
-      <c r="Y39" s="813"/>
-      <c r="Z39" s="871"/>
-      <c r="AA39" s="872"/>
-      <c r="AB39" s="878"/>
-      <c r="AC39" s="871"/>
-      <c r="AD39" s="872"/>
-      <c r="AE39" s="873"/>
+      <c r="Q39" s="907"/>
+      <c r="R39" s="908"/>
+      <c r="S39" s="909"/>
+      <c r="T39" s="913"/>
+      <c r="U39" s="914"/>
+      <c r="V39" s="915"/>
+      <c r="W39" s="916"/>
+      <c r="X39" s="917"/>
+      <c r="Y39" s="917"/>
+      <c r="Z39" s="901"/>
+      <c r="AA39" s="902"/>
+      <c r="AB39" s="931"/>
+      <c r="AC39" s="901"/>
+      <c r="AD39" s="902"/>
+      <c r="AE39" s="903"/>
       <c r="AF39" s="80"/>
       <c r="AG39" s="82"/>
       <c r="AH39" s="82"/>
@@ -37466,21 +37466,21 @@
       <c r="N40" s="82"/>
       <c r="O40" s="83"/>
       <c r="P40" s="87"/>
-      <c r="Q40" s="851"/>
-      <c r="R40" s="852"/>
-      <c r="S40" s="853"/>
-      <c r="T40" s="823"/>
-      <c r="U40" s="824"/>
-      <c r="V40" s="825"/>
-      <c r="W40" s="812"/>
-      <c r="X40" s="813"/>
-      <c r="Y40" s="813"/>
-      <c r="Z40" s="871"/>
-      <c r="AA40" s="872"/>
-      <c r="AB40" s="878"/>
-      <c r="AC40" s="871"/>
-      <c r="AD40" s="872"/>
-      <c r="AE40" s="873"/>
+      <c r="Q40" s="907"/>
+      <c r="R40" s="908"/>
+      <c r="S40" s="909"/>
+      <c r="T40" s="913"/>
+      <c r="U40" s="914"/>
+      <c r="V40" s="915"/>
+      <c r="W40" s="916"/>
+      <c r="X40" s="917"/>
+      <c r="Y40" s="917"/>
+      <c r="Z40" s="901"/>
+      <c r="AA40" s="902"/>
+      <c r="AB40" s="931"/>
+      <c r="AC40" s="901"/>
+      <c r="AD40" s="902"/>
+      <c r="AE40" s="903"/>
       <c r="AF40" s="80"/>
       <c r="AG40" s="82"/>
       <c r="AH40" s="82"/>
@@ -37503,21 +37503,21 @@
       <c r="N41" s="82"/>
       <c r="O41" s="78"/>
       <c r="P41" s="79"/>
-      <c r="Q41" s="848"/>
-      <c r="R41" s="849"/>
-      <c r="S41" s="850"/>
-      <c r="T41" s="838"/>
-      <c r="U41" s="839"/>
-      <c r="V41" s="840"/>
-      <c r="W41" s="831"/>
-      <c r="X41" s="832"/>
-      <c r="Y41" s="832"/>
-      <c r="Z41" s="868"/>
-      <c r="AA41" s="869"/>
-      <c r="AB41" s="880"/>
-      <c r="AC41" s="868"/>
-      <c r="AD41" s="869"/>
-      <c r="AE41" s="870"/>
+      <c r="Q41" s="910"/>
+      <c r="R41" s="911"/>
+      <c r="S41" s="912"/>
+      <c r="T41" s="920"/>
+      <c r="U41" s="921"/>
+      <c r="V41" s="922"/>
+      <c r="W41" s="918"/>
+      <c r="X41" s="919"/>
+      <c r="Y41" s="919"/>
+      <c r="Z41" s="928"/>
+      <c r="AA41" s="929"/>
+      <c r="AB41" s="934"/>
+      <c r="AC41" s="928"/>
+      <c r="AD41" s="929"/>
+      <c r="AE41" s="930"/>
       <c r="AF41" s="80"/>
       <c r="AG41" s="82"/>
       <c r="AH41" s="82"/>
@@ -37540,21 +37540,21 @@
       <c r="N42" s="82"/>
       <c r="O42" s="80"/>
       <c r="P42" s="79"/>
-      <c r="Q42" s="848"/>
-      <c r="R42" s="849"/>
-      <c r="S42" s="850"/>
-      <c r="T42" s="838"/>
-      <c r="U42" s="839"/>
-      <c r="V42" s="840"/>
-      <c r="W42" s="831"/>
-      <c r="X42" s="832"/>
-      <c r="Y42" s="832"/>
-      <c r="Z42" s="868"/>
-      <c r="AA42" s="869"/>
-      <c r="AB42" s="880"/>
-      <c r="AC42" s="868"/>
-      <c r="AD42" s="869"/>
-      <c r="AE42" s="870"/>
+      <c r="Q42" s="910"/>
+      <c r="R42" s="911"/>
+      <c r="S42" s="912"/>
+      <c r="T42" s="920"/>
+      <c r="U42" s="921"/>
+      <c r="V42" s="922"/>
+      <c r="W42" s="918"/>
+      <c r="X42" s="919"/>
+      <c r="Y42" s="919"/>
+      <c r="Z42" s="928"/>
+      <c r="AA42" s="929"/>
+      <c r="AB42" s="934"/>
+      <c r="AC42" s="928"/>
+      <c r="AD42" s="929"/>
+      <c r="AE42" s="930"/>
       <c r="AF42" s="80"/>
       <c r="AG42" s="82"/>
       <c r="AH42" s="82"/>
@@ -37576,21 +37576,21 @@
       <c r="M43" s="82"/>
       <c r="N43" s="82"/>
       <c r="P43" s="79"/>
-      <c r="Q43" s="890"/>
-      <c r="R43" s="891"/>
-      <c r="S43" s="892"/>
-      <c r="T43" s="823"/>
-      <c r="U43" s="824"/>
-      <c r="V43" s="825"/>
-      <c r="W43" s="812"/>
-      <c r="X43" s="813"/>
-      <c r="Y43" s="813"/>
-      <c r="Z43" s="871"/>
-      <c r="AA43" s="872"/>
-      <c r="AB43" s="878"/>
-      <c r="AC43" s="871"/>
-      <c r="AD43" s="872"/>
-      <c r="AE43" s="873"/>
+      <c r="Q43" s="904"/>
+      <c r="R43" s="905"/>
+      <c r="S43" s="906"/>
+      <c r="T43" s="913"/>
+      <c r="U43" s="914"/>
+      <c r="V43" s="915"/>
+      <c r="W43" s="916"/>
+      <c r="X43" s="917"/>
+      <c r="Y43" s="917"/>
+      <c r="Z43" s="901"/>
+      <c r="AA43" s="902"/>
+      <c r="AB43" s="931"/>
+      <c r="AC43" s="901"/>
+      <c r="AD43" s="902"/>
+      <c r="AE43" s="903"/>
       <c r="AF43" s="80"/>
       <c r="AG43" s="82"/>
       <c r="AH43" s="82"/>
@@ -37613,21 +37613,21 @@
       <c r="N44" s="82"/>
       <c r="O44" s="78"/>
       <c r="P44" s="103"/>
-      <c r="Q44" s="890"/>
-      <c r="R44" s="891"/>
-      <c r="S44" s="892"/>
-      <c r="T44" s="823"/>
-      <c r="U44" s="824"/>
-      <c r="V44" s="825"/>
-      <c r="W44" s="812"/>
-      <c r="X44" s="813"/>
-      <c r="Y44" s="813"/>
-      <c r="Z44" s="871"/>
-      <c r="AA44" s="872"/>
-      <c r="AB44" s="878"/>
-      <c r="AC44" s="871"/>
-      <c r="AD44" s="872"/>
-      <c r="AE44" s="873"/>
+      <c r="Q44" s="904"/>
+      <c r="R44" s="905"/>
+      <c r="S44" s="906"/>
+      <c r="T44" s="913"/>
+      <c r="U44" s="914"/>
+      <c r="V44" s="915"/>
+      <c r="W44" s="916"/>
+      <c r="X44" s="917"/>
+      <c r="Y44" s="917"/>
+      <c r="Z44" s="901"/>
+      <c r="AA44" s="902"/>
+      <c r="AB44" s="931"/>
+      <c r="AC44" s="901"/>
+      <c r="AD44" s="902"/>
+      <c r="AE44" s="903"/>
       <c r="AF44" s="80"/>
       <c r="AG44" s="82"/>
       <c r="AH44" s="82"/>
@@ -37650,21 +37650,21 @@
       <c r="N45" s="82"/>
       <c r="O45" s="83"/>
       <c r="P45" s="103"/>
-      <c r="Q45" s="806"/>
-      <c r="R45" s="807"/>
-      <c r="S45" s="808"/>
-      <c r="T45" s="842"/>
-      <c r="U45" s="843"/>
-      <c r="V45" s="844"/>
-      <c r="W45" s="881"/>
-      <c r="X45" s="882"/>
-      <c r="Y45" s="882"/>
-      <c r="Z45" s="874"/>
-      <c r="AA45" s="875"/>
-      <c r="AB45" s="879"/>
-      <c r="AC45" s="874"/>
-      <c r="AD45" s="875"/>
-      <c r="AE45" s="876"/>
+      <c r="Q45" s="979"/>
+      <c r="R45" s="980"/>
+      <c r="S45" s="981"/>
+      <c r="T45" s="967"/>
+      <c r="U45" s="968"/>
+      <c r="V45" s="969"/>
+      <c r="W45" s="956"/>
+      <c r="X45" s="957"/>
+      <c r="Y45" s="957"/>
+      <c r="Z45" s="950"/>
+      <c r="AA45" s="951"/>
+      <c r="AB45" s="955"/>
+      <c r="AC45" s="950"/>
+      <c r="AD45" s="951"/>
+      <c r="AE45" s="952"/>
       <c r="AF45" s="80"/>
       <c r="AG45" s="82"/>
       <c r="AH45" s="82"/>
@@ -37687,21 +37687,21 @@
       <c r="N46" s="82"/>
       <c r="O46" s="83"/>
       <c r="P46" s="103"/>
-      <c r="Q46" s="809"/>
-      <c r="R46" s="810"/>
-      <c r="S46" s="810"/>
-      <c r="T46" s="841"/>
-      <c r="U46" s="841"/>
-      <c r="V46" s="841"/>
-      <c r="W46" s="811"/>
-      <c r="X46" s="811"/>
-      <c r="Y46" s="811"/>
-      <c r="Z46" s="811"/>
-      <c r="AA46" s="811"/>
-      <c r="AB46" s="811"/>
-      <c r="AC46" s="811"/>
-      <c r="AD46" s="811"/>
-      <c r="AE46" s="877"/>
+      <c r="Q46" s="982"/>
+      <c r="R46" s="983"/>
+      <c r="S46" s="983"/>
+      <c r="T46" s="966"/>
+      <c r="U46" s="966"/>
+      <c r="V46" s="966"/>
+      <c r="W46" s="953"/>
+      <c r="X46" s="953"/>
+      <c r="Y46" s="953"/>
+      <c r="Z46" s="953"/>
+      <c r="AA46" s="953"/>
+      <c r="AB46" s="953"/>
+      <c r="AC46" s="953"/>
+      <c r="AD46" s="953"/>
+      <c r="AE46" s="954"/>
       <c r="AF46" s="80"/>
       <c r="AG46" s="82"/>
       <c r="AH46" s="82"/>
@@ -37724,21 +37724,21 @@
       <c r="N47" s="82"/>
       <c r="O47" s="83"/>
       <c r="P47" s="103"/>
-      <c r="Q47" s="803"/>
-      <c r="R47" s="804"/>
-      <c r="S47" s="805"/>
-      <c r="T47" s="833"/>
-      <c r="U47" s="834"/>
-      <c r="V47" s="835"/>
-      <c r="W47" s="836"/>
-      <c r="X47" s="837"/>
-      <c r="Y47" s="837"/>
-      <c r="Z47" s="857"/>
-      <c r="AA47" s="858"/>
-      <c r="AB47" s="859"/>
-      <c r="AC47" s="857"/>
-      <c r="AD47" s="858"/>
-      <c r="AE47" s="860"/>
+      <c r="Q47" s="976"/>
+      <c r="R47" s="977"/>
+      <c r="S47" s="978"/>
+      <c r="T47" s="961"/>
+      <c r="U47" s="962"/>
+      <c r="V47" s="963"/>
+      <c r="W47" s="964"/>
+      <c r="X47" s="965"/>
+      <c r="Y47" s="965"/>
+      <c r="Z47" s="935"/>
+      <c r="AA47" s="936"/>
+      <c r="AB47" s="937"/>
+      <c r="AC47" s="935"/>
+      <c r="AD47" s="936"/>
+      <c r="AE47" s="938"/>
       <c r="AF47" s="83"/>
       <c r="AG47" s="90"/>
       <c r="AH47" s="82"/>
@@ -38042,21 +38042,105 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F12:L13"/>
-    <mergeCell ref="M12:N15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B12:E15"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="W46:Y46"/>
+    <mergeCell ref="W38:Y38"/>
+    <mergeCell ref="W39:Y39"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="T36:V36"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="W30:Y30"/>
+    <mergeCell ref="W31:Y31"/>
+    <mergeCell ref="W32:Y32"/>
+    <mergeCell ref="T47:V47"/>
+    <mergeCell ref="W47:Y47"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="T46:V46"/>
+    <mergeCell ref="T45:V45"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="T31:V31"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="T35:V35"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="AC47:AE47"/>
+    <mergeCell ref="B33:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="AC41:AE41"/>
+    <mergeCell ref="AC42:AE42"/>
+    <mergeCell ref="AC43:AE43"/>
+    <mergeCell ref="AC44:AE44"/>
+    <mergeCell ref="AC45:AE45"/>
+    <mergeCell ref="AC46:AE46"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="Z46:AB46"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="Z43:AB43"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="W33:Y33"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="W35:Y35"/>
+    <mergeCell ref="W36:Y36"/>
+    <mergeCell ref="W37:Y37"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="AC33:AE33"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="Z31:AB31"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="AC38:AE38"/>
+    <mergeCell ref="AC39:AE39"/>
+    <mergeCell ref="AC40:AE40"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="W40:Y40"/>
+    <mergeCell ref="W41:Y41"/>
+    <mergeCell ref="W42:Y42"/>
+    <mergeCell ref="W43:Y43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="T44:V44"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="Q30:S30"/>
@@ -38081,105 +38165,21 @@
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="J17:L17"/>
     <mergeCell ref="M17:N17"/>
-    <mergeCell ref="AC40:AE40"/>
-    <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="W40:Y40"/>
-    <mergeCell ref="W41:Y41"/>
-    <mergeCell ref="W42:Y42"/>
-    <mergeCell ref="W43:Y43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="T42:V42"/>
-    <mergeCell ref="T43:V43"/>
-    <mergeCell ref="T44:V44"/>
-    <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="AC32:AE32"/>
-    <mergeCell ref="AC33:AE33"/>
-    <mergeCell ref="AC34:AE34"/>
-    <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="AC36:AE36"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="Z31:AB31"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="Z36:AB36"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="AC37:AE37"/>
-    <mergeCell ref="AC38:AE38"/>
-    <mergeCell ref="AC39:AE39"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="AC47:AE47"/>
-    <mergeCell ref="B33:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="AC41:AE41"/>
-    <mergeCell ref="AC42:AE42"/>
-    <mergeCell ref="AC43:AE43"/>
-    <mergeCell ref="AC44:AE44"/>
-    <mergeCell ref="AC45:AE45"/>
-    <mergeCell ref="AC46:AE46"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="Z45:AB45"/>
-    <mergeCell ref="Z46:AB46"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z42:AB42"/>
-    <mergeCell ref="Z43:AB43"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="W33:Y33"/>
-    <mergeCell ref="W34:Y34"/>
-    <mergeCell ref="W35:Y35"/>
-    <mergeCell ref="W36:Y36"/>
-    <mergeCell ref="W37:Y37"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="W30:Y30"/>
-    <mergeCell ref="W31:Y31"/>
-    <mergeCell ref="W32:Y32"/>
-    <mergeCell ref="T47:V47"/>
-    <mergeCell ref="W47:Y47"/>
-    <mergeCell ref="T41:V41"/>
-    <mergeCell ref="T46:V46"/>
-    <mergeCell ref="T45:V45"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="T31:V31"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="T34:V34"/>
-    <mergeCell ref="T35:V35"/>
-    <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="W46:Y46"/>
-    <mergeCell ref="W38:Y38"/>
-    <mergeCell ref="W39:Y39"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="F33:L33"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="T36:V36"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F12:L13"/>
+    <mergeCell ref="M12:N15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B12:E15"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J14:L15"/>
   </mergeCells>
   <conditionalFormatting sqref="S13:AF13">
     <cfRule type="cellIs" dxfId="26" priority="29" operator="greaterThanOrEqual">
@@ -38350,14 +38350,14 @@
       <c r="G2" s="364"/>
       <c r="H2" s="364"/>
       <c r="I2" s="364"/>
-      <c r="J2" s="548" t="s">
+      <c r="J2" s="558" t="s">
         <v>126</v>
       </c>
-      <c r="K2" s="548"/>
-      <c r="L2" s="548"/>
-      <c r="M2" s="548"/>
-      <c r="N2" s="548"/>
-      <c r="O2" s="548"/>
+      <c r="K2" s="558"/>
+      <c r="L2" s="558"/>
+      <c r="M2" s="558"/>
+      <c r="N2" s="558"/>
+      <c r="O2" s="558"/>
       <c r="P2" s="364"/>
       <c r="Q2" s="364"/>
       <c r="R2" s="364"/>
@@ -38398,14 +38398,14 @@
       <c r="I4" s="365" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="547" t="s">
+      <c r="J4" s="557" t="s">
         <v>125</v>
       </c>
-      <c r="K4" s="547"/>
-      <c r="L4" s="547"/>
-      <c r="M4" s="547"/>
-      <c r="N4" s="547"/>
-      <c r="O4" s="547"/>
+      <c r="K4" s="557"/>
+      <c r="L4" s="557"/>
+      <c r="M4" s="557"/>
+      <c r="N4" s="557"/>
+      <c r="O4" s="557"/>
       <c r="P4" s="366"/>
       <c r="Q4" s="366"/>
       <c r="R4" s="367"/>
@@ -38421,17 +38421,17 @@
       <c r="G5" s="368"/>
       <c r="H5" s="368"/>
       <c r="I5" s="369"/>
-      <c r="J5" s="558" t="s">
+      <c r="J5" s="550" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="558"/>
-      <c r="L5" s="558"/>
-      <c r="M5" s="558"/>
-      <c r="N5" s="555" t="s">
+      <c r="K5" s="550"/>
+      <c r="L5" s="550"/>
+      <c r="M5" s="550"/>
+      <c r="N5" s="562" t="s">
         <v>154</v>
       </c>
-      <c r="O5" s="555"/>
-      <c r="P5" s="555"/>
+      <c r="O5" s="562"/>
+      <c r="P5" s="562"/>
       <c r="Q5" s="370"/>
       <c r="R5" s="370"/>
       <c r="S5" s="22"/>
@@ -38462,12 +38462,12 @@
     </row>
     <row r="8" spans="1:19" ht="45.75" customHeight="1" thickBot="1">
       <c r="A8" s="23"/>
-      <c r="C8" s="559" t="str">
+      <c r="C8" s="553" t="str">
         <f>_xlfn.CONCAT("PERIODO ", N5)</f>
         <v>PERIODO ABRIL - 2025</v>
       </c>
-      <c r="D8" s="560"/>
-      <c r="E8" s="561"/>
+      <c r="D8" s="554"/>
+      <c r="E8" s="555"/>
       <c r="G8" s="56" t="s">
         <v>1</v>
       </c>
@@ -38510,11 +38510,11 @@
     </row>
     <row r="10" spans="1:19" ht="42" customHeight="1">
       <c r="A10" s="23"/>
-      <c r="C10" s="562" t="s">
+      <c r="C10" s="556" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="562"/>
-      <c r="E10" s="562"/>
+      <c r="D10" s="556"/>
+      <c r="E10" s="556"/>
       <c r="G10" s="76" t="s">
         <v>8</v>
       </c>
@@ -38664,11 +38664,11 @@
       <c r="C15" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="557">
+      <c r="D15" s="548">
         <f>R14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="557"/>
+      <c r="E15" s="548"/>
       <c r="H15" s="35"/>
       <c r="M15" s="35"/>
       <c r="N15" s="35"/>
@@ -38711,11 +38711,11 @@
     </row>
     <row r="24" spans="1:19" ht="50.25" customHeight="1">
       <c r="A24" s="23"/>
-      <c r="C24" s="550" t="s">
+      <c r="C24" s="559" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="551"/>
-      <c r="E24" s="552"/>
+      <c r="D24" s="560"/>
+      <c r="E24" s="561"/>
       <c r="S24" s="22"/>
     </row>
     <row r="25" spans="1:19" ht="32.25" customHeight="1">
@@ -38723,11 +38723,11 @@
       <c r="C25" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="553">
+      <c r="D25" s="551">
         <f>SUM(M13:O13)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="554"/>
+      <c r="E25" s="552"/>
       <c r="S25" s="22"/>
     </row>
     <row r="26" spans="1:19" ht="33.75" customHeight="1">
@@ -38735,11 +38735,11 @@
       <c r="C26" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="553">
+      <c r="D26" s="551">
         <f>SUM(M12:O12)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="554"/>
+      <c r="E26" s="552"/>
       <c r="S26" s="22"/>
     </row>
     <row r="27" spans="1:19" ht="38.25" customHeight="1">
@@ -38771,11 +38771,11 @@
       <c r="C29" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="556">
+      <c r="D29" s="547">
         <f>SUM(M14:O14)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="556"/>
+      <c r="E29" s="547"/>
       <c r="S29" s="22"/>
     </row>
     <row r="30" spans="1:19">
@@ -38889,6 +38889,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="N5:P5"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D27:E27"/>
@@ -38900,16 +38906,10 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="5" scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="50" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="51" max="18" man="1"/>
   </rowBreaks>
@@ -43677,9 +43677,9 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="602"/>
-      <c r="C1" s="603"/>
-      <c r="D1" s="604"/>
+      <c r="B1" s="609"/>
+      <c r="C1" s="610"/>
+      <c r="D1" s="611"/>
       <c r="E1" s="79"/>
       <c r="F1" s="82"/>
       <c r="G1" s="80"/>
@@ -43701,10 +43701,10 @@
       <c r="E2" s="88"/>
       <c r="G2" s="90"/>
       <c r="H2" s="82"/>
-      <c r="I2" s="615" t="s">
+      <c r="I2" s="605" t="s">
         <v>155</v>
       </c>
-      <c r="J2" s="616"/>
+      <c r="J2" s="606"/>
       <c r="K2" s="93"/>
       <c r="L2" s="82"/>
       <c r="M2" s="90"/>
@@ -43758,10 +43758,10 @@
       <c r="B5" s="363" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="608" t="s">
+      <c r="C5" s="612" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="609"/>
+      <c r="D5" s="613"/>
       <c r="E5" s="360" t="s">
         <v>60</v>
       </c>
@@ -43789,8 +43789,8 @@
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1">
       <c r="B6" s="209"/>
-      <c r="C6" s="610"/>
-      <c r="D6" s="611"/>
+      <c r="C6" s="614"/>
+      <c r="D6" s="615"/>
       <c r="E6" s="438"/>
       <c r="F6" s="438"/>
       <c r="G6" s="438"/>
@@ -43808,8 +43808,8 @@
     <row r="7" spans="1:17" ht="45.75" customHeight="1">
       <c r="A7" s="99"/>
       <c r="B7" s="210"/>
-      <c r="C7" s="612"/>
-      <c r="D7" s="613"/>
+      <c r="C7" s="616"/>
+      <c r="D7" s="617"/>
       <c r="E7" s="439"/>
       <c r="F7" s="439"/>
       <c r="G7" s="439"/>
@@ -43825,8 +43825,8 @@
     <row r="8" spans="1:17" ht="44.25" customHeight="1">
       <c r="A8" s="100"/>
       <c r="B8" s="210"/>
-      <c r="C8" s="612"/>
-      <c r="D8" s="613"/>
+      <c r="C8" s="616"/>
+      <c r="D8" s="617"/>
       <c r="E8" s="439"/>
       <c r="F8" s="439"/>
       <c r="G8" s="439"/>
@@ -43843,8 +43843,8 @@
     <row r="9" spans="1:17" ht="39.75" customHeight="1">
       <c r="A9" s="100"/>
       <c r="B9" s="210"/>
-      <c r="C9" s="612"/>
-      <c r="D9" s="613"/>
+      <c r="C9" s="616"/>
+      <c r="D9" s="617"/>
       <c r="E9" s="439"/>
       <c r="F9" s="439"/>
       <c r="G9" s="439"/>
@@ -43862,8 +43862,8 @@
     <row r="10" spans="1:17" ht="55.5" customHeight="1">
       <c r="A10" s="102"/>
       <c r="B10" s="210"/>
-      <c r="C10" s="612"/>
-      <c r="D10" s="613"/>
+      <c r="C10" s="616"/>
+      <c r="D10" s="617"/>
       <c r="E10" s="439"/>
       <c r="F10" s="439"/>
       <c r="G10" s="439"/>
@@ -43880,8 +43880,8 @@
     <row r="11" spans="1:17" ht="55.5" customHeight="1">
       <c r="A11" s="101"/>
       <c r="B11" s="210"/>
-      <c r="C11" s="612"/>
-      <c r="D11" s="614"/>
+      <c r="C11" s="616"/>
+      <c r="D11" s="618"/>
       <c r="E11" s="439"/>
       <c r="F11" s="439"/>
       <c r="G11" s="439"/>
@@ -43897,8 +43897,8 @@
     <row r="12" spans="1:17" ht="44.25" customHeight="1">
       <c r="A12" s="101"/>
       <c r="B12" s="210"/>
-      <c r="C12" s="612"/>
-      <c r="D12" s="613"/>
+      <c r="C12" s="616"/>
+      <c r="D12" s="617"/>
       <c r="E12" s="439"/>
       <c r="F12" s="439"/>
       <c r="G12" s="439"/>
@@ -43915,8 +43915,8 @@
     <row r="13" spans="1:17" ht="63" customHeight="1" thickBot="1">
       <c r="A13" s="100"/>
       <c r="B13" s="211"/>
-      <c r="C13" s="617"/>
-      <c r="D13" s="618"/>
+      <c r="C13" s="607"/>
+      <c r="D13" s="608"/>
       <c r="E13" s="440"/>
       <c r="F13" s="440"/>
       <c r="G13" s="440"/>
@@ -43976,12 +43976,12 @@
       </c>
       <c r="C16" s="447"/>
       <c r="D16" s="284"/>
-      <c r="E16" s="605"/>
-      <c r="F16" s="606"/>
-      <c r="G16" s="606"/>
-      <c r="H16" s="606"/>
-      <c r="I16" s="606"/>
-      <c r="J16" s="607"/>
+      <c r="E16" s="602"/>
+      <c r="F16" s="603"/>
+      <c r="G16" s="603"/>
+      <c r="H16" s="603"/>
+      <c r="I16" s="603"/>
+      <c r="J16" s="604"/>
       <c r="K16" s="291"/>
       <c r="L16" s="115"/>
       <c r="M16" s="113"/>
@@ -43995,12 +43995,12 @@
       </c>
       <c r="C17" s="449"/>
       <c r="D17" s="284"/>
-      <c r="E17" s="605"/>
-      <c r="F17" s="606"/>
-      <c r="G17" s="606"/>
-      <c r="H17" s="606"/>
-      <c r="I17" s="606"/>
-      <c r="J17" s="607"/>
+      <c r="E17" s="602"/>
+      <c r="F17" s="603"/>
+      <c r="G17" s="603"/>
+      <c r="H17" s="603"/>
+      <c r="I17" s="603"/>
+      <c r="J17" s="604"/>
       <c r="K17" s="136"/>
       <c r="L17" s="123"/>
       <c r="M17" s="115"/>
@@ -44015,12 +44015,12 @@
       </c>
       <c r="C18" s="449"/>
       <c r="D18" s="285"/>
-      <c r="E18" s="605"/>
-      <c r="F18" s="606"/>
-      <c r="G18" s="606"/>
-      <c r="H18" s="606"/>
-      <c r="I18" s="606"/>
-      <c r="J18" s="607"/>
+      <c r="E18" s="602"/>
+      <c r="F18" s="603"/>
+      <c r="G18" s="603"/>
+      <c r="H18" s="603"/>
+      <c r="I18" s="603"/>
+      <c r="J18" s="604"/>
       <c r="L18" s="115"/>
       <c r="M18" s="111"/>
       <c r="N18" s="110"/>
@@ -44032,12 +44032,12 @@
       <c r="B19" s="87"/>
       <c r="C19" s="87"/>
       <c r="D19" s="286"/>
-      <c r="E19" s="605"/>
-      <c r="F19" s="606"/>
-      <c r="G19" s="606"/>
-      <c r="H19" s="606"/>
-      <c r="I19" s="606"/>
-      <c r="J19" s="607"/>
+      <c r="E19" s="602"/>
+      <c r="F19" s="603"/>
+      <c r="G19" s="603"/>
+      <c r="H19" s="603"/>
+      <c r="I19" s="603"/>
+      <c r="J19" s="604"/>
       <c r="K19" s="136"/>
       <c r="L19" s="123"/>
       <c r="M19" s="111"/>
@@ -44049,12 +44049,12 @@
       <c r="A20" s="79"/>
       <c r="B20" s="90"/>
       <c r="D20" s="285"/>
-      <c r="E20" s="605"/>
-      <c r="F20" s="606"/>
-      <c r="G20" s="606"/>
-      <c r="H20" s="606"/>
-      <c r="I20" s="606"/>
-      <c r="J20" s="607"/>
+      <c r="E20" s="602"/>
+      <c r="F20" s="603"/>
+      <c r="G20" s="603"/>
+      <c r="H20" s="603"/>
+      <c r="I20" s="603"/>
+      <c r="J20" s="604"/>
       <c r="K20" s="292"/>
       <c r="L20" s="287"/>
       <c r="M20" s="114"/>
@@ -44064,12 +44064,12 @@
     <row r="21" spans="1:16" ht="84.75" customHeight="1" thickBot="1">
       <c r="B21" s="90"/>
       <c r="D21" s="285"/>
-      <c r="E21" s="605"/>
-      <c r="F21" s="606"/>
-      <c r="G21" s="606"/>
-      <c r="H21" s="606"/>
-      <c r="I21" s="606"/>
-      <c r="J21" s="607"/>
+      <c r="E21" s="602"/>
+      <c r="F21" s="603"/>
+      <c r="G21" s="603"/>
+      <c r="H21" s="603"/>
+      <c r="I21" s="603"/>
+      <c r="J21" s="604"/>
       <c r="K21" s="292"/>
       <c r="L21" s="58"/>
       <c r="M21" s="114"/>
@@ -44080,12 +44080,12 @@
       <c r="B22" s="221"/>
       <c r="C22" s="222"/>
       <c r="D22" s="285"/>
-      <c r="E22" s="605"/>
-      <c r="F22" s="606"/>
-      <c r="G22" s="606"/>
-      <c r="H22" s="606"/>
-      <c r="I22" s="606"/>
-      <c r="J22" s="607"/>
+      <c r="E22" s="602"/>
+      <c r="F22" s="603"/>
+      <c r="G22" s="603"/>
+      <c r="H22" s="603"/>
+      <c r="I22" s="603"/>
+      <c r="J22" s="604"/>
       <c r="K22" s="293"/>
       <c r="L22" s="58"/>
       <c r="M22" s="112"/>
@@ -44503,14 +44503,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="E21:J21"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E18:J18"/>
     <mergeCell ref="C5:D5"/>
@@ -44521,6 +44513,14 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E20:J20"/>
+    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="E21:J21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -44541,6 +44541,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="dd0678842d65e4207392abd035356b9c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d84746cc30da1fe182e7a313d44b54c" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -44795,15 +44804,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83E8CA1-0683-49D4-9501-EE88776F2630}">
   <ds:schemaRefs>
@@ -44822,6 +44822,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE64779-B9F2-4AEC-A5E9-E8076DA89A71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -44838,12 +44846,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6AC9645-B568-450E-BF2C-C54CDA88D1C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B6B6C8-9ED8-4B7A-8D02-CB699EC0B708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAF7192-60B9-4711-8C50-761B1DA6ED59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Convenios ADP_II" sheetId="54" state="hidden" r:id="rId10"/>
     <sheet name="Gestión de riesgos" sheetId="48" r:id="rId11"/>
     <sheet name="data_riesgos" sheetId="49" state="hidden" r:id="rId12"/>
-    <sheet name="Planes de tratamientos" sheetId="55" r:id="rId13"/>
+    <sheet name="Planes de tratamientos" sheetId="55" state="hidden" r:id="rId13"/>
     <sheet name="Planes tratamientos" sheetId="53" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames>
@@ -9270,6 +9270,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9277,7 +9278,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9663,6 +9663,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9670,7 +9671,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9883,6 +9883,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9890,7 +9891,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10103,6 +10103,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10110,7 +10111,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10676,6 +10676,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10683,7 +10684,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11013,6 +11013,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11020,7 +11021,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11342,6 +11342,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11349,7 +11350,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11685,6 +11685,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11692,7 +11693,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12871,6 +12871,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -12878,7 +12879,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -14048,6 +14048,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -14055,7 +14056,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15002,6 +15002,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -15009,7 +15010,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -15526,6 +15526,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -15533,7 +15534,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15890,6 +15890,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -15897,7 +15898,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -25550,7 +25550,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382782"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382922"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25615,7 +25615,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382783"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382923"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25732,7 +25732,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s382784"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s382924"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25797,7 +25797,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s382785"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s382925"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25862,7 +25862,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s382786"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s382926"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25927,7 +25927,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s382787"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s382927"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25992,7 +25992,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s382788"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s382928"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26057,7 +26057,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s382789"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s382929"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26122,7 +26122,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s382790"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s382930"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26187,7 +26187,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s382791"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s382931"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -38909,7 +38909,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="5" scale="50" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="51" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="51" max="18" man="1"/>
   </rowBreaks>

--- a/Backend/Input/format_reports/formato.xlsx
+++ b/Backend/Input/format_reports/formato.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAF7192-60B9-4711-8C50-761B1DA6ED59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC7EBB6-E908-4A87-A2A5-8D8280959CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="719" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="52" r:id="rId1"/>
@@ -25550,7 +25550,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382922"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s394286"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25615,7 +25615,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s382923"/>
+                  <a14:cameraTool cellRange="data_status_NC!#REF!" spid="_x0000_s394287"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25732,7 +25732,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s382924"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$6:$C$10" spid="_x0000_s394288"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25797,7 +25797,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s382925"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$11:$C$14" spid="_x0000_s394289"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25862,7 +25862,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s382926"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$15:$C$18" spid="_x0000_s394290"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25927,7 +25927,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s382927"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$19:$C$26" spid="_x0000_s394291"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -25992,7 +25992,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s382928"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$27:$C$32" spid="_x0000_s394292"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26057,7 +26057,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s382929"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$33:$C$39" spid="_x0000_s394293"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26122,7 +26122,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s382930"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$40:$C$46" spid="_x0000_s394294"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -26187,7 +26187,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s382931"/>
+                  <a14:cameraTool cellRange="data_status_NC!$B$3:$C$5" spid="_x0000_s394295"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
